--- a/Journals/Angular ჟურნალი.xlsx
+++ b/Journals/Angular ჟურნალი.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\411\Desktop\12-2024 - web\0 -docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\411\Desktop\12-2024 - web\Mermisi-main\Journals\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -542,38 +542,26 @@
     <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="2" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -603,7 +591,16 @@
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -626,14 +623,17 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -896,28 +896,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="38"/>
-      <c r="F1" s="50">
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="34"/>
+      <c r="F1" s="49">
         <v>4</v>
       </c>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="50">
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="49">
         <v>4</v>
       </c>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="23"/>
-      <c r="O1" s="23"/>
-      <c r="P1" s="23"/>
-      <c r="Q1" s="23"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="49">
+        <v>4</v>
+      </c>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="51"/>
       <c r="R1" s="23"/>
       <c r="S1" s="23"/>
       <c r="T1" s="23"/>
@@ -1027,1305 +1029,1313 @@
       <c r="DT1" s="24"/>
       <c r="DU1" s="1">
         <f>SUM(F1:DT1)</f>
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:125" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="39"/>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="42" t="s">
+      <c r="A2" s="35"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="27">
+      <c r="F2" s="25">
         <v>46276</v>
       </c>
-      <c r="G2" s="27">
+      <c r="G2" s="25">
         <v>46276</v>
       </c>
-      <c r="H2" s="27">
+      <c r="H2" s="25">
         <v>46276</v>
       </c>
-      <c r="I2" s="27">
+      <c r="I2" s="25">
         <v>46276</v>
       </c>
-      <c r="J2" s="27">
+      <c r="J2" s="25">
         <v>46283</v>
       </c>
-      <c r="K2" s="27">
+      <c r="K2" s="25">
         <v>46283</v>
       </c>
-      <c r="L2" s="27">
+      <c r="L2" s="25">
         <v>46283</v>
       </c>
-      <c r="M2" s="27">
+      <c r="M2" s="25">
         <v>46283</v>
       </c>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="27"/>
-      <c r="R2" s="27"/>
-      <c r="S2" s="27"/>
-      <c r="T2" s="27"/>
-      <c r="U2" s="27"/>
-      <c r="V2" s="27"/>
-      <c r="W2" s="27"/>
-      <c r="X2" s="27"/>
-      <c r="Y2" s="27"/>
-      <c r="Z2" s="27"/>
-      <c r="AA2" s="27"/>
-      <c r="AB2" s="27"/>
-      <c r="AC2" s="27"/>
-      <c r="AD2" s="27"/>
-      <c r="AE2" s="27"/>
-      <c r="AF2" s="27"/>
-      <c r="AG2" s="27"/>
-      <c r="AH2" s="27"/>
-      <c r="AI2" s="27"/>
-      <c r="AJ2" s="27"/>
-      <c r="AK2" s="27"/>
-      <c r="AL2" s="27"/>
-      <c r="AM2" s="27"/>
-      <c r="AN2" s="27"/>
-      <c r="AO2" s="27"/>
-      <c r="AP2" s="27"/>
-      <c r="AQ2" s="27"/>
-      <c r="AR2" s="27"/>
-      <c r="AS2" s="27"/>
-      <c r="AT2" s="27"/>
-      <c r="AU2" s="27"/>
-      <c r="AV2" s="27"/>
-      <c r="AW2" s="27"/>
-      <c r="AX2" s="27"/>
-      <c r="AY2" s="27"/>
-      <c r="AZ2" s="27"/>
-      <c r="BA2" s="27"/>
-      <c r="BB2" s="27"/>
-      <c r="BC2" s="27"/>
-      <c r="BD2" s="27"/>
-      <c r="BE2" s="27"/>
-      <c r="BF2" s="27"/>
-      <c r="BG2" s="27"/>
-      <c r="BH2" s="27"/>
-      <c r="BI2" s="27"/>
-      <c r="BJ2" s="27"/>
-      <c r="BK2" s="27"/>
-      <c r="BL2" s="27"/>
-      <c r="BM2" s="27"/>
-      <c r="BN2" s="27"/>
-      <c r="BO2" s="27"/>
-      <c r="BP2" s="27"/>
-      <c r="BQ2" s="27"/>
-      <c r="BR2" s="27"/>
-      <c r="BS2" s="27"/>
-      <c r="BT2" s="27"/>
-      <c r="BU2" s="27"/>
-      <c r="BV2" s="27"/>
-      <c r="BW2" s="27"/>
-      <c r="BX2" s="27"/>
-      <c r="BY2" s="27"/>
-      <c r="BZ2" s="27"/>
-      <c r="CA2" s="27"/>
-      <c r="CB2" s="27"/>
-      <c r="CC2" s="27"/>
-      <c r="CD2" s="27"/>
-      <c r="CE2" s="27"/>
-      <c r="CF2" s="27"/>
-      <c r="CG2" s="27"/>
-      <c r="CH2" s="27"/>
-      <c r="CI2" s="27"/>
-      <c r="CJ2" s="27"/>
-      <c r="CK2" s="27"/>
-      <c r="CL2" s="27"/>
-      <c r="CM2" s="27"/>
-      <c r="CN2" s="27"/>
-      <c r="CO2" s="27"/>
-      <c r="CP2" s="27"/>
-      <c r="CQ2" s="27"/>
-      <c r="CR2" s="27"/>
-      <c r="CS2" s="27"/>
-      <c r="CT2" s="27"/>
-      <c r="CU2" s="27"/>
-      <c r="CV2" s="27"/>
-      <c r="CW2" s="27"/>
-      <c r="CX2" s="27"/>
-      <c r="CY2" s="27"/>
-      <c r="CZ2" s="27"/>
-      <c r="DA2" s="27"/>
-      <c r="DB2" s="27"/>
-      <c r="DC2" s="27"/>
-      <c r="DD2" s="27"/>
-      <c r="DE2" s="27"/>
-      <c r="DF2" s="27"/>
-      <c r="DG2" s="27"/>
-      <c r="DH2" s="27"/>
-      <c r="DI2" s="27"/>
-      <c r="DJ2" s="27"/>
-      <c r="DK2" s="27"/>
-      <c r="DL2" s="27"/>
-      <c r="DM2" s="27"/>
-      <c r="DN2" s="27"/>
-      <c r="DO2" s="27"/>
-      <c r="DP2" s="27"/>
-      <c r="DQ2" s="27"/>
-      <c r="DR2" s="27"/>
-      <c r="DS2" s="27"/>
-      <c r="DT2" s="27"/>
+      <c r="N2" s="25">
+        <v>46290</v>
+      </c>
+      <c r="O2" s="25">
+        <v>46290</v>
+      </c>
+      <c r="P2" s="25">
+        <v>46290</v>
+      </c>
+      <c r="Q2" s="25">
+        <v>46290</v>
+      </c>
+      <c r="R2" s="25"/>
+      <c r="S2" s="25"/>
+      <c r="T2" s="25"/>
+      <c r="U2" s="25"/>
+      <c r="V2" s="25"/>
+      <c r="W2" s="25"/>
+      <c r="X2" s="25"/>
+      <c r="Y2" s="25"/>
+      <c r="Z2" s="25"/>
+      <c r="AA2" s="25"/>
+      <c r="AB2" s="25"/>
+      <c r="AC2" s="25"/>
+      <c r="AD2" s="25"/>
+      <c r="AE2" s="25"/>
+      <c r="AF2" s="25"/>
+      <c r="AG2" s="25"/>
+      <c r="AH2" s="25"/>
+      <c r="AI2" s="25"/>
+      <c r="AJ2" s="25"/>
+      <c r="AK2" s="25"/>
+      <c r="AL2" s="25"/>
+      <c r="AM2" s="25"/>
+      <c r="AN2" s="25"/>
+      <c r="AO2" s="25"/>
+      <c r="AP2" s="25"/>
+      <c r="AQ2" s="25"/>
+      <c r="AR2" s="25"/>
+      <c r="AS2" s="25"/>
+      <c r="AT2" s="25"/>
+      <c r="AU2" s="25"/>
+      <c r="AV2" s="25"/>
+      <c r="AW2" s="25"/>
+      <c r="AX2" s="25"/>
+      <c r="AY2" s="25"/>
+      <c r="AZ2" s="25"/>
+      <c r="BA2" s="25"/>
+      <c r="BB2" s="25"/>
+      <c r="BC2" s="25"/>
+      <c r="BD2" s="25"/>
+      <c r="BE2" s="25"/>
+      <c r="BF2" s="25"/>
+      <c r="BG2" s="25"/>
+      <c r="BH2" s="25"/>
+      <c r="BI2" s="25"/>
+      <c r="BJ2" s="25"/>
+      <c r="BK2" s="25"/>
+      <c r="BL2" s="25"/>
+      <c r="BM2" s="25"/>
+      <c r="BN2" s="25"/>
+      <c r="BO2" s="25"/>
+      <c r="BP2" s="25"/>
+      <c r="BQ2" s="25"/>
+      <c r="BR2" s="25"/>
+      <c r="BS2" s="25"/>
+      <c r="BT2" s="25"/>
+      <c r="BU2" s="25"/>
+      <c r="BV2" s="25"/>
+      <c r="BW2" s="25"/>
+      <c r="BX2" s="25"/>
+      <c r="BY2" s="25"/>
+      <c r="BZ2" s="25"/>
+      <c r="CA2" s="25"/>
+      <c r="CB2" s="25"/>
+      <c r="CC2" s="25"/>
+      <c r="CD2" s="25"/>
+      <c r="CE2" s="25"/>
+      <c r="CF2" s="25"/>
+      <c r="CG2" s="25"/>
+      <c r="CH2" s="25"/>
+      <c r="CI2" s="25"/>
+      <c r="CJ2" s="25"/>
+      <c r="CK2" s="25"/>
+      <c r="CL2" s="25"/>
+      <c r="CM2" s="25"/>
+      <c r="CN2" s="25"/>
+      <c r="CO2" s="25"/>
+      <c r="CP2" s="25"/>
+      <c r="CQ2" s="25"/>
+      <c r="CR2" s="25"/>
+      <c r="CS2" s="25"/>
+      <c r="CT2" s="25"/>
+      <c r="CU2" s="25"/>
+      <c r="CV2" s="25"/>
+      <c r="CW2" s="25"/>
+      <c r="CX2" s="25"/>
+      <c r="CY2" s="25"/>
+      <c r="CZ2" s="25"/>
+      <c r="DA2" s="25"/>
+      <c r="DB2" s="25"/>
+      <c r="DC2" s="25"/>
+      <c r="DD2" s="25"/>
+      <c r="DE2" s="25"/>
+      <c r="DF2" s="25"/>
+      <c r="DG2" s="25"/>
+      <c r="DH2" s="25"/>
+      <c r="DI2" s="25"/>
+      <c r="DJ2" s="25"/>
+      <c r="DK2" s="25"/>
+      <c r="DL2" s="25"/>
+      <c r="DM2" s="25"/>
+      <c r="DN2" s="25"/>
+      <c r="DO2" s="25"/>
+      <c r="DP2" s="25"/>
+      <c r="DQ2" s="25"/>
+      <c r="DR2" s="25"/>
+      <c r="DS2" s="25"/>
+      <c r="DT2" s="25"/>
     </row>
     <row r="3" spans="1:125" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="33"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="27"/>
-      <c r="K3" s="27"/>
-      <c r="L3" s="27"/>
-      <c r="M3" s="27"/>
-      <c r="N3" s="27"/>
-      <c r="O3" s="27"/>
-      <c r="P3" s="27"/>
-      <c r="Q3" s="27"/>
-      <c r="R3" s="27"/>
-      <c r="S3" s="27"/>
-      <c r="T3" s="27"/>
-      <c r="U3" s="27"/>
-      <c r="V3" s="27"/>
-      <c r="W3" s="27"/>
-      <c r="X3" s="27"/>
-      <c r="Y3" s="27"/>
-      <c r="Z3" s="27"/>
-      <c r="AA3" s="27"/>
-      <c r="AB3" s="27"/>
-      <c r="AC3" s="27"/>
-      <c r="AD3" s="27"/>
-      <c r="AE3" s="27"/>
-      <c r="AF3" s="27"/>
-      <c r="AG3" s="27"/>
-      <c r="AH3" s="27"/>
-      <c r="AI3" s="27"/>
-      <c r="AJ3" s="27"/>
-      <c r="AK3" s="27"/>
-      <c r="AL3" s="27"/>
-      <c r="AM3" s="27"/>
-      <c r="AN3" s="27"/>
-      <c r="AO3" s="27"/>
-      <c r="AP3" s="27"/>
-      <c r="AQ3" s="27"/>
-      <c r="AR3" s="27"/>
-      <c r="AS3" s="27"/>
-      <c r="AT3" s="27"/>
-      <c r="AU3" s="27"/>
-      <c r="AV3" s="27"/>
-      <c r="AW3" s="27"/>
-      <c r="AX3" s="27"/>
-      <c r="AY3" s="27"/>
-      <c r="AZ3" s="27"/>
-      <c r="BA3" s="27"/>
-      <c r="BB3" s="27"/>
-      <c r="BC3" s="27"/>
-      <c r="BD3" s="27"/>
-      <c r="BE3" s="27"/>
-      <c r="BF3" s="27"/>
-      <c r="BG3" s="27"/>
-      <c r="BH3" s="27"/>
-      <c r="BI3" s="27"/>
-      <c r="BJ3" s="27"/>
-      <c r="BK3" s="27"/>
-      <c r="BL3" s="27"/>
-      <c r="BM3" s="27"/>
-      <c r="BN3" s="27"/>
-      <c r="BO3" s="27"/>
-      <c r="BP3" s="27"/>
-      <c r="BQ3" s="27"/>
-      <c r="BR3" s="27"/>
-      <c r="BS3" s="27"/>
-      <c r="BT3" s="27"/>
-      <c r="BU3" s="27"/>
-      <c r="BV3" s="27"/>
-      <c r="BW3" s="27"/>
-      <c r="BX3" s="27"/>
-      <c r="BY3" s="27"/>
-      <c r="BZ3" s="27"/>
-      <c r="CA3" s="27"/>
-      <c r="CB3" s="27"/>
-      <c r="CC3" s="27"/>
-      <c r="CD3" s="27"/>
-      <c r="CE3" s="27"/>
-      <c r="CF3" s="27"/>
-      <c r="CG3" s="27"/>
-      <c r="CH3" s="27"/>
-      <c r="CI3" s="27"/>
-      <c r="CJ3" s="27"/>
-      <c r="CK3" s="27"/>
-      <c r="CL3" s="27"/>
-      <c r="CM3" s="27"/>
-      <c r="CN3" s="27"/>
-      <c r="CO3" s="27"/>
-      <c r="CP3" s="27"/>
-      <c r="CQ3" s="27"/>
-      <c r="CR3" s="27"/>
-      <c r="CS3" s="27"/>
-      <c r="CT3" s="27"/>
-      <c r="CU3" s="27"/>
-      <c r="CV3" s="27"/>
-      <c r="CW3" s="27"/>
-      <c r="CX3" s="27"/>
-      <c r="CY3" s="27"/>
-      <c r="CZ3" s="27"/>
-      <c r="DA3" s="27"/>
-      <c r="DB3" s="27"/>
-      <c r="DC3" s="27"/>
-      <c r="DD3" s="27"/>
-      <c r="DE3" s="27"/>
-      <c r="DF3" s="27"/>
-      <c r="DG3" s="27"/>
-      <c r="DH3" s="27"/>
-      <c r="DI3" s="27"/>
-      <c r="DJ3" s="27"/>
-      <c r="DK3" s="27"/>
-      <c r="DL3" s="27"/>
-      <c r="DM3" s="27"/>
-      <c r="DN3" s="27"/>
-      <c r="DO3" s="27"/>
-      <c r="DP3" s="27"/>
-      <c r="DQ3" s="27"/>
-      <c r="DR3" s="27"/>
-      <c r="DS3" s="27"/>
-      <c r="DT3" s="27"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="25"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25"/>
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25"/>
+      <c r="R3" s="25"/>
+      <c r="S3" s="25"/>
+      <c r="T3" s="25"/>
+      <c r="U3" s="25"/>
+      <c r="V3" s="25"/>
+      <c r="W3" s="25"/>
+      <c r="X3" s="25"/>
+      <c r="Y3" s="25"/>
+      <c r="Z3" s="25"/>
+      <c r="AA3" s="25"/>
+      <c r="AB3" s="25"/>
+      <c r="AC3" s="25"/>
+      <c r="AD3" s="25"/>
+      <c r="AE3" s="25"/>
+      <c r="AF3" s="25"/>
+      <c r="AG3" s="25"/>
+      <c r="AH3" s="25"/>
+      <c r="AI3" s="25"/>
+      <c r="AJ3" s="25"/>
+      <c r="AK3" s="25"/>
+      <c r="AL3" s="25"/>
+      <c r="AM3" s="25"/>
+      <c r="AN3" s="25"/>
+      <c r="AO3" s="25"/>
+      <c r="AP3" s="25"/>
+      <c r="AQ3" s="25"/>
+      <c r="AR3" s="25"/>
+      <c r="AS3" s="25"/>
+      <c r="AT3" s="25"/>
+      <c r="AU3" s="25"/>
+      <c r="AV3" s="25"/>
+      <c r="AW3" s="25"/>
+      <c r="AX3" s="25"/>
+      <c r="AY3" s="25"/>
+      <c r="AZ3" s="25"/>
+      <c r="BA3" s="25"/>
+      <c r="BB3" s="25"/>
+      <c r="BC3" s="25"/>
+      <c r="BD3" s="25"/>
+      <c r="BE3" s="25"/>
+      <c r="BF3" s="25"/>
+      <c r="BG3" s="25"/>
+      <c r="BH3" s="25"/>
+      <c r="BI3" s="25"/>
+      <c r="BJ3" s="25"/>
+      <c r="BK3" s="25"/>
+      <c r="BL3" s="25"/>
+      <c r="BM3" s="25"/>
+      <c r="BN3" s="25"/>
+      <c r="BO3" s="25"/>
+      <c r="BP3" s="25"/>
+      <c r="BQ3" s="25"/>
+      <c r="BR3" s="25"/>
+      <c r="BS3" s="25"/>
+      <c r="BT3" s="25"/>
+      <c r="BU3" s="25"/>
+      <c r="BV3" s="25"/>
+      <c r="BW3" s="25"/>
+      <c r="BX3" s="25"/>
+      <c r="BY3" s="25"/>
+      <c r="BZ3" s="25"/>
+      <c r="CA3" s="25"/>
+      <c r="CB3" s="25"/>
+      <c r="CC3" s="25"/>
+      <c r="CD3" s="25"/>
+      <c r="CE3" s="25"/>
+      <c r="CF3" s="25"/>
+      <c r="CG3" s="25"/>
+      <c r="CH3" s="25"/>
+      <c r="CI3" s="25"/>
+      <c r="CJ3" s="25"/>
+      <c r="CK3" s="25"/>
+      <c r="CL3" s="25"/>
+      <c r="CM3" s="25"/>
+      <c r="CN3" s="25"/>
+      <c r="CO3" s="25"/>
+      <c r="CP3" s="25"/>
+      <c r="CQ3" s="25"/>
+      <c r="CR3" s="25"/>
+      <c r="CS3" s="25"/>
+      <c r="CT3" s="25"/>
+      <c r="CU3" s="25"/>
+      <c r="CV3" s="25"/>
+      <c r="CW3" s="25"/>
+      <c r="CX3" s="25"/>
+      <c r="CY3" s="25"/>
+      <c r="CZ3" s="25"/>
+      <c r="DA3" s="25"/>
+      <c r="DB3" s="25"/>
+      <c r="DC3" s="25"/>
+      <c r="DD3" s="25"/>
+      <c r="DE3" s="25"/>
+      <c r="DF3" s="25"/>
+      <c r="DG3" s="25"/>
+      <c r="DH3" s="25"/>
+      <c r="DI3" s="25"/>
+      <c r="DJ3" s="25"/>
+      <c r="DK3" s="25"/>
+      <c r="DL3" s="25"/>
+      <c r="DM3" s="25"/>
+      <c r="DN3" s="25"/>
+      <c r="DO3" s="25"/>
+      <c r="DP3" s="25"/>
+      <c r="DQ3" s="25"/>
+      <c r="DR3" s="25"/>
+      <c r="DS3" s="25"/>
+      <c r="DT3" s="25"/>
     </row>
     <row r="4" spans="1:125" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="30" t="s">
+      <c r="A4" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="42"/>
+      <c r="C4" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="32"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="27"/>
-      <c r="L4" s="27"/>
-      <c r="M4" s="27"/>
-      <c r="N4" s="27"/>
-      <c r="O4" s="27"/>
-      <c r="P4" s="27"/>
-      <c r="Q4" s="27"/>
-      <c r="R4" s="27"/>
-      <c r="S4" s="27"/>
-      <c r="T4" s="27"/>
-      <c r="U4" s="27"/>
-      <c r="V4" s="27"/>
-      <c r="W4" s="27"/>
-      <c r="X4" s="27"/>
-      <c r="Y4" s="27"/>
-      <c r="Z4" s="27"/>
-      <c r="AA4" s="27"/>
-      <c r="AB4" s="27"/>
-      <c r="AC4" s="27"/>
-      <c r="AD4" s="27"/>
-      <c r="AE4" s="27"/>
-      <c r="AF4" s="27"/>
-      <c r="AG4" s="27"/>
-      <c r="AH4" s="27"/>
-      <c r="AI4" s="27"/>
-      <c r="AJ4" s="27"/>
-      <c r="AK4" s="27"/>
-      <c r="AL4" s="27"/>
-      <c r="AM4" s="27"/>
-      <c r="AN4" s="27"/>
-      <c r="AO4" s="27"/>
-      <c r="AP4" s="27"/>
-      <c r="AQ4" s="27"/>
-      <c r="AR4" s="27"/>
-      <c r="AS4" s="27"/>
-      <c r="AT4" s="27"/>
-      <c r="AU4" s="27"/>
-      <c r="AV4" s="27"/>
-      <c r="AW4" s="27"/>
-      <c r="AX4" s="27"/>
-      <c r="AY4" s="27"/>
-      <c r="AZ4" s="27"/>
-      <c r="BA4" s="27"/>
-      <c r="BB4" s="27"/>
-      <c r="BC4" s="27"/>
-      <c r="BD4" s="27"/>
-      <c r="BE4" s="27"/>
-      <c r="BF4" s="27"/>
-      <c r="BG4" s="27"/>
-      <c r="BH4" s="27"/>
-      <c r="BI4" s="27"/>
-      <c r="BJ4" s="27"/>
-      <c r="BK4" s="27"/>
-      <c r="BL4" s="27"/>
-      <c r="BM4" s="27"/>
-      <c r="BN4" s="27"/>
-      <c r="BO4" s="27"/>
-      <c r="BP4" s="27"/>
-      <c r="BQ4" s="27"/>
-      <c r="BR4" s="27"/>
-      <c r="BS4" s="27"/>
-      <c r="BT4" s="27"/>
-      <c r="BU4" s="27"/>
-      <c r="BV4" s="27"/>
-      <c r="BW4" s="27"/>
-      <c r="BX4" s="27"/>
-      <c r="BY4" s="27"/>
-      <c r="BZ4" s="27"/>
-      <c r="CA4" s="27"/>
-      <c r="CB4" s="27"/>
-      <c r="CC4" s="27"/>
-      <c r="CD4" s="27"/>
-      <c r="CE4" s="27"/>
-      <c r="CF4" s="27"/>
-      <c r="CG4" s="27"/>
-      <c r="CH4" s="27"/>
-      <c r="CI4" s="27"/>
-      <c r="CJ4" s="27"/>
-      <c r="CK4" s="27"/>
-      <c r="CL4" s="27"/>
-      <c r="CM4" s="27"/>
-      <c r="CN4" s="27"/>
-      <c r="CO4" s="27"/>
-      <c r="CP4" s="27"/>
-      <c r="CQ4" s="27"/>
-      <c r="CR4" s="27"/>
-      <c r="CS4" s="27"/>
-      <c r="CT4" s="27"/>
-      <c r="CU4" s="27"/>
-      <c r="CV4" s="27"/>
-      <c r="CW4" s="27"/>
-      <c r="CX4" s="27"/>
-      <c r="CY4" s="27"/>
-      <c r="CZ4" s="27"/>
-      <c r="DA4" s="27"/>
-      <c r="DB4" s="27"/>
-      <c r="DC4" s="27"/>
-      <c r="DD4" s="27"/>
-      <c r="DE4" s="27"/>
-      <c r="DF4" s="27"/>
-      <c r="DG4" s="27"/>
-      <c r="DH4" s="27"/>
-      <c r="DI4" s="27"/>
-      <c r="DJ4" s="27"/>
-      <c r="DK4" s="27"/>
-      <c r="DL4" s="27"/>
-      <c r="DM4" s="27"/>
-      <c r="DN4" s="27"/>
-      <c r="DO4" s="27"/>
-      <c r="DP4" s="27"/>
-      <c r="DQ4" s="27"/>
-      <c r="DR4" s="27"/>
-      <c r="DS4" s="27"/>
-      <c r="DT4" s="27"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
+      <c r="N4" s="25"/>
+      <c r="O4" s="25"/>
+      <c r="P4" s="25"/>
+      <c r="Q4" s="25"/>
+      <c r="R4" s="25"/>
+      <c r="S4" s="25"/>
+      <c r="T4" s="25"/>
+      <c r="U4" s="25"/>
+      <c r="V4" s="25"/>
+      <c r="W4" s="25"/>
+      <c r="X4" s="25"/>
+      <c r="Y4" s="25"/>
+      <c r="Z4" s="25"/>
+      <c r="AA4" s="25"/>
+      <c r="AB4" s="25"/>
+      <c r="AC4" s="25"/>
+      <c r="AD4" s="25"/>
+      <c r="AE4" s="25"/>
+      <c r="AF4" s="25"/>
+      <c r="AG4" s="25"/>
+      <c r="AH4" s="25"/>
+      <c r="AI4" s="25"/>
+      <c r="AJ4" s="25"/>
+      <c r="AK4" s="25"/>
+      <c r="AL4" s="25"/>
+      <c r="AM4" s="25"/>
+      <c r="AN4" s="25"/>
+      <c r="AO4" s="25"/>
+      <c r="AP4" s="25"/>
+      <c r="AQ4" s="25"/>
+      <c r="AR4" s="25"/>
+      <c r="AS4" s="25"/>
+      <c r="AT4" s="25"/>
+      <c r="AU4" s="25"/>
+      <c r="AV4" s="25"/>
+      <c r="AW4" s="25"/>
+      <c r="AX4" s="25"/>
+      <c r="AY4" s="25"/>
+      <c r="AZ4" s="25"/>
+      <c r="BA4" s="25"/>
+      <c r="BB4" s="25"/>
+      <c r="BC4" s="25"/>
+      <c r="BD4" s="25"/>
+      <c r="BE4" s="25"/>
+      <c r="BF4" s="25"/>
+      <c r="BG4" s="25"/>
+      <c r="BH4" s="25"/>
+      <c r="BI4" s="25"/>
+      <c r="BJ4" s="25"/>
+      <c r="BK4" s="25"/>
+      <c r="BL4" s="25"/>
+      <c r="BM4" s="25"/>
+      <c r="BN4" s="25"/>
+      <c r="BO4" s="25"/>
+      <c r="BP4" s="25"/>
+      <c r="BQ4" s="25"/>
+      <c r="BR4" s="25"/>
+      <c r="BS4" s="25"/>
+      <c r="BT4" s="25"/>
+      <c r="BU4" s="25"/>
+      <c r="BV4" s="25"/>
+      <c r="BW4" s="25"/>
+      <c r="BX4" s="25"/>
+      <c r="BY4" s="25"/>
+      <c r="BZ4" s="25"/>
+      <c r="CA4" s="25"/>
+      <c r="CB4" s="25"/>
+      <c r="CC4" s="25"/>
+      <c r="CD4" s="25"/>
+      <c r="CE4" s="25"/>
+      <c r="CF4" s="25"/>
+      <c r="CG4" s="25"/>
+      <c r="CH4" s="25"/>
+      <c r="CI4" s="25"/>
+      <c r="CJ4" s="25"/>
+      <c r="CK4" s="25"/>
+      <c r="CL4" s="25"/>
+      <c r="CM4" s="25"/>
+      <c r="CN4" s="25"/>
+      <c r="CO4" s="25"/>
+      <c r="CP4" s="25"/>
+      <c r="CQ4" s="25"/>
+      <c r="CR4" s="25"/>
+      <c r="CS4" s="25"/>
+      <c r="CT4" s="25"/>
+      <c r="CU4" s="25"/>
+      <c r="CV4" s="25"/>
+      <c r="CW4" s="25"/>
+      <c r="CX4" s="25"/>
+      <c r="CY4" s="25"/>
+      <c r="CZ4" s="25"/>
+      <c r="DA4" s="25"/>
+      <c r="DB4" s="25"/>
+      <c r="DC4" s="25"/>
+      <c r="DD4" s="25"/>
+      <c r="DE4" s="25"/>
+      <c r="DF4" s="25"/>
+      <c r="DG4" s="25"/>
+      <c r="DH4" s="25"/>
+      <c r="DI4" s="25"/>
+      <c r="DJ4" s="25"/>
+      <c r="DK4" s="25"/>
+      <c r="DL4" s="25"/>
+      <c r="DM4" s="25"/>
+      <c r="DN4" s="25"/>
+      <c r="DO4" s="25"/>
+      <c r="DP4" s="25"/>
+      <c r="DQ4" s="25"/>
+      <c r="DR4" s="25"/>
+      <c r="DS4" s="25"/>
+      <c r="DT4" s="25"/>
     </row>
     <row r="5" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="47">
+      <c r="B5" s="45"/>
+      <c r="C5" s="46">
         <v>60</v>
       </c>
-      <c r="D5" s="48"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27"/>
-      <c r="K5" s="27"/>
-      <c r="L5" s="27"/>
-      <c r="M5" s="27"/>
-      <c r="N5" s="27"/>
-      <c r="O5" s="27"/>
-      <c r="P5" s="27"/>
-      <c r="Q5" s="27"/>
-      <c r="R5" s="27"/>
-      <c r="S5" s="27"/>
-      <c r="T5" s="27"/>
-      <c r="U5" s="27"/>
-      <c r="V5" s="27"/>
-      <c r="W5" s="27"/>
-      <c r="X5" s="27"/>
-      <c r="Y5" s="27"/>
-      <c r="Z5" s="27"/>
-      <c r="AA5" s="27"/>
-      <c r="AB5" s="27"/>
-      <c r="AC5" s="27"/>
-      <c r="AD5" s="27"/>
-      <c r="AE5" s="27"/>
-      <c r="AF5" s="27"/>
-      <c r="AG5" s="27"/>
-      <c r="AH5" s="27"/>
-      <c r="AI5" s="27"/>
-      <c r="AJ5" s="27"/>
-      <c r="AK5" s="27"/>
-      <c r="AL5" s="27"/>
-      <c r="AM5" s="27"/>
-      <c r="AN5" s="27"/>
-      <c r="AO5" s="27"/>
-      <c r="AP5" s="27"/>
-      <c r="AQ5" s="27"/>
-      <c r="AR5" s="27"/>
-      <c r="AS5" s="27"/>
-      <c r="AT5" s="27"/>
-      <c r="AU5" s="27"/>
-      <c r="AV5" s="27"/>
-      <c r="AW5" s="27"/>
-      <c r="AX5" s="27"/>
-      <c r="AY5" s="27"/>
-      <c r="AZ5" s="27"/>
-      <c r="BA5" s="27"/>
-      <c r="BB5" s="27"/>
-      <c r="BC5" s="27"/>
-      <c r="BD5" s="27"/>
-      <c r="BE5" s="27"/>
-      <c r="BF5" s="27"/>
-      <c r="BG5" s="27"/>
-      <c r="BH5" s="27"/>
-      <c r="BI5" s="27"/>
-      <c r="BJ5" s="27"/>
-      <c r="BK5" s="27"/>
-      <c r="BL5" s="27"/>
-      <c r="BM5" s="27"/>
-      <c r="BN5" s="27"/>
-      <c r="BO5" s="27"/>
-      <c r="BP5" s="27"/>
-      <c r="BQ5" s="27"/>
-      <c r="BR5" s="27"/>
-      <c r="BS5" s="27"/>
-      <c r="BT5" s="27"/>
-      <c r="BU5" s="27"/>
-      <c r="BV5" s="27"/>
-      <c r="BW5" s="27"/>
-      <c r="BX5" s="27"/>
-      <c r="BY5" s="27"/>
-      <c r="BZ5" s="27"/>
-      <c r="CA5" s="27"/>
-      <c r="CB5" s="27"/>
-      <c r="CC5" s="27"/>
-      <c r="CD5" s="27"/>
-      <c r="CE5" s="27"/>
-      <c r="CF5" s="27"/>
-      <c r="CG5" s="27"/>
-      <c r="CH5" s="27"/>
-      <c r="CI5" s="27"/>
-      <c r="CJ5" s="27"/>
-      <c r="CK5" s="27"/>
-      <c r="CL5" s="27"/>
-      <c r="CM5" s="27"/>
-      <c r="CN5" s="27"/>
-      <c r="CO5" s="27"/>
-      <c r="CP5" s="27"/>
-      <c r="CQ5" s="27"/>
-      <c r="CR5" s="27"/>
-      <c r="CS5" s="27"/>
-      <c r="CT5" s="27"/>
-      <c r="CU5" s="27"/>
-      <c r="CV5" s="27"/>
-      <c r="CW5" s="27"/>
-      <c r="CX5" s="27"/>
-      <c r="CY5" s="27"/>
-      <c r="CZ5" s="27"/>
-      <c r="DA5" s="27"/>
-      <c r="DB5" s="27"/>
-      <c r="DC5" s="27"/>
-      <c r="DD5" s="27"/>
-      <c r="DE5" s="27"/>
-      <c r="DF5" s="27"/>
-      <c r="DG5" s="27"/>
-      <c r="DH5" s="27"/>
-      <c r="DI5" s="27"/>
-      <c r="DJ5" s="27"/>
-      <c r="DK5" s="27"/>
-      <c r="DL5" s="27"/>
-      <c r="DM5" s="27"/>
-      <c r="DN5" s="27"/>
-      <c r="DO5" s="27"/>
-      <c r="DP5" s="27"/>
-      <c r="DQ5" s="27"/>
-      <c r="DR5" s="27"/>
-      <c r="DS5" s="27"/>
-      <c r="DT5" s="27"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
+      <c r="M5" s="25"/>
+      <c r="N5" s="25"/>
+      <c r="O5" s="25"/>
+      <c r="P5" s="25"/>
+      <c r="Q5" s="25"/>
+      <c r="R5" s="25"/>
+      <c r="S5" s="25"/>
+      <c r="T5" s="25"/>
+      <c r="U5" s="25"/>
+      <c r="V5" s="25"/>
+      <c r="W5" s="25"/>
+      <c r="X5" s="25"/>
+      <c r="Y5" s="25"/>
+      <c r="Z5" s="25"/>
+      <c r="AA5" s="25"/>
+      <c r="AB5" s="25"/>
+      <c r="AC5" s="25"/>
+      <c r="AD5" s="25"/>
+      <c r="AE5" s="25"/>
+      <c r="AF5" s="25"/>
+      <c r="AG5" s="25"/>
+      <c r="AH5" s="25"/>
+      <c r="AI5" s="25"/>
+      <c r="AJ5" s="25"/>
+      <c r="AK5" s="25"/>
+      <c r="AL5" s="25"/>
+      <c r="AM5" s="25"/>
+      <c r="AN5" s="25"/>
+      <c r="AO5" s="25"/>
+      <c r="AP5" s="25"/>
+      <c r="AQ5" s="25"/>
+      <c r="AR5" s="25"/>
+      <c r="AS5" s="25"/>
+      <c r="AT5" s="25"/>
+      <c r="AU5" s="25"/>
+      <c r="AV5" s="25"/>
+      <c r="AW5" s="25"/>
+      <c r="AX5" s="25"/>
+      <c r="AY5" s="25"/>
+      <c r="AZ5" s="25"/>
+      <c r="BA5" s="25"/>
+      <c r="BB5" s="25"/>
+      <c r="BC5" s="25"/>
+      <c r="BD5" s="25"/>
+      <c r="BE5" s="25"/>
+      <c r="BF5" s="25"/>
+      <c r="BG5" s="25"/>
+      <c r="BH5" s="25"/>
+      <c r="BI5" s="25"/>
+      <c r="BJ5" s="25"/>
+      <c r="BK5" s="25"/>
+      <c r="BL5" s="25"/>
+      <c r="BM5" s="25"/>
+      <c r="BN5" s="25"/>
+      <c r="BO5" s="25"/>
+      <c r="BP5" s="25"/>
+      <c r="BQ5" s="25"/>
+      <c r="BR5" s="25"/>
+      <c r="BS5" s="25"/>
+      <c r="BT5" s="25"/>
+      <c r="BU5" s="25"/>
+      <c r="BV5" s="25"/>
+      <c r="BW5" s="25"/>
+      <c r="BX5" s="25"/>
+      <c r="BY5" s="25"/>
+      <c r="BZ5" s="25"/>
+      <c r="CA5" s="25"/>
+      <c r="CB5" s="25"/>
+      <c r="CC5" s="25"/>
+      <c r="CD5" s="25"/>
+      <c r="CE5" s="25"/>
+      <c r="CF5" s="25"/>
+      <c r="CG5" s="25"/>
+      <c r="CH5" s="25"/>
+      <c r="CI5" s="25"/>
+      <c r="CJ5" s="25"/>
+      <c r="CK5" s="25"/>
+      <c r="CL5" s="25"/>
+      <c r="CM5" s="25"/>
+      <c r="CN5" s="25"/>
+      <c r="CO5" s="25"/>
+      <c r="CP5" s="25"/>
+      <c r="CQ5" s="25"/>
+      <c r="CR5" s="25"/>
+      <c r="CS5" s="25"/>
+      <c r="CT5" s="25"/>
+      <c r="CU5" s="25"/>
+      <c r="CV5" s="25"/>
+      <c r="CW5" s="25"/>
+      <c r="CX5" s="25"/>
+      <c r="CY5" s="25"/>
+      <c r="CZ5" s="25"/>
+      <c r="DA5" s="25"/>
+      <c r="DB5" s="25"/>
+      <c r="DC5" s="25"/>
+      <c r="DD5" s="25"/>
+      <c r="DE5" s="25"/>
+      <c r="DF5" s="25"/>
+      <c r="DG5" s="25"/>
+      <c r="DH5" s="25"/>
+      <c r="DI5" s="25"/>
+      <c r="DJ5" s="25"/>
+      <c r="DK5" s="25"/>
+      <c r="DL5" s="25"/>
+      <c r="DM5" s="25"/>
+      <c r="DN5" s="25"/>
+      <c r="DO5" s="25"/>
+      <c r="DP5" s="25"/>
+      <c r="DQ5" s="25"/>
+      <c r="DR5" s="25"/>
+      <c r="DS5" s="25"/>
+      <c r="DT5" s="25"/>
     </row>
     <row r="6" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="46" t="s">
+      <c r="A6" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="46"/>
-      <c r="C6" s="47">
+      <c r="B6" s="45"/>
+      <c r="C6" s="46">
         <v>4</v>
       </c>
-      <c r="D6" s="48"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27"/>
-      <c r="I6" s="27"/>
-      <c r="J6" s="27"/>
-      <c r="K6" s="27"/>
-      <c r="L6" s="27"/>
-      <c r="M6" s="27"/>
-      <c r="N6" s="27"/>
-      <c r="O6" s="27"/>
-      <c r="P6" s="27"/>
-      <c r="Q6" s="27"/>
-      <c r="R6" s="27"/>
-      <c r="S6" s="27"/>
-      <c r="T6" s="27"/>
-      <c r="U6" s="27"/>
-      <c r="V6" s="27"/>
-      <c r="W6" s="27"/>
-      <c r="X6" s="27"/>
-      <c r="Y6" s="27"/>
-      <c r="Z6" s="27"/>
-      <c r="AA6" s="27"/>
-      <c r="AB6" s="27"/>
-      <c r="AC6" s="27"/>
-      <c r="AD6" s="27"/>
-      <c r="AE6" s="27"/>
-      <c r="AF6" s="27"/>
-      <c r="AG6" s="27"/>
-      <c r="AH6" s="27"/>
-      <c r="AI6" s="27"/>
-      <c r="AJ6" s="27"/>
-      <c r="AK6" s="27"/>
-      <c r="AL6" s="27"/>
-      <c r="AM6" s="27"/>
-      <c r="AN6" s="27"/>
-      <c r="AO6" s="27"/>
-      <c r="AP6" s="27"/>
-      <c r="AQ6" s="27"/>
-      <c r="AR6" s="27"/>
-      <c r="AS6" s="27"/>
-      <c r="AT6" s="27"/>
-      <c r="AU6" s="27"/>
-      <c r="AV6" s="27"/>
-      <c r="AW6" s="27"/>
-      <c r="AX6" s="27"/>
-      <c r="AY6" s="27"/>
-      <c r="AZ6" s="27"/>
-      <c r="BA6" s="27"/>
-      <c r="BB6" s="27"/>
-      <c r="BC6" s="27"/>
-      <c r="BD6" s="27"/>
-      <c r="BE6" s="27"/>
-      <c r="BF6" s="27"/>
-      <c r="BG6" s="27"/>
-      <c r="BH6" s="27"/>
-      <c r="BI6" s="27"/>
-      <c r="BJ6" s="27"/>
-      <c r="BK6" s="27"/>
-      <c r="BL6" s="27"/>
-      <c r="BM6" s="27"/>
-      <c r="BN6" s="27"/>
-      <c r="BO6" s="27"/>
-      <c r="BP6" s="27"/>
-      <c r="BQ6" s="27"/>
-      <c r="BR6" s="27"/>
-      <c r="BS6" s="27"/>
-      <c r="BT6" s="27"/>
-      <c r="BU6" s="27"/>
-      <c r="BV6" s="27"/>
-      <c r="BW6" s="27"/>
-      <c r="BX6" s="27"/>
-      <c r="BY6" s="27"/>
-      <c r="BZ6" s="27"/>
-      <c r="CA6" s="27"/>
-      <c r="CB6" s="27"/>
-      <c r="CC6" s="27"/>
-      <c r="CD6" s="27"/>
-      <c r="CE6" s="27"/>
-      <c r="CF6" s="27"/>
-      <c r="CG6" s="27"/>
-      <c r="CH6" s="27"/>
-      <c r="CI6" s="27"/>
-      <c r="CJ6" s="27"/>
-      <c r="CK6" s="27"/>
-      <c r="CL6" s="27"/>
-      <c r="CM6" s="27"/>
-      <c r="CN6" s="27"/>
-      <c r="CO6" s="27"/>
-      <c r="CP6" s="27"/>
-      <c r="CQ6" s="27"/>
-      <c r="CR6" s="27"/>
-      <c r="CS6" s="27"/>
-      <c r="CT6" s="27"/>
-      <c r="CU6" s="27"/>
-      <c r="CV6" s="27"/>
-      <c r="CW6" s="27"/>
-      <c r="CX6" s="27"/>
-      <c r="CY6" s="27"/>
-      <c r="CZ6" s="27"/>
-      <c r="DA6" s="27"/>
-      <c r="DB6" s="27"/>
-      <c r="DC6" s="27"/>
-      <c r="DD6" s="27"/>
-      <c r="DE6" s="27"/>
-      <c r="DF6" s="27"/>
-      <c r="DG6" s="27"/>
-      <c r="DH6" s="27"/>
-      <c r="DI6" s="27"/>
-      <c r="DJ6" s="27"/>
-      <c r="DK6" s="27"/>
-      <c r="DL6" s="27"/>
-      <c r="DM6" s="27"/>
-      <c r="DN6" s="27"/>
-      <c r="DO6" s="27"/>
-      <c r="DP6" s="27"/>
-      <c r="DQ6" s="27"/>
-      <c r="DR6" s="27"/>
-      <c r="DS6" s="27"/>
-      <c r="DT6" s="27"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="25"/>
+      <c r="M6" s="25"/>
+      <c r="N6" s="25"/>
+      <c r="O6" s="25"/>
+      <c r="P6" s="25"/>
+      <c r="Q6" s="25"/>
+      <c r="R6" s="25"/>
+      <c r="S6" s="25"/>
+      <c r="T6" s="25"/>
+      <c r="U6" s="25"/>
+      <c r="V6" s="25"/>
+      <c r="W6" s="25"/>
+      <c r="X6" s="25"/>
+      <c r="Y6" s="25"/>
+      <c r="Z6" s="25"/>
+      <c r="AA6" s="25"/>
+      <c r="AB6" s="25"/>
+      <c r="AC6" s="25"/>
+      <c r="AD6" s="25"/>
+      <c r="AE6" s="25"/>
+      <c r="AF6" s="25"/>
+      <c r="AG6" s="25"/>
+      <c r="AH6" s="25"/>
+      <c r="AI6" s="25"/>
+      <c r="AJ6" s="25"/>
+      <c r="AK6" s="25"/>
+      <c r="AL6" s="25"/>
+      <c r="AM6" s="25"/>
+      <c r="AN6" s="25"/>
+      <c r="AO6" s="25"/>
+      <c r="AP6" s="25"/>
+      <c r="AQ6" s="25"/>
+      <c r="AR6" s="25"/>
+      <c r="AS6" s="25"/>
+      <c r="AT6" s="25"/>
+      <c r="AU6" s="25"/>
+      <c r="AV6" s="25"/>
+      <c r="AW6" s="25"/>
+      <c r="AX6" s="25"/>
+      <c r="AY6" s="25"/>
+      <c r="AZ6" s="25"/>
+      <c r="BA6" s="25"/>
+      <c r="BB6" s="25"/>
+      <c r="BC6" s="25"/>
+      <c r="BD6" s="25"/>
+      <c r="BE6" s="25"/>
+      <c r="BF6" s="25"/>
+      <c r="BG6" s="25"/>
+      <c r="BH6" s="25"/>
+      <c r="BI6" s="25"/>
+      <c r="BJ6" s="25"/>
+      <c r="BK6" s="25"/>
+      <c r="BL6" s="25"/>
+      <c r="BM6" s="25"/>
+      <c r="BN6" s="25"/>
+      <c r="BO6" s="25"/>
+      <c r="BP6" s="25"/>
+      <c r="BQ6" s="25"/>
+      <c r="BR6" s="25"/>
+      <c r="BS6" s="25"/>
+      <c r="BT6" s="25"/>
+      <c r="BU6" s="25"/>
+      <c r="BV6" s="25"/>
+      <c r="BW6" s="25"/>
+      <c r="BX6" s="25"/>
+      <c r="BY6" s="25"/>
+      <c r="BZ6" s="25"/>
+      <c r="CA6" s="25"/>
+      <c r="CB6" s="25"/>
+      <c r="CC6" s="25"/>
+      <c r="CD6" s="25"/>
+      <c r="CE6" s="25"/>
+      <c r="CF6" s="25"/>
+      <c r="CG6" s="25"/>
+      <c r="CH6" s="25"/>
+      <c r="CI6" s="25"/>
+      <c r="CJ6" s="25"/>
+      <c r="CK6" s="25"/>
+      <c r="CL6" s="25"/>
+      <c r="CM6" s="25"/>
+      <c r="CN6" s="25"/>
+      <c r="CO6" s="25"/>
+      <c r="CP6" s="25"/>
+      <c r="CQ6" s="25"/>
+      <c r="CR6" s="25"/>
+      <c r="CS6" s="25"/>
+      <c r="CT6" s="25"/>
+      <c r="CU6" s="25"/>
+      <c r="CV6" s="25"/>
+      <c r="CW6" s="25"/>
+      <c r="CX6" s="25"/>
+      <c r="CY6" s="25"/>
+      <c r="CZ6" s="25"/>
+      <c r="DA6" s="25"/>
+      <c r="DB6" s="25"/>
+      <c r="DC6" s="25"/>
+      <c r="DD6" s="25"/>
+      <c r="DE6" s="25"/>
+      <c r="DF6" s="25"/>
+      <c r="DG6" s="25"/>
+      <c r="DH6" s="25"/>
+      <c r="DI6" s="25"/>
+      <c r="DJ6" s="25"/>
+      <c r="DK6" s="25"/>
+      <c r="DL6" s="25"/>
+      <c r="DM6" s="25"/>
+      <c r="DN6" s="25"/>
+      <c r="DO6" s="25"/>
+      <c r="DP6" s="25"/>
+      <c r="DQ6" s="25"/>
+      <c r="DR6" s="25"/>
+      <c r="DS6" s="25"/>
+      <c r="DT6" s="25"/>
     </row>
     <row r="7" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="49" t="s">
+      <c r="A7" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="47">
+      <c r="B7" s="48"/>
+      <c r="C7" s="46">
         <v>11</v>
       </c>
-      <c r="D7" s="48"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
-      <c r="M7" s="28"/>
-      <c r="N7" s="28"/>
-      <c r="O7" s="28"/>
-      <c r="P7" s="28"/>
-      <c r="Q7" s="28"/>
-      <c r="R7" s="28"/>
-      <c r="S7" s="28"/>
-      <c r="T7" s="28"/>
-      <c r="U7" s="28"/>
-      <c r="V7" s="28"/>
-      <c r="W7" s="28"/>
-      <c r="X7" s="28"/>
-      <c r="Y7" s="28"/>
-      <c r="Z7" s="28"/>
-      <c r="AA7" s="28"/>
-      <c r="AB7" s="28"/>
-      <c r="AC7" s="28"/>
-      <c r="AD7" s="28"/>
-      <c r="AE7" s="28"/>
-      <c r="AF7" s="28"/>
-      <c r="AG7" s="28"/>
-      <c r="AH7" s="28"/>
-      <c r="AI7" s="28"/>
-      <c r="AJ7" s="28"/>
-      <c r="AK7" s="28"/>
-      <c r="AL7" s="28"/>
-      <c r="AM7" s="28"/>
-      <c r="AN7" s="28"/>
-      <c r="AO7" s="28"/>
-      <c r="AP7" s="28"/>
-      <c r="AQ7" s="28"/>
-      <c r="AR7" s="28"/>
-      <c r="AS7" s="28"/>
-      <c r="AT7" s="28"/>
-      <c r="AU7" s="28"/>
-      <c r="AV7" s="28"/>
-      <c r="AW7" s="28"/>
-      <c r="AX7" s="28"/>
-      <c r="AY7" s="28"/>
-      <c r="AZ7" s="28"/>
-      <c r="BA7" s="28"/>
-      <c r="BB7" s="28"/>
-      <c r="BC7" s="28"/>
-      <c r="BD7" s="28"/>
-      <c r="BE7" s="28"/>
-      <c r="BF7" s="28"/>
-      <c r="BG7" s="28"/>
-      <c r="BH7" s="28"/>
-      <c r="BI7" s="28"/>
-      <c r="BJ7" s="28"/>
-      <c r="BK7" s="28"/>
-      <c r="BL7" s="28"/>
-      <c r="BM7" s="28"/>
-      <c r="BN7" s="28"/>
-      <c r="BO7" s="28"/>
-      <c r="BP7" s="28"/>
-      <c r="BQ7" s="28"/>
-      <c r="BR7" s="28"/>
-      <c r="BS7" s="28"/>
-      <c r="BT7" s="28"/>
-      <c r="BU7" s="28"/>
-      <c r="BV7" s="28"/>
-      <c r="BW7" s="28"/>
-      <c r="BX7" s="28"/>
-      <c r="BY7" s="28"/>
-      <c r="BZ7" s="28"/>
-      <c r="CA7" s="28"/>
-      <c r="CB7" s="28"/>
-      <c r="CC7" s="28"/>
-      <c r="CD7" s="28"/>
-      <c r="CE7" s="28"/>
-      <c r="CF7" s="28"/>
-      <c r="CG7" s="28"/>
-      <c r="CH7" s="28"/>
-      <c r="CI7" s="28"/>
-      <c r="CJ7" s="28"/>
-      <c r="CK7" s="28"/>
-      <c r="CL7" s="28"/>
-      <c r="CM7" s="28"/>
-      <c r="CN7" s="28"/>
-      <c r="CO7" s="28"/>
-      <c r="CP7" s="28"/>
-      <c r="CQ7" s="28"/>
-      <c r="CR7" s="28"/>
-      <c r="CS7" s="28"/>
-      <c r="CT7" s="28"/>
-      <c r="CU7" s="28"/>
-      <c r="CV7" s="28"/>
-      <c r="CW7" s="28"/>
-      <c r="CX7" s="28"/>
-      <c r="CY7" s="28"/>
-      <c r="CZ7" s="28"/>
-      <c r="DA7" s="28"/>
-      <c r="DB7" s="28"/>
-      <c r="DC7" s="28"/>
-      <c r="DD7" s="28"/>
-      <c r="DE7" s="28"/>
-      <c r="DF7" s="28"/>
-      <c r="DG7" s="28"/>
-      <c r="DH7" s="28"/>
-      <c r="DI7" s="28"/>
-      <c r="DJ7" s="28"/>
-      <c r="DK7" s="28"/>
-      <c r="DL7" s="28"/>
-      <c r="DM7" s="28"/>
-      <c r="DN7" s="28"/>
-      <c r="DO7" s="28"/>
-      <c r="DP7" s="28"/>
-      <c r="DQ7" s="28"/>
-      <c r="DR7" s="28"/>
-      <c r="DS7" s="28"/>
-      <c r="DT7" s="28"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="26"/>
+      <c r="N7" s="26"/>
+      <c r="O7" s="26"/>
+      <c r="P7" s="26"/>
+      <c r="Q7" s="26"/>
+      <c r="R7" s="26"/>
+      <c r="S7" s="26"/>
+      <c r="T7" s="26"/>
+      <c r="U7" s="26"/>
+      <c r="V7" s="26"/>
+      <c r="W7" s="26"/>
+      <c r="X7" s="26"/>
+      <c r="Y7" s="26"/>
+      <c r="Z7" s="26"/>
+      <c r="AA7" s="26"/>
+      <c r="AB7" s="26"/>
+      <c r="AC7" s="26"/>
+      <c r="AD7" s="26"/>
+      <c r="AE7" s="26"/>
+      <c r="AF7" s="26"/>
+      <c r="AG7" s="26"/>
+      <c r="AH7" s="26"/>
+      <c r="AI7" s="26"/>
+      <c r="AJ7" s="26"/>
+      <c r="AK7" s="26"/>
+      <c r="AL7" s="26"/>
+      <c r="AM7" s="26"/>
+      <c r="AN7" s="26"/>
+      <c r="AO7" s="26"/>
+      <c r="AP7" s="26"/>
+      <c r="AQ7" s="26"/>
+      <c r="AR7" s="26"/>
+      <c r="AS7" s="26"/>
+      <c r="AT7" s="26"/>
+      <c r="AU7" s="26"/>
+      <c r="AV7" s="26"/>
+      <c r="AW7" s="26"/>
+      <c r="AX7" s="26"/>
+      <c r="AY7" s="26"/>
+      <c r="AZ7" s="26"/>
+      <c r="BA7" s="26"/>
+      <c r="BB7" s="26"/>
+      <c r="BC7" s="26"/>
+      <c r="BD7" s="26"/>
+      <c r="BE7" s="26"/>
+      <c r="BF7" s="26"/>
+      <c r="BG7" s="26"/>
+      <c r="BH7" s="26"/>
+      <c r="BI7" s="26"/>
+      <c r="BJ7" s="26"/>
+      <c r="BK7" s="26"/>
+      <c r="BL7" s="26"/>
+      <c r="BM7" s="26"/>
+      <c r="BN7" s="26"/>
+      <c r="BO7" s="26"/>
+      <c r="BP7" s="26"/>
+      <c r="BQ7" s="26"/>
+      <c r="BR7" s="26"/>
+      <c r="BS7" s="26"/>
+      <c r="BT7" s="26"/>
+      <c r="BU7" s="26"/>
+      <c r="BV7" s="26"/>
+      <c r="BW7" s="26"/>
+      <c r="BX7" s="26"/>
+      <c r="BY7" s="26"/>
+      <c r="BZ7" s="26"/>
+      <c r="CA7" s="26"/>
+      <c r="CB7" s="26"/>
+      <c r="CC7" s="26"/>
+      <c r="CD7" s="26"/>
+      <c r="CE7" s="26"/>
+      <c r="CF7" s="26"/>
+      <c r="CG7" s="26"/>
+      <c r="CH7" s="26"/>
+      <c r="CI7" s="26"/>
+      <c r="CJ7" s="26"/>
+      <c r="CK7" s="26"/>
+      <c r="CL7" s="26"/>
+      <c r="CM7" s="26"/>
+      <c r="CN7" s="26"/>
+      <c r="CO7" s="26"/>
+      <c r="CP7" s="26"/>
+      <c r="CQ7" s="26"/>
+      <c r="CR7" s="26"/>
+      <c r="CS7" s="26"/>
+      <c r="CT7" s="26"/>
+      <c r="CU7" s="26"/>
+      <c r="CV7" s="26"/>
+      <c r="CW7" s="26"/>
+      <c r="CX7" s="26"/>
+      <c r="CY7" s="26"/>
+      <c r="CZ7" s="26"/>
+      <c r="DA7" s="26"/>
+      <c r="DB7" s="26"/>
+      <c r="DC7" s="26"/>
+      <c r="DD7" s="26"/>
+      <c r="DE7" s="26"/>
+      <c r="DF7" s="26"/>
+      <c r="DG7" s="26"/>
+      <c r="DH7" s="26"/>
+      <c r="DI7" s="26"/>
+      <c r="DJ7" s="26"/>
+      <c r="DK7" s="26"/>
+      <c r="DL7" s="26"/>
+      <c r="DM7" s="26"/>
+      <c r="DN7" s="26"/>
+      <c r="DO7" s="26"/>
+      <c r="DP7" s="26"/>
+      <c r="DQ7" s="26"/>
+      <c r="DR7" s="26"/>
+      <c r="DS7" s="26"/>
+      <c r="DT7" s="26"/>
     </row>
     <row r="8" spans="1:125" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="29">
+      <c r="B8" s="52"/>
+      <c r="C8" s="53">
         <f>SUM(C5:D7)</f>
         <v>75</v>
       </c>
-      <c r="D8" s="32"/>
+      <c r="D8" s="44"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="25">
-        <v>1</v>
-      </c>
-      <c r="G8" s="25">
+      <c r="F8" s="30">
+        <v>1</v>
+      </c>
+      <c r="G8" s="30">
         <v>2</v>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="30">
         <v>3</v>
       </c>
-      <c r="I8" s="25">
+      <c r="I8" s="30">
         <v>4</v>
       </c>
-      <c r="J8" s="25">
+      <c r="J8" s="30">
         <v>5</v>
       </c>
-      <c r="K8" s="25">
+      <c r="K8" s="30">
         <v>6</v>
       </c>
-      <c r="L8" s="25">
+      <c r="L8" s="30">
         <v>7</v>
       </c>
-      <c r="M8" s="25">
+      <c r="M8" s="30">
         <v>8</v>
       </c>
-      <c r="N8" s="25">
+      <c r="N8" s="30">
         <v>9</v>
       </c>
-      <c r="O8" s="25">
+      <c r="O8" s="30">
         <v>10</v>
       </c>
-      <c r="P8" s="25">
+      <c r="P8" s="30">
         <v>11</v>
       </c>
-      <c r="Q8" s="25">
+      <c r="Q8" s="30">
         <v>12</v>
       </c>
-      <c r="R8" s="25">
+      <c r="R8" s="30">
         <v>13</v>
       </c>
-      <c r="S8" s="25">
+      <c r="S8" s="30">
         <v>14</v>
       </c>
-      <c r="T8" s="25">
+      <c r="T8" s="30">
         <v>15</v>
       </c>
-      <c r="U8" s="25">
+      <c r="U8" s="30">
         <v>16</v>
       </c>
-      <c r="V8" s="25">
+      <c r="V8" s="30">
         <v>17</v>
       </c>
-      <c r="W8" s="25">
+      <c r="W8" s="30">
         <v>18</v>
       </c>
-      <c r="X8" s="25">
+      <c r="X8" s="30">
         <v>19</v>
       </c>
-      <c r="Y8" s="25">
+      <c r="Y8" s="30">
         <v>20</v>
       </c>
-      <c r="Z8" s="25">
+      <c r="Z8" s="30">
         <v>21</v>
       </c>
-      <c r="AA8" s="25">
+      <c r="AA8" s="30">
         <v>22</v>
       </c>
-      <c r="AB8" s="25">
+      <c r="AB8" s="30">
         <v>23</v>
       </c>
-      <c r="AC8" s="25">
+      <c r="AC8" s="30">
         <v>24</v>
       </c>
-      <c r="AD8" s="25">
+      <c r="AD8" s="30">
         <v>25</v>
       </c>
-      <c r="AE8" s="25">
+      <c r="AE8" s="30">
         <v>26</v>
       </c>
-      <c r="AF8" s="25">
+      <c r="AF8" s="30">
         <v>27</v>
       </c>
-      <c r="AG8" s="25">
+      <c r="AG8" s="30">
         <v>28</v>
       </c>
-      <c r="AH8" s="25">
+      <c r="AH8" s="30">
         <v>29</v>
       </c>
-      <c r="AI8" s="25">
+      <c r="AI8" s="30">
         <v>30</v>
       </c>
-      <c r="AJ8" s="25">
+      <c r="AJ8" s="30">
         <v>31</v>
       </c>
-      <c r="AK8" s="25">
+      <c r="AK8" s="30">
         <v>32</v>
       </c>
-      <c r="AL8" s="25">
+      <c r="AL8" s="30">
         <v>33</v>
       </c>
-      <c r="AM8" s="25">
+      <c r="AM8" s="30">
         <v>34</v>
       </c>
-      <c r="AN8" s="25">
+      <c r="AN8" s="30">
         <v>35</v>
       </c>
-      <c r="AO8" s="25">
+      <c r="AO8" s="30">
         <v>36</v>
       </c>
-      <c r="AP8" s="25">
+      <c r="AP8" s="30">
         <v>37</v>
       </c>
-      <c r="AQ8" s="25">
+      <c r="AQ8" s="30">
         <v>38</v>
       </c>
-      <c r="AR8" s="25">
+      <c r="AR8" s="30">
         <v>39</v>
       </c>
-      <c r="AS8" s="25">
+      <c r="AS8" s="30">
         <v>40</v>
       </c>
-      <c r="AT8" s="25">
+      <c r="AT8" s="30">
         <v>41</v>
       </c>
-      <c r="AU8" s="25">
+      <c r="AU8" s="30">
         <v>42</v>
       </c>
-      <c r="AV8" s="25">
+      <c r="AV8" s="30">
         <v>43</v>
       </c>
-      <c r="AW8" s="25">
+      <c r="AW8" s="30">
         <v>44</v>
       </c>
-      <c r="AX8" s="25">
+      <c r="AX8" s="30">
         <v>45</v>
       </c>
-      <c r="AY8" s="25">
+      <c r="AY8" s="30">
         <v>46</v>
       </c>
-      <c r="AZ8" s="25">
+      <c r="AZ8" s="30">
         <v>47</v>
       </c>
-      <c r="BA8" s="25">
+      <c r="BA8" s="30">
         <v>48</v>
       </c>
-      <c r="BB8" s="25">
+      <c r="BB8" s="30">
         <v>49</v>
       </c>
-      <c r="BC8" s="25">
+      <c r="BC8" s="30">
         <v>50</v>
       </c>
-      <c r="BD8" s="25">
+      <c r="BD8" s="30">
         <v>51</v>
       </c>
-      <c r="BE8" s="25">
+      <c r="BE8" s="30">
         <v>52</v>
       </c>
-      <c r="BF8" s="25">
+      <c r="BF8" s="30">
         <v>53</v>
       </c>
-      <c r="BG8" s="25">
+      <c r="BG8" s="30">
         <v>54</v>
       </c>
-      <c r="BH8" s="25">
+      <c r="BH8" s="30">
         <v>55</v>
       </c>
-      <c r="BI8" s="25">
+      <c r="BI8" s="30">
         <v>56</v>
       </c>
-      <c r="BJ8" s="25">
+      <c r="BJ8" s="30">
         <v>57</v>
       </c>
-      <c r="BK8" s="25">
+      <c r="BK8" s="30">
         <v>58</v>
       </c>
-      <c r="BL8" s="25">
+      <c r="BL8" s="30">
         <v>59</v>
       </c>
-      <c r="BM8" s="25">
+      <c r="BM8" s="30">
         <v>60</v>
       </c>
-      <c r="BN8" s="25">
+      <c r="BN8" s="30">
         <v>61</v>
       </c>
-      <c r="BO8" s="25">
+      <c r="BO8" s="30">
         <v>62</v>
       </c>
-      <c r="BP8" s="25">
+      <c r="BP8" s="30">
         <v>63</v>
       </c>
-      <c r="BQ8" s="25">
+      <c r="BQ8" s="30">
         <v>64</v>
       </c>
-      <c r="BR8" s="25">
+      <c r="BR8" s="30">
         <v>65</v>
       </c>
-      <c r="BS8" s="25">
+      <c r="BS8" s="30">
         <v>66</v>
       </c>
-      <c r="BT8" s="25">
+      <c r="BT8" s="30">
         <v>67</v>
       </c>
-      <c r="BU8" s="25">
+      <c r="BU8" s="30">
         <v>68</v>
       </c>
-      <c r="BV8" s="25">
+      <c r="BV8" s="30">
         <v>69</v>
       </c>
-      <c r="BW8" s="25">
+      <c r="BW8" s="30">
         <v>70</v>
       </c>
-      <c r="BX8" s="25">
+      <c r="BX8" s="30">
         <v>71</v>
       </c>
-      <c r="BY8" s="25">
+      <c r="BY8" s="30">
         <v>72</v>
       </c>
-      <c r="BZ8" s="25">
+      <c r="BZ8" s="30">
         <v>73</v>
       </c>
-      <c r="CA8" s="25">
+      <c r="CA8" s="30">
         <v>74</v>
       </c>
-      <c r="CB8" s="25">
+      <c r="CB8" s="30">
         <v>75</v>
       </c>
-      <c r="CC8" s="25">
+      <c r="CC8" s="30">
         <v>76</v>
       </c>
-      <c r="CD8" s="25">
+      <c r="CD8" s="30">
         <v>77</v>
       </c>
-      <c r="CE8" s="25">
+      <c r="CE8" s="30">
         <v>78</v>
       </c>
-      <c r="CF8" s="25">
+      <c r="CF8" s="30">
         <v>79</v>
       </c>
-      <c r="CG8" s="25">
+      <c r="CG8" s="30">
         <v>80</v>
       </c>
-      <c r="CH8" s="25">
+      <c r="CH8" s="30">
         <v>81</v>
       </c>
-      <c r="CI8" s="25">
+      <c r="CI8" s="30">
         <v>82</v>
       </c>
-      <c r="CJ8" s="25">
+      <c r="CJ8" s="30">
         <v>83</v>
       </c>
-      <c r="CK8" s="25">
+      <c r="CK8" s="30">
         <v>84</v>
       </c>
-      <c r="CL8" s="25">
+      <c r="CL8" s="30">
         <v>85</v>
       </c>
-      <c r="CM8" s="25">
+      <c r="CM8" s="30">
         <v>86</v>
       </c>
-      <c r="CN8" s="25">
+      <c r="CN8" s="30">
         <v>87</v>
       </c>
-      <c r="CO8" s="25">
+      <c r="CO8" s="30">
         <v>88</v>
       </c>
-      <c r="CP8" s="25">
+      <c r="CP8" s="30">
         <v>89</v>
       </c>
-      <c r="CQ8" s="25">
+      <c r="CQ8" s="30">
         <v>90</v>
       </c>
-      <c r="CR8" s="25">
+      <c r="CR8" s="30">
         <v>91</v>
       </c>
-      <c r="CS8" s="25">
+      <c r="CS8" s="30">
         <v>92</v>
       </c>
-      <c r="CT8" s="25">
+      <c r="CT8" s="30">
         <v>93</v>
       </c>
-      <c r="CU8" s="25">
+      <c r="CU8" s="30">
         <v>94</v>
       </c>
-      <c r="CV8" s="25">
+      <c r="CV8" s="30">
         <v>95</v>
       </c>
-      <c r="CW8" s="25">
+      <c r="CW8" s="30">
         <v>96</v>
       </c>
-      <c r="CX8" s="25">
+      <c r="CX8" s="30">
         <v>97</v>
       </c>
-      <c r="CY8" s="25">
+      <c r="CY8" s="30">
         <v>98</v>
       </c>
-      <c r="CZ8" s="25">
+      <c r="CZ8" s="30">
         <v>99</v>
       </c>
-      <c r="DA8" s="25">
+      <c r="DA8" s="30">
         <v>100</v>
       </c>
-      <c r="DB8" s="25">
+      <c r="DB8" s="30">
         <v>101</v>
       </c>
-      <c r="DC8" s="25">
+      <c r="DC8" s="30">
         <v>102</v>
       </c>
-      <c r="DD8" s="25">
+      <c r="DD8" s="30">
         <v>103</v>
       </c>
-      <c r="DE8" s="25">
+      <c r="DE8" s="30">
         <v>104</v>
       </c>
-      <c r="DF8" s="25">
+      <c r="DF8" s="30">
         <v>105</v>
       </c>
-      <c r="DG8" s="25">
+      <c r="DG8" s="30">
         <v>106</v>
       </c>
-      <c r="DH8" s="25">
+      <c r="DH8" s="30">
         <v>107</v>
       </c>
-      <c r="DI8" s="25">
+      <c r="DI8" s="30">
         <v>108</v>
       </c>
-      <c r="DJ8" s="25">
+      <c r="DJ8" s="30">
         <v>109</v>
       </c>
-      <c r="DK8" s="25">
+      <c r="DK8" s="30">
         <v>110</v>
       </c>
-      <c r="DL8" s="25">
+      <c r="DL8" s="30">
         <v>111</v>
       </c>
-      <c r="DM8" s="25">
+      <c r="DM8" s="30">
         <v>112</v>
       </c>
-      <c r="DN8" s="25">
+      <c r="DN8" s="30">
         <v>113</v>
       </c>
-      <c r="DO8" s="25">
+      <c r="DO8" s="30">
         <v>114</v>
       </c>
-      <c r="DP8" s="25">
+      <c r="DP8" s="30">
         <v>115</v>
       </c>
-      <c r="DQ8" s="25">
+      <c r="DQ8" s="30">
         <v>116</v>
       </c>
-      <c r="DR8" s="25">
+      <c r="DR8" s="30">
         <v>117</v>
       </c>
-      <c r="DS8" s="25">
+      <c r="DS8" s="30">
         <v>118</v>
       </c>
-      <c r="DT8" s="25">
+      <c r="DT8" s="30">
         <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="33" t="s">
+      <c r="A9" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="34" t="s">
+      <c r="B9" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="C9" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="34"/>
+      <c r="D9" s="54"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="26"/>
-      <c r="L9" s="26"/>
-      <c r="M9" s="26"/>
-      <c r="N9" s="26"/>
-      <c r="O9" s="26"/>
-      <c r="P9" s="26"/>
-      <c r="Q9" s="26"/>
-      <c r="R9" s="26"/>
-      <c r="S9" s="26"/>
-      <c r="T9" s="26"/>
-      <c r="U9" s="26"/>
-      <c r="V9" s="26"/>
-      <c r="W9" s="26"/>
-      <c r="X9" s="26"/>
-      <c r="Y9" s="26"/>
-      <c r="Z9" s="26"/>
-      <c r="AA9" s="26"/>
-      <c r="AB9" s="26"/>
-      <c r="AC9" s="26"/>
-      <c r="AD9" s="26"/>
-      <c r="AE9" s="26"/>
-      <c r="AF9" s="26"/>
-      <c r="AG9" s="26"/>
-      <c r="AH9" s="26"/>
-      <c r="AI9" s="26"/>
-      <c r="AJ9" s="26"/>
-      <c r="AK9" s="26"/>
-      <c r="AL9" s="26"/>
-      <c r="AM9" s="26"/>
-      <c r="AN9" s="26"/>
-      <c r="AO9" s="26"/>
-      <c r="AP9" s="26"/>
-      <c r="AQ9" s="26"/>
-      <c r="AR9" s="26"/>
-      <c r="AS9" s="26"/>
-      <c r="AT9" s="26"/>
-      <c r="AU9" s="26"/>
-      <c r="AV9" s="26"/>
-      <c r="AW9" s="26"/>
-      <c r="AX9" s="26"/>
-      <c r="AY9" s="26"/>
-      <c r="AZ9" s="26"/>
-      <c r="BA9" s="26"/>
-      <c r="BB9" s="26"/>
-      <c r="BC9" s="26"/>
-      <c r="BD9" s="26"/>
-      <c r="BE9" s="26"/>
-      <c r="BF9" s="26"/>
-      <c r="BG9" s="26"/>
-      <c r="BH9" s="26"/>
-      <c r="BI9" s="26"/>
-      <c r="BJ9" s="26"/>
-      <c r="BK9" s="26"/>
-      <c r="BL9" s="26"/>
-      <c r="BM9" s="26"/>
-      <c r="BN9" s="26"/>
-      <c r="BO9" s="26"/>
-      <c r="BP9" s="26"/>
-      <c r="BQ9" s="26"/>
-      <c r="BR9" s="26"/>
-      <c r="BS9" s="26"/>
-      <c r="BT9" s="26"/>
-      <c r="BU9" s="26"/>
-      <c r="BV9" s="26"/>
-      <c r="BW9" s="26"/>
-      <c r="BX9" s="26"/>
-      <c r="BY9" s="26"/>
-      <c r="BZ9" s="26"/>
-      <c r="CA9" s="26"/>
-      <c r="CB9" s="26"/>
-      <c r="CC9" s="26"/>
-      <c r="CD9" s="26"/>
-      <c r="CE9" s="26"/>
-      <c r="CF9" s="26"/>
-      <c r="CG9" s="26"/>
-      <c r="CH9" s="26"/>
-      <c r="CI9" s="26"/>
-      <c r="CJ9" s="26"/>
-      <c r="CK9" s="26"/>
-      <c r="CL9" s="26"/>
-      <c r="CM9" s="26"/>
-      <c r="CN9" s="26"/>
-      <c r="CO9" s="26"/>
-      <c r="CP9" s="26"/>
-      <c r="CQ9" s="26"/>
-      <c r="CR9" s="26"/>
-      <c r="CS9" s="26"/>
-      <c r="CT9" s="26"/>
-      <c r="CU9" s="26"/>
-      <c r="CV9" s="26"/>
-      <c r="CW9" s="26"/>
-      <c r="CX9" s="26"/>
-      <c r="CY9" s="26"/>
-      <c r="CZ9" s="26"/>
-      <c r="DA9" s="26"/>
-      <c r="DB9" s="26"/>
-      <c r="DC9" s="26"/>
-      <c r="DD9" s="26"/>
-      <c r="DE9" s="26"/>
-      <c r="DF9" s="26"/>
-      <c r="DG9" s="26"/>
-      <c r="DH9" s="26"/>
-      <c r="DI9" s="26"/>
-      <c r="DJ9" s="26"/>
-      <c r="DK9" s="26"/>
-      <c r="DL9" s="26"/>
-      <c r="DM9" s="26"/>
-      <c r="DN9" s="26"/>
-      <c r="DO9" s="26"/>
-      <c r="DP9" s="26"/>
-      <c r="DQ9" s="26"/>
-      <c r="DR9" s="26"/>
-      <c r="DS9" s="26"/>
-      <c r="DT9" s="26"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="31"/>
+      <c r="M9" s="31"/>
+      <c r="N9" s="31"/>
+      <c r="O9" s="31"/>
+      <c r="P9" s="31"/>
+      <c r="Q9" s="31"/>
+      <c r="R9" s="31"/>
+      <c r="S9" s="31"/>
+      <c r="T9" s="31"/>
+      <c r="U9" s="31"/>
+      <c r="V9" s="31"/>
+      <c r="W9" s="31"/>
+      <c r="X9" s="31"/>
+      <c r="Y9" s="31"/>
+      <c r="Z9" s="31"/>
+      <c r="AA9" s="31"/>
+      <c r="AB9" s="31"/>
+      <c r="AC9" s="31"/>
+      <c r="AD9" s="31"/>
+      <c r="AE9" s="31"/>
+      <c r="AF9" s="31"/>
+      <c r="AG9" s="31"/>
+      <c r="AH9" s="31"/>
+      <c r="AI9" s="31"/>
+      <c r="AJ9" s="31"/>
+      <c r="AK9" s="31"/>
+      <c r="AL9" s="31"/>
+      <c r="AM9" s="31"/>
+      <c r="AN9" s="31"/>
+      <c r="AO9" s="31"/>
+      <c r="AP9" s="31"/>
+      <c r="AQ9" s="31"/>
+      <c r="AR9" s="31"/>
+      <c r="AS9" s="31"/>
+      <c r="AT9" s="31"/>
+      <c r="AU9" s="31"/>
+      <c r="AV9" s="31"/>
+      <c r="AW9" s="31"/>
+      <c r="AX9" s="31"/>
+      <c r="AY9" s="31"/>
+      <c r="AZ9" s="31"/>
+      <c r="BA9" s="31"/>
+      <c r="BB9" s="31"/>
+      <c r="BC9" s="31"/>
+      <c r="BD9" s="31"/>
+      <c r="BE9" s="31"/>
+      <c r="BF9" s="31"/>
+      <c r="BG9" s="31"/>
+      <c r="BH9" s="31"/>
+      <c r="BI9" s="31"/>
+      <c r="BJ9" s="31"/>
+      <c r="BK9" s="31"/>
+      <c r="BL9" s="31"/>
+      <c r="BM9" s="31"/>
+      <c r="BN9" s="31"/>
+      <c r="BO9" s="31"/>
+      <c r="BP9" s="31"/>
+      <c r="BQ9" s="31"/>
+      <c r="BR9" s="31"/>
+      <c r="BS9" s="31"/>
+      <c r="BT9" s="31"/>
+      <c r="BU9" s="31"/>
+      <c r="BV9" s="31"/>
+      <c r="BW9" s="31"/>
+      <c r="BX9" s="31"/>
+      <c r="BY9" s="31"/>
+      <c r="BZ9" s="31"/>
+      <c r="CA9" s="31"/>
+      <c r="CB9" s="31"/>
+      <c r="CC9" s="31"/>
+      <c r="CD9" s="31"/>
+      <c r="CE9" s="31"/>
+      <c r="CF9" s="31"/>
+      <c r="CG9" s="31"/>
+      <c r="CH9" s="31"/>
+      <c r="CI9" s="31"/>
+      <c r="CJ9" s="31"/>
+      <c r="CK9" s="31"/>
+      <c r="CL9" s="31"/>
+      <c r="CM9" s="31"/>
+      <c r="CN9" s="31"/>
+      <c r="CO9" s="31"/>
+      <c r="CP9" s="31"/>
+      <c r="CQ9" s="31"/>
+      <c r="CR9" s="31"/>
+      <c r="CS9" s="31"/>
+      <c r="CT9" s="31"/>
+      <c r="CU9" s="31"/>
+      <c r="CV9" s="31"/>
+      <c r="CW9" s="31"/>
+      <c r="CX9" s="31"/>
+      <c r="CY9" s="31"/>
+      <c r="CZ9" s="31"/>
+      <c r="DA9" s="31"/>
+      <c r="DB9" s="31"/>
+      <c r="DC9" s="31"/>
+      <c r="DD9" s="31"/>
+      <c r="DE9" s="31"/>
+      <c r="DF9" s="31"/>
+      <c r="DG9" s="31"/>
+      <c r="DH9" s="31"/>
+      <c r="DI9" s="31"/>
+      <c r="DJ9" s="31"/>
+      <c r="DK9" s="31"/>
+      <c r="DL9" s="31"/>
+      <c r="DM9" s="31"/>
+      <c r="DN9" s="31"/>
+      <c r="DO9" s="31"/>
+      <c r="DP9" s="31"/>
+      <c r="DQ9" s="31"/>
+      <c r="DR9" s="31"/>
+      <c r="DS9" s="31"/>
+      <c r="DT9" s="31"/>
     </row>
     <row r="10" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="33"/>
-      <c r="B10" s="34"/>
+      <c r="A10" s="41"/>
+      <c r="B10" s="54"/>
       <c r="C10" s="6"/>
       <c r="D10" s="4" t="s">
         <v>10</v>
@@ -4734,247 +4744,250 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E26" s="29"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="30"/>
-      <c r="I26" s="30"/>
-      <c r="J26" s="30"/>
-      <c r="K26" s="30"/>
-      <c r="L26" s="30"/>
-      <c r="M26" s="30"/>
-      <c r="N26" s="30"/>
-      <c r="O26" s="30"/>
-      <c r="P26" s="30"/>
-      <c r="Q26" s="30"/>
-      <c r="R26" s="30"/>
-      <c r="S26" s="30"/>
-      <c r="T26" s="30"/>
-      <c r="U26" s="30"/>
-      <c r="V26" s="30"/>
-      <c r="W26" s="30"/>
-      <c r="X26" s="30"/>
-      <c r="Y26" s="30"/>
-      <c r="Z26" s="30"/>
-      <c r="AA26" s="30"/>
-      <c r="AB26" s="30"/>
-      <c r="AC26" s="30"/>
-      <c r="AD26" s="30"/>
-      <c r="AE26" s="30"/>
-      <c r="AF26" s="30"/>
-      <c r="AG26" s="30"/>
-      <c r="AH26" s="30"/>
-      <c r="AI26" s="30"/>
-      <c r="AJ26" s="30"/>
-      <c r="AK26" s="30"/>
-      <c r="AL26" s="30"/>
-      <c r="AM26" s="30"/>
-      <c r="AN26" s="30"/>
-      <c r="AO26" s="30"/>
-      <c r="AP26" s="30"/>
-      <c r="AQ26" s="30"/>
-      <c r="AR26" s="30"/>
-      <c r="AS26" s="30"/>
-      <c r="AT26" s="30"/>
-      <c r="AU26" s="30"/>
-      <c r="AV26" s="30"/>
-      <c r="AW26" s="30"/>
-      <c r="AX26" s="30"/>
-      <c r="AY26" s="30"/>
-      <c r="AZ26" s="30"/>
-      <c r="BA26" s="30"/>
-      <c r="BB26" s="30"/>
-      <c r="BC26" s="30"/>
-      <c r="BD26" s="30"/>
-      <c r="BE26" s="30"/>
-      <c r="BF26" s="30"/>
-      <c r="BG26" s="30"/>
-      <c r="BH26" s="30"/>
-      <c r="BI26" s="30"/>
-      <c r="BJ26" s="30"/>
-      <c r="BK26" s="30"/>
-      <c r="BL26" s="30"/>
-      <c r="BM26" s="30"/>
-      <c r="BN26" s="30"/>
-      <c r="BO26" s="30"/>
-      <c r="BP26" s="30"/>
-      <c r="BQ26" s="30"/>
-      <c r="BR26" s="30"/>
-      <c r="BS26" s="30"/>
-      <c r="BT26" s="30"/>
-      <c r="BU26" s="30"/>
-      <c r="BV26" s="30"/>
-      <c r="BW26" s="30"/>
-      <c r="BX26" s="30"/>
-      <c r="BY26" s="30"/>
-      <c r="BZ26" s="30"/>
-      <c r="CA26" s="30"/>
-      <c r="CB26" s="30"/>
-      <c r="CC26" s="30"/>
-      <c r="CD26" s="30"/>
-      <c r="CE26" s="30"/>
-      <c r="CF26" s="30"/>
-      <c r="CG26" s="30"/>
-      <c r="CH26" s="30"/>
-      <c r="CI26" s="30"/>
-      <c r="CJ26" s="30"/>
-      <c r="CK26" s="30"/>
-      <c r="CL26" s="30"/>
-      <c r="CM26" s="30"/>
-      <c r="CN26" s="30"/>
-      <c r="CO26" s="30"/>
-      <c r="CP26" s="30"/>
-      <c r="CQ26" s="30"/>
-      <c r="CR26" s="30"/>
-      <c r="CS26" s="30"/>
-      <c r="CT26" s="30"/>
-      <c r="CU26" s="30"/>
-      <c r="CV26" s="30"/>
-      <c r="CW26" s="30"/>
-      <c r="CX26" s="30"/>
-      <c r="CY26" s="30"/>
-      <c r="CZ26" s="30"/>
-      <c r="DA26" s="30"/>
-      <c r="DB26" s="30"/>
-      <c r="DC26" s="30"/>
-      <c r="DD26" s="30"/>
-      <c r="DE26" s="30"/>
-      <c r="DF26" s="30"/>
-      <c r="DG26" s="30"/>
-      <c r="DH26" s="30"/>
-      <c r="DI26" s="30"/>
-      <c r="DJ26" s="30"/>
-      <c r="DK26" s="30"/>
-      <c r="DL26" s="30"/>
-      <c r="DM26" s="30"/>
-      <c r="DN26" s="30"/>
-      <c r="DO26" s="30"/>
-      <c r="DP26" s="30"/>
-      <c r="DQ26" s="30"/>
-      <c r="DR26" s="30"/>
-      <c r="DS26" s="30"/>
-      <c r="DT26" s="30"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="43"/>
+      <c r="K26" s="43"/>
+      <c r="L26" s="43"/>
+      <c r="M26" s="43"/>
+      <c r="N26" s="43"/>
+      <c r="O26" s="43"/>
+      <c r="P26" s="43"/>
+      <c r="Q26" s="43"/>
+      <c r="R26" s="43"/>
+      <c r="S26" s="43"/>
+      <c r="T26" s="43"/>
+      <c r="U26" s="43"/>
+      <c r="V26" s="43"/>
+      <c r="W26" s="43"/>
+      <c r="X26" s="43"/>
+      <c r="Y26" s="43"/>
+      <c r="Z26" s="43"/>
+      <c r="AA26" s="43"/>
+      <c r="AB26" s="43"/>
+      <c r="AC26" s="43"/>
+      <c r="AD26" s="43"/>
+      <c r="AE26" s="43"/>
+      <c r="AF26" s="43"/>
+      <c r="AG26" s="43"/>
+      <c r="AH26" s="43"/>
+      <c r="AI26" s="43"/>
+      <c r="AJ26" s="43"/>
+      <c r="AK26" s="43"/>
+      <c r="AL26" s="43"/>
+      <c r="AM26" s="43"/>
+      <c r="AN26" s="43"/>
+      <c r="AO26" s="43"/>
+      <c r="AP26" s="43"/>
+      <c r="AQ26" s="43"/>
+      <c r="AR26" s="43"/>
+      <c r="AS26" s="43"/>
+      <c r="AT26" s="43"/>
+      <c r="AU26" s="43"/>
+      <c r="AV26" s="43"/>
+      <c r="AW26" s="43"/>
+      <c r="AX26" s="43"/>
+      <c r="AY26" s="43"/>
+      <c r="AZ26" s="43"/>
+      <c r="BA26" s="43"/>
+      <c r="BB26" s="43"/>
+      <c r="BC26" s="43"/>
+      <c r="BD26" s="43"/>
+      <c r="BE26" s="43"/>
+      <c r="BF26" s="43"/>
+      <c r="BG26" s="43"/>
+      <c r="BH26" s="43"/>
+      <c r="BI26" s="43"/>
+      <c r="BJ26" s="43"/>
+      <c r="BK26" s="43"/>
+      <c r="BL26" s="43"/>
+      <c r="BM26" s="43"/>
+      <c r="BN26" s="43"/>
+      <c r="BO26" s="43"/>
+      <c r="BP26" s="43"/>
+      <c r="BQ26" s="43"/>
+      <c r="BR26" s="43"/>
+      <c r="BS26" s="43"/>
+      <c r="BT26" s="43"/>
+      <c r="BU26" s="43"/>
+      <c r="BV26" s="43"/>
+      <c r="BW26" s="43"/>
+      <c r="BX26" s="43"/>
+      <c r="BY26" s="43"/>
+      <c r="BZ26" s="43"/>
+      <c r="CA26" s="43"/>
+      <c r="CB26" s="43"/>
+      <c r="CC26" s="43"/>
+      <c r="CD26" s="43"/>
+      <c r="CE26" s="43"/>
+      <c r="CF26" s="43"/>
+      <c r="CG26" s="43"/>
+      <c r="CH26" s="43"/>
+      <c r="CI26" s="43"/>
+      <c r="CJ26" s="43"/>
+      <c r="CK26" s="43"/>
+      <c r="CL26" s="43"/>
+      <c r="CM26" s="43"/>
+      <c r="CN26" s="43"/>
+      <c r="CO26" s="43"/>
+      <c r="CP26" s="43"/>
+      <c r="CQ26" s="43"/>
+      <c r="CR26" s="43"/>
+      <c r="CS26" s="43"/>
+      <c r="CT26" s="43"/>
+      <c r="CU26" s="43"/>
+      <c r="CV26" s="43"/>
+      <c r="CW26" s="43"/>
+      <c r="CX26" s="43"/>
+      <c r="CY26" s="43"/>
+      <c r="CZ26" s="43"/>
+      <c r="DA26" s="43"/>
+      <c r="DB26" s="43"/>
+      <c r="DC26" s="43"/>
+      <c r="DD26" s="43"/>
+      <c r="DE26" s="43"/>
+      <c r="DF26" s="43"/>
+      <c r="DG26" s="43"/>
+      <c r="DH26" s="43"/>
+      <c r="DI26" s="43"/>
+      <c r="DJ26" s="43"/>
+      <c r="DK26" s="43"/>
+      <c r="DL26" s="43"/>
+      <c r="DM26" s="43"/>
+      <c r="DN26" s="43"/>
+      <c r="DO26" s="43"/>
+      <c r="DP26" s="43"/>
+      <c r="DQ26" s="43"/>
+      <c r="DR26" s="43"/>
+      <c r="DS26" s="43"/>
+      <c r="DT26" s="43"/>
     </row>
     <row r="27" spans="1:124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F27" s="53"/>
-      <c r="G27" s="53"/>
-      <c r="H27" s="53"/>
-      <c r="I27" s="53"/>
-      <c r="J27" s="53"/>
-      <c r="K27" s="53"/>
-      <c r="L27" s="53"/>
-      <c r="M27" s="53"/>
-      <c r="N27" s="53"/>
-      <c r="O27" s="53"/>
-      <c r="P27" s="53"/>
-      <c r="Q27" s="53"/>
-      <c r="R27" s="53"/>
-      <c r="S27" s="53"/>
-      <c r="T27" s="53"/>
-      <c r="U27" s="53"/>
-      <c r="V27" s="53"/>
-      <c r="W27" s="53"/>
-      <c r="X27" s="53"/>
-      <c r="Y27" s="53"/>
-      <c r="Z27" s="53"/>
-      <c r="AA27" s="53"/>
-      <c r="AB27" s="53"/>
-      <c r="AC27" s="53"/>
-      <c r="AD27" s="53"/>
-      <c r="AE27" s="53"/>
-      <c r="AF27" s="53"/>
-      <c r="AG27" s="53"/>
-      <c r="AH27" s="53"/>
-      <c r="AI27" s="53"/>
-      <c r="AJ27" s="53"/>
-      <c r="AK27" s="53"/>
-      <c r="AL27" s="53"/>
-      <c r="AM27" s="53"/>
-      <c r="AN27" s="53"/>
-      <c r="AO27" s="53"/>
-      <c r="AP27" s="53"/>
-      <c r="AQ27" s="53"/>
-      <c r="AR27" s="53"/>
-      <c r="AS27" s="53"/>
-      <c r="AT27" s="53"/>
-      <c r="AU27" s="53"/>
-      <c r="AV27" s="53"/>
-      <c r="AW27" s="53"/>
-      <c r="AX27" s="53"/>
-      <c r="AY27" s="53"/>
-      <c r="AZ27" s="53"/>
-      <c r="BA27" s="53"/>
-      <c r="BB27" s="53"/>
-      <c r="BC27" s="53"/>
-      <c r="BD27" s="53"/>
-      <c r="BE27" s="53"/>
-      <c r="BF27" s="53"/>
-      <c r="BG27" s="53"/>
-      <c r="BH27" s="53"/>
-      <c r="BI27" s="53"/>
-      <c r="BJ27" s="53"/>
-      <c r="BK27" s="53"/>
-      <c r="BL27" s="53"/>
-      <c r="BM27" s="53"/>
-      <c r="BN27" s="53"/>
-      <c r="BO27" s="53"/>
-      <c r="BP27" s="53"/>
-      <c r="BQ27" s="53"/>
-      <c r="BR27" s="53"/>
-      <c r="BS27" s="53"/>
-      <c r="BT27" s="53"/>
-      <c r="BU27" s="53"/>
-      <c r="BV27" s="53"/>
-      <c r="BW27" s="53"/>
-      <c r="BX27" s="53"/>
-      <c r="BY27" s="53"/>
-      <c r="BZ27" s="53"/>
-      <c r="CA27" s="53"/>
-      <c r="CB27" s="53"/>
-      <c r="CC27" s="53"/>
-      <c r="CD27" s="53"/>
-      <c r="CE27" s="54"/>
-      <c r="CF27" s="55"/>
-      <c r="CG27" s="55"/>
-      <c r="CH27" s="55"/>
-      <c r="CI27" s="55"/>
-      <c r="CJ27" s="55"/>
-      <c r="CK27" s="55"/>
-      <c r="CL27" s="55"/>
-      <c r="CM27" s="55"/>
-      <c r="CN27" s="55"/>
-      <c r="CO27" s="55"/>
-      <c r="CP27" s="55"/>
-      <c r="CQ27" s="55"/>
-      <c r="CR27" s="55"/>
-      <c r="CS27" s="55"/>
-      <c r="CT27" s="55"/>
-      <c r="CU27" s="55"/>
-      <c r="CV27" s="55"/>
-      <c r="CW27" s="55"/>
-      <c r="CX27" s="55"/>
-      <c r="CY27" s="55"/>
-      <c r="CZ27" s="55"/>
-      <c r="DA27" s="55"/>
-      <c r="DB27" s="55"/>
-      <c r="DC27" s="55"/>
-      <c r="DD27" s="55"/>
-      <c r="DE27" s="55"/>
-      <c r="DF27" s="55"/>
-      <c r="DG27" s="55"/>
-      <c r="DH27" s="55"/>
-      <c r="DI27" s="55"/>
-      <c r="DJ27" s="55"/>
-      <c r="DK27" s="55"/>
-      <c r="DL27" s="55"/>
-      <c r="DM27" s="55"/>
-      <c r="DN27" s="55"/>
-      <c r="DO27" s="55"/>
-      <c r="DP27" s="55"/>
-      <c r="DQ27" s="55"/>
-      <c r="DR27" s="55"/>
-      <c r="DS27" s="55"/>
-      <c r="DT27" s="55"/>
+      <c r="E27" s="1">
+        <v>4</v>
+      </c>
+      <c r="F27" s="27"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="27"/>
+      <c r="I27" s="27"/>
+      <c r="J27" s="27"/>
+      <c r="K27" s="27"/>
+      <c r="L27" s="27"/>
+      <c r="M27" s="27"/>
+      <c r="N27" s="27"/>
+      <c r="O27" s="27"/>
+      <c r="P27" s="27"/>
+      <c r="Q27" s="27"/>
+      <c r="R27" s="27"/>
+      <c r="S27" s="27"/>
+      <c r="T27" s="27"/>
+      <c r="U27" s="27"/>
+      <c r="V27" s="27"/>
+      <c r="W27" s="27"/>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="27"/>
+      <c r="Z27" s="27"/>
+      <c r="AA27" s="27"/>
+      <c r="AB27" s="27"/>
+      <c r="AC27" s="27"/>
+      <c r="AD27" s="27"/>
+      <c r="AE27" s="27"/>
+      <c r="AF27" s="27"/>
+      <c r="AG27" s="27"/>
+      <c r="AH27" s="27"/>
+      <c r="AI27" s="27"/>
+      <c r="AJ27" s="27"/>
+      <c r="AK27" s="27"/>
+      <c r="AL27" s="27"/>
+      <c r="AM27" s="27"/>
+      <c r="AN27" s="27"/>
+      <c r="AO27" s="27"/>
+      <c r="AP27" s="27"/>
+      <c r="AQ27" s="27"/>
+      <c r="AR27" s="27"/>
+      <c r="AS27" s="27"/>
+      <c r="AT27" s="27"/>
+      <c r="AU27" s="27"/>
+      <c r="AV27" s="27"/>
+      <c r="AW27" s="27"/>
+      <c r="AX27" s="27"/>
+      <c r="AY27" s="27"/>
+      <c r="AZ27" s="27"/>
+      <c r="BA27" s="27"/>
+      <c r="BB27" s="27"/>
+      <c r="BC27" s="27"/>
+      <c r="BD27" s="27"/>
+      <c r="BE27" s="27"/>
+      <c r="BF27" s="27"/>
+      <c r="BG27" s="27"/>
+      <c r="BH27" s="27"/>
+      <c r="BI27" s="27"/>
+      <c r="BJ27" s="27"/>
+      <c r="BK27" s="27"/>
+      <c r="BL27" s="27"/>
+      <c r="BM27" s="27"/>
+      <c r="BN27" s="27"/>
+      <c r="BO27" s="27"/>
+      <c r="BP27" s="27"/>
+      <c r="BQ27" s="27"/>
+      <c r="BR27" s="27"/>
+      <c r="BS27" s="27"/>
+      <c r="BT27" s="27"/>
+      <c r="BU27" s="27"/>
+      <c r="BV27" s="27"/>
+      <c r="BW27" s="27"/>
+      <c r="BX27" s="27"/>
+      <c r="BY27" s="27"/>
+      <c r="BZ27" s="27"/>
+      <c r="CA27" s="27"/>
+      <c r="CB27" s="27"/>
+      <c r="CC27" s="27"/>
+      <c r="CD27" s="27"/>
+      <c r="CE27" s="28"/>
+      <c r="CF27" s="29"/>
+      <c r="CG27" s="29"/>
+      <c r="CH27" s="29"/>
+      <c r="CI27" s="29"/>
+      <c r="CJ27" s="29"/>
+      <c r="CK27" s="29"/>
+      <c r="CL27" s="29"/>
+      <c r="CM27" s="29"/>
+      <c r="CN27" s="29"/>
+      <c r="CO27" s="29"/>
+      <c r="CP27" s="29"/>
+      <c r="CQ27" s="29"/>
+      <c r="CR27" s="29"/>
+      <c r="CS27" s="29"/>
+      <c r="CT27" s="29"/>
+      <c r="CU27" s="29"/>
+      <c r="CV27" s="29"/>
+      <c r="CW27" s="29"/>
+      <c r="CX27" s="29"/>
+      <c r="CY27" s="29"/>
+      <c r="CZ27" s="29"/>
+      <c r="DA27" s="29"/>
+      <c r="DB27" s="29"/>
+      <c r="DC27" s="29"/>
+      <c r="DD27" s="29"/>
+      <c r="DE27" s="29"/>
+      <c r="DF27" s="29"/>
+      <c r="DG27" s="29"/>
+      <c r="DH27" s="29"/>
+      <c r="DI27" s="29"/>
+      <c r="DJ27" s="29"/>
+      <c r="DK27" s="29"/>
+      <c r="DL27" s="29"/>
+      <c r="DM27" s="29"/>
+      <c r="DN27" s="29"/>
+      <c r="DO27" s="29"/>
+      <c r="DP27" s="29"/>
+      <c r="DQ27" s="29"/>
+      <c r="DR27" s="29"/>
+      <c r="DS27" s="29"/>
+      <c r="DT27" s="29"/>
     </row>
     <row r="29" spans="1:124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E29" s="22">
@@ -4999,27 +5012,225 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="261">
-    <mergeCell ref="DQ2:DQ7"/>
-    <mergeCell ref="DR2:DR7"/>
-    <mergeCell ref="DS2:DS7"/>
-    <mergeCell ref="DT2:DT7"/>
-    <mergeCell ref="CX2:CX7"/>
-    <mergeCell ref="CY2:CY7"/>
-    <mergeCell ref="DA2:DA7"/>
-    <mergeCell ref="DB2:DB7"/>
-    <mergeCell ref="DC2:DC7"/>
-    <mergeCell ref="DD2:DD7"/>
-    <mergeCell ref="DE2:DE7"/>
-    <mergeCell ref="CZ2:CZ7"/>
-    <mergeCell ref="DN2:DN7"/>
-    <mergeCell ref="DO2:DO7"/>
-    <mergeCell ref="DP2:DP7"/>
-    <mergeCell ref="DG2:DG7"/>
-    <mergeCell ref="DH2:DH7"/>
-    <mergeCell ref="DI2:DI7"/>
-    <mergeCell ref="DJ2:DJ7"/>
-    <mergeCell ref="DK2:DK7"/>
+  <mergeCells count="262">
+    <mergeCell ref="N1:Q1"/>
+    <mergeCell ref="BC8:BC9"/>
+    <mergeCell ref="BD8:BD9"/>
+    <mergeCell ref="BE8:BE9"/>
+    <mergeCell ref="AN8:AN9"/>
+    <mergeCell ref="AO8:AO9"/>
+    <mergeCell ref="AP8:AP9"/>
+    <mergeCell ref="AQ8:AQ9"/>
+    <mergeCell ref="AR8:AR9"/>
+    <mergeCell ref="AS8:AS9"/>
+    <mergeCell ref="AT8:AT9"/>
+    <mergeCell ref="AU8:AU9"/>
+    <mergeCell ref="AV8:AV9"/>
+    <mergeCell ref="BO8:BO9"/>
+    <mergeCell ref="BP8:BP9"/>
+    <mergeCell ref="BQ8:BQ9"/>
+    <mergeCell ref="BR8:BR9"/>
+    <mergeCell ref="BS8:BS9"/>
+    <mergeCell ref="BT8:BT9"/>
+    <mergeCell ref="BZ8:BZ9"/>
+    <mergeCell ref="CA8:CA9"/>
+    <mergeCell ref="BH8:BH9"/>
+    <mergeCell ref="BI8:BI9"/>
+    <mergeCell ref="BJ8:BJ9"/>
+    <mergeCell ref="BK8:BK9"/>
+    <mergeCell ref="BL8:BL9"/>
+    <mergeCell ref="BM8:BM9"/>
+    <mergeCell ref="CB8:CB9"/>
+    <mergeCell ref="CC8:CC9"/>
+    <mergeCell ref="CD8:CD9"/>
+    <mergeCell ref="CE8:CE9"/>
+    <mergeCell ref="CF8:CF9"/>
+    <mergeCell ref="CV8:CV9"/>
+    <mergeCell ref="BQ2:BQ7"/>
+    <mergeCell ref="BR2:BR7"/>
+    <mergeCell ref="BS2:BS7"/>
+    <mergeCell ref="BT2:BT7"/>
+    <mergeCell ref="BU2:BU7"/>
+    <mergeCell ref="BV2:BV7"/>
+    <mergeCell ref="CO8:CO9"/>
+    <mergeCell ref="CP8:CP9"/>
+    <mergeCell ref="CH2:CH7"/>
+    <mergeCell ref="CT8:CT9"/>
+    <mergeCell ref="CU8:CU9"/>
+    <mergeCell ref="CB2:CB7"/>
+    <mergeCell ref="CC2:CC7"/>
+    <mergeCell ref="CD2:CD7"/>
+    <mergeCell ref="CE2:CE7"/>
+    <mergeCell ref="CF2:CF7"/>
+    <mergeCell ref="CG2:CG7"/>
+    <mergeCell ref="CJ8:CJ9"/>
+    <mergeCell ref="E26:DT26"/>
+    <mergeCell ref="DF8:DF9"/>
+    <mergeCell ref="DQ8:DQ9"/>
+    <mergeCell ref="DR8:DR9"/>
+    <mergeCell ref="DS8:DS9"/>
+    <mergeCell ref="DT8:DT9"/>
+    <mergeCell ref="CY8:CY9"/>
+    <mergeCell ref="CZ8:CZ9"/>
+    <mergeCell ref="CM8:CM9"/>
+    <mergeCell ref="CW8:CW9"/>
+    <mergeCell ref="CX8:CX9"/>
+    <mergeCell ref="BU8:BU9"/>
+    <mergeCell ref="BV8:BV9"/>
+    <mergeCell ref="BW8:BW9"/>
+    <mergeCell ref="BF8:BF9"/>
+    <mergeCell ref="BG8:BG9"/>
+    <mergeCell ref="CG8:CG9"/>
+    <mergeCell ref="CH8:CH9"/>
+    <mergeCell ref="AW8:AW9"/>
+    <mergeCell ref="AX8:AX9"/>
+    <mergeCell ref="AY8:AY9"/>
+    <mergeCell ref="AZ8:AZ9"/>
+    <mergeCell ref="BA8:BA9"/>
+    <mergeCell ref="BB8:BB9"/>
+    <mergeCell ref="AE8:AE9"/>
+    <mergeCell ref="AF8:AF9"/>
+    <mergeCell ref="AG8:AG9"/>
+    <mergeCell ref="AH8:AH9"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AJ8:AJ9"/>
+    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="AL8:AL9"/>
+    <mergeCell ref="AM8:AM9"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="F2:F7"/>
+    <mergeCell ref="G2:G7"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="I2:I7"/>
+    <mergeCell ref="J2:J7"/>
+    <mergeCell ref="K2:K7"/>
+    <mergeCell ref="L2:L7"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="M2:M7"/>
+    <mergeCell ref="N2:N7"/>
+    <mergeCell ref="O2:O7"/>
+    <mergeCell ref="P2:P7"/>
+    <mergeCell ref="Q2:Q7"/>
+    <mergeCell ref="R2:R7"/>
+    <mergeCell ref="S2:S7"/>
+    <mergeCell ref="T2:T7"/>
+    <mergeCell ref="CN8:CN9"/>
+    <mergeCell ref="Y2:Y7"/>
+    <mergeCell ref="Z2:Z7"/>
+    <mergeCell ref="AA2:AA7"/>
+    <mergeCell ref="AB2:AB7"/>
+    <mergeCell ref="AC2:AC7"/>
+    <mergeCell ref="AD2:AD7"/>
+    <mergeCell ref="AE2:AE7"/>
+    <mergeCell ref="AH2:AH7"/>
+    <mergeCell ref="AI2:AI7"/>
+    <mergeCell ref="AJ2:AJ7"/>
+    <mergeCell ref="AK2:AK7"/>
+    <mergeCell ref="AL2:AL7"/>
+    <mergeCell ref="AM2:AM7"/>
+    <mergeCell ref="AN2:AN7"/>
+    <mergeCell ref="AO2:AO7"/>
+    <mergeCell ref="CW2:CW7"/>
+    <mergeCell ref="CU2:CU7"/>
+    <mergeCell ref="CV2:CV7"/>
+    <mergeCell ref="CQ2:CQ7"/>
+    <mergeCell ref="CR2:CR7"/>
+    <mergeCell ref="CS2:CS7"/>
+    <mergeCell ref="CT2:CT7"/>
+    <mergeCell ref="CI2:CI7"/>
+    <mergeCell ref="CJ2:CJ7"/>
+    <mergeCell ref="CK2:CK7"/>
+    <mergeCell ref="CL2:CL7"/>
+    <mergeCell ref="CM2:CM7"/>
+    <mergeCell ref="CN2:CN7"/>
+    <mergeCell ref="CO2:CO7"/>
+    <mergeCell ref="CP2:CP7"/>
+    <mergeCell ref="AG2:AG7"/>
+    <mergeCell ref="U2:U7"/>
+    <mergeCell ref="V2:V7"/>
+    <mergeCell ref="W2:W7"/>
+    <mergeCell ref="X2:X7"/>
+    <mergeCell ref="AF2:AF7"/>
+    <mergeCell ref="AX2:AX7"/>
+    <mergeCell ref="AY2:AY7"/>
+    <mergeCell ref="AZ2:AZ7"/>
+    <mergeCell ref="BL2:BL7"/>
+    <mergeCell ref="BA2:BA7"/>
+    <mergeCell ref="BB2:BB7"/>
+    <mergeCell ref="BC2:BC7"/>
+    <mergeCell ref="AP2:AP7"/>
+    <mergeCell ref="AQ2:AQ7"/>
+    <mergeCell ref="AR2:AR7"/>
+    <mergeCell ref="AS2:AS7"/>
+    <mergeCell ref="AT2:AT7"/>
+    <mergeCell ref="AU2:AU7"/>
+    <mergeCell ref="AV2:AV7"/>
+    <mergeCell ref="AW2:AW7"/>
+    <mergeCell ref="CK8:CK9"/>
+    <mergeCell ref="CL8:CL9"/>
+    <mergeCell ref="BX8:BX9"/>
+    <mergeCell ref="BY8:BY9"/>
+    <mergeCell ref="DL2:DL7"/>
+    <mergeCell ref="DM2:DM7"/>
+    <mergeCell ref="DF2:DF7"/>
+    <mergeCell ref="BD2:BD7"/>
+    <mergeCell ref="BE2:BE7"/>
+    <mergeCell ref="BF2:BF7"/>
+    <mergeCell ref="BG2:BG7"/>
+    <mergeCell ref="BM2:BM7"/>
+    <mergeCell ref="BN2:BN7"/>
+    <mergeCell ref="BO2:BO7"/>
+    <mergeCell ref="BP2:BP7"/>
+    <mergeCell ref="CA2:CA7"/>
+    <mergeCell ref="BW2:BW7"/>
+    <mergeCell ref="BX2:BX7"/>
+    <mergeCell ref="BY2:BY7"/>
+    <mergeCell ref="BZ2:BZ7"/>
+    <mergeCell ref="BH2:BH7"/>
+    <mergeCell ref="BI2:BI7"/>
+    <mergeCell ref="BJ2:BJ7"/>
+    <mergeCell ref="BK2:BK7"/>
     <mergeCell ref="F27:S27"/>
     <mergeCell ref="T27:AW27"/>
     <mergeCell ref="AX27:CD27"/>
@@ -5044,223 +5255,26 @@
     <mergeCell ref="CS8:CS9"/>
     <mergeCell ref="BN8:BN9"/>
     <mergeCell ref="CI8:CI9"/>
-    <mergeCell ref="CK8:CK9"/>
-    <mergeCell ref="CL8:CL9"/>
-    <mergeCell ref="BX8:BX9"/>
-    <mergeCell ref="BY8:BY9"/>
-    <mergeCell ref="DL2:DL7"/>
-    <mergeCell ref="DM2:DM7"/>
-    <mergeCell ref="DF2:DF7"/>
-    <mergeCell ref="BD2:BD7"/>
-    <mergeCell ref="BE2:BE7"/>
-    <mergeCell ref="BF2:BF7"/>
-    <mergeCell ref="BG2:BG7"/>
-    <mergeCell ref="BM2:BM7"/>
-    <mergeCell ref="BN2:BN7"/>
-    <mergeCell ref="BO2:BO7"/>
-    <mergeCell ref="BP2:BP7"/>
-    <mergeCell ref="CA2:CA7"/>
-    <mergeCell ref="BW2:BW7"/>
-    <mergeCell ref="BX2:BX7"/>
-    <mergeCell ref="BY2:BY7"/>
-    <mergeCell ref="BZ2:BZ7"/>
-    <mergeCell ref="BH2:BH7"/>
-    <mergeCell ref="BI2:BI7"/>
-    <mergeCell ref="BJ2:BJ7"/>
-    <mergeCell ref="BK2:BK7"/>
-    <mergeCell ref="BL2:BL7"/>
-    <mergeCell ref="BA2:BA7"/>
-    <mergeCell ref="BB2:BB7"/>
-    <mergeCell ref="BC2:BC7"/>
-    <mergeCell ref="AP2:AP7"/>
-    <mergeCell ref="AQ2:AQ7"/>
-    <mergeCell ref="AR2:AR7"/>
-    <mergeCell ref="AS2:AS7"/>
-    <mergeCell ref="AT2:AT7"/>
-    <mergeCell ref="AU2:AU7"/>
-    <mergeCell ref="AV2:AV7"/>
-    <mergeCell ref="AW2:AW7"/>
-    <mergeCell ref="AG2:AG7"/>
-    <mergeCell ref="U2:U7"/>
-    <mergeCell ref="V2:V7"/>
-    <mergeCell ref="W2:W7"/>
-    <mergeCell ref="X2:X7"/>
-    <mergeCell ref="AF2:AF7"/>
-    <mergeCell ref="AX2:AX7"/>
-    <mergeCell ref="AY2:AY7"/>
-    <mergeCell ref="AZ2:AZ7"/>
-    <mergeCell ref="CW2:CW7"/>
-    <mergeCell ref="CU2:CU7"/>
-    <mergeCell ref="CV2:CV7"/>
-    <mergeCell ref="CQ2:CQ7"/>
-    <mergeCell ref="CR2:CR7"/>
-    <mergeCell ref="CS2:CS7"/>
-    <mergeCell ref="CT2:CT7"/>
-    <mergeCell ref="CI2:CI7"/>
-    <mergeCell ref="CJ2:CJ7"/>
-    <mergeCell ref="CK2:CK7"/>
-    <mergeCell ref="CL2:CL7"/>
-    <mergeCell ref="CM2:CM7"/>
-    <mergeCell ref="CN2:CN7"/>
-    <mergeCell ref="CO2:CO7"/>
-    <mergeCell ref="CP2:CP7"/>
-    <mergeCell ref="M2:M7"/>
-    <mergeCell ref="N2:N7"/>
-    <mergeCell ref="O2:O7"/>
-    <mergeCell ref="P2:P7"/>
-    <mergeCell ref="Q2:Q7"/>
-    <mergeCell ref="R2:R7"/>
-    <mergeCell ref="S2:S7"/>
-    <mergeCell ref="T2:T7"/>
-    <mergeCell ref="CN8:CN9"/>
-    <mergeCell ref="Y2:Y7"/>
-    <mergeCell ref="Z2:Z7"/>
-    <mergeCell ref="AA2:AA7"/>
-    <mergeCell ref="AB2:AB7"/>
-    <mergeCell ref="AC2:AC7"/>
-    <mergeCell ref="AD2:AD7"/>
-    <mergeCell ref="AE2:AE7"/>
-    <mergeCell ref="AH2:AH7"/>
-    <mergeCell ref="AI2:AI7"/>
-    <mergeCell ref="AJ2:AJ7"/>
-    <mergeCell ref="AK2:AK7"/>
-    <mergeCell ref="AL2:AL7"/>
-    <mergeCell ref="AM2:AM7"/>
-    <mergeCell ref="AN2:AN7"/>
-    <mergeCell ref="AO2:AO7"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="F2:F7"/>
-    <mergeCell ref="G2:G7"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="I2:I7"/>
-    <mergeCell ref="J2:J7"/>
-    <mergeCell ref="K2:K7"/>
-    <mergeCell ref="L2:L7"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="AE8:AE9"/>
-    <mergeCell ref="AF8:AF9"/>
-    <mergeCell ref="AG8:AG9"/>
-    <mergeCell ref="AH8:AH9"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AJ8:AJ9"/>
-    <mergeCell ref="AK8:AK9"/>
-    <mergeCell ref="AL8:AL9"/>
-    <mergeCell ref="AM8:AM9"/>
-    <mergeCell ref="E26:DT26"/>
-    <mergeCell ref="DF8:DF9"/>
-    <mergeCell ref="DQ8:DQ9"/>
-    <mergeCell ref="DR8:DR9"/>
-    <mergeCell ref="DS8:DS9"/>
-    <mergeCell ref="DT8:DT9"/>
-    <mergeCell ref="CY8:CY9"/>
-    <mergeCell ref="CZ8:CZ9"/>
-    <mergeCell ref="CM8:CM9"/>
-    <mergeCell ref="CW8:CW9"/>
-    <mergeCell ref="CX8:CX9"/>
-    <mergeCell ref="BU8:BU9"/>
-    <mergeCell ref="BV8:BV9"/>
-    <mergeCell ref="BW8:BW9"/>
-    <mergeCell ref="BF8:BF9"/>
-    <mergeCell ref="BG8:BG9"/>
-    <mergeCell ref="CG8:CG9"/>
-    <mergeCell ref="CH8:CH9"/>
-    <mergeCell ref="AW8:AW9"/>
-    <mergeCell ref="AX8:AX9"/>
-    <mergeCell ref="AY8:AY9"/>
-    <mergeCell ref="AZ8:AZ9"/>
-    <mergeCell ref="BA8:BA9"/>
-    <mergeCell ref="BB8:BB9"/>
-    <mergeCell ref="CB8:CB9"/>
-    <mergeCell ref="CC8:CC9"/>
-    <mergeCell ref="CD8:CD9"/>
-    <mergeCell ref="CE8:CE9"/>
-    <mergeCell ref="CF8:CF9"/>
-    <mergeCell ref="CV8:CV9"/>
-    <mergeCell ref="BQ2:BQ7"/>
-    <mergeCell ref="BR2:BR7"/>
-    <mergeCell ref="BS2:BS7"/>
-    <mergeCell ref="BT2:BT7"/>
-    <mergeCell ref="BU2:BU7"/>
-    <mergeCell ref="BV2:BV7"/>
-    <mergeCell ref="CO8:CO9"/>
-    <mergeCell ref="CP8:CP9"/>
-    <mergeCell ref="CH2:CH7"/>
-    <mergeCell ref="CT8:CT9"/>
-    <mergeCell ref="CU8:CU9"/>
-    <mergeCell ref="CB2:CB7"/>
-    <mergeCell ref="CC2:CC7"/>
-    <mergeCell ref="CD2:CD7"/>
-    <mergeCell ref="CE2:CE7"/>
-    <mergeCell ref="CF2:CF7"/>
-    <mergeCell ref="CG2:CG7"/>
-    <mergeCell ref="CJ8:CJ9"/>
-    <mergeCell ref="BO8:BO9"/>
-    <mergeCell ref="BP8:BP9"/>
-    <mergeCell ref="BQ8:BQ9"/>
-    <mergeCell ref="BR8:BR9"/>
-    <mergeCell ref="BS8:BS9"/>
-    <mergeCell ref="BT8:BT9"/>
-    <mergeCell ref="BZ8:BZ9"/>
-    <mergeCell ref="CA8:CA9"/>
-    <mergeCell ref="BH8:BH9"/>
-    <mergeCell ref="BI8:BI9"/>
-    <mergeCell ref="BJ8:BJ9"/>
-    <mergeCell ref="BK8:BK9"/>
-    <mergeCell ref="BL8:BL9"/>
-    <mergeCell ref="BM8:BM9"/>
-    <mergeCell ref="BC8:BC9"/>
-    <mergeCell ref="BD8:BD9"/>
-    <mergeCell ref="BE8:BE9"/>
-    <mergeCell ref="AN8:AN9"/>
-    <mergeCell ref="AO8:AO9"/>
-    <mergeCell ref="AP8:AP9"/>
-    <mergeCell ref="AQ8:AQ9"/>
-    <mergeCell ref="AR8:AR9"/>
-    <mergeCell ref="AS8:AS9"/>
-    <mergeCell ref="AT8:AT9"/>
-    <mergeCell ref="AU8:AU9"/>
-    <mergeCell ref="AV8:AV9"/>
+    <mergeCell ref="DQ2:DQ7"/>
+    <mergeCell ref="DR2:DR7"/>
+    <mergeCell ref="DS2:DS7"/>
+    <mergeCell ref="DT2:DT7"/>
+    <mergeCell ref="CX2:CX7"/>
+    <mergeCell ref="CY2:CY7"/>
+    <mergeCell ref="DA2:DA7"/>
+    <mergeCell ref="DB2:DB7"/>
+    <mergeCell ref="DC2:DC7"/>
+    <mergeCell ref="DD2:DD7"/>
+    <mergeCell ref="DE2:DE7"/>
+    <mergeCell ref="CZ2:CZ7"/>
+    <mergeCell ref="DN2:DN7"/>
+    <mergeCell ref="DO2:DO7"/>
+    <mergeCell ref="DP2:DP7"/>
+    <mergeCell ref="DG2:DG7"/>
+    <mergeCell ref="DH2:DH7"/>
+    <mergeCell ref="DI2:DI7"/>
+    <mergeCell ref="DJ2:DJ7"/>
+    <mergeCell ref="DK2:DK7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -5293,7 +5307,7 @@
       <c r="H2" s="57"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="41" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="59" t="s">
@@ -5317,7 +5331,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="33"/>
+      <c r="A4" s="41"/>
       <c r="B4" s="61"/>
       <c r="C4" s="62"/>
       <c r="D4" s="64"/>

--- a/Journals/Angular ჟურნალი.xlsx
+++ b/Journals/Angular ჟურნალი.xlsx
@@ -542,19 +542,13 @@
     <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="2" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -562,6 +556,33 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -591,16 +612,7 @@
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -614,26 +626,14 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -896,34 +896,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="34"/>
-      <c r="F1" s="49">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="41"/>
+      <c r="F1" s="25">
         <v>4</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="49">
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="25">
         <v>4</v>
       </c>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="49">
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="25">
         <v>4</v>
       </c>
-      <c r="O1" s="50"/>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="23"/>
-      <c r="S1" s="23"/>
-      <c r="T1" s="23"/>
-      <c r="U1" s="23"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="27"/>
+      <c r="R1" s="25">
+        <v>4</v>
+      </c>
+      <c r="S1" s="26"/>
+      <c r="T1" s="26"/>
+      <c r="U1" s="27"/>
       <c r="V1" s="23"/>
       <c r="W1" s="23"/>
       <c r="X1" s="23"/>
@@ -1029,1313 +1031,1321 @@
       <c r="DT1" s="24"/>
       <c r="DU1" s="1">
         <f>SUM(F1:DT1)</f>
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:125" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="35"/>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="38" t="s">
+      <c r="A2" s="42"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="25">
+      <c r="F2" s="30">
         <v>46276</v>
       </c>
-      <c r="G2" s="25">
+      <c r="G2" s="30">
         <v>46276</v>
       </c>
-      <c r="H2" s="25">
+      <c r="H2" s="30">
         <v>46276</v>
       </c>
-      <c r="I2" s="25">
+      <c r="I2" s="30">
         <v>46276</v>
       </c>
-      <c r="J2" s="25">
+      <c r="J2" s="30">
         <v>46283</v>
       </c>
-      <c r="K2" s="25">
+      <c r="K2" s="30">
         <v>46283</v>
       </c>
-      <c r="L2" s="25">
+      <c r="L2" s="30">
         <v>46283</v>
       </c>
-      <c r="M2" s="25">
+      <c r="M2" s="30">
         <v>46283</v>
       </c>
-      <c r="N2" s="25">
+      <c r="N2" s="30">
         <v>46290</v>
       </c>
-      <c r="O2" s="25">
+      <c r="O2" s="30">
         <v>46290</v>
       </c>
-      <c r="P2" s="25">
+      <c r="P2" s="30">
         <v>46290</v>
       </c>
-      <c r="Q2" s="25">
+      <c r="Q2" s="30">
         <v>46290</v>
       </c>
-      <c r="R2" s="25"/>
-      <c r="S2" s="25"/>
-      <c r="T2" s="25"/>
-      <c r="U2" s="25"/>
-      <c r="V2" s="25"/>
-      <c r="W2" s="25"/>
-      <c r="X2" s="25"/>
-      <c r="Y2" s="25"/>
-      <c r="Z2" s="25"/>
-      <c r="AA2" s="25"/>
-      <c r="AB2" s="25"/>
-      <c r="AC2" s="25"/>
-      <c r="AD2" s="25"/>
-      <c r="AE2" s="25"/>
-      <c r="AF2" s="25"/>
-      <c r="AG2" s="25"/>
-      <c r="AH2" s="25"/>
-      <c r="AI2" s="25"/>
-      <c r="AJ2" s="25"/>
-      <c r="AK2" s="25"/>
-      <c r="AL2" s="25"/>
-      <c r="AM2" s="25"/>
-      <c r="AN2" s="25"/>
-      <c r="AO2" s="25"/>
-      <c r="AP2" s="25"/>
-      <c r="AQ2" s="25"/>
-      <c r="AR2" s="25"/>
-      <c r="AS2" s="25"/>
-      <c r="AT2" s="25"/>
-      <c r="AU2" s="25"/>
-      <c r="AV2" s="25"/>
-      <c r="AW2" s="25"/>
-      <c r="AX2" s="25"/>
-      <c r="AY2" s="25"/>
-      <c r="AZ2" s="25"/>
-      <c r="BA2" s="25"/>
-      <c r="BB2" s="25"/>
-      <c r="BC2" s="25"/>
-      <c r="BD2" s="25"/>
-      <c r="BE2" s="25"/>
-      <c r="BF2" s="25"/>
-      <c r="BG2" s="25"/>
-      <c r="BH2" s="25"/>
-      <c r="BI2" s="25"/>
-      <c r="BJ2" s="25"/>
-      <c r="BK2" s="25"/>
-      <c r="BL2" s="25"/>
-      <c r="BM2" s="25"/>
-      <c r="BN2" s="25"/>
-      <c r="BO2" s="25"/>
-      <c r="BP2" s="25"/>
-      <c r="BQ2" s="25"/>
-      <c r="BR2" s="25"/>
-      <c r="BS2" s="25"/>
-      <c r="BT2" s="25"/>
-      <c r="BU2" s="25"/>
-      <c r="BV2" s="25"/>
-      <c r="BW2" s="25"/>
-      <c r="BX2" s="25"/>
-      <c r="BY2" s="25"/>
-      <c r="BZ2" s="25"/>
-      <c r="CA2" s="25"/>
-      <c r="CB2" s="25"/>
-      <c r="CC2" s="25"/>
-      <c r="CD2" s="25"/>
-      <c r="CE2" s="25"/>
-      <c r="CF2" s="25"/>
-      <c r="CG2" s="25"/>
-      <c r="CH2" s="25"/>
-      <c r="CI2" s="25"/>
-      <c r="CJ2" s="25"/>
-      <c r="CK2" s="25"/>
-      <c r="CL2" s="25"/>
-      <c r="CM2" s="25"/>
-      <c r="CN2" s="25"/>
-      <c r="CO2" s="25"/>
-      <c r="CP2" s="25"/>
-      <c r="CQ2" s="25"/>
-      <c r="CR2" s="25"/>
-      <c r="CS2" s="25"/>
-      <c r="CT2" s="25"/>
-      <c r="CU2" s="25"/>
-      <c r="CV2" s="25"/>
-      <c r="CW2" s="25"/>
-      <c r="CX2" s="25"/>
-      <c r="CY2" s="25"/>
-      <c r="CZ2" s="25"/>
-      <c r="DA2" s="25"/>
-      <c r="DB2" s="25"/>
-      <c r="DC2" s="25"/>
-      <c r="DD2" s="25"/>
-      <c r="DE2" s="25"/>
-      <c r="DF2" s="25"/>
-      <c r="DG2" s="25"/>
-      <c r="DH2" s="25"/>
-      <c r="DI2" s="25"/>
-      <c r="DJ2" s="25"/>
-      <c r="DK2" s="25"/>
-      <c r="DL2" s="25"/>
-      <c r="DM2" s="25"/>
-      <c r="DN2" s="25"/>
-      <c r="DO2" s="25"/>
-      <c r="DP2" s="25"/>
-      <c r="DQ2" s="25"/>
-      <c r="DR2" s="25"/>
-      <c r="DS2" s="25"/>
-      <c r="DT2" s="25"/>
+      <c r="R2" s="30">
+        <v>46297</v>
+      </c>
+      <c r="S2" s="30">
+        <v>46297</v>
+      </c>
+      <c r="T2" s="30">
+        <v>46297</v>
+      </c>
+      <c r="U2" s="30">
+        <v>46297</v>
+      </c>
+      <c r="V2" s="30"/>
+      <c r="W2" s="30"/>
+      <c r="X2" s="30"/>
+      <c r="Y2" s="30"/>
+      <c r="Z2" s="30"/>
+      <c r="AA2" s="30"/>
+      <c r="AB2" s="30"/>
+      <c r="AC2" s="30"/>
+      <c r="AD2" s="30"/>
+      <c r="AE2" s="30"/>
+      <c r="AF2" s="30"/>
+      <c r="AG2" s="30"/>
+      <c r="AH2" s="30"/>
+      <c r="AI2" s="30"/>
+      <c r="AJ2" s="30"/>
+      <c r="AK2" s="30"/>
+      <c r="AL2" s="30"/>
+      <c r="AM2" s="30"/>
+      <c r="AN2" s="30"/>
+      <c r="AO2" s="30"/>
+      <c r="AP2" s="30"/>
+      <c r="AQ2" s="30"/>
+      <c r="AR2" s="30"/>
+      <c r="AS2" s="30"/>
+      <c r="AT2" s="30"/>
+      <c r="AU2" s="30"/>
+      <c r="AV2" s="30"/>
+      <c r="AW2" s="30"/>
+      <c r="AX2" s="30"/>
+      <c r="AY2" s="30"/>
+      <c r="AZ2" s="30"/>
+      <c r="BA2" s="30"/>
+      <c r="BB2" s="30"/>
+      <c r="BC2" s="30"/>
+      <c r="BD2" s="30"/>
+      <c r="BE2" s="30"/>
+      <c r="BF2" s="30"/>
+      <c r="BG2" s="30"/>
+      <c r="BH2" s="30"/>
+      <c r="BI2" s="30"/>
+      <c r="BJ2" s="30"/>
+      <c r="BK2" s="30"/>
+      <c r="BL2" s="30"/>
+      <c r="BM2" s="30"/>
+      <c r="BN2" s="30"/>
+      <c r="BO2" s="30"/>
+      <c r="BP2" s="30"/>
+      <c r="BQ2" s="30"/>
+      <c r="BR2" s="30"/>
+      <c r="BS2" s="30"/>
+      <c r="BT2" s="30"/>
+      <c r="BU2" s="30"/>
+      <c r="BV2" s="30"/>
+      <c r="BW2" s="30"/>
+      <c r="BX2" s="30"/>
+      <c r="BY2" s="30"/>
+      <c r="BZ2" s="30"/>
+      <c r="CA2" s="30"/>
+      <c r="CB2" s="30"/>
+      <c r="CC2" s="30"/>
+      <c r="CD2" s="30"/>
+      <c r="CE2" s="30"/>
+      <c r="CF2" s="30"/>
+      <c r="CG2" s="30"/>
+      <c r="CH2" s="30"/>
+      <c r="CI2" s="30"/>
+      <c r="CJ2" s="30"/>
+      <c r="CK2" s="30"/>
+      <c r="CL2" s="30"/>
+      <c r="CM2" s="30"/>
+      <c r="CN2" s="30"/>
+      <c r="CO2" s="30"/>
+      <c r="CP2" s="30"/>
+      <c r="CQ2" s="30"/>
+      <c r="CR2" s="30"/>
+      <c r="CS2" s="30"/>
+      <c r="CT2" s="30"/>
+      <c r="CU2" s="30"/>
+      <c r="CV2" s="30"/>
+      <c r="CW2" s="30"/>
+      <c r="CX2" s="30"/>
+      <c r="CY2" s="30"/>
+      <c r="CZ2" s="30"/>
+      <c r="DA2" s="30"/>
+      <c r="DB2" s="30"/>
+      <c r="DC2" s="30"/>
+      <c r="DD2" s="30"/>
+      <c r="DE2" s="30"/>
+      <c r="DF2" s="30"/>
+      <c r="DG2" s="30"/>
+      <c r="DH2" s="30"/>
+      <c r="DI2" s="30"/>
+      <c r="DJ2" s="30"/>
+      <c r="DK2" s="30"/>
+      <c r="DL2" s="30"/>
+      <c r="DM2" s="30"/>
+      <c r="DN2" s="30"/>
+      <c r="DO2" s="30"/>
+      <c r="DP2" s="30"/>
+      <c r="DQ2" s="30"/>
+      <c r="DR2" s="30"/>
+      <c r="DS2" s="30"/>
+      <c r="DT2" s="30"/>
     </row>
     <row r="3" spans="1:125" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="25"/>
-      <c r="R3" s="25"/>
-      <c r="S3" s="25"/>
-      <c r="T3" s="25"/>
-      <c r="U3" s="25"/>
-      <c r="V3" s="25"/>
-      <c r="W3" s="25"/>
-      <c r="X3" s="25"/>
-      <c r="Y3" s="25"/>
-      <c r="Z3" s="25"/>
-      <c r="AA3" s="25"/>
-      <c r="AB3" s="25"/>
-      <c r="AC3" s="25"/>
-      <c r="AD3" s="25"/>
-      <c r="AE3" s="25"/>
-      <c r="AF3" s="25"/>
-      <c r="AG3" s="25"/>
-      <c r="AH3" s="25"/>
-      <c r="AI3" s="25"/>
-      <c r="AJ3" s="25"/>
-      <c r="AK3" s="25"/>
-      <c r="AL3" s="25"/>
-      <c r="AM3" s="25"/>
-      <c r="AN3" s="25"/>
-      <c r="AO3" s="25"/>
-      <c r="AP3" s="25"/>
-      <c r="AQ3" s="25"/>
-      <c r="AR3" s="25"/>
-      <c r="AS3" s="25"/>
-      <c r="AT3" s="25"/>
-      <c r="AU3" s="25"/>
-      <c r="AV3" s="25"/>
-      <c r="AW3" s="25"/>
-      <c r="AX3" s="25"/>
-      <c r="AY3" s="25"/>
-      <c r="AZ3" s="25"/>
-      <c r="BA3" s="25"/>
-      <c r="BB3" s="25"/>
-      <c r="BC3" s="25"/>
-      <c r="BD3" s="25"/>
-      <c r="BE3" s="25"/>
-      <c r="BF3" s="25"/>
-      <c r="BG3" s="25"/>
-      <c r="BH3" s="25"/>
-      <c r="BI3" s="25"/>
-      <c r="BJ3" s="25"/>
-      <c r="BK3" s="25"/>
-      <c r="BL3" s="25"/>
-      <c r="BM3" s="25"/>
-      <c r="BN3" s="25"/>
-      <c r="BO3" s="25"/>
-      <c r="BP3" s="25"/>
-      <c r="BQ3" s="25"/>
-      <c r="BR3" s="25"/>
-      <c r="BS3" s="25"/>
-      <c r="BT3" s="25"/>
-      <c r="BU3" s="25"/>
-      <c r="BV3" s="25"/>
-      <c r="BW3" s="25"/>
-      <c r="BX3" s="25"/>
-      <c r="BY3" s="25"/>
-      <c r="BZ3" s="25"/>
-      <c r="CA3" s="25"/>
-      <c r="CB3" s="25"/>
-      <c r="CC3" s="25"/>
-      <c r="CD3" s="25"/>
-      <c r="CE3" s="25"/>
-      <c r="CF3" s="25"/>
-      <c r="CG3" s="25"/>
-      <c r="CH3" s="25"/>
-      <c r="CI3" s="25"/>
-      <c r="CJ3" s="25"/>
-      <c r="CK3" s="25"/>
-      <c r="CL3" s="25"/>
-      <c r="CM3" s="25"/>
-      <c r="CN3" s="25"/>
-      <c r="CO3" s="25"/>
-      <c r="CP3" s="25"/>
-      <c r="CQ3" s="25"/>
-      <c r="CR3" s="25"/>
-      <c r="CS3" s="25"/>
-      <c r="CT3" s="25"/>
-      <c r="CU3" s="25"/>
-      <c r="CV3" s="25"/>
-      <c r="CW3" s="25"/>
-      <c r="CX3" s="25"/>
-      <c r="CY3" s="25"/>
-      <c r="CZ3" s="25"/>
-      <c r="DA3" s="25"/>
-      <c r="DB3" s="25"/>
-      <c r="DC3" s="25"/>
-      <c r="DD3" s="25"/>
-      <c r="DE3" s="25"/>
-      <c r="DF3" s="25"/>
-      <c r="DG3" s="25"/>
-      <c r="DH3" s="25"/>
-      <c r="DI3" s="25"/>
-      <c r="DJ3" s="25"/>
-      <c r="DK3" s="25"/>
-      <c r="DL3" s="25"/>
-      <c r="DM3" s="25"/>
-      <c r="DN3" s="25"/>
-      <c r="DO3" s="25"/>
-      <c r="DP3" s="25"/>
-      <c r="DQ3" s="25"/>
-      <c r="DR3" s="25"/>
-      <c r="DS3" s="25"/>
-      <c r="DT3" s="25"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="30"/>
+      <c r="M3" s="30"/>
+      <c r="N3" s="30"/>
+      <c r="O3" s="30"/>
+      <c r="P3" s="30"/>
+      <c r="Q3" s="30"/>
+      <c r="R3" s="30"/>
+      <c r="S3" s="30"/>
+      <c r="T3" s="30"/>
+      <c r="U3" s="30"/>
+      <c r="V3" s="30"/>
+      <c r="W3" s="30"/>
+      <c r="X3" s="30"/>
+      <c r="Y3" s="30"/>
+      <c r="Z3" s="30"/>
+      <c r="AA3" s="30"/>
+      <c r="AB3" s="30"/>
+      <c r="AC3" s="30"/>
+      <c r="AD3" s="30"/>
+      <c r="AE3" s="30"/>
+      <c r="AF3" s="30"/>
+      <c r="AG3" s="30"/>
+      <c r="AH3" s="30"/>
+      <c r="AI3" s="30"/>
+      <c r="AJ3" s="30"/>
+      <c r="AK3" s="30"/>
+      <c r="AL3" s="30"/>
+      <c r="AM3" s="30"/>
+      <c r="AN3" s="30"/>
+      <c r="AO3" s="30"/>
+      <c r="AP3" s="30"/>
+      <c r="AQ3" s="30"/>
+      <c r="AR3" s="30"/>
+      <c r="AS3" s="30"/>
+      <c r="AT3" s="30"/>
+      <c r="AU3" s="30"/>
+      <c r="AV3" s="30"/>
+      <c r="AW3" s="30"/>
+      <c r="AX3" s="30"/>
+      <c r="AY3" s="30"/>
+      <c r="AZ3" s="30"/>
+      <c r="BA3" s="30"/>
+      <c r="BB3" s="30"/>
+      <c r="BC3" s="30"/>
+      <c r="BD3" s="30"/>
+      <c r="BE3" s="30"/>
+      <c r="BF3" s="30"/>
+      <c r="BG3" s="30"/>
+      <c r="BH3" s="30"/>
+      <c r="BI3" s="30"/>
+      <c r="BJ3" s="30"/>
+      <c r="BK3" s="30"/>
+      <c r="BL3" s="30"/>
+      <c r="BM3" s="30"/>
+      <c r="BN3" s="30"/>
+      <c r="BO3" s="30"/>
+      <c r="BP3" s="30"/>
+      <c r="BQ3" s="30"/>
+      <c r="BR3" s="30"/>
+      <c r="BS3" s="30"/>
+      <c r="BT3" s="30"/>
+      <c r="BU3" s="30"/>
+      <c r="BV3" s="30"/>
+      <c r="BW3" s="30"/>
+      <c r="BX3" s="30"/>
+      <c r="BY3" s="30"/>
+      <c r="BZ3" s="30"/>
+      <c r="CA3" s="30"/>
+      <c r="CB3" s="30"/>
+      <c r="CC3" s="30"/>
+      <c r="CD3" s="30"/>
+      <c r="CE3" s="30"/>
+      <c r="CF3" s="30"/>
+      <c r="CG3" s="30"/>
+      <c r="CH3" s="30"/>
+      <c r="CI3" s="30"/>
+      <c r="CJ3" s="30"/>
+      <c r="CK3" s="30"/>
+      <c r="CL3" s="30"/>
+      <c r="CM3" s="30"/>
+      <c r="CN3" s="30"/>
+      <c r="CO3" s="30"/>
+      <c r="CP3" s="30"/>
+      <c r="CQ3" s="30"/>
+      <c r="CR3" s="30"/>
+      <c r="CS3" s="30"/>
+      <c r="CT3" s="30"/>
+      <c r="CU3" s="30"/>
+      <c r="CV3" s="30"/>
+      <c r="CW3" s="30"/>
+      <c r="CX3" s="30"/>
+      <c r="CY3" s="30"/>
+      <c r="CZ3" s="30"/>
+      <c r="DA3" s="30"/>
+      <c r="DB3" s="30"/>
+      <c r="DC3" s="30"/>
+      <c r="DD3" s="30"/>
+      <c r="DE3" s="30"/>
+      <c r="DF3" s="30"/>
+      <c r="DG3" s="30"/>
+      <c r="DH3" s="30"/>
+      <c r="DI3" s="30"/>
+      <c r="DJ3" s="30"/>
+      <c r="DK3" s="30"/>
+      <c r="DL3" s="30"/>
+      <c r="DM3" s="30"/>
+      <c r="DN3" s="30"/>
+      <c r="DO3" s="30"/>
+      <c r="DP3" s="30"/>
+      <c r="DQ3" s="30"/>
+      <c r="DR3" s="30"/>
+      <c r="DS3" s="30"/>
+      <c r="DT3" s="30"/>
     </row>
     <row r="4" spans="1:125" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="42"/>
-      <c r="C4" s="43" t="s">
+      <c r="A4" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="48"/>
+      <c r="C4" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="44"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="25"/>
-      <c r="O4" s="25"/>
-      <c r="P4" s="25"/>
-      <c r="Q4" s="25"/>
-      <c r="R4" s="25"/>
-      <c r="S4" s="25"/>
-      <c r="T4" s="25"/>
-      <c r="U4" s="25"/>
-      <c r="V4" s="25"/>
-      <c r="W4" s="25"/>
-      <c r="X4" s="25"/>
-      <c r="Y4" s="25"/>
-      <c r="Z4" s="25"/>
-      <c r="AA4" s="25"/>
-      <c r="AB4" s="25"/>
-      <c r="AC4" s="25"/>
-      <c r="AD4" s="25"/>
-      <c r="AE4" s="25"/>
-      <c r="AF4" s="25"/>
-      <c r="AG4" s="25"/>
-      <c r="AH4" s="25"/>
-      <c r="AI4" s="25"/>
-      <c r="AJ4" s="25"/>
-      <c r="AK4" s="25"/>
-      <c r="AL4" s="25"/>
-      <c r="AM4" s="25"/>
-      <c r="AN4" s="25"/>
-      <c r="AO4" s="25"/>
-      <c r="AP4" s="25"/>
-      <c r="AQ4" s="25"/>
-      <c r="AR4" s="25"/>
-      <c r="AS4" s="25"/>
-      <c r="AT4" s="25"/>
-      <c r="AU4" s="25"/>
-      <c r="AV4" s="25"/>
-      <c r="AW4" s="25"/>
-      <c r="AX4" s="25"/>
-      <c r="AY4" s="25"/>
-      <c r="AZ4" s="25"/>
-      <c r="BA4" s="25"/>
-      <c r="BB4" s="25"/>
-      <c r="BC4" s="25"/>
-      <c r="BD4" s="25"/>
-      <c r="BE4" s="25"/>
-      <c r="BF4" s="25"/>
-      <c r="BG4" s="25"/>
-      <c r="BH4" s="25"/>
-      <c r="BI4" s="25"/>
-      <c r="BJ4" s="25"/>
-      <c r="BK4" s="25"/>
-      <c r="BL4" s="25"/>
-      <c r="BM4" s="25"/>
-      <c r="BN4" s="25"/>
-      <c r="BO4" s="25"/>
-      <c r="BP4" s="25"/>
-      <c r="BQ4" s="25"/>
-      <c r="BR4" s="25"/>
-      <c r="BS4" s="25"/>
-      <c r="BT4" s="25"/>
-      <c r="BU4" s="25"/>
-      <c r="BV4" s="25"/>
-      <c r="BW4" s="25"/>
-      <c r="BX4" s="25"/>
-      <c r="BY4" s="25"/>
-      <c r="BZ4" s="25"/>
-      <c r="CA4" s="25"/>
-      <c r="CB4" s="25"/>
-      <c r="CC4" s="25"/>
-      <c r="CD4" s="25"/>
-      <c r="CE4" s="25"/>
-      <c r="CF4" s="25"/>
-      <c r="CG4" s="25"/>
-      <c r="CH4" s="25"/>
-      <c r="CI4" s="25"/>
-      <c r="CJ4" s="25"/>
-      <c r="CK4" s="25"/>
-      <c r="CL4" s="25"/>
-      <c r="CM4" s="25"/>
-      <c r="CN4" s="25"/>
-      <c r="CO4" s="25"/>
-      <c r="CP4" s="25"/>
-      <c r="CQ4" s="25"/>
-      <c r="CR4" s="25"/>
-      <c r="CS4" s="25"/>
-      <c r="CT4" s="25"/>
-      <c r="CU4" s="25"/>
-      <c r="CV4" s="25"/>
-      <c r="CW4" s="25"/>
-      <c r="CX4" s="25"/>
-      <c r="CY4" s="25"/>
-      <c r="CZ4" s="25"/>
-      <c r="DA4" s="25"/>
-      <c r="DB4" s="25"/>
-      <c r="DC4" s="25"/>
-      <c r="DD4" s="25"/>
-      <c r="DE4" s="25"/>
-      <c r="DF4" s="25"/>
-      <c r="DG4" s="25"/>
-      <c r="DH4" s="25"/>
-      <c r="DI4" s="25"/>
-      <c r="DJ4" s="25"/>
-      <c r="DK4" s="25"/>
-      <c r="DL4" s="25"/>
-      <c r="DM4" s="25"/>
-      <c r="DN4" s="25"/>
-      <c r="DO4" s="25"/>
-      <c r="DP4" s="25"/>
-      <c r="DQ4" s="25"/>
-      <c r="DR4" s="25"/>
-      <c r="DS4" s="25"/>
-      <c r="DT4" s="25"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="30"/>
+      <c r="K4" s="30"/>
+      <c r="L4" s="30"/>
+      <c r="M4" s="30"/>
+      <c r="N4" s="30"/>
+      <c r="O4" s="30"/>
+      <c r="P4" s="30"/>
+      <c r="Q4" s="30"/>
+      <c r="R4" s="30"/>
+      <c r="S4" s="30"/>
+      <c r="T4" s="30"/>
+      <c r="U4" s="30"/>
+      <c r="V4" s="30"/>
+      <c r="W4" s="30"/>
+      <c r="X4" s="30"/>
+      <c r="Y4" s="30"/>
+      <c r="Z4" s="30"/>
+      <c r="AA4" s="30"/>
+      <c r="AB4" s="30"/>
+      <c r="AC4" s="30"/>
+      <c r="AD4" s="30"/>
+      <c r="AE4" s="30"/>
+      <c r="AF4" s="30"/>
+      <c r="AG4" s="30"/>
+      <c r="AH4" s="30"/>
+      <c r="AI4" s="30"/>
+      <c r="AJ4" s="30"/>
+      <c r="AK4" s="30"/>
+      <c r="AL4" s="30"/>
+      <c r="AM4" s="30"/>
+      <c r="AN4" s="30"/>
+      <c r="AO4" s="30"/>
+      <c r="AP4" s="30"/>
+      <c r="AQ4" s="30"/>
+      <c r="AR4" s="30"/>
+      <c r="AS4" s="30"/>
+      <c r="AT4" s="30"/>
+      <c r="AU4" s="30"/>
+      <c r="AV4" s="30"/>
+      <c r="AW4" s="30"/>
+      <c r="AX4" s="30"/>
+      <c r="AY4" s="30"/>
+      <c r="AZ4" s="30"/>
+      <c r="BA4" s="30"/>
+      <c r="BB4" s="30"/>
+      <c r="BC4" s="30"/>
+      <c r="BD4" s="30"/>
+      <c r="BE4" s="30"/>
+      <c r="BF4" s="30"/>
+      <c r="BG4" s="30"/>
+      <c r="BH4" s="30"/>
+      <c r="BI4" s="30"/>
+      <c r="BJ4" s="30"/>
+      <c r="BK4" s="30"/>
+      <c r="BL4" s="30"/>
+      <c r="BM4" s="30"/>
+      <c r="BN4" s="30"/>
+      <c r="BO4" s="30"/>
+      <c r="BP4" s="30"/>
+      <c r="BQ4" s="30"/>
+      <c r="BR4" s="30"/>
+      <c r="BS4" s="30"/>
+      <c r="BT4" s="30"/>
+      <c r="BU4" s="30"/>
+      <c r="BV4" s="30"/>
+      <c r="BW4" s="30"/>
+      <c r="BX4" s="30"/>
+      <c r="BY4" s="30"/>
+      <c r="BZ4" s="30"/>
+      <c r="CA4" s="30"/>
+      <c r="CB4" s="30"/>
+      <c r="CC4" s="30"/>
+      <c r="CD4" s="30"/>
+      <c r="CE4" s="30"/>
+      <c r="CF4" s="30"/>
+      <c r="CG4" s="30"/>
+      <c r="CH4" s="30"/>
+      <c r="CI4" s="30"/>
+      <c r="CJ4" s="30"/>
+      <c r="CK4" s="30"/>
+      <c r="CL4" s="30"/>
+      <c r="CM4" s="30"/>
+      <c r="CN4" s="30"/>
+      <c r="CO4" s="30"/>
+      <c r="CP4" s="30"/>
+      <c r="CQ4" s="30"/>
+      <c r="CR4" s="30"/>
+      <c r="CS4" s="30"/>
+      <c r="CT4" s="30"/>
+      <c r="CU4" s="30"/>
+      <c r="CV4" s="30"/>
+      <c r="CW4" s="30"/>
+      <c r="CX4" s="30"/>
+      <c r="CY4" s="30"/>
+      <c r="CZ4" s="30"/>
+      <c r="DA4" s="30"/>
+      <c r="DB4" s="30"/>
+      <c r="DC4" s="30"/>
+      <c r="DD4" s="30"/>
+      <c r="DE4" s="30"/>
+      <c r="DF4" s="30"/>
+      <c r="DG4" s="30"/>
+      <c r="DH4" s="30"/>
+      <c r="DI4" s="30"/>
+      <c r="DJ4" s="30"/>
+      <c r="DK4" s="30"/>
+      <c r="DL4" s="30"/>
+      <c r="DM4" s="30"/>
+      <c r="DN4" s="30"/>
+      <c r="DO4" s="30"/>
+      <c r="DP4" s="30"/>
+      <c r="DQ4" s="30"/>
+      <c r="DR4" s="30"/>
+      <c r="DS4" s="30"/>
+      <c r="DT4" s="30"/>
     </row>
     <row r="5" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="45" t="s">
+      <c r="A5" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="46">
+      <c r="B5" s="49"/>
+      <c r="C5" s="50">
         <v>60</v>
       </c>
-      <c r="D5" s="47"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="25"/>
-      <c r="N5" s="25"/>
-      <c r="O5" s="25"/>
-      <c r="P5" s="25"/>
-      <c r="Q5" s="25"/>
-      <c r="R5" s="25"/>
-      <c r="S5" s="25"/>
-      <c r="T5" s="25"/>
-      <c r="U5" s="25"/>
-      <c r="V5" s="25"/>
-      <c r="W5" s="25"/>
-      <c r="X5" s="25"/>
-      <c r="Y5" s="25"/>
-      <c r="Z5" s="25"/>
-      <c r="AA5" s="25"/>
-      <c r="AB5" s="25"/>
-      <c r="AC5" s="25"/>
-      <c r="AD5" s="25"/>
-      <c r="AE5" s="25"/>
-      <c r="AF5" s="25"/>
-      <c r="AG5" s="25"/>
-      <c r="AH5" s="25"/>
-      <c r="AI5" s="25"/>
-      <c r="AJ5" s="25"/>
-      <c r="AK5" s="25"/>
-      <c r="AL5" s="25"/>
-      <c r="AM5" s="25"/>
-      <c r="AN5" s="25"/>
-      <c r="AO5" s="25"/>
-      <c r="AP5" s="25"/>
-      <c r="AQ5" s="25"/>
-      <c r="AR5" s="25"/>
-      <c r="AS5" s="25"/>
-      <c r="AT5" s="25"/>
-      <c r="AU5" s="25"/>
-      <c r="AV5" s="25"/>
-      <c r="AW5" s="25"/>
-      <c r="AX5" s="25"/>
-      <c r="AY5" s="25"/>
-      <c r="AZ5" s="25"/>
-      <c r="BA5" s="25"/>
-      <c r="BB5" s="25"/>
-      <c r="BC5" s="25"/>
-      <c r="BD5" s="25"/>
-      <c r="BE5" s="25"/>
-      <c r="BF5" s="25"/>
-      <c r="BG5" s="25"/>
-      <c r="BH5" s="25"/>
-      <c r="BI5" s="25"/>
-      <c r="BJ5" s="25"/>
-      <c r="BK5" s="25"/>
-      <c r="BL5" s="25"/>
-      <c r="BM5" s="25"/>
-      <c r="BN5" s="25"/>
-      <c r="BO5" s="25"/>
-      <c r="BP5" s="25"/>
-      <c r="BQ5" s="25"/>
-      <c r="BR5" s="25"/>
-      <c r="BS5" s="25"/>
-      <c r="BT5" s="25"/>
-      <c r="BU5" s="25"/>
-      <c r="BV5" s="25"/>
-      <c r="BW5" s="25"/>
-      <c r="BX5" s="25"/>
-      <c r="BY5" s="25"/>
-      <c r="BZ5" s="25"/>
-      <c r="CA5" s="25"/>
-      <c r="CB5" s="25"/>
-      <c r="CC5" s="25"/>
-      <c r="CD5" s="25"/>
-      <c r="CE5" s="25"/>
-      <c r="CF5" s="25"/>
-      <c r="CG5" s="25"/>
-      <c r="CH5" s="25"/>
-      <c r="CI5" s="25"/>
-      <c r="CJ5" s="25"/>
-      <c r="CK5" s="25"/>
-      <c r="CL5" s="25"/>
-      <c r="CM5" s="25"/>
-      <c r="CN5" s="25"/>
-      <c r="CO5" s="25"/>
-      <c r="CP5" s="25"/>
-      <c r="CQ5" s="25"/>
-      <c r="CR5" s="25"/>
-      <c r="CS5" s="25"/>
-      <c r="CT5" s="25"/>
-      <c r="CU5" s="25"/>
-      <c r="CV5" s="25"/>
-      <c r="CW5" s="25"/>
-      <c r="CX5" s="25"/>
-      <c r="CY5" s="25"/>
-      <c r="CZ5" s="25"/>
-      <c r="DA5" s="25"/>
-      <c r="DB5" s="25"/>
-      <c r="DC5" s="25"/>
-      <c r="DD5" s="25"/>
-      <c r="DE5" s="25"/>
-      <c r="DF5" s="25"/>
-      <c r="DG5" s="25"/>
-      <c r="DH5" s="25"/>
-      <c r="DI5" s="25"/>
-      <c r="DJ5" s="25"/>
-      <c r="DK5" s="25"/>
-      <c r="DL5" s="25"/>
-      <c r="DM5" s="25"/>
-      <c r="DN5" s="25"/>
-      <c r="DO5" s="25"/>
-      <c r="DP5" s="25"/>
-      <c r="DQ5" s="25"/>
-      <c r="DR5" s="25"/>
-      <c r="DS5" s="25"/>
-      <c r="DT5" s="25"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="30"/>
+      <c r="L5" s="30"/>
+      <c r="M5" s="30"/>
+      <c r="N5" s="30"/>
+      <c r="O5" s="30"/>
+      <c r="P5" s="30"/>
+      <c r="Q5" s="30"/>
+      <c r="R5" s="30"/>
+      <c r="S5" s="30"/>
+      <c r="T5" s="30"/>
+      <c r="U5" s="30"/>
+      <c r="V5" s="30"/>
+      <c r="W5" s="30"/>
+      <c r="X5" s="30"/>
+      <c r="Y5" s="30"/>
+      <c r="Z5" s="30"/>
+      <c r="AA5" s="30"/>
+      <c r="AB5" s="30"/>
+      <c r="AC5" s="30"/>
+      <c r="AD5" s="30"/>
+      <c r="AE5" s="30"/>
+      <c r="AF5" s="30"/>
+      <c r="AG5" s="30"/>
+      <c r="AH5" s="30"/>
+      <c r="AI5" s="30"/>
+      <c r="AJ5" s="30"/>
+      <c r="AK5" s="30"/>
+      <c r="AL5" s="30"/>
+      <c r="AM5" s="30"/>
+      <c r="AN5" s="30"/>
+      <c r="AO5" s="30"/>
+      <c r="AP5" s="30"/>
+      <c r="AQ5" s="30"/>
+      <c r="AR5" s="30"/>
+      <c r="AS5" s="30"/>
+      <c r="AT5" s="30"/>
+      <c r="AU5" s="30"/>
+      <c r="AV5" s="30"/>
+      <c r="AW5" s="30"/>
+      <c r="AX5" s="30"/>
+      <c r="AY5" s="30"/>
+      <c r="AZ5" s="30"/>
+      <c r="BA5" s="30"/>
+      <c r="BB5" s="30"/>
+      <c r="BC5" s="30"/>
+      <c r="BD5" s="30"/>
+      <c r="BE5" s="30"/>
+      <c r="BF5" s="30"/>
+      <c r="BG5" s="30"/>
+      <c r="BH5" s="30"/>
+      <c r="BI5" s="30"/>
+      <c r="BJ5" s="30"/>
+      <c r="BK5" s="30"/>
+      <c r="BL5" s="30"/>
+      <c r="BM5" s="30"/>
+      <c r="BN5" s="30"/>
+      <c r="BO5" s="30"/>
+      <c r="BP5" s="30"/>
+      <c r="BQ5" s="30"/>
+      <c r="BR5" s="30"/>
+      <c r="BS5" s="30"/>
+      <c r="BT5" s="30"/>
+      <c r="BU5" s="30"/>
+      <c r="BV5" s="30"/>
+      <c r="BW5" s="30"/>
+      <c r="BX5" s="30"/>
+      <c r="BY5" s="30"/>
+      <c r="BZ5" s="30"/>
+      <c r="CA5" s="30"/>
+      <c r="CB5" s="30"/>
+      <c r="CC5" s="30"/>
+      <c r="CD5" s="30"/>
+      <c r="CE5" s="30"/>
+      <c r="CF5" s="30"/>
+      <c r="CG5" s="30"/>
+      <c r="CH5" s="30"/>
+      <c r="CI5" s="30"/>
+      <c r="CJ5" s="30"/>
+      <c r="CK5" s="30"/>
+      <c r="CL5" s="30"/>
+      <c r="CM5" s="30"/>
+      <c r="CN5" s="30"/>
+      <c r="CO5" s="30"/>
+      <c r="CP5" s="30"/>
+      <c r="CQ5" s="30"/>
+      <c r="CR5" s="30"/>
+      <c r="CS5" s="30"/>
+      <c r="CT5" s="30"/>
+      <c r="CU5" s="30"/>
+      <c r="CV5" s="30"/>
+      <c r="CW5" s="30"/>
+      <c r="CX5" s="30"/>
+      <c r="CY5" s="30"/>
+      <c r="CZ5" s="30"/>
+      <c r="DA5" s="30"/>
+      <c r="DB5" s="30"/>
+      <c r="DC5" s="30"/>
+      <c r="DD5" s="30"/>
+      <c r="DE5" s="30"/>
+      <c r="DF5" s="30"/>
+      <c r="DG5" s="30"/>
+      <c r="DH5" s="30"/>
+      <c r="DI5" s="30"/>
+      <c r="DJ5" s="30"/>
+      <c r="DK5" s="30"/>
+      <c r="DL5" s="30"/>
+      <c r="DM5" s="30"/>
+      <c r="DN5" s="30"/>
+      <c r="DO5" s="30"/>
+      <c r="DP5" s="30"/>
+      <c r="DQ5" s="30"/>
+      <c r="DR5" s="30"/>
+      <c r="DS5" s="30"/>
+      <c r="DT5" s="30"/>
     </row>
     <row r="6" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="45" t="s">
+      <c r="A6" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="46">
+      <c r="B6" s="49"/>
+      <c r="C6" s="50">
         <v>4</v>
       </c>
-      <c r="D6" s="47"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="25"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="25"/>
-      <c r="P6" s="25"/>
-      <c r="Q6" s="25"/>
-      <c r="R6" s="25"/>
-      <c r="S6" s="25"/>
-      <c r="T6" s="25"/>
-      <c r="U6" s="25"/>
-      <c r="V6" s="25"/>
-      <c r="W6" s="25"/>
-      <c r="X6" s="25"/>
-      <c r="Y6" s="25"/>
-      <c r="Z6" s="25"/>
-      <c r="AA6" s="25"/>
-      <c r="AB6" s="25"/>
-      <c r="AC6" s="25"/>
-      <c r="AD6" s="25"/>
-      <c r="AE6" s="25"/>
-      <c r="AF6" s="25"/>
-      <c r="AG6" s="25"/>
-      <c r="AH6" s="25"/>
-      <c r="AI6" s="25"/>
-      <c r="AJ6" s="25"/>
-      <c r="AK6" s="25"/>
-      <c r="AL6" s="25"/>
-      <c r="AM6" s="25"/>
-      <c r="AN6" s="25"/>
-      <c r="AO6" s="25"/>
-      <c r="AP6" s="25"/>
-      <c r="AQ6" s="25"/>
-      <c r="AR6" s="25"/>
-      <c r="AS6" s="25"/>
-      <c r="AT6" s="25"/>
-      <c r="AU6" s="25"/>
-      <c r="AV6" s="25"/>
-      <c r="AW6" s="25"/>
-      <c r="AX6" s="25"/>
-      <c r="AY6" s="25"/>
-      <c r="AZ6" s="25"/>
-      <c r="BA6" s="25"/>
-      <c r="BB6" s="25"/>
-      <c r="BC6" s="25"/>
-      <c r="BD6" s="25"/>
-      <c r="BE6" s="25"/>
-      <c r="BF6" s="25"/>
-      <c r="BG6" s="25"/>
-      <c r="BH6" s="25"/>
-      <c r="BI6" s="25"/>
-      <c r="BJ6" s="25"/>
-      <c r="BK6" s="25"/>
-      <c r="BL6" s="25"/>
-      <c r="BM6" s="25"/>
-      <c r="BN6" s="25"/>
-      <c r="BO6" s="25"/>
-      <c r="BP6" s="25"/>
-      <c r="BQ6" s="25"/>
-      <c r="BR6" s="25"/>
-      <c r="BS6" s="25"/>
-      <c r="BT6" s="25"/>
-      <c r="BU6" s="25"/>
-      <c r="BV6" s="25"/>
-      <c r="BW6" s="25"/>
-      <c r="BX6" s="25"/>
-      <c r="BY6" s="25"/>
-      <c r="BZ6" s="25"/>
-      <c r="CA6" s="25"/>
-      <c r="CB6" s="25"/>
-      <c r="CC6" s="25"/>
-      <c r="CD6" s="25"/>
-      <c r="CE6" s="25"/>
-      <c r="CF6" s="25"/>
-      <c r="CG6" s="25"/>
-      <c r="CH6" s="25"/>
-      <c r="CI6" s="25"/>
-      <c r="CJ6" s="25"/>
-      <c r="CK6" s="25"/>
-      <c r="CL6" s="25"/>
-      <c r="CM6" s="25"/>
-      <c r="CN6" s="25"/>
-      <c r="CO6" s="25"/>
-      <c r="CP6" s="25"/>
-      <c r="CQ6" s="25"/>
-      <c r="CR6" s="25"/>
-      <c r="CS6" s="25"/>
-      <c r="CT6" s="25"/>
-      <c r="CU6" s="25"/>
-      <c r="CV6" s="25"/>
-      <c r="CW6" s="25"/>
-      <c r="CX6" s="25"/>
-      <c r="CY6" s="25"/>
-      <c r="CZ6" s="25"/>
-      <c r="DA6" s="25"/>
-      <c r="DB6" s="25"/>
-      <c r="DC6" s="25"/>
-      <c r="DD6" s="25"/>
-      <c r="DE6" s="25"/>
-      <c r="DF6" s="25"/>
-      <c r="DG6" s="25"/>
-      <c r="DH6" s="25"/>
-      <c r="DI6" s="25"/>
-      <c r="DJ6" s="25"/>
-      <c r="DK6" s="25"/>
-      <c r="DL6" s="25"/>
-      <c r="DM6" s="25"/>
-      <c r="DN6" s="25"/>
-      <c r="DO6" s="25"/>
-      <c r="DP6" s="25"/>
-      <c r="DQ6" s="25"/>
-      <c r="DR6" s="25"/>
-      <c r="DS6" s="25"/>
-      <c r="DT6" s="25"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="30"/>
+      <c r="L6" s="30"/>
+      <c r="M6" s="30"/>
+      <c r="N6" s="30"/>
+      <c r="O6" s="30"/>
+      <c r="P6" s="30"/>
+      <c r="Q6" s="30"/>
+      <c r="R6" s="30"/>
+      <c r="S6" s="30"/>
+      <c r="T6" s="30"/>
+      <c r="U6" s="30"/>
+      <c r="V6" s="30"/>
+      <c r="W6" s="30"/>
+      <c r="X6" s="30"/>
+      <c r="Y6" s="30"/>
+      <c r="Z6" s="30"/>
+      <c r="AA6" s="30"/>
+      <c r="AB6" s="30"/>
+      <c r="AC6" s="30"/>
+      <c r="AD6" s="30"/>
+      <c r="AE6" s="30"/>
+      <c r="AF6" s="30"/>
+      <c r="AG6" s="30"/>
+      <c r="AH6" s="30"/>
+      <c r="AI6" s="30"/>
+      <c r="AJ6" s="30"/>
+      <c r="AK6" s="30"/>
+      <c r="AL6" s="30"/>
+      <c r="AM6" s="30"/>
+      <c r="AN6" s="30"/>
+      <c r="AO6" s="30"/>
+      <c r="AP6" s="30"/>
+      <c r="AQ6" s="30"/>
+      <c r="AR6" s="30"/>
+      <c r="AS6" s="30"/>
+      <c r="AT6" s="30"/>
+      <c r="AU6" s="30"/>
+      <c r="AV6" s="30"/>
+      <c r="AW6" s="30"/>
+      <c r="AX6" s="30"/>
+      <c r="AY6" s="30"/>
+      <c r="AZ6" s="30"/>
+      <c r="BA6" s="30"/>
+      <c r="BB6" s="30"/>
+      <c r="BC6" s="30"/>
+      <c r="BD6" s="30"/>
+      <c r="BE6" s="30"/>
+      <c r="BF6" s="30"/>
+      <c r="BG6" s="30"/>
+      <c r="BH6" s="30"/>
+      <c r="BI6" s="30"/>
+      <c r="BJ6" s="30"/>
+      <c r="BK6" s="30"/>
+      <c r="BL6" s="30"/>
+      <c r="BM6" s="30"/>
+      <c r="BN6" s="30"/>
+      <c r="BO6" s="30"/>
+      <c r="BP6" s="30"/>
+      <c r="BQ6" s="30"/>
+      <c r="BR6" s="30"/>
+      <c r="BS6" s="30"/>
+      <c r="BT6" s="30"/>
+      <c r="BU6" s="30"/>
+      <c r="BV6" s="30"/>
+      <c r="BW6" s="30"/>
+      <c r="BX6" s="30"/>
+      <c r="BY6" s="30"/>
+      <c r="BZ6" s="30"/>
+      <c r="CA6" s="30"/>
+      <c r="CB6" s="30"/>
+      <c r="CC6" s="30"/>
+      <c r="CD6" s="30"/>
+      <c r="CE6" s="30"/>
+      <c r="CF6" s="30"/>
+      <c r="CG6" s="30"/>
+      <c r="CH6" s="30"/>
+      <c r="CI6" s="30"/>
+      <c r="CJ6" s="30"/>
+      <c r="CK6" s="30"/>
+      <c r="CL6" s="30"/>
+      <c r="CM6" s="30"/>
+      <c r="CN6" s="30"/>
+      <c r="CO6" s="30"/>
+      <c r="CP6" s="30"/>
+      <c r="CQ6" s="30"/>
+      <c r="CR6" s="30"/>
+      <c r="CS6" s="30"/>
+      <c r="CT6" s="30"/>
+      <c r="CU6" s="30"/>
+      <c r="CV6" s="30"/>
+      <c r="CW6" s="30"/>
+      <c r="CX6" s="30"/>
+      <c r="CY6" s="30"/>
+      <c r="CZ6" s="30"/>
+      <c r="DA6" s="30"/>
+      <c r="DB6" s="30"/>
+      <c r="DC6" s="30"/>
+      <c r="DD6" s="30"/>
+      <c r="DE6" s="30"/>
+      <c r="DF6" s="30"/>
+      <c r="DG6" s="30"/>
+      <c r="DH6" s="30"/>
+      <c r="DI6" s="30"/>
+      <c r="DJ6" s="30"/>
+      <c r="DK6" s="30"/>
+      <c r="DL6" s="30"/>
+      <c r="DM6" s="30"/>
+      <c r="DN6" s="30"/>
+      <c r="DO6" s="30"/>
+      <c r="DP6" s="30"/>
+      <c r="DQ6" s="30"/>
+      <c r="DR6" s="30"/>
+      <c r="DS6" s="30"/>
+      <c r="DT6" s="30"/>
     </row>
     <row r="7" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="46">
+      <c r="B7" s="52"/>
+      <c r="C7" s="50">
         <v>11</v>
       </c>
-      <c r="D7" s="47"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26"/>
-      <c r="N7" s="26"/>
-      <c r="O7" s="26"/>
-      <c r="P7" s="26"/>
-      <c r="Q7" s="26"/>
-      <c r="R7" s="26"/>
-      <c r="S7" s="26"/>
-      <c r="T7" s="26"/>
-      <c r="U7" s="26"/>
-      <c r="V7" s="26"/>
-      <c r="W7" s="26"/>
-      <c r="X7" s="26"/>
-      <c r="Y7" s="26"/>
-      <c r="Z7" s="26"/>
-      <c r="AA7" s="26"/>
-      <c r="AB7" s="26"/>
-      <c r="AC7" s="26"/>
-      <c r="AD7" s="26"/>
-      <c r="AE7" s="26"/>
-      <c r="AF7" s="26"/>
-      <c r="AG7" s="26"/>
-      <c r="AH7" s="26"/>
-      <c r="AI7" s="26"/>
-      <c r="AJ7" s="26"/>
-      <c r="AK7" s="26"/>
-      <c r="AL7" s="26"/>
-      <c r="AM7" s="26"/>
-      <c r="AN7" s="26"/>
-      <c r="AO7" s="26"/>
-      <c r="AP7" s="26"/>
-      <c r="AQ7" s="26"/>
-      <c r="AR7" s="26"/>
-      <c r="AS7" s="26"/>
-      <c r="AT7" s="26"/>
-      <c r="AU7" s="26"/>
-      <c r="AV7" s="26"/>
-      <c r="AW7" s="26"/>
-      <c r="AX7" s="26"/>
-      <c r="AY7" s="26"/>
-      <c r="AZ7" s="26"/>
-      <c r="BA7" s="26"/>
-      <c r="BB7" s="26"/>
-      <c r="BC7" s="26"/>
-      <c r="BD7" s="26"/>
-      <c r="BE7" s="26"/>
-      <c r="BF7" s="26"/>
-      <c r="BG7" s="26"/>
-      <c r="BH7" s="26"/>
-      <c r="BI7" s="26"/>
-      <c r="BJ7" s="26"/>
-      <c r="BK7" s="26"/>
-      <c r="BL7" s="26"/>
-      <c r="BM7" s="26"/>
-      <c r="BN7" s="26"/>
-      <c r="BO7" s="26"/>
-      <c r="BP7" s="26"/>
-      <c r="BQ7" s="26"/>
-      <c r="BR7" s="26"/>
-      <c r="BS7" s="26"/>
-      <c r="BT7" s="26"/>
-      <c r="BU7" s="26"/>
-      <c r="BV7" s="26"/>
-      <c r="BW7" s="26"/>
-      <c r="BX7" s="26"/>
-      <c r="BY7" s="26"/>
-      <c r="BZ7" s="26"/>
-      <c r="CA7" s="26"/>
-      <c r="CB7" s="26"/>
-      <c r="CC7" s="26"/>
-      <c r="CD7" s="26"/>
-      <c r="CE7" s="26"/>
-      <c r="CF7" s="26"/>
-      <c r="CG7" s="26"/>
-      <c r="CH7" s="26"/>
-      <c r="CI7" s="26"/>
-      <c r="CJ7" s="26"/>
-      <c r="CK7" s="26"/>
-      <c r="CL7" s="26"/>
-      <c r="CM7" s="26"/>
-      <c r="CN7" s="26"/>
-      <c r="CO7" s="26"/>
-      <c r="CP7" s="26"/>
-      <c r="CQ7" s="26"/>
-      <c r="CR7" s="26"/>
-      <c r="CS7" s="26"/>
-      <c r="CT7" s="26"/>
-      <c r="CU7" s="26"/>
-      <c r="CV7" s="26"/>
-      <c r="CW7" s="26"/>
-      <c r="CX7" s="26"/>
-      <c r="CY7" s="26"/>
-      <c r="CZ7" s="26"/>
-      <c r="DA7" s="26"/>
-      <c r="DB7" s="26"/>
-      <c r="DC7" s="26"/>
-      <c r="DD7" s="26"/>
-      <c r="DE7" s="26"/>
-      <c r="DF7" s="26"/>
-      <c r="DG7" s="26"/>
-      <c r="DH7" s="26"/>
-      <c r="DI7" s="26"/>
-      <c r="DJ7" s="26"/>
-      <c r="DK7" s="26"/>
-      <c r="DL7" s="26"/>
-      <c r="DM7" s="26"/>
-      <c r="DN7" s="26"/>
-      <c r="DO7" s="26"/>
-      <c r="DP7" s="26"/>
-      <c r="DQ7" s="26"/>
-      <c r="DR7" s="26"/>
-      <c r="DS7" s="26"/>
-      <c r="DT7" s="26"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="47"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="31"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="31"/>
+      <c r="O7" s="31"/>
+      <c r="P7" s="31"/>
+      <c r="Q7" s="31"/>
+      <c r="R7" s="31"/>
+      <c r="S7" s="31"/>
+      <c r="T7" s="31"/>
+      <c r="U7" s="31"/>
+      <c r="V7" s="31"/>
+      <c r="W7" s="31"/>
+      <c r="X7" s="31"/>
+      <c r="Y7" s="31"/>
+      <c r="Z7" s="31"/>
+      <c r="AA7" s="31"/>
+      <c r="AB7" s="31"/>
+      <c r="AC7" s="31"/>
+      <c r="AD7" s="31"/>
+      <c r="AE7" s="31"/>
+      <c r="AF7" s="31"/>
+      <c r="AG7" s="31"/>
+      <c r="AH7" s="31"/>
+      <c r="AI7" s="31"/>
+      <c r="AJ7" s="31"/>
+      <c r="AK7" s="31"/>
+      <c r="AL7" s="31"/>
+      <c r="AM7" s="31"/>
+      <c r="AN7" s="31"/>
+      <c r="AO7" s="31"/>
+      <c r="AP7" s="31"/>
+      <c r="AQ7" s="31"/>
+      <c r="AR7" s="31"/>
+      <c r="AS7" s="31"/>
+      <c r="AT7" s="31"/>
+      <c r="AU7" s="31"/>
+      <c r="AV7" s="31"/>
+      <c r="AW7" s="31"/>
+      <c r="AX7" s="31"/>
+      <c r="AY7" s="31"/>
+      <c r="AZ7" s="31"/>
+      <c r="BA7" s="31"/>
+      <c r="BB7" s="31"/>
+      <c r="BC7" s="31"/>
+      <c r="BD7" s="31"/>
+      <c r="BE7" s="31"/>
+      <c r="BF7" s="31"/>
+      <c r="BG7" s="31"/>
+      <c r="BH7" s="31"/>
+      <c r="BI7" s="31"/>
+      <c r="BJ7" s="31"/>
+      <c r="BK7" s="31"/>
+      <c r="BL7" s="31"/>
+      <c r="BM7" s="31"/>
+      <c r="BN7" s="31"/>
+      <c r="BO7" s="31"/>
+      <c r="BP7" s="31"/>
+      <c r="BQ7" s="31"/>
+      <c r="BR7" s="31"/>
+      <c r="BS7" s="31"/>
+      <c r="BT7" s="31"/>
+      <c r="BU7" s="31"/>
+      <c r="BV7" s="31"/>
+      <c r="BW7" s="31"/>
+      <c r="BX7" s="31"/>
+      <c r="BY7" s="31"/>
+      <c r="BZ7" s="31"/>
+      <c r="CA7" s="31"/>
+      <c r="CB7" s="31"/>
+      <c r="CC7" s="31"/>
+      <c r="CD7" s="31"/>
+      <c r="CE7" s="31"/>
+      <c r="CF7" s="31"/>
+      <c r="CG7" s="31"/>
+      <c r="CH7" s="31"/>
+      <c r="CI7" s="31"/>
+      <c r="CJ7" s="31"/>
+      <c r="CK7" s="31"/>
+      <c r="CL7" s="31"/>
+      <c r="CM7" s="31"/>
+      <c r="CN7" s="31"/>
+      <c r="CO7" s="31"/>
+      <c r="CP7" s="31"/>
+      <c r="CQ7" s="31"/>
+      <c r="CR7" s="31"/>
+      <c r="CS7" s="31"/>
+      <c r="CT7" s="31"/>
+      <c r="CU7" s="31"/>
+      <c r="CV7" s="31"/>
+      <c r="CW7" s="31"/>
+      <c r="CX7" s="31"/>
+      <c r="CY7" s="31"/>
+      <c r="CZ7" s="31"/>
+      <c r="DA7" s="31"/>
+      <c r="DB7" s="31"/>
+      <c r="DC7" s="31"/>
+      <c r="DD7" s="31"/>
+      <c r="DE7" s="31"/>
+      <c r="DF7" s="31"/>
+      <c r="DG7" s="31"/>
+      <c r="DH7" s="31"/>
+      <c r="DI7" s="31"/>
+      <c r="DJ7" s="31"/>
+      <c r="DK7" s="31"/>
+      <c r="DL7" s="31"/>
+      <c r="DM7" s="31"/>
+      <c r="DN7" s="31"/>
+      <c r="DO7" s="31"/>
+      <c r="DP7" s="31"/>
+      <c r="DQ7" s="31"/>
+      <c r="DR7" s="31"/>
+      <c r="DS7" s="31"/>
+      <c r="DT7" s="31"/>
     </row>
     <row r="8" spans="1:125" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="52"/>
-      <c r="C8" s="53">
+      <c r="B8" s="34"/>
+      <c r="C8" s="32">
         <f>SUM(C5:D7)</f>
         <v>75</v>
       </c>
-      <c r="D8" s="44"/>
+      <c r="D8" s="35"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="30">
-        <v>1</v>
-      </c>
-      <c r="G8" s="30">
+      <c r="F8" s="28">
+        <v>1</v>
+      </c>
+      <c r="G8" s="28">
         <v>2</v>
       </c>
-      <c r="H8" s="30">
+      <c r="H8" s="28">
         <v>3</v>
       </c>
-      <c r="I8" s="30">
+      <c r="I8" s="28">
         <v>4</v>
       </c>
-      <c r="J8" s="30">
+      <c r="J8" s="28">
         <v>5</v>
       </c>
-      <c r="K8" s="30">
+      <c r="K8" s="28">
         <v>6</v>
       </c>
-      <c r="L8" s="30">
+      <c r="L8" s="28">
         <v>7</v>
       </c>
-      <c r="M8" s="30">
+      <c r="M8" s="28">
         <v>8</v>
       </c>
-      <c r="N8" s="30">
+      <c r="N8" s="28">
         <v>9</v>
       </c>
-      <c r="O8" s="30">
+      <c r="O8" s="28">
         <v>10</v>
       </c>
-      <c r="P8" s="30">
+      <c r="P8" s="28">
         <v>11</v>
       </c>
-      <c r="Q8" s="30">
+      <c r="Q8" s="28">
         <v>12</v>
       </c>
-      <c r="R8" s="30">
+      <c r="R8" s="28">
         <v>13</v>
       </c>
-      <c r="S8" s="30">
+      <c r="S8" s="28">
         <v>14</v>
       </c>
-      <c r="T8" s="30">
+      <c r="T8" s="28">
         <v>15</v>
       </c>
-      <c r="U8" s="30">
+      <c r="U8" s="28">
         <v>16</v>
       </c>
-      <c r="V8" s="30">
+      <c r="V8" s="28">
         <v>17</v>
       </c>
-      <c r="W8" s="30">
+      <c r="W8" s="28">
         <v>18</v>
       </c>
-      <c r="X8" s="30">
+      <c r="X8" s="28">
         <v>19</v>
       </c>
-      <c r="Y8" s="30">
+      <c r="Y8" s="28">
         <v>20</v>
       </c>
-      <c r="Z8" s="30">
+      <c r="Z8" s="28">
         <v>21</v>
       </c>
-      <c r="AA8" s="30">
+      <c r="AA8" s="28">
         <v>22</v>
       </c>
-      <c r="AB8" s="30">
+      <c r="AB8" s="28">
         <v>23</v>
       </c>
-      <c r="AC8" s="30">
+      <c r="AC8" s="28">
         <v>24</v>
       </c>
-      <c r="AD8" s="30">
+      <c r="AD8" s="28">
         <v>25</v>
       </c>
-      <c r="AE8" s="30">
+      <c r="AE8" s="28">
         <v>26</v>
       </c>
-      <c r="AF8" s="30">
+      <c r="AF8" s="28">
         <v>27</v>
       </c>
-      <c r="AG8" s="30">
+      <c r="AG8" s="28">
         <v>28</v>
       </c>
-      <c r="AH8" s="30">
+      <c r="AH8" s="28">
         <v>29</v>
       </c>
-      <c r="AI8" s="30">
+      <c r="AI8" s="28">
         <v>30</v>
       </c>
-      <c r="AJ8" s="30">
+      <c r="AJ8" s="28">
         <v>31</v>
       </c>
-      <c r="AK8" s="30">
+      <c r="AK8" s="28">
         <v>32</v>
       </c>
-      <c r="AL8" s="30">
+      <c r="AL8" s="28">
         <v>33</v>
       </c>
-      <c r="AM8" s="30">
+      <c r="AM8" s="28">
         <v>34</v>
       </c>
-      <c r="AN8" s="30">
+      <c r="AN8" s="28">
         <v>35</v>
       </c>
-      <c r="AO8" s="30">
+      <c r="AO8" s="28">
         <v>36</v>
       </c>
-      <c r="AP8" s="30">
+      <c r="AP8" s="28">
         <v>37</v>
       </c>
-      <c r="AQ8" s="30">
+      <c r="AQ8" s="28">
         <v>38</v>
       </c>
-      <c r="AR8" s="30">
+      <c r="AR8" s="28">
         <v>39</v>
       </c>
-      <c r="AS8" s="30">
+      <c r="AS8" s="28">
         <v>40</v>
       </c>
-      <c r="AT8" s="30">
+      <c r="AT8" s="28">
         <v>41</v>
       </c>
-      <c r="AU8" s="30">
+      <c r="AU8" s="28">
         <v>42</v>
       </c>
-      <c r="AV8" s="30">
+      <c r="AV8" s="28">
         <v>43</v>
       </c>
-      <c r="AW8" s="30">
+      <c r="AW8" s="28">
         <v>44</v>
       </c>
-      <c r="AX8" s="30">
+      <c r="AX8" s="28">
         <v>45</v>
       </c>
-      <c r="AY8" s="30">
+      <c r="AY8" s="28">
         <v>46</v>
       </c>
-      <c r="AZ8" s="30">
+      <c r="AZ8" s="28">
         <v>47</v>
       </c>
-      <c r="BA8" s="30">
+      <c r="BA8" s="28">
         <v>48</v>
       </c>
-      <c r="BB8" s="30">
+      <c r="BB8" s="28">
         <v>49</v>
       </c>
-      <c r="BC8" s="30">
+      <c r="BC8" s="28">
         <v>50</v>
       </c>
-      <c r="BD8" s="30">
+      <c r="BD8" s="28">
         <v>51</v>
       </c>
-      <c r="BE8" s="30">
+      <c r="BE8" s="28">
         <v>52</v>
       </c>
-      <c r="BF8" s="30">
+      <c r="BF8" s="28">
         <v>53</v>
       </c>
-      <c r="BG8" s="30">
+      <c r="BG8" s="28">
         <v>54</v>
       </c>
-      <c r="BH8" s="30">
+      <c r="BH8" s="28">
         <v>55</v>
       </c>
-      <c r="BI8" s="30">
+      <c r="BI8" s="28">
         <v>56</v>
       </c>
-      <c r="BJ8" s="30">
+      <c r="BJ8" s="28">
         <v>57</v>
       </c>
-      <c r="BK8" s="30">
+      <c r="BK8" s="28">
         <v>58</v>
       </c>
-      <c r="BL8" s="30">
+      <c r="BL8" s="28">
         <v>59</v>
       </c>
-      <c r="BM8" s="30">
+      <c r="BM8" s="28">
         <v>60</v>
       </c>
-      <c r="BN8" s="30">
+      <c r="BN8" s="28">
         <v>61</v>
       </c>
-      <c r="BO8" s="30">
+      <c r="BO8" s="28">
         <v>62</v>
       </c>
-      <c r="BP8" s="30">
+      <c r="BP8" s="28">
         <v>63</v>
       </c>
-      <c r="BQ8" s="30">
+      <c r="BQ8" s="28">
         <v>64</v>
       </c>
-      <c r="BR8" s="30">
+      <c r="BR8" s="28">
         <v>65</v>
       </c>
-      <c r="BS8" s="30">
+      <c r="BS8" s="28">
         <v>66</v>
       </c>
-      <c r="BT8" s="30">
+      <c r="BT8" s="28">
         <v>67</v>
       </c>
-      <c r="BU8" s="30">
+      <c r="BU8" s="28">
         <v>68</v>
       </c>
-      <c r="BV8" s="30">
+      <c r="BV8" s="28">
         <v>69</v>
       </c>
-      <c r="BW8" s="30">
+      <c r="BW8" s="28">
         <v>70</v>
       </c>
-      <c r="BX8" s="30">
+      <c r="BX8" s="28">
         <v>71</v>
       </c>
-      <c r="BY8" s="30">
+      <c r="BY8" s="28">
         <v>72</v>
       </c>
-      <c r="BZ8" s="30">
+      <c r="BZ8" s="28">
         <v>73</v>
       </c>
-      <c r="CA8" s="30">
+      <c r="CA8" s="28">
         <v>74</v>
       </c>
-      <c r="CB8" s="30">
+      <c r="CB8" s="28">
         <v>75</v>
       </c>
-      <c r="CC8" s="30">
+      <c r="CC8" s="28">
         <v>76</v>
       </c>
-      <c r="CD8" s="30">
+      <c r="CD8" s="28">
         <v>77</v>
       </c>
-      <c r="CE8" s="30">
+      <c r="CE8" s="28">
         <v>78</v>
       </c>
-      <c r="CF8" s="30">
+      <c r="CF8" s="28">
         <v>79</v>
       </c>
-      <c r="CG8" s="30">
+      <c r="CG8" s="28">
         <v>80</v>
       </c>
-      <c r="CH8" s="30">
+      <c r="CH8" s="28">
         <v>81</v>
       </c>
-      <c r="CI8" s="30">
+      <c r="CI8" s="28">
         <v>82</v>
       </c>
-      <c r="CJ8" s="30">
+      <c r="CJ8" s="28">
         <v>83</v>
       </c>
-      <c r="CK8" s="30">
+      <c r="CK8" s="28">
         <v>84</v>
       </c>
-      <c r="CL8" s="30">
+      <c r="CL8" s="28">
         <v>85</v>
       </c>
-      <c r="CM8" s="30">
+      <c r="CM8" s="28">
         <v>86</v>
       </c>
-      <c r="CN8" s="30">
+      <c r="CN8" s="28">
         <v>87</v>
       </c>
-      <c r="CO8" s="30">
+      <c r="CO8" s="28">
         <v>88</v>
       </c>
-      <c r="CP8" s="30">
+      <c r="CP8" s="28">
         <v>89</v>
       </c>
-      <c r="CQ8" s="30">
+      <c r="CQ8" s="28">
         <v>90</v>
       </c>
-      <c r="CR8" s="30">
+      <c r="CR8" s="28">
         <v>91</v>
       </c>
-      <c r="CS8" s="30">
+      <c r="CS8" s="28">
         <v>92</v>
       </c>
-      <c r="CT8" s="30">
+      <c r="CT8" s="28">
         <v>93</v>
       </c>
-      <c r="CU8" s="30">
+      <c r="CU8" s="28">
         <v>94</v>
       </c>
-      <c r="CV8" s="30">
+      <c r="CV8" s="28">
         <v>95</v>
       </c>
-      <c r="CW8" s="30">
+      <c r="CW8" s="28">
         <v>96</v>
       </c>
-      <c r="CX8" s="30">
+      <c r="CX8" s="28">
         <v>97</v>
       </c>
-      <c r="CY8" s="30">
+      <c r="CY8" s="28">
         <v>98</v>
       </c>
-      <c r="CZ8" s="30">
+      <c r="CZ8" s="28">
         <v>99</v>
       </c>
-      <c r="DA8" s="30">
+      <c r="DA8" s="28">
         <v>100</v>
       </c>
-      <c r="DB8" s="30">
+      <c r="DB8" s="28">
         <v>101</v>
       </c>
-      <c r="DC8" s="30">
+      <c r="DC8" s="28">
         <v>102</v>
       </c>
-      <c r="DD8" s="30">
+      <c r="DD8" s="28">
         <v>103</v>
       </c>
-      <c r="DE8" s="30">
+      <c r="DE8" s="28">
         <v>104</v>
       </c>
-      <c r="DF8" s="30">
+      <c r="DF8" s="28">
         <v>105</v>
       </c>
-      <c r="DG8" s="30">
+      <c r="DG8" s="28">
         <v>106</v>
       </c>
-      <c r="DH8" s="30">
+      <c r="DH8" s="28">
         <v>107</v>
       </c>
-      <c r="DI8" s="30">
+      <c r="DI8" s="28">
         <v>108</v>
       </c>
-      <c r="DJ8" s="30">
+      <c r="DJ8" s="28">
         <v>109</v>
       </c>
-      <c r="DK8" s="30">
+      <c r="DK8" s="28">
         <v>110</v>
       </c>
-      <c r="DL8" s="30">
+      <c r="DL8" s="28">
         <v>111</v>
       </c>
-      <c r="DM8" s="30">
+      <c r="DM8" s="28">
         <v>112</v>
       </c>
-      <c r="DN8" s="30">
+      <c r="DN8" s="28">
         <v>113</v>
       </c>
-      <c r="DO8" s="30">
+      <c r="DO8" s="28">
         <v>114</v>
       </c>
-      <c r="DP8" s="30">
+      <c r="DP8" s="28">
         <v>115</v>
       </c>
-      <c r="DQ8" s="30">
+      <c r="DQ8" s="28">
         <v>116</v>
       </c>
-      <c r="DR8" s="30">
+      <c r="DR8" s="28">
         <v>117</v>
       </c>
-      <c r="DS8" s="30">
+      <c r="DS8" s="28">
         <v>118</v>
       </c>
-      <c r="DT8" s="30">
+      <c r="DT8" s="28">
         <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="41" t="s">
+      <c r="A9" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="54" t="s">
+      <c r="B9" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="55" t="s">
+      <c r="C9" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="54"/>
+      <c r="D9" s="37"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="31"/>
-      <c r="M9" s="31"/>
-      <c r="N9" s="31"/>
-      <c r="O9" s="31"/>
-      <c r="P9" s="31"/>
-      <c r="Q9" s="31"/>
-      <c r="R9" s="31"/>
-      <c r="S9" s="31"/>
-      <c r="T9" s="31"/>
-      <c r="U9" s="31"/>
-      <c r="V9" s="31"/>
-      <c r="W9" s="31"/>
-      <c r="X9" s="31"/>
-      <c r="Y9" s="31"/>
-      <c r="Z9" s="31"/>
-      <c r="AA9" s="31"/>
-      <c r="AB9" s="31"/>
-      <c r="AC9" s="31"/>
-      <c r="AD9" s="31"/>
-      <c r="AE9" s="31"/>
-      <c r="AF9" s="31"/>
-      <c r="AG9" s="31"/>
-      <c r="AH9" s="31"/>
-      <c r="AI9" s="31"/>
-      <c r="AJ9" s="31"/>
-      <c r="AK9" s="31"/>
-      <c r="AL9" s="31"/>
-      <c r="AM9" s="31"/>
-      <c r="AN9" s="31"/>
-      <c r="AO9" s="31"/>
-      <c r="AP9" s="31"/>
-      <c r="AQ9" s="31"/>
-      <c r="AR9" s="31"/>
-      <c r="AS9" s="31"/>
-      <c r="AT9" s="31"/>
-      <c r="AU9" s="31"/>
-      <c r="AV9" s="31"/>
-      <c r="AW9" s="31"/>
-      <c r="AX9" s="31"/>
-      <c r="AY9" s="31"/>
-      <c r="AZ9" s="31"/>
-      <c r="BA9" s="31"/>
-      <c r="BB9" s="31"/>
-      <c r="BC9" s="31"/>
-      <c r="BD9" s="31"/>
-      <c r="BE9" s="31"/>
-      <c r="BF9" s="31"/>
-      <c r="BG9" s="31"/>
-      <c r="BH9" s="31"/>
-      <c r="BI9" s="31"/>
-      <c r="BJ9" s="31"/>
-      <c r="BK9" s="31"/>
-      <c r="BL9" s="31"/>
-      <c r="BM9" s="31"/>
-      <c r="BN9" s="31"/>
-      <c r="BO9" s="31"/>
-      <c r="BP9" s="31"/>
-      <c r="BQ9" s="31"/>
-      <c r="BR9" s="31"/>
-      <c r="BS9" s="31"/>
-      <c r="BT9" s="31"/>
-      <c r="BU9" s="31"/>
-      <c r="BV9" s="31"/>
-      <c r="BW9" s="31"/>
-      <c r="BX9" s="31"/>
-      <c r="BY9" s="31"/>
-      <c r="BZ9" s="31"/>
-      <c r="CA9" s="31"/>
-      <c r="CB9" s="31"/>
-      <c r="CC9" s="31"/>
-      <c r="CD9" s="31"/>
-      <c r="CE9" s="31"/>
-      <c r="CF9" s="31"/>
-      <c r="CG9" s="31"/>
-      <c r="CH9" s="31"/>
-      <c r="CI9" s="31"/>
-      <c r="CJ9" s="31"/>
-      <c r="CK9" s="31"/>
-      <c r="CL9" s="31"/>
-      <c r="CM9" s="31"/>
-      <c r="CN9" s="31"/>
-      <c r="CO9" s="31"/>
-      <c r="CP9" s="31"/>
-      <c r="CQ9" s="31"/>
-      <c r="CR9" s="31"/>
-      <c r="CS9" s="31"/>
-      <c r="CT9" s="31"/>
-      <c r="CU9" s="31"/>
-      <c r="CV9" s="31"/>
-      <c r="CW9" s="31"/>
-      <c r="CX9" s="31"/>
-      <c r="CY9" s="31"/>
-      <c r="CZ9" s="31"/>
-      <c r="DA9" s="31"/>
-      <c r="DB9" s="31"/>
-      <c r="DC9" s="31"/>
-      <c r="DD9" s="31"/>
-      <c r="DE9" s="31"/>
-      <c r="DF9" s="31"/>
-      <c r="DG9" s="31"/>
-      <c r="DH9" s="31"/>
-      <c r="DI9" s="31"/>
-      <c r="DJ9" s="31"/>
-      <c r="DK9" s="31"/>
-      <c r="DL9" s="31"/>
-      <c r="DM9" s="31"/>
-      <c r="DN9" s="31"/>
-      <c r="DO9" s="31"/>
-      <c r="DP9" s="31"/>
-      <c r="DQ9" s="31"/>
-      <c r="DR9" s="31"/>
-      <c r="DS9" s="31"/>
-      <c r="DT9" s="31"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="29"/>
+      <c r="M9" s="29"/>
+      <c r="N9" s="29"/>
+      <c r="O9" s="29"/>
+      <c r="P9" s="29"/>
+      <c r="Q9" s="29"/>
+      <c r="R9" s="29"/>
+      <c r="S9" s="29"/>
+      <c r="T9" s="29"/>
+      <c r="U9" s="29"/>
+      <c r="V9" s="29"/>
+      <c r="W9" s="29"/>
+      <c r="X9" s="29"/>
+      <c r="Y9" s="29"/>
+      <c r="Z9" s="29"/>
+      <c r="AA9" s="29"/>
+      <c r="AB9" s="29"/>
+      <c r="AC9" s="29"/>
+      <c r="AD9" s="29"/>
+      <c r="AE9" s="29"/>
+      <c r="AF9" s="29"/>
+      <c r="AG9" s="29"/>
+      <c r="AH9" s="29"/>
+      <c r="AI9" s="29"/>
+      <c r="AJ9" s="29"/>
+      <c r="AK9" s="29"/>
+      <c r="AL9" s="29"/>
+      <c r="AM9" s="29"/>
+      <c r="AN9" s="29"/>
+      <c r="AO9" s="29"/>
+      <c r="AP9" s="29"/>
+      <c r="AQ9" s="29"/>
+      <c r="AR9" s="29"/>
+      <c r="AS9" s="29"/>
+      <c r="AT9" s="29"/>
+      <c r="AU9" s="29"/>
+      <c r="AV9" s="29"/>
+      <c r="AW9" s="29"/>
+      <c r="AX9" s="29"/>
+      <c r="AY9" s="29"/>
+      <c r="AZ9" s="29"/>
+      <c r="BA9" s="29"/>
+      <c r="BB9" s="29"/>
+      <c r="BC9" s="29"/>
+      <c r="BD9" s="29"/>
+      <c r="BE9" s="29"/>
+      <c r="BF9" s="29"/>
+      <c r="BG9" s="29"/>
+      <c r="BH9" s="29"/>
+      <c r="BI9" s="29"/>
+      <c r="BJ9" s="29"/>
+      <c r="BK9" s="29"/>
+      <c r="BL9" s="29"/>
+      <c r="BM9" s="29"/>
+      <c r="BN9" s="29"/>
+      <c r="BO9" s="29"/>
+      <c r="BP9" s="29"/>
+      <c r="BQ9" s="29"/>
+      <c r="BR9" s="29"/>
+      <c r="BS9" s="29"/>
+      <c r="BT9" s="29"/>
+      <c r="BU9" s="29"/>
+      <c r="BV9" s="29"/>
+      <c r="BW9" s="29"/>
+      <c r="BX9" s="29"/>
+      <c r="BY9" s="29"/>
+      <c r="BZ9" s="29"/>
+      <c r="CA9" s="29"/>
+      <c r="CB9" s="29"/>
+      <c r="CC9" s="29"/>
+      <c r="CD9" s="29"/>
+      <c r="CE9" s="29"/>
+      <c r="CF9" s="29"/>
+      <c r="CG9" s="29"/>
+      <c r="CH9" s="29"/>
+      <c r="CI9" s="29"/>
+      <c r="CJ9" s="29"/>
+      <c r="CK9" s="29"/>
+      <c r="CL9" s="29"/>
+      <c r="CM9" s="29"/>
+      <c r="CN9" s="29"/>
+      <c r="CO9" s="29"/>
+      <c r="CP9" s="29"/>
+      <c r="CQ9" s="29"/>
+      <c r="CR9" s="29"/>
+      <c r="CS9" s="29"/>
+      <c r="CT9" s="29"/>
+      <c r="CU9" s="29"/>
+      <c r="CV9" s="29"/>
+      <c r="CW9" s="29"/>
+      <c r="CX9" s="29"/>
+      <c r="CY9" s="29"/>
+      <c r="CZ9" s="29"/>
+      <c r="DA9" s="29"/>
+      <c r="DB9" s="29"/>
+      <c r="DC9" s="29"/>
+      <c r="DD9" s="29"/>
+      <c r="DE9" s="29"/>
+      <c r="DF9" s="29"/>
+      <c r="DG9" s="29"/>
+      <c r="DH9" s="29"/>
+      <c r="DI9" s="29"/>
+      <c r="DJ9" s="29"/>
+      <c r="DK9" s="29"/>
+      <c r="DL9" s="29"/>
+      <c r="DM9" s="29"/>
+      <c r="DN9" s="29"/>
+      <c r="DO9" s="29"/>
+      <c r="DP9" s="29"/>
+      <c r="DQ9" s="29"/>
+      <c r="DR9" s="29"/>
+      <c r="DS9" s="29"/>
+      <c r="DT9" s="29"/>
     </row>
     <row r="10" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="41"/>
-      <c r="B10" s="54"/>
+      <c r="A10" s="36"/>
+      <c r="B10" s="37"/>
       <c r="C10" s="6"/>
       <c r="D10" s="4" t="s">
         <v>10</v>
@@ -2713,11 +2723,11 @@
       </c>
       <c r="D11" s="11">
         <f t="shared" ref="D11:D26" si="0">COUNT(F11:DT11)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11" s="15">
         <f>D11/C5</f>
-        <v>0</v>
+        <v>3.3333333333333333E-2</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
@@ -2733,8 +2743,12 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
+      <c r="R11" s="3">
+        <v>0</v>
+      </c>
+      <c r="S11" s="3">
+        <v>0</v>
+      </c>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
@@ -2853,11 +2867,11 @@
       </c>
       <c r="D12" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12" s="15">
         <f>D12/C5</f>
-        <v>0</v>
+        <v>3.3333333333333333E-2</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
@@ -2871,8 +2885,12 @@
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
+      <c r="R12" s="3">
+        <v>0</v>
+      </c>
+      <c r="S12" s="3">
+        <v>0</v>
+      </c>
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
       <c r="V12" s="3"/>
@@ -2991,11 +3009,11 @@
       </c>
       <c r="D13" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E13" s="15">
         <f>D13/C5</f>
-        <v>0</v>
+        <v>3.3333333333333333E-2</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
@@ -3009,8 +3027,12 @@
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
       <c r="V13" s="3"/>
@@ -3129,11 +3151,11 @@
       </c>
       <c r="D14" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E14" s="15">
         <f>D14/C5</f>
-        <v>0</v>
+        <v>3.3333333333333333E-2</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
@@ -3147,8 +3169,12 @@
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
       <c r="T14" s="3"/>
       <c r="U14" s="3"/>
       <c r="V14" s="3"/>
@@ -3267,11 +3293,11 @@
       </c>
       <c r="D15" s="11">
         <f>COUNT(F15:DT15)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15" s="15">
         <f>D15/C5</f>
-        <v>0</v>
+        <v>3.3333333333333333E-2</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
@@ -3285,8 +3311,12 @@
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
-      <c r="S15" s="3"/>
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
       <c r="T15" s="3"/>
       <c r="U15" s="3"/>
       <c r="V15" s="3"/>
@@ -3405,11 +3435,11 @@
       </c>
       <c r="D16" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
         <f>D16/C5</f>
-        <v>0</v>
+        <v>3.3333333333333333E-2</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
@@ -3423,8 +3453,12 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
+      <c r="R16" s="3">
+        <v>0</v>
+      </c>
+      <c r="S16" s="3">
+        <v>0</v>
+      </c>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
@@ -3685,11 +3719,11 @@
       </c>
       <c r="D18" s="11">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
         <f>D18/C5</f>
-        <v>0.05</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="F18" s="3">
         <v>0</v>
@@ -3709,8 +3743,12 @@
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
+      <c r="R18" s="3">
+        <v>0</v>
+      </c>
+      <c r="S18" s="3">
+        <v>0</v>
+      </c>
       <c r="T18" s="3"/>
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
@@ -4744,255 +4782,255 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E26" s="53"/>
-      <c r="F26" s="43"/>
-      <c r="G26" s="43"/>
-      <c r="H26" s="43"/>
-      <c r="I26" s="43"/>
-      <c r="J26" s="43"/>
-      <c r="K26" s="43"/>
-      <c r="L26" s="43"/>
-      <c r="M26" s="43"/>
-      <c r="N26" s="43"/>
-      <c r="O26" s="43"/>
-      <c r="P26" s="43"/>
-      <c r="Q26" s="43"/>
-      <c r="R26" s="43"/>
-      <c r="S26" s="43"/>
-      <c r="T26" s="43"/>
-      <c r="U26" s="43"/>
-      <c r="V26" s="43"/>
-      <c r="W26" s="43"/>
-      <c r="X26" s="43"/>
-      <c r="Y26" s="43"/>
-      <c r="Z26" s="43"/>
-      <c r="AA26" s="43"/>
-      <c r="AB26" s="43"/>
-      <c r="AC26" s="43"/>
-      <c r="AD26" s="43"/>
-      <c r="AE26" s="43"/>
-      <c r="AF26" s="43"/>
-      <c r="AG26" s="43"/>
-      <c r="AH26" s="43"/>
-      <c r="AI26" s="43"/>
-      <c r="AJ26" s="43"/>
-      <c r="AK26" s="43"/>
-      <c r="AL26" s="43"/>
-      <c r="AM26" s="43"/>
-      <c r="AN26" s="43"/>
-      <c r="AO26" s="43"/>
-      <c r="AP26" s="43"/>
-      <c r="AQ26" s="43"/>
-      <c r="AR26" s="43"/>
-      <c r="AS26" s="43"/>
-      <c r="AT26" s="43"/>
-      <c r="AU26" s="43"/>
-      <c r="AV26" s="43"/>
-      <c r="AW26" s="43"/>
-      <c r="AX26" s="43"/>
-      <c r="AY26" s="43"/>
-      <c r="AZ26" s="43"/>
-      <c r="BA26" s="43"/>
-      <c r="BB26" s="43"/>
-      <c r="BC26" s="43"/>
-      <c r="BD26" s="43"/>
-      <c r="BE26" s="43"/>
-      <c r="BF26" s="43"/>
-      <c r="BG26" s="43"/>
-      <c r="BH26" s="43"/>
-      <c r="BI26" s="43"/>
-      <c r="BJ26" s="43"/>
-      <c r="BK26" s="43"/>
-      <c r="BL26" s="43"/>
-      <c r="BM26" s="43"/>
-      <c r="BN26" s="43"/>
-      <c r="BO26" s="43"/>
-      <c r="BP26" s="43"/>
-      <c r="BQ26" s="43"/>
-      <c r="BR26" s="43"/>
-      <c r="BS26" s="43"/>
-      <c r="BT26" s="43"/>
-      <c r="BU26" s="43"/>
-      <c r="BV26" s="43"/>
-      <c r="BW26" s="43"/>
-      <c r="BX26" s="43"/>
-      <c r="BY26" s="43"/>
-      <c r="BZ26" s="43"/>
-      <c r="CA26" s="43"/>
-      <c r="CB26" s="43"/>
-      <c r="CC26" s="43"/>
-      <c r="CD26" s="43"/>
-      <c r="CE26" s="43"/>
-      <c r="CF26" s="43"/>
-      <c r="CG26" s="43"/>
-      <c r="CH26" s="43"/>
-      <c r="CI26" s="43"/>
-      <c r="CJ26" s="43"/>
-      <c r="CK26" s="43"/>
-      <c r="CL26" s="43"/>
-      <c r="CM26" s="43"/>
-      <c r="CN26" s="43"/>
-      <c r="CO26" s="43"/>
-      <c r="CP26" s="43"/>
-      <c r="CQ26" s="43"/>
-      <c r="CR26" s="43"/>
-      <c r="CS26" s="43"/>
-      <c r="CT26" s="43"/>
-      <c r="CU26" s="43"/>
-      <c r="CV26" s="43"/>
-      <c r="CW26" s="43"/>
-      <c r="CX26" s="43"/>
-      <c r="CY26" s="43"/>
-      <c r="CZ26" s="43"/>
-      <c r="DA26" s="43"/>
-      <c r="DB26" s="43"/>
-      <c r="DC26" s="43"/>
-      <c r="DD26" s="43"/>
-      <c r="DE26" s="43"/>
-      <c r="DF26" s="43"/>
-      <c r="DG26" s="43"/>
-      <c r="DH26" s="43"/>
-      <c r="DI26" s="43"/>
-      <c r="DJ26" s="43"/>
-      <c r="DK26" s="43"/>
-      <c r="DL26" s="43"/>
-      <c r="DM26" s="43"/>
-      <c r="DN26" s="43"/>
-      <c r="DO26" s="43"/>
-      <c r="DP26" s="43"/>
-      <c r="DQ26" s="43"/>
-      <c r="DR26" s="43"/>
-      <c r="DS26" s="43"/>
-      <c r="DT26" s="43"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="33"/>
+      <c r="L26" s="33"/>
+      <c r="M26" s="33"/>
+      <c r="N26" s="33"/>
+      <c r="O26" s="33"/>
+      <c r="P26" s="33"/>
+      <c r="Q26" s="33"/>
+      <c r="R26" s="33"/>
+      <c r="S26" s="33"/>
+      <c r="T26" s="33"/>
+      <c r="U26" s="33"/>
+      <c r="V26" s="33"/>
+      <c r="W26" s="33"/>
+      <c r="X26" s="33"/>
+      <c r="Y26" s="33"/>
+      <c r="Z26" s="33"/>
+      <c r="AA26" s="33"/>
+      <c r="AB26" s="33"/>
+      <c r="AC26" s="33"/>
+      <c r="AD26" s="33"/>
+      <c r="AE26" s="33"/>
+      <c r="AF26" s="33"/>
+      <c r="AG26" s="33"/>
+      <c r="AH26" s="33"/>
+      <c r="AI26" s="33"/>
+      <c r="AJ26" s="33"/>
+      <c r="AK26" s="33"/>
+      <c r="AL26" s="33"/>
+      <c r="AM26" s="33"/>
+      <c r="AN26" s="33"/>
+      <c r="AO26" s="33"/>
+      <c r="AP26" s="33"/>
+      <c r="AQ26" s="33"/>
+      <c r="AR26" s="33"/>
+      <c r="AS26" s="33"/>
+      <c r="AT26" s="33"/>
+      <c r="AU26" s="33"/>
+      <c r="AV26" s="33"/>
+      <c r="AW26" s="33"/>
+      <c r="AX26" s="33"/>
+      <c r="AY26" s="33"/>
+      <c r="AZ26" s="33"/>
+      <c r="BA26" s="33"/>
+      <c r="BB26" s="33"/>
+      <c r="BC26" s="33"/>
+      <c r="BD26" s="33"/>
+      <c r="BE26" s="33"/>
+      <c r="BF26" s="33"/>
+      <c r="BG26" s="33"/>
+      <c r="BH26" s="33"/>
+      <c r="BI26" s="33"/>
+      <c r="BJ26" s="33"/>
+      <c r="BK26" s="33"/>
+      <c r="BL26" s="33"/>
+      <c r="BM26" s="33"/>
+      <c r="BN26" s="33"/>
+      <c r="BO26" s="33"/>
+      <c r="BP26" s="33"/>
+      <c r="BQ26" s="33"/>
+      <c r="BR26" s="33"/>
+      <c r="BS26" s="33"/>
+      <c r="BT26" s="33"/>
+      <c r="BU26" s="33"/>
+      <c r="BV26" s="33"/>
+      <c r="BW26" s="33"/>
+      <c r="BX26" s="33"/>
+      <c r="BY26" s="33"/>
+      <c r="BZ26" s="33"/>
+      <c r="CA26" s="33"/>
+      <c r="CB26" s="33"/>
+      <c r="CC26" s="33"/>
+      <c r="CD26" s="33"/>
+      <c r="CE26" s="33"/>
+      <c r="CF26" s="33"/>
+      <c r="CG26" s="33"/>
+      <c r="CH26" s="33"/>
+      <c r="CI26" s="33"/>
+      <c r="CJ26" s="33"/>
+      <c r="CK26" s="33"/>
+      <c r="CL26" s="33"/>
+      <c r="CM26" s="33"/>
+      <c r="CN26" s="33"/>
+      <c r="CO26" s="33"/>
+      <c r="CP26" s="33"/>
+      <c r="CQ26" s="33"/>
+      <c r="CR26" s="33"/>
+      <c r="CS26" s="33"/>
+      <c r="CT26" s="33"/>
+      <c r="CU26" s="33"/>
+      <c r="CV26" s="33"/>
+      <c r="CW26" s="33"/>
+      <c r="CX26" s="33"/>
+      <c r="CY26" s="33"/>
+      <c r="CZ26" s="33"/>
+      <c r="DA26" s="33"/>
+      <c r="DB26" s="33"/>
+      <c r="DC26" s="33"/>
+      <c r="DD26" s="33"/>
+      <c r="DE26" s="33"/>
+      <c r="DF26" s="33"/>
+      <c r="DG26" s="33"/>
+      <c r="DH26" s="33"/>
+      <c r="DI26" s="33"/>
+      <c r="DJ26" s="33"/>
+      <c r="DK26" s="33"/>
+      <c r="DL26" s="33"/>
+      <c r="DM26" s="33"/>
+      <c r="DN26" s="33"/>
+      <c r="DO26" s="33"/>
+      <c r="DP26" s="33"/>
+      <c r="DQ26" s="33"/>
+      <c r="DR26" s="33"/>
+      <c r="DS26" s="33"/>
+      <c r="DT26" s="33"/>
     </row>
     <row r="27" spans="1:124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E27" s="1">
         <v>4</v>
       </c>
-      <c r="F27" s="27"/>
-      <c r="G27" s="27"/>
-      <c r="H27" s="27"/>
-      <c r="I27" s="27"/>
-      <c r="J27" s="27"/>
-      <c r="K27" s="27"/>
-      <c r="L27" s="27"/>
-      <c r="M27" s="27"/>
-      <c r="N27" s="27"/>
-      <c r="O27" s="27"/>
-      <c r="P27" s="27"/>
-      <c r="Q27" s="27"/>
-      <c r="R27" s="27"/>
-      <c r="S27" s="27"/>
-      <c r="T27" s="27"/>
-      <c r="U27" s="27"/>
-      <c r="V27" s="27"/>
-      <c r="W27" s="27"/>
-      <c r="X27" s="27"/>
-      <c r="Y27" s="27"/>
-      <c r="Z27" s="27"/>
-      <c r="AA27" s="27"/>
-      <c r="AB27" s="27"/>
-      <c r="AC27" s="27"/>
-      <c r="AD27" s="27"/>
-      <c r="AE27" s="27"/>
-      <c r="AF27" s="27"/>
-      <c r="AG27" s="27"/>
-      <c r="AH27" s="27"/>
-      <c r="AI27" s="27"/>
-      <c r="AJ27" s="27"/>
-      <c r="AK27" s="27"/>
-      <c r="AL27" s="27"/>
-      <c r="AM27" s="27"/>
-      <c r="AN27" s="27"/>
-      <c r="AO27" s="27"/>
-      <c r="AP27" s="27"/>
-      <c r="AQ27" s="27"/>
-      <c r="AR27" s="27"/>
-      <c r="AS27" s="27"/>
-      <c r="AT27" s="27"/>
-      <c r="AU27" s="27"/>
-      <c r="AV27" s="27"/>
-      <c r="AW27" s="27"/>
-      <c r="AX27" s="27"/>
-      <c r="AY27" s="27"/>
-      <c r="AZ27" s="27"/>
-      <c r="BA27" s="27"/>
-      <c r="BB27" s="27"/>
-      <c r="BC27" s="27"/>
-      <c r="BD27" s="27"/>
-      <c r="BE27" s="27"/>
-      <c r="BF27" s="27"/>
-      <c r="BG27" s="27"/>
-      <c r="BH27" s="27"/>
-      <c r="BI27" s="27"/>
-      <c r="BJ27" s="27"/>
-      <c r="BK27" s="27"/>
-      <c r="BL27" s="27"/>
-      <c r="BM27" s="27"/>
-      <c r="BN27" s="27"/>
-      <c r="BO27" s="27"/>
-      <c r="BP27" s="27"/>
-      <c r="BQ27" s="27"/>
-      <c r="BR27" s="27"/>
-      <c r="BS27" s="27"/>
-      <c r="BT27" s="27"/>
-      <c r="BU27" s="27"/>
-      <c r="BV27" s="27"/>
-      <c r="BW27" s="27"/>
-      <c r="BX27" s="27"/>
-      <c r="BY27" s="27"/>
-      <c r="BZ27" s="27"/>
-      <c r="CA27" s="27"/>
-      <c r="CB27" s="27"/>
-      <c r="CC27" s="27"/>
-      <c r="CD27" s="27"/>
-      <c r="CE27" s="28"/>
-      <c r="CF27" s="29"/>
-      <c r="CG27" s="29"/>
-      <c r="CH27" s="29"/>
-      <c r="CI27" s="29"/>
-      <c r="CJ27" s="29"/>
-      <c r="CK27" s="29"/>
-      <c r="CL27" s="29"/>
-      <c r="CM27" s="29"/>
-      <c r="CN27" s="29"/>
-      <c r="CO27" s="29"/>
-      <c r="CP27" s="29"/>
-      <c r="CQ27" s="29"/>
-      <c r="CR27" s="29"/>
-      <c r="CS27" s="29"/>
-      <c r="CT27" s="29"/>
-      <c r="CU27" s="29"/>
-      <c r="CV27" s="29"/>
-      <c r="CW27" s="29"/>
-      <c r="CX27" s="29"/>
-      <c r="CY27" s="29"/>
-      <c r="CZ27" s="29"/>
-      <c r="DA27" s="29"/>
-      <c r="DB27" s="29"/>
-      <c r="DC27" s="29"/>
-      <c r="DD27" s="29"/>
-      <c r="DE27" s="29"/>
-      <c r="DF27" s="29"/>
-      <c r="DG27" s="29"/>
-      <c r="DH27" s="29"/>
-      <c r="DI27" s="29"/>
-      <c r="DJ27" s="29"/>
-      <c r="DK27" s="29"/>
-      <c r="DL27" s="29"/>
-      <c r="DM27" s="29"/>
-      <c r="DN27" s="29"/>
-      <c r="DO27" s="29"/>
-      <c r="DP27" s="29"/>
-      <c r="DQ27" s="29"/>
-      <c r="DR27" s="29"/>
-      <c r="DS27" s="29"/>
-      <c r="DT27" s="29"/>
+      <c r="F27" s="53"/>
+      <c r="G27" s="53"/>
+      <c r="H27" s="53"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="53"/>
+      <c r="L27" s="53"/>
+      <c r="M27" s="53"/>
+      <c r="N27" s="53"/>
+      <c r="O27" s="53"/>
+      <c r="P27" s="53"/>
+      <c r="Q27" s="53"/>
+      <c r="R27" s="53"/>
+      <c r="S27" s="53"/>
+      <c r="T27" s="53"/>
+      <c r="U27" s="53"/>
+      <c r="V27" s="53"/>
+      <c r="W27" s="53"/>
+      <c r="X27" s="53"/>
+      <c r="Y27" s="53"/>
+      <c r="Z27" s="53"/>
+      <c r="AA27" s="53"/>
+      <c r="AB27" s="53"/>
+      <c r="AC27" s="53"/>
+      <c r="AD27" s="53"/>
+      <c r="AE27" s="53"/>
+      <c r="AF27" s="53"/>
+      <c r="AG27" s="53"/>
+      <c r="AH27" s="53"/>
+      <c r="AI27" s="53"/>
+      <c r="AJ27" s="53"/>
+      <c r="AK27" s="53"/>
+      <c r="AL27" s="53"/>
+      <c r="AM27" s="53"/>
+      <c r="AN27" s="53"/>
+      <c r="AO27" s="53"/>
+      <c r="AP27" s="53"/>
+      <c r="AQ27" s="53"/>
+      <c r="AR27" s="53"/>
+      <c r="AS27" s="53"/>
+      <c r="AT27" s="53"/>
+      <c r="AU27" s="53"/>
+      <c r="AV27" s="53"/>
+      <c r="AW27" s="53"/>
+      <c r="AX27" s="53"/>
+      <c r="AY27" s="53"/>
+      <c r="AZ27" s="53"/>
+      <c r="BA27" s="53"/>
+      <c r="BB27" s="53"/>
+      <c r="BC27" s="53"/>
+      <c r="BD27" s="53"/>
+      <c r="BE27" s="53"/>
+      <c r="BF27" s="53"/>
+      <c r="BG27" s="53"/>
+      <c r="BH27" s="53"/>
+      <c r="BI27" s="53"/>
+      <c r="BJ27" s="53"/>
+      <c r="BK27" s="53"/>
+      <c r="BL27" s="53"/>
+      <c r="BM27" s="53"/>
+      <c r="BN27" s="53"/>
+      <c r="BO27" s="53"/>
+      <c r="BP27" s="53"/>
+      <c r="BQ27" s="53"/>
+      <c r="BR27" s="53"/>
+      <c r="BS27" s="53"/>
+      <c r="BT27" s="53"/>
+      <c r="BU27" s="53"/>
+      <c r="BV27" s="53"/>
+      <c r="BW27" s="53"/>
+      <c r="BX27" s="53"/>
+      <c r="BY27" s="53"/>
+      <c r="BZ27" s="53"/>
+      <c r="CA27" s="53"/>
+      <c r="CB27" s="53"/>
+      <c r="CC27" s="53"/>
+      <c r="CD27" s="53"/>
+      <c r="CE27" s="54"/>
+      <c r="CF27" s="55"/>
+      <c r="CG27" s="55"/>
+      <c r="CH27" s="55"/>
+      <c r="CI27" s="55"/>
+      <c r="CJ27" s="55"/>
+      <c r="CK27" s="55"/>
+      <c r="CL27" s="55"/>
+      <c r="CM27" s="55"/>
+      <c r="CN27" s="55"/>
+      <c r="CO27" s="55"/>
+      <c r="CP27" s="55"/>
+      <c r="CQ27" s="55"/>
+      <c r="CR27" s="55"/>
+      <c r="CS27" s="55"/>
+      <c r="CT27" s="55"/>
+      <c r="CU27" s="55"/>
+      <c r="CV27" s="55"/>
+      <c r="CW27" s="55"/>
+      <c r="CX27" s="55"/>
+      <c r="CY27" s="55"/>
+      <c r="CZ27" s="55"/>
+      <c r="DA27" s="55"/>
+      <c r="DB27" s="55"/>
+      <c r="DC27" s="55"/>
+      <c r="DD27" s="55"/>
+      <c r="DE27" s="55"/>
+      <c r="DF27" s="55"/>
+      <c r="DG27" s="55"/>
+      <c r="DH27" s="55"/>
+      <c r="DI27" s="55"/>
+      <c r="DJ27" s="55"/>
+      <c r="DK27" s="55"/>
+      <c r="DL27" s="55"/>
+      <c r="DM27" s="55"/>
+      <c r="DN27" s="55"/>
+      <c r="DO27" s="55"/>
+      <c r="DP27" s="55"/>
+      <c r="DQ27" s="55"/>
+      <c r="DR27" s="55"/>
+      <c r="DS27" s="55"/>
+      <c r="DT27" s="55"/>
     </row>
     <row r="29" spans="1:124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E29" s="22">
         <f>SUM(E11:E18)/8</f>
-        <v>1.0416666666666668E-2</v>
+        <v>3.9583333333333331E-2</v>
       </c>
       <c r="AJ29" s="16"/>
       <c r="AK29" s="17" t="s">
@@ -5012,34 +5050,208 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="262">
-    <mergeCell ref="N1:Q1"/>
-    <mergeCell ref="BC8:BC9"/>
-    <mergeCell ref="BD8:BD9"/>
-    <mergeCell ref="BE8:BE9"/>
-    <mergeCell ref="AN8:AN9"/>
-    <mergeCell ref="AO8:AO9"/>
-    <mergeCell ref="AP8:AP9"/>
-    <mergeCell ref="AQ8:AQ9"/>
-    <mergeCell ref="AR8:AR9"/>
-    <mergeCell ref="AS8:AS9"/>
-    <mergeCell ref="AT8:AT9"/>
-    <mergeCell ref="AU8:AU9"/>
-    <mergeCell ref="AV8:AV9"/>
-    <mergeCell ref="BO8:BO9"/>
-    <mergeCell ref="BP8:BP9"/>
-    <mergeCell ref="BQ8:BQ9"/>
-    <mergeCell ref="BR8:BR9"/>
-    <mergeCell ref="BS8:BS9"/>
-    <mergeCell ref="BT8:BT9"/>
-    <mergeCell ref="BZ8:BZ9"/>
-    <mergeCell ref="CA8:CA9"/>
-    <mergeCell ref="BH8:BH9"/>
-    <mergeCell ref="BI8:BI9"/>
-    <mergeCell ref="BJ8:BJ9"/>
-    <mergeCell ref="BK8:BK9"/>
-    <mergeCell ref="BL8:BL9"/>
-    <mergeCell ref="BM8:BM9"/>
+  <mergeCells count="263">
+    <mergeCell ref="R1:U1"/>
+    <mergeCell ref="DQ2:DQ7"/>
+    <mergeCell ref="DR2:DR7"/>
+    <mergeCell ref="DS2:DS7"/>
+    <mergeCell ref="DT2:DT7"/>
+    <mergeCell ref="CX2:CX7"/>
+    <mergeCell ref="CY2:CY7"/>
+    <mergeCell ref="DA2:DA7"/>
+    <mergeCell ref="DB2:DB7"/>
+    <mergeCell ref="DC2:DC7"/>
+    <mergeCell ref="DD2:DD7"/>
+    <mergeCell ref="DE2:DE7"/>
+    <mergeCell ref="CZ2:CZ7"/>
+    <mergeCell ref="DN2:DN7"/>
+    <mergeCell ref="DO2:DO7"/>
+    <mergeCell ref="DP2:DP7"/>
+    <mergeCell ref="DG2:DG7"/>
+    <mergeCell ref="DH2:DH7"/>
+    <mergeCell ref="DI2:DI7"/>
+    <mergeCell ref="DJ2:DJ7"/>
+    <mergeCell ref="DK2:DK7"/>
+    <mergeCell ref="F27:S27"/>
+    <mergeCell ref="T27:AW27"/>
+    <mergeCell ref="AX27:CD27"/>
+    <mergeCell ref="CE27:DT27"/>
+    <mergeCell ref="DG8:DG9"/>
+    <mergeCell ref="DH8:DH9"/>
+    <mergeCell ref="DI8:DI9"/>
+    <mergeCell ref="DJ8:DJ9"/>
+    <mergeCell ref="DK8:DK9"/>
+    <mergeCell ref="DL8:DL9"/>
+    <mergeCell ref="DM8:DM9"/>
+    <mergeCell ref="DN8:DN9"/>
+    <mergeCell ref="DO8:DO9"/>
+    <mergeCell ref="DP8:DP9"/>
+    <mergeCell ref="DA8:DA9"/>
+    <mergeCell ref="DB8:DB9"/>
+    <mergeCell ref="DC8:DC9"/>
+    <mergeCell ref="DD8:DD9"/>
+    <mergeCell ref="DE8:DE9"/>
+    <mergeCell ref="CQ8:CQ9"/>
+    <mergeCell ref="CR8:CR9"/>
+    <mergeCell ref="CS8:CS9"/>
+    <mergeCell ref="BN8:BN9"/>
+    <mergeCell ref="CI8:CI9"/>
+    <mergeCell ref="CK8:CK9"/>
+    <mergeCell ref="CL8:CL9"/>
+    <mergeCell ref="BX8:BX9"/>
+    <mergeCell ref="BY8:BY9"/>
+    <mergeCell ref="DL2:DL7"/>
+    <mergeCell ref="DM2:DM7"/>
+    <mergeCell ref="DF2:DF7"/>
+    <mergeCell ref="BD2:BD7"/>
+    <mergeCell ref="BE2:BE7"/>
+    <mergeCell ref="BF2:BF7"/>
+    <mergeCell ref="BG2:BG7"/>
+    <mergeCell ref="BM2:BM7"/>
+    <mergeCell ref="BN2:BN7"/>
+    <mergeCell ref="BO2:BO7"/>
+    <mergeCell ref="BP2:BP7"/>
+    <mergeCell ref="CA2:CA7"/>
+    <mergeCell ref="BW2:BW7"/>
+    <mergeCell ref="BX2:BX7"/>
+    <mergeCell ref="BY2:BY7"/>
+    <mergeCell ref="BZ2:BZ7"/>
+    <mergeCell ref="BH2:BH7"/>
+    <mergeCell ref="BI2:BI7"/>
+    <mergeCell ref="BJ2:BJ7"/>
+    <mergeCell ref="BK2:BK7"/>
+    <mergeCell ref="U2:U7"/>
+    <mergeCell ref="V2:V7"/>
+    <mergeCell ref="W2:W7"/>
+    <mergeCell ref="X2:X7"/>
+    <mergeCell ref="AF2:AF7"/>
+    <mergeCell ref="AX2:AX7"/>
+    <mergeCell ref="AY2:AY7"/>
+    <mergeCell ref="AZ2:AZ7"/>
+    <mergeCell ref="BL2:BL7"/>
+    <mergeCell ref="BA2:BA7"/>
+    <mergeCell ref="BB2:BB7"/>
+    <mergeCell ref="BC2:BC7"/>
+    <mergeCell ref="AP2:AP7"/>
+    <mergeCell ref="AQ2:AQ7"/>
+    <mergeCell ref="AR2:AR7"/>
+    <mergeCell ref="AS2:AS7"/>
+    <mergeCell ref="AT2:AT7"/>
+    <mergeCell ref="AU2:AU7"/>
+    <mergeCell ref="AV2:AV7"/>
+    <mergeCell ref="AW2:AW7"/>
+    <mergeCell ref="CW2:CW7"/>
+    <mergeCell ref="CU2:CU7"/>
+    <mergeCell ref="CV2:CV7"/>
+    <mergeCell ref="CQ2:CQ7"/>
+    <mergeCell ref="CR2:CR7"/>
+    <mergeCell ref="CS2:CS7"/>
+    <mergeCell ref="CT2:CT7"/>
+    <mergeCell ref="CI2:CI7"/>
+    <mergeCell ref="CJ2:CJ7"/>
+    <mergeCell ref="CK2:CK7"/>
+    <mergeCell ref="CL2:CL7"/>
+    <mergeCell ref="CM2:CM7"/>
+    <mergeCell ref="CN2:CN7"/>
+    <mergeCell ref="CO2:CO7"/>
+    <mergeCell ref="CP2:CP7"/>
+    <mergeCell ref="N2:N7"/>
+    <mergeCell ref="O2:O7"/>
+    <mergeCell ref="P2:P7"/>
+    <mergeCell ref="Q2:Q7"/>
+    <mergeCell ref="R2:R7"/>
+    <mergeCell ref="S2:S7"/>
+    <mergeCell ref="T2:T7"/>
+    <mergeCell ref="CN8:CN9"/>
+    <mergeCell ref="Y2:Y7"/>
+    <mergeCell ref="Z2:Z7"/>
+    <mergeCell ref="AA2:AA7"/>
+    <mergeCell ref="AB2:AB7"/>
+    <mergeCell ref="AC2:AC7"/>
+    <mergeCell ref="AD2:AD7"/>
+    <mergeCell ref="AE2:AE7"/>
+    <mergeCell ref="AH2:AH7"/>
+    <mergeCell ref="AI2:AI7"/>
+    <mergeCell ref="AJ2:AJ7"/>
+    <mergeCell ref="AK2:AK7"/>
+    <mergeCell ref="AL2:AL7"/>
+    <mergeCell ref="AM2:AM7"/>
+    <mergeCell ref="AN2:AN7"/>
+    <mergeCell ref="AO2:AO7"/>
+    <mergeCell ref="AG2:AG7"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="F2:F7"/>
+    <mergeCell ref="G2:G7"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="I2:I7"/>
+    <mergeCell ref="J2:J7"/>
+    <mergeCell ref="K2:K7"/>
+    <mergeCell ref="L2:L7"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="M2:M7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="E26:DT26"/>
+    <mergeCell ref="DF8:DF9"/>
+    <mergeCell ref="DQ8:DQ9"/>
+    <mergeCell ref="DR8:DR9"/>
+    <mergeCell ref="DS8:DS9"/>
+    <mergeCell ref="DT8:DT9"/>
+    <mergeCell ref="CY8:CY9"/>
+    <mergeCell ref="CZ8:CZ9"/>
+    <mergeCell ref="CM8:CM9"/>
+    <mergeCell ref="CW8:CW9"/>
+    <mergeCell ref="CX8:CX9"/>
+    <mergeCell ref="BU8:BU9"/>
+    <mergeCell ref="BV8:BV9"/>
+    <mergeCell ref="BW8:BW9"/>
+    <mergeCell ref="BF8:BF9"/>
+    <mergeCell ref="BG8:BG9"/>
+    <mergeCell ref="CG8:CG9"/>
+    <mergeCell ref="CH8:CH9"/>
+    <mergeCell ref="AW8:AW9"/>
+    <mergeCell ref="AX8:AX9"/>
+    <mergeCell ref="AY8:AY9"/>
+    <mergeCell ref="AZ8:AZ9"/>
+    <mergeCell ref="BA8:BA9"/>
+    <mergeCell ref="BB8:BB9"/>
     <mergeCell ref="CB8:CB9"/>
     <mergeCell ref="CC8:CC9"/>
     <mergeCell ref="CD8:CD9"/>
@@ -5064,30 +5276,33 @@
     <mergeCell ref="CF2:CF7"/>
     <mergeCell ref="CG2:CG7"/>
     <mergeCell ref="CJ8:CJ9"/>
-    <mergeCell ref="E26:DT26"/>
-    <mergeCell ref="DF8:DF9"/>
-    <mergeCell ref="DQ8:DQ9"/>
-    <mergeCell ref="DR8:DR9"/>
-    <mergeCell ref="DS8:DS9"/>
-    <mergeCell ref="DT8:DT9"/>
-    <mergeCell ref="CY8:CY9"/>
-    <mergeCell ref="CZ8:CZ9"/>
-    <mergeCell ref="CM8:CM9"/>
-    <mergeCell ref="CW8:CW9"/>
-    <mergeCell ref="CX8:CX9"/>
-    <mergeCell ref="BU8:BU9"/>
-    <mergeCell ref="BV8:BV9"/>
-    <mergeCell ref="BW8:BW9"/>
-    <mergeCell ref="BF8:BF9"/>
-    <mergeCell ref="BG8:BG9"/>
-    <mergeCell ref="CG8:CG9"/>
-    <mergeCell ref="CH8:CH9"/>
-    <mergeCell ref="AW8:AW9"/>
-    <mergeCell ref="AX8:AX9"/>
-    <mergeCell ref="AY8:AY9"/>
-    <mergeCell ref="AZ8:AZ9"/>
-    <mergeCell ref="BA8:BA9"/>
-    <mergeCell ref="BB8:BB9"/>
+    <mergeCell ref="BO8:BO9"/>
+    <mergeCell ref="BP8:BP9"/>
+    <mergeCell ref="BQ8:BQ9"/>
+    <mergeCell ref="BR8:BR9"/>
+    <mergeCell ref="BS8:BS9"/>
+    <mergeCell ref="BT8:BT9"/>
+    <mergeCell ref="BZ8:BZ9"/>
+    <mergeCell ref="CA8:CA9"/>
+    <mergeCell ref="BH8:BH9"/>
+    <mergeCell ref="BI8:BI9"/>
+    <mergeCell ref="BJ8:BJ9"/>
+    <mergeCell ref="BK8:BK9"/>
+    <mergeCell ref="BL8:BL9"/>
+    <mergeCell ref="BM8:BM9"/>
+    <mergeCell ref="N1:Q1"/>
+    <mergeCell ref="BC8:BC9"/>
+    <mergeCell ref="BD8:BD9"/>
+    <mergeCell ref="BE8:BE9"/>
+    <mergeCell ref="AN8:AN9"/>
+    <mergeCell ref="AO8:AO9"/>
+    <mergeCell ref="AP8:AP9"/>
+    <mergeCell ref="AQ8:AQ9"/>
+    <mergeCell ref="AR8:AR9"/>
+    <mergeCell ref="AS8:AS9"/>
+    <mergeCell ref="AT8:AT9"/>
+    <mergeCell ref="AU8:AU9"/>
+    <mergeCell ref="AV8:AV9"/>
     <mergeCell ref="AE8:AE9"/>
     <mergeCell ref="AF8:AF9"/>
     <mergeCell ref="AG8:AG9"/>
@@ -5099,182 +5314,6 @@
     <mergeCell ref="AM8:AM9"/>
     <mergeCell ref="V8:V9"/>
     <mergeCell ref="W8:W9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="F2:F7"/>
-    <mergeCell ref="G2:G7"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="I2:I7"/>
-    <mergeCell ref="J2:J7"/>
-    <mergeCell ref="K2:K7"/>
-    <mergeCell ref="L2:L7"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="M2:M7"/>
-    <mergeCell ref="N2:N7"/>
-    <mergeCell ref="O2:O7"/>
-    <mergeCell ref="P2:P7"/>
-    <mergeCell ref="Q2:Q7"/>
-    <mergeCell ref="R2:R7"/>
-    <mergeCell ref="S2:S7"/>
-    <mergeCell ref="T2:T7"/>
-    <mergeCell ref="CN8:CN9"/>
-    <mergeCell ref="Y2:Y7"/>
-    <mergeCell ref="Z2:Z7"/>
-    <mergeCell ref="AA2:AA7"/>
-    <mergeCell ref="AB2:AB7"/>
-    <mergeCell ref="AC2:AC7"/>
-    <mergeCell ref="AD2:AD7"/>
-    <mergeCell ref="AE2:AE7"/>
-    <mergeCell ref="AH2:AH7"/>
-    <mergeCell ref="AI2:AI7"/>
-    <mergeCell ref="AJ2:AJ7"/>
-    <mergeCell ref="AK2:AK7"/>
-    <mergeCell ref="AL2:AL7"/>
-    <mergeCell ref="AM2:AM7"/>
-    <mergeCell ref="AN2:AN7"/>
-    <mergeCell ref="AO2:AO7"/>
-    <mergeCell ref="CW2:CW7"/>
-    <mergeCell ref="CU2:CU7"/>
-    <mergeCell ref="CV2:CV7"/>
-    <mergeCell ref="CQ2:CQ7"/>
-    <mergeCell ref="CR2:CR7"/>
-    <mergeCell ref="CS2:CS7"/>
-    <mergeCell ref="CT2:CT7"/>
-    <mergeCell ref="CI2:CI7"/>
-    <mergeCell ref="CJ2:CJ7"/>
-    <mergeCell ref="CK2:CK7"/>
-    <mergeCell ref="CL2:CL7"/>
-    <mergeCell ref="CM2:CM7"/>
-    <mergeCell ref="CN2:CN7"/>
-    <mergeCell ref="CO2:CO7"/>
-    <mergeCell ref="CP2:CP7"/>
-    <mergeCell ref="AG2:AG7"/>
-    <mergeCell ref="U2:U7"/>
-    <mergeCell ref="V2:V7"/>
-    <mergeCell ref="W2:W7"/>
-    <mergeCell ref="X2:X7"/>
-    <mergeCell ref="AF2:AF7"/>
-    <mergeCell ref="AX2:AX7"/>
-    <mergeCell ref="AY2:AY7"/>
-    <mergeCell ref="AZ2:AZ7"/>
-    <mergeCell ref="BL2:BL7"/>
-    <mergeCell ref="BA2:BA7"/>
-    <mergeCell ref="BB2:BB7"/>
-    <mergeCell ref="BC2:BC7"/>
-    <mergeCell ref="AP2:AP7"/>
-    <mergeCell ref="AQ2:AQ7"/>
-    <mergeCell ref="AR2:AR7"/>
-    <mergeCell ref="AS2:AS7"/>
-    <mergeCell ref="AT2:AT7"/>
-    <mergeCell ref="AU2:AU7"/>
-    <mergeCell ref="AV2:AV7"/>
-    <mergeCell ref="AW2:AW7"/>
-    <mergeCell ref="CK8:CK9"/>
-    <mergeCell ref="CL8:CL9"/>
-    <mergeCell ref="BX8:BX9"/>
-    <mergeCell ref="BY8:BY9"/>
-    <mergeCell ref="DL2:DL7"/>
-    <mergeCell ref="DM2:DM7"/>
-    <mergeCell ref="DF2:DF7"/>
-    <mergeCell ref="BD2:BD7"/>
-    <mergeCell ref="BE2:BE7"/>
-    <mergeCell ref="BF2:BF7"/>
-    <mergeCell ref="BG2:BG7"/>
-    <mergeCell ref="BM2:BM7"/>
-    <mergeCell ref="BN2:BN7"/>
-    <mergeCell ref="BO2:BO7"/>
-    <mergeCell ref="BP2:BP7"/>
-    <mergeCell ref="CA2:CA7"/>
-    <mergeCell ref="BW2:BW7"/>
-    <mergeCell ref="BX2:BX7"/>
-    <mergeCell ref="BY2:BY7"/>
-    <mergeCell ref="BZ2:BZ7"/>
-    <mergeCell ref="BH2:BH7"/>
-    <mergeCell ref="BI2:BI7"/>
-    <mergeCell ref="BJ2:BJ7"/>
-    <mergeCell ref="BK2:BK7"/>
-    <mergeCell ref="F27:S27"/>
-    <mergeCell ref="T27:AW27"/>
-    <mergeCell ref="AX27:CD27"/>
-    <mergeCell ref="CE27:DT27"/>
-    <mergeCell ref="DG8:DG9"/>
-    <mergeCell ref="DH8:DH9"/>
-    <mergeCell ref="DI8:DI9"/>
-    <mergeCell ref="DJ8:DJ9"/>
-    <mergeCell ref="DK8:DK9"/>
-    <mergeCell ref="DL8:DL9"/>
-    <mergeCell ref="DM8:DM9"/>
-    <mergeCell ref="DN8:DN9"/>
-    <mergeCell ref="DO8:DO9"/>
-    <mergeCell ref="DP8:DP9"/>
-    <mergeCell ref="DA8:DA9"/>
-    <mergeCell ref="DB8:DB9"/>
-    <mergeCell ref="DC8:DC9"/>
-    <mergeCell ref="DD8:DD9"/>
-    <mergeCell ref="DE8:DE9"/>
-    <mergeCell ref="CQ8:CQ9"/>
-    <mergeCell ref="CR8:CR9"/>
-    <mergeCell ref="CS8:CS9"/>
-    <mergeCell ref="BN8:BN9"/>
-    <mergeCell ref="CI8:CI9"/>
-    <mergeCell ref="DQ2:DQ7"/>
-    <mergeCell ref="DR2:DR7"/>
-    <mergeCell ref="DS2:DS7"/>
-    <mergeCell ref="DT2:DT7"/>
-    <mergeCell ref="CX2:CX7"/>
-    <mergeCell ref="CY2:CY7"/>
-    <mergeCell ref="DA2:DA7"/>
-    <mergeCell ref="DB2:DB7"/>
-    <mergeCell ref="DC2:DC7"/>
-    <mergeCell ref="DD2:DD7"/>
-    <mergeCell ref="DE2:DE7"/>
-    <mergeCell ref="CZ2:CZ7"/>
-    <mergeCell ref="DN2:DN7"/>
-    <mergeCell ref="DO2:DO7"/>
-    <mergeCell ref="DP2:DP7"/>
-    <mergeCell ref="DG2:DG7"/>
-    <mergeCell ref="DH2:DH7"/>
-    <mergeCell ref="DI2:DI7"/>
-    <mergeCell ref="DJ2:DJ7"/>
-    <mergeCell ref="DK2:DK7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -5307,7 +5346,7 @@
       <c r="H2" s="57"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="36" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="59" t="s">
@@ -5331,7 +5370,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="41"/>
+      <c r="A4" s="36"/>
       <c r="B4" s="61"/>
       <c r="C4" s="62"/>
       <c r="D4" s="64"/>
@@ -5356,7 +5395,7 @@
       </c>
       <c r="E5" s="19">
         <f>COUNTIF(cms!H11:Y11,0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" s="19">
         <f>COUNTIF(cms!Z11:AY11,0)</f>
@@ -5412,7 +5451,7 @@
       </c>
       <c r="E7" s="19">
         <f>COUNTIF(cms!H12:Y12,0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7" s="19">
         <f>COUNTIF(cms!Z12:AY12,0)</f>
@@ -5440,7 +5479,7 @@
       </c>
       <c r="E8" s="19">
         <f>COUNTIF(cms!H13:Y13,0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8" s="19">
         <f>COUNTIF(cms!Z13:AY13,0)</f>
@@ -5496,7 +5535,7 @@
       </c>
       <c r="E10" s="19">
         <f>COUNTIF(cms!H14:Y14,0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" s="19">
         <f>COUNTIF(cms!Z14:AY14,0)</f>
@@ -5524,7 +5563,7 @@
       </c>
       <c r="E11" s="19">
         <f>COUNTIF(cms!H15:Y15,0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F11" s="19">
         <f>COUNTIF(cms!Z15:AY15,0)</f>
@@ -5552,7 +5591,7 @@
       </c>
       <c r="E12" s="19">
         <f>COUNTIF(cms!H16:Y16,0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12" s="19">
         <f>COUNTIF(cms!Z16:AY16,0)</f>
@@ -5636,7 +5675,7 @@
       </c>
       <c r="E15" s="19">
         <f>COUNTIF(cms!H18:Y18,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F15" s="19">
         <f>COUNTIF(cms!Z18:AY18,0)</f>

--- a/Journals/Angular ჟურნალი.xlsx
+++ b/Journals/Angular ჟურნალი.xlsx
@@ -551,38 +551,26 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="2" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -612,7 +600,16 @@
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -626,14 +623,17 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -896,12 +896,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="41"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="37"/>
       <c r="F1" s="25">
         <v>4</v>
       </c>
@@ -1035,1317 +1035,1317 @@
       </c>
     </row>
     <row r="2" spans="1:125" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="42"/>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="45" t="s">
+      <c r="A2" s="38"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="30">
+      <c r="F2" s="28">
         <v>46276</v>
       </c>
-      <c r="G2" s="30">
+      <c r="G2" s="28">
         <v>46276</v>
       </c>
-      <c r="H2" s="30">
+      <c r="H2" s="28">
         <v>46276</v>
       </c>
-      <c r="I2" s="30">
+      <c r="I2" s="28">
         <v>46276</v>
       </c>
-      <c r="J2" s="30">
+      <c r="J2" s="28">
         <v>46283</v>
       </c>
-      <c r="K2" s="30">
+      <c r="K2" s="28">
         <v>46283</v>
       </c>
-      <c r="L2" s="30">
+      <c r="L2" s="28">
         <v>46283</v>
       </c>
-      <c r="M2" s="30">
+      <c r="M2" s="28">
         <v>46283</v>
       </c>
-      <c r="N2" s="30">
+      <c r="N2" s="28">
         <v>46290</v>
       </c>
-      <c r="O2" s="30">
+      <c r="O2" s="28">
         <v>46290</v>
       </c>
-      <c r="P2" s="30">
+      <c r="P2" s="28">
         <v>46290</v>
       </c>
-      <c r="Q2" s="30">
+      <c r="Q2" s="28">
         <v>46290</v>
       </c>
-      <c r="R2" s="30">
+      <c r="R2" s="28">
         <v>46297</v>
       </c>
-      <c r="S2" s="30">
+      <c r="S2" s="28">
         <v>46297</v>
       </c>
-      <c r="T2" s="30">
+      <c r="T2" s="28">
         <v>46297</v>
       </c>
-      <c r="U2" s="30">
+      <c r="U2" s="28">
         <v>46297</v>
       </c>
-      <c r="V2" s="30"/>
-      <c r="W2" s="30"/>
-      <c r="X2" s="30"/>
-      <c r="Y2" s="30"/>
-      <c r="Z2" s="30"/>
-      <c r="AA2" s="30"/>
-      <c r="AB2" s="30"/>
-      <c r="AC2" s="30"/>
-      <c r="AD2" s="30"/>
-      <c r="AE2" s="30"/>
-      <c r="AF2" s="30"/>
-      <c r="AG2" s="30"/>
-      <c r="AH2" s="30"/>
-      <c r="AI2" s="30"/>
-      <c r="AJ2" s="30"/>
-      <c r="AK2" s="30"/>
-      <c r="AL2" s="30"/>
-      <c r="AM2" s="30"/>
-      <c r="AN2" s="30"/>
-      <c r="AO2" s="30"/>
-      <c r="AP2" s="30"/>
-      <c r="AQ2" s="30"/>
-      <c r="AR2" s="30"/>
-      <c r="AS2" s="30"/>
-      <c r="AT2" s="30"/>
-      <c r="AU2" s="30"/>
-      <c r="AV2" s="30"/>
-      <c r="AW2" s="30"/>
-      <c r="AX2" s="30"/>
-      <c r="AY2" s="30"/>
-      <c r="AZ2" s="30"/>
-      <c r="BA2" s="30"/>
-      <c r="BB2" s="30"/>
-      <c r="BC2" s="30"/>
-      <c r="BD2" s="30"/>
-      <c r="BE2" s="30"/>
-      <c r="BF2" s="30"/>
-      <c r="BG2" s="30"/>
-      <c r="BH2" s="30"/>
-      <c r="BI2" s="30"/>
-      <c r="BJ2" s="30"/>
-      <c r="BK2" s="30"/>
-      <c r="BL2" s="30"/>
-      <c r="BM2" s="30"/>
-      <c r="BN2" s="30"/>
-      <c r="BO2" s="30"/>
-      <c r="BP2" s="30"/>
-      <c r="BQ2" s="30"/>
-      <c r="BR2" s="30"/>
-      <c r="BS2" s="30"/>
-      <c r="BT2" s="30"/>
-      <c r="BU2" s="30"/>
-      <c r="BV2" s="30"/>
-      <c r="BW2" s="30"/>
-      <c r="BX2" s="30"/>
-      <c r="BY2" s="30"/>
-      <c r="BZ2" s="30"/>
-      <c r="CA2" s="30"/>
-      <c r="CB2" s="30"/>
-      <c r="CC2" s="30"/>
-      <c r="CD2" s="30"/>
-      <c r="CE2" s="30"/>
-      <c r="CF2" s="30"/>
-      <c r="CG2" s="30"/>
-      <c r="CH2" s="30"/>
-      <c r="CI2" s="30"/>
-      <c r="CJ2" s="30"/>
-      <c r="CK2" s="30"/>
-      <c r="CL2" s="30"/>
-      <c r="CM2" s="30"/>
-      <c r="CN2" s="30"/>
-      <c r="CO2" s="30"/>
-      <c r="CP2" s="30"/>
-      <c r="CQ2" s="30"/>
-      <c r="CR2" s="30"/>
-      <c r="CS2" s="30"/>
-      <c r="CT2" s="30"/>
-      <c r="CU2" s="30"/>
-      <c r="CV2" s="30"/>
-      <c r="CW2" s="30"/>
-      <c r="CX2" s="30"/>
-      <c r="CY2" s="30"/>
-      <c r="CZ2" s="30"/>
-      <c r="DA2" s="30"/>
-      <c r="DB2" s="30"/>
-      <c r="DC2" s="30"/>
-      <c r="DD2" s="30"/>
-      <c r="DE2" s="30"/>
-      <c r="DF2" s="30"/>
-      <c r="DG2" s="30"/>
-      <c r="DH2" s="30"/>
-      <c r="DI2" s="30"/>
-      <c r="DJ2" s="30"/>
-      <c r="DK2" s="30"/>
-      <c r="DL2" s="30"/>
-      <c r="DM2" s="30"/>
-      <c r="DN2" s="30"/>
-      <c r="DO2" s="30"/>
-      <c r="DP2" s="30"/>
-      <c r="DQ2" s="30"/>
-      <c r="DR2" s="30"/>
-      <c r="DS2" s="30"/>
-      <c r="DT2" s="30"/>
+      <c r="V2" s="28"/>
+      <c r="W2" s="28"/>
+      <c r="X2" s="28"/>
+      <c r="Y2" s="28"/>
+      <c r="Z2" s="28"/>
+      <c r="AA2" s="28"/>
+      <c r="AB2" s="28"/>
+      <c r="AC2" s="28"/>
+      <c r="AD2" s="28"/>
+      <c r="AE2" s="28"/>
+      <c r="AF2" s="28"/>
+      <c r="AG2" s="28"/>
+      <c r="AH2" s="28"/>
+      <c r="AI2" s="28"/>
+      <c r="AJ2" s="28"/>
+      <c r="AK2" s="28"/>
+      <c r="AL2" s="28"/>
+      <c r="AM2" s="28"/>
+      <c r="AN2" s="28"/>
+      <c r="AO2" s="28"/>
+      <c r="AP2" s="28"/>
+      <c r="AQ2" s="28"/>
+      <c r="AR2" s="28"/>
+      <c r="AS2" s="28"/>
+      <c r="AT2" s="28"/>
+      <c r="AU2" s="28"/>
+      <c r="AV2" s="28"/>
+      <c r="AW2" s="28"/>
+      <c r="AX2" s="28"/>
+      <c r="AY2" s="28"/>
+      <c r="AZ2" s="28"/>
+      <c r="BA2" s="28"/>
+      <c r="BB2" s="28"/>
+      <c r="BC2" s="28"/>
+      <c r="BD2" s="28"/>
+      <c r="BE2" s="28"/>
+      <c r="BF2" s="28"/>
+      <c r="BG2" s="28"/>
+      <c r="BH2" s="28"/>
+      <c r="BI2" s="28"/>
+      <c r="BJ2" s="28"/>
+      <c r="BK2" s="28"/>
+      <c r="BL2" s="28"/>
+      <c r="BM2" s="28"/>
+      <c r="BN2" s="28"/>
+      <c r="BO2" s="28"/>
+      <c r="BP2" s="28"/>
+      <c r="BQ2" s="28"/>
+      <c r="BR2" s="28"/>
+      <c r="BS2" s="28"/>
+      <c r="BT2" s="28"/>
+      <c r="BU2" s="28"/>
+      <c r="BV2" s="28"/>
+      <c r="BW2" s="28"/>
+      <c r="BX2" s="28"/>
+      <c r="BY2" s="28"/>
+      <c r="BZ2" s="28"/>
+      <c r="CA2" s="28"/>
+      <c r="CB2" s="28"/>
+      <c r="CC2" s="28"/>
+      <c r="CD2" s="28"/>
+      <c r="CE2" s="28"/>
+      <c r="CF2" s="28"/>
+      <c r="CG2" s="28"/>
+      <c r="CH2" s="28"/>
+      <c r="CI2" s="28"/>
+      <c r="CJ2" s="28"/>
+      <c r="CK2" s="28"/>
+      <c r="CL2" s="28"/>
+      <c r="CM2" s="28"/>
+      <c r="CN2" s="28"/>
+      <c r="CO2" s="28"/>
+      <c r="CP2" s="28"/>
+      <c r="CQ2" s="28"/>
+      <c r="CR2" s="28"/>
+      <c r="CS2" s="28"/>
+      <c r="CT2" s="28"/>
+      <c r="CU2" s="28"/>
+      <c r="CV2" s="28"/>
+      <c r="CW2" s="28"/>
+      <c r="CX2" s="28"/>
+      <c r="CY2" s="28"/>
+      <c r="CZ2" s="28"/>
+      <c r="DA2" s="28"/>
+      <c r="DB2" s="28"/>
+      <c r="DC2" s="28"/>
+      <c r="DD2" s="28"/>
+      <c r="DE2" s="28"/>
+      <c r="DF2" s="28"/>
+      <c r="DG2" s="28"/>
+      <c r="DH2" s="28"/>
+      <c r="DI2" s="28"/>
+      <c r="DJ2" s="28"/>
+      <c r="DK2" s="28"/>
+      <c r="DL2" s="28"/>
+      <c r="DM2" s="28"/>
+      <c r="DN2" s="28"/>
+      <c r="DO2" s="28"/>
+      <c r="DP2" s="28"/>
+      <c r="DQ2" s="28"/>
+      <c r="DR2" s="28"/>
+      <c r="DS2" s="28"/>
+      <c r="DT2" s="28"/>
     </row>
     <row r="3" spans="1:125" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30"/>
-      <c r="N3" s="30"/>
-      <c r="O3" s="30"/>
-      <c r="P3" s="30"/>
-      <c r="Q3" s="30"/>
-      <c r="R3" s="30"/>
-      <c r="S3" s="30"/>
-      <c r="T3" s="30"/>
-      <c r="U3" s="30"/>
-      <c r="V3" s="30"/>
-      <c r="W3" s="30"/>
-      <c r="X3" s="30"/>
-      <c r="Y3" s="30"/>
-      <c r="Z3" s="30"/>
-      <c r="AA3" s="30"/>
-      <c r="AB3" s="30"/>
-      <c r="AC3" s="30"/>
-      <c r="AD3" s="30"/>
-      <c r="AE3" s="30"/>
-      <c r="AF3" s="30"/>
-      <c r="AG3" s="30"/>
-      <c r="AH3" s="30"/>
-      <c r="AI3" s="30"/>
-      <c r="AJ3" s="30"/>
-      <c r="AK3" s="30"/>
-      <c r="AL3" s="30"/>
-      <c r="AM3" s="30"/>
-      <c r="AN3" s="30"/>
-      <c r="AO3" s="30"/>
-      <c r="AP3" s="30"/>
-      <c r="AQ3" s="30"/>
-      <c r="AR3" s="30"/>
-      <c r="AS3" s="30"/>
-      <c r="AT3" s="30"/>
-      <c r="AU3" s="30"/>
-      <c r="AV3" s="30"/>
-      <c r="AW3" s="30"/>
-      <c r="AX3" s="30"/>
-      <c r="AY3" s="30"/>
-      <c r="AZ3" s="30"/>
-      <c r="BA3" s="30"/>
-      <c r="BB3" s="30"/>
-      <c r="BC3" s="30"/>
-      <c r="BD3" s="30"/>
-      <c r="BE3" s="30"/>
-      <c r="BF3" s="30"/>
-      <c r="BG3" s="30"/>
-      <c r="BH3" s="30"/>
-      <c r="BI3" s="30"/>
-      <c r="BJ3" s="30"/>
-      <c r="BK3" s="30"/>
-      <c r="BL3" s="30"/>
-      <c r="BM3" s="30"/>
-      <c r="BN3" s="30"/>
-      <c r="BO3" s="30"/>
-      <c r="BP3" s="30"/>
-      <c r="BQ3" s="30"/>
-      <c r="BR3" s="30"/>
-      <c r="BS3" s="30"/>
-      <c r="BT3" s="30"/>
-      <c r="BU3" s="30"/>
-      <c r="BV3" s="30"/>
-      <c r="BW3" s="30"/>
-      <c r="BX3" s="30"/>
-      <c r="BY3" s="30"/>
-      <c r="BZ3" s="30"/>
-      <c r="CA3" s="30"/>
-      <c r="CB3" s="30"/>
-      <c r="CC3" s="30"/>
-      <c r="CD3" s="30"/>
-      <c r="CE3" s="30"/>
-      <c r="CF3" s="30"/>
-      <c r="CG3" s="30"/>
-      <c r="CH3" s="30"/>
-      <c r="CI3" s="30"/>
-      <c r="CJ3" s="30"/>
-      <c r="CK3" s="30"/>
-      <c r="CL3" s="30"/>
-      <c r="CM3" s="30"/>
-      <c r="CN3" s="30"/>
-      <c r="CO3" s="30"/>
-      <c r="CP3" s="30"/>
-      <c r="CQ3" s="30"/>
-      <c r="CR3" s="30"/>
-      <c r="CS3" s="30"/>
-      <c r="CT3" s="30"/>
-      <c r="CU3" s="30"/>
-      <c r="CV3" s="30"/>
-      <c r="CW3" s="30"/>
-      <c r="CX3" s="30"/>
-      <c r="CY3" s="30"/>
-      <c r="CZ3" s="30"/>
-      <c r="DA3" s="30"/>
-      <c r="DB3" s="30"/>
-      <c r="DC3" s="30"/>
-      <c r="DD3" s="30"/>
-      <c r="DE3" s="30"/>
-      <c r="DF3" s="30"/>
-      <c r="DG3" s="30"/>
-      <c r="DH3" s="30"/>
-      <c r="DI3" s="30"/>
-      <c r="DJ3" s="30"/>
-      <c r="DK3" s="30"/>
-      <c r="DL3" s="30"/>
-      <c r="DM3" s="30"/>
-      <c r="DN3" s="30"/>
-      <c r="DO3" s="30"/>
-      <c r="DP3" s="30"/>
-      <c r="DQ3" s="30"/>
-      <c r="DR3" s="30"/>
-      <c r="DS3" s="30"/>
-      <c r="DT3" s="30"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="28"/>
+      <c r="O3" s="28"/>
+      <c r="P3" s="28"/>
+      <c r="Q3" s="28"/>
+      <c r="R3" s="28"/>
+      <c r="S3" s="28"/>
+      <c r="T3" s="28"/>
+      <c r="U3" s="28"/>
+      <c r="V3" s="28"/>
+      <c r="W3" s="28"/>
+      <c r="X3" s="28"/>
+      <c r="Y3" s="28"/>
+      <c r="Z3" s="28"/>
+      <c r="AA3" s="28"/>
+      <c r="AB3" s="28"/>
+      <c r="AC3" s="28"/>
+      <c r="AD3" s="28"/>
+      <c r="AE3" s="28"/>
+      <c r="AF3" s="28"/>
+      <c r="AG3" s="28"/>
+      <c r="AH3" s="28"/>
+      <c r="AI3" s="28"/>
+      <c r="AJ3" s="28"/>
+      <c r="AK3" s="28"/>
+      <c r="AL3" s="28"/>
+      <c r="AM3" s="28"/>
+      <c r="AN3" s="28"/>
+      <c r="AO3" s="28"/>
+      <c r="AP3" s="28"/>
+      <c r="AQ3" s="28"/>
+      <c r="AR3" s="28"/>
+      <c r="AS3" s="28"/>
+      <c r="AT3" s="28"/>
+      <c r="AU3" s="28"/>
+      <c r="AV3" s="28"/>
+      <c r="AW3" s="28"/>
+      <c r="AX3" s="28"/>
+      <c r="AY3" s="28"/>
+      <c r="AZ3" s="28"/>
+      <c r="BA3" s="28"/>
+      <c r="BB3" s="28"/>
+      <c r="BC3" s="28"/>
+      <c r="BD3" s="28"/>
+      <c r="BE3" s="28"/>
+      <c r="BF3" s="28"/>
+      <c r="BG3" s="28"/>
+      <c r="BH3" s="28"/>
+      <c r="BI3" s="28"/>
+      <c r="BJ3" s="28"/>
+      <c r="BK3" s="28"/>
+      <c r="BL3" s="28"/>
+      <c r="BM3" s="28"/>
+      <c r="BN3" s="28"/>
+      <c r="BO3" s="28"/>
+      <c r="BP3" s="28"/>
+      <c r="BQ3" s="28"/>
+      <c r="BR3" s="28"/>
+      <c r="BS3" s="28"/>
+      <c r="BT3" s="28"/>
+      <c r="BU3" s="28"/>
+      <c r="BV3" s="28"/>
+      <c r="BW3" s="28"/>
+      <c r="BX3" s="28"/>
+      <c r="BY3" s="28"/>
+      <c r="BZ3" s="28"/>
+      <c r="CA3" s="28"/>
+      <c r="CB3" s="28"/>
+      <c r="CC3" s="28"/>
+      <c r="CD3" s="28"/>
+      <c r="CE3" s="28"/>
+      <c r="CF3" s="28"/>
+      <c r="CG3" s="28"/>
+      <c r="CH3" s="28"/>
+      <c r="CI3" s="28"/>
+      <c r="CJ3" s="28"/>
+      <c r="CK3" s="28"/>
+      <c r="CL3" s="28"/>
+      <c r="CM3" s="28"/>
+      <c r="CN3" s="28"/>
+      <c r="CO3" s="28"/>
+      <c r="CP3" s="28"/>
+      <c r="CQ3" s="28"/>
+      <c r="CR3" s="28"/>
+      <c r="CS3" s="28"/>
+      <c r="CT3" s="28"/>
+      <c r="CU3" s="28"/>
+      <c r="CV3" s="28"/>
+      <c r="CW3" s="28"/>
+      <c r="CX3" s="28"/>
+      <c r="CY3" s="28"/>
+      <c r="CZ3" s="28"/>
+      <c r="DA3" s="28"/>
+      <c r="DB3" s="28"/>
+      <c r="DC3" s="28"/>
+      <c r="DD3" s="28"/>
+      <c r="DE3" s="28"/>
+      <c r="DF3" s="28"/>
+      <c r="DG3" s="28"/>
+      <c r="DH3" s="28"/>
+      <c r="DI3" s="28"/>
+      <c r="DJ3" s="28"/>
+      <c r="DK3" s="28"/>
+      <c r="DL3" s="28"/>
+      <c r="DM3" s="28"/>
+      <c r="DN3" s="28"/>
+      <c r="DO3" s="28"/>
+      <c r="DP3" s="28"/>
+      <c r="DQ3" s="28"/>
+      <c r="DR3" s="28"/>
+      <c r="DS3" s="28"/>
+      <c r="DT3" s="28"/>
     </row>
     <row r="4" spans="1:125" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="48"/>
-      <c r="C4" s="33" t="s">
+      <c r="A4" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="45"/>
+      <c r="C4" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="35"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="30"/>
-      <c r="O4" s="30"/>
-      <c r="P4" s="30"/>
-      <c r="Q4" s="30"/>
-      <c r="R4" s="30"/>
-      <c r="S4" s="30"/>
-      <c r="T4" s="30"/>
-      <c r="U4" s="30"/>
-      <c r="V4" s="30"/>
-      <c r="W4" s="30"/>
-      <c r="X4" s="30"/>
-      <c r="Y4" s="30"/>
-      <c r="Z4" s="30"/>
-      <c r="AA4" s="30"/>
-      <c r="AB4" s="30"/>
-      <c r="AC4" s="30"/>
-      <c r="AD4" s="30"/>
-      <c r="AE4" s="30"/>
-      <c r="AF4" s="30"/>
-      <c r="AG4" s="30"/>
-      <c r="AH4" s="30"/>
-      <c r="AI4" s="30"/>
-      <c r="AJ4" s="30"/>
-      <c r="AK4" s="30"/>
-      <c r="AL4" s="30"/>
-      <c r="AM4" s="30"/>
-      <c r="AN4" s="30"/>
-      <c r="AO4" s="30"/>
-      <c r="AP4" s="30"/>
-      <c r="AQ4" s="30"/>
-      <c r="AR4" s="30"/>
-      <c r="AS4" s="30"/>
-      <c r="AT4" s="30"/>
-      <c r="AU4" s="30"/>
-      <c r="AV4" s="30"/>
-      <c r="AW4" s="30"/>
-      <c r="AX4" s="30"/>
-      <c r="AY4" s="30"/>
-      <c r="AZ4" s="30"/>
-      <c r="BA4" s="30"/>
-      <c r="BB4" s="30"/>
-      <c r="BC4" s="30"/>
-      <c r="BD4" s="30"/>
-      <c r="BE4" s="30"/>
-      <c r="BF4" s="30"/>
-      <c r="BG4" s="30"/>
-      <c r="BH4" s="30"/>
-      <c r="BI4" s="30"/>
-      <c r="BJ4" s="30"/>
-      <c r="BK4" s="30"/>
-      <c r="BL4" s="30"/>
-      <c r="BM4" s="30"/>
-      <c r="BN4" s="30"/>
-      <c r="BO4" s="30"/>
-      <c r="BP4" s="30"/>
-      <c r="BQ4" s="30"/>
-      <c r="BR4" s="30"/>
-      <c r="BS4" s="30"/>
-      <c r="BT4" s="30"/>
-      <c r="BU4" s="30"/>
-      <c r="BV4" s="30"/>
-      <c r="BW4" s="30"/>
-      <c r="BX4" s="30"/>
-      <c r="BY4" s="30"/>
-      <c r="BZ4" s="30"/>
-      <c r="CA4" s="30"/>
-      <c r="CB4" s="30"/>
-      <c r="CC4" s="30"/>
-      <c r="CD4" s="30"/>
-      <c r="CE4" s="30"/>
-      <c r="CF4" s="30"/>
-      <c r="CG4" s="30"/>
-      <c r="CH4" s="30"/>
-      <c r="CI4" s="30"/>
-      <c r="CJ4" s="30"/>
-      <c r="CK4" s="30"/>
-      <c r="CL4" s="30"/>
-      <c r="CM4" s="30"/>
-      <c r="CN4" s="30"/>
-      <c r="CO4" s="30"/>
-      <c r="CP4" s="30"/>
-      <c r="CQ4" s="30"/>
-      <c r="CR4" s="30"/>
-      <c r="CS4" s="30"/>
-      <c r="CT4" s="30"/>
-      <c r="CU4" s="30"/>
-      <c r="CV4" s="30"/>
-      <c r="CW4" s="30"/>
-      <c r="CX4" s="30"/>
-      <c r="CY4" s="30"/>
-      <c r="CZ4" s="30"/>
-      <c r="DA4" s="30"/>
-      <c r="DB4" s="30"/>
-      <c r="DC4" s="30"/>
-      <c r="DD4" s="30"/>
-      <c r="DE4" s="30"/>
-      <c r="DF4" s="30"/>
-      <c r="DG4" s="30"/>
-      <c r="DH4" s="30"/>
-      <c r="DI4" s="30"/>
-      <c r="DJ4" s="30"/>
-      <c r="DK4" s="30"/>
-      <c r="DL4" s="30"/>
-      <c r="DM4" s="30"/>
-      <c r="DN4" s="30"/>
-      <c r="DO4" s="30"/>
-      <c r="DP4" s="30"/>
-      <c r="DQ4" s="30"/>
-      <c r="DR4" s="30"/>
-      <c r="DS4" s="30"/>
-      <c r="DT4" s="30"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="28"/>
+      <c r="Q4" s="28"/>
+      <c r="R4" s="28"/>
+      <c r="S4" s="28"/>
+      <c r="T4" s="28"/>
+      <c r="U4" s="28"/>
+      <c r="V4" s="28"/>
+      <c r="W4" s="28"/>
+      <c r="X4" s="28"/>
+      <c r="Y4" s="28"/>
+      <c r="Z4" s="28"/>
+      <c r="AA4" s="28"/>
+      <c r="AB4" s="28"/>
+      <c r="AC4" s="28"/>
+      <c r="AD4" s="28"/>
+      <c r="AE4" s="28"/>
+      <c r="AF4" s="28"/>
+      <c r="AG4" s="28"/>
+      <c r="AH4" s="28"/>
+      <c r="AI4" s="28"/>
+      <c r="AJ4" s="28"/>
+      <c r="AK4" s="28"/>
+      <c r="AL4" s="28"/>
+      <c r="AM4" s="28"/>
+      <c r="AN4" s="28"/>
+      <c r="AO4" s="28"/>
+      <c r="AP4" s="28"/>
+      <c r="AQ4" s="28"/>
+      <c r="AR4" s="28"/>
+      <c r="AS4" s="28"/>
+      <c r="AT4" s="28"/>
+      <c r="AU4" s="28"/>
+      <c r="AV4" s="28"/>
+      <c r="AW4" s="28"/>
+      <c r="AX4" s="28"/>
+      <c r="AY4" s="28"/>
+      <c r="AZ4" s="28"/>
+      <c r="BA4" s="28"/>
+      <c r="BB4" s="28"/>
+      <c r="BC4" s="28"/>
+      <c r="BD4" s="28"/>
+      <c r="BE4" s="28"/>
+      <c r="BF4" s="28"/>
+      <c r="BG4" s="28"/>
+      <c r="BH4" s="28"/>
+      <c r="BI4" s="28"/>
+      <c r="BJ4" s="28"/>
+      <c r="BK4" s="28"/>
+      <c r="BL4" s="28"/>
+      <c r="BM4" s="28"/>
+      <c r="BN4" s="28"/>
+      <c r="BO4" s="28"/>
+      <c r="BP4" s="28"/>
+      <c r="BQ4" s="28"/>
+      <c r="BR4" s="28"/>
+      <c r="BS4" s="28"/>
+      <c r="BT4" s="28"/>
+      <c r="BU4" s="28"/>
+      <c r="BV4" s="28"/>
+      <c r="BW4" s="28"/>
+      <c r="BX4" s="28"/>
+      <c r="BY4" s="28"/>
+      <c r="BZ4" s="28"/>
+      <c r="CA4" s="28"/>
+      <c r="CB4" s="28"/>
+      <c r="CC4" s="28"/>
+      <c r="CD4" s="28"/>
+      <c r="CE4" s="28"/>
+      <c r="CF4" s="28"/>
+      <c r="CG4" s="28"/>
+      <c r="CH4" s="28"/>
+      <c r="CI4" s="28"/>
+      <c r="CJ4" s="28"/>
+      <c r="CK4" s="28"/>
+      <c r="CL4" s="28"/>
+      <c r="CM4" s="28"/>
+      <c r="CN4" s="28"/>
+      <c r="CO4" s="28"/>
+      <c r="CP4" s="28"/>
+      <c r="CQ4" s="28"/>
+      <c r="CR4" s="28"/>
+      <c r="CS4" s="28"/>
+      <c r="CT4" s="28"/>
+      <c r="CU4" s="28"/>
+      <c r="CV4" s="28"/>
+      <c r="CW4" s="28"/>
+      <c r="CX4" s="28"/>
+      <c r="CY4" s="28"/>
+      <c r="CZ4" s="28"/>
+      <c r="DA4" s="28"/>
+      <c r="DB4" s="28"/>
+      <c r="DC4" s="28"/>
+      <c r="DD4" s="28"/>
+      <c r="DE4" s="28"/>
+      <c r="DF4" s="28"/>
+      <c r="DG4" s="28"/>
+      <c r="DH4" s="28"/>
+      <c r="DI4" s="28"/>
+      <c r="DJ4" s="28"/>
+      <c r="DK4" s="28"/>
+      <c r="DL4" s="28"/>
+      <c r="DM4" s="28"/>
+      <c r="DN4" s="28"/>
+      <c r="DO4" s="28"/>
+      <c r="DP4" s="28"/>
+      <c r="DQ4" s="28"/>
+      <c r="DR4" s="28"/>
+      <c r="DS4" s="28"/>
+      <c r="DT4" s="28"/>
     </row>
     <row r="5" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="49"/>
-      <c r="C5" s="50">
+      <c r="B5" s="48"/>
+      <c r="C5" s="49">
         <v>60</v>
       </c>
-      <c r="D5" s="51"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="30"/>
-      <c r="K5" s="30"/>
-      <c r="L5" s="30"/>
-      <c r="M5" s="30"/>
-      <c r="N5" s="30"/>
-      <c r="O5" s="30"/>
-      <c r="P5" s="30"/>
-      <c r="Q5" s="30"/>
-      <c r="R5" s="30"/>
-      <c r="S5" s="30"/>
-      <c r="T5" s="30"/>
-      <c r="U5" s="30"/>
-      <c r="V5" s="30"/>
-      <c r="W5" s="30"/>
-      <c r="X5" s="30"/>
-      <c r="Y5" s="30"/>
-      <c r="Z5" s="30"/>
-      <c r="AA5" s="30"/>
-      <c r="AB5" s="30"/>
-      <c r="AC5" s="30"/>
-      <c r="AD5" s="30"/>
-      <c r="AE5" s="30"/>
-      <c r="AF5" s="30"/>
-      <c r="AG5" s="30"/>
-      <c r="AH5" s="30"/>
-      <c r="AI5" s="30"/>
-      <c r="AJ5" s="30"/>
-      <c r="AK5" s="30"/>
-      <c r="AL5" s="30"/>
-      <c r="AM5" s="30"/>
-      <c r="AN5" s="30"/>
-      <c r="AO5" s="30"/>
-      <c r="AP5" s="30"/>
-      <c r="AQ5" s="30"/>
-      <c r="AR5" s="30"/>
-      <c r="AS5" s="30"/>
-      <c r="AT5" s="30"/>
-      <c r="AU5" s="30"/>
-      <c r="AV5" s="30"/>
-      <c r="AW5" s="30"/>
-      <c r="AX5" s="30"/>
-      <c r="AY5" s="30"/>
-      <c r="AZ5" s="30"/>
-      <c r="BA5" s="30"/>
-      <c r="BB5" s="30"/>
-      <c r="BC5" s="30"/>
-      <c r="BD5" s="30"/>
-      <c r="BE5" s="30"/>
-      <c r="BF5" s="30"/>
-      <c r="BG5" s="30"/>
-      <c r="BH5" s="30"/>
-      <c r="BI5" s="30"/>
-      <c r="BJ5" s="30"/>
-      <c r="BK5" s="30"/>
-      <c r="BL5" s="30"/>
-      <c r="BM5" s="30"/>
-      <c r="BN5" s="30"/>
-      <c r="BO5" s="30"/>
-      <c r="BP5" s="30"/>
-      <c r="BQ5" s="30"/>
-      <c r="BR5" s="30"/>
-      <c r="BS5" s="30"/>
-      <c r="BT5" s="30"/>
-      <c r="BU5" s="30"/>
-      <c r="BV5" s="30"/>
-      <c r="BW5" s="30"/>
-      <c r="BX5" s="30"/>
-      <c r="BY5" s="30"/>
-      <c r="BZ5" s="30"/>
-      <c r="CA5" s="30"/>
-      <c r="CB5" s="30"/>
-      <c r="CC5" s="30"/>
-      <c r="CD5" s="30"/>
-      <c r="CE5" s="30"/>
-      <c r="CF5" s="30"/>
-      <c r="CG5" s="30"/>
-      <c r="CH5" s="30"/>
-      <c r="CI5" s="30"/>
-      <c r="CJ5" s="30"/>
-      <c r="CK5" s="30"/>
-      <c r="CL5" s="30"/>
-      <c r="CM5" s="30"/>
-      <c r="CN5" s="30"/>
-      <c r="CO5" s="30"/>
-      <c r="CP5" s="30"/>
-      <c r="CQ5" s="30"/>
-      <c r="CR5" s="30"/>
-      <c r="CS5" s="30"/>
-      <c r="CT5" s="30"/>
-      <c r="CU5" s="30"/>
-      <c r="CV5" s="30"/>
-      <c r="CW5" s="30"/>
-      <c r="CX5" s="30"/>
-      <c r="CY5" s="30"/>
-      <c r="CZ5" s="30"/>
-      <c r="DA5" s="30"/>
-      <c r="DB5" s="30"/>
-      <c r="DC5" s="30"/>
-      <c r="DD5" s="30"/>
-      <c r="DE5" s="30"/>
-      <c r="DF5" s="30"/>
-      <c r="DG5" s="30"/>
-      <c r="DH5" s="30"/>
-      <c r="DI5" s="30"/>
-      <c r="DJ5" s="30"/>
-      <c r="DK5" s="30"/>
-      <c r="DL5" s="30"/>
-      <c r="DM5" s="30"/>
-      <c r="DN5" s="30"/>
-      <c r="DO5" s="30"/>
-      <c r="DP5" s="30"/>
-      <c r="DQ5" s="30"/>
-      <c r="DR5" s="30"/>
-      <c r="DS5" s="30"/>
-      <c r="DT5" s="30"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
+      <c r="Q5" s="28"/>
+      <c r="R5" s="28"/>
+      <c r="S5" s="28"/>
+      <c r="T5" s="28"/>
+      <c r="U5" s="28"/>
+      <c r="V5" s="28"/>
+      <c r="W5" s="28"/>
+      <c r="X5" s="28"/>
+      <c r="Y5" s="28"/>
+      <c r="Z5" s="28"/>
+      <c r="AA5" s="28"/>
+      <c r="AB5" s="28"/>
+      <c r="AC5" s="28"/>
+      <c r="AD5" s="28"/>
+      <c r="AE5" s="28"/>
+      <c r="AF5" s="28"/>
+      <c r="AG5" s="28"/>
+      <c r="AH5" s="28"/>
+      <c r="AI5" s="28"/>
+      <c r="AJ5" s="28"/>
+      <c r="AK5" s="28"/>
+      <c r="AL5" s="28"/>
+      <c r="AM5" s="28"/>
+      <c r="AN5" s="28"/>
+      <c r="AO5" s="28"/>
+      <c r="AP5" s="28"/>
+      <c r="AQ5" s="28"/>
+      <c r="AR5" s="28"/>
+      <c r="AS5" s="28"/>
+      <c r="AT5" s="28"/>
+      <c r="AU5" s="28"/>
+      <c r="AV5" s="28"/>
+      <c r="AW5" s="28"/>
+      <c r="AX5" s="28"/>
+      <c r="AY5" s="28"/>
+      <c r="AZ5" s="28"/>
+      <c r="BA5" s="28"/>
+      <c r="BB5" s="28"/>
+      <c r="BC5" s="28"/>
+      <c r="BD5" s="28"/>
+      <c r="BE5" s="28"/>
+      <c r="BF5" s="28"/>
+      <c r="BG5" s="28"/>
+      <c r="BH5" s="28"/>
+      <c r="BI5" s="28"/>
+      <c r="BJ5" s="28"/>
+      <c r="BK5" s="28"/>
+      <c r="BL5" s="28"/>
+      <c r="BM5" s="28"/>
+      <c r="BN5" s="28"/>
+      <c r="BO5" s="28"/>
+      <c r="BP5" s="28"/>
+      <c r="BQ5" s="28"/>
+      <c r="BR5" s="28"/>
+      <c r="BS5" s="28"/>
+      <c r="BT5" s="28"/>
+      <c r="BU5" s="28"/>
+      <c r="BV5" s="28"/>
+      <c r="BW5" s="28"/>
+      <c r="BX5" s="28"/>
+      <c r="BY5" s="28"/>
+      <c r="BZ5" s="28"/>
+      <c r="CA5" s="28"/>
+      <c r="CB5" s="28"/>
+      <c r="CC5" s="28"/>
+      <c r="CD5" s="28"/>
+      <c r="CE5" s="28"/>
+      <c r="CF5" s="28"/>
+      <c r="CG5" s="28"/>
+      <c r="CH5" s="28"/>
+      <c r="CI5" s="28"/>
+      <c r="CJ5" s="28"/>
+      <c r="CK5" s="28"/>
+      <c r="CL5" s="28"/>
+      <c r="CM5" s="28"/>
+      <c r="CN5" s="28"/>
+      <c r="CO5" s="28"/>
+      <c r="CP5" s="28"/>
+      <c r="CQ5" s="28"/>
+      <c r="CR5" s="28"/>
+      <c r="CS5" s="28"/>
+      <c r="CT5" s="28"/>
+      <c r="CU5" s="28"/>
+      <c r="CV5" s="28"/>
+      <c r="CW5" s="28"/>
+      <c r="CX5" s="28"/>
+      <c r="CY5" s="28"/>
+      <c r="CZ5" s="28"/>
+      <c r="DA5" s="28"/>
+      <c r="DB5" s="28"/>
+      <c r="DC5" s="28"/>
+      <c r="DD5" s="28"/>
+      <c r="DE5" s="28"/>
+      <c r="DF5" s="28"/>
+      <c r="DG5" s="28"/>
+      <c r="DH5" s="28"/>
+      <c r="DI5" s="28"/>
+      <c r="DJ5" s="28"/>
+      <c r="DK5" s="28"/>
+      <c r="DL5" s="28"/>
+      <c r="DM5" s="28"/>
+      <c r="DN5" s="28"/>
+      <c r="DO5" s="28"/>
+      <c r="DP5" s="28"/>
+      <c r="DQ5" s="28"/>
+      <c r="DR5" s="28"/>
+      <c r="DS5" s="28"/>
+      <c r="DT5" s="28"/>
     </row>
     <row r="6" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="50">
+      <c r="B6" s="48"/>
+      <c r="C6" s="49">
         <v>4</v>
       </c>
-      <c r="D6" s="51"/>
-      <c r="E6" s="46"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="30"/>
-      <c r="J6" s="30"/>
-      <c r="K6" s="30"/>
-      <c r="L6" s="30"/>
-      <c r="M6" s="30"/>
-      <c r="N6" s="30"/>
-      <c r="O6" s="30"/>
-      <c r="P6" s="30"/>
-      <c r="Q6" s="30"/>
-      <c r="R6" s="30"/>
-      <c r="S6" s="30"/>
-      <c r="T6" s="30"/>
-      <c r="U6" s="30"/>
-      <c r="V6" s="30"/>
-      <c r="W6" s="30"/>
-      <c r="X6" s="30"/>
-      <c r="Y6" s="30"/>
-      <c r="Z6" s="30"/>
-      <c r="AA6" s="30"/>
-      <c r="AB6" s="30"/>
-      <c r="AC6" s="30"/>
-      <c r="AD6" s="30"/>
-      <c r="AE6" s="30"/>
-      <c r="AF6" s="30"/>
-      <c r="AG6" s="30"/>
-      <c r="AH6" s="30"/>
-      <c r="AI6" s="30"/>
-      <c r="AJ6" s="30"/>
-      <c r="AK6" s="30"/>
-      <c r="AL6" s="30"/>
-      <c r="AM6" s="30"/>
-      <c r="AN6" s="30"/>
-      <c r="AO6" s="30"/>
-      <c r="AP6" s="30"/>
-      <c r="AQ6" s="30"/>
-      <c r="AR6" s="30"/>
-      <c r="AS6" s="30"/>
-      <c r="AT6" s="30"/>
-      <c r="AU6" s="30"/>
-      <c r="AV6" s="30"/>
-      <c r="AW6" s="30"/>
-      <c r="AX6" s="30"/>
-      <c r="AY6" s="30"/>
-      <c r="AZ6" s="30"/>
-      <c r="BA6" s="30"/>
-      <c r="BB6" s="30"/>
-      <c r="BC6" s="30"/>
-      <c r="BD6" s="30"/>
-      <c r="BE6" s="30"/>
-      <c r="BF6" s="30"/>
-      <c r="BG6" s="30"/>
-      <c r="BH6" s="30"/>
-      <c r="BI6" s="30"/>
-      <c r="BJ6" s="30"/>
-      <c r="BK6" s="30"/>
-      <c r="BL6" s="30"/>
-      <c r="BM6" s="30"/>
-      <c r="BN6" s="30"/>
-      <c r="BO6" s="30"/>
-      <c r="BP6" s="30"/>
-      <c r="BQ6" s="30"/>
-      <c r="BR6" s="30"/>
-      <c r="BS6" s="30"/>
-      <c r="BT6" s="30"/>
-      <c r="BU6" s="30"/>
-      <c r="BV6" s="30"/>
-      <c r="BW6" s="30"/>
-      <c r="BX6" s="30"/>
-      <c r="BY6" s="30"/>
-      <c r="BZ6" s="30"/>
-      <c r="CA6" s="30"/>
-      <c r="CB6" s="30"/>
-      <c r="CC6" s="30"/>
-      <c r="CD6" s="30"/>
-      <c r="CE6" s="30"/>
-      <c r="CF6" s="30"/>
-      <c r="CG6" s="30"/>
-      <c r="CH6" s="30"/>
-      <c r="CI6" s="30"/>
-      <c r="CJ6" s="30"/>
-      <c r="CK6" s="30"/>
-      <c r="CL6" s="30"/>
-      <c r="CM6" s="30"/>
-      <c r="CN6" s="30"/>
-      <c r="CO6" s="30"/>
-      <c r="CP6" s="30"/>
-      <c r="CQ6" s="30"/>
-      <c r="CR6" s="30"/>
-      <c r="CS6" s="30"/>
-      <c r="CT6" s="30"/>
-      <c r="CU6" s="30"/>
-      <c r="CV6" s="30"/>
-      <c r="CW6" s="30"/>
-      <c r="CX6" s="30"/>
-      <c r="CY6" s="30"/>
-      <c r="CZ6" s="30"/>
-      <c r="DA6" s="30"/>
-      <c r="DB6" s="30"/>
-      <c r="DC6" s="30"/>
-      <c r="DD6" s="30"/>
-      <c r="DE6" s="30"/>
-      <c r="DF6" s="30"/>
-      <c r="DG6" s="30"/>
-      <c r="DH6" s="30"/>
-      <c r="DI6" s="30"/>
-      <c r="DJ6" s="30"/>
-      <c r="DK6" s="30"/>
-      <c r="DL6" s="30"/>
-      <c r="DM6" s="30"/>
-      <c r="DN6" s="30"/>
-      <c r="DO6" s="30"/>
-      <c r="DP6" s="30"/>
-      <c r="DQ6" s="30"/>
-      <c r="DR6" s="30"/>
-      <c r="DS6" s="30"/>
-      <c r="DT6" s="30"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="28"/>
+      <c r="M6" s="28"/>
+      <c r="N6" s="28"/>
+      <c r="O6" s="28"/>
+      <c r="P6" s="28"/>
+      <c r="Q6" s="28"/>
+      <c r="R6" s="28"/>
+      <c r="S6" s="28"/>
+      <c r="T6" s="28"/>
+      <c r="U6" s="28"/>
+      <c r="V6" s="28"/>
+      <c r="W6" s="28"/>
+      <c r="X6" s="28"/>
+      <c r="Y6" s="28"/>
+      <c r="Z6" s="28"/>
+      <c r="AA6" s="28"/>
+      <c r="AB6" s="28"/>
+      <c r="AC6" s="28"/>
+      <c r="AD6" s="28"/>
+      <c r="AE6" s="28"/>
+      <c r="AF6" s="28"/>
+      <c r="AG6" s="28"/>
+      <c r="AH6" s="28"/>
+      <c r="AI6" s="28"/>
+      <c r="AJ6" s="28"/>
+      <c r="AK6" s="28"/>
+      <c r="AL6" s="28"/>
+      <c r="AM6" s="28"/>
+      <c r="AN6" s="28"/>
+      <c r="AO6" s="28"/>
+      <c r="AP6" s="28"/>
+      <c r="AQ6" s="28"/>
+      <c r="AR6" s="28"/>
+      <c r="AS6" s="28"/>
+      <c r="AT6" s="28"/>
+      <c r="AU6" s="28"/>
+      <c r="AV6" s="28"/>
+      <c r="AW6" s="28"/>
+      <c r="AX6" s="28"/>
+      <c r="AY6" s="28"/>
+      <c r="AZ6" s="28"/>
+      <c r="BA6" s="28"/>
+      <c r="BB6" s="28"/>
+      <c r="BC6" s="28"/>
+      <c r="BD6" s="28"/>
+      <c r="BE6" s="28"/>
+      <c r="BF6" s="28"/>
+      <c r="BG6" s="28"/>
+      <c r="BH6" s="28"/>
+      <c r="BI6" s="28"/>
+      <c r="BJ6" s="28"/>
+      <c r="BK6" s="28"/>
+      <c r="BL6" s="28"/>
+      <c r="BM6" s="28"/>
+      <c r="BN6" s="28"/>
+      <c r="BO6" s="28"/>
+      <c r="BP6" s="28"/>
+      <c r="BQ6" s="28"/>
+      <c r="BR6" s="28"/>
+      <c r="BS6" s="28"/>
+      <c r="BT6" s="28"/>
+      <c r="BU6" s="28"/>
+      <c r="BV6" s="28"/>
+      <c r="BW6" s="28"/>
+      <c r="BX6" s="28"/>
+      <c r="BY6" s="28"/>
+      <c r="BZ6" s="28"/>
+      <c r="CA6" s="28"/>
+      <c r="CB6" s="28"/>
+      <c r="CC6" s="28"/>
+      <c r="CD6" s="28"/>
+      <c r="CE6" s="28"/>
+      <c r="CF6" s="28"/>
+      <c r="CG6" s="28"/>
+      <c r="CH6" s="28"/>
+      <c r="CI6" s="28"/>
+      <c r="CJ6" s="28"/>
+      <c r="CK6" s="28"/>
+      <c r="CL6" s="28"/>
+      <c r="CM6" s="28"/>
+      <c r="CN6" s="28"/>
+      <c r="CO6" s="28"/>
+      <c r="CP6" s="28"/>
+      <c r="CQ6" s="28"/>
+      <c r="CR6" s="28"/>
+      <c r="CS6" s="28"/>
+      <c r="CT6" s="28"/>
+      <c r="CU6" s="28"/>
+      <c r="CV6" s="28"/>
+      <c r="CW6" s="28"/>
+      <c r="CX6" s="28"/>
+      <c r="CY6" s="28"/>
+      <c r="CZ6" s="28"/>
+      <c r="DA6" s="28"/>
+      <c r="DB6" s="28"/>
+      <c r="DC6" s="28"/>
+      <c r="DD6" s="28"/>
+      <c r="DE6" s="28"/>
+      <c r="DF6" s="28"/>
+      <c r="DG6" s="28"/>
+      <c r="DH6" s="28"/>
+      <c r="DI6" s="28"/>
+      <c r="DJ6" s="28"/>
+      <c r="DK6" s="28"/>
+      <c r="DL6" s="28"/>
+      <c r="DM6" s="28"/>
+      <c r="DN6" s="28"/>
+      <c r="DO6" s="28"/>
+      <c r="DP6" s="28"/>
+      <c r="DQ6" s="28"/>
+      <c r="DR6" s="28"/>
+      <c r="DS6" s="28"/>
+      <c r="DT6" s="28"/>
     </row>
     <row r="7" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="52"/>
-      <c r="C7" s="50">
+      <c r="B7" s="51"/>
+      <c r="C7" s="49">
         <v>11</v>
       </c>
-      <c r="D7" s="51"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="31"/>
-      <c r="M7" s="31"/>
-      <c r="N7" s="31"/>
-      <c r="O7" s="31"/>
-      <c r="P7" s="31"/>
-      <c r="Q7" s="31"/>
-      <c r="R7" s="31"/>
-      <c r="S7" s="31"/>
-      <c r="T7" s="31"/>
-      <c r="U7" s="31"/>
-      <c r="V7" s="31"/>
-      <c r="W7" s="31"/>
-      <c r="X7" s="31"/>
-      <c r="Y7" s="31"/>
-      <c r="Z7" s="31"/>
-      <c r="AA7" s="31"/>
-      <c r="AB7" s="31"/>
-      <c r="AC7" s="31"/>
-      <c r="AD7" s="31"/>
-      <c r="AE7" s="31"/>
-      <c r="AF7" s="31"/>
-      <c r="AG7" s="31"/>
-      <c r="AH7" s="31"/>
-      <c r="AI7" s="31"/>
-      <c r="AJ7" s="31"/>
-      <c r="AK7" s="31"/>
-      <c r="AL7" s="31"/>
-      <c r="AM7" s="31"/>
-      <c r="AN7" s="31"/>
-      <c r="AO7" s="31"/>
-      <c r="AP7" s="31"/>
-      <c r="AQ7" s="31"/>
-      <c r="AR7" s="31"/>
-      <c r="AS7" s="31"/>
-      <c r="AT7" s="31"/>
-      <c r="AU7" s="31"/>
-      <c r="AV7" s="31"/>
-      <c r="AW7" s="31"/>
-      <c r="AX7" s="31"/>
-      <c r="AY7" s="31"/>
-      <c r="AZ7" s="31"/>
-      <c r="BA7" s="31"/>
-      <c r="BB7" s="31"/>
-      <c r="BC7" s="31"/>
-      <c r="BD7" s="31"/>
-      <c r="BE7" s="31"/>
-      <c r="BF7" s="31"/>
-      <c r="BG7" s="31"/>
-      <c r="BH7" s="31"/>
-      <c r="BI7" s="31"/>
-      <c r="BJ7" s="31"/>
-      <c r="BK7" s="31"/>
-      <c r="BL7" s="31"/>
-      <c r="BM7" s="31"/>
-      <c r="BN7" s="31"/>
-      <c r="BO7" s="31"/>
-      <c r="BP7" s="31"/>
-      <c r="BQ7" s="31"/>
-      <c r="BR7" s="31"/>
-      <c r="BS7" s="31"/>
-      <c r="BT7" s="31"/>
-      <c r="BU7" s="31"/>
-      <c r="BV7" s="31"/>
-      <c r="BW7" s="31"/>
-      <c r="BX7" s="31"/>
-      <c r="BY7" s="31"/>
-      <c r="BZ7" s="31"/>
-      <c r="CA7" s="31"/>
-      <c r="CB7" s="31"/>
-      <c r="CC7" s="31"/>
-      <c r="CD7" s="31"/>
-      <c r="CE7" s="31"/>
-      <c r="CF7" s="31"/>
-      <c r="CG7" s="31"/>
-      <c r="CH7" s="31"/>
-      <c r="CI7" s="31"/>
-      <c r="CJ7" s="31"/>
-      <c r="CK7" s="31"/>
-      <c r="CL7" s="31"/>
-      <c r="CM7" s="31"/>
-      <c r="CN7" s="31"/>
-      <c r="CO7" s="31"/>
-      <c r="CP7" s="31"/>
-      <c r="CQ7" s="31"/>
-      <c r="CR7" s="31"/>
-      <c r="CS7" s="31"/>
-      <c r="CT7" s="31"/>
-      <c r="CU7" s="31"/>
-      <c r="CV7" s="31"/>
-      <c r="CW7" s="31"/>
-      <c r="CX7" s="31"/>
-      <c r="CY7" s="31"/>
-      <c r="CZ7" s="31"/>
-      <c r="DA7" s="31"/>
-      <c r="DB7" s="31"/>
-      <c r="DC7" s="31"/>
-      <c r="DD7" s="31"/>
-      <c r="DE7" s="31"/>
-      <c r="DF7" s="31"/>
-      <c r="DG7" s="31"/>
-      <c r="DH7" s="31"/>
-      <c r="DI7" s="31"/>
-      <c r="DJ7" s="31"/>
-      <c r="DK7" s="31"/>
-      <c r="DL7" s="31"/>
-      <c r="DM7" s="31"/>
-      <c r="DN7" s="31"/>
-      <c r="DO7" s="31"/>
-      <c r="DP7" s="31"/>
-      <c r="DQ7" s="31"/>
-      <c r="DR7" s="31"/>
-      <c r="DS7" s="31"/>
-      <c r="DT7" s="31"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="29"/>
+      <c r="N7" s="29"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="29"/>
+      <c r="Q7" s="29"/>
+      <c r="R7" s="29"/>
+      <c r="S7" s="29"/>
+      <c r="T7" s="29"/>
+      <c r="U7" s="29"/>
+      <c r="V7" s="29"/>
+      <c r="W7" s="29"/>
+      <c r="X7" s="29"/>
+      <c r="Y7" s="29"/>
+      <c r="Z7" s="29"/>
+      <c r="AA7" s="29"/>
+      <c r="AB7" s="29"/>
+      <c r="AC7" s="29"/>
+      <c r="AD7" s="29"/>
+      <c r="AE7" s="29"/>
+      <c r="AF7" s="29"/>
+      <c r="AG7" s="29"/>
+      <c r="AH7" s="29"/>
+      <c r="AI7" s="29"/>
+      <c r="AJ7" s="29"/>
+      <c r="AK7" s="29"/>
+      <c r="AL7" s="29"/>
+      <c r="AM7" s="29"/>
+      <c r="AN7" s="29"/>
+      <c r="AO7" s="29"/>
+      <c r="AP7" s="29"/>
+      <c r="AQ7" s="29"/>
+      <c r="AR7" s="29"/>
+      <c r="AS7" s="29"/>
+      <c r="AT7" s="29"/>
+      <c r="AU7" s="29"/>
+      <c r="AV7" s="29"/>
+      <c r="AW7" s="29"/>
+      <c r="AX7" s="29"/>
+      <c r="AY7" s="29"/>
+      <c r="AZ7" s="29"/>
+      <c r="BA7" s="29"/>
+      <c r="BB7" s="29"/>
+      <c r="BC7" s="29"/>
+      <c r="BD7" s="29"/>
+      <c r="BE7" s="29"/>
+      <c r="BF7" s="29"/>
+      <c r="BG7" s="29"/>
+      <c r="BH7" s="29"/>
+      <c r="BI7" s="29"/>
+      <c r="BJ7" s="29"/>
+      <c r="BK7" s="29"/>
+      <c r="BL7" s="29"/>
+      <c r="BM7" s="29"/>
+      <c r="BN7" s="29"/>
+      <c r="BO7" s="29"/>
+      <c r="BP7" s="29"/>
+      <c r="BQ7" s="29"/>
+      <c r="BR7" s="29"/>
+      <c r="BS7" s="29"/>
+      <c r="BT7" s="29"/>
+      <c r="BU7" s="29"/>
+      <c r="BV7" s="29"/>
+      <c r="BW7" s="29"/>
+      <c r="BX7" s="29"/>
+      <c r="BY7" s="29"/>
+      <c r="BZ7" s="29"/>
+      <c r="CA7" s="29"/>
+      <c r="CB7" s="29"/>
+      <c r="CC7" s="29"/>
+      <c r="CD7" s="29"/>
+      <c r="CE7" s="29"/>
+      <c r="CF7" s="29"/>
+      <c r="CG7" s="29"/>
+      <c r="CH7" s="29"/>
+      <c r="CI7" s="29"/>
+      <c r="CJ7" s="29"/>
+      <c r="CK7" s="29"/>
+      <c r="CL7" s="29"/>
+      <c r="CM7" s="29"/>
+      <c r="CN7" s="29"/>
+      <c r="CO7" s="29"/>
+      <c r="CP7" s="29"/>
+      <c r="CQ7" s="29"/>
+      <c r="CR7" s="29"/>
+      <c r="CS7" s="29"/>
+      <c r="CT7" s="29"/>
+      <c r="CU7" s="29"/>
+      <c r="CV7" s="29"/>
+      <c r="CW7" s="29"/>
+      <c r="CX7" s="29"/>
+      <c r="CY7" s="29"/>
+      <c r="CZ7" s="29"/>
+      <c r="DA7" s="29"/>
+      <c r="DB7" s="29"/>
+      <c r="DC7" s="29"/>
+      <c r="DD7" s="29"/>
+      <c r="DE7" s="29"/>
+      <c r="DF7" s="29"/>
+      <c r="DG7" s="29"/>
+      <c r="DH7" s="29"/>
+      <c r="DI7" s="29"/>
+      <c r="DJ7" s="29"/>
+      <c r="DK7" s="29"/>
+      <c r="DL7" s="29"/>
+      <c r="DM7" s="29"/>
+      <c r="DN7" s="29"/>
+      <c r="DO7" s="29"/>
+      <c r="DP7" s="29"/>
+      <c r="DQ7" s="29"/>
+      <c r="DR7" s="29"/>
+      <c r="DS7" s="29"/>
+      <c r="DT7" s="29"/>
     </row>
     <row r="8" spans="1:125" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="32">
+      <c r="B8" s="52"/>
+      <c r="C8" s="53">
         <f>SUM(C5:D7)</f>
         <v>75</v>
       </c>
-      <c r="D8" s="35"/>
+      <c r="D8" s="47"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="28">
-        <v>1</v>
-      </c>
-      <c r="G8" s="28">
+      <c r="F8" s="33">
+        <v>1</v>
+      </c>
+      <c r="G8" s="33">
         <v>2</v>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="33">
         <v>3</v>
       </c>
-      <c r="I8" s="28">
+      <c r="I8" s="33">
         <v>4</v>
       </c>
-      <c r="J8" s="28">
+      <c r="J8" s="33">
         <v>5</v>
       </c>
-      <c r="K8" s="28">
+      <c r="K8" s="33">
         <v>6</v>
       </c>
-      <c r="L8" s="28">
+      <c r="L8" s="33">
         <v>7</v>
       </c>
-      <c r="M8" s="28">
+      <c r="M8" s="33">
         <v>8</v>
       </c>
-      <c r="N8" s="28">
+      <c r="N8" s="33">
         <v>9</v>
       </c>
-      <c r="O8" s="28">
+      <c r="O8" s="33">
         <v>10</v>
       </c>
-      <c r="P8" s="28">
+      <c r="P8" s="33">
         <v>11</v>
       </c>
-      <c r="Q8" s="28">
+      <c r="Q8" s="33">
         <v>12</v>
       </c>
-      <c r="R8" s="28">
+      <c r="R8" s="33">
         <v>13</v>
       </c>
-      <c r="S8" s="28">
+      <c r="S8" s="33">
         <v>14</v>
       </c>
-      <c r="T8" s="28">
+      <c r="T8" s="33">
         <v>15</v>
       </c>
-      <c r="U8" s="28">
+      <c r="U8" s="33">
         <v>16</v>
       </c>
-      <c r="V8" s="28">
+      <c r="V8" s="33">
         <v>17</v>
       </c>
-      <c r="W8" s="28">
+      <c r="W8" s="33">
         <v>18</v>
       </c>
-      <c r="X8" s="28">
+      <c r="X8" s="33">
         <v>19</v>
       </c>
-      <c r="Y8" s="28">
+      <c r="Y8" s="33">
         <v>20</v>
       </c>
-      <c r="Z8" s="28">
+      <c r="Z8" s="33">
         <v>21</v>
       </c>
-      <c r="AA8" s="28">
+      <c r="AA8" s="33">
         <v>22</v>
       </c>
-      <c r="AB8" s="28">
+      <c r="AB8" s="33">
         <v>23</v>
       </c>
-      <c r="AC8" s="28">
+      <c r="AC8" s="33">
         <v>24</v>
       </c>
-      <c r="AD8" s="28">
+      <c r="AD8" s="33">
         <v>25</v>
       </c>
-      <c r="AE8" s="28">
+      <c r="AE8" s="33">
         <v>26</v>
       </c>
-      <c r="AF8" s="28">
+      <c r="AF8" s="33">
         <v>27</v>
       </c>
-      <c r="AG8" s="28">
+      <c r="AG8" s="33">
         <v>28</v>
       </c>
-      <c r="AH8" s="28">
+      <c r="AH8" s="33">
         <v>29</v>
       </c>
-      <c r="AI8" s="28">
+      <c r="AI8" s="33">
         <v>30</v>
       </c>
-      <c r="AJ8" s="28">
+      <c r="AJ8" s="33">
         <v>31</v>
       </c>
-      <c r="AK8" s="28">
+      <c r="AK8" s="33">
         <v>32</v>
       </c>
-      <c r="AL8" s="28">
+      <c r="AL8" s="33">
         <v>33</v>
       </c>
-      <c r="AM8" s="28">
+      <c r="AM8" s="33">
         <v>34</v>
       </c>
-      <c r="AN8" s="28">
+      <c r="AN8" s="33">
         <v>35</v>
       </c>
-      <c r="AO8" s="28">
+      <c r="AO8" s="33">
         <v>36</v>
       </c>
-      <c r="AP8" s="28">
+      <c r="AP8" s="33">
         <v>37</v>
       </c>
-      <c r="AQ8" s="28">
+      <c r="AQ8" s="33">
         <v>38</v>
       </c>
-      <c r="AR8" s="28">
+      <c r="AR8" s="33">
         <v>39</v>
       </c>
-      <c r="AS8" s="28">
+      <c r="AS8" s="33">
         <v>40</v>
       </c>
-      <c r="AT8" s="28">
+      <c r="AT8" s="33">
         <v>41</v>
       </c>
-      <c r="AU8" s="28">
+      <c r="AU8" s="33">
         <v>42</v>
       </c>
-      <c r="AV8" s="28">
+      <c r="AV8" s="33">
         <v>43</v>
       </c>
-      <c r="AW8" s="28">
+      <c r="AW8" s="33">
         <v>44</v>
       </c>
-      <c r="AX8" s="28">
+      <c r="AX8" s="33">
         <v>45</v>
       </c>
-      <c r="AY8" s="28">
+      <c r="AY8" s="33">
         <v>46</v>
       </c>
-      <c r="AZ8" s="28">
+      <c r="AZ8" s="33">
         <v>47</v>
       </c>
-      <c r="BA8" s="28">
+      <c r="BA8" s="33">
         <v>48</v>
       </c>
-      <c r="BB8" s="28">
+      <c r="BB8" s="33">
         <v>49</v>
       </c>
-      <c r="BC8" s="28">
+      <c r="BC8" s="33">
         <v>50</v>
       </c>
-      <c r="BD8" s="28">
+      <c r="BD8" s="33">
         <v>51</v>
       </c>
-      <c r="BE8" s="28">
+      <c r="BE8" s="33">
         <v>52</v>
       </c>
-      <c r="BF8" s="28">
+      <c r="BF8" s="33">
         <v>53</v>
       </c>
-      <c r="BG8" s="28">
+      <c r="BG8" s="33">
         <v>54</v>
       </c>
-      <c r="BH8" s="28">
+      <c r="BH8" s="33">
         <v>55</v>
       </c>
-      <c r="BI8" s="28">
+      <c r="BI8" s="33">
         <v>56</v>
       </c>
-      <c r="BJ8" s="28">
+      <c r="BJ8" s="33">
         <v>57</v>
       </c>
-      <c r="BK8" s="28">
+      <c r="BK8" s="33">
         <v>58</v>
       </c>
-      <c r="BL8" s="28">
+      <c r="BL8" s="33">
         <v>59</v>
       </c>
-      <c r="BM8" s="28">
+      <c r="BM8" s="33">
         <v>60</v>
       </c>
-      <c r="BN8" s="28">
+      <c r="BN8" s="33">
         <v>61</v>
       </c>
-      <c r="BO8" s="28">
+      <c r="BO8" s="33">
         <v>62</v>
       </c>
-      <c r="BP8" s="28">
+      <c r="BP8" s="33">
         <v>63</v>
       </c>
-      <c r="BQ8" s="28">
+      <c r="BQ8" s="33">
         <v>64</v>
       </c>
-      <c r="BR8" s="28">
+      <c r="BR8" s="33">
         <v>65</v>
       </c>
-      <c r="BS8" s="28">
+      <c r="BS8" s="33">
         <v>66</v>
       </c>
-      <c r="BT8" s="28">
+      <c r="BT8" s="33">
         <v>67</v>
       </c>
-      <c r="BU8" s="28">
+      <c r="BU8" s="33">
         <v>68</v>
       </c>
-      <c r="BV8" s="28">
+      <c r="BV8" s="33">
         <v>69</v>
       </c>
-      <c r="BW8" s="28">
+      <c r="BW8" s="33">
         <v>70</v>
       </c>
-      <c r="BX8" s="28">
+      <c r="BX8" s="33">
         <v>71</v>
       </c>
-      <c r="BY8" s="28">
+      <c r="BY8" s="33">
         <v>72</v>
       </c>
-      <c r="BZ8" s="28">
+      <c r="BZ8" s="33">
         <v>73</v>
       </c>
-      <c r="CA8" s="28">
+      <c r="CA8" s="33">
         <v>74</v>
       </c>
-      <c r="CB8" s="28">
+      <c r="CB8" s="33">
         <v>75</v>
       </c>
-      <c r="CC8" s="28">
+      <c r="CC8" s="33">
         <v>76</v>
       </c>
-      <c r="CD8" s="28">
+      <c r="CD8" s="33">
         <v>77</v>
       </c>
-      <c r="CE8" s="28">
+      <c r="CE8" s="33">
         <v>78</v>
       </c>
-      <c r="CF8" s="28">
+      <c r="CF8" s="33">
         <v>79</v>
       </c>
-      <c r="CG8" s="28">
+      <c r="CG8" s="33">
         <v>80</v>
       </c>
-      <c r="CH8" s="28">
+      <c r="CH8" s="33">
         <v>81</v>
       </c>
-      <c r="CI8" s="28">
+      <c r="CI8" s="33">
         <v>82</v>
       </c>
-      <c r="CJ8" s="28">
+      <c r="CJ8" s="33">
         <v>83</v>
       </c>
-      <c r="CK8" s="28">
+      <c r="CK8" s="33">
         <v>84</v>
       </c>
-      <c r="CL8" s="28">
+      <c r="CL8" s="33">
         <v>85</v>
       </c>
-      <c r="CM8" s="28">
+      <c r="CM8" s="33">
         <v>86</v>
       </c>
-      <c r="CN8" s="28">
+      <c r="CN8" s="33">
         <v>87</v>
       </c>
-      <c r="CO8" s="28">
+      <c r="CO8" s="33">
         <v>88</v>
       </c>
-      <c r="CP8" s="28">
+      <c r="CP8" s="33">
         <v>89</v>
       </c>
-      <c r="CQ8" s="28">
+      <c r="CQ8" s="33">
         <v>90</v>
       </c>
-      <c r="CR8" s="28">
+      <c r="CR8" s="33">
         <v>91</v>
       </c>
-      <c r="CS8" s="28">
+      <c r="CS8" s="33">
         <v>92</v>
       </c>
-      <c r="CT8" s="28">
+      <c r="CT8" s="33">
         <v>93</v>
       </c>
-      <c r="CU8" s="28">
+      <c r="CU8" s="33">
         <v>94</v>
       </c>
-      <c r="CV8" s="28">
+      <c r="CV8" s="33">
         <v>95</v>
       </c>
-      <c r="CW8" s="28">
+      <c r="CW8" s="33">
         <v>96</v>
       </c>
-      <c r="CX8" s="28">
+      <c r="CX8" s="33">
         <v>97</v>
       </c>
-      <c r="CY8" s="28">
+      <c r="CY8" s="33">
         <v>98</v>
       </c>
-      <c r="CZ8" s="28">
+      <c r="CZ8" s="33">
         <v>99</v>
       </c>
-      <c r="DA8" s="28">
+      <c r="DA8" s="33">
         <v>100</v>
       </c>
-      <c r="DB8" s="28">
+      <c r="DB8" s="33">
         <v>101</v>
       </c>
-      <c r="DC8" s="28">
+      <c r="DC8" s="33">
         <v>102</v>
       </c>
-      <c r="DD8" s="28">
+      <c r="DD8" s="33">
         <v>103</v>
       </c>
-      <c r="DE8" s="28">
+      <c r="DE8" s="33">
         <v>104</v>
       </c>
-      <c r="DF8" s="28">
+      <c r="DF8" s="33">
         <v>105</v>
       </c>
-      <c r="DG8" s="28">
+      <c r="DG8" s="33">
         <v>106</v>
       </c>
-      <c r="DH8" s="28">
+      <c r="DH8" s="33">
         <v>107</v>
       </c>
-      <c r="DI8" s="28">
+      <c r="DI8" s="33">
         <v>108</v>
       </c>
-      <c r="DJ8" s="28">
+      <c r="DJ8" s="33">
         <v>109</v>
       </c>
-      <c r="DK8" s="28">
+      <c r="DK8" s="33">
         <v>110</v>
       </c>
-      <c r="DL8" s="28">
+      <c r="DL8" s="33">
         <v>111</v>
       </c>
-      <c r="DM8" s="28">
+      <c r="DM8" s="33">
         <v>112</v>
       </c>
-      <c r="DN8" s="28">
+      <c r="DN8" s="33">
         <v>113</v>
       </c>
-      <c r="DO8" s="28">
+      <c r="DO8" s="33">
         <v>114</v>
       </c>
-      <c r="DP8" s="28">
+      <c r="DP8" s="33">
         <v>115</v>
       </c>
-      <c r="DQ8" s="28">
+      <c r="DQ8" s="33">
         <v>116</v>
       </c>
-      <c r="DR8" s="28">
+      <c r="DR8" s="33">
         <v>117</v>
       </c>
-      <c r="DS8" s="28">
+      <c r="DS8" s="33">
         <v>118</v>
       </c>
-      <c r="DT8" s="28">
+      <c r="DT8" s="33">
         <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="37" t="s">
+      <c r="B9" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="38" t="s">
+      <c r="C9" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="37"/>
+      <c r="D9" s="54"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="29"/>
-      <c r="P9" s="29"/>
-      <c r="Q9" s="29"/>
-      <c r="R9" s="29"/>
-      <c r="S9" s="29"/>
-      <c r="T9" s="29"/>
-      <c r="U9" s="29"/>
-      <c r="V9" s="29"/>
-      <c r="W9" s="29"/>
-      <c r="X9" s="29"/>
-      <c r="Y9" s="29"/>
-      <c r="Z9" s="29"/>
-      <c r="AA9" s="29"/>
-      <c r="AB9" s="29"/>
-      <c r="AC9" s="29"/>
-      <c r="AD9" s="29"/>
-      <c r="AE9" s="29"/>
-      <c r="AF9" s="29"/>
-      <c r="AG9" s="29"/>
-      <c r="AH9" s="29"/>
-      <c r="AI9" s="29"/>
-      <c r="AJ9" s="29"/>
-      <c r="AK9" s="29"/>
-      <c r="AL9" s="29"/>
-      <c r="AM9" s="29"/>
-      <c r="AN9" s="29"/>
-      <c r="AO9" s="29"/>
-      <c r="AP9" s="29"/>
-      <c r="AQ9" s="29"/>
-      <c r="AR9" s="29"/>
-      <c r="AS9" s="29"/>
-      <c r="AT9" s="29"/>
-      <c r="AU9" s="29"/>
-      <c r="AV9" s="29"/>
-      <c r="AW9" s="29"/>
-      <c r="AX9" s="29"/>
-      <c r="AY9" s="29"/>
-      <c r="AZ9" s="29"/>
-      <c r="BA9" s="29"/>
-      <c r="BB9" s="29"/>
-      <c r="BC9" s="29"/>
-      <c r="BD9" s="29"/>
-      <c r="BE9" s="29"/>
-      <c r="BF9" s="29"/>
-      <c r="BG9" s="29"/>
-      <c r="BH9" s="29"/>
-      <c r="BI9" s="29"/>
-      <c r="BJ9" s="29"/>
-      <c r="BK9" s="29"/>
-      <c r="BL9" s="29"/>
-      <c r="BM9" s="29"/>
-      <c r="BN9" s="29"/>
-      <c r="BO9" s="29"/>
-      <c r="BP9" s="29"/>
-      <c r="BQ9" s="29"/>
-      <c r="BR9" s="29"/>
-      <c r="BS9" s="29"/>
-      <c r="BT9" s="29"/>
-      <c r="BU9" s="29"/>
-      <c r="BV9" s="29"/>
-      <c r="BW9" s="29"/>
-      <c r="BX9" s="29"/>
-      <c r="BY9" s="29"/>
-      <c r="BZ9" s="29"/>
-      <c r="CA9" s="29"/>
-      <c r="CB9" s="29"/>
-      <c r="CC9" s="29"/>
-      <c r="CD9" s="29"/>
-      <c r="CE9" s="29"/>
-      <c r="CF9" s="29"/>
-      <c r="CG9" s="29"/>
-      <c r="CH9" s="29"/>
-      <c r="CI9" s="29"/>
-      <c r="CJ9" s="29"/>
-      <c r="CK9" s="29"/>
-      <c r="CL9" s="29"/>
-      <c r="CM9" s="29"/>
-      <c r="CN9" s="29"/>
-      <c r="CO9" s="29"/>
-      <c r="CP9" s="29"/>
-      <c r="CQ9" s="29"/>
-      <c r="CR9" s="29"/>
-      <c r="CS9" s="29"/>
-      <c r="CT9" s="29"/>
-      <c r="CU9" s="29"/>
-      <c r="CV9" s="29"/>
-      <c r="CW9" s="29"/>
-      <c r="CX9" s="29"/>
-      <c r="CY9" s="29"/>
-      <c r="CZ9" s="29"/>
-      <c r="DA9" s="29"/>
-      <c r="DB9" s="29"/>
-      <c r="DC9" s="29"/>
-      <c r="DD9" s="29"/>
-      <c r="DE9" s="29"/>
-      <c r="DF9" s="29"/>
-      <c r="DG9" s="29"/>
-      <c r="DH9" s="29"/>
-      <c r="DI9" s="29"/>
-      <c r="DJ9" s="29"/>
-      <c r="DK9" s="29"/>
-      <c r="DL9" s="29"/>
-      <c r="DM9" s="29"/>
-      <c r="DN9" s="29"/>
-      <c r="DO9" s="29"/>
-      <c r="DP9" s="29"/>
-      <c r="DQ9" s="29"/>
-      <c r="DR9" s="29"/>
-      <c r="DS9" s="29"/>
-      <c r="DT9" s="29"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
+      <c r="K9" s="34"/>
+      <c r="L9" s="34"/>
+      <c r="M9" s="34"/>
+      <c r="N9" s="34"/>
+      <c r="O9" s="34"/>
+      <c r="P9" s="34"/>
+      <c r="Q9" s="34"/>
+      <c r="R9" s="34"/>
+      <c r="S9" s="34"/>
+      <c r="T9" s="34"/>
+      <c r="U9" s="34"/>
+      <c r="V9" s="34"/>
+      <c r="W9" s="34"/>
+      <c r="X9" s="34"/>
+      <c r="Y9" s="34"/>
+      <c r="Z9" s="34"/>
+      <c r="AA9" s="34"/>
+      <c r="AB9" s="34"/>
+      <c r="AC9" s="34"/>
+      <c r="AD9" s="34"/>
+      <c r="AE9" s="34"/>
+      <c r="AF9" s="34"/>
+      <c r="AG9" s="34"/>
+      <c r="AH9" s="34"/>
+      <c r="AI9" s="34"/>
+      <c r="AJ9" s="34"/>
+      <c r="AK9" s="34"/>
+      <c r="AL9" s="34"/>
+      <c r="AM9" s="34"/>
+      <c r="AN9" s="34"/>
+      <c r="AO9" s="34"/>
+      <c r="AP9" s="34"/>
+      <c r="AQ9" s="34"/>
+      <c r="AR9" s="34"/>
+      <c r="AS9" s="34"/>
+      <c r="AT9" s="34"/>
+      <c r="AU9" s="34"/>
+      <c r="AV9" s="34"/>
+      <c r="AW9" s="34"/>
+      <c r="AX9" s="34"/>
+      <c r="AY9" s="34"/>
+      <c r="AZ9" s="34"/>
+      <c r="BA9" s="34"/>
+      <c r="BB9" s="34"/>
+      <c r="BC9" s="34"/>
+      <c r="BD9" s="34"/>
+      <c r="BE9" s="34"/>
+      <c r="BF9" s="34"/>
+      <c r="BG9" s="34"/>
+      <c r="BH9" s="34"/>
+      <c r="BI9" s="34"/>
+      <c r="BJ9" s="34"/>
+      <c r="BK9" s="34"/>
+      <c r="BL9" s="34"/>
+      <c r="BM9" s="34"/>
+      <c r="BN9" s="34"/>
+      <c r="BO9" s="34"/>
+      <c r="BP9" s="34"/>
+      <c r="BQ9" s="34"/>
+      <c r="BR9" s="34"/>
+      <c r="BS9" s="34"/>
+      <c r="BT9" s="34"/>
+      <c r="BU9" s="34"/>
+      <c r="BV9" s="34"/>
+      <c r="BW9" s="34"/>
+      <c r="BX9" s="34"/>
+      <c r="BY9" s="34"/>
+      <c r="BZ9" s="34"/>
+      <c r="CA9" s="34"/>
+      <c r="CB9" s="34"/>
+      <c r="CC9" s="34"/>
+      <c r="CD9" s="34"/>
+      <c r="CE9" s="34"/>
+      <c r="CF9" s="34"/>
+      <c r="CG9" s="34"/>
+      <c r="CH9" s="34"/>
+      <c r="CI9" s="34"/>
+      <c r="CJ9" s="34"/>
+      <c r="CK9" s="34"/>
+      <c r="CL9" s="34"/>
+      <c r="CM9" s="34"/>
+      <c r="CN9" s="34"/>
+      <c r="CO9" s="34"/>
+      <c r="CP9" s="34"/>
+      <c r="CQ9" s="34"/>
+      <c r="CR9" s="34"/>
+      <c r="CS9" s="34"/>
+      <c r="CT9" s="34"/>
+      <c r="CU9" s="34"/>
+      <c r="CV9" s="34"/>
+      <c r="CW9" s="34"/>
+      <c r="CX9" s="34"/>
+      <c r="CY9" s="34"/>
+      <c r="CZ9" s="34"/>
+      <c r="DA9" s="34"/>
+      <c r="DB9" s="34"/>
+      <c r="DC9" s="34"/>
+      <c r="DD9" s="34"/>
+      <c r="DE9" s="34"/>
+      <c r="DF9" s="34"/>
+      <c r="DG9" s="34"/>
+      <c r="DH9" s="34"/>
+      <c r="DI9" s="34"/>
+      <c r="DJ9" s="34"/>
+      <c r="DK9" s="34"/>
+      <c r="DL9" s="34"/>
+      <c r="DM9" s="34"/>
+      <c r="DN9" s="34"/>
+      <c r="DO9" s="34"/>
+      <c r="DP9" s="34"/>
+      <c r="DQ9" s="34"/>
+      <c r="DR9" s="34"/>
+      <c r="DS9" s="34"/>
+      <c r="DT9" s="34"/>
     </row>
     <row r="10" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="36"/>
-      <c r="B10" s="37"/>
+      <c r="A10" s="44"/>
+      <c r="B10" s="54"/>
       <c r="C10" s="6"/>
       <c r="D10" s="4" t="s">
         <v>10</v>
@@ -4782,250 +4782,250 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E26" s="32"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33"/>
-      <c r="K26" s="33"/>
-      <c r="L26" s="33"/>
-      <c r="M26" s="33"/>
-      <c r="N26" s="33"/>
-      <c r="O26" s="33"/>
-      <c r="P26" s="33"/>
-      <c r="Q26" s="33"/>
-      <c r="R26" s="33"/>
-      <c r="S26" s="33"/>
-      <c r="T26" s="33"/>
-      <c r="U26" s="33"/>
-      <c r="V26" s="33"/>
-      <c r="W26" s="33"/>
-      <c r="X26" s="33"/>
-      <c r="Y26" s="33"/>
-      <c r="Z26" s="33"/>
-      <c r="AA26" s="33"/>
-      <c r="AB26" s="33"/>
-      <c r="AC26" s="33"/>
-      <c r="AD26" s="33"/>
-      <c r="AE26" s="33"/>
-      <c r="AF26" s="33"/>
-      <c r="AG26" s="33"/>
-      <c r="AH26" s="33"/>
-      <c r="AI26" s="33"/>
-      <c r="AJ26" s="33"/>
-      <c r="AK26" s="33"/>
-      <c r="AL26" s="33"/>
-      <c r="AM26" s="33"/>
-      <c r="AN26" s="33"/>
-      <c r="AO26" s="33"/>
-      <c r="AP26" s="33"/>
-      <c r="AQ26" s="33"/>
-      <c r="AR26" s="33"/>
-      <c r="AS26" s="33"/>
-      <c r="AT26" s="33"/>
-      <c r="AU26" s="33"/>
-      <c r="AV26" s="33"/>
-      <c r="AW26" s="33"/>
-      <c r="AX26" s="33"/>
-      <c r="AY26" s="33"/>
-      <c r="AZ26" s="33"/>
-      <c r="BA26" s="33"/>
-      <c r="BB26" s="33"/>
-      <c r="BC26" s="33"/>
-      <c r="BD26" s="33"/>
-      <c r="BE26" s="33"/>
-      <c r="BF26" s="33"/>
-      <c r="BG26" s="33"/>
-      <c r="BH26" s="33"/>
-      <c r="BI26" s="33"/>
-      <c r="BJ26" s="33"/>
-      <c r="BK26" s="33"/>
-      <c r="BL26" s="33"/>
-      <c r="BM26" s="33"/>
-      <c r="BN26" s="33"/>
-      <c r="BO26" s="33"/>
-      <c r="BP26" s="33"/>
-      <c r="BQ26" s="33"/>
-      <c r="BR26" s="33"/>
-      <c r="BS26" s="33"/>
-      <c r="BT26" s="33"/>
-      <c r="BU26" s="33"/>
-      <c r="BV26" s="33"/>
-      <c r="BW26" s="33"/>
-      <c r="BX26" s="33"/>
-      <c r="BY26" s="33"/>
-      <c r="BZ26" s="33"/>
-      <c r="CA26" s="33"/>
-      <c r="CB26" s="33"/>
-      <c r="CC26" s="33"/>
-      <c r="CD26" s="33"/>
-      <c r="CE26" s="33"/>
-      <c r="CF26" s="33"/>
-      <c r="CG26" s="33"/>
-      <c r="CH26" s="33"/>
-      <c r="CI26" s="33"/>
-      <c r="CJ26" s="33"/>
-      <c r="CK26" s="33"/>
-      <c r="CL26" s="33"/>
-      <c r="CM26" s="33"/>
-      <c r="CN26" s="33"/>
-      <c r="CO26" s="33"/>
-      <c r="CP26" s="33"/>
-      <c r="CQ26" s="33"/>
-      <c r="CR26" s="33"/>
-      <c r="CS26" s="33"/>
-      <c r="CT26" s="33"/>
-      <c r="CU26" s="33"/>
-      <c r="CV26" s="33"/>
-      <c r="CW26" s="33"/>
-      <c r="CX26" s="33"/>
-      <c r="CY26" s="33"/>
-      <c r="CZ26" s="33"/>
-      <c r="DA26" s="33"/>
-      <c r="DB26" s="33"/>
-      <c r="DC26" s="33"/>
-      <c r="DD26" s="33"/>
-      <c r="DE26" s="33"/>
-      <c r="DF26" s="33"/>
-      <c r="DG26" s="33"/>
-      <c r="DH26" s="33"/>
-      <c r="DI26" s="33"/>
-      <c r="DJ26" s="33"/>
-      <c r="DK26" s="33"/>
-      <c r="DL26" s="33"/>
-      <c r="DM26" s="33"/>
-      <c r="DN26" s="33"/>
-      <c r="DO26" s="33"/>
-      <c r="DP26" s="33"/>
-      <c r="DQ26" s="33"/>
-      <c r="DR26" s="33"/>
-      <c r="DS26" s="33"/>
-      <c r="DT26" s="33"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="46"/>
+      <c r="I26" s="46"/>
+      <c r="J26" s="46"/>
+      <c r="K26" s="46"/>
+      <c r="L26" s="46"/>
+      <c r="M26" s="46"/>
+      <c r="N26" s="46"/>
+      <c r="O26" s="46"/>
+      <c r="P26" s="46"/>
+      <c r="Q26" s="46"/>
+      <c r="R26" s="46"/>
+      <c r="S26" s="46"/>
+      <c r="T26" s="46"/>
+      <c r="U26" s="46"/>
+      <c r="V26" s="46"/>
+      <c r="W26" s="46"/>
+      <c r="X26" s="46"/>
+      <c r="Y26" s="46"/>
+      <c r="Z26" s="46"/>
+      <c r="AA26" s="46"/>
+      <c r="AB26" s="46"/>
+      <c r="AC26" s="46"/>
+      <c r="AD26" s="46"/>
+      <c r="AE26" s="46"/>
+      <c r="AF26" s="46"/>
+      <c r="AG26" s="46"/>
+      <c r="AH26" s="46"/>
+      <c r="AI26" s="46"/>
+      <c r="AJ26" s="46"/>
+      <c r="AK26" s="46"/>
+      <c r="AL26" s="46"/>
+      <c r="AM26" s="46"/>
+      <c r="AN26" s="46"/>
+      <c r="AO26" s="46"/>
+      <c r="AP26" s="46"/>
+      <c r="AQ26" s="46"/>
+      <c r="AR26" s="46"/>
+      <c r="AS26" s="46"/>
+      <c r="AT26" s="46"/>
+      <c r="AU26" s="46"/>
+      <c r="AV26" s="46"/>
+      <c r="AW26" s="46"/>
+      <c r="AX26" s="46"/>
+      <c r="AY26" s="46"/>
+      <c r="AZ26" s="46"/>
+      <c r="BA26" s="46"/>
+      <c r="BB26" s="46"/>
+      <c r="BC26" s="46"/>
+      <c r="BD26" s="46"/>
+      <c r="BE26" s="46"/>
+      <c r="BF26" s="46"/>
+      <c r="BG26" s="46"/>
+      <c r="BH26" s="46"/>
+      <c r="BI26" s="46"/>
+      <c r="BJ26" s="46"/>
+      <c r="BK26" s="46"/>
+      <c r="BL26" s="46"/>
+      <c r="BM26" s="46"/>
+      <c r="BN26" s="46"/>
+      <c r="BO26" s="46"/>
+      <c r="BP26" s="46"/>
+      <c r="BQ26" s="46"/>
+      <c r="BR26" s="46"/>
+      <c r="BS26" s="46"/>
+      <c r="BT26" s="46"/>
+      <c r="BU26" s="46"/>
+      <c r="BV26" s="46"/>
+      <c r="BW26" s="46"/>
+      <c r="BX26" s="46"/>
+      <c r="BY26" s="46"/>
+      <c r="BZ26" s="46"/>
+      <c r="CA26" s="46"/>
+      <c r="CB26" s="46"/>
+      <c r="CC26" s="46"/>
+      <c r="CD26" s="46"/>
+      <c r="CE26" s="46"/>
+      <c r="CF26" s="46"/>
+      <c r="CG26" s="46"/>
+      <c r="CH26" s="46"/>
+      <c r="CI26" s="46"/>
+      <c r="CJ26" s="46"/>
+      <c r="CK26" s="46"/>
+      <c r="CL26" s="46"/>
+      <c r="CM26" s="46"/>
+      <c r="CN26" s="46"/>
+      <c r="CO26" s="46"/>
+      <c r="CP26" s="46"/>
+      <c r="CQ26" s="46"/>
+      <c r="CR26" s="46"/>
+      <c r="CS26" s="46"/>
+      <c r="CT26" s="46"/>
+      <c r="CU26" s="46"/>
+      <c r="CV26" s="46"/>
+      <c r="CW26" s="46"/>
+      <c r="CX26" s="46"/>
+      <c r="CY26" s="46"/>
+      <c r="CZ26" s="46"/>
+      <c r="DA26" s="46"/>
+      <c r="DB26" s="46"/>
+      <c r="DC26" s="46"/>
+      <c r="DD26" s="46"/>
+      <c r="DE26" s="46"/>
+      <c r="DF26" s="46"/>
+      <c r="DG26" s="46"/>
+      <c r="DH26" s="46"/>
+      <c r="DI26" s="46"/>
+      <c r="DJ26" s="46"/>
+      <c r="DK26" s="46"/>
+      <c r="DL26" s="46"/>
+      <c r="DM26" s="46"/>
+      <c r="DN26" s="46"/>
+      <c r="DO26" s="46"/>
+      <c r="DP26" s="46"/>
+      <c r="DQ26" s="46"/>
+      <c r="DR26" s="46"/>
+      <c r="DS26" s="46"/>
+      <c r="DT26" s="46"/>
     </row>
     <row r="27" spans="1:124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E27" s="1">
         <v>4</v>
       </c>
-      <c r="F27" s="53"/>
-      <c r="G27" s="53"/>
-      <c r="H27" s="53"/>
-      <c r="I27" s="53"/>
-      <c r="J27" s="53"/>
-      <c r="K27" s="53"/>
-      <c r="L27" s="53"/>
-      <c r="M27" s="53"/>
-      <c r="N27" s="53"/>
-      <c r="O27" s="53"/>
-      <c r="P27" s="53"/>
-      <c r="Q27" s="53"/>
-      <c r="R27" s="53"/>
-      <c r="S27" s="53"/>
-      <c r="T27" s="53"/>
-      <c r="U27" s="53"/>
-      <c r="V27" s="53"/>
-      <c r="W27" s="53"/>
-      <c r="X27" s="53"/>
-      <c r="Y27" s="53"/>
-      <c r="Z27" s="53"/>
-      <c r="AA27" s="53"/>
-      <c r="AB27" s="53"/>
-      <c r="AC27" s="53"/>
-      <c r="AD27" s="53"/>
-      <c r="AE27" s="53"/>
-      <c r="AF27" s="53"/>
-      <c r="AG27" s="53"/>
-      <c r="AH27" s="53"/>
-      <c r="AI27" s="53"/>
-      <c r="AJ27" s="53"/>
-      <c r="AK27" s="53"/>
-      <c r="AL27" s="53"/>
-      <c r="AM27" s="53"/>
-      <c r="AN27" s="53"/>
-      <c r="AO27" s="53"/>
-      <c r="AP27" s="53"/>
-      <c r="AQ27" s="53"/>
-      <c r="AR27" s="53"/>
-      <c r="AS27" s="53"/>
-      <c r="AT27" s="53"/>
-      <c r="AU27" s="53"/>
-      <c r="AV27" s="53"/>
-      <c r="AW27" s="53"/>
-      <c r="AX27" s="53"/>
-      <c r="AY27" s="53"/>
-      <c r="AZ27" s="53"/>
-      <c r="BA27" s="53"/>
-      <c r="BB27" s="53"/>
-      <c r="BC27" s="53"/>
-      <c r="BD27" s="53"/>
-      <c r="BE27" s="53"/>
-      <c r="BF27" s="53"/>
-      <c r="BG27" s="53"/>
-      <c r="BH27" s="53"/>
-      <c r="BI27" s="53"/>
-      <c r="BJ27" s="53"/>
-      <c r="BK27" s="53"/>
-      <c r="BL27" s="53"/>
-      <c r="BM27" s="53"/>
-      <c r="BN27" s="53"/>
-      <c r="BO27" s="53"/>
-      <c r="BP27" s="53"/>
-      <c r="BQ27" s="53"/>
-      <c r="BR27" s="53"/>
-      <c r="BS27" s="53"/>
-      <c r="BT27" s="53"/>
-      <c r="BU27" s="53"/>
-      <c r="BV27" s="53"/>
-      <c r="BW27" s="53"/>
-      <c r="BX27" s="53"/>
-      <c r="BY27" s="53"/>
-      <c r="BZ27" s="53"/>
-      <c r="CA27" s="53"/>
-      <c r="CB27" s="53"/>
-      <c r="CC27" s="53"/>
-      <c r="CD27" s="53"/>
-      <c r="CE27" s="54"/>
-      <c r="CF27" s="55"/>
-      <c r="CG27" s="55"/>
-      <c r="CH27" s="55"/>
-      <c r="CI27" s="55"/>
-      <c r="CJ27" s="55"/>
-      <c r="CK27" s="55"/>
-      <c r="CL27" s="55"/>
-      <c r="CM27" s="55"/>
-      <c r="CN27" s="55"/>
-      <c r="CO27" s="55"/>
-      <c r="CP27" s="55"/>
-      <c r="CQ27" s="55"/>
-      <c r="CR27" s="55"/>
-      <c r="CS27" s="55"/>
-      <c r="CT27" s="55"/>
-      <c r="CU27" s="55"/>
-      <c r="CV27" s="55"/>
-      <c r="CW27" s="55"/>
-      <c r="CX27" s="55"/>
-      <c r="CY27" s="55"/>
-      <c r="CZ27" s="55"/>
-      <c r="DA27" s="55"/>
-      <c r="DB27" s="55"/>
-      <c r="DC27" s="55"/>
-      <c r="DD27" s="55"/>
-      <c r="DE27" s="55"/>
-      <c r="DF27" s="55"/>
-      <c r="DG27" s="55"/>
-      <c r="DH27" s="55"/>
-      <c r="DI27" s="55"/>
-      <c r="DJ27" s="55"/>
-      <c r="DK27" s="55"/>
-      <c r="DL27" s="55"/>
-      <c r="DM27" s="55"/>
-      <c r="DN27" s="55"/>
-      <c r="DO27" s="55"/>
-      <c r="DP27" s="55"/>
-      <c r="DQ27" s="55"/>
-      <c r="DR27" s="55"/>
-      <c r="DS27" s="55"/>
-      <c r="DT27" s="55"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="30"/>
+      <c r="I27" s="30"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="30"/>
+      <c r="L27" s="30"/>
+      <c r="M27" s="30"/>
+      <c r="N27" s="30"/>
+      <c r="O27" s="30"/>
+      <c r="P27" s="30"/>
+      <c r="Q27" s="30"/>
+      <c r="R27" s="30"/>
+      <c r="S27" s="30"/>
+      <c r="T27" s="30"/>
+      <c r="U27" s="30"/>
+      <c r="V27" s="30"/>
+      <c r="W27" s="30"/>
+      <c r="X27" s="30"/>
+      <c r="Y27" s="30"/>
+      <c r="Z27" s="30"/>
+      <c r="AA27" s="30"/>
+      <c r="AB27" s="30"/>
+      <c r="AC27" s="30"/>
+      <c r="AD27" s="30"/>
+      <c r="AE27" s="30"/>
+      <c r="AF27" s="30"/>
+      <c r="AG27" s="30"/>
+      <c r="AH27" s="30"/>
+      <c r="AI27" s="30"/>
+      <c r="AJ27" s="30"/>
+      <c r="AK27" s="30"/>
+      <c r="AL27" s="30"/>
+      <c r="AM27" s="30"/>
+      <c r="AN27" s="30"/>
+      <c r="AO27" s="30"/>
+      <c r="AP27" s="30"/>
+      <c r="AQ27" s="30"/>
+      <c r="AR27" s="30"/>
+      <c r="AS27" s="30"/>
+      <c r="AT27" s="30"/>
+      <c r="AU27" s="30"/>
+      <c r="AV27" s="30"/>
+      <c r="AW27" s="30"/>
+      <c r="AX27" s="30"/>
+      <c r="AY27" s="30"/>
+      <c r="AZ27" s="30"/>
+      <c r="BA27" s="30"/>
+      <c r="BB27" s="30"/>
+      <c r="BC27" s="30"/>
+      <c r="BD27" s="30"/>
+      <c r="BE27" s="30"/>
+      <c r="BF27" s="30"/>
+      <c r="BG27" s="30"/>
+      <c r="BH27" s="30"/>
+      <c r="BI27" s="30"/>
+      <c r="BJ27" s="30"/>
+      <c r="BK27" s="30"/>
+      <c r="BL27" s="30"/>
+      <c r="BM27" s="30"/>
+      <c r="BN27" s="30"/>
+      <c r="BO27" s="30"/>
+      <c r="BP27" s="30"/>
+      <c r="BQ27" s="30"/>
+      <c r="BR27" s="30"/>
+      <c r="BS27" s="30"/>
+      <c r="BT27" s="30"/>
+      <c r="BU27" s="30"/>
+      <c r="BV27" s="30"/>
+      <c r="BW27" s="30"/>
+      <c r="BX27" s="30"/>
+      <c r="BY27" s="30"/>
+      <c r="BZ27" s="30"/>
+      <c r="CA27" s="30"/>
+      <c r="CB27" s="30"/>
+      <c r="CC27" s="30"/>
+      <c r="CD27" s="30"/>
+      <c r="CE27" s="31"/>
+      <c r="CF27" s="32"/>
+      <c r="CG27" s="32"/>
+      <c r="CH27" s="32"/>
+      <c r="CI27" s="32"/>
+      <c r="CJ27" s="32"/>
+      <c r="CK27" s="32"/>
+      <c r="CL27" s="32"/>
+      <c r="CM27" s="32"/>
+      <c r="CN27" s="32"/>
+      <c r="CO27" s="32"/>
+      <c r="CP27" s="32"/>
+      <c r="CQ27" s="32"/>
+      <c r="CR27" s="32"/>
+      <c r="CS27" s="32"/>
+      <c r="CT27" s="32"/>
+      <c r="CU27" s="32"/>
+      <c r="CV27" s="32"/>
+      <c r="CW27" s="32"/>
+      <c r="CX27" s="32"/>
+      <c r="CY27" s="32"/>
+      <c r="CZ27" s="32"/>
+      <c r="DA27" s="32"/>
+      <c r="DB27" s="32"/>
+      <c r="DC27" s="32"/>
+      <c r="DD27" s="32"/>
+      <c r="DE27" s="32"/>
+      <c r="DF27" s="32"/>
+      <c r="DG27" s="32"/>
+      <c r="DH27" s="32"/>
+      <c r="DI27" s="32"/>
+      <c r="DJ27" s="32"/>
+      <c r="DK27" s="32"/>
+      <c r="DL27" s="32"/>
+      <c r="DM27" s="32"/>
+      <c r="DN27" s="32"/>
+      <c r="DO27" s="32"/>
+      <c r="DP27" s="32"/>
+      <c r="DQ27" s="32"/>
+      <c r="DR27" s="32"/>
+      <c r="DS27" s="32"/>
+      <c r="DT27" s="32"/>
     </row>
     <row r="29" spans="1:124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E29" s="22">
@@ -5051,27 +5051,221 @@
     </row>
   </sheetData>
   <mergeCells count="263">
-    <mergeCell ref="R1:U1"/>
-    <mergeCell ref="DQ2:DQ7"/>
-    <mergeCell ref="DR2:DR7"/>
-    <mergeCell ref="DS2:DS7"/>
-    <mergeCell ref="DT2:DT7"/>
-    <mergeCell ref="CX2:CX7"/>
-    <mergeCell ref="CY2:CY7"/>
-    <mergeCell ref="DA2:DA7"/>
-    <mergeCell ref="DB2:DB7"/>
-    <mergeCell ref="DC2:DC7"/>
-    <mergeCell ref="DD2:DD7"/>
-    <mergeCell ref="DE2:DE7"/>
-    <mergeCell ref="CZ2:CZ7"/>
-    <mergeCell ref="DN2:DN7"/>
-    <mergeCell ref="DO2:DO7"/>
-    <mergeCell ref="DP2:DP7"/>
-    <mergeCell ref="DG2:DG7"/>
-    <mergeCell ref="DH2:DH7"/>
-    <mergeCell ref="DI2:DI7"/>
-    <mergeCell ref="DJ2:DJ7"/>
-    <mergeCell ref="DK2:DK7"/>
+    <mergeCell ref="N1:Q1"/>
+    <mergeCell ref="BC8:BC9"/>
+    <mergeCell ref="BD8:BD9"/>
+    <mergeCell ref="BE8:BE9"/>
+    <mergeCell ref="AN8:AN9"/>
+    <mergeCell ref="AO8:AO9"/>
+    <mergeCell ref="AP8:AP9"/>
+    <mergeCell ref="AQ8:AQ9"/>
+    <mergeCell ref="AR8:AR9"/>
+    <mergeCell ref="AS8:AS9"/>
+    <mergeCell ref="AT8:AT9"/>
+    <mergeCell ref="AU8:AU9"/>
+    <mergeCell ref="AV8:AV9"/>
+    <mergeCell ref="AE8:AE9"/>
+    <mergeCell ref="AF8:AF9"/>
+    <mergeCell ref="AG8:AG9"/>
+    <mergeCell ref="AH8:AH9"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AJ8:AJ9"/>
+    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="AL8:AL9"/>
+    <mergeCell ref="AM8:AM9"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="BO8:BO9"/>
+    <mergeCell ref="BP8:BP9"/>
+    <mergeCell ref="BQ8:BQ9"/>
+    <mergeCell ref="BR8:BR9"/>
+    <mergeCell ref="BS8:BS9"/>
+    <mergeCell ref="BT8:BT9"/>
+    <mergeCell ref="BZ8:BZ9"/>
+    <mergeCell ref="CA8:CA9"/>
+    <mergeCell ref="BH8:BH9"/>
+    <mergeCell ref="BI8:BI9"/>
+    <mergeCell ref="BJ8:BJ9"/>
+    <mergeCell ref="BK8:BK9"/>
+    <mergeCell ref="BL8:BL9"/>
+    <mergeCell ref="BM8:BM9"/>
+    <mergeCell ref="CB8:CB9"/>
+    <mergeCell ref="CC8:CC9"/>
+    <mergeCell ref="CD8:CD9"/>
+    <mergeCell ref="CE8:CE9"/>
+    <mergeCell ref="CF8:CF9"/>
+    <mergeCell ref="CV8:CV9"/>
+    <mergeCell ref="BQ2:BQ7"/>
+    <mergeCell ref="BR2:BR7"/>
+    <mergeCell ref="BS2:BS7"/>
+    <mergeCell ref="BT2:BT7"/>
+    <mergeCell ref="BU2:BU7"/>
+    <mergeCell ref="BV2:BV7"/>
+    <mergeCell ref="CO8:CO9"/>
+    <mergeCell ref="CP8:CP9"/>
+    <mergeCell ref="CH2:CH7"/>
+    <mergeCell ref="CT8:CT9"/>
+    <mergeCell ref="CU8:CU9"/>
+    <mergeCell ref="CB2:CB7"/>
+    <mergeCell ref="CC2:CC7"/>
+    <mergeCell ref="CD2:CD7"/>
+    <mergeCell ref="CE2:CE7"/>
+    <mergeCell ref="CF2:CF7"/>
+    <mergeCell ref="CG2:CG7"/>
+    <mergeCell ref="CJ8:CJ9"/>
+    <mergeCell ref="E26:DT26"/>
+    <mergeCell ref="DF8:DF9"/>
+    <mergeCell ref="DQ8:DQ9"/>
+    <mergeCell ref="DR8:DR9"/>
+    <mergeCell ref="DS8:DS9"/>
+    <mergeCell ref="DT8:DT9"/>
+    <mergeCell ref="CY8:CY9"/>
+    <mergeCell ref="CZ8:CZ9"/>
+    <mergeCell ref="CM8:CM9"/>
+    <mergeCell ref="CW8:CW9"/>
+    <mergeCell ref="CX8:CX9"/>
+    <mergeCell ref="BU8:BU9"/>
+    <mergeCell ref="BV8:BV9"/>
+    <mergeCell ref="BW8:BW9"/>
+    <mergeCell ref="BF8:BF9"/>
+    <mergeCell ref="BG8:BG9"/>
+    <mergeCell ref="CG8:CG9"/>
+    <mergeCell ref="CH8:CH9"/>
+    <mergeCell ref="AW8:AW9"/>
+    <mergeCell ref="AX8:AX9"/>
+    <mergeCell ref="AY8:AY9"/>
+    <mergeCell ref="AZ8:AZ9"/>
+    <mergeCell ref="BA8:BA9"/>
+    <mergeCell ref="BB8:BB9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="F2:F7"/>
+    <mergeCell ref="G2:G7"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="I2:I7"/>
+    <mergeCell ref="J2:J7"/>
+    <mergeCell ref="K2:K7"/>
+    <mergeCell ref="L2:L7"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="M2:M7"/>
+    <mergeCell ref="N2:N7"/>
+    <mergeCell ref="O2:O7"/>
+    <mergeCell ref="P2:P7"/>
+    <mergeCell ref="Q2:Q7"/>
+    <mergeCell ref="R2:R7"/>
+    <mergeCell ref="S2:S7"/>
+    <mergeCell ref="T2:T7"/>
+    <mergeCell ref="CN8:CN9"/>
+    <mergeCell ref="Y2:Y7"/>
+    <mergeCell ref="Z2:Z7"/>
+    <mergeCell ref="AA2:AA7"/>
+    <mergeCell ref="AB2:AB7"/>
+    <mergeCell ref="AC2:AC7"/>
+    <mergeCell ref="AD2:AD7"/>
+    <mergeCell ref="AE2:AE7"/>
+    <mergeCell ref="AH2:AH7"/>
+    <mergeCell ref="AI2:AI7"/>
+    <mergeCell ref="AJ2:AJ7"/>
+    <mergeCell ref="AK2:AK7"/>
+    <mergeCell ref="AL2:AL7"/>
+    <mergeCell ref="AM2:AM7"/>
+    <mergeCell ref="AN2:AN7"/>
+    <mergeCell ref="AO2:AO7"/>
+    <mergeCell ref="AG2:AG7"/>
+    <mergeCell ref="CW2:CW7"/>
+    <mergeCell ref="CU2:CU7"/>
+    <mergeCell ref="CV2:CV7"/>
+    <mergeCell ref="CQ2:CQ7"/>
+    <mergeCell ref="CR2:CR7"/>
+    <mergeCell ref="CS2:CS7"/>
+    <mergeCell ref="CT2:CT7"/>
+    <mergeCell ref="CI2:CI7"/>
+    <mergeCell ref="CJ2:CJ7"/>
+    <mergeCell ref="CK2:CK7"/>
+    <mergeCell ref="CL2:CL7"/>
+    <mergeCell ref="CM2:CM7"/>
+    <mergeCell ref="CN2:CN7"/>
+    <mergeCell ref="CO2:CO7"/>
+    <mergeCell ref="CP2:CP7"/>
+    <mergeCell ref="X2:X7"/>
+    <mergeCell ref="AF2:AF7"/>
+    <mergeCell ref="AX2:AX7"/>
+    <mergeCell ref="AY2:AY7"/>
+    <mergeCell ref="AZ2:AZ7"/>
+    <mergeCell ref="BL2:BL7"/>
+    <mergeCell ref="BA2:BA7"/>
+    <mergeCell ref="BB2:BB7"/>
+    <mergeCell ref="BC2:BC7"/>
+    <mergeCell ref="AP2:AP7"/>
+    <mergeCell ref="AQ2:AQ7"/>
+    <mergeCell ref="AR2:AR7"/>
+    <mergeCell ref="AS2:AS7"/>
+    <mergeCell ref="AT2:AT7"/>
+    <mergeCell ref="AU2:AU7"/>
+    <mergeCell ref="AV2:AV7"/>
+    <mergeCell ref="AW2:AW7"/>
+    <mergeCell ref="CK8:CK9"/>
+    <mergeCell ref="CL8:CL9"/>
+    <mergeCell ref="BX8:BX9"/>
+    <mergeCell ref="BY8:BY9"/>
+    <mergeCell ref="DL2:DL7"/>
+    <mergeCell ref="DM2:DM7"/>
+    <mergeCell ref="DF2:DF7"/>
+    <mergeCell ref="BD2:BD7"/>
+    <mergeCell ref="BE2:BE7"/>
+    <mergeCell ref="BF2:BF7"/>
+    <mergeCell ref="BG2:BG7"/>
+    <mergeCell ref="BM2:BM7"/>
+    <mergeCell ref="BN2:BN7"/>
+    <mergeCell ref="BO2:BO7"/>
+    <mergeCell ref="BP2:BP7"/>
+    <mergeCell ref="CA2:CA7"/>
+    <mergeCell ref="BW2:BW7"/>
+    <mergeCell ref="BX2:BX7"/>
+    <mergeCell ref="BY2:BY7"/>
+    <mergeCell ref="BZ2:BZ7"/>
+    <mergeCell ref="BH2:BH7"/>
+    <mergeCell ref="BI2:BI7"/>
+    <mergeCell ref="BJ2:BJ7"/>
+    <mergeCell ref="BK2:BK7"/>
     <mergeCell ref="F27:S27"/>
     <mergeCell ref="T27:AW27"/>
     <mergeCell ref="AX27:CD27"/>
@@ -5096,224 +5290,30 @@
     <mergeCell ref="CS8:CS9"/>
     <mergeCell ref="BN8:BN9"/>
     <mergeCell ref="CI8:CI9"/>
-    <mergeCell ref="CK8:CK9"/>
-    <mergeCell ref="CL8:CL9"/>
-    <mergeCell ref="BX8:BX9"/>
-    <mergeCell ref="BY8:BY9"/>
-    <mergeCell ref="DL2:DL7"/>
-    <mergeCell ref="DM2:DM7"/>
-    <mergeCell ref="DF2:DF7"/>
-    <mergeCell ref="BD2:BD7"/>
-    <mergeCell ref="BE2:BE7"/>
-    <mergeCell ref="BF2:BF7"/>
-    <mergeCell ref="BG2:BG7"/>
-    <mergeCell ref="BM2:BM7"/>
-    <mergeCell ref="BN2:BN7"/>
-    <mergeCell ref="BO2:BO7"/>
-    <mergeCell ref="BP2:BP7"/>
-    <mergeCell ref="CA2:CA7"/>
-    <mergeCell ref="BW2:BW7"/>
-    <mergeCell ref="BX2:BX7"/>
-    <mergeCell ref="BY2:BY7"/>
-    <mergeCell ref="BZ2:BZ7"/>
-    <mergeCell ref="BH2:BH7"/>
-    <mergeCell ref="BI2:BI7"/>
-    <mergeCell ref="BJ2:BJ7"/>
-    <mergeCell ref="BK2:BK7"/>
+    <mergeCell ref="R1:U1"/>
+    <mergeCell ref="DQ2:DQ7"/>
+    <mergeCell ref="DR2:DR7"/>
+    <mergeCell ref="DS2:DS7"/>
+    <mergeCell ref="DT2:DT7"/>
+    <mergeCell ref="CX2:CX7"/>
+    <mergeCell ref="CY2:CY7"/>
+    <mergeCell ref="DA2:DA7"/>
+    <mergeCell ref="DB2:DB7"/>
+    <mergeCell ref="DC2:DC7"/>
+    <mergeCell ref="DD2:DD7"/>
+    <mergeCell ref="DE2:DE7"/>
+    <mergeCell ref="CZ2:CZ7"/>
+    <mergeCell ref="DN2:DN7"/>
+    <mergeCell ref="DO2:DO7"/>
+    <mergeCell ref="DP2:DP7"/>
+    <mergeCell ref="DG2:DG7"/>
+    <mergeCell ref="DH2:DH7"/>
+    <mergeCell ref="DI2:DI7"/>
+    <mergeCell ref="DJ2:DJ7"/>
+    <mergeCell ref="DK2:DK7"/>
     <mergeCell ref="U2:U7"/>
     <mergeCell ref="V2:V7"/>
     <mergeCell ref="W2:W7"/>
-    <mergeCell ref="X2:X7"/>
-    <mergeCell ref="AF2:AF7"/>
-    <mergeCell ref="AX2:AX7"/>
-    <mergeCell ref="AY2:AY7"/>
-    <mergeCell ref="AZ2:AZ7"/>
-    <mergeCell ref="BL2:BL7"/>
-    <mergeCell ref="BA2:BA7"/>
-    <mergeCell ref="BB2:BB7"/>
-    <mergeCell ref="BC2:BC7"/>
-    <mergeCell ref="AP2:AP7"/>
-    <mergeCell ref="AQ2:AQ7"/>
-    <mergeCell ref="AR2:AR7"/>
-    <mergeCell ref="AS2:AS7"/>
-    <mergeCell ref="AT2:AT7"/>
-    <mergeCell ref="AU2:AU7"/>
-    <mergeCell ref="AV2:AV7"/>
-    <mergeCell ref="AW2:AW7"/>
-    <mergeCell ref="CW2:CW7"/>
-    <mergeCell ref="CU2:CU7"/>
-    <mergeCell ref="CV2:CV7"/>
-    <mergeCell ref="CQ2:CQ7"/>
-    <mergeCell ref="CR2:CR7"/>
-    <mergeCell ref="CS2:CS7"/>
-    <mergeCell ref="CT2:CT7"/>
-    <mergeCell ref="CI2:CI7"/>
-    <mergeCell ref="CJ2:CJ7"/>
-    <mergeCell ref="CK2:CK7"/>
-    <mergeCell ref="CL2:CL7"/>
-    <mergeCell ref="CM2:CM7"/>
-    <mergeCell ref="CN2:CN7"/>
-    <mergeCell ref="CO2:CO7"/>
-    <mergeCell ref="CP2:CP7"/>
-    <mergeCell ref="N2:N7"/>
-    <mergeCell ref="O2:O7"/>
-    <mergeCell ref="P2:P7"/>
-    <mergeCell ref="Q2:Q7"/>
-    <mergeCell ref="R2:R7"/>
-    <mergeCell ref="S2:S7"/>
-    <mergeCell ref="T2:T7"/>
-    <mergeCell ref="CN8:CN9"/>
-    <mergeCell ref="Y2:Y7"/>
-    <mergeCell ref="Z2:Z7"/>
-    <mergeCell ref="AA2:AA7"/>
-    <mergeCell ref="AB2:AB7"/>
-    <mergeCell ref="AC2:AC7"/>
-    <mergeCell ref="AD2:AD7"/>
-    <mergeCell ref="AE2:AE7"/>
-    <mergeCell ref="AH2:AH7"/>
-    <mergeCell ref="AI2:AI7"/>
-    <mergeCell ref="AJ2:AJ7"/>
-    <mergeCell ref="AK2:AK7"/>
-    <mergeCell ref="AL2:AL7"/>
-    <mergeCell ref="AM2:AM7"/>
-    <mergeCell ref="AN2:AN7"/>
-    <mergeCell ref="AO2:AO7"/>
-    <mergeCell ref="AG2:AG7"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="F2:F7"/>
-    <mergeCell ref="G2:G7"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="I2:I7"/>
-    <mergeCell ref="J2:J7"/>
-    <mergeCell ref="K2:K7"/>
-    <mergeCell ref="L2:L7"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="M2:M7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="E26:DT26"/>
-    <mergeCell ref="DF8:DF9"/>
-    <mergeCell ref="DQ8:DQ9"/>
-    <mergeCell ref="DR8:DR9"/>
-    <mergeCell ref="DS8:DS9"/>
-    <mergeCell ref="DT8:DT9"/>
-    <mergeCell ref="CY8:CY9"/>
-    <mergeCell ref="CZ8:CZ9"/>
-    <mergeCell ref="CM8:CM9"/>
-    <mergeCell ref="CW8:CW9"/>
-    <mergeCell ref="CX8:CX9"/>
-    <mergeCell ref="BU8:BU9"/>
-    <mergeCell ref="BV8:BV9"/>
-    <mergeCell ref="BW8:BW9"/>
-    <mergeCell ref="BF8:BF9"/>
-    <mergeCell ref="BG8:BG9"/>
-    <mergeCell ref="CG8:CG9"/>
-    <mergeCell ref="CH8:CH9"/>
-    <mergeCell ref="AW8:AW9"/>
-    <mergeCell ref="AX8:AX9"/>
-    <mergeCell ref="AY8:AY9"/>
-    <mergeCell ref="AZ8:AZ9"/>
-    <mergeCell ref="BA8:BA9"/>
-    <mergeCell ref="BB8:BB9"/>
-    <mergeCell ref="CB8:CB9"/>
-    <mergeCell ref="CC8:CC9"/>
-    <mergeCell ref="CD8:CD9"/>
-    <mergeCell ref="CE8:CE9"/>
-    <mergeCell ref="CF8:CF9"/>
-    <mergeCell ref="CV8:CV9"/>
-    <mergeCell ref="BQ2:BQ7"/>
-    <mergeCell ref="BR2:BR7"/>
-    <mergeCell ref="BS2:BS7"/>
-    <mergeCell ref="BT2:BT7"/>
-    <mergeCell ref="BU2:BU7"/>
-    <mergeCell ref="BV2:BV7"/>
-    <mergeCell ref="CO8:CO9"/>
-    <mergeCell ref="CP8:CP9"/>
-    <mergeCell ref="CH2:CH7"/>
-    <mergeCell ref="CT8:CT9"/>
-    <mergeCell ref="CU8:CU9"/>
-    <mergeCell ref="CB2:CB7"/>
-    <mergeCell ref="CC2:CC7"/>
-    <mergeCell ref="CD2:CD7"/>
-    <mergeCell ref="CE2:CE7"/>
-    <mergeCell ref="CF2:CF7"/>
-    <mergeCell ref="CG2:CG7"/>
-    <mergeCell ref="CJ8:CJ9"/>
-    <mergeCell ref="BO8:BO9"/>
-    <mergeCell ref="BP8:BP9"/>
-    <mergeCell ref="BQ8:BQ9"/>
-    <mergeCell ref="BR8:BR9"/>
-    <mergeCell ref="BS8:BS9"/>
-    <mergeCell ref="BT8:BT9"/>
-    <mergeCell ref="BZ8:BZ9"/>
-    <mergeCell ref="CA8:CA9"/>
-    <mergeCell ref="BH8:BH9"/>
-    <mergeCell ref="BI8:BI9"/>
-    <mergeCell ref="BJ8:BJ9"/>
-    <mergeCell ref="BK8:BK9"/>
-    <mergeCell ref="BL8:BL9"/>
-    <mergeCell ref="BM8:BM9"/>
-    <mergeCell ref="N1:Q1"/>
-    <mergeCell ref="BC8:BC9"/>
-    <mergeCell ref="BD8:BD9"/>
-    <mergeCell ref="BE8:BE9"/>
-    <mergeCell ref="AN8:AN9"/>
-    <mergeCell ref="AO8:AO9"/>
-    <mergeCell ref="AP8:AP9"/>
-    <mergeCell ref="AQ8:AQ9"/>
-    <mergeCell ref="AR8:AR9"/>
-    <mergeCell ref="AS8:AS9"/>
-    <mergeCell ref="AT8:AT9"/>
-    <mergeCell ref="AU8:AU9"/>
-    <mergeCell ref="AV8:AV9"/>
-    <mergeCell ref="AE8:AE9"/>
-    <mergeCell ref="AF8:AF9"/>
-    <mergeCell ref="AG8:AG9"/>
-    <mergeCell ref="AH8:AH9"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AJ8:AJ9"/>
-    <mergeCell ref="AK8:AK9"/>
-    <mergeCell ref="AL8:AL9"/>
-    <mergeCell ref="AM8:AM9"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="W8:W9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -5346,7 +5346,7 @@
       <c r="H2" s="57"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="44" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="59" t="s">
@@ -5370,7 +5370,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="36"/>
+      <c r="A4" s="44"/>
       <c r="B4" s="61"/>
       <c r="C4" s="62"/>
       <c r="D4" s="64"/>

--- a/Journals/Angular ჟურნალი.xlsx
+++ b/Journals/Angular ჟურნალი.xlsx
@@ -488,7 +488,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -551,26 +551,38 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="2" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -600,16 +612,7 @@
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -623,17 +626,14 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -661,6 +661,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -896,14 +902,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="37"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="41"/>
       <c r="F1" s="25">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G1" s="26"/>
       <c r="H1" s="26"/>
@@ -926,10 +932,12 @@
       <c r="S1" s="26"/>
       <c r="T1" s="26"/>
       <c r="U1" s="27"/>
-      <c r="V1" s="23"/>
-      <c r="W1" s="23"/>
-      <c r="X1" s="23"/>
-      <c r="Y1" s="23"/>
+      <c r="V1" s="25">
+        <v>4</v>
+      </c>
+      <c r="W1" s="26"/>
+      <c r="X1" s="26"/>
+      <c r="Y1" s="27"/>
       <c r="Z1" s="23"/>
       <c r="AA1" s="23"/>
       <c r="AB1" s="23"/>
@@ -1031,1321 +1039,1329 @@
       <c r="DT1" s="24"/>
       <c r="DU1" s="1">
         <f>SUM(F1:DT1)</f>
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:125" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="38"/>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="41" t="s">
+      <c r="A2" s="42"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="28">
+      <c r="F2" s="30">
         <v>46276</v>
       </c>
-      <c r="G2" s="28">
+      <c r="G2" s="30">
         <v>46276</v>
       </c>
-      <c r="H2" s="28">
+      <c r="H2" s="30">
         <v>46276</v>
       </c>
-      <c r="I2" s="28">
+      <c r="I2" s="30">
         <v>46276</v>
       </c>
-      <c r="J2" s="28">
+      <c r="J2" s="30">
         <v>46283</v>
       </c>
-      <c r="K2" s="28">
+      <c r="K2" s="30">
         <v>46283</v>
       </c>
-      <c r="L2" s="28">
+      <c r="L2" s="30">
         <v>46283</v>
       </c>
-      <c r="M2" s="28">
+      <c r="M2" s="30">
         <v>46283</v>
       </c>
-      <c r="N2" s="28">
+      <c r="N2" s="30">
         <v>46290</v>
       </c>
-      <c r="O2" s="28">
+      <c r="O2" s="30">
         <v>46290</v>
       </c>
-      <c r="P2" s="28">
+      <c r="P2" s="30">
         <v>46290</v>
       </c>
-      <c r="Q2" s="28">
+      <c r="Q2" s="30">
         <v>46290</v>
       </c>
-      <c r="R2" s="28">
+      <c r="R2" s="30">
         <v>46297</v>
       </c>
-      <c r="S2" s="28">
+      <c r="S2" s="30">
         <v>46297</v>
       </c>
-      <c r="T2" s="28">
+      <c r="T2" s="30">
         <v>46297</v>
       </c>
-      <c r="U2" s="28">
+      <c r="U2" s="30">
         <v>46297</v>
       </c>
-      <c r="V2" s="28"/>
-      <c r="W2" s="28"/>
-      <c r="X2" s="28"/>
-      <c r="Y2" s="28"/>
-      <c r="Z2" s="28"/>
-      <c r="AA2" s="28"/>
-      <c r="AB2" s="28"/>
-      <c r="AC2" s="28"/>
-      <c r="AD2" s="28"/>
-      <c r="AE2" s="28"/>
-      <c r="AF2" s="28"/>
-      <c r="AG2" s="28"/>
-      <c r="AH2" s="28"/>
-      <c r="AI2" s="28"/>
-      <c r="AJ2" s="28"/>
-      <c r="AK2" s="28"/>
-      <c r="AL2" s="28"/>
-      <c r="AM2" s="28"/>
-      <c r="AN2" s="28"/>
-      <c r="AO2" s="28"/>
-      <c r="AP2" s="28"/>
-      <c r="AQ2" s="28"/>
-      <c r="AR2" s="28"/>
-      <c r="AS2" s="28"/>
-      <c r="AT2" s="28"/>
-      <c r="AU2" s="28"/>
-      <c r="AV2" s="28"/>
-      <c r="AW2" s="28"/>
-      <c r="AX2" s="28"/>
-      <c r="AY2" s="28"/>
-      <c r="AZ2" s="28"/>
-      <c r="BA2" s="28"/>
-      <c r="BB2" s="28"/>
-      <c r="BC2" s="28"/>
-      <c r="BD2" s="28"/>
-      <c r="BE2" s="28"/>
-      <c r="BF2" s="28"/>
-      <c r="BG2" s="28"/>
-      <c r="BH2" s="28"/>
-      <c r="BI2" s="28"/>
-      <c r="BJ2" s="28"/>
-      <c r="BK2" s="28"/>
-      <c r="BL2" s="28"/>
-      <c r="BM2" s="28"/>
-      <c r="BN2" s="28"/>
-      <c r="BO2" s="28"/>
-      <c r="BP2" s="28"/>
-      <c r="BQ2" s="28"/>
-      <c r="BR2" s="28"/>
-      <c r="BS2" s="28"/>
-      <c r="BT2" s="28"/>
-      <c r="BU2" s="28"/>
-      <c r="BV2" s="28"/>
-      <c r="BW2" s="28"/>
-      <c r="BX2" s="28"/>
-      <c r="BY2" s="28"/>
-      <c r="BZ2" s="28"/>
-      <c r="CA2" s="28"/>
-      <c r="CB2" s="28"/>
-      <c r="CC2" s="28"/>
-      <c r="CD2" s="28"/>
-      <c r="CE2" s="28"/>
-      <c r="CF2" s="28"/>
-      <c r="CG2" s="28"/>
-      <c r="CH2" s="28"/>
-      <c r="CI2" s="28"/>
-      <c r="CJ2" s="28"/>
-      <c r="CK2" s="28"/>
-      <c r="CL2" s="28"/>
-      <c r="CM2" s="28"/>
-      <c r="CN2" s="28"/>
-      <c r="CO2" s="28"/>
-      <c r="CP2" s="28"/>
-      <c r="CQ2" s="28"/>
-      <c r="CR2" s="28"/>
-      <c r="CS2" s="28"/>
-      <c r="CT2" s="28"/>
-      <c r="CU2" s="28"/>
-      <c r="CV2" s="28"/>
-      <c r="CW2" s="28"/>
-      <c r="CX2" s="28"/>
-      <c r="CY2" s="28"/>
-      <c r="CZ2" s="28"/>
-      <c r="DA2" s="28"/>
-      <c r="DB2" s="28"/>
-      <c r="DC2" s="28"/>
-      <c r="DD2" s="28"/>
-      <c r="DE2" s="28"/>
-      <c r="DF2" s="28"/>
-      <c r="DG2" s="28"/>
-      <c r="DH2" s="28"/>
-      <c r="DI2" s="28"/>
-      <c r="DJ2" s="28"/>
-      <c r="DK2" s="28"/>
-      <c r="DL2" s="28"/>
-      <c r="DM2" s="28"/>
-      <c r="DN2" s="28"/>
-      <c r="DO2" s="28"/>
-      <c r="DP2" s="28"/>
-      <c r="DQ2" s="28"/>
-      <c r="DR2" s="28"/>
-      <c r="DS2" s="28"/>
-      <c r="DT2" s="28"/>
+      <c r="V2" s="65">
+        <v>46304</v>
+      </c>
+      <c r="W2" s="65">
+        <v>46304</v>
+      </c>
+      <c r="X2" s="30">
+        <v>46304</v>
+      </c>
+      <c r="Y2" s="30">
+        <v>46304</v>
+      </c>
+      <c r="Z2" s="30"/>
+      <c r="AA2" s="30"/>
+      <c r="AB2" s="30"/>
+      <c r="AC2" s="30"/>
+      <c r="AD2" s="30"/>
+      <c r="AE2" s="30"/>
+      <c r="AF2" s="30"/>
+      <c r="AG2" s="30"/>
+      <c r="AH2" s="30"/>
+      <c r="AI2" s="30"/>
+      <c r="AJ2" s="30"/>
+      <c r="AK2" s="30"/>
+      <c r="AL2" s="30"/>
+      <c r="AM2" s="30"/>
+      <c r="AN2" s="30"/>
+      <c r="AO2" s="30"/>
+      <c r="AP2" s="30"/>
+      <c r="AQ2" s="30"/>
+      <c r="AR2" s="30"/>
+      <c r="AS2" s="30"/>
+      <c r="AT2" s="30"/>
+      <c r="AU2" s="30"/>
+      <c r="AV2" s="30"/>
+      <c r="AW2" s="30"/>
+      <c r="AX2" s="30"/>
+      <c r="AY2" s="30"/>
+      <c r="AZ2" s="30"/>
+      <c r="BA2" s="30"/>
+      <c r="BB2" s="30"/>
+      <c r="BC2" s="30"/>
+      <c r="BD2" s="30"/>
+      <c r="BE2" s="30"/>
+      <c r="BF2" s="30"/>
+      <c r="BG2" s="30"/>
+      <c r="BH2" s="30"/>
+      <c r="BI2" s="30"/>
+      <c r="BJ2" s="30"/>
+      <c r="BK2" s="30"/>
+      <c r="BL2" s="30"/>
+      <c r="BM2" s="30"/>
+      <c r="BN2" s="30"/>
+      <c r="BO2" s="30"/>
+      <c r="BP2" s="30"/>
+      <c r="BQ2" s="30"/>
+      <c r="BR2" s="30"/>
+      <c r="BS2" s="30"/>
+      <c r="BT2" s="30"/>
+      <c r="BU2" s="30"/>
+      <c r="BV2" s="30"/>
+      <c r="BW2" s="30"/>
+      <c r="BX2" s="30"/>
+      <c r="BY2" s="30"/>
+      <c r="BZ2" s="30"/>
+      <c r="CA2" s="30"/>
+      <c r="CB2" s="30"/>
+      <c r="CC2" s="30"/>
+      <c r="CD2" s="30"/>
+      <c r="CE2" s="30"/>
+      <c r="CF2" s="30"/>
+      <c r="CG2" s="30"/>
+      <c r="CH2" s="30"/>
+      <c r="CI2" s="30"/>
+      <c r="CJ2" s="30"/>
+      <c r="CK2" s="30"/>
+      <c r="CL2" s="30"/>
+      <c r="CM2" s="30"/>
+      <c r="CN2" s="30"/>
+      <c r="CO2" s="30"/>
+      <c r="CP2" s="30"/>
+      <c r="CQ2" s="30"/>
+      <c r="CR2" s="30"/>
+      <c r="CS2" s="30"/>
+      <c r="CT2" s="30"/>
+      <c r="CU2" s="30"/>
+      <c r="CV2" s="30"/>
+      <c r="CW2" s="30"/>
+      <c r="CX2" s="30"/>
+      <c r="CY2" s="30"/>
+      <c r="CZ2" s="30"/>
+      <c r="DA2" s="30"/>
+      <c r="DB2" s="30"/>
+      <c r="DC2" s="30"/>
+      <c r="DD2" s="30"/>
+      <c r="DE2" s="30"/>
+      <c r="DF2" s="30"/>
+      <c r="DG2" s="30"/>
+      <c r="DH2" s="30"/>
+      <c r="DI2" s="30"/>
+      <c r="DJ2" s="30"/>
+      <c r="DK2" s="30"/>
+      <c r="DL2" s="30"/>
+      <c r="DM2" s="30"/>
+      <c r="DN2" s="30"/>
+      <c r="DO2" s="30"/>
+      <c r="DP2" s="30"/>
+      <c r="DQ2" s="30"/>
+      <c r="DR2" s="30"/>
+      <c r="DS2" s="30"/>
+      <c r="DT2" s="30"/>
     </row>
     <row r="3" spans="1:125" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="28"/>
-      <c r="O3" s="28"/>
-      <c r="P3" s="28"/>
-      <c r="Q3" s="28"/>
-      <c r="R3" s="28"/>
-      <c r="S3" s="28"/>
-      <c r="T3" s="28"/>
-      <c r="U3" s="28"/>
-      <c r="V3" s="28"/>
-      <c r="W3" s="28"/>
-      <c r="X3" s="28"/>
-      <c r="Y3" s="28"/>
-      <c r="Z3" s="28"/>
-      <c r="AA3" s="28"/>
-      <c r="AB3" s="28"/>
-      <c r="AC3" s="28"/>
-      <c r="AD3" s="28"/>
-      <c r="AE3" s="28"/>
-      <c r="AF3" s="28"/>
-      <c r="AG3" s="28"/>
-      <c r="AH3" s="28"/>
-      <c r="AI3" s="28"/>
-      <c r="AJ3" s="28"/>
-      <c r="AK3" s="28"/>
-      <c r="AL3" s="28"/>
-      <c r="AM3" s="28"/>
-      <c r="AN3" s="28"/>
-      <c r="AO3" s="28"/>
-      <c r="AP3" s="28"/>
-      <c r="AQ3" s="28"/>
-      <c r="AR3" s="28"/>
-      <c r="AS3" s="28"/>
-      <c r="AT3" s="28"/>
-      <c r="AU3" s="28"/>
-      <c r="AV3" s="28"/>
-      <c r="AW3" s="28"/>
-      <c r="AX3" s="28"/>
-      <c r="AY3" s="28"/>
-      <c r="AZ3" s="28"/>
-      <c r="BA3" s="28"/>
-      <c r="BB3" s="28"/>
-      <c r="BC3" s="28"/>
-      <c r="BD3" s="28"/>
-      <c r="BE3" s="28"/>
-      <c r="BF3" s="28"/>
-      <c r="BG3" s="28"/>
-      <c r="BH3" s="28"/>
-      <c r="BI3" s="28"/>
-      <c r="BJ3" s="28"/>
-      <c r="BK3" s="28"/>
-      <c r="BL3" s="28"/>
-      <c r="BM3" s="28"/>
-      <c r="BN3" s="28"/>
-      <c r="BO3" s="28"/>
-      <c r="BP3" s="28"/>
-      <c r="BQ3" s="28"/>
-      <c r="BR3" s="28"/>
-      <c r="BS3" s="28"/>
-      <c r="BT3" s="28"/>
-      <c r="BU3" s="28"/>
-      <c r="BV3" s="28"/>
-      <c r="BW3" s="28"/>
-      <c r="BX3" s="28"/>
-      <c r="BY3" s="28"/>
-      <c r="BZ3" s="28"/>
-      <c r="CA3" s="28"/>
-      <c r="CB3" s="28"/>
-      <c r="CC3" s="28"/>
-      <c r="CD3" s="28"/>
-      <c r="CE3" s="28"/>
-      <c r="CF3" s="28"/>
-      <c r="CG3" s="28"/>
-      <c r="CH3" s="28"/>
-      <c r="CI3" s="28"/>
-      <c r="CJ3" s="28"/>
-      <c r="CK3" s="28"/>
-      <c r="CL3" s="28"/>
-      <c r="CM3" s="28"/>
-      <c r="CN3" s="28"/>
-      <c r="CO3" s="28"/>
-      <c r="CP3" s="28"/>
-      <c r="CQ3" s="28"/>
-      <c r="CR3" s="28"/>
-      <c r="CS3" s="28"/>
-      <c r="CT3" s="28"/>
-      <c r="CU3" s="28"/>
-      <c r="CV3" s="28"/>
-      <c r="CW3" s="28"/>
-      <c r="CX3" s="28"/>
-      <c r="CY3" s="28"/>
-      <c r="CZ3" s="28"/>
-      <c r="DA3" s="28"/>
-      <c r="DB3" s="28"/>
-      <c r="DC3" s="28"/>
-      <c r="DD3" s="28"/>
-      <c r="DE3" s="28"/>
-      <c r="DF3" s="28"/>
-      <c r="DG3" s="28"/>
-      <c r="DH3" s="28"/>
-      <c r="DI3" s="28"/>
-      <c r="DJ3" s="28"/>
-      <c r="DK3" s="28"/>
-      <c r="DL3" s="28"/>
-      <c r="DM3" s="28"/>
-      <c r="DN3" s="28"/>
-      <c r="DO3" s="28"/>
-      <c r="DP3" s="28"/>
-      <c r="DQ3" s="28"/>
-      <c r="DR3" s="28"/>
-      <c r="DS3" s="28"/>
-      <c r="DT3" s="28"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="30"/>
+      <c r="M3" s="30"/>
+      <c r="N3" s="30"/>
+      <c r="O3" s="30"/>
+      <c r="P3" s="30"/>
+      <c r="Q3" s="30"/>
+      <c r="R3" s="30"/>
+      <c r="S3" s="30"/>
+      <c r="T3" s="30"/>
+      <c r="U3" s="30"/>
+      <c r="V3" s="65"/>
+      <c r="W3" s="65"/>
+      <c r="X3" s="30"/>
+      <c r="Y3" s="30"/>
+      <c r="Z3" s="30"/>
+      <c r="AA3" s="30"/>
+      <c r="AB3" s="30"/>
+      <c r="AC3" s="30"/>
+      <c r="AD3" s="30"/>
+      <c r="AE3" s="30"/>
+      <c r="AF3" s="30"/>
+      <c r="AG3" s="30"/>
+      <c r="AH3" s="30"/>
+      <c r="AI3" s="30"/>
+      <c r="AJ3" s="30"/>
+      <c r="AK3" s="30"/>
+      <c r="AL3" s="30"/>
+      <c r="AM3" s="30"/>
+      <c r="AN3" s="30"/>
+      <c r="AO3" s="30"/>
+      <c r="AP3" s="30"/>
+      <c r="AQ3" s="30"/>
+      <c r="AR3" s="30"/>
+      <c r="AS3" s="30"/>
+      <c r="AT3" s="30"/>
+      <c r="AU3" s="30"/>
+      <c r="AV3" s="30"/>
+      <c r="AW3" s="30"/>
+      <c r="AX3" s="30"/>
+      <c r="AY3" s="30"/>
+      <c r="AZ3" s="30"/>
+      <c r="BA3" s="30"/>
+      <c r="BB3" s="30"/>
+      <c r="BC3" s="30"/>
+      <c r="BD3" s="30"/>
+      <c r="BE3" s="30"/>
+      <c r="BF3" s="30"/>
+      <c r="BG3" s="30"/>
+      <c r="BH3" s="30"/>
+      <c r="BI3" s="30"/>
+      <c r="BJ3" s="30"/>
+      <c r="BK3" s="30"/>
+      <c r="BL3" s="30"/>
+      <c r="BM3" s="30"/>
+      <c r="BN3" s="30"/>
+      <c r="BO3" s="30"/>
+      <c r="BP3" s="30"/>
+      <c r="BQ3" s="30"/>
+      <c r="BR3" s="30"/>
+      <c r="BS3" s="30"/>
+      <c r="BT3" s="30"/>
+      <c r="BU3" s="30"/>
+      <c r="BV3" s="30"/>
+      <c r="BW3" s="30"/>
+      <c r="BX3" s="30"/>
+      <c r="BY3" s="30"/>
+      <c r="BZ3" s="30"/>
+      <c r="CA3" s="30"/>
+      <c r="CB3" s="30"/>
+      <c r="CC3" s="30"/>
+      <c r="CD3" s="30"/>
+      <c r="CE3" s="30"/>
+      <c r="CF3" s="30"/>
+      <c r="CG3" s="30"/>
+      <c r="CH3" s="30"/>
+      <c r="CI3" s="30"/>
+      <c r="CJ3" s="30"/>
+      <c r="CK3" s="30"/>
+      <c r="CL3" s="30"/>
+      <c r="CM3" s="30"/>
+      <c r="CN3" s="30"/>
+      <c r="CO3" s="30"/>
+      <c r="CP3" s="30"/>
+      <c r="CQ3" s="30"/>
+      <c r="CR3" s="30"/>
+      <c r="CS3" s="30"/>
+      <c r="CT3" s="30"/>
+      <c r="CU3" s="30"/>
+      <c r="CV3" s="30"/>
+      <c r="CW3" s="30"/>
+      <c r="CX3" s="30"/>
+      <c r="CY3" s="30"/>
+      <c r="CZ3" s="30"/>
+      <c r="DA3" s="30"/>
+      <c r="DB3" s="30"/>
+      <c r="DC3" s="30"/>
+      <c r="DD3" s="30"/>
+      <c r="DE3" s="30"/>
+      <c r="DF3" s="30"/>
+      <c r="DG3" s="30"/>
+      <c r="DH3" s="30"/>
+      <c r="DI3" s="30"/>
+      <c r="DJ3" s="30"/>
+      <c r="DK3" s="30"/>
+      <c r="DL3" s="30"/>
+      <c r="DM3" s="30"/>
+      <c r="DN3" s="30"/>
+      <c r="DO3" s="30"/>
+      <c r="DP3" s="30"/>
+      <c r="DQ3" s="30"/>
+      <c r="DR3" s="30"/>
+      <c r="DS3" s="30"/>
+      <c r="DT3" s="30"/>
     </row>
     <row r="4" spans="1:125" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="46" t="s">
+      <c r="A4" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="48"/>
+      <c r="C4" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="47"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="28"/>
-      <c r="M4" s="28"/>
-      <c r="N4" s="28"/>
-      <c r="O4" s="28"/>
-      <c r="P4" s="28"/>
-      <c r="Q4" s="28"/>
-      <c r="R4" s="28"/>
-      <c r="S4" s="28"/>
-      <c r="T4" s="28"/>
-      <c r="U4" s="28"/>
-      <c r="V4" s="28"/>
-      <c r="W4" s="28"/>
-      <c r="X4" s="28"/>
-      <c r="Y4" s="28"/>
-      <c r="Z4" s="28"/>
-      <c r="AA4" s="28"/>
-      <c r="AB4" s="28"/>
-      <c r="AC4" s="28"/>
-      <c r="AD4" s="28"/>
-      <c r="AE4" s="28"/>
-      <c r="AF4" s="28"/>
-      <c r="AG4" s="28"/>
-      <c r="AH4" s="28"/>
-      <c r="AI4" s="28"/>
-      <c r="AJ4" s="28"/>
-      <c r="AK4" s="28"/>
-      <c r="AL4" s="28"/>
-      <c r="AM4" s="28"/>
-      <c r="AN4" s="28"/>
-      <c r="AO4" s="28"/>
-      <c r="AP4" s="28"/>
-      <c r="AQ4" s="28"/>
-      <c r="AR4" s="28"/>
-      <c r="AS4" s="28"/>
-      <c r="AT4" s="28"/>
-      <c r="AU4" s="28"/>
-      <c r="AV4" s="28"/>
-      <c r="AW4" s="28"/>
-      <c r="AX4" s="28"/>
-      <c r="AY4" s="28"/>
-      <c r="AZ4" s="28"/>
-      <c r="BA4" s="28"/>
-      <c r="BB4" s="28"/>
-      <c r="BC4" s="28"/>
-      <c r="BD4" s="28"/>
-      <c r="BE4" s="28"/>
-      <c r="BF4" s="28"/>
-      <c r="BG4" s="28"/>
-      <c r="BH4" s="28"/>
-      <c r="BI4" s="28"/>
-      <c r="BJ4" s="28"/>
-      <c r="BK4" s="28"/>
-      <c r="BL4" s="28"/>
-      <c r="BM4" s="28"/>
-      <c r="BN4" s="28"/>
-      <c r="BO4" s="28"/>
-      <c r="BP4" s="28"/>
-      <c r="BQ4" s="28"/>
-      <c r="BR4" s="28"/>
-      <c r="BS4" s="28"/>
-      <c r="BT4" s="28"/>
-      <c r="BU4" s="28"/>
-      <c r="BV4" s="28"/>
-      <c r="BW4" s="28"/>
-      <c r="BX4" s="28"/>
-      <c r="BY4" s="28"/>
-      <c r="BZ4" s="28"/>
-      <c r="CA4" s="28"/>
-      <c r="CB4" s="28"/>
-      <c r="CC4" s="28"/>
-      <c r="CD4" s="28"/>
-      <c r="CE4" s="28"/>
-      <c r="CF4" s="28"/>
-      <c r="CG4" s="28"/>
-      <c r="CH4" s="28"/>
-      <c r="CI4" s="28"/>
-      <c r="CJ4" s="28"/>
-      <c r="CK4" s="28"/>
-      <c r="CL4" s="28"/>
-      <c r="CM4" s="28"/>
-      <c r="CN4" s="28"/>
-      <c r="CO4" s="28"/>
-      <c r="CP4" s="28"/>
-      <c r="CQ4" s="28"/>
-      <c r="CR4" s="28"/>
-      <c r="CS4" s="28"/>
-      <c r="CT4" s="28"/>
-      <c r="CU4" s="28"/>
-      <c r="CV4" s="28"/>
-      <c r="CW4" s="28"/>
-      <c r="CX4" s="28"/>
-      <c r="CY4" s="28"/>
-      <c r="CZ4" s="28"/>
-      <c r="DA4" s="28"/>
-      <c r="DB4" s="28"/>
-      <c r="DC4" s="28"/>
-      <c r="DD4" s="28"/>
-      <c r="DE4" s="28"/>
-      <c r="DF4" s="28"/>
-      <c r="DG4" s="28"/>
-      <c r="DH4" s="28"/>
-      <c r="DI4" s="28"/>
-      <c r="DJ4" s="28"/>
-      <c r="DK4" s="28"/>
-      <c r="DL4" s="28"/>
-      <c r="DM4" s="28"/>
-      <c r="DN4" s="28"/>
-      <c r="DO4" s="28"/>
-      <c r="DP4" s="28"/>
-      <c r="DQ4" s="28"/>
-      <c r="DR4" s="28"/>
-      <c r="DS4" s="28"/>
-      <c r="DT4" s="28"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="30"/>
+      <c r="K4" s="30"/>
+      <c r="L4" s="30"/>
+      <c r="M4" s="30"/>
+      <c r="N4" s="30"/>
+      <c r="O4" s="30"/>
+      <c r="P4" s="30"/>
+      <c r="Q4" s="30"/>
+      <c r="R4" s="30"/>
+      <c r="S4" s="30"/>
+      <c r="T4" s="30"/>
+      <c r="U4" s="30"/>
+      <c r="V4" s="65"/>
+      <c r="W4" s="65"/>
+      <c r="X4" s="30"/>
+      <c r="Y4" s="30"/>
+      <c r="Z4" s="30"/>
+      <c r="AA4" s="30"/>
+      <c r="AB4" s="30"/>
+      <c r="AC4" s="30"/>
+      <c r="AD4" s="30"/>
+      <c r="AE4" s="30"/>
+      <c r="AF4" s="30"/>
+      <c r="AG4" s="30"/>
+      <c r="AH4" s="30"/>
+      <c r="AI4" s="30"/>
+      <c r="AJ4" s="30"/>
+      <c r="AK4" s="30"/>
+      <c r="AL4" s="30"/>
+      <c r="AM4" s="30"/>
+      <c r="AN4" s="30"/>
+      <c r="AO4" s="30"/>
+      <c r="AP4" s="30"/>
+      <c r="AQ4" s="30"/>
+      <c r="AR4" s="30"/>
+      <c r="AS4" s="30"/>
+      <c r="AT4" s="30"/>
+      <c r="AU4" s="30"/>
+      <c r="AV4" s="30"/>
+      <c r="AW4" s="30"/>
+      <c r="AX4" s="30"/>
+      <c r="AY4" s="30"/>
+      <c r="AZ4" s="30"/>
+      <c r="BA4" s="30"/>
+      <c r="BB4" s="30"/>
+      <c r="BC4" s="30"/>
+      <c r="BD4" s="30"/>
+      <c r="BE4" s="30"/>
+      <c r="BF4" s="30"/>
+      <c r="BG4" s="30"/>
+      <c r="BH4" s="30"/>
+      <c r="BI4" s="30"/>
+      <c r="BJ4" s="30"/>
+      <c r="BK4" s="30"/>
+      <c r="BL4" s="30"/>
+      <c r="BM4" s="30"/>
+      <c r="BN4" s="30"/>
+      <c r="BO4" s="30"/>
+      <c r="BP4" s="30"/>
+      <c r="BQ4" s="30"/>
+      <c r="BR4" s="30"/>
+      <c r="BS4" s="30"/>
+      <c r="BT4" s="30"/>
+      <c r="BU4" s="30"/>
+      <c r="BV4" s="30"/>
+      <c r="BW4" s="30"/>
+      <c r="BX4" s="30"/>
+      <c r="BY4" s="30"/>
+      <c r="BZ4" s="30"/>
+      <c r="CA4" s="30"/>
+      <c r="CB4" s="30"/>
+      <c r="CC4" s="30"/>
+      <c r="CD4" s="30"/>
+      <c r="CE4" s="30"/>
+      <c r="CF4" s="30"/>
+      <c r="CG4" s="30"/>
+      <c r="CH4" s="30"/>
+      <c r="CI4" s="30"/>
+      <c r="CJ4" s="30"/>
+      <c r="CK4" s="30"/>
+      <c r="CL4" s="30"/>
+      <c r="CM4" s="30"/>
+      <c r="CN4" s="30"/>
+      <c r="CO4" s="30"/>
+      <c r="CP4" s="30"/>
+      <c r="CQ4" s="30"/>
+      <c r="CR4" s="30"/>
+      <c r="CS4" s="30"/>
+      <c r="CT4" s="30"/>
+      <c r="CU4" s="30"/>
+      <c r="CV4" s="30"/>
+      <c r="CW4" s="30"/>
+      <c r="CX4" s="30"/>
+      <c r="CY4" s="30"/>
+      <c r="CZ4" s="30"/>
+      <c r="DA4" s="30"/>
+      <c r="DB4" s="30"/>
+      <c r="DC4" s="30"/>
+      <c r="DD4" s="30"/>
+      <c r="DE4" s="30"/>
+      <c r="DF4" s="30"/>
+      <c r="DG4" s="30"/>
+      <c r="DH4" s="30"/>
+      <c r="DI4" s="30"/>
+      <c r="DJ4" s="30"/>
+      <c r="DK4" s="30"/>
+      <c r="DL4" s="30"/>
+      <c r="DM4" s="30"/>
+      <c r="DN4" s="30"/>
+      <c r="DO4" s="30"/>
+      <c r="DP4" s="30"/>
+      <c r="DQ4" s="30"/>
+      <c r="DR4" s="30"/>
+      <c r="DS4" s="30"/>
+      <c r="DT4" s="30"/>
     </row>
     <row r="5" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="49">
+      <c r="B5" s="49"/>
+      <c r="C5" s="50">
         <v>60</v>
       </c>
-      <c r="D5" s="50"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
-      <c r="K5" s="28"/>
-      <c r="L5" s="28"/>
-      <c r="M5" s="28"/>
-      <c r="N5" s="28"/>
-      <c r="O5" s="28"/>
-      <c r="P5" s="28"/>
-      <c r="Q5" s="28"/>
-      <c r="R5" s="28"/>
-      <c r="S5" s="28"/>
-      <c r="T5" s="28"/>
-      <c r="U5" s="28"/>
-      <c r="V5" s="28"/>
-      <c r="W5" s="28"/>
-      <c r="X5" s="28"/>
-      <c r="Y5" s="28"/>
-      <c r="Z5" s="28"/>
-      <c r="AA5" s="28"/>
-      <c r="AB5" s="28"/>
-      <c r="AC5" s="28"/>
-      <c r="AD5" s="28"/>
-      <c r="AE5" s="28"/>
-      <c r="AF5" s="28"/>
-      <c r="AG5" s="28"/>
-      <c r="AH5" s="28"/>
-      <c r="AI5" s="28"/>
-      <c r="AJ5" s="28"/>
-      <c r="AK5" s="28"/>
-      <c r="AL5" s="28"/>
-      <c r="AM5" s="28"/>
-      <c r="AN5" s="28"/>
-      <c r="AO5" s="28"/>
-      <c r="AP5" s="28"/>
-      <c r="AQ5" s="28"/>
-      <c r="AR5" s="28"/>
-      <c r="AS5" s="28"/>
-      <c r="AT5" s="28"/>
-      <c r="AU5" s="28"/>
-      <c r="AV5" s="28"/>
-      <c r="AW5" s="28"/>
-      <c r="AX5" s="28"/>
-      <c r="AY5" s="28"/>
-      <c r="AZ5" s="28"/>
-      <c r="BA5" s="28"/>
-      <c r="BB5" s="28"/>
-      <c r="BC5" s="28"/>
-      <c r="BD5" s="28"/>
-      <c r="BE5" s="28"/>
-      <c r="BF5" s="28"/>
-      <c r="BG5" s="28"/>
-      <c r="BH5" s="28"/>
-      <c r="BI5" s="28"/>
-      <c r="BJ5" s="28"/>
-      <c r="BK5" s="28"/>
-      <c r="BL5" s="28"/>
-      <c r="BM5" s="28"/>
-      <c r="BN5" s="28"/>
-      <c r="BO5" s="28"/>
-      <c r="BP5" s="28"/>
-      <c r="BQ5" s="28"/>
-      <c r="BR5" s="28"/>
-      <c r="BS5" s="28"/>
-      <c r="BT5" s="28"/>
-      <c r="BU5" s="28"/>
-      <c r="BV5" s="28"/>
-      <c r="BW5" s="28"/>
-      <c r="BX5" s="28"/>
-      <c r="BY5" s="28"/>
-      <c r="BZ5" s="28"/>
-      <c r="CA5" s="28"/>
-      <c r="CB5" s="28"/>
-      <c r="CC5" s="28"/>
-      <c r="CD5" s="28"/>
-      <c r="CE5" s="28"/>
-      <c r="CF5" s="28"/>
-      <c r="CG5" s="28"/>
-      <c r="CH5" s="28"/>
-      <c r="CI5" s="28"/>
-      <c r="CJ5" s="28"/>
-      <c r="CK5" s="28"/>
-      <c r="CL5" s="28"/>
-      <c r="CM5" s="28"/>
-      <c r="CN5" s="28"/>
-      <c r="CO5" s="28"/>
-      <c r="CP5" s="28"/>
-      <c r="CQ5" s="28"/>
-      <c r="CR5" s="28"/>
-      <c r="CS5" s="28"/>
-      <c r="CT5" s="28"/>
-      <c r="CU5" s="28"/>
-      <c r="CV5" s="28"/>
-      <c r="CW5" s="28"/>
-      <c r="CX5" s="28"/>
-      <c r="CY5" s="28"/>
-      <c r="CZ5" s="28"/>
-      <c r="DA5" s="28"/>
-      <c r="DB5" s="28"/>
-      <c r="DC5" s="28"/>
-      <c r="DD5" s="28"/>
-      <c r="DE5" s="28"/>
-      <c r="DF5" s="28"/>
-      <c r="DG5" s="28"/>
-      <c r="DH5" s="28"/>
-      <c r="DI5" s="28"/>
-      <c r="DJ5" s="28"/>
-      <c r="DK5" s="28"/>
-      <c r="DL5" s="28"/>
-      <c r="DM5" s="28"/>
-      <c r="DN5" s="28"/>
-      <c r="DO5" s="28"/>
-      <c r="DP5" s="28"/>
-      <c r="DQ5" s="28"/>
-      <c r="DR5" s="28"/>
-      <c r="DS5" s="28"/>
-      <c r="DT5" s="28"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="30"/>
+      <c r="L5" s="30"/>
+      <c r="M5" s="30"/>
+      <c r="N5" s="30"/>
+      <c r="O5" s="30"/>
+      <c r="P5" s="30"/>
+      <c r="Q5" s="30"/>
+      <c r="R5" s="30"/>
+      <c r="S5" s="30"/>
+      <c r="T5" s="30"/>
+      <c r="U5" s="30"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="30"/>
+      <c r="Y5" s="30"/>
+      <c r="Z5" s="30"/>
+      <c r="AA5" s="30"/>
+      <c r="AB5" s="30"/>
+      <c r="AC5" s="30"/>
+      <c r="AD5" s="30"/>
+      <c r="AE5" s="30"/>
+      <c r="AF5" s="30"/>
+      <c r="AG5" s="30"/>
+      <c r="AH5" s="30"/>
+      <c r="AI5" s="30"/>
+      <c r="AJ5" s="30"/>
+      <c r="AK5" s="30"/>
+      <c r="AL5" s="30"/>
+      <c r="AM5" s="30"/>
+      <c r="AN5" s="30"/>
+      <c r="AO5" s="30"/>
+      <c r="AP5" s="30"/>
+      <c r="AQ5" s="30"/>
+      <c r="AR5" s="30"/>
+      <c r="AS5" s="30"/>
+      <c r="AT5" s="30"/>
+      <c r="AU5" s="30"/>
+      <c r="AV5" s="30"/>
+      <c r="AW5" s="30"/>
+      <c r="AX5" s="30"/>
+      <c r="AY5" s="30"/>
+      <c r="AZ5" s="30"/>
+      <c r="BA5" s="30"/>
+      <c r="BB5" s="30"/>
+      <c r="BC5" s="30"/>
+      <c r="BD5" s="30"/>
+      <c r="BE5" s="30"/>
+      <c r="BF5" s="30"/>
+      <c r="BG5" s="30"/>
+      <c r="BH5" s="30"/>
+      <c r="BI5" s="30"/>
+      <c r="BJ5" s="30"/>
+      <c r="BK5" s="30"/>
+      <c r="BL5" s="30"/>
+      <c r="BM5" s="30"/>
+      <c r="BN5" s="30"/>
+      <c r="BO5" s="30"/>
+      <c r="BP5" s="30"/>
+      <c r="BQ5" s="30"/>
+      <c r="BR5" s="30"/>
+      <c r="BS5" s="30"/>
+      <c r="BT5" s="30"/>
+      <c r="BU5" s="30"/>
+      <c r="BV5" s="30"/>
+      <c r="BW5" s="30"/>
+      <c r="BX5" s="30"/>
+      <c r="BY5" s="30"/>
+      <c r="BZ5" s="30"/>
+      <c r="CA5" s="30"/>
+      <c r="CB5" s="30"/>
+      <c r="CC5" s="30"/>
+      <c r="CD5" s="30"/>
+      <c r="CE5" s="30"/>
+      <c r="CF5" s="30"/>
+      <c r="CG5" s="30"/>
+      <c r="CH5" s="30"/>
+      <c r="CI5" s="30"/>
+      <c r="CJ5" s="30"/>
+      <c r="CK5" s="30"/>
+      <c r="CL5" s="30"/>
+      <c r="CM5" s="30"/>
+      <c r="CN5" s="30"/>
+      <c r="CO5" s="30"/>
+      <c r="CP5" s="30"/>
+      <c r="CQ5" s="30"/>
+      <c r="CR5" s="30"/>
+      <c r="CS5" s="30"/>
+      <c r="CT5" s="30"/>
+      <c r="CU5" s="30"/>
+      <c r="CV5" s="30"/>
+      <c r="CW5" s="30"/>
+      <c r="CX5" s="30"/>
+      <c r="CY5" s="30"/>
+      <c r="CZ5" s="30"/>
+      <c r="DA5" s="30"/>
+      <c r="DB5" s="30"/>
+      <c r="DC5" s="30"/>
+      <c r="DD5" s="30"/>
+      <c r="DE5" s="30"/>
+      <c r="DF5" s="30"/>
+      <c r="DG5" s="30"/>
+      <c r="DH5" s="30"/>
+      <c r="DI5" s="30"/>
+      <c r="DJ5" s="30"/>
+      <c r="DK5" s="30"/>
+      <c r="DL5" s="30"/>
+      <c r="DM5" s="30"/>
+      <c r="DN5" s="30"/>
+      <c r="DO5" s="30"/>
+      <c r="DP5" s="30"/>
+      <c r="DQ5" s="30"/>
+      <c r="DR5" s="30"/>
+      <c r="DS5" s="30"/>
+      <c r="DT5" s="30"/>
     </row>
     <row r="6" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="48" t="s">
+      <c r="A6" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="49">
+      <c r="B6" s="49"/>
+      <c r="C6" s="50">
         <v>4</v>
       </c>
-      <c r="D6" s="50"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="28"/>
-      <c r="K6" s="28"/>
-      <c r="L6" s="28"/>
-      <c r="M6" s="28"/>
-      <c r="N6" s="28"/>
-      <c r="O6" s="28"/>
-      <c r="P6" s="28"/>
-      <c r="Q6" s="28"/>
-      <c r="R6" s="28"/>
-      <c r="S6" s="28"/>
-      <c r="T6" s="28"/>
-      <c r="U6" s="28"/>
-      <c r="V6" s="28"/>
-      <c r="W6" s="28"/>
-      <c r="X6" s="28"/>
-      <c r="Y6" s="28"/>
-      <c r="Z6" s="28"/>
-      <c r="AA6" s="28"/>
-      <c r="AB6" s="28"/>
-      <c r="AC6" s="28"/>
-      <c r="AD6" s="28"/>
-      <c r="AE6" s="28"/>
-      <c r="AF6" s="28"/>
-      <c r="AG6" s="28"/>
-      <c r="AH6" s="28"/>
-      <c r="AI6" s="28"/>
-      <c r="AJ6" s="28"/>
-      <c r="AK6" s="28"/>
-      <c r="AL6" s="28"/>
-      <c r="AM6" s="28"/>
-      <c r="AN6" s="28"/>
-      <c r="AO6" s="28"/>
-      <c r="AP6" s="28"/>
-      <c r="AQ6" s="28"/>
-      <c r="AR6" s="28"/>
-      <c r="AS6" s="28"/>
-      <c r="AT6" s="28"/>
-      <c r="AU6" s="28"/>
-      <c r="AV6" s="28"/>
-      <c r="AW6" s="28"/>
-      <c r="AX6" s="28"/>
-      <c r="AY6" s="28"/>
-      <c r="AZ6" s="28"/>
-      <c r="BA6" s="28"/>
-      <c r="BB6" s="28"/>
-      <c r="BC6" s="28"/>
-      <c r="BD6" s="28"/>
-      <c r="BE6" s="28"/>
-      <c r="BF6" s="28"/>
-      <c r="BG6" s="28"/>
-      <c r="BH6" s="28"/>
-      <c r="BI6" s="28"/>
-      <c r="BJ6" s="28"/>
-      <c r="BK6" s="28"/>
-      <c r="BL6" s="28"/>
-      <c r="BM6" s="28"/>
-      <c r="BN6" s="28"/>
-      <c r="BO6" s="28"/>
-      <c r="BP6" s="28"/>
-      <c r="BQ6" s="28"/>
-      <c r="BR6" s="28"/>
-      <c r="BS6" s="28"/>
-      <c r="BT6" s="28"/>
-      <c r="BU6" s="28"/>
-      <c r="BV6" s="28"/>
-      <c r="BW6" s="28"/>
-      <c r="BX6" s="28"/>
-      <c r="BY6" s="28"/>
-      <c r="BZ6" s="28"/>
-      <c r="CA6" s="28"/>
-      <c r="CB6" s="28"/>
-      <c r="CC6" s="28"/>
-      <c r="CD6" s="28"/>
-      <c r="CE6" s="28"/>
-      <c r="CF6" s="28"/>
-      <c r="CG6" s="28"/>
-      <c r="CH6" s="28"/>
-      <c r="CI6" s="28"/>
-      <c r="CJ6" s="28"/>
-      <c r="CK6" s="28"/>
-      <c r="CL6" s="28"/>
-      <c r="CM6" s="28"/>
-      <c r="CN6" s="28"/>
-      <c r="CO6" s="28"/>
-      <c r="CP6" s="28"/>
-      <c r="CQ6" s="28"/>
-      <c r="CR6" s="28"/>
-      <c r="CS6" s="28"/>
-      <c r="CT6" s="28"/>
-      <c r="CU6" s="28"/>
-      <c r="CV6" s="28"/>
-      <c r="CW6" s="28"/>
-      <c r="CX6" s="28"/>
-      <c r="CY6" s="28"/>
-      <c r="CZ6" s="28"/>
-      <c r="DA6" s="28"/>
-      <c r="DB6" s="28"/>
-      <c r="DC6" s="28"/>
-      <c r="DD6" s="28"/>
-      <c r="DE6" s="28"/>
-      <c r="DF6" s="28"/>
-      <c r="DG6" s="28"/>
-      <c r="DH6" s="28"/>
-      <c r="DI6" s="28"/>
-      <c r="DJ6" s="28"/>
-      <c r="DK6" s="28"/>
-      <c r="DL6" s="28"/>
-      <c r="DM6" s="28"/>
-      <c r="DN6" s="28"/>
-      <c r="DO6" s="28"/>
-      <c r="DP6" s="28"/>
-      <c r="DQ6" s="28"/>
-      <c r="DR6" s="28"/>
-      <c r="DS6" s="28"/>
-      <c r="DT6" s="28"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="30"/>
+      <c r="L6" s="30"/>
+      <c r="M6" s="30"/>
+      <c r="N6" s="30"/>
+      <c r="O6" s="30"/>
+      <c r="P6" s="30"/>
+      <c r="Q6" s="30"/>
+      <c r="R6" s="30"/>
+      <c r="S6" s="30"/>
+      <c r="T6" s="30"/>
+      <c r="U6" s="30"/>
+      <c r="V6" s="65"/>
+      <c r="W6" s="65"/>
+      <c r="X6" s="30"/>
+      <c r="Y6" s="30"/>
+      <c r="Z6" s="30"/>
+      <c r="AA6" s="30"/>
+      <c r="AB6" s="30"/>
+      <c r="AC6" s="30"/>
+      <c r="AD6" s="30"/>
+      <c r="AE6" s="30"/>
+      <c r="AF6" s="30"/>
+      <c r="AG6" s="30"/>
+      <c r="AH6" s="30"/>
+      <c r="AI6" s="30"/>
+      <c r="AJ6" s="30"/>
+      <c r="AK6" s="30"/>
+      <c r="AL6" s="30"/>
+      <c r="AM6" s="30"/>
+      <c r="AN6" s="30"/>
+      <c r="AO6" s="30"/>
+      <c r="AP6" s="30"/>
+      <c r="AQ6" s="30"/>
+      <c r="AR6" s="30"/>
+      <c r="AS6" s="30"/>
+      <c r="AT6" s="30"/>
+      <c r="AU6" s="30"/>
+      <c r="AV6" s="30"/>
+      <c r="AW6" s="30"/>
+      <c r="AX6" s="30"/>
+      <c r="AY6" s="30"/>
+      <c r="AZ6" s="30"/>
+      <c r="BA6" s="30"/>
+      <c r="BB6" s="30"/>
+      <c r="BC6" s="30"/>
+      <c r="BD6" s="30"/>
+      <c r="BE6" s="30"/>
+      <c r="BF6" s="30"/>
+      <c r="BG6" s="30"/>
+      <c r="BH6" s="30"/>
+      <c r="BI6" s="30"/>
+      <c r="BJ6" s="30"/>
+      <c r="BK6" s="30"/>
+      <c r="BL6" s="30"/>
+      <c r="BM6" s="30"/>
+      <c r="BN6" s="30"/>
+      <c r="BO6" s="30"/>
+      <c r="BP6" s="30"/>
+      <c r="BQ6" s="30"/>
+      <c r="BR6" s="30"/>
+      <c r="BS6" s="30"/>
+      <c r="BT6" s="30"/>
+      <c r="BU6" s="30"/>
+      <c r="BV6" s="30"/>
+      <c r="BW6" s="30"/>
+      <c r="BX6" s="30"/>
+      <c r="BY6" s="30"/>
+      <c r="BZ6" s="30"/>
+      <c r="CA6" s="30"/>
+      <c r="CB6" s="30"/>
+      <c r="CC6" s="30"/>
+      <c r="CD6" s="30"/>
+      <c r="CE6" s="30"/>
+      <c r="CF6" s="30"/>
+      <c r="CG6" s="30"/>
+      <c r="CH6" s="30"/>
+      <c r="CI6" s="30"/>
+      <c r="CJ6" s="30"/>
+      <c r="CK6" s="30"/>
+      <c r="CL6" s="30"/>
+      <c r="CM6" s="30"/>
+      <c r="CN6" s="30"/>
+      <c r="CO6" s="30"/>
+      <c r="CP6" s="30"/>
+      <c r="CQ6" s="30"/>
+      <c r="CR6" s="30"/>
+      <c r="CS6" s="30"/>
+      <c r="CT6" s="30"/>
+      <c r="CU6" s="30"/>
+      <c r="CV6" s="30"/>
+      <c r="CW6" s="30"/>
+      <c r="CX6" s="30"/>
+      <c r="CY6" s="30"/>
+      <c r="CZ6" s="30"/>
+      <c r="DA6" s="30"/>
+      <c r="DB6" s="30"/>
+      <c r="DC6" s="30"/>
+      <c r="DD6" s="30"/>
+      <c r="DE6" s="30"/>
+      <c r="DF6" s="30"/>
+      <c r="DG6" s="30"/>
+      <c r="DH6" s="30"/>
+      <c r="DI6" s="30"/>
+      <c r="DJ6" s="30"/>
+      <c r="DK6" s="30"/>
+      <c r="DL6" s="30"/>
+      <c r="DM6" s="30"/>
+      <c r="DN6" s="30"/>
+      <c r="DO6" s="30"/>
+      <c r="DP6" s="30"/>
+      <c r="DQ6" s="30"/>
+      <c r="DR6" s="30"/>
+      <c r="DS6" s="30"/>
+      <c r="DT6" s="30"/>
     </row>
     <row r="7" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="51" t="s">
+      <c r="A7" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="51"/>
-      <c r="C7" s="49">
+      <c r="B7" s="52"/>
+      <c r="C7" s="50">
         <v>11</v>
       </c>
-      <c r="D7" s="50"/>
-      <c r="E7" s="43"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="29"/>
-      <c r="J7" s="29"/>
-      <c r="K7" s="29"/>
-      <c r="L7" s="29"/>
-      <c r="M7" s="29"/>
-      <c r="N7" s="29"/>
-      <c r="O7" s="29"/>
-      <c r="P7" s="29"/>
-      <c r="Q7" s="29"/>
-      <c r="R7" s="29"/>
-      <c r="S7" s="29"/>
-      <c r="T7" s="29"/>
-      <c r="U7" s="29"/>
-      <c r="V7" s="29"/>
-      <c r="W7" s="29"/>
-      <c r="X7" s="29"/>
-      <c r="Y7" s="29"/>
-      <c r="Z7" s="29"/>
-      <c r="AA7" s="29"/>
-      <c r="AB7" s="29"/>
-      <c r="AC7" s="29"/>
-      <c r="AD7" s="29"/>
-      <c r="AE7" s="29"/>
-      <c r="AF7" s="29"/>
-      <c r="AG7" s="29"/>
-      <c r="AH7" s="29"/>
-      <c r="AI7" s="29"/>
-      <c r="AJ7" s="29"/>
-      <c r="AK7" s="29"/>
-      <c r="AL7" s="29"/>
-      <c r="AM7" s="29"/>
-      <c r="AN7" s="29"/>
-      <c r="AO7" s="29"/>
-      <c r="AP7" s="29"/>
-      <c r="AQ7" s="29"/>
-      <c r="AR7" s="29"/>
-      <c r="AS7" s="29"/>
-      <c r="AT7" s="29"/>
-      <c r="AU7" s="29"/>
-      <c r="AV7" s="29"/>
-      <c r="AW7" s="29"/>
-      <c r="AX7" s="29"/>
-      <c r="AY7" s="29"/>
-      <c r="AZ7" s="29"/>
-      <c r="BA7" s="29"/>
-      <c r="BB7" s="29"/>
-      <c r="BC7" s="29"/>
-      <c r="BD7" s="29"/>
-      <c r="BE7" s="29"/>
-      <c r="BF7" s="29"/>
-      <c r="BG7" s="29"/>
-      <c r="BH7" s="29"/>
-      <c r="BI7" s="29"/>
-      <c r="BJ7" s="29"/>
-      <c r="BK7" s="29"/>
-      <c r="BL7" s="29"/>
-      <c r="BM7" s="29"/>
-      <c r="BN7" s="29"/>
-      <c r="BO7" s="29"/>
-      <c r="BP7" s="29"/>
-      <c r="BQ7" s="29"/>
-      <c r="BR7" s="29"/>
-      <c r="BS7" s="29"/>
-      <c r="BT7" s="29"/>
-      <c r="BU7" s="29"/>
-      <c r="BV7" s="29"/>
-      <c r="BW7" s="29"/>
-      <c r="BX7" s="29"/>
-      <c r="BY7" s="29"/>
-      <c r="BZ7" s="29"/>
-      <c r="CA7" s="29"/>
-      <c r="CB7" s="29"/>
-      <c r="CC7" s="29"/>
-      <c r="CD7" s="29"/>
-      <c r="CE7" s="29"/>
-      <c r="CF7" s="29"/>
-      <c r="CG7" s="29"/>
-      <c r="CH7" s="29"/>
-      <c r="CI7" s="29"/>
-      <c r="CJ7" s="29"/>
-      <c r="CK7" s="29"/>
-      <c r="CL7" s="29"/>
-      <c r="CM7" s="29"/>
-      <c r="CN7" s="29"/>
-      <c r="CO7" s="29"/>
-      <c r="CP7" s="29"/>
-      <c r="CQ7" s="29"/>
-      <c r="CR7" s="29"/>
-      <c r="CS7" s="29"/>
-      <c r="CT7" s="29"/>
-      <c r="CU7" s="29"/>
-      <c r="CV7" s="29"/>
-      <c r="CW7" s="29"/>
-      <c r="CX7" s="29"/>
-      <c r="CY7" s="29"/>
-      <c r="CZ7" s="29"/>
-      <c r="DA7" s="29"/>
-      <c r="DB7" s="29"/>
-      <c r="DC7" s="29"/>
-      <c r="DD7" s="29"/>
-      <c r="DE7" s="29"/>
-      <c r="DF7" s="29"/>
-      <c r="DG7" s="29"/>
-      <c r="DH7" s="29"/>
-      <c r="DI7" s="29"/>
-      <c r="DJ7" s="29"/>
-      <c r="DK7" s="29"/>
-      <c r="DL7" s="29"/>
-      <c r="DM7" s="29"/>
-      <c r="DN7" s="29"/>
-      <c r="DO7" s="29"/>
-      <c r="DP7" s="29"/>
-      <c r="DQ7" s="29"/>
-      <c r="DR7" s="29"/>
-      <c r="DS7" s="29"/>
-      <c r="DT7" s="29"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="47"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="31"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="31"/>
+      <c r="O7" s="31"/>
+      <c r="P7" s="31"/>
+      <c r="Q7" s="31"/>
+      <c r="R7" s="31"/>
+      <c r="S7" s="31"/>
+      <c r="T7" s="31"/>
+      <c r="U7" s="31"/>
+      <c r="V7" s="66"/>
+      <c r="W7" s="66"/>
+      <c r="X7" s="31"/>
+      <c r="Y7" s="31"/>
+      <c r="Z7" s="31"/>
+      <c r="AA7" s="31"/>
+      <c r="AB7" s="31"/>
+      <c r="AC7" s="31"/>
+      <c r="AD7" s="31"/>
+      <c r="AE7" s="31"/>
+      <c r="AF7" s="31"/>
+      <c r="AG7" s="31"/>
+      <c r="AH7" s="31"/>
+      <c r="AI7" s="31"/>
+      <c r="AJ7" s="31"/>
+      <c r="AK7" s="31"/>
+      <c r="AL7" s="31"/>
+      <c r="AM7" s="31"/>
+      <c r="AN7" s="31"/>
+      <c r="AO7" s="31"/>
+      <c r="AP7" s="31"/>
+      <c r="AQ7" s="31"/>
+      <c r="AR7" s="31"/>
+      <c r="AS7" s="31"/>
+      <c r="AT7" s="31"/>
+      <c r="AU7" s="31"/>
+      <c r="AV7" s="31"/>
+      <c r="AW7" s="31"/>
+      <c r="AX7" s="31"/>
+      <c r="AY7" s="31"/>
+      <c r="AZ7" s="31"/>
+      <c r="BA7" s="31"/>
+      <c r="BB7" s="31"/>
+      <c r="BC7" s="31"/>
+      <c r="BD7" s="31"/>
+      <c r="BE7" s="31"/>
+      <c r="BF7" s="31"/>
+      <c r="BG7" s="31"/>
+      <c r="BH7" s="31"/>
+      <c r="BI7" s="31"/>
+      <c r="BJ7" s="31"/>
+      <c r="BK7" s="31"/>
+      <c r="BL7" s="31"/>
+      <c r="BM7" s="31"/>
+      <c r="BN7" s="31"/>
+      <c r="BO7" s="31"/>
+      <c r="BP7" s="31"/>
+      <c r="BQ7" s="31"/>
+      <c r="BR7" s="31"/>
+      <c r="BS7" s="31"/>
+      <c r="BT7" s="31"/>
+      <c r="BU7" s="31"/>
+      <c r="BV7" s="31"/>
+      <c r="BW7" s="31"/>
+      <c r="BX7" s="31"/>
+      <c r="BY7" s="31"/>
+      <c r="BZ7" s="31"/>
+      <c r="CA7" s="31"/>
+      <c r="CB7" s="31"/>
+      <c r="CC7" s="31"/>
+      <c r="CD7" s="31"/>
+      <c r="CE7" s="31"/>
+      <c r="CF7" s="31"/>
+      <c r="CG7" s="31"/>
+      <c r="CH7" s="31"/>
+      <c r="CI7" s="31"/>
+      <c r="CJ7" s="31"/>
+      <c r="CK7" s="31"/>
+      <c r="CL7" s="31"/>
+      <c r="CM7" s="31"/>
+      <c r="CN7" s="31"/>
+      <c r="CO7" s="31"/>
+      <c r="CP7" s="31"/>
+      <c r="CQ7" s="31"/>
+      <c r="CR7" s="31"/>
+      <c r="CS7" s="31"/>
+      <c r="CT7" s="31"/>
+      <c r="CU7" s="31"/>
+      <c r="CV7" s="31"/>
+      <c r="CW7" s="31"/>
+      <c r="CX7" s="31"/>
+      <c r="CY7" s="31"/>
+      <c r="CZ7" s="31"/>
+      <c r="DA7" s="31"/>
+      <c r="DB7" s="31"/>
+      <c r="DC7" s="31"/>
+      <c r="DD7" s="31"/>
+      <c r="DE7" s="31"/>
+      <c r="DF7" s="31"/>
+      <c r="DG7" s="31"/>
+      <c r="DH7" s="31"/>
+      <c r="DI7" s="31"/>
+      <c r="DJ7" s="31"/>
+      <c r="DK7" s="31"/>
+      <c r="DL7" s="31"/>
+      <c r="DM7" s="31"/>
+      <c r="DN7" s="31"/>
+      <c r="DO7" s="31"/>
+      <c r="DP7" s="31"/>
+      <c r="DQ7" s="31"/>
+      <c r="DR7" s="31"/>
+      <c r="DS7" s="31"/>
+      <c r="DT7" s="31"/>
     </row>
     <row r="8" spans="1:125" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="52"/>
-      <c r="C8" s="53">
+      <c r="B8" s="34"/>
+      <c r="C8" s="32">
         <f>SUM(C5:D7)</f>
         <v>75</v>
       </c>
-      <c r="D8" s="47"/>
+      <c r="D8" s="35"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="33">
-        <v>1</v>
-      </c>
-      <c r="G8" s="33">
+      <c r="F8" s="28">
+        <v>1</v>
+      </c>
+      <c r="G8" s="28">
         <v>2</v>
       </c>
-      <c r="H8" s="33">
+      <c r="H8" s="28">
         <v>3</v>
       </c>
-      <c r="I8" s="33">
+      <c r="I8" s="28">
         <v>4</v>
       </c>
-      <c r="J8" s="33">
+      <c r="J8" s="28">
         <v>5</v>
       </c>
-      <c r="K8" s="33">
+      <c r="K8" s="28">
         <v>6</v>
       </c>
-      <c r="L8" s="33">
+      <c r="L8" s="28">
         <v>7</v>
       </c>
-      <c r="M8" s="33">
+      <c r="M8" s="28">
         <v>8</v>
       </c>
-      <c r="N8" s="33">
+      <c r="N8" s="28">
         <v>9</v>
       </c>
-      <c r="O8" s="33">
+      <c r="O8" s="28">
         <v>10</v>
       </c>
-      <c r="P8" s="33">
+      <c r="P8" s="28">
         <v>11</v>
       </c>
-      <c r="Q8" s="33">
+      <c r="Q8" s="28">
         <v>12</v>
       </c>
-      <c r="R8" s="33">
+      <c r="R8" s="28">
         <v>13</v>
       </c>
-      <c r="S8" s="33">
+      <c r="S8" s="28">
         <v>14</v>
       </c>
-      <c r="T8" s="33">
+      <c r="T8" s="28">
         <v>15</v>
       </c>
-      <c r="U8" s="33">
+      <c r="U8" s="28">
         <v>16</v>
       </c>
-      <c r="V8" s="33">
+      <c r="V8" s="28">
         <v>17</v>
       </c>
-      <c r="W8" s="33">
+      <c r="W8" s="28">
         <v>18</v>
       </c>
-      <c r="X8" s="33">
+      <c r="X8" s="28">
         <v>19</v>
       </c>
-      <c r="Y8" s="33">
+      <c r="Y8" s="28">
         <v>20</v>
       </c>
-      <c r="Z8" s="33">
+      <c r="Z8" s="28">
         <v>21</v>
       </c>
-      <c r="AA8" s="33">
+      <c r="AA8" s="28">
         <v>22</v>
       </c>
-      <c r="AB8" s="33">
+      <c r="AB8" s="28">
         <v>23</v>
       </c>
-      <c r="AC8" s="33">
+      <c r="AC8" s="28">
         <v>24</v>
       </c>
-      <c r="AD8" s="33">
+      <c r="AD8" s="28">
         <v>25</v>
       </c>
-      <c r="AE8" s="33">
+      <c r="AE8" s="28">
         <v>26</v>
       </c>
-      <c r="AF8" s="33">
+      <c r="AF8" s="28">
         <v>27</v>
       </c>
-      <c r="AG8" s="33">
+      <c r="AG8" s="28">
         <v>28</v>
       </c>
-      <c r="AH8" s="33">
+      <c r="AH8" s="28">
         <v>29</v>
       </c>
-      <c r="AI8" s="33">
+      <c r="AI8" s="28">
         <v>30</v>
       </c>
-      <c r="AJ8" s="33">
+      <c r="AJ8" s="28">
         <v>31</v>
       </c>
-      <c r="AK8" s="33">
+      <c r="AK8" s="28">
         <v>32</v>
       </c>
-      <c r="AL8" s="33">
+      <c r="AL8" s="28">
         <v>33</v>
       </c>
-      <c r="AM8" s="33">
+      <c r="AM8" s="28">
         <v>34</v>
       </c>
-      <c r="AN8" s="33">
+      <c r="AN8" s="28">
         <v>35</v>
       </c>
-      <c r="AO8" s="33">
+      <c r="AO8" s="28">
         <v>36</v>
       </c>
-      <c r="AP8" s="33">
+      <c r="AP8" s="28">
         <v>37</v>
       </c>
-      <c r="AQ8" s="33">
+      <c r="AQ8" s="28">
         <v>38</v>
       </c>
-      <c r="AR8" s="33">
+      <c r="AR8" s="28">
         <v>39</v>
       </c>
-      <c r="AS8" s="33">
+      <c r="AS8" s="28">
         <v>40</v>
       </c>
-      <c r="AT8" s="33">
+      <c r="AT8" s="28">
         <v>41</v>
       </c>
-      <c r="AU8" s="33">
+      <c r="AU8" s="28">
         <v>42</v>
       </c>
-      <c r="AV8" s="33">
+      <c r="AV8" s="28">
         <v>43</v>
       </c>
-      <c r="AW8" s="33">
+      <c r="AW8" s="28">
         <v>44</v>
       </c>
-      <c r="AX8" s="33">
+      <c r="AX8" s="28">
         <v>45</v>
       </c>
-      <c r="AY8" s="33">
+      <c r="AY8" s="28">
         <v>46</v>
       </c>
-      <c r="AZ8" s="33">
+      <c r="AZ8" s="28">
         <v>47</v>
       </c>
-      <c r="BA8" s="33">
+      <c r="BA8" s="28">
         <v>48</v>
       </c>
-      <c r="BB8" s="33">
+      <c r="BB8" s="28">
         <v>49</v>
       </c>
-      <c r="BC8" s="33">
+      <c r="BC8" s="28">
         <v>50</v>
       </c>
-      <c r="BD8" s="33">
+      <c r="BD8" s="28">
         <v>51</v>
       </c>
-      <c r="BE8" s="33">
+      <c r="BE8" s="28">
         <v>52</v>
       </c>
-      <c r="BF8" s="33">
+      <c r="BF8" s="28">
         <v>53</v>
       </c>
-      <c r="BG8" s="33">
+      <c r="BG8" s="28">
         <v>54</v>
       </c>
-      <c r="BH8" s="33">
+      <c r="BH8" s="28">
         <v>55</v>
       </c>
-      <c r="BI8" s="33">
+      <c r="BI8" s="28">
         <v>56</v>
       </c>
-      <c r="BJ8" s="33">
+      <c r="BJ8" s="28">
         <v>57</v>
       </c>
-      <c r="BK8" s="33">
+      <c r="BK8" s="28">
         <v>58</v>
       </c>
-      <c r="BL8" s="33">
+      <c r="BL8" s="28">
         <v>59</v>
       </c>
-      <c r="BM8" s="33">
+      <c r="BM8" s="28">
         <v>60</v>
       </c>
-      <c r="BN8" s="33">
+      <c r="BN8" s="28">
         <v>61</v>
       </c>
-      <c r="BO8" s="33">
+      <c r="BO8" s="28">
         <v>62</v>
       </c>
-      <c r="BP8" s="33">
+      <c r="BP8" s="28">
         <v>63</v>
       </c>
-      <c r="BQ8" s="33">
+      <c r="BQ8" s="28">
         <v>64</v>
       </c>
-      <c r="BR8" s="33">
+      <c r="BR8" s="28">
         <v>65</v>
       </c>
-      <c r="BS8" s="33">
+      <c r="BS8" s="28">
         <v>66</v>
       </c>
-      <c r="BT8" s="33">
+      <c r="BT8" s="28">
         <v>67</v>
       </c>
-      <c r="BU8" s="33">
+      <c r="BU8" s="28">
         <v>68</v>
       </c>
-      <c r="BV8" s="33">
+      <c r="BV8" s="28">
         <v>69</v>
       </c>
-      <c r="BW8" s="33">
+      <c r="BW8" s="28">
         <v>70</v>
       </c>
-      <c r="BX8" s="33">
+      <c r="BX8" s="28">
         <v>71</v>
       </c>
-      <c r="BY8" s="33">
+      <c r="BY8" s="28">
         <v>72</v>
       </c>
-      <c r="BZ8" s="33">
+      <c r="BZ8" s="28">
         <v>73</v>
       </c>
-      <c r="CA8" s="33">
+      <c r="CA8" s="28">
         <v>74</v>
       </c>
-      <c r="CB8" s="33">
+      <c r="CB8" s="28">
         <v>75</v>
       </c>
-      <c r="CC8" s="33">
+      <c r="CC8" s="28">
         <v>76</v>
       </c>
-      <c r="CD8" s="33">
+      <c r="CD8" s="28">
         <v>77</v>
       </c>
-      <c r="CE8" s="33">
+      <c r="CE8" s="28">
         <v>78</v>
       </c>
-      <c r="CF8" s="33">
+      <c r="CF8" s="28">
         <v>79</v>
       </c>
-      <c r="CG8" s="33">
+      <c r="CG8" s="28">
         <v>80</v>
       </c>
-      <c r="CH8" s="33">
+      <c r="CH8" s="28">
         <v>81</v>
       </c>
-      <c r="CI8" s="33">
+      <c r="CI8" s="28">
         <v>82</v>
       </c>
-      <c r="CJ8" s="33">
+      <c r="CJ8" s="28">
         <v>83</v>
       </c>
-      <c r="CK8" s="33">
+      <c r="CK8" s="28">
         <v>84</v>
       </c>
-      <c r="CL8" s="33">
+      <c r="CL8" s="28">
         <v>85</v>
       </c>
-      <c r="CM8" s="33">
+      <c r="CM8" s="28">
         <v>86</v>
       </c>
-      <c r="CN8" s="33">
+      <c r="CN8" s="28">
         <v>87</v>
       </c>
-      <c r="CO8" s="33">
+      <c r="CO8" s="28">
         <v>88</v>
       </c>
-      <c r="CP8" s="33">
+      <c r="CP8" s="28">
         <v>89</v>
       </c>
-      <c r="CQ8" s="33">
+      <c r="CQ8" s="28">
         <v>90</v>
       </c>
-      <c r="CR8" s="33">
+      <c r="CR8" s="28">
         <v>91</v>
       </c>
-      <c r="CS8" s="33">
+      <c r="CS8" s="28">
         <v>92</v>
       </c>
-      <c r="CT8" s="33">
+      <c r="CT8" s="28">
         <v>93</v>
       </c>
-      <c r="CU8" s="33">
+      <c r="CU8" s="28">
         <v>94</v>
       </c>
-      <c r="CV8" s="33">
+      <c r="CV8" s="28">
         <v>95</v>
       </c>
-      <c r="CW8" s="33">
+      <c r="CW8" s="28">
         <v>96</v>
       </c>
-      <c r="CX8" s="33">
+      <c r="CX8" s="28">
         <v>97</v>
       </c>
-      <c r="CY8" s="33">
+      <c r="CY8" s="28">
         <v>98</v>
       </c>
-      <c r="CZ8" s="33">
+      <c r="CZ8" s="28">
         <v>99</v>
       </c>
-      <c r="DA8" s="33">
+      <c r="DA8" s="28">
         <v>100</v>
       </c>
-      <c r="DB8" s="33">
+      <c r="DB8" s="28">
         <v>101</v>
       </c>
-      <c r="DC8" s="33">
+      <c r="DC8" s="28">
         <v>102</v>
       </c>
-      <c r="DD8" s="33">
+      <c r="DD8" s="28">
         <v>103</v>
       </c>
-      <c r="DE8" s="33">
+      <c r="DE8" s="28">
         <v>104</v>
       </c>
-      <c r="DF8" s="33">
+      <c r="DF8" s="28">
         <v>105</v>
       </c>
-      <c r="DG8" s="33">
+      <c r="DG8" s="28">
         <v>106</v>
       </c>
-      <c r="DH8" s="33">
+      <c r="DH8" s="28">
         <v>107</v>
       </c>
-      <c r="DI8" s="33">
+      <c r="DI8" s="28">
         <v>108</v>
       </c>
-      <c r="DJ8" s="33">
+      <c r="DJ8" s="28">
         <v>109</v>
       </c>
-      <c r="DK8" s="33">
+      <c r="DK8" s="28">
         <v>110</v>
       </c>
-      <c r="DL8" s="33">
+      <c r="DL8" s="28">
         <v>111</v>
       </c>
-      <c r="DM8" s="33">
+      <c r="DM8" s="28">
         <v>112</v>
       </c>
-      <c r="DN8" s="33">
+      <c r="DN8" s="28">
         <v>113</v>
       </c>
-      <c r="DO8" s="33">
+      <c r="DO8" s="28">
         <v>114</v>
       </c>
-      <c r="DP8" s="33">
+      <c r="DP8" s="28">
         <v>115</v>
       </c>
-      <c r="DQ8" s="33">
+      <c r="DQ8" s="28">
         <v>116</v>
       </c>
-      <c r="DR8" s="33">
+      <c r="DR8" s="28">
         <v>117</v>
       </c>
-      <c r="DS8" s="33">
+      <c r="DS8" s="28">
         <v>118</v>
       </c>
-      <c r="DT8" s="33">
+      <c r="DT8" s="28">
         <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="44" t="s">
+      <c r="A9" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="54" t="s">
+      <c r="B9" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="55" t="s">
+      <c r="C9" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="54"/>
+      <c r="D9" s="37"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
-      <c r="K9" s="34"/>
-      <c r="L9" s="34"/>
-      <c r="M9" s="34"/>
-      <c r="N9" s="34"/>
-      <c r="O9" s="34"/>
-      <c r="P9" s="34"/>
-      <c r="Q9" s="34"/>
-      <c r="R9" s="34"/>
-      <c r="S9" s="34"/>
-      <c r="T9" s="34"/>
-      <c r="U9" s="34"/>
-      <c r="V9" s="34"/>
-      <c r="W9" s="34"/>
-      <c r="X9" s="34"/>
-      <c r="Y9" s="34"/>
-      <c r="Z9" s="34"/>
-      <c r="AA9" s="34"/>
-      <c r="AB9" s="34"/>
-      <c r="AC9" s="34"/>
-      <c r="AD9" s="34"/>
-      <c r="AE9" s="34"/>
-      <c r="AF9" s="34"/>
-      <c r="AG9" s="34"/>
-      <c r="AH9" s="34"/>
-      <c r="AI9" s="34"/>
-      <c r="AJ9" s="34"/>
-      <c r="AK9" s="34"/>
-      <c r="AL9" s="34"/>
-      <c r="AM9" s="34"/>
-      <c r="AN9" s="34"/>
-      <c r="AO9" s="34"/>
-      <c r="AP9" s="34"/>
-      <c r="AQ9" s="34"/>
-      <c r="AR9" s="34"/>
-      <c r="AS9" s="34"/>
-      <c r="AT9" s="34"/>
-      <c r="AU9" s="34"/>
-      <c r="AV9" s="34"/>
-      <c r="AW9" s="34"/>
-      <c r="AX9" s="34"/>
-      <c r="AY9" s="34"/>
-      <c r="AZ9" s="34"/>
-      <c r="BA9" s="34"/>
-      <c r="BB9" s="34"/>
-      <c r="BC9" s="34"/>
-      <c r="BD9" s="34"/>
-      <c r="BE9" s="34"/>
-      <c r="BF9" s="34"/>
-      <c r="BG9" s="34"/>
-      <c r="BH9" s="34"/>
-      <c r="BI9" s="34"/>
-      <c r="BJ9" s="34"/>
-      <c r="BK9" s="34"/>
-      <c r="BL9" s="34"/>
-      <c r="BM9" s="34"/>
-      <c r="BN9" s="34"/>
-      <c r="BO9" s="34"/>
-      <c r="BP9" s="34"/>
-      <c r="BQ9" s="34"/>
-      <c r="BR9" s="34"/>
-      <c r="BS9" s="34"/>
-      <c r="BT9" s="34"/>
-      <c r="BU9" s="34"/>
-      <c r="BV9" s="34"/>
-      <c r="BW9" s="34"/>
-      <c r="BX9" s="34"/>
-      <c r="BY9" s="34"/>
-      <c r="BZ9" s="34"/>
-      <c r="CA9" s="34"/>
-      <c r="CB9" s="34"/>
-      <c r="CC9" s="34"/>
-      <c r="CD9" s="34"/>
-      <c r="CE9" s="34"/>
-      <c r="CF9" s="34"/>
-      <c r="CG9" s="34"/>
-      <c r="CH9" s="34"/>
-      <c r="CI9" s="34"/>
-      <c r="CJ9" s="34"/>
-      <c r="CK9" s="34"/>
-      <c r="CL9" s="34"/>
-      <c r="CM9" s="34"/>
-      <c r="CN9" s="34"/>
-      <c r="CO9" s="34"/>
-      <c r="CP9" s="34"/>
-      <c r="CQ9" s="34"/>
-      <c r="CR9" s="34"/>
-      <c r="CS9" s="34"/>
-      <c r="CT9" s="34"/>
-      <c r="CU9" s="34"/>
-      <c r="CV9" s="34"/>
-      <c r="CW9" s="34"/>
-      <c r="CX9" s="34"/>
-      <c r="CY9" s="34"/>
-      <c r="CZ9" s="34"/>
-      <c r="DA9" s="34"/>
-      <c r="DB9" s="34"/>
-      <c r="DC9" s="34"/>
-      <c r="DD9" s="34"/>
-      <c r="DE9" s="34"/>
-      <c r="DF9" s="34"/>
-      <c r="DG9" s="34"/>
-      <c r="DH9" s="34"/>
-      <c r="DI9" s="34"/>
-      <c r="DJ9" s="34"/>
-      <c r="DK9" s="34"/>
-      <c r="DL9" s="34"/>
-      <c r="DM9" s="34"/>
-      <c r="DN9" s="34"/>
-      <c r="DO9" s="34"/>
-      <c r="DP9" s="34"/>
-      <c r="DQ9" s="34"/>
-      <c r="DR9" s="34"/>
-      <c r="DS9" s="34"/>
-      <c r="DT9" s="34"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="29"/>
+      <c r="M9" s="29"/>
+      <c r="N9" s="29"/>
+      <c r="O9" s="29"/>
+      <c r="P9" s="29"/>
+      <c r="Q9" s="29"/>
+      <c r="R9" s="29"/>
+      <c r="S9" s="29"/>
+      <c r="T9" s="29"/>
+      <c r="U9" s="29"/>
+      <c r="V9" s="29"/>
+      <c r="W9" s="29"/>
+      <c r="X9" s="29"/>
+      <c r="Y9" s="29"/>
+      <c r="Z9" s="29"/>
+      <c r="AA9" s="29"/>
+      <c r="AB9" s="29"/>
+      <c r="AC9" s="29"/>
+      <c r="AD9" s="29"/>
+      <c r="AE9" s="29"/>
+      <c r="AF9" s="29"/>
+      <c r="AG9" s="29"/>
+      <c r="AH9" s="29"/>
+      <c r="AI9" s="29"/>
+      <c r="AJ9" s="29"/>
+      <c r="AK9" s="29"/>
+      <c r="AL9" s="29"/>
+      <c r="AM9" s="29"/>
+      <c r="AN9" s="29"/>
+      <c r="AO9" s="29"/>
+      <c r="AP9" s="29"/>
+      <c r="AQ9" s="29"/>
+      <c r="AR9" s="29"/>
+      <c r="AS9" s="29"/>
+      <c r="AT9" s="29"/>
+      <c r="AU9" s="29"/>
+      <c r="AV9" s="29"/>
+      <c r="AW9" s="29"/>
+      <c r="AX9" s="29"/>
+      <c r="AY9" s="29"/>
+      <c r="AZ9" s="29"/>
+      <c r="BA9" s="29"/>
+      <c r="BB9" s="29"/>
+      <c r="BC9" s="29"/>
+      <c r="BD9" s="29"/>
+      <c r="BE9" s="29"/>
+      <c r="BF9" s="29"/>
+      <c r="BG9" s="29"/>
+      <c r="BH9" s="29"/>
+      <c r="BI9" s="29"/>
+      <c r="BJ9" s="29"/>
+      <c r="BK9" s="29"/>
+      <c r="BL9" s="29"/>
+      <c r="BM9" s="29"/>
+      <c r="BN9" s="29"/>
+      <c r="BO9" s="29"/>
+      <c r="BP9" s="29"/>
+      <c r="BQ9" s="29"/>
+      <c r="BR9" s="29"/>
+      <c r="BS9" s="29"/>
+      <c r="BT9" s="29"/>
+      <c r="BU9" s="29"/>
+      <c r="BV9" s="29"/>
+      <c r="BW9" s="29"/>
+      <c r="BX9" s="29"/>
+      <c r="BY9" s="29"/>
+      <c r="BZ9" s="29"/>
+      <c r="CA9" s="29"/>
+      <c r="CB9" s="29"/>
+      <c r="CC9" s="29"/>
+      <c r="CD9" s="29"/>
+      <c r="CE9" s="29"/>
+      <c r="CF9" s="29"/>
+      <c r="CG9" s="29"/>
+      <c r="CH9" s="29"/>
+      <c r="CI9" s="29"/>
+      <c r="CJ9" s="29"/>
+      <c r="CK9" s="29"/>
+      <c r="CL9" s="29"/>
+      <c r="CM9" s="29"/>
+      <c r="CN9" s="29"/>
+      <c r="CO9" s="29"/>
+      <c r="CP9" s="29"/>
+      <c r="CQ9" s="29"/>
+      <c r="CR9" s="29"/>
+      <c r="CS9" s="29"/>
+      <c r="CT9" s="29"/>
+      <c r="CU9" s="29"/>
+      <c r="CV9" s="29"/>
+      <c r="CW9" s="29"/>
+      <c r="CX9" s="29"/>
+      <c r="CY9" s="29"/>
+      <c r="CZ9" s="29"/>
+      <c r="DA9" s="29"/>
+      <c r="DB9" s="29"/>
+      <c r="DC9" s="29"/>
+      <c r="DD9" s="29"/>
+      <c r="DE9" s="29"/>
+      <c r="DF9" s="29"/>
+      <c r="DG9" s="29"/>
+      <c r="DH9" s="29"/>
+      <c r="DI9" s="29"/>
+      <c r="DJ9" s="29"/>
+      <c r="DK9" s="29"/>
+      <c r="DL9" s="29"/>
+      <c r="DM9" s="29"/>
+      <c r="DN9" s="29"/>
+      <c r="DO9" s="29"/>
+      <c r="DP9" s="29"/>
+      <c r="DQ9" s="29"/>
+      <c r="DR9" s="29"/>
+      <c r="DS9" s="29"/>
+      <c r="DT9" s="29"/>
     </row>
     <row r="10" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="44"/>
-      <c r="B10" s="54"/>
+      <c r="A10" s="36"/>
+      <c r="B10" s="37"/>
       <c r="C10" s="6"/>
       <c r="D10" s="4" t="s">
         <v>10</v>
@@ -4782,250 +4798,250 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E26" s="53"/>
-      <c r="F26" s="46"/>
-      <c r="G26" s="46"/>
-      <c r="H26" s="46"/>
-      <c r="I26" s="46"/>
-      <c r="J26" s="46"/>
-      <c r="K26" s="46"/>
-      <c r="L26" s="46"/>
-      <c r="M26" s="46"/>
-      <c r="N26" s="46"/>
-      <c r="O26" s="46"/>
-      <c r="P26" s="46"/>
-      <c r="Q26" s="46"/>
-      <c r="R26" s="46"/>
-      <c r="S26" s="46"/>
-      <c r="T26" s="46"/>
-      <c r="U26" s="46"/>
-      <c r="V26" s="46"/>
-      <c r="W26" s="46"/>
-      <c r="X26" s="46"/>
-      <c r="Y26" s="46"/>
-      <c r="Z26" s="46"/>
-      <c r="AA26" s="46"/>
-      <c r="AB26" s="46"/>
-      <c r="AC26" s="46"/>
-      <c r="AD26" s="46"/>
-      <c r="AE26" s="46"/>
-      <c r="AF26" s="46"/>
-      <c r="AG26" s="46"/>
-      <c r="AH26" s="46"/>
-      <c r="AI26" s="46"/>
-      <c r="AJ26" s="46"/>
-      <c r="AK26" s="46"/>
-      <c r="AL26" s="46"/>
-      <c r="AM26" s="46"/>
-      <c r="AN26" s="46"/>
-      <c r="AO26" s="46"/>
-      <c r="AP26" s="46"/>
-      <c r="AQ26" s="46"/>
-      <c r="AR26" s="46"/>
-      <c r="AS26" s="46"/>
-      <c r="AT26" s="46"/>
-      <c r="AU26" s="46"/>
-      <c r="AV26" s="46"/>
-      <c r="AW26" s="46"/>
-      <c r="AX26" s="46"/>
-      <c r="AY26" s="46"/>
-      <c r="AZ26" s="46"/>
-      <c r="BA26" s="46"/>
-      <c r="BB26" s="46"/>
-      <c r="BC26" s="46"/>
-      <c r="BD26" s="46"/>
-      <c r="BE26" s="46"/>
-      <c r="BF26" s="46"/>
-      <c r="BG26" s="46"/>
-      <c r="BH26" s="46"/>
-      <c r="BI26" s="46"/>
-      <c r="BJ26" s="46"/>
-      <c r="BK26" s="46"/>
-      <c r="BL26" s="46"/>
-      <c r="BM26" s="46"/>
-      <c r="BN26" s="46"/>
-      <c r="BO26" s="46"/>
-      <c r="BP26" s="46"/>
-      <c r="BQ26" s="46"/>
-      <c r="BR26" s="46"/>
-      <c r="BS26" s="46"/>
-      <c r="BT26" s="46"/>
-      <c r="BU26" s="46"/>
-      <c r="BV26" s="46"/>
-      <c r="BW26" s="46"/>
-      <c r="BX26" s="46"/>
-      <c r="BY26" s="46"/>
-      <c r="BZ26" s="46"/>
-      <c r="CA26" s="46"/>
-      <c r="CB26" s="46"/>
-      <c r="CC26" s="46"/>
-      <c r="CD26" s="46"/>
-      <c r="CE26" s="46"/>
-      <c r="CF26" s="46"/>
-      <c r="CG26" s="46"/>
-      <c r="CH26" s="46"/>
-      <c r="CI26" s="46"/>
-      <c r="CJ26" s="46"/>
-      <c r="CK26" s="46"/>
-      <c r="CL26" s="46"/>
-      <c r="CM26" s="46"/>
-      <c r="CN26" s="46"/>
-      <c r="CO26" s="46"/>
-      <c r="CP26" s="46"/>
-      <c r="CQ26" s="46"/>
-      <c r="CR26" s="46"/>
-      <c r="CS26" s="46"/>
-      <c r="CT26" s="46"/>
-      <c r="CU26" s="46"/>
-      <c r="CV26" s="46"/>
-      <c r="CW26" s="46"/>
-      <c r="CX26" s="46"/>
-      <c r="CY26" s="46"/>
-      <c r="CZ26" s="46"/>
-      <c r="DA26" s="46"/>
-      <c r="DB26" s="46"/>
-      <c r="DC26" s="46"/>
-      <c r="DD26" s="46"/>
-      <c r="DE26" s="46"/>
-      <c r="DF26" s="46"/>
-      <c r="DG26" s="46"/>
-      <c r="DH26" s="46"/>
-      <c r="DI26" s="46"/>
-      <c r="DJ26" s="46"/>
-      <c r="DK26" s="46"/>
-      <c r="DL26" s="46"/>
-      <c r="DM26" s="46"/>
-      <c r="DN26" s="46"/>
-      <c r="DO26" s="46"/>
-      <c r="DP26" s="46"/>
-      <c r="DQ26" s="46"/>
-      <c r="DR26" s="46"/>
-      <c r="DS26" s="46"/>
-      <c r="DT26" s="46"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="33"/>
+      <c r="L26" s="33"/>
+      <c r="M26" s="33"/>
+      <c r="N26" s="33"/>
+      <c r="O26" s="33"/>
+      <c r="P26" s="33"/>
+      <c r="Q26" s="33"/>
+      <c r="R26" s="33"/>
+      <c r="S26" s="33"/>
+      <c r="T26" s="33"/>
+      <c r="U26" s="33"/>
+      <c r="V26" s="33"/>
+      <c r="W26" s="33"/>
+      <c r="X26" s="33"/>
+      <c r="Y26" s="33"/>
+      <c r="Z26" s="33"/>
+      <c r="AA26" s="33"/>
+      <c r="AB26" s="33"/>
+      <c r="AC26" s="33"/>
+      <c r="AD26" s="33"/>
+      <c r="AE26" s="33"/>
+      <c r="AF26" s="33"/>
+      <c r="AG26" s="33"/>
+      <c r="AH26" s="33"/>
+      <c r="AI26" s="33"/>
+      <c r="AJ26" s="33"/>
+      <c r="AK26" s="33"/>
+      <c r="AL26" s="33"/>
+      <c r="AM26" s="33"/>
+      <c r="AN26" s="33"/>
+      <c r="AO26" s="33"/>
+      <c r="AP26" s="33"/>
+      <c r="AQ26" s="33"/>
+      <c r="AR26" s="33"/>
+      <c r="AS26" s="33"/>
+      <c r="AT26" s="33"/>
+      <c r="AU26" s="33"/>
+      <c r="AV26" s="33"/>
+      <c r="AW26" s="33"/>
+      <c r="AX26" s="33"/>
+      <c r="AY26" s="33"/>
+      <c r="AZ26" s="33"/>
+      <c r="BA26" s="33"/>
+      <c r="BB26" s="33"/>
+      <c r="BC26" s="33"/>
+      <c r="BD26" s="33"/>
+      <c r="BE26" s="33"/>
+      <c r="BF26" s="33"/>
+      <c r="BG26" s="33"/>
+      <c r="BH26" s="33"/>
+      <c r="BI26" s="33"/>
+      <c r="BJ26" s="33"/>
+      <c r="BK26" s="33"/>
+      <c r="BL26" s="33"/>
+      <c r="BM26" s="33"/>
+      <c r="BN26" s="33"/>
+      <c r="BO26" s="33"/>
+      <c r="BP26" s="33"/>
+      <c r="BQ26" s="33"/>
+      <c r="BR26" s="33"/>
+      <c r="BS26" s="33"/>
+      <c r="BT26" s="33"/>
+      <c r="BU26" s="33"/>
+      <c r="BV26" s="33"/>
+      <c r="BW26" s="33"/>
+      <c r="BX26" s="33"/>
+      <c r="BY26" s="33"/>
+      <c r="BZ26" s="33"/>
+      <c r="CA26" s="33"/>
+      <c r="CB26" s="33"/>
+      <c r="CC26" s="33"/>
+      <c r="CD26" s="33"/>
+      <c r="CE26" s="33"/>
+      <c r="CF26" s="33"/>
+      <c r="CG26" s="33"/>
+      <c r="CH26" s="33"/>
+      <c r="CI26" s="33"/>
+      <c r="CJ26" s="33"/>
+      <c r="CK26" s="33"/>
+      <c r="CL26" s="33"/>
+      <c r="CM26" s="33"/>
+      <c r="CN26" s="33"/>
+      <c r="CO26" s="33"/>
+      <c r="CP26" s="33"/>
+      <c r="CQ26" s="33"/>
+      <c r="CR26" s="33"/>
+      <c r="CS26" s="33"/>
+      <c r="CT26" s="33"/>
+      <c r="CU26" s="33"/>
+      <c r="CV26" s="33"/>
+      <c r="CW26" s="33"/>
+      <c r="CX26" s="33"/>
+      <c r="CY26" s="33"/>
+      <c r="CZ26" s="33"/>
+      <c r="DA26" s="33"/>
+      <c r="DB26" s="33"/>
+      <c r="DC26" s="33"/>
+      <c r="DD26" s="33"/>
+      <c r="DE26" s="33"/>
+      <c r="DF26" s="33"/>
+      <c r="DG26" s="33"/>
+      <c r="DH26" s="33"/>
+      <c r="DI26" s="33"/>
+      <c r="DJ26" s="33"/>
+      <c r="DK26" s="33"/>
+      <c r="DL26" s="33"/>
+      <c r="DM26" s="33"/>
+      <c r="DN26" s="33"/>
+      <c r="DO26" s="33"/>
+      <c r="DP26" s="33"/>
+      <c r="DQ26" s="33"/>
+      <c r="DR26" s="33"/>
+      <c r="DS26" s="33"/>
+      <c r="DT26" s="33"/>
     </row>
     <row r="27" spans="1:124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E27" s="1">
         <v>4</v>
       </c>
-      <c r="F27" s="30"/>
-      <c r="G27" s="30"/>
-      <c r="H27" s="30"/>
-      <c r="I27" s="30"/>
-      <c r="J27" s="30"/>
-      <c r="K27" s="30"/>
-      <c r="L27" s="30"/>
-      <c r="M27" s="30"/>
-      <c r="N27" s="30"/>
-      <c r="O27" s="30"/>
-      <c r="P27" s="30"/>
-      <c r="Q27" s="30"/>
-      <c r="R27" s="30"/>
-      <c r="S27" s="30"/>
-      <c r="T27" s="30"/>
-      <c r="U27" s="30"/>
-      <c r="V27" s="30"/>
-      <c r="W27" s="30"/>
-      <c r="X27" s="30"/>
-      <c r="Y27" s="30"/>
-      <c r="Z27" s="30"/>
-      <c r="AA27" s="30"/>
-      <c r="AB27" s="30"/>
-      <c r="AC27" s="30"/>
-      <c r="AD27" s="30"/>
-      <c r="AE27" s="30"/>
-      <c r="AF27" s="30"/>
-      <c r="AG27" s="30"/>
-      <c r="AH27" s="30"/>
-      <c r="AI27" s="30"/>
-      <c r="AJ27" s="30"/>
-      <c r="AK27" s="30"/>
-      <c r="AL27" s="30"/>
-      <c r="AM27" s="30"/>
-      <c r="AN27" s="30"/>
-      <c r="AO27" s="30"/>
-      <c r="AP27" s="30"/>
-      <c r="AQ27" s="30"/>
-      <c r="AR27" s="30"/>
-      <c r="AS27" s="30"/>
-      <c r="AT27" s="30"/>
-      <c r="AU27" s="30"/>
-      <c r="AV27" s="30"/>
-      <c r="AW27" s="30"/>
-      <c r="AX27" s="30"/>
-      <c r="AY27" s="30"/>
-      <c r="AZ27" s="30"/>
-      <c r="BA27" s="30"/>
-      <c r="BB27" s="30"/>
-      <c r="BC27" s="30"/>
-      <c r="BD27" s="30"/>
-      <c r="BE27" s="30"/>
-      <c r="BF27" s="30"/>
-      <c r="BG27" s="30"/>
-      <c r="BH27" s="30"/>
-      <c r="BI27" s="30"/>
-      <c r="BJ27" s="30"/>
-      <c r="BK27" s="30"/>
-      <c r="BL27" s="30"/>
-      <c r="BM27" s="30"/>
-      <c r="BN27" s="30"/>
-      <c r="BO27" s="30"/>
-      <c r="BP27" s="30"/>
-      <c r="BQ27" s="30"/>
-      <c r="BR27" s="30"/>
-      <c r="BS27" s="30"/>
-      <c r="BT27" s="30"/>
-      <c r="BU27" s="30"/>
-      <c r="BV27" s="30"/>
-      <c r="BW27" s="30"/>
-      <c r="BX27" s="30"/>
-      <c r="BY27" s="30"/>
-      <c r="BZ27" s="30"/>
-      <c r="CA27" s="30"/>
-      <c r="CB27" s="30"/>
-      <c r="CC27" s="30"/>
-      <c r="CD27" s="30"/>
-      <c r="CE27" s="31"/>
-      <c r="CF27" s="32"/>
-      <c r="CG27" s="32"/>
-      <c r="CH27" s="32"/>
-      <c r="CI27" s="32"/>
-      <c r="CJ27" s="32"/>
-      <c r="CK27" s="32"/>
-      <c r="CL27" s="32"/>
-      <c r="CM27" s="32"/>
-      <c r="CN27" s="32"/>
-      <c r="CO27" s="32"/>
-      <c r="CP27" s="32"/>
-      <c r="CQ27" s="32"/>
-      <c r="CR27" s="32"/>
-      <c r="CS27" s="32"/>
-      <c r="CT27" s="32"/>
-      <c r="CU27" s="32"/>
-      <c r="CV27" s="32"/>
-      <c r="CW27" s="32"/>
-      <c r="CX27" s="32"/>
-      <c r="CY27" s="32"/>
-      <c r="CZ27" s="32"/>
-      <c r="DA27" s="32"/>
-      <c r="DB27" s="32"/>
-      <c r="DC27" s="32"/>
-      <c r="DD27" s="32"/>
-      <c r="DE27" s="32"/>
-      <c r="DF27" s="32"/>
-      <c r="DG27" s="32"/>
-      <c r="DH27" s="32"/>
-      <c r="DI27" s="32"/>
-      <c r="DJ27" s="32"/>
-      <c r="DK27" s="32"/>
-      <c r="DL27" s="32"/>
-      <c r="DM27" s="32"/>
-      <c r="DN27" s="32"/>
-      <c r="DO27" s="32"/>
-      <c r="DP27" s="32"/>
-      <c r="DQ27" s="32"/>
-      <c r="DR27" s="32"/>
-      <c r="DS27" s="32"/>
-      <c r="DT27" s="32"/>
+      <c r="F27" s="53"/>
+      <c r="G27" s="53"/>
+      <c r="H27" s="53"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="53"/>
+      <c r="L27" s="53"/>
+      <c r="M27" s="53"/>
+      <c r="N27" s="53"/>
+      <c r="O27" s="53"/>
+      <c r="P27" s="53"/>
+      <c r="Q27" s="53"/>
+      <c r="R27" s="53"/>
+      <c r="S27" s="53"/>
+      <c r="T27" s="53"/>
+      <c r="U27" s="53"/>
+      <c r="V27" s="53"/>
+      <c r="W27" s="53"/>
+      <c r="X27" s="53"/>
+      <c r="Y27" s="53"/>
+      <c r="Z27" s="53"/>
+      <c r="AA27" s="53"/>
+      <c r="AB27" s="53"/>
+      <c r="AC27" s="53"/>
+      <c r="AD27" s="53"/>
+      <c r="AE27" s="53"/>
+      <c r="AF27" s="53"/>
+      <c r="AG27" s="53"/>
+      <c r="AH27" s="53"/>
+      <c r="AI27" s="53"/>
+      <c r="AJ27" s="53"/>
+      <c r="AK27" s="53"/>
+      <c r="AL27" s="53"/>
+      <c r="AM27" s="53"/>
+      <c r="AN27" s="53"/>
+      <c r="AO27" s="53"/>
+      <c r="AP27" s="53"/>
+      <c r="AQ27" s="53"/>
+      <c r="AR27" s="53"/>
+      <c r="AS27" s="53"/>
+      <c r="AT27" s="53"/>
+      <c r="AU27" s="53"/>
+      <c r="AV27" s="53"/>
+      <c r="AW27" s="53"/>
+      <c r="AX27" s="53"/>
+      <c r="AY27" s="53"/>
+      <c r="AZ27" s="53"/>
+      <c r="BA27" s="53"/>
+      <c r="BB27" s="53"/>
+      <c r="BC27" s="53"/>
+      <c r="BD27" s="53"/>
+      <c r="BE27" s="53"/>
+      <c r="BF27" s="53"/>
+      <c r="BG27" s="53"/>
+      <c r="BH27" s="53"/>
+      <c r="BI27" s="53"/>
+      <c r="BJ27" s="53"/>
+      <c r="BK27" s="53"/>
+      <c r="BL27" s="53"/>
+      <c r="BM27" s="53"/>
+      <c r="BN27" s="53"/>
+      <c r="BO27" s="53"/>
+      <c r="BP27" s="53"/>
+      <c r="BQ27" s="53"/>
+      <c r="BR27" s="53"/>
+      <c r="BS27" s="53"/>
+      <c r="BT27" s="53"/>
+      <c r="BU27" s="53"/>
+      <c r="BV27" s="53"/>
+      <c r="BW27" s="53"/>
+      <c r="BX27" s="53"/>
+      <c r="BY27" s="53"/>
+      <c r="BZ27" s="53"/>
+      <c r="CA27" s="53"/>
+      <c r="CB27" s="53"/>
+      <c r="CC27" s="53"/>
+      <c r="CD27" s="53"/>
+      <c r="CE27" s="54"/>
+      <c r="CF27" s="55"/>
+      <c r="CG27" s="55"/>
+      <c r="CH27" s="55"/>
+      <c r="CI27" s="55"/>
+      <c r="CJ27" s="55"/>
+      <c r="CK27" s="55"/>
+      <c r="CL27" s="55"/>
+      <c r="CM27" s="55"/>
+      <c r="CN27" s="55"/>
+      <c r="CO27" s="55"/>
+      <c r="CP27" s="55"/>
+      <c r="CQ27" s="55"/>
+      <c r="CR27" s="55"/>
+      <c r="CS27" s="55"/>
+      <c r="CT27" s="55"/>
+      <c r="CU27" s="55"/>
+      <c r="CV27" s="55"/>
+      <c r="CW27" s="55"/>
+      <c r="CX27" s="55"/>
+      <c r="CY27" s="55"/>
+      <c r="CZ27" s="55"/>
+      <c r="DA27" s="55"/>
+      <c r="DB27" s="55"/>
+      <c r="DC27" s="55"/>
+      <c r="DD27" s="55"/>
+      <c r="DE27" s="55"/>
+      <c r="DF27" s="55"/>
+      <c r="DG27" s="55"/>
+      <c r="DH27" s="55"/>
+      <c r="DI27" s="55"/>
+      <c r="DJ27" s="55"/>
+      <c r="DK27" s="55"/>
+      <c r="DL27" s="55"/>
+      <c r="DM27" s="55"/>
+      <c r="DN27" s="55"/>
+      <c r="DO27" s="55"/>
+      <c r="DP27" s="55"/>
+      <c r="DQ27" s="55"/>
+      <c r="DR27" s="55"/>
+      <c r="DS27" s="55"/>
+      <c r="DT27" s="55"/>
     </row>
     <row r="29" spans="1:124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E29" s="22">
@@ -5050,7 +5066,247 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="263">
+  <mergeCells count="264">
+    <mergeCell ref="V1:Y1"/>
+    <mergeCell ref="R1:U1"/>
+    <mergeCell ref="DQ2:DQ7"/>
+    <mergeCell ref="DR2:DR7"/>
+    <mergeCell ref="DS2:DS7"/>
+    <mergeCell ref="DT2:DT7"/>
+    <mergeCell ref="CX2:CX7"/>
+    <mergeCell ref="CY2:CY7"/>
+    <mergeCell ref="DA2:DA7"/>
+    <mergeCell ref="DB2:DB7"/>
+    <mergeCell ref="DC2:DC7"/>
+    <mergeCell ref="DD2:DD7"/>
+    <mergeCell ref="DE2:DE7"/>
+    <mergeCell ref="CZ2:CZ7"/>
+    <mergeCell ref="DN2:DN7"/>
+    <mergeCell ref="DO2:DO7"/>
+    <mergeCell ref="DP2:DP7"/>
+    <mergeCell ref="DG2:DG7"/>
+    <mergeCell ref="DH2:DH7"/>
+    <mergeCell ref="DI2:DI7"/>
+    <mergeCell ref="DJ2:DJ7"/>
+    <mergeCell ref="DK2:DK7"/>
+    <mergeCell ref="U2:U7"/>
+    <mergeCell ref="V2:V7"/>
+    <mergeCell ref="W2:W7"/>
+    <mergeCell ref="F27:S27"/>
+    <mergeCell ref="T27:AW27"/>
+    <mergeCell ref="AX27:CD27"/>
+    <mergeCell ref="CE27:DT27"/>
+    <mergeCell ref="DG8:DG9"/>
+    <mergeCell ref="DH8:DH9"/>
+    <mergeCell ref="DI8:DI9"/>
+    <mergeCell ref="DJ8:DJ9"/>
+    <mergeCell ref="DK8:DK9"/>
+    <mergeCell ref="DL8:DL9"/>
+    <mergeCell ref="DM8:DM9"/>
+    <mergeCell ref="DN8:DN9"/>
+    <mergeCell ref="DO8:DO9"/>
+    <mergeCell ref="DP8:DP9"/>
+    <mergeCell ref="DA8:DA9"/>
+    <mergeCell ref="DB8:DB9"/>
+    <mergeCell ref="DC8:DC9"/>
+    <mergeCell ref="DD8:DD9"/>
+    <mergeCell ref="DE8:DE9"/>
+    <mergeCell ref="CQ8:CQ9"/>
+    <mergeCell ref="CR8:CR9"/>
+    <mergeCell ref="CS8:CS9"/>
+    <mergeCell ref="BN8:BN9"/>
+    <mergeCell ref="CI8:CI9"/>
+    <mergeCell ref="CK8:CK9"/>
+    <mergeCell ref="CL8:CL9"/>
+    <mergeCell ref="BX8:BX9"/>
+    <mergeCell ref="BY8:BY9"/>
+    <mergeCell ref="DL2:DL7"/>
+    <mergeCell ref="DM2:DM7"/>
+    <mergeCell ref="DF2:DF7"/>
+    <mergeCell ref="BD2:BD7"/>
+    <mergeCell ref="BE2:BE7"/>
+    <mergeCell ref="BF2:BF7"/>
+    <mergeCell ref="BG2:BG7"/>
+    <mergeCell ref="BM2:BM7"/>
+    <mergeCell ref="BN2:BN7"/>
+    <mergeCell ref="BO2:BO7"/>
+    <mergeCell ref="BP2:BP7"/>
+    <mergeCell ref="CA2:CA7"/>
+    <mergeCell ref="BW2:BW7"/>
+    <mergeCell ref="BX2:BX7"/>
+    <mergeCell ref="BY2:BY7"/>
+    <mergeCell ref="BZ2:BZ7"/>
+    <mergeCell ref="BH2:BH7"/>
+    <mergeCell ref="BI2:BI7"/>
+    <mergeCell ref="BJ2:BJ7"/>
+    <mergeCell ref="BK2:BK7"/>
+    <mergeCell ref="X2:X7"/>
+    <mergeCell ref="AF2:AF7"/>
+    <mergeCell ref="AX2:AX7"/>
+    <mergeCell ref="AY2:AY7"/>
+    <mergeCell ref="AZ2:AZ7"/>
+    <mergeCell ref="BL2:BL7"/>
+    <mergeCell ref="BA2:BA7"/>
+    <mergeCell ref="BB2:BB7"/>
+    <mergeCell ref="BC2:BC7"/>
+    <mergeCell ref="AP2:AP7"/>
+    <mergeCell ref="AQ2:AQ7"/>
+    <mergeCell ref="AR2:AR7"/>
+    <mergeCell ref="AS2:AS7"/>
+    <mergeCell ref="AT2:AT7"/>
+    <mergeCell ref="AU2:AU7"/>
+    <mergeCell ref="AV2:AV7"/>
+    <mergeCell ref="AW2:AW7"/>
+    <mergeCell ref="CW2:CW7"/>
+    <mergeCell ref="CU2:CU7"/>
+    <mergeCell ref="CV2:CV7"/>
+    <mergeCell ref="CQ2:CQ7"/>
+    <mergeCell ref="CR2:CR7"/>
+    <mergeCell ref="CS2:CS7"/>
+    <mergeCell ref="CT2:CT7"/>
+    <mergeCell ref="CI2:CI7"/>
+    <mergeCell ref="CJ2:CJ7"/>
+    <mergeCell ref="CK2:CK7"/>
+    <mergeCell ref="CL2:CL7"/>
+    <mergeCell ref="CM2:CM7"/>
+    <mergeCell ref="CN2:CN7"/>
+    <mergeCell ref="CO2:CO7"/>
+    <mergeCell ref="CP2:CP7"/>
+    <mergeCell ref="N2:N7"/>
+    <mergeCell ref="O2:O7"/>
+    <mergeCell ref="P2:P7"/>
+    <mergeCell ref="Q2:Q7"/>
+    <mergeCell ref="R2:R7"/>
+    <mergeCell ref="S2:S7"/>
+    <mergeCell ref="T2:T7"/>
+    <mergeCell ref="CN8:CN9"/>
+    <mergeCell ref="Y2:Y7"/>
+    <mergeCell ref="Z2:Z7"/>
+    <mergeCell ref="AA2:AA7"/>
+    <mergeCell ref="AB2:AB7"/>
+    <mergeCell ref="AC2:AC7"/>
+    <mergeCell ref="AD2:AD7"/>
+    <mergeCell ref="AE2:AE7"/>
+    <mergeCell ref="AH2:AH7"/>
+    <mergeCell ref="AI2:AI7"/>
+    <mergeCell ref="AJ2:AJ7"/>
+    <mergeCell ref="AK2:AK7"/>
+    <mergeCell ref="AL2:AL7"/>
+    <mergeCell ref="AM2:AM7"/>
+    <mergeCell ref="AN2:AN7"/>
+    <mergeCell ref="AO2:AO7"/>
+    <mergeCell ref="AG2:AG7"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="F2:F7"/>
+    <mergeCell ref="G2:G7"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="I2:I7"/>
+    <mergeCell ref="J2:J7"/>
+    <mergeCell ref="K2:K7"/>
+    <mergeCell ref="L2:L7"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="M2:M7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="E26:DT26"/>
+    <mergeCell ref="DF8:DF9"/>
+    <mergeCell ref="DQ8:DQ9"/>
+    <mergeCell ref="DR8:DR9"/>
+    <mergeCell ref="DS8:DS9"/>
+    <mergeCell ref="DT8:DT9"/>
+    <mergeCell ref="CY8:CY9"/>
+    <mergeCell ref="CZ8:CZ9"/>
+    <mergeCell ref="CM8:CM9"/>
+    <mergeCell ref="CW8:CW9"/>
+    <mergeCell ref="CX8:CX9"/>
+    <mergeCell ref="BU8:BU9"/>
+    <mergeCell ref="BV8:BV9"/>
+    <mergeCell ref="BW8:BW9"/>
+    <mergeCell ref="BF8:BF9"/>
+    <mergeCell ref="BG8:BG9"/>
+    <mergeCell ref="CG8:CG9"/>
+    <mergeCell ref="CH8:CH9"/>
+    <mergeCell ref="AW8:AW9"/>
+    <mergeCell ref="AX8:AX9"/>
+    <mergeCell ref="AY8:AY9"/>
+    <mergeCell ref="AZ8:AZ9"/>
+    <mergeCell ref="BA8:BA9"/>
+    <mergeCell ref="BB8:BB9"/>
+    <mergeCell ref="CB8:CB9"/>
+    <mergeCell ref="CC8:CC9"/>
+    <mergeCell ref="CD8:CD9"/>
+    <mergeCell ref="CE8:CE9"/>
+    <mergeCell ref="CF8:CF9"/>
+    <mergeCell ref="CV8:CV9"/>
+    <mergeCell ref="BQ2:BQ7"/>
+    <mergeCell ref="BR2:BR7"/>
+    <mergeCell ref="BS2:BS7"/>
+    <mergeCell ref="BT2:BT7"/>
+    <mergeCell ref="BU2:BU7"/>
+    <mergeCell ref="BV2:BV7"/>
+    <mergeCell ref="CO8:CO9"/>
+    <mergeCell ref="CP8:CP9"/>
+    <mergeCell ref="CH2:CH7"/>
+    <mergeCell ref="CT8:CT9"/>
+    <mergeCell ref="CU8:CU9"/>
+    <mergeCell ref="CB2:CB7"/>
+    <mergeCell ref="CC2:CC7"/>
+    <mergeCell ref="CD2:CD7"/>
+    <mergeCell ref="CE2:CE7"/>
+    <mergeCell ref="CF2:CF7"/>
+    <mergeCell ref="CG2:CG7"/>
+    <mergeCell ref="CJ8:CJ9"/>
+    <mergeCell ref="BO8:BO9"/>
+    <mergeCell ref="BP8:BP9"/>
+    <mergeCell ref="BQ8:BQ9"/>
+    <mergeCell ref="BR8:BR9"/>
+    <mergeCell ref="BS8:BS9"/>
+    <mergeCell ref="BT8:BT9"/>
+    <mergeCell ref="BZ8:BZ9"/>
+    <mergeCell ref="CA8:CA9"/>
+    <mergeCell ref="BH8:BH9"/>
+    <mergeCell ref="BI8:BI9"/>
+    <mergeCell ref="BJ8:BJ9"/>
+    <mergeCell ref="BK8:BK9"/>
+    <mergeCell ref="BL8:BL9"/>
+    <mergeCell ref="BM8:BM9"/>
     <mergeCell ref="N1:Q1"/>
     <mergeCell ref="BC8:BC9"/>
     <mergeCell ref="BD8:BD9"/>
@@ -5075,245 +5331,6 @@
     <mergeCell ref="AM8:AM9"/>
     <mergeCell ref="V8:V9"/>
     <mergeCell ref="W8:W9"/>
-    <mergeCell ref="BO8:BO9"/>
-    <mergeCell ref="BP8:BP9"/>
-    <mergeCell ref="BQ8:BQ9"/>
-    <mergeCell ref="BR8:BR9"/>
-    <mergeCell ref="BS8:BS9"/>
-    <mergeCell ref="BT8:BT9"/>
-    <mergeCell ref="BZ8:BZ9"/>
-    <mergeCell ref="CA8:CA9"/>
-    <mergeCell ref="BH8:BH9"/>
-    <mergeCell ref="BI8:BI9"/>
-    <mergeCell ref="BJ8:BJ9"/>
-    <mergeCell ref="BK8:BK9"/>
-    <mergeCell ref="BL8:BL9"/>
-    <mergeCell ref="BM8:BM9"/>
-    <mergeCell ref="CB8:CB9"/>
-    <mergeCell ref="CC8:CC9"/>
-    <mergeCell ref="CD8:CD9"/>
-    <mergeCell ref="CE8:CE9"/>
-    <mergeCell ref="CF8:CF9"/>
-    <mergeCell ref="CV8:CV9"/>
-    <mergeCell ref="BQ2:BQ7"/>
-    <mergeCell ref="BR2:BR7"/>
-    <mergeCell ref="BS2:BS7"/>
-    <mergeCell ref="BT2:BT7"/>
-    <mergeCell ref="BU2:BU7"/>
-    <mergeCell ref="BV2:BV7"/>
-    <mergeCell ref="CO8:CO9"/>
-    <mergeCell ref="CP8:CP9"/>
-    <mergeCell ref="CH2:CH7"/>
-    <mergeCell ref="CT8:CT9"/>
-    <mergeCell ref="CU8:CU9"/>
-    <mergeCell ref="CB2:CB7"/>
-    <mergeCell ref="CC2:CC7"/>
-    <mergeCell ref="CD2:CD7"/>
-    <mergeCell ref="CE2:CE7"/>
-    <mergeCell ref="CF2:CF7"/>
-    <mergeCell ref="CG2:CG7"/>
-    <mergeCell ref="CJ8:CJ9"/>
-    <mergeCell ref="E26:DT26"/>
-    <mergeCell ref="DF8:DF9"/>
-    <mergeCell ref="DQ8:DQ9"/>
-    <mergeCell ref="DR8:DR9"/>
-    <mergeCell ref="DS8:DS9"/>
-    <mergeCell ref="DT8:DT9"/>
-    <mergeCell ref="CY8:CY9"/>
-    <mergeCell ref="CZ8:CZ9"/>
-    <mergeCell ref="CM8:CM9"/>
-    <mergeCell ref="CW8:CW9"/>
-    <mergeCell ref="CX8:CX9"/>
-    <mergeCell ref="BU8:BU9"/>
-    <mergeCell ref="BV8:BV9"/>
-    <mergeCell ref="BW8:BW9"/>
-    <mergeCell ref="BF8:BF9"/>
-    <mergeCell ref="BG8:BG9"/>
-    <mergeCell ref="CG8:CG9"/>
-    <mergeCell ref="CH8:CH9"/>
-    <mergeCell ref="AW8:AW9"/>
-    <mergeCell ref="AX8:AX9"/>
-    <mergeCell ref="AY8:AY9"/>
-    <mergeCell ref="AZ8:AZ9"/>
-    <mergeCell ref="BA8:BA9"/>
-    <mergeCell ref="BB8:BB9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="F2:F7"/>
-    <mergeCell ref="G2:G7"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="I2:I7"/>
-    <mergeCell ref="J2:J7"/>
-    <mergeCell ref="K2:K7"/>
-    <mergeCell ref="L2:L7"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="M2:M7"/>
-    <mergeCell ref="N2:N7"/>
-    <mergeCell ref="O2:O7"/>
-    <mergeCell ref="P2:P7"/>
-    <mergeCell ref="Q2:Q7"/>
-    <mergeCell ref="R2:R7"/>
-    <mergeCell ref="S2:S7"/>
-    <mergeCell ref="T2:T7"/>
-    <mergeCell ref="CN8:CN9"/>
-    <mergeCell ref="Y2:Y7"/>
-    <mergeCell ref="Z2:Z7"/>
-    <mergeCell ref="AA2:AA7"/>
-    <mergeCell ref="AB2:AB7"/>
-    <mergeCell ref="AC2:AC7"/>
-    <mergeCell ref="AD2:AD7"/>
-    <mergeCell ref="AE2:AE7"/>
-    <mergeCell ref="AH2:AH7"/>
-    <mergeCell ref="AI2:AI7"/>
-    <mergeCell ref="AJ2:AJ7"/>
-    <mergeCell ref="AK2:AK7"/>
-    <mergeCell ref="AL2:AL7"/>
-    <mergeCell ref="AM2:AM7"/>
-    <mergeCell ref="AN2:AN7"/>
-    <mergeCell ref="AO2:AO7"/>
-    <mergeCell ref="AG2:AG7"/>
-    <mergeCell ref="CW2:CW7"/>
-    <mergeCell ref="CU2:CU7"/>
-    <mergeCell ref="CV2:CV7"/>
-    <mergeCell ref="CQ2:CQ7"/>
-    <mergeCell ref="CR2:CR7"/>
-    <mergeCell ref="CS2:CS7"/>
-    <mergeCell ref="CT2:CT7"/>
-    <mergeCell ref="CI2:CI7"/>
-    <mergeCell ref="CJ2:CJ7"/>
-    <mergeCell ref="CK2:CK7"/>
-    <mergeCell ref="CL2:CL7"/>
-    <mergeCell ref="CM2:CM7"/>
-    <mergeCell ref="CN2:CN7"/>
-    <mergeCell ref="CO2:CO7"/>
-    <mergeCell ref="CP2:CP7"/>
-    <mergeCell ref="X2:X7"/>
-    <mergeCell ref="AF2:AF7"/>
-    <mergeCell ref="AX2:AX7"/>
-    <mergeCell ref="AY2:AY7"/>
-    <mergeCell ref="AZ2:AZ7"/>
-    <mergeCell ref="BL2:BL7"/>
-    <mergeCell ref="BA2:BA7"/>
-    <mergeCell ref="BB2:BB7"/>
-    <mergeCell ref="BC2:BC7"/>
-    <mergeCell ref="AP2:AP7"/>
-    <mergeCell ref="AQ2:AQ7"/>
-    <mergeCell ref="AR2:AR7"/>
-    <mergeCell ref="AS2:AS7"/>
-    <mergeCell ref="AT2:AT7"/>
-    <mergeCell ref="AU2:AU7"/>
-    <mergeCell ref="AV2:AV7"/>
-    <mergeCell ref="AW2:AW7"/>
-    <mergeCell ref="CK8:CK9"/>
-    <mergeCell ref="CL8:CL9"/>
-    <mergeCell ref="BX8:BX9"/>
-    <mergeCell ref="BY8:BY9"/>
-    <mergeCell ref="DL2:DL7"/>
-    <mergeCell ref="DM2:DM7"/>
-    <mergeCell ref="DF2:DF7"/>
-    <mergeCell ref="BD2:BD7"/>
-    <mergeCell ref="BE2:BE7"/>
-    <mergeCell ref="BF2:BF7"/>
-    <mergeCell ref="BG2:BG7"/>
-    <mergeCell ref="BM2:BM7"/>
-    <mergeCell ref="BN2:BN7"/>
-    <mergeCell ref="BO2:BO7"/>
-    <mergeCell ref="BP2:BP7"/>
-    <mergeCell ref="CA2:CA7"/>
-    <mergeCell ref="BW2:BW7"/>
-    <mergeCell ref="BX2:BX7"/>
-    <mergeCell ref="BY2:BY7"/>
-    <mergeCell ref="BZ2:BZ7"/>
-    <mergeCell ref="BH2:BH7"/>
-    <mergeCell ref="BI2:BI7"/>
-    <mergeCell ref="BJ2:BJ7"/>
-    <mergeCell ref="BK2:BK7"/>
-    <mergeCell ref="F27:S27"/>
-    <mergeCell ref="T27:AW27"/>
-    <mergeCell ref="AX27:CD27"/>
-    <mergeCell ref="CE27:DT27"/>
-    <mergeCell ref="DG8:DG9"/>
-    <mergeCell ref="DH8:DH9"/>
-    <mergeCell ref="DI8:DI9"/>
-    <mergeCell ref="DJ8:DJ9"/>
-    <mergeCell ref="DK8:DK9"/>
-    <mergeCell ref="DL8:DL9"/>
-    <mergeCell ref="DM8:DM9"/>
-    <mergeCell ref="DN8:DN9"/>
-    <mergeCell ref="DO8:DO9"/>
-    <mergeCell ref="DP8:DP9"/>
-    <mergeCell ref="DA8:DA9"/>
-    <mergeCell ref="DB8:DB9"/>
-    <mergeCell ref="DC8:DC9"/>
-    <mergeCell ref="DD8:DD9"/>
-    <mergeCell ref="DE8:DE9"/>
-    <mergeCell ref="CQ8:CQ9"/>
-    <mergeCell ref="CR8:CR9"/>
-    <mergeCell ref="CS8:CS9"/>
-    <mergeCell ref="BN8:BN9"/>
-    <mergeCell ref="CI8:CI9"/>
-    <mergeCell ref="R1:U1"/>
-    <mergeCell ref="DQ2:DQ7"/>
-    <mergeCell ref="DR2:DR7"/>
-    <mergeCell ref="DS2:DS7"/>
-    <mergeCell ref="DT2:DT7"/>
-    <mergeCell ref="CX2:CX7"/>
-    <mergeCell ref="CY2:CY7"/>
-    <mergeCell ref="DA2:DA7"/>
-    <mergeCell ref="DB2:DB7"/>
-    <mergeCell ref="DC2:DC7"/>
-    <mergeCell ref="DD2:DD7"/>
-    <mergeCell ref="DE2:DE7"/>
-    <mergeCell ref="CZ2:CZ7"/>
-    <mergeCell ref="DN2:DN7"/>
-    <mergeCell ref="DO2:DO7"/>
-    <mergeCell ref="DP2:DP7"/>
-    <mergeCell ref="DG2:DG7"/>
-    <mergeCell ref="DH2:DH7"/>
-    <mergeCell ref="DI2:DI7"/>
-    <mergeCell ref="DJ2:DJ7"/>
-    <mergeCell ref="DK2:DK7"/>
-    <mergeCell ref="U2:U7"/>
-    <mergeCell ref="V2:V7"/>
-    <mergeCell ref="W2:W7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -5346,7 +5363,7 @@
       <c r="H2" s="57"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="36" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="59" t="s">
@@ -5370,7 +5387,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="44"/>
+      <c r="A4" s="36"/>
       <c r="B4" s="61"/>
       <c r="C4" s="62"/>
       <c r="D4" s="64"/>

--- a/Journals/Angular ჟურნალი.xlsx
+++ b/Journals/Angular ჟურნალი.xlsx
@@ -164,7 +164,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -258,6 +258,12 @@
     <font>
       <b/>
       <sz val="9"/>
+      <color theme="1"/>
+      <name val="Sylfaen"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Sylfaen"/>
       <family val="1"/>
@@ -488,7 +494,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -551,38 +557,32 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="2" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -612,7 +612,16 @@
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -626,14 +635,17 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -662,10 +674,10 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="16" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="16" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
@@ -902,12 +914,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="41"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="39"/>
       <c r="F1" s="25">
         <v>8</v>
       </c>
@@ -938,10 +950,10 @@
       <c r="W1" s="26"/>
       <c r="X1" s="26"/>
       <c r="Y1" s="27"/>
-      <c r="Z1" s="23"/>
-      <c r="AA1" s="23"/>
-      <c r="AB1" s="23"/>
-      <c r="AC1" s="23"/>
+      <c r="Z1" s="25"/>
+      <c r="AA1" s="26"/>
+      <c r="AB1" s="26"/>
+      <c r="AC1" s="27"/>
       <c r="AD1" s="23"/>
       <c r="AE1" s="23"/>
       <c r="AF1" s="23"/>
@@ -1043,1325 +1055,1333 @@
       </c>
     </row>
     <row r="2" spans="1:125" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="42"/>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="45" t="s">
+      <c r="A2" s="40"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="30">
+      <c r="F2" s="28">
         <v>46276</v>
       </c>
-      <c r="G2" s="30">
+      <c r="G2" s="28">
         <v>46276</v>
       </c>
-      <c r="H2" s="30">
+      <c r="H2" s="28">
         <v>46276</v>
       </c>
-      <c r="I2" s="30">
+      <c r="I2" s="28">
         <v>46276</v>
       </c>
-      <c r="J2" s="30">
+      <c r="J2" s="28">
         <v>46283</v>
       </c>
-      <c r="K2" s="30">
+      <c r="K2" s="28">
         <v>46283</v>
       </c>
-      <c r="L2" s="30">
+      <c r="L2" s="28">
         <v>46283</v>
       </c>
-      <c r="M2" s="30">
+      <c r="M2" s="28">
         <v>46283</v>
       </c>
-      <c r="N2" s="30">
+      <c r="N2" s="28">
         <v>46290</v>
       </c>
-      <c r="O2" s="30">
+      <c r="O2" s="28">
         <v>46290</v>
       </c>
-      <c r="P2" s="30">
+      <c r="P2" s="28">
         <v>46290</v>
       </c>
-      <c r="Q2" s="30">
+      <c r="Q2" s="28">
         <v>46290</v>
       </c>
-      <c r="R2" s="30">
+      <c r="R2" s="28">
         <v>46297</v>
       </c>
-      <c r="S2" s="30">
+      <c r="S2" s="28">
         <v>46297</v>
       </c>
-      <c r="T2" s="30">
+      <c r="T2" s="28">
         <v>46297</v>
       </c>
-      <c r="U2" s="30">
+      <c r="U2" s="28">
         <v>46297</v>
       </c>
-      <c r="V2" s="65">
+      <c r="V2" s="30">
         <v>46304</v>
       </c>
-      <c r="W2" s="65">
+      <c r="W2" s="30">
         <v>46304</v>
       </c>
-      <c r="X2" s="30">
+      <c r="X2" s="28">
         <v>46304</v>
       </c>
-      <c r="Y2" s="30">
+      <c r="Y2" s="28">
         <v>46304</v>
       </c>
-      <c r="Z2" s="30"/>
-      <c r="AA2" s="30"/>
-      <c r="AB2" s="30"/>
-      <c r="AC2" s="30"/>
-      <c r="AD2" s="30"/>
-      <c r="AE2" s="30"/>
-      <c r="AF2" s="30"/>
-      <c r="AG2" s="30"/>
-      <c r="AH2" s="30"/>
-      <c r="AI2" s="30"/>
-      <c r="AJ2" s="30"/>
-      <c r="AK2" s="30"/>
-      <c r="AL2" s="30"/>
-      <c r="AM2" s="30"/>
-      <c r="AN2" s="30"/>
-      <c r="AO2" s="30"/>
-      <c r="AP2" s="30"/>
-      <c r="AQ2" s="30"/>
-      <c r="AR2" s="30"/>
-      <c r="AS2" s="30"/>
-      <c r="AT2" s="30"/>
-      <c r="AU2" s="30"/>
-      <c r="AV2" s="30"/>
-      <c r="AW2" s="30"/>
-      <c r="AX2" s="30"/>
-      <c r="AY2" s="30"/>
-      <c r="AZ2" s="30"/>
-      <c r="BA2" s="30"/>
-      <c r="BB2" s="30"/>
-      <c r="BC2" s="30"/>
-      <c r="BD2" s="30"/>
-      <c r="BE2" s="30"/>
-      <c r="BF2" s="30"/>
-      <c r="BG2" s="30"/>
-      <c r="BH2" s="30"/>
-      <c r="BI2" s="30"/>
-      <c r="BJ2" s="30"/>
-      <c r="BK2" s="30"/>
-      <c r="BL2" s="30"/>
-      <c r="BM2" s="30"/>
-      <c r="BN2" s="30"/>
-      <c r="BO2" s="30"/>
-      <c r="BP2" s="30"/>
-      <c r="BQ2" s="30"/>
-      <c r="BR2" s="30"/>
-      <c r="BS2" s="30"/>
-      <c r="BT2" s="30"/>
-      <c r="BU2" s="30"/>
-      <c r="BV2" s="30"/>
-      <c r="BW2" s="30"/>
-      <c r="BX2" s="30"/>
-      <c r="BY2" s="30"/>
-      <c r="BZ2" s="30"/>
-      <c r="CA2" s="30"/>
-      <c r="CB2" s="30"/>
-      <c r="CC2" s="30"/>
-      <c r="CD2" s="30"/>
-      <c r="CE2" s="30"/>
-      <c r="CF2" s="30"/>
-      <c r="CG2" s="30"/>
-      <c r="CH2" s="30"/>
-      <c r="CI2" s="30"/>
-      <c r="CJ2" s="30"/>
-      <c r="CK2" s="30"/>
-      <c r="CL2" s="30"/>
-      <c r="CM2" s="30"/>
-      <c r="CN2" s="30"/>
-      <c r="CO2" s="30"/>
-      <c r="CP2" s="30"/>
-      <c r="CQ2" s="30"/>
-      <c r="CR2" s="30"/>
-      <c r="CS2" s="30"/>
-      <c r="CT2" s="30"/>
-      <c r="CU2" s="30"/>
-      <c r="CV2" s="30"/>
-      <c r="CW2" s="30"/>
-      <c r="CX2" s="30"/>
-      <c r="CY2" s="30"/>
-      <c r="CZ2" s="30"/>
-      <c r="DA2" s="30"/>
-      <c r="DB2" s="30"/>
-      <c r="DC2" s="30"/>
-      <c r="DD2" s="30"/>
-      <c r="DE2" s="30"/>
-      <c r="DF2" s="30"/>
-      <c r="DG2" s="30"/>
-      <c r="DH2" s="30"/>
-      <c r="DI2" s="30"/>
-      <c r="DJ2" s="30"/>
-      <c r="DK2" s="30"/>
-      <c r="DL2" s="30"/>
-      <c r="DM2" s="30"/>
-      <c r="DN2" s="30"/>
-      <c r="DO2" s="30"/>
-      <c r="DP2" s="30"/>
-      <c r="DQ2" s="30"/>
-      <c r="DR2" s="30"/>
-      <c r="DS2" s="30"/>
-      <c r="DT2" s="30"/>
+      <c r="Z2" s="67">
+        <v>46311</v>
+      </c>
+      <c r="AA2" s="67">
+        <v>46311</v>
+      </c>
+      <c r="AB2" s="67">
+        <v>46311</v>
+      </c>
+      <c r="AC2" s="67">
+        <v>46311</v>
+      </c>
+      <c r="AD2" s="28"/>
+      <c r="AE2" s="28"/>
+      <c r="AF2" s="28"/>
+      <c r="AG2" s="28"/>
+      <c r="AH2" s="28"/>
+      <c r="AI2" s="28"/>
+      <c r="AJ2" s="28"/>
+      <c r="AK2" s="28"/>
+      <c r="AL2" s="28"/>
+      <c r="AM2" s="28"/>
+      <c r="AN2" s="28"/>
+      <c r="AO2" s="28"/>
+      <c r="AP2" s="28"/>
+      <c r="AQ2" s="28"/>
+      <c r="AR2" s="28"/>
+      <c r="AS2" s="28"/>
+      <c r="AT2" s="28"/>
+      <c r="AU2" s="28"/>
+      <c r="AV2" s="28"/>
+      <c r="AW2" s="28"/>
+      <c r="AX2" s="28"/>
+      <c r="AY2" s="28"/>
+      <c r="AZ2" s="28"/>
+      <c r="BA2" s="28"/>
+      <c r="BB2" s="28"/>
+      <c r="BC2" s="28"/>
+      <c r="BD2" s="28"/>
+      <c r="BE2" s="28"/>
+      <c r="BF2" s="28"/>
+      <c r="BG2" s="28"/>
+      <c r="BH2" s="28"/>
+      <c r="BI2" s="28"/>
+      <c r="BJ2" s="28"/>
+      <c r="BK2" s="28"/>
+      <c r="BL2" s="28"/>
+      <c r="BM2" s="28"/>
+      <c r="BN2" s="28"/>
+      <c r="BO2" s="28"/>
+      <c r="BP2" s="28"/>
+      <c r="BQ2" s="28"/>
+      <c r="BR2" s="28"/>
+      <c r="BS2" s="28"/>
+      <c r="BT2" s="28"/>
+      <c r="BU2" s="28"/>
+      <c r="BV2" s="28"/>
+      <c r="BW2" s="28"/>
+      <c r="BX2" s="28"/>
+      <c r="BY2" s="28"/>
+      <c r="BZ2" s="28"/>
+      <c r="CA2" s="28"/>
+      <c r="CB2" s="28"/>
+      <c r="CC2" s="28"/>
+      <c r="CD2" s="28"/>
+      <c r="CE2" s="28"/>
+      <c r="CF2" s="28"/>
+      <c r="CG2" s="28"/>
+      <c r="CH2" s="28"/>
+      <c r="CI2" s="28"/>
+      <c r="CJ2" s="28"/>
+      <c r="CK2" s="28"/>
+      <c r="CL2" s="28"/>
+      <c r="CM2" s="28"/>
+      <c r="CN2" s="28"/>
+      <c r="CO2" s="28"/>
+      <c r="CP2" s="28"/>
+      <c r="CQ2" s="28"/>
+      <c r="CR2" s="28"/>
+      <c r="CS2" s="28"/>
+      <c r="CT2" s="28"/>
+      <c r="CU2" s="28"/>
+      <c r="CV2" s="28"/>
+      <c r="CW2" s="28"/>
+      <c r="CX2" s="28"/>
+      <c r="CY2" s="28"/>
+      <c r="CZ2" s="28"/>
+      <c r="DA2" s="28"/>
+      <c r="DB2" s="28"/>
+      <c r="DC2" s="28"/>
+      <c r="DD2" s="28"/>
+      <c r="DE2" s="28"/>
+      <c r="DF2" s="28"/>
+      <c r="DG2" s="28"/>
+      <c r="DH2" s="28"/>
+      <c r="DI2" s="28"/>
+      <c r="DJ2" s="28"/>
+      <c r="DK2" s="28"/>
+      <c r="DL2" s="28"/>
+      <c r="DM2" s="28"/>
+      <c r="DN2" s="28"/>
+      <c r="DO2" s="28"/>
+      <c r="DP2" s="28"/>
+      <c r="DQ2" s="28"/>
+      <c r="DR2" s="28"/>
+      <c r="DS2" s="28"/>
+      <c r="DT2" s="28"/>
     </row>
     <row r="3" spans="1:125" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30"/>
-      <c r="N3" s="30"/>
-      <c r="O3" s="30"/>
-      <c r="P3" s="30"/>
-      <c r="Q3" s="30"/>
-      <c r="R3" s="30"/>
-      <c r="S3" s="30"/>
-      <c r="T3" s="30"/>
-      <c r="U3" s="30"/>
-      <c r="V3" s="65"/>
-      <c r="W3" s="65"/>
-      <c r="X3" s="30"/>
-      <c r="Y3" s="30"/>
-      <c r="Z3" s="30"/>
-      <c r="AA3" s="30"/>
-      <c r="AB3" s="30"/>
-      <c r="AC3" s="30"/>
-      <c r="AD3" s="30"/>
-      <c r="AE3" s="30"/>
-      <c r="AF3" s="30"/>
-      <c r="AG3" s="30"/>
-      <c r="AH3" s="30"/>
-      <c r="AI3" s="30"/>
-      <c r="AJ3" s="30"/>
-      <c r="AK3" s="30"/>
-      <c r="AL3" s="30"/>
-      <c r="AM3" s="30"/>
-      <c r="AN3" s="30"/>
-      <c r="AO3" s="30"/>
-      <c r="AP3" s="30"/>
-      <c r="AQ3" s="30"/>
-      <c r="AR3" s="30"/>
-      <c r="AS3" s="30"/>
-      <c r="AT3" s="30"/>
-      <c r="AU3" s="30"/>
-      <c r="AV3" s="30"/>
-      <c r="AW3" s="30"/>
-      <c r="AX3" s="30"/>
-      <c r="AY3" s="30"/>
-      <c r="AZ3" s="30"/>
-      <c r="BA3" s="30"/>
-      <c r="BB3" s="30"/>
-      <c r="BC3" s="30"/>
-      <c r="BD3" s="30"/>
-      <c r="BE3" s="30"/>
-      <c r="BF3" s="30"/>
-      <c r="BG3" s="30"/>
-      <c r="BH3" s="30"/>
-      <c r="BI3" s="30"/>
-      <c r="BJ3" s="30"/>
-      <c r="BK3" s="30"/>
-      <c r="BL3" s="30"/>
-      <c r="BM3" s="30"/>
-      <c r="BN3" s="30"/>
-      <c r="BO3" s="30"/>
-      <c r="BP3" s="30"/>
-      <c r="BQ3" s="30"/>
-      <c r="BR3" s="30"/>
-      <c r="BS3" s="30"/>
-      <c r="BT3" s="30"/>
-      <c r="BU3" s="30"/>
-      <c r="BV3" s="30"/>
-      <c r="BW3" s="30"/>
-      <c r="BX3" s="30"/>
-      <c r="BY3" s="30"/>
-      <c r="BZ3" s="30"/>
-      <c r="CA3" s="30"/>
-      <c r="CB3" s="30"/>
-      <c r="CC3" s="30"/>
-      <c r="CD3" s="30"/>
-      <c r="CE3" s="30"/>
-      <c r="CF3" s="30"/>
-      <c r="CG3" s="30"/>
-      <c r="CH3" s="30"/>
-      <c r="CI3" s="30"/>
-      <c r="CJ3" s="30"/>
-      <c r="CK3" s="30"/>
-      <c r="CL3" s="30"/>
-      <c r="CM3" s="30"/>
-      <c r="CN3" s="30"/>
-      <c r="CO3" s="30"/>
-      <c r="CP3" s="30"/>
-      <c r="CQ3" s="30"/>
-      <c r="CR3" s="30"/>
-      <c r="CS3" s="30"/>
-      <c r="CT3" s="30"/>
-      <c r="CU3" s="30"/>
-      <c r="CV3" s="30"/>
-      <c r="CW3" s="30"/>
-      <c r="CX3" s="30"/>
-      <c r="CY3" s="30"/>
-      <c r="CZ3" s="30"/>
-      <c r="DA3" s="30"/>
-      <c r="DB3" s="30"/>
-      <c r="DC3" s="30"/>
-      <c r="DD3" s="30"/>
-      <c r="DE3" s="30"/>
-      <c r="DF3" s="30"/>
-      <c r="DG3" s="30"/>
-      <c r="DH3" s="30"/>
-      <c r="DI3" s="30"/>
-      <c r="DJ3" s="30"/>
-      <c r="DK3" s="30"/>
-      <c r="DL3" s="30"/>
-      <c r="DM3" s="30"/>
-      <c r="DN3" s="30"/>
-      <c r="DO3" s="30"/>
-      <c r="DP3" s="30"/>
-      <c r="DQ3" s="30"/>
-      <c r="DR3" s="30"/>
-      <c r="DS3" s="30"/>
-      <c r="DT3" s="30"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="28"/>
+      <c r="O3" s="28"/>
+      <c r="P3" s="28"/>
+      <c r="Q3" s="28"/>
+      <c r="R3" s="28"/>
+      <c r="S3" s="28"/>
+      <c r="T3" s="28"/>
+      <c r="U3" s="28"/>
+      <c r="V3" s="30"/>
+      <c r="W3" s="30"/>
+      <c r="X3" s="28"/>
+      <c r="Y3" s="28"/>
+      <c r="Z3" s="67"/>
+      <c r="AA3" s="67"/>
+      <c r="AB3" s="67"/>
+      <c r="AC3" s="67"/>
+      <c r="AD3" s="28"/>
+      <c r="AE3" s="28"/>
+      <c r="AF3" s="28"/>
+      <c r="AG3" s="28"/>
+      <c r="AH3" s="28"/>
+      <c r="AI3" s="28"/>
+      <c r="AJ3" s="28"/>
+      <c r="AK3" s="28"/>
+      <c r="AL3" s="28"/>
+      <c r="AM3" s="28"/>
+      <c r="AN3" s="28"/>
+      <c r="AO3" s="28"/>
+      <c r="AP3" s="28"/>
+      <c r="AQ3" s="28"/>
+      <c r="AR3" s="28"/>
+      <c r="AS3" s="28"/>
+      <c r="AT3" s="28"/>
+      <c r="AU3" s="28"/>
+      <c r="AV3" s="28"/>
+      <c r="AW3" s="28"/>
+      <c r="AX3" s="28"/>
+      <c r="AY3" s="28"/>
+      <c r="AZ3" s="28"/>
+      <c r="BA3" s="28"/>
+      <c r="BB3" s="28"/>
+      <c r="BC3" s="28"/>
+      <c r="BD3" s="28"/>
+      <c r="BE3" s="28"/>
+      <c r="BF3" s="28"/>
+      <c r="BG3" s="28"/>
+      <c r="BH3" s="28"/>
+      <c r="BI3" s="28"/>
+      <c r="BJ3" s="28"/>
+      <c r="BK3" s="28"/>
+      <c r="BL3" s="28"/>
+      <c r="BM3" s="28"/>
+      <c r="BN3" s="28"/>
+      <c r="BO3" s="28"/>
+      <c r="BP3" s="28"/>
+      <c r="BQ3" s="28"/>
+      <c r="BR3" s="28"/>
+      <c r="BS3" s="28"/>
+      <c r="BT3" s="28"/>
+      <c r="BU3" s="28"/>
+      <c r="BV3" s="28"/>
+      <c r="BW3" s="28"/>
+      <c r="BX3" s="28"/>
+      <c r="BY3" s="28"/>
+      <c r="BZ3" s="28"/>
+      <c r="CA3" s="28"/>
+      <c r="CB3" s="28"/>
+      <c r="CC3" s="28"/>
+      <c r="CD3" s="28"/>
+      <c r="CE3" s="28"/>
+      <c r="CF3" s="28"/>
+      <c r="CG3" s="28"/>
+      <c r="CH3" s="28"/>
+      <c r="CI3" s="28"/>
+      <c r="CJ3" s="28"/>
+      <c r="CK3" s="28"/>
+      <c r="CL3" s="28"/>
+      <c r="CM3" s="28"/>
+      <c r="CN3" s="28"/>
+      <c r="CO3" s="28"/>
+      <c r="CP3" s="28"/>
+      <c r="CQ3" s="28"/>
+      <c r="CR3" s="28"/>
+      <c r="CS3" s="28"/>
+      <c r="CT3" s="28"/>
+      <c r="CU3" s="28"/>
+      <c r="CV3" s="28"/>
+      <c r="CW3" s="28"/>
+      <c r="CX3" s="28"/>
+      <c r="CY3" s="28"/>
+      <c r="CZ3" s="28"/>
+      <c r="DA3" s="28"/>
+      <c r="DB3" s="28"/>
+      <c r="DC3" s="28"/>
+      <c r="DD3" s="28"/>
+      <c r="DE3" s="28"/>
+      <c r="DF3" s="28"/>
+      <c r="DG3" s="28"/>
+      <c r="DH3" s="28"/>
+      <c r="DI3" s="28"/>
+      <c r="DJ3" s="28"/>
+      <c r="DK3" s="28"/>
+      <c r="DL3" s="28"/>
+      <c r="DM3" s="28"/>
+      <c r="DN3" s="28"/>
+      <c r="DO3" s="28"/>
+      <c r="DP3" s="28"/>
+      <c r="DQ3" s="28"/>
+      <c r="DR3" s="28"/>
+      <c r="DS3" s="28"/>
+      <c r="DT3" s="28"/>
     </row>
     <row r="4" spans="1:125" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="48"/>
-      <c r="C4" s="33" t="s">
+      <c r="A4" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="47"/>
+      <c r="C4" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="35"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="30"/>
-      <c r="O4" s="30"/>
-      <c r="P4" s="30"/>
-      <c r="Q4" s="30"/>
-      <c r="R4" s="30"/>
-      <c r="S4" s="30"/>
-      <c r="T4" s="30"/>
-      <c r="U4" s="30"/>
-      <c r="V4" s="65"/>
-      <c r="W4" s="65"/>
-      <c r="X4" s="30"/>
-      <c r="Y4" s="30"/>
-      <c r="Z4" s="30"/>
-      <c r="AA4" s="30"/>
-      <c r="AB4" s="30"/>
-      <c r="AC4" s="30"/>
-      <c r="AD4" s="30"/>
-      <c r="AE4" s="30"/>
-      <c r="AF4" s="30"/>
-      <c r="AG4" s="30"/>
-      <c r="AH4" s="30"/>
-      <c r="AI4" s="30"/>
-      <c r="AJ4" s="30"/>
-      <c r="AK4" s="30"/>
-      <c r="AL4" s="30"/>
-      <c r="AM4" s="30"/>
-      <c r="AN4" s="30"/>
-      <c r="AO4" s="30"/>
-      <c r="AP4" s="30"/>
-      <c r="AQ4" s="30"/>
-      <c r="AR4" s="30"/>
-      <c r="AS4" s="30"/>
-      <c r="AT4" s="30"/>
-      <c r="AU4" s="30"/>
-      <c r="AV4" s="30"/>
-      <c r="AW4" s="30"/>
-      <c r="AX4" s="30"/>
-      <c r="AY4" s="30"/>
-      <c r="AZ4" s="30"/>
-      <c r="BA4" s="30"/>
-      <c r="BB4" s="30"/>
-      <c r="BC4" s="30"/>
-      <c r="BD4" s="30"/>
-      <c r="BE4" s="30"/>
-      <c r="BF4" s="30"/>
-      <c r="BG4" s="30"/>
-      <c r="BH4" s="30"/>
-      <c r="BI4" s="30"/>
-      <c r="BJ4" s="30"/>
-      <c r="BK4" s="30"/>
-      <c r="BL4" s="30"/>
-      <c r="BM4" s="30"/>
-      <c r="BN4" s="30"/>
-      <c r="BO4" s="30"/>
-      <c r="BP4" s="30"/>
-      <c r="BQ4" s="30"/>
-      <c r="BR4" s="30"/>
-      <c r="BS4" s="30"/>
-      <c r="BT4" s="30"/>
-      <c r="BU4" s="30"/>
-      <c r="BV4" s="30"/>
-      <c r="BW4" s="30"/>
-      <c r="BX4" s="30"/>
-      <c r="BY4" s="30"/>
-      <c r="BZ4" s="30"/>
-      <c r="CA4" s="30"/>
-      <c r="CB4" s="30"/>
-      <c r="CC4" s="30"/>
-      <c r="CD4" s="30"/>
-      <c r="CE4" s="30"/>
-      <c r="CF4" s="30"/>
-      <c r="CG4" s="30"/>
-      <c r="CH4" s="30"/>
-      <c r="CI4" s="30"/>
-      <c r="CJ4" s="30"/>
-      <c r="CK4" s="30"/>
-      <c r="CL4" s="30"/>
-      <c r="CM4" s="30"/>
-      <c r="CN4" s="30"/>
-      <c r="CO4" s="30"/>
-      <c r="CP4" s="30"/>
-      <c r="CQ4" s="30"/>
-      <c r="CR4" s="30"/>
-      <c r="CS4" s="30"/>
-      <c r="CT4" s="30"/>
-      <c r="CU4" s="30"/>
-      <c r="CV4" s="30"/>
-      <c r="CW4" s="30"/>
-      <c r="CX4" s="30"/>
-      <c r="CY4" s="30"/>
-      <c r="CZ4" s="30"/>
-      <c r="DA4" s="30"/>
-      <c r="DB4" s="30"/>
-      <c r="DC4" s="30"/>
-      <c r="DD4" s="30"/>
-      <c r="DE4" s="30"/>
-      <c r="DF4" s="30"/>
-      <c r="DG4" s="30"/>
-      <c r="DH4" s="30"/>
-      <c r="DI4" s="30"/>
-      <c r="DJ4" s="30"/>
-      <c r="DK4" s="30"/>
-      <c r="DL4" s="30"/>
-      <c r="DM4" s="30"/>
-      <c r="DN4" s="30"/>
-      <c r="DO4" s="30"/>
-      <c r="DP4" s="30"/>
-      <c r="DQ4" s="30"/>
-      <c r="DR4" s="30"/>
-      <c r="DS4" s="30"/>
-      <c r="DT4" s="30"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="28"/>
+      <c r="Q4" s="28"/>
+      <c r="R4" s="28"/>
+      <c r="S4" s="28"/>
+      <c r="T4" s="28"/>
+      <c r="U4" s="28"/>
+      <c r="V4" s="30"/>
+      <c r="W4" s="30"/>
+      <c r="X4" s="28"/>
+      <c r="Y4" s="28"/>
+      <c r="Z4" s="67"/>
+      <c r="AA4" s="67"/>
+      <c r="AB4" s="67"/>
+      <c r="AC4" s="67"/>
+      <c r="AD4" s="28"/>
+      <c r="AE4" s="28"/>
+      <c r="AF4" s="28"/>
+      <c r="AG4" s="28"/>
+      <c r="AH4" s="28"/>
+      <c r="AI4" s="28"/>
+      <c r="AJ4" s="28"/>
+      <c r="AK4" s="28"/>
+      <c r="AL4" s="28"/>
+      <c r="AM4" s="28"/>
+      <c r="AN4" s="28"/>
+      <c r="AO4" s="28"/>
+      <c r="AP4" s="28"/>
+      <c r="AQ4" s="28"/>
+      <c r="AR4" s="28"/>
+      <c r="AS4" s="28"/>
+      <c r="AT4" s="28"/>
+      <c r="AU4" s="28"/>
+      <c r="AV4" s="28"/>
+      <c r="AW4" s="28"/>
+      <c r="AX4" s="28"/>
+      <c r="AY4" s="28"/>
+      <c r="AZ4" s="28"/>
+      <c r="BA4" s="28"/>
+      <c r="BB4" s="28"/>
+      <c r="BC4" s="28"/>
+      <c r="BD4" s="28"/>
+      <c r="BE4" s="28"/>
+      <c r="BF4" s="28"/>
+      <c r="BG4" s="28"/>
+      <c r="BH4" s="28"/>
+      <c r="BI4" s="28"/>
+      <c r="BJ4" s="28"/>
+      <c r="BK4" s="28"/>
+      <c r="BL4" s="28"/>
+      <c r="BM4" s="28"/>
+      <c r="BN4" s="28"/>
+      <c r="BO4" s="28"/>
+      <c r="BP4" s="28"/>
+      <c r="BQ4" s="28"/>
+      <c r="BR4" s="28"/>
+      <c r="BS4" s="28"/>
+      <c r="BT4" s="28"/>
+      <c r="BU4" s="28"/>
+      <c r="BV4" s="28"/>
+      <c r="BW4" s="28"/>
+      <c r="BX4" s="28"/>
+      <c r="BY4" s="28"/>
+      <c r="BZ4" s="28"/>
+      <c r="CA4" s="28"/>
+      <c r="CB4" s="28"/>
+      <c r="CC4" s="28"/>
+      <c r="CD4" s="28"/>
+      <c r="CE4" s="28"/>
+      <c r="CF4" s="28"/>
+      <c r="CG4" s="28"/>
+      <c r="CH4" s="28"/>
+      <c r="CI4" s="28"/>
+      <c r="CJ4" s="28"/>
+      <c r="CK4" s="28"/>
+      <c r="CL4" s="28"/>
+      <c r="CM4" s="28"/>
+      <c r="CN4" s="28"/>
+      <c r="CO4" s="28"/>
+      <c r="CP4" s="28"/>
+      <c r="CQ4" s="28"/>
+      <c r="CR4" s="28"/>
+      <c r="CS4" s="28"/>
+      <c r="CT4" s="28"/>
+      <c r="CU4" s="28"/>
+      <c r="CV4" s="28"/>
+      <c r="CW4" s="28"/>
+      <c r="CX4" s="28"/>
+      <c r="CY4" s="28"/>
+      <c r="CZ4" s="28"/>
+      <c r="DA4" s="28"/>
+      <c r="DB4" s="28"/>
+      <c r="DC4" s="28"/>
+      <c r="DD4" s="28"/>
+      <c r="DE4" s="28"/>
+      <c r="DF4" s="28"/>
+      <c r="DG4" s="28"/>
+      <c r="DH4" s="28"/>
+      <c r="DI4" s="28"/>
+      <c r="DJ4" s="28"/>
+      <c r="DK4" s="28"/>
+      <c r="DL4" s="28"/>
+      <c r="DM4" s="28"/>
+      <c r="DN4" s="28"/>
+      <c r="DO4" s="28"/>
+      <c r="DP4" s="28"/>
+      <c r="DQ4" s="28"/>
+      <c r="DR4" s="28"/>
+      <c r="DS4" s="28"/>
+      <c r="DT4" s="28"/>
     </row>
     <row r="5" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="49"/>
-      <c r="C5" s="50">
+      <c r="B5" s="50"/>
+      <c r="C5" s="51">
         <v>60</v>
       </c>
-      <c r="D5" s="51"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="30"/>
-      <c r="K5" s="30"/>
-      <c r="L5" s="30"/>
-      <c r="M5" s="30"/>
-      <c r="N5" s="30"/>
-      <c r="O5" s="30"/>
-      <c r="P5" s="30"/>
-      <c r="Q5" s="30"/>
-      <c r="R5" s="30"/>
-      <c r="S5" s="30"/>
-      <c r="T5" s="30"/>
-      <c r="U5" s="30"/>
-      <c r="V5" s="65"/>
-      <c r="W5" s="65"/>
-      <c r="X5" s="30"/>
-      <c r="Y5" s="30"/>
-      <c r="Z5" s="30"/>
-      <c r="AA5" s="30"/>
-      <c r="AB5" s="30"/>
-      <c r="AC5" s="30"/>
-      <c r="AD5" s="30"/>
-      <c r="AE5" s="30"/>
-      <c r="AF5" s="30"/>
-      <c r="AG5" s="30"/>
-      <c r="AH5" s="30"/>
-      <c r="AI5" s="30"/>
-      <c r="AJ5" s="30"/>
-      <c r="AK5" s="30"/>
-      <c r="AL5" s="30"/>
-      <c r="AM5" s="30"/>
-      <c r="AN5" s="30"/>
-      <c r="AO5" s="30"/>
-      <c r="AP5" s="30"/>
-      <c r="AQ5" s="30"/>
-      <c r="AR5" s="30"/>
-      <c r="AS5" s="30"/>
-      <c r="AT5" s="30"/>
-      <c r="AU5" s="30"/>
-      <c r="AV5" s="30"/>
-      <c r="AW5" s="30"/>
-      <c r="AX5" s="30"/>
-      <c r="AY5" s="30"/>
-      <c r="AZ5" s="30"/>
-      <c r="BA5" s="30"/>
-      <c r="BB5" s="30"/>
-      <c r="BC5" s="30"/>
-      <c r="BD5" s="30"/>
-      <c r="BE5" s="30"/>
-      <c r="BF5" s="30"/>
-      <c r="BG5" s="30"/>
-      <c r="BH5" s="30"/>
-      <c r="BI5" s="30"/>
-      <c r="BJ5" s="30"/>
-      <c r="BK5" s="30"/>
-      <c r="BL5" s="30"/>
-      <c r="BM5" s="30"/>
-      <c r="BN5" s="30"/>
-      <c r="BO5" s="30"/>
-      <c r="BP5" s="30"/>
-      <c r="BQ5" s="30"/>
-      <c r="BR5" s="30"/>
-      <c r="BS5" s="30"/>
-      <c r="BT5" s="30"/>
-      <c r="BU5" s="30"/>
-      <c r="BV5" s="30"/>
-      <c r="BW5" s="30"/>
-      <c r="BX5" s="30"/>
-      <c r="BY5" s="30"/>
-      <c r="BZ5" s="30"/>
-      <c r="CA5" s="30"/>
-      <c r="CB5" s="30"/>
-      <c r="CC5" s="30"/>
-      <c r="CD5" s="30"/>
-      <c r="CE5" s="30"/>
-      <c r="CF5" s="30"/>
-      <c r="CG5" s="30"/>
-      <c r="CH5" s="30"/>
-      <c r="CI5" s="30"/>
-      <c r="CJ5" s="30"/>
-      <c r="CK5" s="30"/>
-      <c r="CL5" s="30"/>
-      <c r="CM5" s="30"/>
-      <c r="CN5" s="30"/>
-      <c r="CO5" s="30"/>
-      <c r="CP5" s="30"/>
-      <c r="CQ5" s="30"/>
-      <c r="CR5" s="30"/>
-      <c r="CS5" s="30"/>
-      <c r="CT5" s="30"/>
-      <c r="CU5" s="30"/>
-      <c r="CV5" s="30"/>
-      <c r="CW5" s="30"/>
-      <c r="CX5" s="30"/>
-      <c r="CY5" s="30"/>
-      <c r="CZ5" s="30"/>
-      <c r="DA5" s="30"/>
-      <c r="DB5" s="30"/>
-      <c r="DC5" s="30"/>
-      <c r="DD5" s="30"/>
-      <c r="DE5" s="30"/>
-      <c r="DF5" s="30"/>
-      <c r="DG5" s="30"/>
-      <c r="DH5" s="30"/>
-      <c r="DI5" s="30"/>
-      <c r="DJ5" s="30"/>
-      <c r="DK5" s="30"/>
-      <c r="DL5" s="30"/>
-      <c r="DM5" s="30"/>
-      <c r="DN5" s="30"/>
-      <c r="DO5" s="30"/>
-      <c r="DP5" s="30"/>
-      <c r="DQ5" s="30"/>
-      <c r="DR5" s="30"/>
-      <c r="DS5" s="30"/>
-      <c r="DT5" s="30"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
+      <c r="Q5" s="28"/>
+      <c r="R5" s="28"/>
+      <c r="S5" s="28"/>
+      <c r="T5" s="28"/>
+      <c r="U5" s="28"/>
+      <c r="V5" s="30"/>
+      <c r="W5" s="30"/>
+      <c r="X5" s="28"/>
+      <c r="Y5" s="28"/>
+      <c r="Z5" s="67"/>
+      <c r="AA5" s="67"/>
+      <c r="AB5" s="67"/>
+      <c r="AC5" s="67"/>
+      <c r="AD5" s="28"/>
+      <c r="AE5" s="28"/>
+      <c r="AF5" s="28"/>
+      <c r="AG5" s="28"/>
+      <c r="AH5" s="28"/>
+      <c r="AI5" s="28"/>
+      <c r="AJ5" s="28"/>
+      <c r="AK5" s="28"/>
+      <c r="AL5" s="28"/>
+      <c r="AM5" s="28"/>
+      <c r="AN5" s="28"/>
+      <c r="AO5" s="28"/>
+      <c r="AP5" s="28"/>
+      <c r="AQ5" s="28"/>
+      <c r="AR5" s="28"/>
+      <c r="AS5" s="28"/>
+      <c r="AT5" s="28"/>
+      <c r="AU5" s="28"/>
+      <c r="AV5" s="28"/>
+      <c r="AW5" s="28"/>
+      <c r="AX5" s="28"/>
+      <c r="AY5" s="28"/>
+      <c r="AZ5" s="28"/>
+      <c r="BA5" s="28"/>
+      <c r="BB5" s="28"/>
+      <c r="BC5" s="28"/>
+      <c r="BD5" s="28"/>
+      <c r="BE5" s="28"/>
+      <c r="BF5" s="28"/>
+      <c r="BG5" s="28"/>
+      <c r="BH5" s="28"/>
+      <c r="BI5" s="28"/>
+      <c r="BJ5" s="28"/>
+      <c r="BK5" s="28"/>
+      <c r="BL5" s="28"/>
+      <c r="BM5" s="28"/>
+      <c r="BN5" s="28"/>
+      <c r="BO5" s="28"/>
+      <c r="BP5" s="28"/>
+      <c r="BQ5" s="28"/>
+      <c r="BR5" s="28"/>
+      <c r="BS5" s="28"/>
+      <c r="BT5" s="28"/>
+      <c r="BU5" s="28"/>
+      <c r="BV5" s="28"/>
+      <c r="BW5" s="28"/>
+      <c r="BX5" s="28"/>
+      <c r="BY5" s="28"/>
+      <c r="BZ5" s="28"/>
+      <c r="CA5" s="28"/>
+      <c r="CB5" s="28"/>
+      <c r="CC5" s="28"/>
+      <c r="CD5" s="28"/>
+      <c r="CE5" s="28"/>
+      <c r="CF5" s="28"/>
+      <c r="CG5" s="28"/>
+      <c r="CH5" s="28"/>
+      <c r="CI5" s="28"/>
+      <c r="CJ5" s="28"/>
+      <c r="CK5" s="28"/>
+      <c r="CL5" s="28"/>
+      <c r="CM5" s="28"/>
+      <c r="CN5" s="28"/>
+      <c r="CO5" s="28"/>
+      <c r="CP5" s="28"/>
+      <c r="CQ5" s="28"/>
+      <c r="CR5" s="28"/>
+      <c r="CS5" s="28"/>
+      <c r="CT5" s="28"/>
+      <c r="CU5" s="28"/>
+      <c r="CV5" s="28"/>
+      <c r="CW5" s="28"/>
+      <c r="CX5" s="28"/>
+      <c r="CY5" s="28"/>
+      <c r="CZ5" s="28"/>
+      <c r="DA5" s="28"/>
+      <c r="DB5" s="28"/>
+      <c r="DC5" s="28"/>
+      <c r="DD5" s="28"/>
+      <c r="DE5" s="28"/>
+      <c r="DF5" s="28"/>
+      <c r="DG5" s="28"/>
+      <c r="DH5" s="28"/>
+      <c r="DI5" s="28"/>
+      <c r="DJ5" s="28"/>
+      <c r="DK5" s="28"/>
+      <c r="DL5" s="28"/>
+      <c r="DM5" s="28"/>
+      <c r="DN5" s="28"/>
+      <c r="DO5" s="28"/>
+      <c r="DP5" s="28"/>
+      <c r="DQ5" s="28"/>
+      <c r="DR5" s="28"/>
+      <c r="DS5" s="28"/>
+      <c r="DT5" s="28"/>
     </row>
     <row r="6" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="50">
+      <c r="B6" s="50"/>
+      <c r="C6" s="51">
         <v>4</v>
       </c>
-      <c r="D6" s="51"/>
-      <c r="E6" s="46"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="30"/>
-      <c r="J6" s="30"/>
-      <c r="K6" s="30"/>
-      <c r="L6" s="30"/>
-      <c r="M6" s="30"/>
-      <c r="N6" s="30"/>
-      <c r="O6" s="30"/>
-      <c r="P6" s="30"/>
-      <c r="Q6" s="30"/>
-      <c r="R6" s="30"/>
-      <c r="S6" s="30"/>
-      <c r="T6" s="30"/>
-      <c r="U6" s="30"/>
-      <c r="V6" s="65"/>
-      <c r="W6" s="65"/>
-      <c r="X6" s="30"/>
-      <c r="Y6" s="30"/>
-      <c r="Z6" s="30"/>
-      <c r="AA6" s="30"/>
-      <c r="AB6" s="30"/>
-      <c r="AC6" s="30"/>
-      <c r="AD6" s="30"/>
-      <c r="AE6" s="30"/>
-      <c r="AF6" s="30"/>
-      <c r="AG6" s="30"/>
-      <c r="AH6" s="30"/>
-      <c r="AI6" s="30"/>
-      <c r="AJ6" s="30"/>
-      <c r="AK6" s="30"/>
-      <c r="AL6" s="30"/>
-      <c r="AM6" s="30"/>
-      <c r="AN6" s="30"/>
-      <c r="AO6" s="30"/>
-      <c r="AP6" s="30"/>
-      <c r="AQ6" s="30"/>
-      <c r="AR6" s="30"/>
-      <c r="AS6" s="30"/>
-      <c r="AT6" s="30"/>
-      <c r="AU6" s="30"/>
-      <c r="AV6" s="30"/>
-      <c r="AW6" s="30"/>
-      <c r="AX6" s="30"/>
-      <c r="AY6" s="30"/>
-      <c r="AZ6" s="30"/>
-      <c r="BA6" s="30"/>
-      <c r="BB6" s="30"/>
-      <c r="BC6" s="30"/>
-      <c r="BD6" s="30"/>
-      <c r="BE6" s="30"/>
-      <c r="BF6" s="30"/>
-      <c r="BG6" s="30"/>
-      <c r="BH6" s="30"/>
-      <c r="BI6" s="30"/>
-      <c r="BJ6" s="30"/>
-      <c r="BK6" s="30"/>
-      <c r="BL6" s="30"/>
-      <c r="BM6" s="30"/>
-      <c r="BN6" s="30"/>
-      <c r="BO6" s="30"/>
-      <c r="BP6" s="30"/>
-      <c r="BQ6" s="30"/>
-      <c r="BR6" s="30"/>
-      <c r="BS6" s="30"/>
-      <c r="BT6" s="30"/>
-      <c r="BU6" s="30"/>
-      <c r="BV6" s="30"/>
-      <c r="BW6" s="30"/>
-      <c r="BX6" s="30"/>
-      <c r="BY6" s="30"/>
-      <c r="BZ6" s="30"/>
-      <c r="CA6" s="30"/>
-      <c r="CB6" s="30"/>
-      <c r="CC6" s="30"/>
-      <c r="CD6" s="30"/>
-      <c r="CE6" s="30"/>
-      <c r="CF6" s="30"/>
-      <c r="CG6" s="30"/>
-      <c r="CH6" s="30"/>
-      <c r="CI6" s="30"/>
-      <c r="CJ6" s="30"/>
-      <c r="CK6" s="30"/>
-      <c r="CL6" s="30"/>
-      <c r="CM6" s="30"/>
-      <c r="CN6" s="30"/>
-      <c r="CO6" s="30"/>
-      <c r="CP6" s="30"/>
-      <c r="CQ6" s="30"/>
-      <c r="CR6" s="30"/>
-      <c r="CS6" s="30"/>
-      <c r="CT6" s="30"/>
-      <c r="CU6" s="30"/>
-      <c r="CV6" s="30"/>
-      <c r="CW6" s="30"/>
-      <c r="CX6" s="30"/>
-      <c r="CY6" s="30"/>
-      <c r="CZ6" s="30"/>
-      <c r="DA6" s="30"/>
-      <c r="DB6" s="30"/>
-      <c r="DC6" s="30"/>
-      <c r="DD6" s="30"/>
-      <c r="DE6" s="30"/>
-      <c r="DF6" s="30"/>
-      <c r="DG6" s="30"/>
-      <c r="DH6" s="30"/>
-      <c r="DI6" s="30"/>
-      <c r="DJ6" s="30"/>
-      <c r="DK6" s="30"/>
-      <c r="DL6" s="30"/>
-      <c r="DM6" s="30"/>
-      <c r="DN6" s="30"/>
-      <c r="DO6" s="30"/>
-      <c r="DP6" s="30"/>
-      <c r="DQ6" s="30"/>
-      <c r="DR6" s="30"/>
-      <c r="DS6" s="30"/>
-      <c r="DT6" s="30"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="28"/>
+      <c r="M6" s="28"/>
+      <c r="N6" s="28"/>
+      <c r="O6" s="28"/>
+      <c r="P6" s="28"/>
+      <c r="Q6" s="28"/>
+      <c r="R6" s="28"/>
+      <c r="S6" s="28"/>
+      <c r="T6" s="28"/>
+      <c r="U6" s="28"/>
+      <c r="V6" s="30"/>
+      <c r="W6" s="30"/>
+      <c r="X6" s="28"/>
+      <c r="Y6" s="28"/>
+      <c r="Z6" s="67"/>
+      <c r="AA6" s="67"/>
+      <c r="AB6" s="67"/>
+      <c r="AC6" s="67"/>
+      <c r="AD6" s="28"/>
+      <c r="AE6" s="28"/>
+      <c r="AF6" s="28"/>
+      <c r="AG6" s="28"/>
+      <c r="AH6" s="28"/>
+      <c r="AI6" s="28"/>
+      <c r="AJ6" s="28"/>
+      <c r="AK6" s="28"/>
+      <c r="AL6" s="28"/>
+      <c r="AM6" s="28"/>
+      <c r="AN6" s="28"/>
+      <c r="AO6" s="28"/>
+      <c r="AP6" s="28"/>
+      <c r="AQ6" s="28"/>
+      <c r="AR6" s="28"/>
+      <c r="AS6" s="28"/>
+      <c r="AT6" s="28"/>
+      <c r="AU6" s="28"/>
+      <c r="AV6" s="28"/>
+      <c r="AW6" s="28"/>
+      <c r="AX6" s="28"/>
+      <c r="AY6" s="28"/>
+      <c r="AZ6" s="28"/>
+      <c r="BA6" s="28"/>
+      <c r="BB6" s="28"/>
+      <c r="BC6" s="28"/>
+      <c r="BD6" s="28"/>
+      <c r="BE6" s="28"/>
+      <c r="BF6" s="28"/>
+      <c r="BG6" s="28"/>
+      <c r="BH6" s="28"/>
+      <c r="BI6" s="28"/>
+      <c r="BJ6" s="28"/>
+      <c r="BK6" s="28"/>
+      <c r="BL6" s="28"/>
+      <c r="BM6" s="28"/>
+      <c r="BN6" s="28"/>
+      <c r="BO6" s="28"/>
+      <c r="BP6" s="28"/>
+      <c r="BQ6" s="28"/>
+      <c r="BR6" s="28"/>
+      <c r="BS6" s="28"/>
+      <c r="BT6" s="28"/>
+      <c r="BU6" s="28"/>
+      <c r="BV6" s="28"/>
+      <c r="BW6" s="28"/>
+      <c r="BX6" s="28"/>
+      <c r="BY6" s="28"/>
+      <c r="BZ6" s="28"/>
+      <c r="CA6" s="28"/>
+      <c r="CB6" s="28"/>
+      <c r="CC6" s="28"/>
+      <c r="CD6" s="28"/>
+      <c r="CE6" s="28"/>
+      <c r="CF6" s="28"/>
+      <c r="CG6" s="28"/>
+      <c r="CH6" s="28"/>
+      <c r="CI6" s="28"/>
+      <c r="CJ6" s="28"/>
+      <c r="CK6" s="28"/>
+      <c r="CL6" s="28"/>
+      <c r="CM6" s="28"/>
+      <c r="CN6" s="28"/>
+      <c r="CO6" s="28"/>
+      <c r="CP6" s="28"/>
+      <c r="CQ6" s="28"/>
+      <c r="CR6" s="28"/>
+      <c r="CS6" s="28"/>
+      <c r="CT6" s="28"/>
+      <c r="CU6" s="28"/>
+      <c r="CV6" s="28"/>
+      <c r="CW6" s="28"/>
+      <c r="CX6" s="28"/>
+      <c r="CY6" s="28"/>
+      <c r="CZ6" s="28"/>
+      <c r="DA6" s="28"/>
+      <c r="DB6" s="28"/>
+      <c r="DC6" s="28"/>
+      <c r="DD6" s="28"/>
+      <c r="DE6" s="28"/>
+      <c r="DF6" s="28"/>
+      <c r="DG6" s="28"/>
+      <c r="DH6" s="28"/>
+      <c r="DI6" s="28"/>
+      <c r="DJ6" s="28"/>
+      <c r="DK6" s="28"/>
+      <c r="DL6" s="28"/>
+      <c r="DM6" s="28"/>
+      <c r="DN6" s="28"/>
+      <c r="DO6" s="28"/>
+      <c r="DP6" s="28"/>
+      <c r="DQ6" s="28"/>
+      <c r="DR6" s="28"/>
+      <c r="DS6" s="28"/>
+      <c r="DT6" s="28"/>
     </row>
     <row r="7" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="52"/>
-      <c r="C7" s="50">
+      <c r="B7" s="53"/>
+      <c r="C7" s="51">
         <v>11</v>
       </c>
-      <c r="D7" s="51"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="31"/>
-      <c r="M7" s="31"/>
-      <c r="N7" s="31"/>
-      <c r="O7" s="31"/>
-      <c r="P7" s="31"/>
-      <c r="Q7" s="31"/>
-      <c r="R7" s="31"/>
-      <c r="S7" s="31"/>
-      <c r="T7" s="31"/>
-      <c r="U7" s="31"/>
-      <c r="V7" s="66"/>
-      <c r="W7" s="66"/>
-      <c r="X7" s="31"/>
-      <c r="Y7" s="31"/>
-      <c r="Z7" s="31"/>
-      <c r="AA7" s="31"/>
-      <c r="AB7" s="31"/>
-      <c r="AC7" s="31"/>
-      <c r="AD7" s="31"/>
-      <c r="AE7" s="31"/>
-      <c r="AF7" s="31"/>
-      <c r="AG7" s="31"/>
-      <c r="AH7" s="31"/>
-      <c r="AI7" s="31"/>
-      <c r="AJ7" s="31"/>
-      <c r="AK7" s="31"/>
-      <c r="AL7" s="31"/>
-      <c r="AM7" s="31"/>
-      <c r="AN7" s="31"/>
-      <c r="AO7" s="31"/>
-      <c r="AP7" s="31"/>
-      <c r="AQ7" s="31"/>
-      <c r="AR7" s="31"/>
-      <c r="AS7" s="31"/>
-      <c r="AT7" s="31"/>
-      <c r="AU7" s="31"/>
-      <c r="AV7" s="31"/>
-      <c r="AW7" s="31"/>
-      <c r="AX7" s="31"/>
-      <c r="AY7" s="31"/>
-      <c r="AZ7" s="31"/>
-      <c r="BA7" s="31"/>
-      <c r="BB7" s="31"/>
-      <c r="BC7" s="31"/>
-      <c r="BD7" s="31"/>
-      <c r="BE7" s="31"/>
-      <c r="BF7" s="31"/>
-      <c r="BG7" s="31"/>
-      <c r="BH7" s="31"/>
-      <c r="BI7" s="31"/>
-      <c r="BJ7" s="31"/>
-      <c r="BK7" s="31"/>
-      <c r="BL7" s="31"/>
-      <c r="BM7" s="31"/>
-      <c r="BN7" s="31"/>
-      <c r="BO7" s="31"/>
-      <c r="BP7" s="31"/>
-      <c r="BQ7" s="31"/>
-      <c r="BR7" s="31"/>
-      <c r="BS7" s="31"/>
-      <c r="BT7" s="31"/>
-      <c r="BU7" s="31"/>
-      <c r="BV7" s="31"/>
-      <c r="BW7" s="31"/>
-      <c r="BX7" s="31"/>
-      <c r="BY7" s="31"/>
-      <c r="BZ7" s="31"/>
-      <c r="CA7" s="31"/>
-      <c r="CB7" s="31"/>
-      <c r="CC7" s="31"/>
-      <c r="CD7" s="31"/>
-      <c r="CE7" s="31"/>
-      <c r="CF7" s="31"/>
-      <c r="CG7" s="31"/>
-      <c r="CH7" s="31"/>
-      <c r="CI7" s="31"/>
-      <c r="CJ7" s="31"/>
-      <c r="CK7" s="31"/>
-      <c r="CL7" s="31"/>
-      <c r="CM7" s="31"/>
-      <c r="CN7" s="31"/>
-      <c r="CO7" s="31"/>
-      <c r="CP7" s="31"/>
-      <c r="CQ7" s="31"/>
-      <c r="CR7" s="31"/>
-      <c r="CS7" s="31"/>
-      <c r="CT7" s="31"/>
-      <c r="CU7" s="31"/>
-      <c r="CV7" s="31"/>
-      <c r="CW7" s="31"/>
-      <c r="CX7" s="31"/>
-      <c r="CY7" s="31"/>
-      <c r="CZ7" s="31"/>
-      <c r="DA7" s="31"/>
-      <c r="DB7" s="31"/>
-      <c r="DC7" s="31"/>
-      <c r="DD7" s="31"/>
-      <c r="DE7" s="31"/>
-      <c r="DF7" s="31"/>
-      <c r="DG7" s="31"/>
-      <c r="DH7" s="31"/>
-      <c r="DI7" s="31"/>
-      <c r="DJ7" s="31"/>
-      <c r="DK7" s="31"/>
-      <c r="DL7" s="31"/>
-      <c r="DM7" s="31"/>
-      <c r="DN7" s="31"/>
-      <c r="DO7" s="31"/>
-      <c r="DP7" s="31"/>
-      <c r="DQ7" s="31"/>
-      <c r="DR7" s="31"/>
-      <c r="DS7" s="31"/>
-      <c r="DT7" s="31"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="29"/>
+      <c r="N7" s="29"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="29"/>
+      <c r="Q7" s="29"/>
+      <c r="R7" s="29"/>
+      <c r="S7" s="29"/>
+      <c r="T7" s="29"/>
+      <c r="U7" s="29"/>
+      <c r="V7" s="31"/>
+      <c r="W7" s="31"/>
+      <c r="X7" s="29"/>
+      <c r="Y7" s="29"/>
+      <c r="Z7" s="68"/>
+      <c r="AA7" s="68"/>
+      <c r="AB7" s="68"/>
+      <c r="AC7" s="68"/>
+      <c r="AD7" s="29"/>
+      <c r="AE7" s="29"/>
+      <c r="AF7" s="29"/>
+      <c r="AG7" s="29"/>
+      <c r="AH7" s="29"/>
+      <c r="AI7" s="29"/>
+      <c r="AJ7" s="29"/>
+      <c r="AK7" s="29"/>
+      <c r="AL7" s="29"/>
+      <c r="AM7" s="29"/>
+      <c r="AN7" s="29"/>
+      <c r="AO7" s="29"/>
+      <c r="AP7" s="29"/>
+      <c r="AQ7" s="29"/>
+      <c r="AR7" s="29"/>
+      <c r="AS7" s="29"/>
+      <c r="AT7" s="29"/>
+      <c r="AU7" s="29"/>
+      <c r="AV7" s="29"/>
+      <c r="AW7" s="29"/>
+      <c r="AX7" s="29"/>
+      <c r="AY7" s="29"/>
+      <c r="AZ7" s="29"/>
+      <c r="BA7" s="29"/>
+      <c r="BB7" s="29"/>
+      <c r="BC7" s="29"/>
+      <c r="BD7" s="29"/>
+      <c r="BE7" s="29"/>
+      <c r="BF7" s="29"/>
+      <c r="BG7" s="29"/>
+      <c r="BH7" s="29"/>
+      <c r="BI7" s="29"/>
+      <c r="BJ7" s="29"/>
+      <c r="BK7" s="29"/>
+      <c r="BL7" s="29"/>
+      <c r="BM7" s="29"/>
+      <c r="BN7" s="29"/>
+      <c r="BO7" s="29"/>
+      <c r="BP7" s="29"/>
+      <c r="BQ7" s="29"/>
+      <c r="BR7" s="29"/>
+      <c r="BS7" s="29"/>
+      <c r="BT7" s="29"/>
+      <c r="BU7" s="29"/>
+      <c r="BV7" s="29"/>
+      <c r="BW7" s="29"/>
+      <c r="BX7" s="29"/>
+      <c r="BY7" s="29"/>
+      <c r="BZ7" s="29"/>
+      <c r="CA7" s="29"/>
+      <c r="CB7" s="29"/>
+      <c r="CC7" s="29"/>
+      <c r="CD7" s="29"/>
+      <c r="CE7" s="29"/>
+      <c r="CF7" s="29"/>
+      <c r="CG7" s="29"/>
+      <c r="CH7" s="29"/>
+      <c r="CI7" s="29"/>
+      <c r="CJ7" s="29"/>
+      <c r="CK7" s="29"/>
+      <c r="CL7" s="29"/>
+      <c r="CM7" s="29"/>
+      <c r="CN7" s="29"/>
+      <c r="CO7" s="29"/>
+      <c r="CP7" s="29"/>
+      <c r="CQ7" s="29"/>
+      <c r="CR7" s="29"/>
+      <c r="CS7" s="29"/>
+      <c r="CT7" s="29"/>
+      <c r="CU7" s="29"/>
+      <c r="CV7" s="29"/>
+      <c r="CW7" s="29"/>
+      <c r="CX7" s="29"/>
+      <c r="CY7" s="29"/>
+      <c r="CZ7" s="29"/>
+      <c r="DA7" s="29"/>
+      <c r="DB7" s="29"/>
+      <c r="DC7" s="29"/>
+      <c r="DD7" s="29"/>
+      <c r="DE7" s="29"/>
+      <c r="DF7" s="29"/>
+      <c r="DG7" s="29"/>
+      <c r="DH7" s="29"/>
+      <c r="DI7" s="29"/>
+      <c r="DJ7" s="29"/>
+      <c r="DK7" s="29"/>
+      <c r="DL7" s="29"/>
+      <c r="DM7" s="29"/>
+      <c r="DN7" s="29"/>
+      <c r="DO7" s="29"/>
+      <c r="DP7" s="29"/>
+      <c r="DQ7" s="29"/>
+      <c r="DR7" s="29"/>
+      <c r="DS7" s="29"/>
+      <c r="DT7" s="29"/>
     </row>
     <row r="8" spans="1:125" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="32">
+      <c r="B8" s="54"/>
+      <c r="C8" s="55">
         <f>SUM(C5:D7)</f>
         <v>75</v>
       </c>
-      <c r="D8" s="35"/>
+      <c r="D8" s="49"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="28">
-        <v>1</v>
-      </c>
-      <c r="G8" s="28">
+      <c r="F8" s="35">
+        <v>1</v>
+      </c>
+      <c r="G8" s="35">
         <v>2</v>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="35">
         <v>3</v>
       </c>
-      <c r="I8" s="28">
+      <c r="I8" s="35">
         <v>4</v>
       </c>
-      <c r="J8" s="28">
+      <c r="J8" s="35">
         <v>5</v>
       </c>
-      <c r="K8" s="28">
+      <c r="K8" s="35">
         <v>6</v>
       </c>
-      <c r="L8" s="28">
+      <c r="L8" s="35">
         <v>7</v>
       </c>
-      <c r="M8" s="28">
+      <c r="M8" s="35">
         <v>8</v>
       </c>
-      <c r="N8" s="28">
+      <c r="N8" s="35">
         <v>9</v>
       </c>
-      <c r="O8" s="28">
+      <c r="O8" s="35">
         <v>10</v>
       </c>
-      <c r="P8" s="28">
+      <c r="P8" s="35">
         <v>11</v>
       </c>
-      <c r="Q8" s="28">
+      <c r="Q8" s="35">
         <v>12</v>
       </c>
-      <c r="R8" s="28">
+      <c r="R8" s="35">
         <v>13</v>
       </c>
-      <c r="S8" s="28">
+      <c r="S8" s="35">
         <v>14</v>
       </c>
-      <c r="T8" s="28">
+      <c r="T8" s="35">
         <v>15</v>
       </c>
-      <c r="U8" s="28">
+      <c r="U8" s="35">
         <v>16</v>
       </c>
-      <c r="V8" s="28">
+      <c r="V8" s="35">
         <v>17</v>
       </c>
-      <c r="W8" s="28">
+      <c r="W8" s="35">
         <v>18</v>
       </c>
-      <c r="X8" s="28">
+      <c r="X8" s="35">
         <v>19</v>
       </c>
-      <c r="Y8" s="28">
+      <c r="Y8" s="35">
         <v>20</v>
       </c>
-      <c r="Z8" s="28">
+      <c r="Z8" s="35">
         <v>21</v>
       </c>
-      <c r="AA8" s="28">
+      <c r="AA8" s="35">
         <v>22</v>
       </c>
-      <c r="AB8" s="28">
+      <c r="AB8" s="35">
         <v>23</v>
       </c>
-      <c r="AC8" s="28">
+      <c r="AC8" s="35">
         <v>24</v>
       </c>
-      <c r="AD8" s="28">
+      <c r="AD8" s="35">
         <v>25</v>
       </c>
-      <c r="AE8" s="28">
+      <c r="AE8" s="35">
         <v>26</v>
       </c>
-      <c r="AF8" s="28">
+      <c r="AF8" s="35">
         <v>27</v>
       </c>
-      <c r="AG8" s="28">
+      <c r="AG8" s="35">
         <v>28</v>
       </c>
-      <c r="AH8" s="28">
+      <c r="AH8" s="35">
         <v>29</v>
       </c>
-      <c r="AI8" s="28">
+      <c r="AI8" s="35">
         <v>30</v>
       </c>
-      <c r="AJ8" s="28">
+      <c r="AJ8" s="35">
         <v>31</v>
       </c>
-      <c r="AK8" s="28">
+      <c r="AK8" s="35">
         <v>32</v>
       </c>
-      <c r="AL8" s="28">
+      <c r="AL8" s="35">
         <v>33</v>
       </c>
-      <c r="AM8" s="28">
+      <c r="AM8" s="35">
         <v>34</v>
       </c>
-      <c r="AN8" s="28">
+      <c r="AN8" s="35">
         <v>35</v>
       </c>
-      <c r="AO8" s="28">
+      <c r="AO8" s="35">
         <v>36</v>
       </c>
-      <c r="AP8" s="28">
+      <c r="AP8" s="35">
         <v>37</v>
       </c>
-      <c r="AQ8" s="28">
+      <c r="AQ8" s="35">
         <v>38</v>
       </c>
-      <c r="AR8" s="28">
+      <c r="AR8" s="35">
         <v>39</v>
       </c>
-      <c r="AS8" s="28">
+      <c r="AS8" s="35">
         <v>40</v>
       </c>
-      <c r="AT8" s="28">
+      <c r="AT8" s="35">
         <v>41</v>
       </c>
-      <c r="AU8" s="28">
+      <c r="AU8" s="35">
         <v>42</v>
       </c>
-      <c r="AV8" s="28">
+      <c r="AV8" s="35">
         <v>43</v>
       </c>
-      <c r="AW8" s="28">
+      <c r="AW8" s="35">
         <v>44</v>
       </c>
-      <c r="AX8" s="28">
+      <c r="AX8" s="35">
         <v>45</v>
       </c>
-      <c r="AY8" s="28">
+      <c r="AY8" s="35">
         <v>46</v>
       </c>
-      <c r="AZ8" s="28">
+      <c r="AZ8" s="35">
         <v>47</v>
       </c>
-      <c r="BA8" s="28">
+      <c r="BA8" s="35">
         <v>48</v>
       </c>
-      <c r="BB8" s="28">
+      <c r="BB8" s="35">
         <v>49</v>
       </c>
-      <c r="BC8" s="28">
+      <c r="BC8" s="35">
         <v>50</v>
       </c>
-      <c r="BD8" s="28">
+      <c r="BD8" s="35">
         <v>51</v>
       </c>
-      <c r="BE8" s="28">
+      <c r="BE8" s="35">
         <v>52</v>
       </c>
-      <c r="BF8" s="28">
+      <c r="BF8" s="35">
         <v>53</v>
       </c>
-      <c r="BG8" s="28">
+      <c r="BG8" s="35">
         <v>54</v>
       </c>
-      <c r="BH8" s="28">
+      <c r="BH8" s="35">
         <v>55</v>
       </c>
-      <c r="BI8" s="28">
+      <c r="BI8" s="35">
         <v>56</v>
       </c>
-      <c r="BJ8" s="28">
+      <c r="BJ8" s="35">
         <v>57</v>
       </c>
-      <c r="BK8" s="28">
+      <c r="BK8" s="35">
         <v>58</v>
       </c>
-      <c r="BL8" s="28">
+      <c r="BL8" s="35">
         <v>59</v>
       </c>
-      <c r="BM8" s="28">
+      <c r="BM8" s="35">
         <v>60</v>
       </c>
-      <c r="BN8" s="28">
+      <c r="BN8" s="35">
         <v>61</v>
       </c>
-      <c r="BO8" s="28">
+      <c r="BO8" s="35">
         <v>62</v>
       </c>
-      <c r="BP8" s="28">
+      <c r="BP8" s="35">
         <v>63</v>
       </c>
-      <c r="BQ8" s="28">
+      <c r="BQ8" s="35">
         <v>64</v>
       </c>
-      <c r="BR8" s="28">
+      <c r="BR8" s="35">
         <v>65</v>
       </c>
-      <c r="BS8" s="28">
+      <c r="BS8" s="35">
         <v>66</v>
       </c>
-      <c r="BT8" s="28">
+      <c r="BT8" s="35">
         <v>67</v>
       </c>
-      <c r="BU8" s="28">
+      <c r="BU8" s="35">
         <v>68</v>
       </c>
-      <c r="BV8" s="28">
+      <c r="BV8" s="35">
         <v>69</v>
       </c>
-      <c r="BW8" s="28">
+      <c r="BW8" s="35">
         <v>70</v>
       </c>
-      <c r="BX8" s="28">
+      <c r="BX8" s="35">
         <v>71</v>
       </c>
-      <c r="BY8" s="28">
+      <c r="BY8" s="35">
         <v>72</v>
       </c>
-      <c r="BZ8" s="28">
+      <c r="BZ8" s="35">
         <v>73</v>
       </c>
-      <c r="CA8" s="28">
+      <c r="CA8" s="35">
         <v>74</v>
       </c>
-      <c r="CB8" s="28">
+      <c r="CB8" s="35">
         <v>75</v>
       </c>
-      <c r="CC8" s="28">
+      <c r="CC8" s="35">
         <v>76</v>
       </c>
-      <c r="CD8" s="28">
+      <c r="CD8" s="35">
         <v>77</v>
       </c>
-      <c r="CE8" s="28">
+      <c r="CE8" s="35">
         <v>78</v>
       </c>
-      <c r="CF8" s="28">
+      <c r="CF8" s="35">
         <v>79</v>
       </c>
-      <c r="CG8" s="28">
+      <c r="CG8" s="35">
         <v>80</v>
       </c>
-      <c r="CH8" s="28">
+      <c r="CH8" s="35">
         <v>81</v>
       </c>
-      <c r="CI8" s="28">
+      <c r="CI8" s="35">
         <v>82</v>
       </c>
-      <c r="CJ8" s="28">
+      <c r="CJ8" s="35">
         <v>83</v>
       </c>
-      <c r="CK8" s="28">
+      <c r="CK8" s="35">
         <v>84</v>
       </c>
-      <c r="CL8" s="28">
+      <c r="CL8" s="35">
         <v>85</v>
       </c>
-      <c r="CM8" s="28">
+      <c r="CM8" s="35">
         <v>86</v>
       </c>
-      <c r="CN8" s="28">
+      <c r="CN8" s="35">
         <v>87</v>
       </c>
-      <c r="CO8" s="28">
+      <c r="CO8" s="35">
         <v>88</v>
       </c>
-      <c r="CP8" s="28">
+      <c r="CP8" s="35">
         <v>89</v>
       </c>
-      <c r="CQ8" s="28">
+      <c r="CQ8" s="35">
         <v>90</v>
       </c>
-      <c r="CR8" s="28">
+      <c r="CR8" s="35">
         <v>91</v>
       </c>
-      <c r="CS8" s="28">
+      <c r="CS8" s="35">
         <v>92</v>
       </c>
-      <c r="CT8" s="28">
+      <c r="CT8" s="35">
         <v>93</v>
       </c>
-      <c r="CU8" s="28">
+      <c r="CU8" s="35">
         <v>94</v>
       </c>
-      <c r="CV8" s="28">
+      <c r="CV8" s="35">
         <v>95</v>
       </c>
-      <c r="CW8" s="28">
+      <c r="CW8" s="35">
         <v>96</v>
       </c>
-      <c r="CX8" s="28">
+      <c r="CX8" s="35">
         <v>97</v>
       </c>
-      <c r="CY8" s="28">
+      <c r="CY8" s="35">
         <v>98</v>
       </c>
-      <c r="CZ8" s="28">
+      <c r="CZ8" s="35">
         <v>99</v>
       </c>
-      <c r="DA8" s="28">
+      <c r="DA8" s="35">
         <v>100</v>
       </c>
-      <c r="DB8" s="28">
+      <c r="DB8" s="35">
         <v>101</v>
       </c>
-      <c r="DC8" s="28">
+      <c r="DC8" s="35">
         <v>102</v>
       </c>
-      <c r="DD8" s="28">
+      <c r="DD8" s="35">
         <v>103</v>
       </c>
-      <c r="DE8" s="28">
+      <c r="DE8" s="35">
         <v>104</v>
       </c>
-      <c r="DF8" s="28">
+      <c r="DF8" s="35">
         <v>105</v>
       </c>
-      <c r="DG8" s="28">
+      <c r="DG8" s="35">
         <v>106</v>
       </c>
-      <c r="DH8" s="28">
+      <c r="DH8" s="35">
         <v>107</v>
       </c>
-      <c r="DI8" s="28">
+      <c r="DI8" s="35">
         <v>108</v>
       </c>
-      <c r="DJ8" s="28">
+      <c r="DJ8" s="35">
         <v>109</v>
       </c>
-      <c r="DK8" s="28">
+      <c r="DK8" s="35">
         <v>110</v>
       </c>
-      <c r="DL8" s="28">
+      <c r="DL8" s="35">
         <v>111</v>
       </c>
-      <c r="DM8" s="28">
+      <c r="DM8" s="35">
         <v>112</v>
       </c>
-      <c r="DN8" s="28">
+      <c r="DN8" s="35">
         <v>113</v>
       </c>
-      <c r="DO8" s="28">
+      <c r="DO8" s="35">
         <v>114</v>
       </c>
-      <c r="DP8" s="28">
+      <c r="DP8" s="35">
         <v>115</v>
       </c>
-      <c r="DQ8" s="28">
+      <c r="DQ8" s="35">
         <v>116</v>
       </c>
-      <c r="DR8" s="28">
+      <c r="DR8" s="35">
         <v>117</v>
       </c>
-      <c r="DS8" s="28">
+      <c r="DS8" s="35">
         <v>118</v>
       </c>
-      <c r="DT8" s="28">
+      <c r="DT8" s="35">
         <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="37" t="s">
+      <c r="B9" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="38" t="s">
+      <c r="C9" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="37"/>
+      <c r="D9" s="56"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="29"/>
-      <c r="P9" s="29"/>
-      <c r="Q9" s="29"/>
-      <c r="R9" s="29"/>
-      <c r="S9" s="29"/>
-      <c r="T9" s="29"/>
-      <c r="U9" s="29"/>
-      <c r="V9" s="29"/>
-      <c r="W9" s="29"/>
-      <c r="X9" s="29"/>
-      <c r="Y9" s="29"/>
-      <c r="Z9" s="29"/>
-      <c r="AA9" s="29"/>
-      <c r="AB9" s="29"/>
-      <c r="AC9" s="29"/>
-      <c r="AD9" s="29"/>
-      <c r="AE9" s="29"/>
-      <c r="AF9" s="29"/>
-      <c r="AG9" s="29"/>
-      <c r="AH9" s="29"/>
-      <c r="AI9" s="29"/>
-      <c r="AJ9" s="29"/>
-      <c r="AK9" s="29"/>
-      <c r="AL9" s="29"/>
-      <c r="AM9" s="29"/>
-      <c r="AN9" s="29"/>
-      <c r="AO9" s="29"/>
-      <c r="AP9" s="29"/>
-      <c r="AQ9" s="29"/>
-      <c r="AR9" s="29"/>
-      <c r="AS9" s="29"/>
-      <c r="AT9" s="29"/>
-      <c r="AU9" s="29"/>
-      <c r="AV9" s="29"/>
-      <c r="AW9" s="29"/>
-      <c r="AX9" s="29"/>
-      <c r="AY9" s="29"/>
-      <c r="AZ9" s="29"/>
-      <c r="BA9" s="29"/>
-      <c r="BB9" s="29"/>
-      <c r="BC9" s="29"/>
-      <c r="BD9" s="29"/>
-      <c r="BE9" s="29"/>
-      <c r="BF9" s="29"/>
-      <c r="BG9" s="29"/>
-      <c r="BH9" s="29"/>
-      <c r="BI9" s="29"/>
-      <c r="BJ9" s="29"/>
-      <c r="BK9" s="29"/>
-      <c r="BL9" s="29"/>
-      <c r="BM9" s="29"/>
-      <c r="BN9" s="29"/>
-      <c r="BO9" s="29"/>
-      <c r="BP9" s="29"/>
-      <c r="BQ9" s="29"/>
-      <c r="BR9" s="29"/>
-      <c r="BS9" s="29"/>
-      <c r="BT9" s="29"/>
-      <c r="BU9" s="29"/>
-      <c r="BV9" s="29"/>
-      <c r="BW9" s="29"/>
-      <c r="BX9" s="29"/>
-      <c r="BY9" s="29"/>
-      <c r="BZ9" s="29"/>
-      <c r="CA9" s="29"/>
-      <c r="CB9" s="29"/>
-      <c r="CC9" s="29"/>
-      <c r="CD9" s="29"/>
-      <c r="CE9" s="29"/>
-      <c r="CF9" s="29"/>
-      <c r="CG9" s="29"/>
-      <c r="CH9" s="29"/>
-      <c r="CI9" s="29"/>
-      <c r="CJ9" s="29"/>
-      <c r="CK9" s="29"/>
-      <c r="CL9" s="29"/>
-      <c r="CM9" s="29"/>
-      <c r="CN9" s="29"/>
-      <c r="CO9" s="29"/>
-      <c r="CP9" s="29"/>
-      <c r="CQ9" s="29"/>
-      <c r="CR9" s="29"/>
-      <c r="CS9" s="29"/>
-      <c r="CT9" s="29"/>
-      <c r="CU9" s="29"/>
-      <c r="CV9" s="29"/>
-      <c r="CW9" s="29"/>
-      <c r="CX9" s="29"/>
-      <c r="CY9" s="29"/>
-      <c r="CZ9" s="29"/>
-      <c r="DA9" s="29"/>
-      <c r="DB9" s="29"/>
-      <c r="DC9" s="29"/>
-      <c r="DD9" s="29"/>
-      <c r="DE9" s="29"/>
-      <c r="DF9" s="29"/>
-      <c r="DG9" s="29"/>
-      <c r="DH9" s="29"/>
-      <c r="DI9" s="29"/>
-      <c r="DJ9" s="29"/>
-      <c r="DK9" s="29"/>
-      <c r="DL9" s="29"/>
-      <c r="DM9" s="29"/>
-      <c r="DN9" s="29"/>
-      <c r="DO9" s="29"/>
-      <c r="DP9" s="29"/>
-      <c r="DQ9" s="29"/>
-      <c r="DR9" s="29"/>
-      <c r="DS9" s="29"/>
-      <c r="DT9" s="29"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="36"/>
+      <c r="K9" s="36"/>
+      <c r="L9" s="36"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="36"/>
+      <c r="S9" s="36"/>
+      <c r="T9" s="36"/>
+      <c r="U9" s="36"/>
+      <c r="V9" s="36"/>
+      <c r="W9" s="36"/>
+      <c r="X9" s="36"/>
+      <c r="Y9" s="36"/>
+      <c r="Z9" s="36"/>
+      <c r="AA9" s="36"/>
+      <c r="AB9" s="36"/>
+      <c r="AC9" s="36"/>
+      <c r="AD9" s="36"/>
+      <c r="AE9" s="36"/>
+      <c r="AF9" s="36"/>
+      <c r="AG9" s="36"/>
+      <c r="AH9" s="36"/>
+      <c r="AI9" s="36"/>
+      <c r="AJ9" s="36"/>
+      <c r="AK9" s="36"/>
+      <c r="AL9" s="36"/>
+      <c r="AM9" s="36"/>
+      <c r="AN9" s="36"/>
+      <c r="AO9" s="36"/>
+      <c r="AP9" s="36"/>
+      <c r="AQ9" s="36"/>
+      <c r="AR9" s="36"/>
+      <c r="AS9" s="36"/>
+      <c r="AT9" s="36"/>
+      <c r="AU9" s="36"/>
+      <c r="AV9" s="36"/>
+      <c r="AW9" s="36"/>
+      <c r="AX9" s="36"/>
+      <c r="AY9" s="36"/>
+      <c r="AZ9" s="36"/>
+      <c r="BA9" s="36"/>
+      <c r="BB9" s="36"/>
+      <c r="BC9" s="36"/>
+      <c r="BD9" s="36"/>
+      <c r="BE9" s="36"/>
+      <c r="BF9" s="36"/>
+      <c r="BG9" s="36"/>
+      <c r="BH9" s="36"/>
+      <c r="BI9" s="36"/>
+      <c r="BJ9" s="36"/>
+      <c r="BK9" s="36"/>
+      <c r="BL9" s="36"/>
+      <c r="BM9" s="36"/>
+      <c r="BN9" s="36"/>
+      <c r="BO9" s="36"/>
+      <c r="BP9" s="36"/>
+      <c r="BQ9" s="36"/>
+      <c r="BR9" s="36"/>
+      <c r="BS9" s="36"/>
+      <c r="BT9" s="36"/>
+      <c r="BU9" s="36"/>
+      <c r="BV9" s="36"/>
+      <c r="BW9" s="36"/>
+      <c r="BX9" s="36"/>
+      <c r="BY9" s="36"/>
+      <c r="BZ9" s="36"/>
+      <c r="CA9" s="36"/>
+      <c r="CB9" s="36"/>
+      <c r="CC9" s="36"/>
+      <c r="CD9" s="36"/>
+      <c r="CE9" s="36"/>
+      <c r="CF9" s="36"/>
+      <c r="CG9" s="36"/>
+      <c r="CH9" s="36"/>
+      <c r="CI9" s="36"/>
+      <c r="CJ9" s="36"/>
+      <c r="CK9" s="36"/>
+      <c r="CL9" s="36"/>
+      <c r="CM9" s="36"/>
+      <c r="CN9" s="36"/>
+      <c r="CO9" s="36"/>
+      <c r="CP9" s="36"/>
+      <c r="CQ9" s="36"/>
+      <c r="CR9" s="36"/>
+      <c r="CS9" s="36"/>
+      <c r="CT9" s="36"/>
+      <c r="CU9" s="36"/>
+      <c r="CV9" s="36"/>
+      <c r="CW9" s="36"/>
+      <c r="CX9" s="36"/>
+      <c r="CY9" s="36"/>
+      <c r="CZ9" s="36"/>
+      <c r="DA9" s="36"/>
+      <c r="DB9" s="36"/>
+      <c r="DC9" s="36"/>
+      <c r="DD9" s="36"/>
+      <c r="DE9" s="36"/>
+      <c r="DF9" s="36"/>
+      <c r="DG9" s="36"/>
+      <c r="DH9" s="36"/>
+      <c r="DI9" s="36"/>
+      <c r="DJ9" s="36"/>
+      <c r="DK9" s="36"/>
+      <c r="DL9" s="36"/>
+      <c r="DM9" s="36"/>
+      <c r="DN9" s="36"/>
+      <c r="DO9" s="36"/>
+      <c r="DP9" s="36"/>
+      <c r="DQ9" s="36"/>
+      <c r="DR9" s="36"/>
+      <c r="DS9" s="36"/>
+      <c r="DT9" s="36"/>
     </row>
     <row r="10" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="36"/>
-      <c r="B10" s="37"/>
+      <c r="A10" s="46"/>
+      <c r="B10" s="56"/>
       <c r="C10" s="6"/>
       <c r="D10" s="4" t="s">
         <v>10</v>
@@ -4798,250 +4818,250 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E26" s="32"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33"/>
-      <c r="K26" s="33"/>
-      <c r="L26" s="33"/>
-      <c r="M26" s="33"/>
-      <c r="N26" s="33"/>
-      <c r="O26" s="33"/>
-      <c r="P26" s="33"/>
-      <c r="Q26" s="33"/>
-      <c r="R26" s="33"/>
-      <c r="S26" s="33"/>
-      <c r="T26" s="33"/>
-      <c r="U26" s="33"/>
-      <c r="V26" s="33"/>
-      <c r="W26" s="33"/>
-      <c r="X26" s="33"/>
-      <c r="Y26" s="33"/>
-      <c r="Z26" s="33"/>
-      <c r="AA26" s="33"/>
-      <c r="AB26" s="33"/>
-      <c r="AC26" s="33"/>
-      <c r="AD26" s="33"/>
-      <c r="AE26" s="33"/>
-      <c r="AF26" s="33"/>
-      <c r="AG26" s="33"/>
-      <c r="AH26" s="33"/>
-      <c r="AI26" s="33"/>
-      <c r="AJ26" s="33"/>
-      <c r="AK26" s="33"/>
-      <c r="AL26" s="33"/>
-      <c r="AM26" s="33"/>
-      <c r="AN26" s="33"/>
-      <c r="AO26" s="33"/>
-      <c r="AP26" s="33"/>
-      <c r="AQ26" s="33"/>
-      <c r="AR26" s="33"/>
-      <c r="AS26" s="33"/>
-      <c r="AT26" s="33"/>
-      <c r="AU26" s="33"/>
-      <c r="AV26" s="33"/>
-      <c r="AW26" s="33"/>
-      <c r="AX26" s="33"/>
-      <c r="AY26" s="33"/>
-      <c r="AZ26" s="33"/>
-      <c r="BA26" s="33"/>
-      <c r="BB26" s="33"/>
-      <c r="BC26" s="33"/>
-      <c r="BD26" s="33"/>
-      <c r="BE26" s="33"/>
-      <c r="BF26" s="33"/>
-      <c r="BG26" s="33"/>
-      <c r="BH26" s="33"/>
-      <c r="BI26" s="33"/>
-      <c r="BJ26" s="33"/>
-      <c r="BK26" s="33"/>
-      <c r="BL26" s="33"/>
-      <c r="BM26" s="33"/>
-      <c r="BN26" s="33"/>
-      <c r="BO26" s="33"/>
-      <c r="BP26" s="33"/>
-      <c r="BQ26" s="33"/>
-      <c r="BR26" s="33"/>
-      <c r="BS26" s="33"/>
-      <c r="BT26" s="33"/>
-      <c r="BU26" s="33"/>
-      <c r="BV26" s="33"/>
-      <c r="BW26" s="33"/>
-      <c r="BX26" s="33"/>
-      <c r="BY26" s="33"/>
-      <c r="BZ26" s="33"/>
-      <c r="CA26" s="33"/>
-      <c r="CB26" s="33"/>
-      <c r="CC26" s="33"/>
-      <c r="CD26" s="33"/>
-      <c r="CE26" s="33"/>
-      <c r="CF26" s="33"/>
-      <c r="CG26" s="33"/>
-      <c r="CH26" s="33"/>
-      <c r="CI26" s="33"/>
-      <c r="CJ26" s="33"/>
-      <c r="CK26" s="33"/>
-      <c r="CL26" s="33"/>
-      <c r="CM26" s="33"/>
-      <c r="CN26" s="33"/>
-      <c r="CO26" s="33"/>
-      <c r="CP26" s="33"/>
-      <c r="CQ26" s="33"/>
-      <c r="CR26" s="33"/>
-      <c r="CS26" s="33"/>
-      <c r="CT26" s="33"/>
-      <c r="CU26" s="33"/>
-      <c r="CV26" s="33"/>
-      <c r="CW26" s="33"/>
-      <c r="CX26" s="33"/>
-      <c r="CY26" s="33"/>
-      <c r="CZ26" s="33"/>
-      <c r="DA26" s="33"/>
-      <c r="DB26" s="33"/>
-      <c r="DC26" s="33"/>
-      <c r="DD26" s="33"/>
-      <c r="DE26" s="33"/>
-      <c r="DF26" s="33"/>
-      <c r="DG26" s="33"/>
-      <c r="DH26" s="33"/>
-      <c r="DI26" s="33"/>
-      <c r="DJ26" s="33"/>
-      <c r="DK26" s="33"/>
-      <c r="DL26" s="33"/>
-      <c r="DM26" s="33"/>
-      <c r="DN26" s="33"/>
-      <c r="DO26" s="33"/>
-      <c r="DP26" s="33"/>
-      <c r="DQ26" s="33"/>
-      <c r="DR26" s="33"/>
-      <c r="DS26" s="33"/>
-      <c r="DT26" s="33"/>
+      <c r="E26" s="55"/>
+      <c r="F26" s="48"/>
+      <c r="G26" s="48"/>
+      <c r="H26" s="48"/>
+      <c r="I26" s="48"/>
+      <c r="J26" s="48"/>
+      <c r="K26" s="48"/>
+      <c r="L26" s="48"/>
+      <c r="M26" s="48"/>
+      <c r="N26" s="48"/>
+      <c r="O26" s="48"/>
+      <c r="P26" s="48"/>
+      <c r="Q26" s="48"/>
+      <c r="R26" s="48"/>
+      <c r="S26" s="48"/>
+      <c r="T26" s="48"/>
+      <c r="U26" s="48"/>
+      <c r="V26" s="48"/>
+      <c r="W26" s="48"/>
+      <c r="X26" s="48"/>
+      <c r="Y26" s="48"/>
+      <c r="Z26" s="48"/>
+      <c r="AA26" s="48"/>
+      <c r="AB26" s="48"/>
+      <c r="AC26" s="48"/>
+      <c r="AD26" s="48"/>
+      <c r="AE26" s="48"/>
+      <c r="AF26" s="48"/>
+      <c r="AG26" s="48"/>
+      <c r="AH26" s="48"/>
+      <c r="AI26" s="48"/>
+      <c r="AJ26" s="48"/>
+      <c r="AK26" s="48"/>
+      <c r="AL26" s="48"/>
+      <c r="AM26" s="48"/>
+      <c r="AN26" s="48"/>
+      <c r="AO26" s="48"/>
+      <c r="AP26" s="48"/>
+      <c r="AQ26" s="48"/>
+      <c r="AR26" s="48"/>
+      <c r="AS26" s="48"/>
+      <c r="AT26" s="48"/>
+      <c r="AU26" s="48"/>
+      <c r="AV26" s="48"/>
+      <c r="AW26" s="48"/>
+      <c r="AX26" s="48"/>
+      <c r="AY26" s="48"/>
+      <c r="AZ26" s="48"/>
+      <c r="BA26" s="48"/>
+      <c r="BB26" s="48"/>
+      <c r="BC26" s="48"/>
+      <c r="BD26" s="48"/>
+      <c r="BE26" s="48"/>
+      <c r="BF26" s="48"/>
+      <c r="BG26" s="48"/>
+      <c r="BH26" s="48"/>
+      <c r="BI26" s="48"/>
+      <c r="BJ26" s="48"/>
+      <c r="BK26" s="48"/>
+      <c r="BL26" s="48"/>
+      <c r="BM26" s="48"/>
+      <c r="BN26" s="48"/>
+      <c r="BO26" s="48"/>
+      <c r="BP26" s="48"/>
+      <c r="BQ26" s="48"/>
+      <c r="BR26" s="48"/>
+      <c r="BS26" s="48"/>
+      <c r="BT26" s="48"/>
+      <c r="BU26" s="48"/>
+      <c r="BV26" s="48"/>
+      <c r="BW26" s="48"/>
+      <c r="BX26" s="48"/>
+      <c r="BY26" s="48"/>
+      <c r="BZ26" s="48"/>
+      <c r="CA26" s="48"/>
+      <c r="CB26" s="48"/>
+      <c r="CC26" s="48"/>
+      <c r="CD26" s="48"/>
+      <c r="CE26" s="48"/>
+      <c r="CF26" s="48"/>
+      <c r="CG26" s="48"/>
+      <c r="CH26" s="48"/>
+      <c r="CI26" s="48"/>
+      <c r="CJ26" s="48"/>
+      <c r="CK26" s="48"/>
+      <c r="CL26" s="48"/>
+      <c r="CM26" s="48"/>
+      <c r="CN26" s="48"/>
+      <c r="CO26" s="48"/>
+      <c r="CP26" s="48"/>
+      <c r="CQ26" s="48"/>
+      <c r="CR26" s="48"/>
+      <c r="CS26" s="48"/>
+      <c r="CT26" s="48"/>
+      <c r="CU26" s="48"/>
+      <c r="CV26" s="48"/>
+      <c r="CW26" s="48"/>
+      <c r="CX26" s="48"/>
+      <c r="CY26" s="48"/>
+      <c r="CZ26" s="48"/>
+      <c r="DA26" s="48"/>
+      <c r="DB26" s="48"/>
+      <c r="DC26" s="48"/>
+      <c r="DD26" s="48"/>
+      <c r="DE26" s="48"/>
+      <c r="DF26" s="48"/>
+      <c r="DG26" s="48"/>
+      <c r="DH26" s="48"/>
+      <c r="DI26" s="48"/>
+      <c r="DJ26" s="48"/>
+      <c r="DK26" s="48"/>
+      <c r="DL26" s="48"/>
+      <c r="DM26" s="48"/>
+      <c r="DN26" s="48"/>
+      <c r="DO26" s="48"/>
+      <c r="DP26" s="48"/>
+      <c r="DQ26" s="48"/>
+      <c r="DR26" s="48"/>
+      <c r="DS26" s="48"/>
+      <c r="DT26" s="48"/>
     </row>
     <row r="27" spans="1:124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E27" s="1">
         <v>4</v>
       </c>
-      <c r="F27" s="53"/>
-      <c r="G27" s="53"/>
-      <c r="H27" s="53"/>
-      <c r="I27" s="53"/>
-      <c r="J27" s="53"/>
-      <c r="K27" s="53"/>
-      <c r="L27" s="53"/>
-      <c r="M27" s="53"/>
-      <c r="N27" s="53"/>
-      <c r="O27" s="53"/>
-      <c r="P27" s="53"/>
-      <c r="Q27" s="53"/>
-      <c r="R27" s="53"/>
-      <c r="S27" s="53"/>
-      <c r="T27" s="53"/>
-      <c r="U27" s="53"/>
-      <c r="V27" s="53"/>
-      <c r="W27" s="53"/>
-      <c r="X27" s="53"/>
-      <c r="Y27" s="53"/>
-      <c r="Z27" s="53"/>
-      <c r="AA27" s="53"/>
-      <c r="AB27" s="53"/>
-      <c r="AC27" s="53"/>
-      <c r="AD27" s="53"/>
-      <c r="AE27" s="53"/>
-      <c r="AF27" s="53"/>
-      <c r="AG27" s="53"/>
-      <c r="AH27" s="53"/>
-      <c r="AI27" s="53"/>
-      <c r="AJ27" s="53"/>
-      <c r="AK27" s="53"/>
-      <c r="AL27" s="53"/>
-      <c r="AM27" s="53"/>
-      <c r="AN27" s="53"/>
-      <c r="AO27" s="53"/>
-      <c r="AP27" s="53"/>
-      <c r="AQ27" s="53"/>
-      <c r="AR27" s="53"/>
-      <c r="AS27" s="53"/>
-      <c r="AT27" s="53"/>
-      <c r="AU27" s="53"/>
-      <c r="AV27" s="53"/>
-      <c r="AW27" s="53"/>
-      <c r="AX27" s="53"/>
-      <c r="AY27" s="53"/>
-      <c r="AZ27" s="53"/>
-      <c r="BA27" s="53"/>
-      <c r="BB27" s="53"/>
-      <c r="BC27" s="53"/>
-      <c r="BD27" s="53"/>
-      <c r="BE27" s="53"/>
-      <c r="BF27" s="53"/>
-      <c r="BG27" s="53"/>
-      <c r="BH27" s="53"/>
-      <c r="BI27" s="53"/>
-      <c r="BJ27" s="53"/>
-      <c r="BK27" s="53"/>
-      <c r="BL27" s="53"/>
-      <c r="BM27" s="53"/>
-      <c r="BN27" s="53"/>
-      <c r="BO27" s="53"/>
-      <c r="BP27" s="53"/>
-      <c r="BQ27" s="53"/>
-      <c r="BR27" s="53"/>
-      <c r="BS27" s="53"/>
-      <c r="BT27" s="53"/>
-      <c r="BU27" s="53"/>
-      <c r="BV27" s="53"/>
-      <c r="BW27" s="53"/>
-      <c r="BX27" s="53"/>
-      <c r="BY27" s="53"/>
-      <c r="BZ27" s="53"/>
-      <c r="CA27" s="53"/>
-      <c r="CB27" s="53"/>
-      <c r="CC27" s="53"/>
-      <c r="CD27" s="53"/>
-      <c r="CE27" s="54"/>
-      <c r="CF27" s="55"/>
-      <c r="CG27" s="55"/>
-      <c r="CH27" s="55"/>
-      <c r="CI27" s="55"/>
-      <c r="CJ27" s="55"/>
-      <c r="CK27" s="55"/>
-      <c r="CL27" s="55"/>
-      <c r="CM27" s="55"/>
-      <c r="CN27" s="55"/>
-      <c r="CO27" s="55"/>
-      <c r="CP27" s="55"/>
-      <c r="CQ27" s="55"/>
-      <c r="CR27" s="55"/>
-      <c r="CS27" s="55"/>
-      <c r="CT27" s="55"/>
-      <c r="CU27" s="55"/>
-      <c r="CV27" s="55"/>
-      <c r="CW27" s="55"/>
-      <c r="CX27" s="55"/>
-      <c r="CY27" s="55"/>
-      <c r="CZ27" s="55"/>
-      <c r="DA27" s="55"/>
-      <c r="DB27" s="55"/>
-      <c r="DC27" s="55"/>
-      <c r="DD27" s="55"/>
-      <c r="DE27" s="55"/>
-      <c r="DF27" s="55"/>
-      <c r="DG27" s="55"/>
-      <c r="DH27" s="55"/>
-      <c r="DI27" s="55"/>
-      <c r="DJ27" s="55"/>
-      <c r="DK27" s="55"/>
-      <c r="DL27" s="55"/>
-      <c r="DM27" s="55"/>
-      <c r="DN27" s="55"/>
-      <c r="DO27" s="55"/>
-      <c r="DP27" s="55"/>
-      <c r="DQ27" s="55"/>
-      <c r="DR27" s="55"/>
-      <c r="DS27" s="55"/>
-      <c r="DT27" s="55"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="32"/>
+      <c r="J27" s="32"/>
+      <c r="K27" s="32"/>
+      <c r="L27" s="32"/>
+      <c r="M27" s="32"/>
+      <c r="N27" s="32"/>
+      <c r="O27" s="32"/>
+      <c r="P27" s="32"/>
+      <c r="Q27" s="32"/>
+      <c r="R27" s="32"/>
+      <c r="S27" s="32"/>
+      <c r="T27" s="32"/>
+      <c r="U27" s="32"/>
+      <c r="V27" s="32"/>
+      <c r="W27" s="32"/>
+      <c r="X27" s="32"/>
+      <c r="Y27" s="32"/>
+      <c r="Z27" s="32"/>
+      <c r="AA27" s="32"/>
+      <c r="AB27" s="32"/>
+      <c r="AC27" s="32"/>
+      <c r="AD27" s="32"/>
+      <c r="AE27" s="32"/>
+      <c r="AF27" s="32"/>
+      <c r="AG27" s="32"/>
+      <c r="AH27" s="32"/>
+      <c r="AI27" s="32"/>
+      <c r="AJ27" s="32"/>
+      <c r="AK27" s="32"/>
+      <c r="AL27" s="32"/>
+      <c r="AM27" s="32"/>
+      <c r="AN27" s="32"/>
+      <c r="AO27" s="32"/>
+      <c r="AP27" s="32"/>
+      <c r="AQ27" s="32"/>
+      <c r="AR27" s="32"/>
+      <c r="AS27" s="32"/>
+      <c r="AT27" s="32"/>
+      <c r="AU27" s="32"/>
+      <c r="AV27" s="32"/>
+      <c r="AW27" s="32"/>
+      <c r="AX27" s="32"/>
+      <c r="AY27" s="32"/>
+      <c r="AZ27" s="32"/>
+      <c r="BA27" s="32"/>
+      <c r="BB27" s="32"/>
+      <c r="BC27" s="32"/>
+      <c r="BD27" s="32"/>
+      <c r="BE27" s="32"/>
+      <c r="BF27" s="32"/>
+      <c r="BG27" s="32"/>
+      <c r="BH27" s="32"/>
+      <c r="BI27" s="32"/>
+      <c r="BJ27" s="32"/>
+      <c r="BK27" s="32"/>
+      <c r="BL27" s="32"/>
+      <c r="BM27" s="32"/>
+      <c r="BN27" s="32"/>
+      <c r="BO27" s="32"/>
+      <c r="BP27" s="32"/>
+      <c r="BQ27" s="32"/>
+      <c r="BR27" s="32"/>
+      <c r="BS27" s="32"/>
+      <c r="BT27" s="32"/>
+      <c r="BU27" s="32"/>
+      <c r="BV27" s="32"/>
+      <c r="BW27" s="32"/>
+      <c r="BX27" s="32"/>
+      <c r="BY27" s="32"/>
+      <c r="BZ27" s="32"/>
+      <c r="CA27" s="32"/>
+      <c r="CB27" s="32"/>
+      <c r="CC27" s="32"/>
+      <c r="CD27" s="32"/>
+      <c r="CE27" s="33"/>
+      <c r="CF27" s="34"/>
+      <c r="CG27" s="34"/>
+      <c r="CH27" s="34"/>
+      <c r="CI27" s="34"/>
+      <c r="CJ27" s="34"/>
+      <c r="CK27" s="34"/>
+      <c r="CL27" s="34"/>
+      <c r="CM27" s="34"/>
+      <c r="CN27" s="34"/>
+      <c r="CO27" s="34"/>
+      <c r="CP27" s="34"/>
+      <c r="CQ27" s="34"/>
+      <c r="CR27" s="34"/>
+      <c r="CS27" s="34"/>
+      <c r="CT27" s="34"/>
+      <c r="CU27" s="34"/>
+      <c r="CV27" s="34"/>
+      <c r="CW27" s="34"/>
+      <c r="CX27" s="34"/>
+      <c r="CY27" s="34"/>
+      <c r="CZ27" s="34"/>
+      <c r="DA27" s="34"/>
+      <c r="DB27" s="34"/>
+      <c r="DC27" s="34"/>
+      <c r="DD27" s="34"/>
+      <c r="DE27" s="34"/>
+      <c r="DF27" s="34"/>
+      <c r="DG27" s="34"/>
+      <c r="DH27" s="34"/>
+      <c r="DI27" s="34"/>
+      <c r="DJ27" s="34"/>
+      <c r="DK27" s="34"/>
+      <c r="DL27" s="34"/>
+      <c r="DM27" s="34"/>
+      <c r="DN27" s="34"/>
+      <c r="DO27" s="34"/>
+      <c r="DP27" s="34"/>
+      <c r="DQ27" s="34"/>
+      <c r="DR27" s="34"/>
+      <c r="DS27" s="34"/>
+      <c r="DT27" s="34"/>
     </row>
     <row r="29" spans="1:124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E29" s="22">
@@ -5066,7 +5086,248 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="264">
+  <mergeCells count="265">
+    <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="N1:Q1"/>
+    <mergeCell ref="BC8:BC9"/>
+    <mergeCell ref="BD8:BD9"/>
+    <mergeCell ref="BE8:BE9"/>
+    <mergeCell ref="AN8:AN9"/>
+    <mergeCell ref="AO8:AO9"/>
+    <mergeCell ref="AP8:AP9"/>
+    <mergeCell ref="AQ8:AQ9"/>
+    <mergeCell ref="AR8:AR9"/>
+    <mergeCell ref="AS8:AS9"/>
+    <mergeCell ref="AT8:AT9"/>
+    <mergeCell ref="AU8:AU9"/>
+    <mergeCell ref="AV8:AV9"/>
+    <mergeCell ref="AE8:AE9"/>
+    <mergeCell ref="AF8:AF9"/>
+    <mergeCell ref="AG8:AG9"/>
+    <mergeCell ref="AH8:AH9"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AJ8:AJ9"/>
+    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="AL8:AL9"/>
+    <mergeCell ref="AM8:AM9"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="BO8:BO9"/>
+    <mergeCell ref="BP8:BP9"/>
+    <mergeCell ref="BQ8:BQ9"/>
+    <mergeCell ref="BR8:BR9"/>
+    <mergeCell ref="BS8:BS9"/>
+    <mergeCell ref="BT8:BT9"/>
+    <mergeCell ref="BZ8:BZ9"/>
+    <mergeCell ref="CA8:CA9"/>
+    <mergeCell ref="BH8:BH9"/>
+    <mergeCell ref="BI8:BI9"/>
+    <mergeCell ref="BJ8:BJ9"/>
+    <mergeCell ref="BK8:BK9"/>
+    <mergeCell ref="BL8:BL9"/>
+    <mergeCell ref="BM8:BM9"/>
+    <mergeCell ref="CB8:CB9"/>
+    <mergeCell ref="CC8:CC9"/>
+    <mergeCell ref="CD8:CD9"/>
+    <mergeCell ref="CE8:CE9"/>
+    <mergeCell ref="CF8:CF9"/>
+    <mergeCell ref="CV8:CV9"/>
+    <mergeCell ref="BQ2:BQ7"/>
+    <mergeCell ref="BR2:BR7"/>
+    <mergeCell ref="BS2:BS7"/>
+    <mergeCell ref="BT2:BT7"/>
+    <mergeCell ref="BU2:BU7"/>
+    <mergeCell ref="BV2:BV7"/>
+    <mergeCell ref="CO8:CO9"/>
+    <mergeCell ref="CP8:CP9"/>
+    <mergeCell ref="CH2:CH7"/>
+    <mergeCell ref="CT8:CT9"/>
+    <mergeCell ref="CU8:CU9"/>
+    <mergeCell ref="CB2:CB7"/>
+    <mergeCell ref="CC2:CC7"/>
+    <mergeCell ref="CD2:CD7"/>
+    <mergeCell ref="CE2:CE7"/>
+    <mergeCell ref="CF2:CF7"/>
+    <mergeCell ref="CG2:CG7"/>
+    <mergeCell ref="CJ8:CJ9"/>
+    <mergeCell ref="E26:DT26"/>
+    <mergeCell ref="DF8:DF9"/>
+    <mergeCell ref="DQ8:DQ9"/>
+    <mergeCell ref="DR8:DR9"/>
+    <mergeCell ref="DS8:DS9"/>
+    <mergeCell ref="DT8:DT9"/>
+    <mergeCell ref="CY8:CY9"/>
+    <mergeCell ref="CZ8:CZ9"/>
+    <mergeCell ref="CM8:CM9"/>
+    <mergeCell ref="CW8:CW9"/>
+    <mergeCell ref="CX8:CX9"/>
+    <mergeCell ref="BU8:BU9"/>
+    <mergeCell ref="BV8:BV9"/>
+    <mergeCell ref="BW8:BW9"/>
+    <mergeCell ref="BF8:BF9"/>
+    <mergeCell ref="BG8:BG9"/>
+    <mergeCell ref="CG8:CG9"/>
+    <mergeCell ref="CH8:CH9"/>
+    <mergeCell ref="AW8:AW9"/>
+    <mergeCell ref="AX8:AX9"/>
+    <mergeCell ref="AY8:AY9"/>
+    <mergeCell ref="AZ8:AZ9"/>
+    <mergeCell ref="BA8:BA9"/>
+    <mergeCell ref="BB8:BB9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="F2:F7"/>
+    <mergeCell ref="G2:G7"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="I2:I7"/>
+    <mergeCell ref="J2:J7"/>
+    <mergeCell ref="K2:K7"/>
+    <mergeCell ref="L2:L7"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="M2:M7"/>
+    <mergeCell ref="N2:N7"/>
+    <mergeCell ref="O2:O7"/>
+    <mergeCell ref="P2:P7"/>
+    <mergeCell ref="Q2:Q7"/>
+    <mergeCell ref="R2:R7"/>
+    <mergeCell ref="S2:S7"/>
+    <mergeCell ref="T2:T7"/>
+    <mergeCell ref="CN8:CN9"/>
+    <mergeCell ref="Y2:Y7"/>
+    <mergeCell ref="Z2:Z7"/>
+    <mergeCell ref="AA2:AA7"/>
+    <mergeCell ref="AB2:AB7"/>
+    <mergeCell ref="AC2:AC7"/>
+    <mergeCell ref="AD2:AD7"/>
+    <mergeCell ref="AE2:AE7"/>
+    <mergeCell ref="AH2:AH7"/>
+    <mergeCell ref="AI2:AI7"/>
+    <mergeCell ref="AJ2:AJ7"/>
+    <mergeCell ref="AK2:AK7"/>
+    <mergeCell ref="AL2:AL7"/>
+    <mergeCell ref="AM2:AM7"/>
+    <mergeCell ref="AN2:AN7"/>
+    <mergeCell ref="AO2:AO7"/>
+    <mergeCell ref="AG2:AG7"/>
+    <mergeCell ref="CW2:CW7"/>
+    <mergeCell ref="CU2:CU7"/>
+    <mergeCell ref="CV2:CV7"/>
+    <mergeCell ref="CQ2:CQ7"/>
+    <mergeCell ref="CR2:CR7"/>
+    <mergeCell ref="CS2:CS7"/>
+    <mergeCell ref="CT2:CT7"/>
+    <mergeCell ref="CI2:CI7"/>
+    <mergeCell ref="CJ2:CJ7"/>
+    <mergeCell ref="CK2:CK7"/>
+    <mergeCell ref="CL2:CL7"/>
+    <mergeCell ref="CM2:CM7"/>
+    <mergeCell ref="CN2:CN7"/>
+    <mergeCell ref="CO2:CO7"/>
+    <mergeCell ref="CP2:CP7"/>
+    <mergeCell ref="BK2:BK7"/>
+    <mergeCell ref="X2:X7"/>
+    <mergeCell ref="AF2:AF7"/>
+    <mergeCell ref="AX2:AX7"/>
+    <mergeCell ref="AY2:AY7"/>
+    <mergeCell ref="AZ2:AZ7"/>
+    <mergeCell ref="BL2:BL7"/>
+    <mergeCell ref="BA2:BA7"/>
+    <mergeCell ref="BB2:BB7"/>
+    <mergeCell ref="BC2:BC7"/>
+    <mergeCell ref="AP2:AP7"/>
+    <mergeCell ref="AQ2:AQ7"/>
+    <mergeCell ref="AR2:AR7"/>
+    <mergeCell ref="AS2:AS7"/>
+    <mergeCell ref="AT2:AT7"/>
+    <mergeCell ref="AU2:AU7"/>
+    <mergeCell ref="AV2:AV7"/>
+    <mergeCell ref="AW2:AW7"/>
+    <mergeCell ref="CI8:CI9"/>
+    <mergeCell ref="CK8:CK9"/>
+    <mergeCell ref="CL8:CL9"/>
+    <mergeCell ref="BX8:BX9"/>
+    <mergeCell ref="BY8:BY9"/>
+    <mergeCell ref="DL2:DL7"/>
+    <mergeCell ref="DM2:DM7"/>
+    <mergeCell ref="DF2:DF7"/>
+    <mergeCell ref="BD2:BD7"/>
+    <mergeCell ref="BE2:BE7"/>
+    <mergeCell ref="BF2:BF7"/>
+    <mergeCell ref="BG2:BG7"/>
+    <mergeCell ref="BM2:BM7"/>
+    <mergeCell ref="BN2:BN7"/>
+    <mergeCell ref="BO2:BO7"/>
+    <mergeCell ref="BP2:BP7"/>
+    <mergeCell ref="CA2:CA7"/>
+    <mergeCell ref="BW2:BW7"/>
+    <mergeCell ref="BX2:BX7"/>
+    <mergeCell ref="BY2:BY7"/>
+    <mergeCell ref="BZ2:BZ7"/>
+    <mergeCell ref="BH2:BH7"/>
+    <mergeCell ref="BI2:BI7"/>
+    <mergeCell ref="BJ2:BJ7"/>
+    <mergeCell ref="W2:W7"/>
+    <mergeCell ref="F27:S27"/>
+    <mergeCell ref="T27:AW27"/>
+    <mergeCell ref="AX27:CD27"/>
+    <mergeCell ref="CE27:DT27"/>
+    <mergeCell ref="DG8:DG9"/>
+    <mergeCell ref="DH8:DH9"/>
+    <mergeCell ref="DI8:DI9"/>
+    <mergeCell ref="DJ8:DJ9"/>
+    <mergeCell ref="DK8:DK9"/>
+    <mergeCell ref="DL8:DL9"/>
+    <mergeCell ref="DM8:DM9"/>
+    <mergeCell ref="DN8:DN9"/>
+    <mergeCell ref="DO8:DO9"/>
+    <mergeCell ref="DP8:DP9"/>
+    <mergeCell ref="DA8:DA9"/>
+    <mergeCell ref="DB8:DB9"/>
+    <mergeCell ref="DC8:DC9"/>
+    <mergeCell ref="DD8:DD9"/>
+    <mergeCell ref="DE8:DE9"/>
+    <mergeCell ref="CQ8:CQ9"/>
+    <mergeCell ref="CR8:CR9"/>
+    <mergeCell ref="CS8:CS9"/>
+    <mergeCell ref="BN8:BN9"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="R1:U1"/>
     <mergeCell ref="DQ2:DQ7"/>
@@ -5091,246 +5352,6 @@
     <mergeCell ref="DK2:DK7"/>
     <mergeCell ref="U2:U7"/>
     <mergeCell ref="V2:V7"/>
-    <mergeCell ref="W2:W7"/>
-    <mergeCell ref="F27:S27"/>
-    <mergeCell ref="T27:AW27"/>
-    <mergeCell ref="AX27:CD27"/>
-    <mergeCell ref="CE27:DT27"/>
-    <mergeCell ref="DG8:DG9"/>
-    <mergeCell ref="DH8:DH9"/>
-    <mergeCell ref="DI8:DI9"/>
-    <mergeCell ref="DJ8:DJ9"/>
-    <mergeCell ref="DK8:DK9"/>
-    <mergeCell ref="DL8:DL9"/>
-    <mergeCell ref="DM8:DM9"/>
-    <mergeCell ref="DN8:DN9"/>
-    <mergeCell ref="DO8:DO9"/>
-    <mergeCell ref="DP8:DP9"/>
-    <mergeCell ref="DA8:DA9"/>
-    <mergeCell ref="DB8:DB9"/>
-    <mergeCell ref="DC8:DC9"/>
-    <mergeCell ref="DD8:DD9"/>
-    <mergeCell ref="DE8:DE9"/>
-    <mergeCell ref="CQ8:CQ9"/>
-    <mergeCell ref="CR8:CR9"/>
-    <mergeCell ref="CS8:CS9"/>
-    <mergeCell ref="BN8:BN9"/>
-    <mergeCell ref="CI8:CI9"/>
-    <mergeCell ref="CK8:CK9"/>
-    <mergeCell ref="CL8:CL9"/>
-    <mergeCell ref="BX8:BX9"/>
-    <mergeCell ref="BY8:BY9"/>
-    <mergeCell ref="DL2:DL7"/>
-    <mergeCell ref="DM2:DM7"/>
-    <mergeCell ref="DF2:DF7"/>
-    <mergeCell ref="BD2:BD7"/>
-    <mergeCell ref="BE2:BE7"/>
-    <mergeCell ref="BF2:BF7"/>
-    <mergeCell ref="BG2:BG7"/>
-    <mergeCell ref="BM2:BM7"/>
-    <mergeCell ref="BN2:BN7"/>
-    <mergeCell ref="BO2:BO7"/>
-    <mergeCell ref="BP2:BP7"/>
-    <mergeCell ref="CA2:CA7"/>
-    <mergeCell ref="BW2:BW7"/>
-    <mergeCell ref="BX2:BX7"/>
-    <mergeCell ref="BY2:BY7"/>
-    <mergeCell ref="BZ2:BZ7"/>
-    <mergeCell ref="BH2:BH7"/>
-    <mergeCell ref="BI2:BI7"/>
-    <mergeCell ref="BJ2:BJ7"/>
-    <mergeCell ref="BK2:BK7"/>
-    <mergeCell ref="X2:X7"/>
-    <mergeCell ref="AF2:AF7"/>
-    <mergeCell ref="AX2:AX7"/>
-    <mergeCell ref="AY2:AY7"/>
-    <mergeCell ref="AZ2:AZ7"/>
-    <mergeCell ref="BL2:BL7"/>
-    <mergeCell ref="BA2:BA7"/>
-    <mergeCell ref="BB2:BB7"/>
-    <mergeCell ref="BC2:BC7"/>
-    <mergeCell ref="AP2:AP7"/>
-    <mergeCell ref="AQ2:AQ7"/>
-    <mergeCell ref="AR2:AR7"/>
-    <mergeCell ref="AS2:AS7"/>
-    <mergeCell ref="AT2:AT7"/>
-    <mergeCell ref="AU2:AU7"/>
-    <mergeCell ref="AV2:AV7"/>
-    <mergeCell ref="AW2:AW7"/>
-    <mergeCell ref="CW2:CW7"/>
-    <mergeCell ref="CU2:CU7"/>
-    <mergeCell ref="CV2:CV7"/>
-    <mergeCell ref="CQ2:CQ7"/>
-    <mergeCell ref="CR2:CR7"/>
-    <mergeCell ref="CS2:CS7"/>
-    <mergeCell ref="CT2:CT7"/>
-    <mergeCell ref="CI2:CI7"/>
-    <mergeCell ref="CJ2:CJ7"/>
-    <mergeCell ref="CK2:CK7"/>
-    <mergeCell ref="CL2:CL7"/>
-    <mergeCell ref="CM2:CM7"/>
-    <mergeCell ref="CN2:CN7"/>
-    <mergeCell ref="CO2:CO7"/>
-    <mergeCell ref="CP2:CP7"/>
-    <mergeCell ref="N2:N7"/>
-    <mergeCell ref="O2:O7"/>
-    <mergeCell ref="P2:P7"/>
-    <mergeCell ref="Q2:Q7"/>
-    <mergeCell ref="R2:R7"/>
-    <mergeCell ref="S2:S7"/>
-    <mergeCell ref="T2:T7"/>
-    <mergeCell ref="CN8:CN9"/>
-    <mergeCell ref="Y2:Y7"/>
-    <mergeCell ref="Z2:Z7"/>
-    <mergeCell ref="AA2:AA7"/>
-    <mergeCell ref="AB2:AB7"/>
-    <mergeCell ref="AC2:AC7"/>
-    <mergeCell ref="AD2:AD7"/>
-    <mergeCell ref="AE2:AE7"/>
-    <mergeCell ref="AH2:AH7"/>
-    <mergeCell ref="AI2:AI7"/>
-    <mergeCell ref="AJ2:AJ7"/>
-    <mergeCell ref="AK2:AK7"/>
-    <mergeCell ref="AL2:AL7"/>
-    <mergeCell ref="AM2:AM7"/>
-    <mergeCell ref="AN2:AN7"/>
-    <mergeCell ref="AO2:AO7"/>
-    <mergeCell ref="AG2:AG7"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="F2:F7"/>
-    <mergeCell ref="G2:G7"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="I2:I7"/>
-    <mergeCell ref="J2:J7"/>
-    <mergeCell ref="K2:K7"/>
-    <mergeCell ref="L2:L7"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="M2:M7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="E26:DT26"/>
-    <mergeCell ref="DF8:DF9"/>
-    <mergeCell ref="DQ8:DQ9"/>
-    <mergeCell ref="DR8:DR9"/>
-    <mergeCell ref="DS8:DS9"/>
-    <mergeCell ref="DT8:DT9"/>
-    <mergeCell ref="CY8:CY9"/>
-    <mergeCell ref="CZ8:CZ9"/>
-    <mergeCell ref="CM8:CM9"/>
-    <mergeCell ref="CW8:CW9"/>
-    <mergeCell ref="CX8:CX9"/>
-    <mergeCell ref="BU8:BU9"/>
-    <mergeCell ref="BV8:BV9"/>
-    <mergeCell ref="BW8:BW9"/>
-    <mergeCell ref="BF8:BF9"/>
-    <mergeCell ref="BG8:BG9"/>
-    <mergeCell ref="CG8:CG9"/>
-    <mergeCell ref="CH8:CH9"/>
-    <mergeCell ref="AW8:AW9"/>
-    <mergeCell ref="AX8:AX9"/>
-    <mergeCell ref="AY8:AY9"/>
-    <mergeCell ref="AZ8:AZ9"/>
-    <mergeCell ref="BA8:BA9"/>
-    <mergeCell ref="BB8:BB9"/>
-    <mergeCell ref="CB8:CB9"/>
-    <mergeCell ref="CC8:CC9"/>
-    <mergeCell ref="CD8:CD9"/>
-    <mergeCell ref="CE8:CE9"/>
-    <mergeCell ref="CF8:CF9"/>
-    <mergeCell ref="CV8:CV9"/>
-    <mergeCell ref="BQ2:BQ7"/>
-    <mergeCell ref="BR2:BR7"/>
-    <mergeCell ref="BS2:BS7"/>
-    <mergeCell ref="BT2:BT7"/>
-    <mergeCell ref="BU2:BU7"/>
-    <mergeCell ref="BV2:BV7"/>
-    <mergeCell ref="CO8:CO9"/>
-    <mergeCell ref="CP8:CP9"/>
-    <mergeCell ref="CH2:CH7"/>
-    <mergeCell ref="CT8:CT9"/>
-    <mergeCell ref="CU8:CU9"/>
-    <mergeCell ref="CB2:CB7"/>
-    <mergeCell ref="CC2:CC7"/>
-    <mergeCell ref="CD2:CD7"/>
-    <mergeCell ref="CE2:CE7"/>
-    <mergeCell ref="CF2:CF7"/>
-    <mergeCell ref="CG2:CG7"/>
-    <mergeCell ref="CJ8:CJ9"/>
-    <mergeCell ref="BO8:BO9"/>
-    <mergeCell ref="BP8:BP9"/>
-    <mergeCell ref="BQ8:BQ9"/>
-    <mergeCell ref="BR8:BR9"/>
-    <mergeCell ref="BS8:BS9"/>
-    <mergeCell ref="BT8:BT9"/>
-    <mergeCell ref="BZ8:BZ9"/>
-    <mergeCell ref="CA8:CA9"/>
-    <mergeCell ref="BH8:BH9"/>
-    <mergeCell ref="BI8:BI9"/>
-    <mergeCell ref="BJ8:BJ9"/>
-    <mergeCell ref="BK8:BK9"/>
-    <mergeCell ref="BL8:BL9"/>
-    <mergeCell ref="BM8:BM9"/>
-    <mergeCell ref="N1:Q1"/>
-    <mergeCell ref="BC8:BC9"/>
-    <mergeCell ref="BD8:BD9"/>
-    <mergeCell ref="BE8:BE9"/>
-    <mergeCell ref="AN8:AN9"/>
-    <mergeCell ref="AO8:AO9"/>
-    <mergeCell ref="AP8:AP9"/>
-    <mergeCell ref="AQ8:AQ9"/>
-    <mergeCell ref="AR8:AR9"/>
-    <mergeCell ref="AS8:AS9"/>
-    <mergeCell ref="AT8:AT9"/>
-    <mergeCell ref="AU8:AU9"/>
-    <mergeCell ref="AV8:AV9"/>
-    <mergeCell ref="AE8:AE9"/>
-    <mergeCell ref="AF8:AF9"/>
-    <mergeCell ref="AG8:AG9"/>
-    <mergeCell ref="AH8:AH9"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AJ8:AJ9"/>
-    <mergeCell ref="AK8:AK9"/>
-    <mergeCell ref="AL8:AL9"/>
-    <mergeCell ref="AM8:AM9"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="W8:W9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -5352,49 +5373,49 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="57" t="s">
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="59" t="s">
+      <c r="B3" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="60"/>
-      <c r="D3" s="63" t="s">
+      <c r="C3" s="62"/>
+      <c r="D3" s="65" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="56" t="s">
+      <c r="E3" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="56" t="s">
+      <c r="F3" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="56" t="s">
+      <c r="G3" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="H3" s="57" t="s">
+      <c r="H3" s="59" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="36"/>
-      <c r="B4" s="61"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="57"/>
+      <c r="A4" s="46"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="59"/>
     </row>
     <row r="5" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9">

--- a/Journals/Angular ჟურნალი.xlsx
+++ b/Journals/Angular ჟურნალი.xlsx
@@ -557,32 +557,38 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="2" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -612,16 +618,7 @@
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -635,17 +632,26 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="14" fontId="16" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="14" fontId="16" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -673,12 +679,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="16" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="16" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -914,12 +914,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="39"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="41"/>
       <c r="F1" s="25">
         <v>8</v>
       </c>
@@ -954,10 +954,12 @@
       <c r="AA1" s="26"/>
       <c r="AB1" s="26"/>
       <c r="AC1" s="27"/>
-      <c r="AD1" s="23"/>
-      <c r="AE1" s="23"/>
-      <c r="AF1" s="23"/>
-      <c r="AG1" s="23"/>
+      <c r="AD1" s="25">
+        <v>4</v>
+      </c>
+      <c r="AE1" s="26"/>
+      <c r="AF1" s="26"/>
+      <c r="AG1" s="27"/>
       <c r="AH1" s="23"/>
       <c r="AI1" s="23"/>
       <c r="AJ1" s="23"/>
@@ -1051,1337 +1053,1345 @@
       <c r="DT1" s="24"/>
       <c r="DU1" s="1">
         <f>SUM(F1:DT1)</f>
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:125" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="40"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="43" t="s">
+      <c r="A2" s="42"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="28">
+      <c r="F2" s="30">
         <v>46276</v>
       </c>
-      <c r="G2" s="28">
+      <c r="G2" s="30">
         <v>46276</v>
       </c>
-      <c r="H2" s="28">
+      <c r="H2" s="30">
         <v>46276</v>
       </c>
-      <c r="I2" s="28">
+      <c r="I2" s="30">
         <v>46276</v>
       </c>
-      <c r="J2" s="28">
+      <c r="J2" s="30">
         <v>46283</v>
       </c>
-      <c r="K2" s="28">
+      <c r="K2" s="30">
         <v>46283</v>
       </c>
-      <c r="L2" s="28">
+      <c r="L2" s="30">
         <v>46283</v>
       </c>
-      <c r="M2" s="28">
+      <c r="M2" s="30">
         <v>46283</v>
       </c>
-      <c r="N2" s="28">
+      <c r="N2" s="30">
         <v>46290</v>
       </c>
-      <c r="O2" s="28">
+      <c r="O2" s="30">
         <v>46290</v>
       </c>
-      <c r="P2" s="28">
+      <c r="P2" s="30">
         <v>46290</v>
       </c>
-      <c r="Q2" s="28">
+      <c r="Q2" s="30">
         <v>46290</v>
       </c>
-      <c r="R2" s="28">
+      <c r="R2" s="30">
         <v>46297</v>
       </c>
-      <c r="S2" s="28">
+      <c r="S2" s="30">
         <v>46297</v>
       </c>
-      <c r="T2" s="28">
+      <c r="T2" s="30">
         <v>46297</v>
       </c>
-      <c r="U2" s="28">
+      <c r="U2" s="30">
         <v>46297</v>
       </c>
-      <c r="V2" s="30">
+      <c r="V2" s="55">
         <v>46304</v>
       </c>
-      <c r="W2" s="30">
+      <c r="W2" s="55">
         <v>46304</v>
       </c>
-      <c r="X2" s="28">
+      <c r="X2" s="30">
         <v>46304</v>
       </c>
-      <c r="Y2" s="28">
+      <c r="Y2" s="30">
         <v>46304</v>
       </c>
-      <c r="Z2" s="67">
+      <c r="Z2" s="53">
         <v>46311</v>
       </c>
-      <c r="AA2" s="67">
+      <c r="AA2" s="53">
         <v>46311</v>
       </c>
-      <c r="AB2" s="67">
+      <c r="AB2" s="53">
         <v>46311</v>
       </c>
-      <c r="AC2" s="67">
+      <c r="AC2" s="53">
         <v>46311</v>
       </c>
-      <c r="AD2" s="28"/>
-      <c r="AE2" s="28"/>
-      <c r="AF2" s="28"/>
-      <c r="AG2" s="28"/>
-      <c r="AH2" s="28"/>
-      <c r="AI2" s="28"/>
-      <c r="AJ2" s="28"/>
-      <c r="AK2" s="28"/>
-      <c r="AL2" s="28"/>
-      <c r="AM2" s="28"/>
-      <c r="AN2" s="28"/>
-      <c r="AO2" s="28"/>
-      <c r="AP2" s="28"/>
-      <c r="AQ2" s="28"/>
-      <c r="AR2" s="28"/>
-      <c r="AS2" s="28"/>
-      <c r="AT2" s="28"/>
-      <c r="AU2" s="28"/>
-      <c r="AV2" s="28"/>
-      <c r="AW2" s="28"/>
-      <c r="AX2" s="28"/>
-      <c r="AY2" s="28"/>
-      <c r="AZ2" s="28"/>
-      <c r="BA2" s="28"/>
-      <c r="BB2" s="28"/>
-      <c r="BC2" s="28"/>
-      <c r="BD2" s="28"/>
-      <c r="BE2" s="28"/>
-      <c r="BF2" s="28"/>
-      <c r="BG2" s="28"/>
-      <c r="BH2" s="28"/>
-      <c r="BI2" s="28"/>
-      <c r="BJ2" s="28"/>
-      <c r="BK2" s="28"/>
-      <c r="BL2" s="28"/>
-      <c r="BM2" s="28"/>
-      <c r="BN2" s="28"/>
-      <c r="BO2" s="28"/>
-      <c r="BP2" s="28"/>
-      <c r="BQ2" s="28"/>
-      <c r="BR2" s="28"/>
-      <c r="BS2" s="28"/>
-      <c r="BT2" s="28"/>
-      <c r="BU2" s="28"/>
-      <c r="BV2" s="28"/>
-      <c r="BW2" s="28"/>
-      <c r="BX2" s="28"/>
-      <c r="BY2" s="28"/>
-      <c r="BZ2" s="28"/>
-      <c r="CA2" s="28"/>
-      <c r="CB2" s="28"/>
-      <c r="CC2" s="28"/>
-      <c r="CD2" s="28"/>
-      <c r="CE2" s="28"/>
-      <c r="CF2" s="28"/>
-      <c r="CG2" s="28"/>
-      <c r="CH2" s="28"/>
-      <c r="CI2" s="28"/>
-      <c r="CJ2" s="28"/>
-      <c r="CK2" s="28"/>
-      <c r="CL2" s="28"/>
-      <c r="CM2" s="28"/>
-      <c r="CN2" s="28"/>
-      <c r="CO2" s="28"/>
-      <c r="CP2" s="28"/>
-      <c r="CQ2" s="28"/>
-      <c r="CR2" s="28"/>
-      <c r="CS2" s="28"/>
-      <c r="CT2" s="28"/>
-      <c r="CU2" s="28"/>
-      <c r="CV2" s="28"/>
-      <c r="CW2" s="28"/>
-      <c r="CX2" s="28"/>
-      <c r="CY2" s="28"/>
-      <c r="CZ2" s="28"/>
-      <c r="DA2" s="28"/>
-      <c r="DB2" s="28"/>
-      <c r="DC2" s="28"/>
-      <c r="DD2" s="28"/>
-      <c r="DE2" s="28"/>
-      <c r="DF2" s="28"/>
-      <c r="DG2" s="28"/>
-      <c r="DH2" s="28"/>
-      <c r="DI2" s="28"/>
-      <c r="DJ2" s="28"/>
-      <c r="DK2" s="28"/>
-      <c r="DL2" s="28"/>
-      <c r="DM2" s="28"/>
-      <c r="DN2" s="28"/>
-      <c r="DO2" s="28"/>
-      <c r="DP2" s="28"/>
-      <c r="DQ2" s="28"/>
-      <c r="DR2" s="28"/>
-      <c r="DS2" s="28"/>
-      <c r="DT2" s="28"/>
+      <c r="AD2" s="30">
+        <v>46318</v>
+      </c>
+      <c r="AE2" s="30">
+        <v>46318</v>
+      </c>
+      <c r="AF2" s="30">
+        <v>46318</v>
+      </c>
+      <c r="AG2" s="30">
+        <v>46318</v>
+      </c>
+      <c r="AH2" s="30"/>
+      <c r="AI2" s="30"/>
+      <c r="AJ2" s="30"/>
+      <c r="AK2" s="30"/>
+      <c r="AL2" s="30"/>
+      <c r="AM2" s="30"/>
+      <c r="AN2" s="30"/>
+      <c r="AO2" s="30"/>
+      <c r="AP2" s="30"/>
+      <c r="AQ2" s="30"/>
+      <c r="AR2" s="30"/>
+      <c r="AS2" s="30"/>
+      <c r="AT2" s="30"/>
+      <c r="AU2" s="30"/>
+      <c r="AV2" s="30"/>
+      <c r="AW2" s="30"/>
+      <c r="AX2" s="30"/>
+      <c r="AY2" s="30"/>
+      <c r="AZ2" s="30"/>
+      <c r="BA2" s="30"/>
+      <c r="BB2" s="30"/>
+      <c r="BC2" s="30"/>
+      <c r="BD2" s="30"/>
+      <c r="BE2" s="30"/>
+      <c r="BF2" s="30"/>
+      <c r="BG2" s="30"/>
+      <c r="BH2" s="30"/>
+      <c r="BI2" s="30"/>
+      <c r="BJ2" s="30"/>
+      <c r="BK2" s="30"/>
+      <c r="BL2" s="30"/>
+      <c r="BM2" s="30"/>
+      <c r="BN2" s="30"/>
+      <c r="BO2" s="30"/>
+      <c r="BP2" s="30"/>
+      <c r="BQ2" s="30"/>
+      <c r="BR2" s="30"/>
+      <c r="BS2" s="30"/>
+      <c r="BT2" s="30"/>
+      <c r="BU2" s="30"/>
+      <c r="BV2" s="30"/>
+      <c r="BW2" s="30"/>
+      <c r="BX2" s="30"/>
+      <c r="BY2" s="30"/>
+      <c r="BZ2" s="30"/>
+      <c r="CA2" s="30"/>
+      <c r="CB2" s="30"/>
+      <c r="CC2" s="30"/>
+      <c r="CD2" s="30"/>
+      <c r="CE2" s="30"/>
+      <c r="CF2" s="30"/>
+      <c r="CG2" s="30"/>
+      <c r="CH2" s="30"/>
+      <c r="CI2" s="30"/>
+      <c r="CJ2" s="30"/>
+      <c r="CK2" s="30"/>
+      <c r="CL2" s="30"/>
+      <c r="CM2" s="30"/>
+      <c r="CN2" s="30"/>
+      <c r="CO2" s="30"/>
+      <c r="CP2" s="30"/>
+      <c r="CQ2" s="30"/>
+      <c r="CR2" s="30"/>
+      <c r="CS2" s="30"/>
+      <c r="CT2" s="30"/>
+      <c r="CU2" s="30"/>
+      <c r="CV2" s="30"/>
+      <c r="CW2" s="30"/>
+      <c r="CX2" s="30"/>
+      <c r="CY2" s="30"/>
+      <c r="CZ2" s="30"/>
+      <c r="DA2" s="30"/>
+      <c r="DB2" s="30"/>
+      <c r="DC2" s="30"/>
+      <c r="DD2" s="30"/>
+      <c r="DE2" s="30"/>
+      <c r="DF2" s="30"/>
+      <c r="DG2" s="30"/>
+      <c r="DH2" s="30"/>
+      <c r="DI2" s="30"/>
+      <c r="DJ2" s="30"/>
+      <c r="DK2" s="30"/>
+      <c r="DL2" s="30"/>
+      <c r="DM2" s="30"/>
+      <c r="DN2" s="30"/>
+      <c r="DO2" s="30"/>
+      <c r="DP2" s="30"/>
+      <c r="DQ2" s="30"/>
+      <c r="DR2" s="30"/>
+      <c r="DS2" s="30"/>
+      <c r="DT2" s="30"/>
     </row>
     <row r="3" spans="1:125" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="28"/>
-      <c r="O3" s="28"/>
-      <c r="P3" s="28"/>
-      <c r="Q3" s="28"/>
-      <c r="R3" s="28"/>
-      <c r="S3" s="28"/>
-      <c r="T3" s="28"/>
-      <c r="U3" s="28"/>
-      <c r="V3" s="30"/>
-      <c r="W3" s="30"/>
-      <c r="X3" s="28"/>
-      <c r="Y3" s="28"/>
-      <c r="Z3" s="67"/>
-      <c r="AA3" s="67"/>
-      <c r="AB3" s="67"/>
-      <c r="AC3" s="67"/>
-      <c r="AD3" s="28"/>
-      <c r="AE3" s="28"/>
-      <c r="AF3" s="28"/>
-      <c r="AG3" s="28"/>
-      <c r="AH3" s="28"/>
-      <c r="AI3" s="28"/>
-      <c r="AJ3" s="28"/>
-      <c r="AK3" s="28"/>
-      <c r="AL3" s="28"/>
-      <c r="AM3" s="28"/>
-      <c r="AN3" s="28"/>
-      <c r="AO3" s="28"/>
-      <c r="AP3" s="28"/>
-      <c r="AQ3" s="28"/>
-      <c r="AR3" s="28"/>
-      <c r="AS3" s="28"/>
-      <c r="AT3" s="28"/>
-      <c r="AU3" s="28"/>
-      <c r="AV3" s="28"/>
-      <c r="AW3" s="28"/>
-      <c r="AX3" s="28"/>
-      <c r="AY3" s="28"/>
-      <c r="AZ3" s="28"/>
-      <c r="BA3" s="28"/>
-      <c r="BB3" s="28"/>
-      <c r="BC3" s="28"/>
-      <c r="BD3" s="28"/>
-      <c r="BE3" s="28"/>
-      <c r="BF3" s="28"/>
-      <c r="BG3" s="28"/>
-      <c r="BH3" s="28"/>
-      <c r="BI3" s="28"/>
-      <c r="BJ3" s="28"/>
-      <c r="BK3" s="28"/>
-      <c r="BL3" s="28"/>
-      <c r="BM3" s="28"/>
-      <c r="BN3" s="28"/>
-      <c r="BO3" s="28"/>
-      <c r="BP3" s="28"/>
-      <c r="BQ3" s="28"/>
-      <c r="BR3" s="28"/>
-      <c r="BS3" s="28"/>
-      <c r="BT3" s="28"/>
-      <c r="BU3" s="28"/>
-      <c r="BV3" s="28"/>
-      <c r="BW3" s="28"/>
-      <c r="BX3" s="28"/>
-      <c r="BY3" s="28"/>
-      <c r="BZ3" s="28"/>
-      <c r="CA3" s="28"/>
-      <c r="CB3" s="28"/>
-      <c r="CC3" s="28"/>
-      <c r="CD3" s="28"/>
-      <c r="CE3" s="28"/>
-      <c r="CF3" s="28"/>
-      <c r="CG3" s="28"/>
-      <c r="CH3" s="28"/>
-      <c r="CI3" s="28"/>
-      <c r="CJ3" s="28"/>
-      <c r="CK3" s="28"/>
-      <c r="CL3" s="28"/>
-      <c r="CM3" s="28"/>
-      <c r="CN3" s="28"/>
-      <c r="CO3" s="28"/>
-      <c r="CP3" s="28"/>
-      <c r="CQ3" s="28"/>
-      <c r="CR3" s="28"/>
-      <c r="CS3" s="28"/>
-      <c r="CT3" s="28"/>
-      <c r="CU3" s="28"/>
-      <c r="CV3" s="28"/>
-      <c r="CW3" s="28"/>
-      <c r="CX3" s="28"/>
-      <c r="CY3" s="28"/>
-      <c r="CZ3" s="28"/>
-      <c r="DA3" s="28"/>
-      <c r="DB3" s="28"/>
-      <c r="DC3" s="28"/>
-      <c r="DD3" s="28"/>
-      <c r="DE3" s="28"/>
-      <c r="DF3" s="28"/>
-      <c r="DG3" s="28"/>
-      <c r="DH3" s="28"/>
-      <c r="DI3" s="28"/>
-      <c r="DJ3" s="28"/>
-      <c r="DK3" s="28"/>
-      <c r="DL3" s="28"/>
-      <c r="DM3" s="28"/>
-      <c r="DN3" s="28"/>
-      <c r="DO3" s="28"/>
-      <c r="DP3" s="28"/>
-      <c r="DQ3" s="28"/>
-      <c r="DR3" s="28"/>
-      <c r="DS3" s="28"/>
-      <c r="DT3" s="28"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="30"/>
+      <c r="M3" s="30"/>
+      <c r="N3" s="30"/>
+      <c r="O3" s="30"/>
+      <c r="P3" s="30"/>
+      <c r="Q3" s="30"/>
+      <c r="R3" s="30"/>
+      <c r="S3" s="30"/>
+      <c r="T3" s="30"/>
+      <c r="U3" s="30"/>
+      <c r="V3" s="55"/>
+      <c r="W3" s="55"/>
+      <c r="X3" s="30"/>
+      <c r="Y3" s="30"/>
+      <c r="Z3" s="53"/>
+      <c r="AA3" s="53"/>
+      <c r="AB3" s="53"/>
+      <c r="AC3" s="53"/>
+      <c r="AD3" s="30"/>
+      <c r="AE3" s="30"/>
+      <c r="AF3" s="30"/>
+      <c r="AG3" s="30"/>
+      <c r="AH3" s="30"/>
+      <c r="AI3" s="30"/>
+      <c r="AJ3" s="30"/>
+      <c r="AK3" s="30"/>
+      <c r="AL3" s="30"/>
+      <c r="AM3" s="30"/>
+      <c r="AN3" s="30"/>
+      <c r="AO3" s="30"/>
+      <c r="AP3" s="30"/>
+      <c r="AQ3" s="30"/>
+      <c r="AR3" s="30"/>
+      <c r="AS3" s="30"/>
+      <c r="AT3" s="30"/>
+      <c r="AU3" s="30"/>
+      <c r="AV3" s="30"/>
+      <c r="AW3" s="30"/>
+      <c r="AX3" s="30"/>
+      <c r="AY3" s="30"/>
+      <c r="AZ3" s="30"/>
+      <c r="BA3" s="30"/>
+      <c r="BB3" s="30"/>
+      <c r="BC3" s="30"/>
+      <c r="BD3" s="30"/>
+      <c r="BE3" s="30"/>
+      <c r="BF3" s="30"/>
+      <c r="BG3" s="30"/>
+      <c r="BH3" s="30"/>
+      <c r="BI3" s="30"/>
+      <c r="BJ3" s="30"/>
+      <c r="BK3" s="30"/>
+      <c r="BL3" s="30"/>
+      <c r="BM3" s="30"/>
+      <c r="BN3" s="30"/>
+      <c r="BO3" s="30"/>
+      <c r="BP3" s="30"/>
+      <c r="BQ3" s="30"/>
+      <c r="BR3" s="30"/>
+      <c r="BS3" s="30"/>
+      <c r="BT3" s="30"/>
+      <c r="BU3" s="30"/>
+      <c r="BV3" s="30"/>
+      <c r="BW3" s="30"/>
+      <c r="BX3" s="30"/>
+      <c r="BY3" s="30"/>
+      <c r="BZ3" s="30"/>
+      <c r="CA3" s="30"/>
+      <c r="CB3" s="30"/>
+      <c r="CC3" s="30"/>
+      <c r="CD3" s="30"/>
+      <c r="CE3" s="30"/>
+      <c r="CF3" s="30"/>
+      <c r="CG3" s="30"/>
+      <c r="CH3" s="30"/>
+      <c r="CI3" s="30"/>
+      <c r="CJ3" s="30"/>
+      <c r="CK3" s="30"/>
+      <c r="CL3" s="30"/>
+      <c r="CM3" s="30"/>
+      <c r="CN3" s="30"/>
+      <c r="CO3" s="30"/>
+      <c r="CP3" s="30"/>
+      <c r="CQ3" s="30"/>
+      <c r="CR3" s="30"/>
+      <c r="CS3" s="30"/>
+      <c r="CT3" s="30"/>
+      <c r="CU3" s="30"/>
+      <c r="CV3" s="30"/>
+      <c r="CW3" s="30"/>
+      <c r="CX3" s="30"/>
+      <c r="CY3" s="30"/>
+      <c r="CZ3" s="30"/>
+      <c r="DA3" s="30"/>
+      <c r="DB3" s="30"/>
+      <c r="DC3" s="30"/>
+      <c r="DD3" s="30"/>
+      <c r="DE3" s="30"/>
+      <c r="DF3" s="30"/>
+      <c r="DG3" s="30"/>
+      <c r="DH3" s="30"/>
+      <c r="DI3" s="30"/>
+      <c r="DJ3" s="30"/>
+      <c r="DK3" s="30"/>
+      <c r="DL3" s="30"/>
+      <c r="DM3" s="30"/>
+      <c r="DN3" s="30"/>
+      <c r="DO3" s="30"/>
+      <c r="DP3" s="30"/>
+      <c r="DQ3" s="30"/>
+      <c r="DR3" s="30"/>
+      <c r="DS3" s="30"/>
+      <c r="DT3" s="30"/>
     </row>
     <row r="4" spans="1:125" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="48" t="s">
+      <c r="A4" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="48"/>
+      <c r="C4" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="49"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="28"/>
-      <c r="M4" s="28"/>
-      <c r="N4" s="28"/>
-      <c r="O4" s="28"/>
-      <c r="P4" s="28"/>
-      <c r="Q4" s="28"/>
-      <c r="R4" s="28"/>
-      <c r="S4" s="28"/>
-      <c r="T4" s="28"/>
-      <c r="U4" s="28"/>
-      <c r="V4" s="30"/>
-      <c r="W4" s="30"/>
-      <c r="X4" s="28"/>
-      <c r="Y4" s="28"/>
-      <c r="Z4" s="67"/>
-      <c r="AA4" s="67"/>
-      <c r="AB4" s="67"/>
-      <c r="AC4" s="67"/>
-      <c r="AD4" s="28"/>
-      <c r="AE4" s="28"/>
-      <c r="AF4" s="28"/>
-      <c r="AG4" s="28"/>
-      <c r="AH4" s="28"/>
-      <c r="AI4" s="28"/>
-      <c r="AJ4" s="28"/>
-      <c r="AK4" s="28"/>
-      <c r="AL4" s="28"/>
-      <c r="AM4" s="28"/>
-      <c r="AN4" s="28"/>
-      <c r="AO4" s="28"/>
-      <c r="AP4" s="28"/>
-      <c r="AQ4" s="28"/>
-      <c r="AR4" s="28"/>
-      <c r="AS4" s="28"/>
-      <c r="AT4" s="28"/>
-      <c r="AU4" s="28"/>
-      <c r="AV4" s="28"/>
-      <c r="AW4" s="28"/>
-      <c r="AX4" s="28"/>
-      <c r="AY4" s="28"/>
-      <c r="AZ4" s="28"/>
-      <c r="BA4" s="28"/>
-      <c r="BB4" s="28"/>
-      <c r="BC4" s="28"/>
-      <c r="BD4" s="28"/>
-      <c r="BE4" s="28"/>
-      <c r="BF4" s="28"/>
-      <c r="BG4" s="28"/>
-      <c r="BH4" s="28"/>
-      <c r="BI4" s="28"/>
-      <c r="BJ4" s="28"/>
-      <c r="BK4" s="28"/>
-      <c r="BL4" s="28"/>
-      <c r="BM4" s="28"/>
-      <c r="BN4" s="28"/>
-      <c r="BO4" s="28"/>
-      <c r="BP4" s="28"/>
-      <c r="BQ4" s="28"/>
-      <c r="BR4" s="28"/>
-      <c r="BS4" s="28"/>
-      <c r="BT4" s="28"/>
-      <c r="BU4" s="28"/>
-      <c r="BV4" s="28"/>
-      <c r="BW4" s="28"/>
-      <c r="BX4" s="28"/>
-      <c r="BY4" s="28"/>
-      <c r="BZ4" s="28"/>
-      <c r="CA4" s="28"/>
-      <c r="CB4" s="28"/>
-      <c r="CC4" s="28"/>
-      <c r="CD4" s="28"/>
-      <c r="CE4" s="28"/>
-      <c r="CF4" s="28"/>
-      <c r="CG4" s="28"/>
-      <c r="CH4" s="28"/>
-      <c r="CI4" s="28"/>
-      <c r="CJ4" s="28"/>
-      <c r="CK4" s="28"/>
-      <c r="CL4" s="28"/>
-      <c r="CM4" s="28"/>
-      <c r="CN4" s="28"/>
-      <c r="CO4" s="28"/>
-      <c r="CP4" s="28"/>
-      <c r="CQ4" s="28"/>
-      <c r="CR4" s="28"/>
-      <c r="CS4" s="28"/>
-      <c r="CT4" s="28"/>
-      <c r="CU4" s="28"/>
-      <c r="CV4" s="28"/>
-      <c r="CW4" s="28"/>
-      <c r="CX4" s="28"/>
-      <c r="CY4" s="28"/>
-      <c r="CZ4" s="28"/>
-      <c r="DA4" s="28"/>
-      <c r="DB4" s="28"/>
-      <c r="DC4" s="28"/>
-      <c r="DD4" s="28"/>
-      <c r="DE4" s="28"/>
-      <c r="DF4" s="28"/>
-      <c r="DG4" s="28"/>
-      <c r="DH4" s="28"/>
-      <c r="DI4" s="28"/>
-      <c r="DJ4" s="28"/>
-      <c r="DK4" s="28"/>
-      <c r="DL4" s="28"/>
-      <c r="DM4" s="28"/>
-      <c r="DN4" s="28"/>
-      <c r="DO4" s="28"/>
-      <c r="DP4" s="28"/>
-      <c r="DQ4" s="28"/>
-      <c r="DR4" s="28"/>
-      <c r="DS4" s="28"/>
-      <c r="DT4" s="28"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="30"/>
+      <c r="K4" s="30"/>
+      <c r="L4" s="30"/>
+      <c r="M4" s="30"/>
+      <c r="N4" s="30"/>
+      <c r="O4" s="30"/>
+      <c r="P4" s="30"/>
+      <c r="Q4" s="30"/>
+      <c r="R4" s="30"/>
+      <c r="S4" s="30"/>
+      <c r="T4" s="30"/>
+      <c r="U4" s="30"/>
+      <c r="V4" s="55"/>
+      <c r="W4" s="55"/>
+      <c r="X4" s="30"/>
+      <c r="Y4" s="30"/>
+      <c r="Z4" s="53"/>
+      <c r="AA4" s="53"/>
+      <c r="AB4" s="53"/>
+      <c r="AC4" s="53"/>
+      <c r="AD4" s="30"/>
+      <c r="AE4" s="30"/>
+      <c r="AF4" s="30"/>
+      <c r="AG4" s="30"/>
+      <c r="AH4" s="30"/>
+      <c r="AI4" s="30"/>
+      <c r="AJ4" s="30"/>
+      <c r="AK4" s="30"/>
+      <c r="AL4" s="30"/>
+      <c r="AM4" s="30"/>
+      <c r="AN4" s="30"/>
+      <c r="AO4" s="30"/>
+      <c r="AP4" s="30"/>
+      <c r="AQ4" s="30"/>
+      <c r="AR4" s="30"/>
+      <c r="AS4" s="30"/>
+      <c r="AT4" s="30"/>
+      <c r="AU4" s="30"/>
+      <c r="AV4" s="30"/>
+      <c r="AW4" s="30"/>
+      <c r="AX4" s="30"/>
+      <c r="AY4" s="30"/>
+      <c r="AZ4" s="30"/>
+      <c r="BA4" s="30"/>
+      <c r="BB4" s="30"/>
+      <c r="BC4" s="30"/>
+      <c r="BD4" s="30"/>
+      <c r="BE4" s="30"/>
+      <c r="BF4" s="30"/>
+      <c r="BG4" s="30"/>
+      <c r="BH4" s="30"/>
+      <c r="BI4" s="30"/>
+      <c r="BJ4" s="30"/>
+      <c r="BK4" s="30"/>
+      <c r="BL4" s="30"/>
+      <c r="BM4" s="30"/>
+      <c r="BN4" s="30"/>
+      <c r="BO4" s="30"/>
+      <c r="BP4" s="30"/>
+      <c r="BQ4" s="30"/>
+      <c r="BR4" s="30"/>
+      <c r="BS4" s="30"/>
+      <c r="BT4" s="30"/>
+      <c r="BU4" s="30"/>
+      <c r="BV4" s="30"/>
+      <c r="BW4" s="30"/>
+      <c r="BX4" s="30"/>
+      <c r="BY4" s="30"/>
+      <c r="BZ4" s="30"/>
+      <c r="CA4" s="30"/>
+      <c r="CB4" s="30"/>
+      <c r="CC4" s="30"/>
+      <c r="CD4" s="30"/>
+      <c r="CE4" s="30"/>
+      <c r="CF4" s="30"/>
+      <c r="CG4" s="30"/>
+      <c r="CH4" s="30"/>
+      <c r="CI4" s="30"/>
+      <c r="CJ4" s="30"/>
+      <c r="CK4" s="30"/>
+      <c r="CL4" s="30"/>
+      <c r="CM4" s="30"/>
+      <c r="CN4" s="30"/>
+      <c r="CO4" s="30"/>
+      <c r="CP4" s="30"/>
+      <c r="CQ4" s="30"/>
+      <c r="CR4" s="30"/>
+      <c r="CS4" s="30"/>
+      <c r="CT4" s="30"/>
+      <c r="CU4" s="30"/>
+      <c r="CV4" s="30"/>
+      <c r="CW4" s="30"/>
+      <c r="CX4" s="30"/>
+      <c r="CY4" s="30"/>
+      <c r="CZ4" s="30"/>
+      <c r="DA4" s="30"/>
+      <c r="DB4" s="30"/>
+      <c r="DC4" s="30"/>
+      <c r="DD4" s="30"/>
+      <c r="DE4" s="30"/>
+      <c r="DF4" s="30"/>
+      <c r="DG4" s="30"/>
+      <c r="DH4" s="30"/>
+      <c r="DI4" s="30"/>
+      <c r="DJ4" s="30"/>
+      <c r="DK4" s="30"/>
+      <c r="DL4" s="30"/>
+      <c r="DM4" s="30"/>
+      <c r="DN4" s="30"/>
+      <c r="DO4" s="30"/>
+      <c r="DP4" s="30"/>
+      <c r="DQ4" s="30"/>
+      <c r="DR4" s="30"/>
+      <c r="DS4" s="30"/>
+      <c r="DT4" s="30"/>
     </row>
     <row r="5" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="51">
+      <c r="B5" s="49"/>
+      <c r="C5" s="50">
         <v>60</v>
       </c>
-      <c r="D5" s="52"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
-      <c r="K5" s="28"/>
-      <c r="L5" s="28"/>
-      <c r="M5" s="28"/>
-      <c r="N5" s="28"/>
-      <c r="O5" s="28"/>
-      <c r="P5" s="28"/>
-      <c r="Q5" s="28"/>
-      <c r="R5" s="28"/>
-      <c r="S5" s="28"/>
-      <c r="T5" s="28"/>
-      <c r="U5" s="28"/>
-      <c r="V5" s="30"/>
-      <c r="W5" s="30"/>
-      <c r="X5" s="28"/>
-      <c r="Y5" s="28"/>
-      <c r="Z5" s="67"/>
-      <c r="AA5" s="67"/>
-      <c r="AB5" s="67"/>
-      <c r="AC5" s="67"/>
-      <c r="AD5" s="28"/>
-      <c r="AE5" s="28"/>
-      <c r="AF5" s="28"/>
-      <c r="AG5" s="28"/>
-      <c r="AH5" s="28"/>
-      <c r="AI5" s="28"/>
-      <c r="AJ5" s="28"/>
-      <c r="AK5" s="28"/>
-      <c r="AL5" s="28"/>
-      <c r="AM5" s="28"/>
-      <c r="AN5" s="28"/>
-      <c r="AO5" s="28"/>
-      <c r="AP5" s="28"/>
-      <c r="AQ5" s="28"/>
-      <c r="AR5" s="28"/>
-      <c r="AS5" s="28"/>
-      <c r="AT5" s="28"/>
-      <c r="AU5" s="28"/>
-      <c r="AV5" s="28"/>
-      <c r="AW5" s="28"/>
-      <c r="AX5" s="28"/>
-      <c r="AY5" s="28"/>
-      <c r="AZ5" s="28"/>
-      <c r="BA5" s="28"/>
-      <c r="BB5" s="28"/>
-      <c r="BC5" s="28"/>
-      <c r="BD5" s="28"/>
-      <c r="BE5" s="28"/>
-      <c r="BF5" s="28"/>
-      <c r="BG5" s="28"/>
-      <c r="BH5" s="28"/>
-      <c r="BI5" s="28"/>
-      <c r="BJ5" s="28"/>
-      <c r="BK5" s="28"/>
-      <c r="BL5" s="28"/>
-      <c r="BM5" s="28"/>
-      <c r="BN5" s="28"/>
-      <c r="BO5" s="28"/>
-      <c r="BP5" s="28"/>
-      <c r="BQ5" s="28"/>
-      <c r="BR5" s="28"/>
-      <c r="BS5" s="28"/>
-      <c r="BT5" s="28"/>
-      <c r="BU5" s="28"/>
-      <c r="BV5" s="28"/>
-      <c r="BW5" s="28"/>
-      <c r="BX5" s="28"/>
-      <c r="BY5" s="28"/>
-      <c r="BZ5" s="28"/>
-      <c r="CA5" s="28"/>
-      <c r="CB5" s="28"/>
-      <c r="CC5" s="28"/>
-      <c r="CD5" s="28"/>
-      <c r="CE5" s="28"/>
-      <c r="CF5" s="28"/>
-      <c r="CG5" s="28"/>
-      <c r="CH5" s="28"/>
-      <c r="CI5" s="28"/>
-      <c r="CJ5" s="28"/>
-      <c r="CK5" s="28"/>
-      <c r="CL5" s="28"/>
-      <c r="CM5" s="28"/>
-      <c r="CN5" s="28"/>
-      <c r="CO5" s="28"/>
-      <c r="CP5" s="28"/>
-      <c r="CQ5" s="28"/>
-      <c r="CR5" s="28"/>
-      <c r="CS5" s="28"/>
-      <c r="CT5" s="28"/>
-      <c r="CU5" s="28"/>
-      <c r="CV5" s="28"/>
-      <c r="CW5" s="28"/>
-      <c r="CX5" s="28"/>
-      <c r="CY5" s="28"/>
-      <c r="CZ5" s="28"/>
-      <c r="DA5" s="28"/>
-      <c r="DB5" s="28"/>
-      <c r="DC5" s="28"/>
-      <c r="DD5" s="28"/>
-      <c r="DE5" s="28"/>
-      <c r="DF5" s="28"/>
-      <c r="DG5" s="28"/>
-      <c r="DH5" s="28"/>
-      <c r="DI5" s="28"/>
-      <c r="DJ5" s="28"/>
-      <c r="DK5" s="28"/>
-      <c r="DL5" s="28"/>
-      <c r="DM5" s="28"/>
-      <c r="DN5" s="28"/>
-      <c r="DO5" s="28"/>
-      <c r="DP5" s="28"/>
-      <c r="DQ5" s="28"/>
-      <c r="DR5" s="28"/>
-      <c r="DS5" s="28"/>
-      <c r="DT5" s="28"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="30"/>
+      <c r="L5" s="30"/>
+      <c r="M5" s="30"/>
+      <c r="N5" s="30"/>
+      <c r="O5" s="30"/>
+      <c r="P5" s="30"/>
+      <c r="Q5" s="30"/>
+      <c r="R5" s="30"/>
+      <c r="S5" s="30"/>
+      <c r="T5" s="30"/>
+      <c r="U5" s="30"/>
+      <c r="V5" s="55"/>
+      <c r="W5" s="55"/>
+      <c r="X5" s="30"/>
+      <c r="Y5" s="30"/>
+      <c r="Z5" s="53"/>
+      <c r="AA5" s="53"/>
+      <c r="AB5" s="53"/>
+      <c r="AC5" s="53"/>
+      <c r="AD5" s="30"/>
+      <c r="AE5" s="30"/>
+      <c r="AF5" s="30"/>
+      <c r="AG5" s="30"/>
+      <c r="AH5" s="30"/>
+      <c r="AI5" s="30"/>
+      <c r="AJ5" s="30"/>
+      <c r="AK5" s="30"/>
+      <c r="AL5" s="30"/>
+      <c r="AM5" s="30"/>
+      <c r="AN5" s="30"/>
+      <c r="AO5" s="30"/>
+      <c r="AP5" s="30"/>
+      <c r="AQ5" s="30"/>
+      <c r="AR5" s="30"/>
+      <c r="AS5" s="30"/>
+      <c r="AT5" s="30"/>
+      <c r="AU5" s="30"/>
+      <c r="AV5" s="30"/>
+      <c r="AW5" s="30"/>
+      <c r="AX5" s="30"/>
+      <c r="AY5" s="30"/>
+      <c r="AZ5" s="30"/>
+      <c r="BA5" s="30"/>
+      <c r="BB5" s="30"/>
+      <c r="BC5" s="30"/>
+      <c r="BD5" s="30"/>
+      <c r="BE5" s="30"/>
+      <c r="BF5" s="30"/>
+      <c r="BG5" s="30"/>
+      <c r="BH5" s="30"/>
+      <c r="BI5" s="30"/>
+      <c r="BJ5" s="30"/>
+      <c r="BK5" s="30"/>
+      <c r="BL5" s="30"/>
+      <c r="BM5" s="30"/>
+      <c r="BN5" s="30"/>
+      <c r="BO5" s="30"/>
+      <c r="BP5" s="30"/>
+      <c r="BQ5" s="30"/>
+      <c r="BR5" s="30"/>
+      <c r="BS5" s="30"/>
+      <c r="BT5" s="30"/>
+      <c r="BU5" s="30"/>
+      <c r="BV5" s="30"/>
+      <c r="BW5" s="30"/>
+      <c r="BX5" s="30"/>
+      <c r="BY5" s="30"/>
+      <c r="BZ5" s="30"/>
+      <c r="CA5" s="30"/>
+      <c r="CB5" s="30"/>
+      <c r="CC5" s="30"/>
+      <c r="CD5" s="30"/>
+      <c r="CE5" s="30"/>
+      <c r="CF5" s="30"/>
+      <c r="CG5" s="30"/>
+      <c r="CH5" s="30"/>
+      <c r="CI5" s="30"/>
+      <c r="CJ5" s="30"/>
+      <c r="CK5" s="30"/>
+      <c r="CL5" s="30"/>
+      <c r="CM5" s="30"/>
+      <c r="CN5" s="30"/>
+      <c r="CO5" s="30"/>
+      <c r="CP5" s="30"/>
+      <c r="CQ5" s="30"/>
+      <c r="CR5" s="30"/>
+      <c r="CS5" s="30"/>
+      <c r="CT5" s="30"/>
+      <c r="CU5" s="30"/>
+      <c r="CV5" s="30"/>
+      <c r="CW5" s="30"/>
+      <c r="CX5" s="30"/>
+      <c r="CY5" s="30"/>
+      <c r="CZ5" s="30"/>
+      <c r="DA5" s="30"/>
+      <c r="DB5" s="30"/>
+      <c r="DC5" s="30"/>
+      <c r="DD5" s="30"/>
+      <c r="DE5" s="30"/>
+      <c r="DF5" s="30"/>
+      <c r="DG5" s="30"/>
+      <c r="DH5" s="30"/>
+      <c r="DI5" s="30"/>
+      <c r="DJ5" s="30"/>
+      <c r="DK5" s="30"/>
+      <c r="DL5" s="30"/>
+      <c r="DM5" s="30"/>
+      <c r="DN5" s="30"/>
+      <c r="DO5" s="30"/>
+      <c r="DP5" s="30"/>
+      <c r="DQ5" s="30"/>
+      <c r="DR5" s="30"/>
+      <c r="DS5" s="30"/>
+      <c r="DT5" s="30"/>
     </row>
     <row r="6" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="50" t="s">
+      <c r="A6" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="50"/>
-      <c r="C6" s="51">
+      <c r="B6" s="49"/>
+      <c r="C6" s="50">
         <v>4</v>
       </c>
-      <c r="D6" s="52"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="28"/>
-      <c r="K6" s="28"/>
-      <c r="L6" s="28"/>
-      <c r="M6" s="28"/>
-      <c r="N6" s="28"/>
-      <c r="O6" s="28"/>
-      <c r="P6" s="28"/>
-      <c r="Q6" s="28"/>
-      <c r="R6" s="28"/>
-      <c r="S6" s="28"/>
-      <c r="T6" s="28"/>
-      <c r="U6" s="28"/>
-      <c r="V6" s="30"/>
-      <c r="W6" s="30"/>
-      <c r="X6" s="28"/>
-      <c r="Y6" s="28"/>
-      <c r="Z6" s="67"/>
-      <c r="AA6" s="67"/>
-      <c r="AB6" s="67"/>
-      <c r="AC6" s="67"/>
-      <c r="AD6" s="28"/>
-      <c r="AE6" s="28"/>
-      <c r="AF6" s="28"/>
-      <c r="AG6" s="28"/>
-      <c r="AH6" s="28"/>
-      <c r="AI6" s="28"/>
-      <c r="AJ6" s="28"/>
-      <c r="AK6" s="28"/>
-      <c r="AL6" s="28"/>
-      <c r="AM6" s="28"/>
-      <c r="AN6" s="28"/>
-      <c r="AO6" s="28"/>
-      <c r="AP6" s="28"/>
-      <c r="AQ6" s="28"/>
-      <c r="AR6" s="28"/>
-      <c r="AS6" s="28"/>
-      <c r="AT6" s="28"/>
-      <c r="AU6" s="28"/>
-      <c r="AV6" s="28"/>
-      <c r="AW6" s="28"/>
-      <c r="AX6" s="28"/>
-      <c r="AY6" s="28"/>
-      <c r="AZ6" s="28"/>
-      <c r="BA6" s="28"/>
-      <c r="BB6" s="28"/>
-      <c r="BC6" s="28"/>
-      <c r="BD6" s="28"/>
-      <c r="BE6" s="28"/>
-      <c r="BF6" s="28"/>
-      <c r="BG6" s="28"/>
-      <c r="BH6" s="28"/>
-      <c r="BI6" s="28"/>
-      <c r="BJ6" s="28"/>
-      <c r="BK6" s="28"/>
-      <c r="BL6" s="28"/>
-      <c r="BM6" s="28"/>
-      <c r="BN6" s="28"/>
-      <c r="BO6" s="28"/>
-      <c r="BP6" s="28"/>
-      <c r="BQ6" s="28"/>
-      <c r="BR6" s="28"/>
-      <c r="BS6" s="28"/>
-      <c r="BT6" s="28"/>
-      <c r="BU6" s="28"/>
-      <c r="BV6" s="28"/>
-      <c r="BW6" s="28"/>
-      <c r="BX6" s="28"/>
-      <c r="BY6" s="28"/>
-      <c r="BZ6" s="28"/>
-      <c r="CA6" s="28"/>
-      <c r="CB6" s="28"/>
-      <c r="CC6" s="28"/>
-      <c r="CD6" s="28"/>
-      <c r="CE6" s="28"/>
-      <c r="CF6" s="28"/>
-      <c r="CG6" s="28"/>
-      <c r="CH6" s="28"/>
-      <c r="CI6" s="28"/>
-      <c r="CJ6" s="28"/>
-      <c r="CK6" s="28"/>
-      <c r="CL6" s="28"/>
-      <c r="CM6" s="28"/>
-      <c r="CN6" s="28"/>
-      <c r="CO6" s="28"/>
-      <c r="CP6" s="28"/>
-      <c r="CQ6" s="28"/>
-      <c r="CR6" s="28"/>
-      <c r="CS6" s="28"/>
-      <c r="CT6" s="28"/>
-      <c r="CU6" s="28"/>
-      <c r="CV6" s="28"/>
-      <c r="CW6" s="28"/>
-      <c r="CX6" s="28"/>
-      <c r="CY6" s="28"/>
-      <c r="CZ6" s="28"/>
-      <c r="DA6" s="28"/>
-      <c r="DB6" s="28"/>
-      <c r="DC6" s="28"/>
-      <c r="DD6" s="28"/>
-      <c r="DE6" s="28"/>
-      <c r="DF6" s="28"/>
-      <c r="DG6" s="28"/>
-      <c r="DH6" s="28"/>
-      <c r="DI6" s="28"/>
-      <c r="DJ6" s="28"/>
-      <c r="DK6" s="28"/>
-      <c r="DL6" s="28"/>
-      <c r="DM6" s="28"/>
-      <c r="DN6" s="28"/>
-      <c r="DO6" s="28"/>
-      <c r="DP6" s="28"/>
-      <c r="DQ6" s="28"/>
-      <c r="DR6" s="28"/>
-      <c r="DS6" s="28"/>
-      <c r="DT6" s="28"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="30"/>
+      <c r="L6" s="30"/>
+      <c r="M6" s="30"/>
+      <c r="N6" s="30"/>
+      <c r="O6" s="30"/>
+      <c r="P6" s="30"/>
+      <c r="Q6" s="30"/>
+      <c r="R6" s="30"/>
+      <c r="S6" s="30"/>
+      <c r="T6" s="30"/>
+      <c r="U6" s="30"/>
+      <c r="V6" s="55"/>
+      <c r="W6" s="55"/>
+      <c r="X6" s="30"/>
+      <c r="Y6" s="30"/>
+      <c r="Z6" s="53"/>
+      <c r="AA6" s="53"/>
+      <c r="AB6" s="53"/>
+      <c r="AC6" s="53"/>
+      <c r="AD6" s="30"/>
+      <c r="AE6" s="30"/>
+      <c r="AF6" s="30"/>
+      <c r="AG6" s="30"/>
+      <c r="AH6" s="30"/>
+      <c r="AI6" s="30"/>
+      <c r="AJ6" s="30"/>
+      <c r="AK6" s="30"/>
+      <c r="AL6" s="30"/>
+      <c r="AM6" s="30"/>
+      <c r="AN6" s="30"/>
+      <c r="AO6" s="30"/>
+      <c r="AP6" s="30"/>
+      <c r="AQ6" s="30"/>
+      <c r="AR6" s="30"/>
+      <c r="AS6" s="30"/>
+      <c r="AT6" s="30"/>
+      <c r="AU6" s="30"/>
+      <c r="AV6" s="30"/>
+      <c r="AW6" s="30"/>
+      <c r="AX6" s="30"/>
+      <c r="AY6" s="30"/>
+      <c r="AZ6" s="30"/>
+      <c r="BA6" s="30"/>
+      <c r="BB6" s="30"/>
+      <c r="BC6" s="30"/>
+      <c r="BD6" s="30"/>
+      <c r="BE6" s="30"/>
+      <c r="BF6" s="30"/>
+      <c r="BG6" s="30"/>
+      <c r="BH6" s="30"/>
+      <c r="BI6" s="30"/>
+      <c r="BJ6" s="30"/>
+      <c r="BK6" s="30"/>
+      <c r="BL6" s="30"/>
+      <c r="BM6" s="30"/>
+      <c r="BN6" s="30"/>
+      <c r="BO6" s="30"/>
+      <c r="BP6" s="30"/>
+      <c r="BQ6" s="30"/>
+      <c r="BR6" s="30"/>
+      <c r="BS6" s="30"/>
+      <c r="BT6" s="30"/>
+      <c r="BU6" s="30"/>
+      <c r="BV6" s="30"/>
+      <c r="BW6" s="30"/>
+      <c r="BX6" s="30"/>
+      <c r="BY6" s="30"/>
+      <c r="BZ6" s="30"/>
+      <c r="CA6" s="30"/>
+      <c r="CB6" s="30"/>
+      <c r="CC6" s="30"/>
+      <c r="CD6" s="30"/>
+      <c r="CE6" s="30"/>
+      <c r="CF6" s="30"/>
+      <c r="CG6" s="30"/>
+      <c r="CH6" s="30"/>
+      <c r="CI6" s="30"/>
+      <c r="CJ6" s="30"/>
+      <c r="CK6" s="30"/>
+      <c r="CL6" s="30"/>
+      <c r="CM6" s="30"/>
+      <c r="CN6" s="30"/>
+      <c r="CO6" s="30"/>
+      <c r="CP6" s="30"/>
+      <c r="CQ6" s="30"/>
+      <c r="CR6" s="30"/>
+      <c r="CS6" s="30"/>
+      <c r="CT6" s="30"/>
+      <c r="CU6" s="30"/>
+      <c r="CV6" s="30"/>
+      <c r="CW6" s="30"/>
+      <c r="CX6" s="30"/>
+      <c r="CY6" s="30"/>
+      <c r="CZ6" s="30"/>
+      <c r="DA6" s="30"/>
+      <c r="DB6" s="30"/>
+      <c r="DC6" s="30"/>
+      <c r="DD6" s="30"/>
+      <c r="DE6" s="30"/>
+      <c r="DF6" s="30"/>
+      <c r="DG6" s="30"/>
+      <c r="DH6" s="30"/>
+      <c r="DI6" s="30"/>
+      <c r="DJ6" s="30"/>
+      <c r="DK6" s="30"/>
+      <c r="DL6" s="30"/>
+      <c r="DM6" s="30"/>
+      <c r="DN6" s="30"/>
+      <c r="DO6" s="30"/>
+      <c r="DP6" s="30"/>
+      <c r="DQ6" s="30"/>
+      <c r="DR6" s="30"/>
+      <c r="DS6" s="30"/>
+      <c r="DT6" s="30"/>
     </row>
     <row r="7" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="53" t="s">
+      <c r="A7" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="53"/>
-      <c r="C7" s="51">
+      <c r="B7" s="52"/>
+      <c r="C7" s="50">
         <v>11</v>
       </c>
-      <c r="D7" s="52"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="29"/>
-      <c r="J7" s="29"/>
-      <c r="K7" s="29"/>
-      <c r="L7" s="29"/>
-      <c r="M7" s="29"/>
-      <c r="N7" s="29"/>
-      <c r="O7" s="29"/>
-      <c r="P7" s="29"/>
-      <c r="Q7" s="29"/>
-      <c r="R7" s="29"/>
-      <c r="S7" s="29"/>
-      <c r="T7" s="29"/>
-      <c r="U7" s="29"/>
-      <c r="V7" s="31"/>
-      <c r="W7" s="31"/>
-      <c r="X7" s="29"/>
-      <c r="Y7" s="29"/>
-      <c r="Z7" s="68"/>
-      <c r="AA7" s="68"/>
-      <c r="AB7" s="68"/>
-      <c r="AC7" s="68"/>
-      <c r="AD7" s="29"/>
-      <c r="AE7" s="29"/>
-      <c r="AF7" s="29"/>
-      <c r="AG7" s="29"/>
-      <c r="AH7" s="29"/>
-      <c r="AI7" s="29"/>
-      <c r="AJ7" s="29"/>
-      <c r="AK7" s="29"/>
-      <c r="AL7" s="29"/>
-      <c r="AM7" s="29"/>
-      <c r="AN7" s="29"/>
-      <c r="AO7" s="29"/>
-      <c r="AP7" s="29"/>
-      <c r="AQ7" s="29"/>
-      <c r="AR7" s="29"/>
-      <c r="AS7" s="29"/>
-      <c r="AT7" s="29"/>
-      <c r="AU7" s="29"/>
-      <c r="AV7" s="29"/>
-      <c r="AW7" s="29"/>
-      <c r="AX7" s="29"/>
-      <c r="AY7" s="29"/>
-      <c r="AZ7" s="29"/>
-      <c r="BA7" s="29"/>
-      <c r="BB7" s="29"/>
-      <c r="BC7" s="29"/>
-      <c r="BD7" s="29"/>
-      <c r="BE7" s="29"/>
-      <c r="BF7" s="29"/>
-      <c r="BG7" s="29"/>
-      <c r="BH7" s="29"/>
-      <c r="BI7" s="29"/>
-      <c r="BJ7" s="29"/>
-      <c r="BK7" s="29"/>
-      <c r="BL7" s="29"/>
-      <c r="BM7" s="29"/>
-      <c r="BN7" s="29"/>
-      <c r="BO7" s="29"/>
-      <c r="BP7" s="29"/>
-      <c r="BQ7" s="29"/>
-      <c r="BR7" s="29"/>
-      <c r="BS7" s="29"/>
-      <c r="BT7" s="29"/>
-      <c r="BU7" s="29"/>
-      <c r="BV7" s="29"/>
-      <c r="BW7" s="29"/>
-      <c r="BX7" s="29"/>
-      <c r="BY7" s="29"/>
-      <c r="BZ7" s="29"/>
-      <c r="CA7" s="29"/>
-      <c r="CB7" s="29"/>
-      <c r="CC7" s="29"/>
-      <c r="CD7" s="29"/>
-      <c r="CE7" s="29"/>
-      <c r="CF7" s="29"/>
-      <c r="CG7" s="29"/>
-      <c r="CH7" s="29"/>
-      <c r="CI7" s="29"/>
-      <c r="CJ7" s="29"/>
-      <c r="CK7" s="29"/>
-      <c r="CL7" s="29"/>
-      <c r="CM7" s="29"/>
-      <c r="CN7" s="29"/>
-      <c r="CO7" s="29"/>
-      <c r="CP7" s="29"/>
-      <c r="CQ7" s="29"/>
-      <c r="CR7" s="29"/>
-      <c r="CS7" s="29"/>
-      <c r="CT7" s="29"/>
-      <c r="CU7" s="29"/>
-      <c r="CV7" s="29"/>
-      <c r="CW7" s="29"/>
-      <c r="CX7" s="29"/>
-      <c r="CY7" s="29"/>
-      <c r="CZ7" s="29"/>
-      <c r="DA7" s="29"/>
-      <c r="DB7" s="29"/>
-      <c r="DC7" s="29"/>
-      <c r="DD7" s="29"/>
-      <c r="DE7" s="29"/>
-      <c r="DF7" s="29"/>
-      <c r="DG7" s="29"/>
-      <c r="DH7" s="29"/>
-      <c r="DI7" s="29"/>
-      <c r="DJ7" s="29"/>
-      <c r="DK7" s="29"/>
-      <c r="DL7" s="29"/>
-      <c r="DM7" s="29"/>
-      <c r="DN7" s="29"/>
-      <c r="DO7" s="29"/>
-      <c r="DP7" s="29"/>
-      <c r="DQ7" s="29"/>
-      <c r="DR7" s="29"/>
-      <c r="DS7" s="29"/>
-      <c r="DT7" s="29"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="47"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="31"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="31"/>
+      <c r="O7" s="31"/>
+      <c r="P7" s="31"/>
+      <c r="Q7" s="31"/>
+      <c r="R7" s="31"/>
+      <c r="S7" s="31"/>
+      <c r="T7" s="31"/>
+      <c r="U7" s="31"/>
+      <c r="V7" s="56"/>
+      <c r="W7" s="56"/>
+      <c r="X7" s="31"/>
+      <c r="Y7" s="31"/>
+      <c r="Z7" s="54"/>
+      <c r="AA7" s="54"/>
+      <c r="AB7" s="54"/>
+      <c r="AC7" s="54"/>
+      <c r="AD7" s="31"/>
+      <c r="AE7" s="31"/>
+      <c r="AF7" s="31"/>
+      <c r="AG7" s="31"/>
+      <c r="AH7" s="31"/>
+      <c r="AI7" s="31"/>
+      <c r="AJ7" s="31"/>
+      <c r="AK7" s="31"/>
+      <c r="AL7" s="31"/>
+      <c r="AM7" s="31"/>
+      <c r="AN7" s="31"/>
+      <c r="AO7" s="31"/>
+      <c r="AP7" s="31"/>
+      <c r="AQ7" s="31"/>
+      <c r="AR7" s="31"/>
+      <c r="AS7" s="31"/>
+      <c r="AT7" s="31"/>
+      <c r="AU7" s="31"/>
+      <c r="AV7" s="31"/>
+      <c r="AW7" s="31"/>
+      <c r="AX7" s="31"/>
+      <c r="AY7" s="31"/>
+      <c r="AZ7" s="31"/>
+      <c r="BA7" s="31"/>
+      <c r="BB7" s="31"/>
+      <c r="BC7" s="31"/>
+      <c r="BD7" s="31"/>
+      <c r="BE7" s="31"/>
+      <c r="BF7" s="31"/>
+      <c r="BG7" s="31"/>
+      <c r="BH7" s="31"/>
+      <c r="BI7" s="31"/>
+      <c r="BJ7" s="31"/>
+      <c r="BK7" s="31"/>
+      <c r="BL7" s="31"/>
+      <c r="BM7" s="31"/>
+      <c r="BN7" s="31"/>
+      <c r="BO7" s="31"/>
+      <c r="BP7" s="31"/>
+      <c r="BQ7" s="31"/>
+      <c r="BR7" s="31"/>
+      <c r="BS7" s="31"/>
+      <c r="BT7" s="31"/>
+      <c r="BU7" s="31"/>
+      <c r="BV7" s="31"/>
+      <c r="BW7" s="31"/>
+      <c r="BX7" s="31"/>
+      <c r="BY7" s="31"/>
+      <c r="BZ7" s="31"/>
+      <c r="CA7" s="31"/>
+      <c r="CB7" s="31"/>
+      <c r="CC7" s="31"/>
+      <c r="CD7" s="31"/>
+      <c r="CE7" s="31"/>
+      <c r="CF7" s="31"/>
+      <c r="CG7" s="31"/>
+      <c r="CH7" s="31"/>
+      <c r="CI7" s="31"/>
+      <c r="CJ7" s="31"/>
+      <c r="CK7" s="31"/>
+      <c r="CL7" s="31"/>
+      <c r="CM7" s="31"/>
+      <c r="CN7" s="31"/>
+      <c r="CO7" s="31"/>
+      <c r="CP7" s="31"/>
+      <c r="CQ7" s="31"/>
+      <c r="CR7" s="31"/>
+      <c r="CS7" s="31"/>
+      <c r="CT7" s="31"/>
+      <c r="CU7" s="31"/>
+      <c r="CV7" s="31"/>
+      <c r="CW7" s="31"/>
+      <c r="CX7" s="31"/>
+      <c r="CY7" s="31"/>
+      <c r="CZ7" s="31"/>
+      <c r="DA7" s="31"/>
+      <c r="DB7" s="31"/>
+      <c r="DC7" s="31"/>
+      <c r="DD7" s="31"/>
+      <c r="DE7" s="31"/>
+      <c r="DF7" s="31"/>
+      <c r="DG7" s="31"/>
+      <c r="DH7" s="31"/>
+      <c r="DI7" s="31"/>
+      <c r="DJ7" s="31"/>
+      <c r="DK7" s="31"/>
+      <c r="DL7" s="31"/>
+      <c r="DM7" s="31"/>
+      <c r="DN7" s="31"/>
+      <c r="DO7" s="31"/>
+      <c r="DP7" s="31"/>
+      <c r="DQ7" s="31"/>
+      <c r="DR7" s="31"/>
+      <c r="DS7" s="31"/>
+      <c r="DT7" s="31"/>
     </row>
     <row r="8" spans="1:125" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="54" t="s">
+      <c r="A8" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="54"/>
-      <c r="C8" s="55">
+      <c r="B8" s="34"/>
+      <c r="C8" s="32">
         <f>SUM(C5:D7)</f>
         <v>75</v>
       </c>
-      <c r="D8" s="49"/>
+      <c r="D8" s="35"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="35">
-        <v>1</v>
-      </c>
-      <c r="G8" s="35">
+      <c r="F8" s="28">
+        <v>1</v>
+      </c>
+      <c r="G8" s="28">
         <v>2</v>
       </c>
-      <c r="H8" s="35">
+      <c r="H8" s="28">
         <v>3</v>
       </c>
-      <c r="I8" s="35">
+      <c r="I8" s="28">
         <v>4</v>
       </c>
-      <c r="J8" s="35">
+      <c r="J8" s="28">
         <v>5</v>
       </c>
-      <c r="K8" s="35">
+      <c r="K8" s="28">
         <v>6</v>
       </c>
-      <c r="L8" s="35">
+      <c r="L8" s="28">
         <v>7</v>
       </c>
-      <c r="M8" s="35">
+      <c r="M8" s="28">
         <v>8</v>
       </c>
-      <c r="N8" s="35">
+      <c r="N8" s="28">
         <v>9</v>
       </c>
-      <c r="O8" s="35">
+      <c r="O8" s="28">
         <v>10</v>
       </c>
-      <c r="P8" s="35">
+      <c r="P8" s="28">
         <v>11</v>
       </c>
-      <c r="Q8" s="35">
+      <c r="Q8" s="28">
         <v>12</v>
       </c>
-      <c r="R8" s="35">
+      <c r="R8" s="28">
         <v>13</v>
       </c>
-      <c r="S8" s="35">
+      <c r="S8" s="28">
         <v>14</v>
       </c>
-      <c r="T8" s="35">
+      <c r="T8" s="28">
         <v>15</v>
       </c>
-      <c r="U8" s="35">
+      <c r="U8" s="28">
         <v>16</v>
       </c>
-      <c r="V8" s="35">
+      <c r="V8" s="28">
         <v>17</v>
       </c>
-      <c r="W8" s="35">
+      <c r="W8" s="28">
         <v>18</v>
       </c>
-      <c r="X8" s="35">
+      <c r="X8" s="28">
         <v>19</v>
       </c>
-      <c r="Y8" s="35">
+      <c r="Y8" s="28">
         <v>20</v>
       </c>
-      <c r="Z8" s="35">
+      <c r="Z8" s="28">
         <v>21</v>
       </c>
-      <c r="AA8" s="35">
+      <c r="AA8" s="28">
         <v>22</v>
       </c>
-      <c r="AB8" s="35">
+      <c r="AB8" s="28">
         <v>23</v>
       </c>
-      <c r="AC8" s="35">
+      <c r="AC8" s="28">
         <v>24</v>
       </c>
-      <c r="AD8" s="35">
+      <c r="AD8" s="28">
         <v>25</v>
       </c>
-      <c r="AE8" s="35">
+      <c r="AE8" s="28">
         <v>26</v>
       </c>
-      <c r="AF8" s="35">
+      <c r="AF8" s="28">
         <v>27</v>
       </c>
-      <c r="AG8" s="35">
+      <c r="AG8" s="28">
         <v>28</v>
       </c>
-      <c r="AH8" s="35">
+      <c r="AH8" s="28">
         <v>29</v>
       </c>
-      <c r="AI8" s="35">
+      <c r="AI8" s="28">
         <v>30</v>
       </c>
-      <c r="AJ8" s="35">
+      <c r="AJ8" s="28">
         <v>31</v>
       </c>
-      <c r="AK8" s="35">
+      <c r="AK8" s="28">
         <v>32</v>
       </c>
-      <c r="AL8" s="35">
+      <c r="AL8" s="28">
         <v>33</v>
       </c>
-      <c r="AM8" s="35">
+      <c r="AM8" s="28">
         <v>34</v>
       </c>
-      <c r="AN8" s="35">
+      <c r="AN8" s="28">
         <v>35</v>
       </c>
-      <c r="AO8" s="35">
+      <c r="AO8" s="28">
         <v>36</v>
       </c>
-      <c r="AP8" s="35">
+      <c r="AP8" s="28">
         <v>37</v>
       </c>
-      <c r="AQ8" s="35">
+      <c r="AQ8" s="28">
         <v>38</v>
       </c>
-      <c r="AR8" s="35">
+      <c r="AR8" s="28">
         <v>39</v>
       </c>
-      <c r="AS8" s="35">
+      <c r="AS8" s="28">
         <v>40</v>
       </c>
-      <c r="AT8" s="35">
+      <c r="AT8" s="28">
         <v>41</v>
       </c>
-      <c r="AU8" s="35">
+      <c r="AU8" s="28">
         <v>42</v>
       </c>
-      <c r="AV8" s="35">
+      <c r="AV8" s="28">
         <v>43</v>
       </c>
-      <c r="AW8" s="35">
+      <c r="AW8" s="28">
         <v>44</v>
       </c>
-      <c r="AX8" s="35">
+      <c r="AX8" s="28">
         <v>45</v>
       </c>
-      <c r="AY8" s="35">
+      <c r="AY8" s="28">
         <v>46</v>
       </c>
-      <c r="AZ8" s="35">
+      <c r="AZ8" s="28">
         <v>47</v>
       </c>
-      <c r="BA8" s="35">
+      <c r="BA8" s="28">
         <v>48</v>
       </c>
-      <c r="BB8" s="35">
+      <c r="BB8" s="28">
         <v>49</v>
       </c>
-      <c r="BC8" s="35">
+      <c r="BC8" s="28">
         <v>50</v>
       </c>
-      <c r="BD8" s="35">
+      <c r="BD8" s="28">
         <v>51</v>
       </c>
-      <c r="BE8" s="35">
+      <c r="BE8" s="28">
         <v>52</v>
       </c>
-      <c r="BF8" s="35">
+      <c r="BF8" s="28">
         <v>53</v>
       </c>
-      <c r="BG8" s="35">
+      <c r="BG8" s="28">
         <v>54</v>
       </c>
-      <c r="BH8" s="35">
+      <c r="BH8" s="28">
         <v>55</v>
       </c>
-      <c r="BI8" s="35">
+      <c r="BI8" s="28">
         <v>56</v>
       </c>
-      <c r="BJ8" s="35">
+      <c r="BJ8" s="28">
         <v>57</v>
       </c>
-      <c r="BK8" s="35">
+      <c r="BK8" s="28">
         <v>58</v>
       </c>
-      <c r="BL8" s="35">
+      <c r="BL8" s="28">
         <v>59</v>
       </c>
-      <c r="BM8" s="35">
+      <c r="BM8" s="28">
         <v>60</v>
       </c>
-      <c r="BN8" s="35">
+      <c r="BN8" s="28">
         <v>61</v>
       </c>
-      <c r="BO8" s="35">
+      <c r="BO8" s="28">
         <v>62</v>
       </c>
-      <c r="BP8" s="35">
+      <c r="BP8" s="28">
         <v>63</v>
       </c>
-      <c r="BQ8" s="35">
+      <c r="BQ8" s="28">
         <v>64</v>
       </c>
-      <c r="BR8" s="35">
+      <c r="BR8" s="28">
         <v>65</v>
       </c>
-      <c r="BS8" s="35">
+      <c r="BS8" s="28">
         <v>66</v>
       </c>
-      <c r="BT8" s="35">
+      <c r="BT8" s="28">
         <v>67</v>
       </c>
-      <c r="BU8" s="35">
+      <c r="BU8" s="28">
         <v>68</v>
       </c>
-      <c r="BV8" s="35">
+      <c r="BV8" s="28">
         <v>69</v>
       </c>
-      <c r="BW8" s="35">
+      <c r="BW8" s="28">
         <v>70</v>
       </c>
-      <c r="BX8" s="35">
+      <c r="BX8" s="28">
         <v>71</v>
       </c>
-      <c r="BY8" s="35">
+      <c r="BY8" s="28">
         <v>72</v>
       </c>
-      <c r="BZ8" s="35">
+      <c r="BZ8" s="28">
         <v>73</v>
       </c>
-      <c r="CA8" s="35">
+      <c r="CA8" s="28">
         <v>74</v>
       </c>
-      <c r="CB8" s="35">
+      <c r="CB8" s="28">
         <v>75</v>
       </c>
-      <c r="CC8" s="35">
+      <c r="CC8" s="28">
         <v>76</v>
       </c>
-      <c r="CD8" s="35">
+      <c r="CD8" s="28">
         <v>77</v>
       </c>
-      <c r="CE8" s="35">
+      <c r="CE8" s="28">
         <v>78</v>
       </c>
-      <c r="CF8" s="35">
+      <c r="CF8" s="28">
         <v>79</v>
       </c>
-      <c r="CG8" s="35">
+      <c r="CG8" s="28">
         <v>80</v>
       </c>
-      <c r="CH8" s="35">
+      <c r="CH8" s="28">
         <v>81</v>
       </c>
-      <c r="CI8" s="35">
+      <c r="CI8" s="28">
         <v>82</v>
       </c>
-      <c r="CJ8" s="35">
+      <c r="CJ8" s="28">
         <v>83</v>
       </c>
-      <c r="CK8" s="35">
+      <c r="CK8" s="28">
         <v>84</v>
       </c>
-      <c r="CL8" s="35">
+      <c r="CL8" s="28">
         <v>85</v>
       </c>
-      <c r="CM8" s="35">
+      <c r="CM8" s="28">
         <v>86</v>
       </c>
-      <c r="CN8" s="35">
+      <c r="CN8" s="28">
         <v>87</v>
       </c>
-      <c r="CO8" s="35">
+      <c r="CO8" s="28">
         <v>88</v>
       </c>
-      <c r="CP8" s="35">
+      <c r="CP8" s="28">
         <v>89</v>
       </c>
-      <c r="CQ8" s="35">
+      <c r="CQ8" s="28">
         <v>90</v>
       </c>
-      <c r="CR8" s="35">
+      <c r="CR8" s="28">
         <v>91</v>
       </c>
-      <c r="CS8" s="35">
+      <c r="CS8" s="28">
         <v>92</v>
       </c>
-      <c r="CT8" s="35">
+      <c r="CT8" s="28">
         <v>93</v>
       </c>
-      <c r="CU8" s="35">
+      <c r="CU8" s="28">
         <v>94</v>
       </c>
-      <c r="CV8" s="35">
+      <c r="CV8" s="28">
         <v>95</v>
       </c>
-      <c r="CW8" s="35">
+      <c r="CW8" s="28">
         <v>96</v>
       </c>
-      <c r="CX8" s="35">
+      <c r="CX8" s="28">
         <v>97</v>
       </c>
-      <c r="CY8" s="35">
+      <c r="CY8" s="28">
         <v>98</v>
       </c>
-      <c r="CZ8" s="35">
+      <c r="CZ8" s="28">
         <v>99</v>
       </c>
-      <c r="DA8" s="35">
+      <c r="DA8" s="28">
         <v>100</v>
       </c>
-      <c r="DB8" s="35">
+      <c r="DB8" s="28">
         <v>101</v>
       </c>
-      <c r="DC8" s="35">
+      <c r="DC8" s="28">
         <v>102</v>
       </c>
-      <c r="DD8" s="35">
+      <c r="DD8" s="28">
         <v>103</v>
       </c>
-      <c r="DE8" s="35">
+      <c r="DE8" s="28">
         <v>104</v>
       </c>
-      <c r="DF8" s="35">
+      <c r="DF8" s="28">
         <v>105</v>
       </c>
-      <c r="DG8" s="35">
+      <c r="DG8" s="28">
         <v>106</v>
       </c>
-      <c r="DH8" s="35">
+      <c r="DH8" s="28">
         <v>107</v>
       </c>
-      <c r="DI8" s="35">
+      <c r="DI8" s="28">
         <v>108</v>
       </c>
-      <c r="DJ8" s="35">
+      <c r="DJ8" s="28">
         <v>109</v>
       </c>
-      <c r="DK8" s="35">
+      <c r="DK8" s="28">
         <v>110</v>
       </c>
-      <c r="DL8" s="35">
+      <c r="DL8" s="28">
         <v>111</v>
       </c>
-      <c r="DM8" s="35">
+      <c r="DM8" s="28">
         <v>112</v>
       </c>
-      <c r="DN8" s="35">
+      <c r="DN8" s="28">
         <v>113</v>
       </c>
-      <c r="DO8" s="35">
+      <c r="DO8" s="28">
         <v>114</v>
       </c>
-      <c r="DP8" s="35">
+      <c r="DP8" s="28">
         <v>115</v>
       </c>
-      <c r="DQ8" s="35">
+      <c r="DQ8" s="28">
         <v>116</v>
       </c>
-      <c r="DR8" s="35">
+      <c r="DR8" s="28">
         <v>117</v>
       </c>
-      <c r="DS8" s="35">
+      <c r="DS8" s="28">
         <v>118</v>
       </c>
-      <c r="DT8" s="35">
+      <c r="DT8" s="28">
         <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="46" t="s">
+      <c r="A9" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="56" t="s">
+      <c r="B9" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="57" t="s">
+      <c r="C9" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="56"/>
+      <c r="D9" s="37"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="36"/>
-      <c r="K9" s="36"/>
-      <c r="L9" s="36"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="36"/>
-      <c r="P9" s="36"/>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="36"/>
-      <c r="S9" s="36"/>
-      <c r="T9" s="36"/>
-      <c r="U9" s="36"/>
-      <c r="V9" s="36"/>
-      <c r="W9" s="36"/>
-      <c r="X9" s="36"/>
-      <c r="Y9" s="36"/>
-      <c r="Z9" s="36"/>
-      <c r="AA9" s="36"/>
-      <c r="AB9" s="36"/>
-      <c r="AC9" s="36"/>
-      <c r="AD9" s="36"/>
-      <c r="AE9" s="36"/>
-      <c r="AF9" s="36"/>
-      <c r="AG9" s="36"/>
-      <c r="AH9" s="36"/>
-      <c r="AI9" s="36"/>
-      <c r="AJ9" s="36"/>
-      <c r="AK9" s="36"/>
-      <c r="AL9" s="36"/>
-      <c r="AM9" s="36"/>
-      <c r="AN9" s="36"/>
-      <c r="AO9" s="36"/>
-      <c r="AP9" s="36"/>
-      <c r="AQ9" s="36"/>
-      <c r="AR9" s="36"/>
-      <c r="AS9" s="36"/>
-      <c r="AT9" s="36"/>
-      <c r="AU9" s="36"/>
-      <c r="AV9" s="36"/>
-      <c r="AW9" s="36"/>
-      <c r="AX9" s="36"/>
-      <c r="AY9" s="36"/>
-      <c r="AZ9" s="36"/>
-      <c r="BA9" s="36"/>
-      <c r="BB9" s="36"/>
-      <c r="BC9" s="36"/>
-      <c r="BD9" s="36"/>
-      <c r="BE9" s="36"/>
-      <c r="BF9" s="36"/>
-      <c r="BG9" s="36"/>
-      <c r="BH9" s="36"/>
-      <c r="BI9" s="36"/>
-      <c r="BJ9" s="36"/>
-      <c r="BK9" s="36"/>
-      <c r="BL9" s="36"/>
-      <c r="BM9" s="36"/>
-      <c r="BN9" s="36"/>
-      <c r="BO9" s="36"/>
-      <c r="BP9" s="36"/>
-      <c r="BQ9" s="36"/>
-      <c r="BR9" s="36"/>
-      <c r="BS9" s="36"/>
-      <c r="BT9" s="36"/>
-      <c r="BU9" s="36"/>
-      <c r="BV9" s="36"/>
-      <c r="BW9" s="36"/>
-      <c r="BX9" s="36"/>
-      <c r="BY9" s="36"/>
-      <c r="BZ9" s="36"/>
-      <c r="CA9" s="36"/>
-      <c r="CB9" s="36"/>
-      <c r="CC9" s="36"/>
-      <c r="CD9" s="36"/>
-      <c r="CE9" s="36"/>
-      <c r="CF9" s="36"/>
-      <c r="CG9" s="36"/>
-      <c r="CH9" s="36"/>
-      <c r="CI9" s="36"/>
-      <c r="CJ9" s="36"/>
-      <c r="CK9" s="36"/>
-      <c r="CL9" s="36"/>
-      <c r="CM9" s="36"/>
-      <c r="CN9" s="36"/>
-      <c r="CO9" s="36"/>
-      <c r="CP9" s="36"/>
-      <c r="CQ9" s="36"/>
-      <c r="CR9" s="36"/>
-      <c r="CS9" s="36"/>
-      <c r="CT9" s="36"/>
-      <c r="CU9" s="36"/>
-      <c r="CV9" s="36"/>
-      <c r="CW9" s="36"/>
-      <c r="CX9" s="36"/>
-      <c r="CY9" s="36"/>
-      <c r="CZ9" s="36"/>
-      <c r="DA9" s="36"/>
-      <c r="DB9" s="36"/>
-      <c r="DC9" s="36"/>
-      <c r="DD9" s="36"/>
-      <c r="DE9" s="36"/>
-      <c r="DF9" s="36"/>
-      <c r="DG9" s="36"/>
-      <c r="DH9" s="36"/>
-      <c r="DI9" s="36"/>
-      <c r="DJ9" s="36"/>
-      <c r="DK9" s="36"/>
-      <c r="DL9" s="36"/>
-      <c r="DM9" s="36"/>
-      <c r="DN9" s="36"/>
-      <c r="DO9" s="36"/>
-      <c r="DP9" s="36"/>
-      <c r="DQ9" s="36"/>
-      <c r="DR9" s="36"/>
-      <c r="DS9" s="36"/>
-      <c r="DT9" s="36"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="29"/>
+      <c r="M9" s="29"/>
+      <c r="N9" s="29"/>
+      <c r="O9" s="29"/>
+      <c r="P9" s="29"/>
+      <c r="Q9" s="29"/>
+      <c r="R9" s="29"/>
+      <c r="S9" s="29"/>
+      <c r="T9" s="29"/>
+      <c r="U9" s="29"/>
+      <c r="V9" s="29"/>
+      <c r="W9" s="29"/>
+      <c r="X9" s="29"/>
+      <c r="Y9" s="29"/>
+      <c r="Z9" s="29"/>
+      <c r="AA9" s="29"/>
+      <c r="AB9" s="29"/>
+      <c r="AC9" s="29"/>
+      <c r="AD9" s="29"/>
+      <c r="AE9" s="29"/>
+      <c r="AF9" s="29"/>
+      <c r="AG9" s="29"/>
+      <c r="AH9" s="29"/>
+      <c r="AI9" s="29"/>
+      <c r="AJ9" s="29"/>
+      <c r="AK9" s="29"/>
+      <c r="AL9" s="29"/>
+      <c r="AM9" s="29"/>
+      <c r="AN9" s="29"/>
+      <c r="AO9" s="29"/>
+      <c r="AP9" s="29"/>
+      <c r="AQ9" s="29"/>
+      <c r="AR9" s="29"/>
+      <c r="AS9" s="29"/>
+      <c r="AT9" s="29"/>
+      <c r="AU9" s="29"/>
+      <c r="AV9" s="29"/>
+      <c r="AW9" s="29"/>
+      <c r="AX9" s="29"/>
+      <c r="AY9" s="29"/>
+      <c r="AZ9" s="29"/>
+      <c r="BA9" s="29"/>
+      <c r="BB9" s="29"/>
+      <c r="BC9" s="29"/>
+      <c r="BD9" s="29"/>
+      <c r="BE9" s="29"/>
+      <c r="BF9" s="29"/>
+      <c r="BG9" s="29"/>
+      <c r="BH9" s="29"/>
+      <c r="BI9" s="29"/>
+      <c r="BJ9" s="29"/>
+      <c r="BK9" s="29"/>
+      <c r="BL9" s="29"/>
+      <c r="BM9" s="29"/>
+      <c r="BN9" s="29"/>
+      <c r="BO9" s="29"/>
+      <c r="BP9" s="29"/>
+      <c r="BQ9" s="29"/>
+      <c r="BR9" s="29"/>
+      <c r="BS9" s="29"/>
+      <c r="BT9" s="29"/>
+      <c r="BU9" s="29"/>
+      <c r="BV9" s="29"/>
+      <c r="BW9" s="29"/>
+      <c r="BX9" s="29"/>
+      <c r="BY9" s="29"/>
+      <c r="BZ9" s="29"/>
+      <c r="CA9" s="29"/>
+      <c r="CB9" s="29"/>
+      <c r="CC9" s="29"/>
+      <c r="CD9" s="29"/>
+      <c r="CE9" s="29"/>
+      <c r="CF9" s="29"/>
+      <c r="CG9" s="29"/>
+      <c r="CH9" s="29"/>
+      <c r="CI9" s="29"/>
+      <c r="CJ9" s="29"/>
+      <c r="CK9" s="29"/>
+      <c r="CL9" s="29"/>
+      <c r="CM9" s="29"/>
+      <c r="CN9" s="29"/>
+      <c r="CO9" s="29"/>
+      <c r="CP9" s="29"/>
+      <c r="CQ9" s="29"/>
+      <c r="CR9" s="29"/>
+      <c r="CS9" s="29"/>
+      <c r="CT9" s="29"/>
+      <c r="CU9" s="29"/>
+      <c r="CV9" s="29"/>
+      <c r="CW9" s="29"/>
+      <c r="CX9" s="29"/>
+      <c r="CY9" s="29"/>
+      <c r="CZ9" s="29"/>
+      <c r="DA9" s="29"/>
+      <c r="DB9" s="29"/>
+      <c r="DC9" s="29"/>
+      <c r="DD9" s="29"/>
+      <c r="DE9" s="29"/>
+      <c r="DF9" s="29"/>
+      <c r="DG9" s="29"/>
+      <c r="DH9" s="29"/>
+      <c r="DI9" s="29"/>
+      <c r="DJ9" s="29"/>
+      <c r="DK9" s="29"/>
+      <c r="DL9" s="29"/>
+      <c r="DM9" s="29"/>
+      <c r="DN9" s="29"/>
+      <c r="DO9" s="29"/>
+      <c r="DP9" s="29"/>
+      <c r="DQ9" s="29"/>
+      <c r="DR9" s="29"/>
+      <c r="DS9" s="29"/>
+      <c r="DT9" s="29"/>
     </row>
     <row r="10" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="46"/>
-      <c r="B10" s="56"/>
+      <c r="A10" s="36"/>
+      <c r="B10" s="37"/>
       <c r="C10" s="6"/>
       <c r="D10" s="4" t="s">
         <v>10</v>
@@ -4818,250 +4828,250 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E26" s="55"/>
-      <c r="F26" s="48"/>
-      <c r="G26" s="48"/>
-      <c r="H26" s="48"/>
-      <c r="I26" s="48"/>
-      <c r="J26" s="48"/>
-      <c r="K26" s="48"/>
-      <c r="L26" s="48"/>
-      <c r="M26" s="48"/>
-      <c r="N26" s="48"/>
-      <c r="O26" s="48"/>
-      <c r="P26" s="48"/>
-      <c r="Q26" s="48"/>
-      <c r="R26" s="48"/>
-      <c r="S26" s="48"/>
-      <c r="T26" s="48"/>
-      <c r="U26" s="48"/>
-      <c r="V26" s="48"/>
-      <c r="W26" s="48"/>
-      <c r="X26" s="48"/>
-      <c r="Y26" s="48"/>
-      <c r="Z26" s="48"/>
-      <c r="AA26" s="48"/>
-      <c r="AB26" s="48"/>
-      <c r="AC26" s="48"/>
-      <c r="AD26" s="48"/>
-      <c r="AE26" s="48"/>
-      <c r="AF26" s="48"/>
-      <c r="AG26" s="48"/>
-      <c r="AH26" s="48"/>
-      <c r="AI26" s="48"/>
-      <c r="AJ26" s="48"/>
-      <c r="AK26" s="48"/>
-      <c r="AL26" s="48"/>
-      <c r="AM26" s="48"/>
-      <c r="AN26" s="48"/>
-      <c r="AO26" s="48"/>
-      <c r="AP26" s="48"/>
-      <c r="AQ26" s="48"/>
-      <c r="AR26" s="48"/>
-      <c r="AS26" s="48"/>
-      <c r="AT26" s="48"/>
-      <c r="AU26" s="48"/>
-      <c r="AV26" s="48"/>
-      <c r="AW26" s="48"/>
-      <c r="AX26" s="48"/>
-      <c r="AY26" s="48"/>
-      <c r="AZ26" s="48"/>
-      <c r="BA26" s="48"/>
-      <c r="BB26" s="48"/>
-      <c r="BC26" s="48"/>
-      <c r="BD26" s="48"/>
-      <c r="BE26" s="48"/>
-      <c r="BF26" s="48"/>
-      <c r="BG26" s="48"/>
-      <c r="BH26" s="48"/>
-      <c r="BI26" s="48"/>
-      <c r="BJ26" s="48"/>
-      <c r="BK26" s="48"/>
-      <c r="BL26" s="48"/>
-      <c r="BM26" s="48"/>
-      <c r="BN26" s="48"/>
-      <c r="BO26" s="48"/>
-      <c r="BP26" s="48"/>
-      <c r="BQ26" s="48"/>
-      <c r="BR26" s="48"/>
-      <c r="BS26" s="48"/>
-      <c r="BT26" s="48"/>
-      <c r="BU26" s="48"/>
-      <c r="BV26" s="48"/>
-      <c r="BW26" s="48"/>
-      <c r="BX26" s="48"/>
-      <c r="BY26" s="48"/>
-      <c r="BZ26" s="48"/>
-      <c r="CA26" s="48"/>
-      <c r="CB26" s="48"/>
-      <c r="CC26" s="48"/>
-      <c r="CD26" s="48"/>
-      <c r="CE26" s="48"/>
-      <c r="CF26" s="48"/>
-      <c r="CG26" s="48"/>
-      <c r="CH26" s="48"/>
-      <c r="CI26" s="48"/>
-      <c r="CJ26" s="48"/>
-      <c r="CK26" s="48"/>
-      <c r="CL26" s="48"/>
-      <c r="CM26" s="48"/>
-      <c r="CN26" s="48"/>
-      <c r="CO26" s="48"/>
-      <c r="CP26" s="48"/>
-      <c r="CQ26" s="48"/>
-      <c r="CR26" s="48"/>
-      <c r="CS26" s="48"/>
-      <c r="CT26" s="48"/>
-      <c r="CU26" s="48"/>
-      <c r="CV26" s="48"/>
-      <c r="CW26" s="48"/>
-      <c r="CX26" s="48"/>
-      <c r="CY26" s="48"/>
-      <c r="CZ26" s="48"/>
-      <c r="DA26" s="48"/>
-      <c r="DB26" s="48"/>
-      <c r="DC26" s="48"/>
-      <c r="DD26" s="48"/>
-      <c r="DE26" s="48"/>
-      <c r="DF26" s="48"/>
-      <c r="DG26" s="48"/>
-      <c r="DH26" s="48"/>
-      <c r="DI26" s="48"/>
-      <c r="DJ26" s="48"/>
-      <c r="DK26" s="48"/>
-      <c r="DL26" s="48"/>
-      <c r="DM26" s="48"/>
-      <c r="DN26" s="48"/>
-      <c r="DO26" s="48"/>
-      <c r="DP26" s="48"/>
-      <c r="DQ26" s="48"/>
-      <c r="DR26" s="48"/>
-      <c r="DS26" s="48"/>
-      <c r="DT26" s="48"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="33"/>
+      <c r="L26" s="33"/>
+      <c r="M26" s="33"/>
+      <c r="N26" s="33"/>
+      <c r="O26" s="33"/>
+      <c r="P26" s="33"/>
+      <c r="Q26" s="33"/>
+      <c r="R26" s="33"/>
+      <c r="S26" s="33"/>
+      <c r="T26" s="33"/>
+      <c r="U26" s="33"/>
+      <c r="V26" s="33"/>
+      <c r="W26" s="33"/>
+      <c r="X26" s="33"/>
+      <c r="Y26" s="33"/>
+      <c r="Z26" s="33"/>
+      <c r="AA26" s="33"/>
+      <c r="AB26" s="33"/>
+      <c r="AC26" s="33"/>
+      <c r="AD26" s="33"/>
+      <c r="AE26" s="33"/>
+      <c r="AF26" s="33"/>
+      <c r="AG26" s="33"/>
+      <c r="AH26" s="33"/>
+      <c r="AI26" s="33"/>
+      <c r="AJ26" s="33"/>
+      <c r="AK26" s="33"/>
+      <c r="AL26" s="33"/>
+      <c r="AM26" s="33"/>
+      <c r="AN26" s="33"/>
+      <c r="AO26" s="33"/>
+      <c r="AP26" s="33"/>
+      <c r="AQ26" s="33"/>
+      <c r="AR26" s="33"/>
+      <c r="AS26" s="33"/>
+      <c r="AT26" s="33"/>
+      <c r="AU26" s="33"/>
+      <c r="AV26" s="33"/>
+      <c r="AW26" s="33"/>
+      <c r="AX26" s="33"/>
+      <c r="AY26" s="33"/>
+      <c r="AZ26" s="33"/>
+      <c r="BA26" s="33"/>
+      <c r="BB26" s="33"/>
+      <c r="BC26" s="33"/>
+      <c r="BD26" s="33"/>
+      <c r="BE26" s="33"/>
+      <c r="BF26" s="33"/>
+      <c r="BG26" s="33"/>
+      <c r="BH26" s="33"/>
+      <c r="BI26" s="33"/>
+      <c r="BJ26" s="33"/>
+      <c r="BK26" s="33"/>
+      <c r="BL26" s="33"/>
+      <c r="BM26" s="33"/>
+      <c r="BN26" s="33"/>
+      <c r="BO26" s="33"/>
+      <c r="BP26" s="33"/>
+      <c r="BQ26" s="33"/>
+      <c r="BR26" s="33"/>
+      <c r="BS26" s="33"/>
+      <c r="BT26" s="33"/>
+      <c r="BU26" s="33"/>
+      <c r="BV26" s="33"/>
+      <c r="BW26" s="33"/>
+      <c r="BX26" s="33"/>
+      <c r="BY26" s="33"/>
+      <c r="BZ26" s="33"/>
+      <c r="CA26" s="33"/>
+      <c r="CB26" s="33"/>
+      <c r="CC26" s="33"/>
+      <c r="CD26" s="33"/>
+      <c r="CE26" s="33"/>
+      <c r="CF26" s="33"/>
+      <c r="CG26" s="33"/>
+      <c r="CH26" s="33"/>
+      <c r="CI26" s="33"/>
+      <c r="CJ26" s="33"/>
+      <c r="CK26" s="33"/>
+      <c r="CL26" s="33"/>
+      <c r="CM26" s="33"/>
+      <c r="CN26" s="33"/>
+      <c r="CO26" s="33"/>
+      <c r="CP26" s="33"/>
+      <c r="CQ26" s="33"/>
+      <c r="CR26" s="33"/>
+      <c r="CS26" s="33"/>
+      <c r="CT26" s="33"/>
+      <c r="CU26" s="33"/>
+      <c r="CV26" s="33"/>
+      <c r="CW26" s="33"/>
+      <c r="CX26" s="33"/>
+      <c r="CY26" s="33"/>
+      <c r="CZ26" s="33"/>
+      <c r="DA26" s="33"/>
+      <c r="DB26" s="33"/>
+      <c r="DC26" s="33"/>
+      <c r="DD26" s="33"/>
+      <c r="DE26" s="33"/>
+      <c r="DF26" s="33"/>
+      <c r="DG26" s="33"/>
+      <c r="DH26" s="33"/>
+      <c r="DI26" s="33"/>
+      <c r="DJ26" s="33"/>
+      <c r="DK26" s="33"/>
+      <c r="DL26" s="33"/>
+      <c r="DM26" s="33"/>
+      <c r="DN26" s="33"/>
+      <c r="DO26" s="33"/>
+      <c r="DP26" s="33"/>
+      <c r="DQ26" s="33"/>
+      <c r="DR26" s="33"/>
+      <c r="DS26" s="33"/>
+      <c r="DT26" s="33"/>
     </row>
     <row r="27" spans="1:124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E27" s="1">
         <v>4</v>
       </c>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="32"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="32"/>
-      <c r="K27" s="32"/>
-      <c r="L27" s="32"/>
-      <c r="M27" s="32"/>
-      <c r="N27" s="32"/>
-      <c r="O27" s="32"/>
-      <c r="P27" s="32"/>
-      <c r="Q27" s="32"/>
-      <c r="R27" s="32"/>
-      <c r="S27" s="32"/>
-      <c r="T27" s="32"/>
-      <c r="U27" s="32"/>
-      <c r="V27" s="32"/>
-      <c r="W27" s="32"/>
-      <c r="X27" s="32"/>
-      <c r="Y27" s="32"/>
-      <c r="Z27" s="32"/>
-      <c r="AA27" s="32"/>
-      <c r="AB27" s="32"/>
-      <c r="AC27" s="32"/>
-      <c r="AD27" s="32"/>
-      <c r="AE27" s="32"/>
-      <c r="AF27" s="32"/>
-      <c r="AG27" s="32"/>
-      <c r="AH27" s="32"/>
-      <c r="AI27" s="32"/>
-      <c r="AJ27" s="32"/>
-      <c r="AK27" s="32"/>
-      <c r="AL27" s="32"/>
-      <c r="AM27" s="32"/>
-      <c r="AN27" s="32"/>
-      <c r="AO27" s="32"/>
-      <c r="AP27" s="32"/>
-      <c r="AQ27" s="32"/>
-      <c r="AR27" s="32"/>
-      <c r="AS27" s="32"/>
-      <c r="AT27" s="32"/>
-      <c r="AU27" s="32"/>
-      <c r="AV27" s="32"/>
-      <c r="AW27" s="32"/>
-      <c r="AX27" s="32"/>
-      <c r="AY27" s="32"/>
-      <c r="AZ27" s="32"/>
-      <c r="BA27" s="32"/>
-      <c r="BB27" s="32"/>
-      <c r="BC27" s="32"/>
-      <c r="BD27" s="32"/>
-      <c r="BE27" s="32"/>
-      <c r="BF27" s="32"/>
-      <c r="BG27" s="32"/>
-      <c r="BH27" s="32"/>
-      <c r="BI27" s="32"/>
-      <c r="BJ27" s="32"/>
-      <c r="BK27" s="32"/>
-      <c r="BL27" s="32"/>
-      <c r="BM27" s="32"/>
-      <c r="BN27" s="32"/>
-      <c r="BO27" s="32"/>
-      <c r="BP27" s="32"/>
-      <c r="BQ27" s="32"/>
-      <c r="BR27" s="32"/>
-      <c r="BS27" s="32"/>
-      <c r="BT27" s="32"/>
-      <c r="BU27" s="32"/>
-      <c r="BV27" s="32"/>
-      <c r="BW27" s="32"/>
-      <c r="BX27" s="32"/>
-      <c r="BY27" s="32"/>
-      <c r="BZ27" s="32"/>
-      <c r="CA27" s="32"/>
-      <c r="CB27" s="32"/>
-      <c r="CC27" s="32"/>
-      <c r="CD27" s="32"/>
-      <c r="CE27" s="33"/>
-      <c r="CF27" s="34"/>
-      <c r="CG27" s="34"/>
-      <c r="CH27" s="34"/>
-      <c r="CI27" s="34"/>
-      <c r="CJ27" s="34"/>
-      <c r="CK27" s="34"/>
-      <c r="CL27" s="34"/>
-      <c r="CM27" s="34"/>
-      <c r="CN27" s="34"/>
-      <c r="CO27" s="34"/>
-      <c r="CP27" s="34"/>
-      <c r="CQ27" s="34"/>
-      <c r="CR27" s="34"/>
-      <c r="CS27" s="34"/>
-      <c r="CT27" s="34"/>
-      <c r="CU27" s="34"/>
-      <c r="CV27" s="34"/>
-      <c r="CW27" s="34"/>
-      <c r="CX27" s="34"/>
-      <c r="CY27" s="34"/>
-      <c r="CZ27" s="34"/>
-      <c r="DA27" s="34"/>
-      <c r="DB27" s="34"/>
-      <c r="DC27" s="34"/>
-      <c r="DD27" s="34"/>
-      <c r="DE27" s="34"/>
-      <c r="DF27" s="34"/>
-      <c r="DG27" s="34"/>
-      <c r="DH27" s="34"/>
-      <c r="DI27" s="34"/>
-      <c r="DJ27" s="34"/>
-      <c r="DK27" s="34"/>
-      <c r="DL27" s="34"/>
-      <c r="DM27" s="34"/>
-      <c r="DN27" s="34"/>
-      <c r="DO27" s="34"/>
-      <c r="DP27" s="34"/>
-      <c r="DQ27" s="34"/>
-      <c r="DR27" s="34"/>
-      <c r="DS27" s="34"/>
-      <c r="DT27" s="34"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="57"/>
+      <c r="H27" s="57"/>
+      <c r="I27" s="57"/>
+      <c r="J27" s="57"/>
+      <c r="K27" s="57"/>
+      <c r="L27" s="57"/>
+      <c r="M27" s="57"/>
+      <c r="N27" s="57"/>
+      <c r="O27" s="57"/>
+      <c r="P27" s="57"/>
+      <c r="Q27" s="57"/>
+      <c r="R27" s="57"/>
+      <c r="S27" s="57"/>
+      <c r="T27" s="57"/>
+      <c r="U27" s="57"/>
+      <c r="V27" s="57"/>
+      <c r="W27" s="57"/>
+      <c r="X27" s="57"/>
+      <c r="Y27" s="57"/>
+      <c r="Z27" s="57"/>
+      <c r="AA27" s="57"/>
+      <c r="AB27" s="57"/>
+      <c r="AC27" s="57"/>
+      <c r="AD27" s="57"/>
+      <c r="AE27" s="57"/>
+      <c r="AF27" s="57"/>
+      <c r="AG27" s="57"/>
+      <c r="AH27" s="57"/>
+      <c r="AI27" s="57"/>
+      <c r="AJ27" s="57"/>
+      <c r="AK27" s="57"/>
+      <c r="AL27" s="57"/>
+      <c r="AM27" s="57"/>
+      <c r="AN27" s="57"/>
+      <c r="AO27" s="57"/>
+      <c r="AP27" s="57"/>
+      <c r="AQ27" s="57"/>
+      <c r="AR27" s="57"/>
+      <c r="AS27" s="57"/>
+      <c r="AT27" s="57"/>
+      <c r="AU27" s="57"/>
+      <c r="AV27" s="57"/>
+      <c r="AW27" s="57"/>
+      <c r="AX27" s="57"/>
+      <c r="AY27" s="57"/>
+      <c r="AZ27" s="57"/>
+      <c r="BA27" s="57"/>
+      <c r="BB27" s="57"/>
+      <c r="BC27" s="57"/>
+      <c r="BD27" s="57"/>
+      <c r="BE27" s="57"/>
+      <c r="BF27" s="57"/>
+      <c r="BG27" s="57"/>
+      <c r="BH27" s="57"/>
+      <c r="BI27" s="57"/>
+      <c r="BJ27" s="57"/>
+      <c r="BK27" s="57"/>
+      <c r="BL27" s="57"/>
+      <c r="BM27" s="57"/>
+      <c r="BN27" s="57"/>
+      <c r="BO27" s="57"/>
+      <c r="BP27" s="57"/>
+      <c r="BQ27" s="57"/>
+      <c r="BR27" s="57"/>
+      <c r="BS27" s="57"/>
+      <c r="BT27" s="57"/>
+      <c r="BU27" s="57"/>
+      <c r="BV27" s="57"/>
+      <c r="BW27" s="57"/>
+      <c r="BX27" s="57"/>
+      <c r="BY27" s="57"/>
+      <c r="BZ27" s="57"/>
+      <c r="CA27" s="57"/>
+      <c r="CB27" s="57"/>
+      <c r="CC27" s="57"/>
+      <c r="CD27" s="57"/>
+      <c r="CE27" s="58"/>
+      <c r="CF27" s="59"/>
+      <c r="CG27" s="59"/>
+      <c r="CH27" s="59"/>
+      <c r="CI27" s="59"/>
+      <c r="CJ27" s="59"/>
+      <c r="CK27" s="59"/>
+      <c r="CL27" s="59"/>
+      <c r="CM27" s="59"/>
+      <c r="CN27" s="59"/>
+      <c r="CO27" s="59"/>
+      <c r="CP27" s="59"/>
+      <c r="CQ27" s="59"/>
+      <c r="CR27" s="59"/>
+      <c r="CS27" s="59"/>
+      <c r="CT27" s="59"/>
+      <c r="CU27" s="59"/>
+      <c r="CV27" s="59"/>
+      <c r="CW27" s="59"/>
+      <c r="CX27" s="59"/>
+      <c r="CY27" s="59"/>
+      <c r="CZ27" s="59"/>
+      <c r="DA27" s="59"/>
+      <c r="DB27" s="59"/>
+      <c r="DC27" s="59"/>
+      <c r="DD27" s="59"/>
+      <c r="DE27" s="59"/>
+      <c r="DF27" s="59"/>
+      <c r="DG27" s="59"/>
+      <c r="DH27" s="59"/>
+      <c r="DI27" s="59"/>
+      <c r="DJ27" s="59"/>
+      <c r="DK27" s="59"/>
+      <c r="DL27" s="59"/>
+      <c r="DM27" s="59"/>
+      <c r="DN27" s="59"/>
+      <c r="DO27" s="59"/>
+      <c r="DP27" s="59"/>
+      <c r="DQ27" s="59"/>
+      <c r="DR27" s="59"/>
+      <c r="DS27" s="59"/>
+      <c r="DT27" s="59"/>
     </row>
     <row r="29" spans="1:124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E29" s="22">
@@ -5086,7 +5096,249 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="265">
+  <mergeCells count="266">
+    <mergeCell ref="AD1:AG1"/>
+    <mergeCell ref="V1:Y1"/>
+    <mergeCell ref="R1:U1"/>
+    <mergeCell ref="DQ2:DQ7"/>
+    <mergeCell ref="DR2:DR7"/>
+    <mergeCell ref="DS2:DS7"/>
+    <mergeCell ref="DT2:DT7"/>
+    <mergeCell ref="CX2:CX7"/>
+    <mergeCell ref="CY2:CY7"/>
+    <mergeCell ref="DA2:DA7"/>
+    <mergeCell ref="DB2:DB7"/>
+    <mergeCell ref="DC2:DC7"/>
+    <mergeCell ref="DD2:DD7"/>
+    <mergeCell ref="DE2:DE7"/>
+    <mergeCell ref="CZ2:CZ7"/>
+    <mergeCell ref="DN2:DN7"/>
+    <mergeCell ref="DO2:DO7"/>
+    <mergeCell ref="DP2:DP7"/>
+    <mergeCell ref="DG2:DG7"/>
+    <mergeCell ref="DH2:DH7"/>
+    <mergeCell ref="DI2:DI7"/>
+    <mergeCell ref="DJ2:DJ7"/>
+    <mergeCell ref="DK2:DK7"/>
+    <mergeCell ref="U2:U7"/>
+    <mergeCell ref="V2:V7"/>
+    <mergeCell ref="W2:W7"/>
+    <mergeCell ref="F27:S27"/>
+    <mergeCell ref="T27:AW27"/>
+    <mergeCell ref="AX27:CD27"/>
+    <mergeCell ref="CE27:DT27"/>
+    <mergeCell ref="DG8:DG9"/>
+    <mergeCell ref="DH8:DH9"/>
+    <mergeCell ref="DI8:DI9"/>
+    <mergeCell ref="DJ8:DJ9"/>
+    <mergeCell ref="DK8:DK9"/>
+    <mergeCell ref="DL8:DL9"/>
+    <mergeCell ref="DM8:DM9"/>
+    <mergeCell ref="DN8:DN9"/>
+    <mergeCell ref="DO8:DO9"/>
+    <mergeCell ref="DP8:DP9"/>
+    <mergeCell ref="DA8:DA9"/>
+    <mergeCell ref="DB8:DB9"/>
+    <mergeCell ref="DC8:DC9"/>
+    <mergeCell ref="DD8:DD9"/>
+    <mergeCell ref="DE8:DE9"/>
+    <mergeCell ref="CQ8:CQ9"/>
+    <mergeCell ref="CR8:CR9"/>
+    <mergeCell ref="CS8:CS9"/>
+    <mergeCell ref="BN8:BN9"/>
+    <mergeCell ref="CI8:CI9"/>
+    <mergeCell ref="CK8:CK9"/>
+    <mergeCell ref="CL8:CL9"/>
+    <mergeCell ref="BX8:BX9"/>
+    <mergeCell ref="BY8:BY9"/>
+    <mergeCell ref="DL2:DL7"/>
+    <mergeCell ref="DM2:DM7"/>
+    <mergeCell ref="DF2:DF7"/>
+    <mergeCell ref="BD2:BD7"/>
+    <mergeCell ref="BE2:BE7"/>
+    <mergeCell ref="BF2:BF7"/>
+    <mergeCell ref="BG2:BG7"/>
+    <mergeCell ref="BM2:BM7"/>
+    <mergeCell ref="BN2:BN7"/>
+    <mergeCell ref="BO2:BO7"/>
+    <mergeCell ref="BP2:BP7"/>
+    <mergeCell ref="CA2:CA7"/>
+    <mergeCell ref="BW2:BW7"/>
+    <mergeCell ref="BX2:BX7"/>
+    <mergeCell ref="BY2:BY7"/>
+    <mergeCell ref="BZ2:BZ7"/>
+    <mergeCell ref="BH2:BH7"/>
+    <mergeCell ref="BI2:BI7"/>
+    <mergeCell ref="BJ2:BJ7"/>
+    <mergeCell ref="BK2:BK7"/>
+    <mergeCell ref="X2:X7"/>
+    <mergeCell ref="AF2:AF7"/>
+    <mergeCell ref="AX2:AX7"/>
+    <mergeCell ref="AY2:AY7"/>
+    <mergeCell ref="AZ2:AZ7"/>
+    <mergeCell ref="BL2:BL7"/>
+    <mergeCell ref="BA2:BA7"/>
+    <mergeCell ref="BB2:BB7"/>
+    <mergeCell ref="BC2:BC7"/>
+    <mergeCell ref="AP2:AP7"/>
+    <mergeCell ref="AQ2:AQ7"/>
+    <mergeCell ref="AR2:AR7"/>
+    <mergeCell ref="AS2:AS7"/>
+    <mergeCell ref="AT2:AT7"/>
+    <mergeCell ref="AU2:AU7"/>
+    <mergeCell ref="AV2:AV7"/>
+    <mergeCell ref="AW2:AW7"/>
+    <mergeCell ref="CW2:CW7"/>
+    <mergeCell ref="CU2:CU7"/>
+    <mergeCell ref="CV2:CV7"/>
+    <mergeCell ref="CQ2:CQ7"/>
+    <mergeCell ref="CR2:CR7"/>
+    <mergeCell ref="CS2:CS7"/>
+    <mergeCell ref="CT2:CT7"/>
+    <mergeCell ref="CI2:CI7"/>
+    <mergeCell ref="CJ2:CJ7"/>
+    <mergeCell ref="CK2:CK7"/>
+    <mergeCell ref="CL2:CL7"/>
+    <mergeCell ref="CM2:CM7"/>
+    <mergeCell ref="CN2:CN7"/>
+    <mergeCell ref="CO2:CO7"/>
+    <mergeCell ref="CP2:CP7"/>
+    <mergeCell ref="N2:N7"/>
+    <mergeCell ref="O2:O7"/>
+    <mergeCell ref="P2:P7"/>
+    <mergeCell ref="Q2:Q7"/>
+    <mergeCell ref="R2:R7"/>
+    <mergeCell ref="S2:S7"/>
+    <mergeCell ref="T2:T7"/>
+    <mergeCell ref="CN8:CN9"/>
+    <mergeCell ref="Y2:Y7"/>
+    <mergeCell ref="Z2:Z7"/>
+    <mergeCell ref="AA2:AA7"/>
+    <mergeCell ref="AB2:AB7"/>
+    <mergeCell ref="AC2:AC7"/>
+    <mergeCell ref="AD2:AD7"/>
+    <mergeCell ref="AE2:AE7"/>
+    <mergeCell ref="AH2:AH7"/>
+    <mergeCell ref="AI2:AI7"/>
+    <mergeCell ref="AJ2:AJ7"/>
+    <mergeCell ref="AK2:AK7"/>
+    <mergeCell ref="AL2:AL7"/>
+    <mergeCell ref="AM2:AM7"/>
+    <mergeCell ref="AN2:AN7"/>
+    <mergeCell ref="AO2:AO7"/>
+    <mergeCell ref="AG2:AG7"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="F2:F7"/>
+    <mergeCell ref="G2:G7"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="I2:I7"/>
+    <mergeCell ref="J2:J7"/>
+    <mergeCell ref="K2:K7"/>
+    <mergeCell ref="L2:L7"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="M2:M7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="E26:DT26"/>
+    <mergeCell ref="DF8:DF9"/>
+    <mergeCell ref="DQ8:DQ9"/>
+    <mergeCell ref="DR8:DR9"/>
+    <mergeCell ref="DS8:DS9"/>
+    <mergeCell ref="DT8:DT9"/>
+    <mergeCell ref="CY8:CY9"/>
+    <mergeCell ref="CZ8:CZ9"/>
+    <mergeCell ref="CM8:CM9"/>
+    <mergeCell ref="CW8:CW9"/>
+    <mergeCell ref="CX8:CX9"/>
+    <mergeCell ref="BU8:BU9"/>
+    <mergeCell ref="BV8:BV9"/>
+    <mergeCell ref="BW8:BW9"/>
+    <mergeCell ref="BF8:BF9"/>
+    <mergeCell ref="BG8:BG9"/>
+    <mergeCell ref="CG8:CG9"/>
+    <mergeCell ref="CH8:CH9"/>
+    <mergeCell ref="AW8:AW9"/>
+    <mergeCell ref="AX8:AX9"/>
+    <mergeCell ref="AY8:AY9"/>
+    <mergeCell ref="AZ8:AZ9"/>
+    <mergeCell ref="BA8:BA9"/>
+    <mergeCell ref="BB8:BB9"/>
+    <mergeCell ref="CB8:CB9"/>
+    <mergeCell ref="CC8:CC9"/>
+    <mergeCell ref="CD8:CD9"/>
+    <mergeCell ref="CE8:CE9"/>
+    <mergeCell ref="CF8:CF9"/>
+    <mergeCell ref="CV8:CV9"/>
+    <mergeCell ref="BQ2:BQ7"/>
+    <mergeCell ref="BR2:BR7"/>
+    <mergeCell ref="BS2:BS7"/>
+    <mergeCell ref="BT2:BT7"/>
+    <mergeCell ref="BU2:BU7"/>
+    <mergeCell ref="BV2:BV7"/>
+    <mergeCell ref="CO8:CO9"/>
+    <mergeCell ref="CP8:CP9"/>
+    <mergeCell ref="CH2:CH7"/>
+    <mergeCell ref="CT8:CT9"/>
+    <mergeCell ref="CU8:CU9"/>
+    <mergeCell ref="CB2:CB7"/>
+    <mergeCell ref="CC2:CC7"/>
+    <mergeCell ref="CD2:CD7"/>
+    <mergeCell ref="CE2:CE7"/>
+    <mergeCell ref="CF2:CF7"/>
+    <mergeCell ref="CG2:CG7"/>
+    <mergeCell ref="CJ8:CJ9"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="BO8:BO9"/>
+    <mergeCell ref="BP8:BP9"/>
+    <mergeCell ref="BQ8:BQ9"/>
+    <mergeCell ref="BR8:BR9"/>
+    <mergeCell ref="BS8:BS9"/>
+    <mergeCell ref="BT8:BT9"/>
+    <mergeCell ref="BZ8:BZ9"/>
+    <mergeCell ref="CA8:CA9"/>
+    <mergeCell ref="BH8:BH9"/>
+    <mergeCell ref="BI8:BI9"/>
+    <mergeCell ref="BJ8:BJ9"/>
+    <mergeCell ref="BK8:BK9"/>
+    <mergeCell ref="BL8:BL9"/>
+    <mergeCell ref="BM8:BM9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="N1:Q1"/>
     <mergeCell ref="BC8:BC9"/>
@@ -5111,247 +5363,6 @@
     <mergeCell ref="AL8:AL9"/>
     <mergeCell ref="AM8:AM9"/>
     <mergeCell ref="V8:V9"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="BO8:BO9"/>
-    <mergeCell ref="BP8:BP9"/>
-    <mergeCell ref="BQ8:BQ9"/>
-    <mergeCell ref="BR8:BR9"/>
-    <mergeCell ref="BS8:BS9"/>
-    <mergeCell ref="BT8:BT9"/>
-    <mergeCell ref="BZ8:BZ9"/>
-    <mergeCell ref="CA8:CA9"/>
-    <mergeCell ref="BH8:BH9"/>
-    <mergeCell ref="BI8:BI9"/>
-    <mergeCell ref="BJ8:BJ9"/>
-    <mergeCell ref="BK8:BK9"/>
-    <mergeCell ref="BL8:BL9"/>
-    <mergeCell ref="BM8:BM9"/>
-    <mergeCell ref="CB8:CB9"/>
-    <mergeCell ref="CC8:CC9"/>
-    <mergeCell ref="CD8:CD9"/>
-    <mergeCell ref="CE8:CE9"/>
-    <mergeCell ref="CF8:CF9"/>
-    <mergeCell ref="CV8:CV9"/>
-    <mergeCell ref="BQ2:BQ7"/>
-    <mergeCell ref="BR2:BR7"/>
-    <mergeCell ref="BS2:BS7"/>
-    <mergeCell ref="BT2:BT7"/>
-    <mergeCell ref="BU2:BU7"/>
-    <mergeCell ref="BV2:BV7"/>
-    <mergeCell ref="CO8:CO9"/>
-    <mergeCell ref="CP8:CP9"/>
-    <mergeCell ref="CH2:CH7"/>
-    <mergeCell ref="CT8:CT9"/>
-    <mergeCell ref="CU8:CU9"/>
-    <mergeCell ref="CB2:CB7"/>
-    <mergeCell ref="CC2:CC7"/>
-    <mergeCell ref="CD2:CD7"/>
-    <mergeCell ref="CE2:CE7"/>
-    <mergeCell ref="CF2:CF7"/>
-    <mergeCell ref="CG2:CG7"/>
-    <mergeCell ref="CJ8:CJ9"/>
-    <mergeCell ref="E26:DT26"/>
-    <mergeCell ref="DF8:DF9"/>
-    <mergeCell ref="DQ8:DQ9"/>
-    <mergeCell ref="DR8:DR9"/>
-    <mergeCell ref="DS8:DS9"/>
-    <mergeCell ref="DT8:DT9"/>
-    <mergeCell ref="CY8:CY9"/>
-    <mergeCell ref="CZ8:CZ9"/>
-    <mergeCell ref="CM8:CM9"/>
-    <mergeCell ref="CW8:CW9"/>
-    <mergeCell ref="CX8:CX9"/>
-    <mergeCell ref="BU8:BU9"/>
-    <mergeCell ref="BV8:BV9"/>
-    <mergeCell ref="BW8:BW9"/>
-    <mergeCell ref="BF8:BF9"/>
-    <mergeCell ref="BG8:BG9"/>
-    <mergeCell ref="CG8:CG9"/>
-    <mergeCell ref="CH8:CH9"/>
-    <mergeCell ref="AW8:AW9"/>
-    <mergeCell ref="AX8:AX9"/>
-    <mergeCell ref="AY8:AY9"/>
-    <mergeCell ref="AZ8:AZ9"/>
-    <mergeCell ref="BA8:BA9"/>
-    <mergeCell ref="BB8:BB9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="F2:F7"/>
-    <mergeCell ref="G2:G7"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="I2:I7"/>
-    <mergeCell ref="J2:J7"/>
-    <mergeCell ref="K2:K7"/>
-    <mergeCell ref="L2:L7"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="M2:M7"/>
-    <mergeCell ref="N2:N7"/>
-    <mergeCell ref="O2:O7"/>
-    <mergeCell ref="P2:P7"/>
-    <mergeCell ref="Q2:Q7"/>
-    <mergeCell ref="R2:R7"/>
-    <mergeCell ref="S2:S7"/>
-    <mergeCell ref="T2:T7"/>
-    <mergeCell ref="CN8:CN9"/>
-    <mergeCell ref="Y2:Y7"/>
-    <mergeCell ref="Z2:Z7"/>
-    <mergeCell ref="AA2:AA7"/>
-    <mergeCell ref="AB2:AB7"/>
-    <mergeCell ref="AC2:AC7"/>
-    <mergeCell ref="AD2:AD7"/>
-    <mergeCell ref="AE2:AE7"/>
-    <mergeCell ref="AH2:AH7"/>
-    <mergeCell ref="AI2:AI7"/>
-    <mergeCell ref="AJ2:AJ7"/>
-    <mergeCell ref="AK2:AK7"/>
-    <mergeCell ref="AL2:AL7"/>
-    <mergeCell ref="AM2:AM7"/>
-    <mergeCell ref="AN2:AN7"/>
-    <mergeCell ref="AO2:AO7"/>
-    <mergeCell ref="AG2:AG7"/>
-    <mergeCell ref="CW2:CW7"/>
-    <mergeCell ref="CU2:CU7"/>
-    <mergeCell ref="CV2:CV7"/>
-    <mergeCell ref="CQ2:CQ7"/>
-    <mergeCell ref="CR2:CR7"/>
-    <mergeCell ref="CS2:CS7"/>
-    <mergeCell ref="CT2:CT7"/>
-    <mergeCell ref="CI2:CI7"/>
-    <mergeCell ref="CJ2:CJ7"/>
-    <mergeCell ref="CK2:CK7"/>
-    <mergeCell ref="CL2:CL7"/>
-    <mergeCell ref="CM2:CM7"/>
-    <mergeCell ref="CN2:CN7"/>
-    <mergeCell ref="CO2:CO7"/>
-    <mergeCell ref="CP2:CP7"/>
-    <mergeCell ref="BK2:BK7"/>
-    <mergeCell ref="X2:X7"/>
-    <mergeCell ref="AF2:AF7"/>
-    <mergeCell ref="AX2:AX7"/>
-    <mergeCell ref="AY2:AY7"/>
-    <mergeCell ref="AZ2:AZ7"/>
-    <mergeCell ref="BL2:BL7"/>
-    <mergeCell ref="BA2:BA7"/>
-    <mergeCell ref="BB2:BB7"/>
-    <mergeCell ref="BC2:BC7"/>
-    <mergeCell ref="AP2:AP7"/>
-    <mergeCell ref="AQ2:AQ7"/>
-    <mergeCell ref="AR2:AR7"/>
-    <mergeCell ref="AS2:AS7"/>
-    <mergeCell ref="AT2:AT7"/>
-    <mergeCell ref="AU2:AU7"/>
-    <mergeCell ref="AV2:AV7"/>
-    <mergeCell ref="AW2:AW7"/>
-    <mergeCell ref="CI8:CI9"/>
-    <mergeCell ref="CK8:CK9"/>
-    <mergeCell ref="CL8:CL9"/>
-    <mergeCell ref="BX8:BX9"/>
-    <mergeCell ref="BY8:BY9"/>
-    <mergeCell ref="DL2:DL7"/>
-    <mergeCell ref="DM2:DM7"/>
-    <mergeCell ref="DF2:DF7"/>
-    <mergeCell ref="BD2:BD7"/>
-    <mergeCell ref="BE2:BE7"/>
-    <mergeCell ref="BF2:BF7"/>
-    <mergeCell ref="BG2:BG7"/>
-    <mergeCell ref="BM2:BM7"/>
-    <mergeCell ref="BN2:BN7"/>
-    <mergeCell ref="BO2:BO7"/>
-    <mergeCell ref="BP2:BP7"/>
-    <mergeCell ref="CA2:CA7"/>
-    <mergeCell ref="BW2:BW7"/>
-    <mergeCell ref="BX2:BX7"/>
-    <mergeCell ref="BY2:BY7"/>
-    <mergeCell ref="BZ2:BZ7"/>
-    <mergeCell ref="BH2:BH7"/>
-    <mergeCell ref="BI2:BI7"/>
-    <mergeCell ref="BJ2:BJ7"/>
-    <mergeCell ref="W2:W7"/>
-    <mergeCell ref="F27:S27"/>
-    <mergeCell ref="T27:AW27"/>
-    <mergeCell ref="AX27:CD27"/>
-    <mergeCell ref="CE27:DT27"/>
-    <mergeCell ref="DG8:DG9"/>
-    <mergeCell ref="DH8:DH9"/>
-    <mergeCell ref="DI8:DI9"/>
-    <mergeCell ref="DJ8:DJ9"/>
-    <mergeCell ref="DK8:DK9"/>
-    <mergeCell ref="DL8:DL9"/>
-    <mergeCell ref="DM8:DM9"/>
-    <mergeCell ref="DN8:DN9"/>
-    <mergeCell ref="DO8:DO9"/>
-    <mergeCell ref="DP8:DP9"/>
-    <mergeCell ref="DA8:DA9"/>
-    <mergeCell ref="DB8:DB9"/>
-    <mergeCell ref="DC8:DC9"/>
-    <mergeCell ref="DD8:DD9"/>
-    <mergeCell ref="DE8:DE9"/>
-    <mergeCell ref="CQ8:CQ9"/>
-    <mergeCell ref="CR8:CR9"/>
-    <mergeCell ref="CS8:CS9"/>
-    <mergeCell ref="BN8:BN9"/>
-    <mergeCell ref="V1:Y1"/>
-    <mergeCell ref="R1:U1"/>
-    <mergeCell ref="DQ2:DQ7"/>
-    <mergeCell ref="DR2:DR7"/>
-    <mergeCell ref="DS2:DS7"/>
-    <mergeCell ref="DT2:DT7"/>
-    <mergeCell ref="CX2:CX7"/>
-    <mergeCell ref="CY2:CY7"/>
-    <mergeCell ref="DA2:DA7"/>
-    <mergeCell ref="DB2:DB7"/>
-    <mergeCell ref="DC2:DC7"/>
-    <mergeCell ref="DD2:DD7"/>
-    <mergeCell ref="DE2:DE7"/>
-    <mergeCell ref="CZ2:CZ7"/>
-    <mergeCell ref="DN2:DN7"/>
-    <mergeCell ref="DO2:DO7"/>
-    <mergeCell ref="DP2:DP7"/>
-    <mergeCell ref="DG2:DG7"/>
-    <mergeCell ref="DH2:DH7"/>
-    <mergeCell ref="DI2:DI7"/>
-    <mergeCell ref="DJ2:DJ7"/>
-    <mergeCell ref="DK2:DK7"/>
-    <mergeCell ref="U2:U7"/>
-    <mergeCell ref="V2:V7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -5373,49 +5384,49 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="59" t="s">
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="61" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="62"/>
-      <c r="D3" s="65" t="s">
+      <c r="C3" s="64"/>
+      <c r="D3" s="67" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="58" t="s">
+      <c r="E3" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="58" t="s">
+      <c r="F3" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="58" t="s">
+      <c r="G3" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="H3" s="59" t="s">
+      <c r="H3" s="61" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="46"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="59"/>
+      <c r="A4" s="36"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="61"/>
     </row>
     <row r="5" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9">

--- a/Journals/Angular ჟურნალი.xlsx
+++ b/Journals/Angular ჟურნალი.xlsx
@@ -557,38 +557,38 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="2" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="16" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="16" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -618,7 +618,16 @@
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -632,26 +641,17 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="16" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="16" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1064,1334 +1064,1334 @@
       <c r="E2" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="30">
+      <c r="F2" s="28">
         <v>46276</v>
       </c>
-      <c r="G2" s="30">
+      <c r="G2" s="28">
         <v>46276</v>
       </c>
-      <c r="H2" s="30">
+      <c r="H2" s="28">
         <v>46276</v>
       </c>
-      <c r="I2" s="30">
+      <c r="I2" s="28">
         <v>46276</v>
       </c>
-      <c r="J2" s="30">
+      <c r="J2" s="28">
         <v>46283</v>
       </c>
-      <c r="K2" s="30">
+      <c r="K2" s="28">
         <v>46283</v>
       </c>
-      <c r="L2" s="30">
+      <c r="L2" s="28">
         <v>46283</v>
       </c>
-      <c r="M2" s="30">
+      <c r="M2" s="28">
         <v>46283</v>
       </c>
-      <c r="N2" s="30">
+      <c r="N2" s="28">
         <v>46290</v>
       </c>
-      <c r="O2" s="30">
+      <c r="O2" s="28">
         <v>46290</v>
       </c>
-      <c r="P2" s="30">
+      <c r="P2" s="28">
         <v>46290</v>
       </c>
-      <c r="Q2" s="30">
+      <c r="Q2" s="28">
         <v>46290</v>
       </c>
-      <c r="R2" s="30">
+      <c r="R2" s="28">
         <v>46297</v>
       </c>
-      <c r="S2" s="30">
+      <c r="S2" s="28">
         <v>46297</v>
       </c>
-      <c r="T2" s="30">
+      <c r="T2" s="28">
         <v>46297</v>
       </c>
-      <c r="U2" s="30">
+      <c r="U2" s="28">
         <v>46297</v>
       </c>
-      <c r="V2" s="55">
+      <c r="V2" s="30">
         <v>46304</v>
       </c>
-      <c r="W2" s="55">
+      <c r="W2" s="30">
         <v>46304</v>
       </c>
-      <c r="X2" s="30">
+      <c r="X2" s="28">
         <v>46304</v>
       </c>
-      <c r="Y2" s="30">
+      <c r="Y2" s="28">
         <v>46304</v>
       </c>
-      <c r="Z2" s="53">
+      <c r="Z2" s="37">
         <v>46311</v>
       </c>
-      <c r="AA2" s="53">
+      <c r="AA2" s="37">
         <v>46311</v>
       </c>
-      <c r="AB2" s="53">
+      <c r="AB2" s="37">
         <v>46311</v>
       </c>
-      <c r="AC2" s="53">
+      <c r="AC2" s="37">
         <v>46311</v>
       </c>
-      <c r="AD2" s="30">
+      <c r="AD2" s="28">
         <v>46318</v>
       </c>
-      <c r="AE2" s="30">
+      <c r="AE2" s="28">
         <v>46318</v>
       </c>
-      <c r="AF2" s="30">
+      <c r="AF2" s="28">
         <v>46318</v>
       </c>
-      <c r="AG2" s="30">
+      <c r="AG2" s="28">
         <v>46318</v>
       </c>
-      <c r="AH2" s="30"/>
-      <c r="AI2" s="30"/>
-      <c r="AJ2" s="30"/>
-      <c r="AK2" s="30"/>
-      <c r="AL2" s="30"/>
-      <c r="AM2" s="30"/>
-      <c r="AN2" s="30"/>
-      <c r="AO2" s="30"/>
-      <c r="AP2" s="30"/>
-      <c r="AQ2" s="30"/>
-      <c r="AR2" s="30"/>
-      <c r="AS2" s="30"/>
-      <c r="AT2" s="30"/>
-      <c r="AU2" s="30"/>
-      <c r="AV2" s="30"/>
-      <c r="AW2" s="30"/>
-      <c r="AX2" s="30"/>
-      <c r="AY2" s="30"/>
-      <c r="AZ2" s="30"/>
-      <c r="BA2" s="30"/>
-      <c r="BB2" s="30"/>
-      <c r="BC2" s="30"/>
-      <c r="BD2" s="30"/>
-      <c r="BE2" s="30"/>
-      <c r="BF2" s="30"/>
-      <c r="BG2" s="30"/>
-      <c r="BH2" s="30"/>
-      <c r="BI2" s="30"/>
-      <c r="BJ2" s="30"/>
-      <c r="BK2" s="30"/>
-      <c r="BL2" s="30"/>
-      <c r="BM2" s="30"/>
-      <c r="BN2" s="30"/>
-      <c r="BO2" s="30"/>
-      <c r="BP2" s="30"/>
-      <c r="BQ2" s="30"/>
-      <c r="BR2" s="30"/>
-      <c r="BS2" s="30"/>
-      <c r="BT2" s="30"/>
-      <c r="BU2" s="30"/>
-      <c r="BV2" s="30"/>
-      <c r="BW2" s="30"/>
-      <c r="BX2" s="30"/>
-      <c r="BY2" s="30"/>
-      <c r="BZ2" s="30"/>
-      <c r="CA2" s="30"/>
-      <c r="CB2" s="30"/>
-      <c r="CC2" s="30"/>
-      <c r="CD2" s="30"/>
-      <c r="CE2" s="30"/>
-      <c r="CF2" s="30"/>
-      <c r="CG2" s="30"/>
-      <c r="CH2" s="30"/>
-      <c r="CI2" s="30"/>
-      <c r="CJ2" s="30"/>
-      <c r="CK2" s="30"/>
-      <c r="CL2" s="30"/>
-      <c r="CM2" s="30"/>
-      <c r="CN2" s="30"/>
-      <c r="CO2" s="30"/>
-      <c r="CP2" s="30"/>
-      <c r="CQ2" s="30"/>
-      <c r="CR2" s="30"/>
-      <c r="CS2" s="30"/>
-      <c r="CT2" s="30"/>
-      <c r="CU2" s="30"/>
-      <c r="CV2" s="30"/>
-      <c r="CW2" s="30"/>
-      <c r="CX2" s="30"/>
-      <c r="CY2" s="30"/>
-      <c r="CZ2" s="30"/>
-      <c r="DA2" s="30"/>
-      <c r="DB2" s="30"/>
-      <c r="DC2" s="30"/>
-      <c r="DD2" s="30"/>
-      <c r="DE2" s="30"/>
-      <c r="DF2" s="30"/>
-      <c r="DG2" s="30"/>
-      <c r="DH2" s="30"/>
-      <c r="DI2" s="30"/>
-      <c r="DJ2" s="30"/>
-      <c r="DK2" s="30"/>
-      <c r="DL2" s="30"/>
-      <c r="DM2" s="30"/>
-      <c r="DN2" s="30"/>
-      <c r="DO2" s="30"/>
-      <c r="DP2" s="30"/>
-      <c r="DQ2" s="30"/>
-      <c r="DR2" s="30"/>
-      <c r="DS2" s="30"/>
-      <c r="DT2" s="30"/>
+      <c r="AH2" s="28"/>
+      <c r="AI2" s="28"/>
+      <c r="AJ2" s="28"/>
+      <c r="AK2" s="28"/>
+      <c r="AL2" s="28"/>
+      <c r="AM2" s="28"/>
+      <c r="AN2" s="28"/>
+      <c r="AO2" s="28"/>
+      <c r="AP2" s="28"/>
+      <c r="AQ2" s="28"/>
+      <c r="AR2" s="28"/>
+      <c r="AS2" s="28"/>
+      <c r="AT2" s="28"/>
+      <c r="AU2" s="28"/>
+      <c r="AV2" s="28"/>
+      <c r="AW2" s="28"/>
+      <c r="AX2" s="28"/>
+      <c r="AY2" s="28"/>
+      <c r="AZ2" s="28"/>
+      <c r="BA2" s="28"/>
+      <c r="BB2" s="28"/>
+      <c r="BC2" s="28"/>
+      <c r="BD2" s="28"/>
+      <c r="BE2" s="28"/>
+      <c r="BF2" s="28"/>
+      <c r="BG2" s="28"/>
+      <c r="BH2" s="28"/>
+      <c r="BI2" s="28"/>
+      <c r="BJ2" s="28"/>
+      <c r="BK2" s="28"/>
+      <c r="BL2" s="28"/>
+      <c r="BM2" s="28"/>
+      <c r="BN2" s="28"/>
+      <c r="BO2" s="28"/>
+      <c r="BP2" s="28"/>
+      <c r="BQ2" s="28"/>
+      <c r="BR2" s="28"/>
+      <c r="BS2" s="28"/>
+      <c r="BT2" s="28"/>
+      <c r="BU2" s="28"/>
+      <c r="BV2" s="28"/>
+      <c r="BW2" s="28"/>
+      <c r="BX2" s="28"/>
+      <c r="BY2" s="28"/>
+      <c r="BZ2" s="28"/>
+      <c r="CA2" s="28"/>
+      <c r="CB2" s="28"/>
+      <c r="CC2" s="28"/>
+      <c r="CD2" s="28"/>
+      <c r="CE2" s="28"/>
+      <c r="CF2" s="28"/>
+      <c r="CG2" s="28"/>
+      <c r="CH2" s="28"/>
+      <c r="CI2" s="28"/>
+      <c r="CJ2" s="28"/>
+      <c r="CK2" s="28"/>
+      <c r="CL2" s="28"/>
+      <c r="CM2" s="28"/>
+      <c r="CN2" s="28"/>
+      <c r="CO2" s="28"/>
+      <c r="CP2" s="28"/>
+      <c r="CQ2" s="28"/>
+      <c r="CR2" s="28"/>
+      <c r="CS2" s="28"/>
+      <c r="CT2" s="28"/>
+      <c r="CU2" s="28"/>
+      <c r="CV2" s="28"/>
+      <c r="CW2" s="28"/>
+      <c r="CX2" s="28"/>
+      <c r="CY2" s="28"/>
+      <c r="CZ2" s="28"/>
+      <c r="DA2" s="28"/>
+      <c r="DB2" s="28"/>
+      <c r="DC2" s="28"/>
+      <c r="DD2" s="28"/>
+      <c r="DE2" s="28"/>
+      <c r="DF2" s="28"/>
+      <c r="DG2" s="28"/>
+      <c r="DH2" s="28"/>
+      <c r="DI2" s="28"/>
+      <c r="DJ2" s="28"/>
+      <c r="DK2" s="28"/>
+      <c r="DL2" s="28"/>
+      <c r="DM2" s="28"/>
+      <c r="DN2" s="28"/>
+      <c r="DO2" s="28"/>
+      <c r="DP2" s="28"/>
+      <c r="DQ2" s="28"/>
+      <c r="DR2" s="28"/>
+      <c r="DS2" s="28"/>
+      <c r="DT2" s="28"/>
     </row>
     <row r="3" spans="1:125" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
       <c r="E3" s="46"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30"/>
-      <c r="N3" s="30"/>
-      <c r="O3" s="30"/>
-      <c r="P3" s="30"/>
-      <c r="Q3" s="30"/>
-      <c r="R3" s="30"/>
-      <c r="S3" s="30"/>
-      <c r="T3" s="30"/>
-      <c r="U3" s="30"/>
-      <c r="V3" s="55"/>
-      <c r="W3" s="55"/>
-      <c r="X3" s="30"/>
-      <c r="Y3" s="30"/>
-      <c r="Z3" s="53"/>
-      <c r="AA3" s="53"/>
-      <c r="AB3" s="53"/>
-      <c r="AC3" s="53"/>
-      <c r="AD3" s="30"/>
-      <c r="AE3" s="30"/>
-      <c r="AF3" s="30"/>
-      <c r="AG3" s="30"/>
-      <c r="AH3" s="30"/>
-      <c r="AI3" s="30"/>
-      <c r="AJ3" s="30"/>
-      <c r="AK3" s="30"/>
-      <c r="AL3" s="30"/>
-      <c r="AM3" s="30"/>
-      <c r="AN3" s="30"/>
-      <c r="AO3" s="30"/>
-      <c r="AP3" s="30"/>
-      <c r="AQ3" s="30"/>
-      <c r="AR3" s="30"/>
-      <c r="AS3" s="30"/>
-      <c r="AT3" s="30"/>
-      <c r="AU3" s="30"/>
-      <c r="AV3" s="30"/>
-      <c r="AW3" s="30"/>
-      <c r="AX3" s="30"/>
-      <c r="AY3" s="30"/>
-      <c r="AZ3" s="30"/>
-      <c r="BA3" s="30"/>
-      <c r="BB3" s="30"/>
-      <c r="BC3" s="30"/>
-      <c r="BD3" s="30"/>
-      <c r="BE3" s="30"/>
-      <c r="BF3" s="30"/>
-      <c r="BG3" s="30"/>
-      <c r="BH3" s="30"/>
-      <c r="BI3" s="30"/>
-      <c r="BJ3" s="30"/>
-      <c r="BK3" s="30"/>
-      <c r="BL3" s="30"/>
-      <c r="BM3" s="30"/>
-      <c r="BN3" s="30"/>
-      <c r="BO3" s="30"/>
-      <c r="BP3" s="30"/>
-      <c r="BQ3" s="30"/>
-      <c r="BR3" s="30"/>
-      <c r="BS3" s="30"/>
-      <c r="BT3" s="30"/>
-      <c r="BU3" s="30"/>
-      <c r="BV3" s="30"/>
-      <c r="BW3" s="30"/>
-      <c r="BX3" s="30"/>
-      <c r="BY3" s="30"/>
-      <c r="BZ3" s="30"/>
-      <c r="CA3" s="30"/>
-      <c r="CB3" s="30"/>
-      <c r="CC3" s="30"/>
-      <c r="CD3" s="30"/>
-      <c r="CE3" s="30"/>
-      <c r="CF3" s="30"/>
-      <c r="CG3" s="30"/>
-      <c r="CH3" s="30"/>
-      <c r="CI3" s="30"/>
-      <c r="CJ3" s="30"/>
-      <c r="CK3" s="30"/>
-      <c r="CL3" s="30"/>
-      <c r="CM3" s="30"/>
-      <c r="CN3" s="30"/>
-      <c r="CO3" s="30"/>
-      <c r="CP3" s="30"/>
-      <c r="CQ3" s="30"/>
-      <c r="CR3" s="30"/>
-      <c r="CS3" s="30"/>
-      <c r="CT3" s="30"/>
-      <c r="CU3" s="30"/>
-      <c r="CV3" s="30"/>
-      <c r="CW3" s="30"/>
-      <c r="CX3" s="30"/>
-      <c r="CY3" s="30"/>
-      <c r="CZ3" s="30"/>
-      <c r="DA3" s="30"/>
-      <c r="DB3" s="30"/>
-      <c r="DC3" s="30"/>
-      <c r="DD3" s="30"/>
-      <c r="DE3" s="30"/>
-      <c r="DF3" s="30"/>
-      <c r="DG3" s="30"/>
-      <c r="DH3" s="30"/>
-      <c r="DI3" s="30"/>
-      <c r="DJ3" s="30"/>
-      <c r="DK3" s="30"/>
-      <c r="DL3" s="30"/>
-      <c r="DM3" s="30"/>
-      <c r="DN3" s="30"/>
-      <c r="DO3" s="30"/>
-      <c r="DP3" s="30"/>
-      <c r="DQ3" s="30"/>
-      <c r="DR3" s="30"/>
-      <c r="DS3" s="30"/>
-      <c r="DT3" s="30"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="28"/>
+      <c r="O3" s="28"/>
+      <c r="P3" s="28"/>
+      <c r="Q3" s="28"/>
+      <c r="R3" s="28"/>
+      <c r="S3" s="28"/>
+      <c r="T3" s="28"/>
+      <c r="U3" s="28"/>
+      <c r="V3" s="30"/>
+      <c r="W3" s="30"/>
+      <c r="X3" s="28"/>
+      <c r="Y3" s="28"/>
+      <c r="Z3" s="37"/>
+      <c r="AA3" s="37"/>
+      <c r="AB3" s="37"/>
+      <c r="AC3" s="37"/>
+      <c r="AD3" s="28"/>
+      <c r="AE3" s="28"/>
+      <c r="AF3" s="28"/>
+      <c r="AG3" s="28"/>
+      <c r="AH3" s="28"/>
+      <c r="AI3" s="28"/>
+      <c r="AJ3" s="28"/>
+      <c r="AK3" s="28"/>
+      <c r="AL3" s="28"/>
+      <c r="AM3" s="28"/>
+      <c r="AN3" s="28"/>
+      <c r="AO3" s="28"/>
+      <c r="AP3" s="28"/>
+      <c r="AQ3" s="28"/>
+      <c r="AR3" s="28"/>
+      <c r="AS3" s="28"/>
+      <c r="AT3" s="28"/>
+      <c r="AU3" s="28"/>
+      <c r="AV3" s="28"/>
+      <c r="AW3" s="28"/>
+      <c r="AX3" s="28"/>
+      <c r="AY3" s="28"/>
+      <c r="AZ3" s="28"/>
+      <c r="BA3" s="28"/>
+      <c r="BB3" s="28"/>
+      <c r="BC3" s="28"/>
+      <c r="BD3" s="28"/>
+      <c r="BE3" s="28"/>
+      <c r="BF3" s="28"/>
+      <c r="BG3" s="28"/>
+      <c r="BH3" s="28"/>
+      <c r="BI3" s="28"/>
+      <c r="BJ3" s="28"/>
+      <c r="BK3" s="28"/>
+      <c r="BL3" s="28"/>
+      <c r="BM3" s="28"/>
+      <c r="BN3" s="28"/>
+      <c r="BO3" s="28"/>
+      <c r="BP3" s="28"/>
+      <c r="BQ3" s="28"/>
+      <c r="BR3" s="28"/>
+      <c r="BS3" s="28"/>
+      <c r="BT3" s="28"/>
+      <c r="BU3" s="28"/>
+      <c r="BV3" s="28"/>
+      <c r="BW3" s="28"/>
+      <c r="BX3" s="28"/>
+      <c r="BY3" s="28"/>
+      <c r="BZ3" s="28"/>
+      <c r="CA3" s="28"/>
+      <c r="CB3" s="28"/>
+      <c r="CC3" s="28"/>
+      <c r="CD3" s="28"/>
+      <c r="CE3" s="28"/>
+      <c r="CF3" s="28"/>
+      <c r="CG3" s="28"/>
+      <c r="CH3" s="28"/>
+      <c r="CI3" s="28"/>
+      <c r="CJ3" s="28"/>
+      <c r="CK3" s="28"/>
+      <c r="CL3" s="28"/>
+      <c r="CM3" s="28"/>
+      <c r="CN3" s="28"/>
+      <c r="CO3" s="28"/>
+      <c r="CP3" s="28"/>
+      <c r="CQ3" s="28"/>
+      <c r="CR3" s="28"/>
+      <c r="CS3" s="28"/>
+      <c r="CT3" s="28"/>
+      <c r="CU3" s="28"/>
+      <c r="CV3" s="28"/>
+      <c r="CW3" s="28"/>
+      <c r="CX3" s="28"/>
+      <c r="CY3" s="28"/>
+      <c r="CZ3" s="28"/>
+      <c r="DA3" s="28"/>
+      <c r="DB3" s="28"/>
+      <c r="DC3" s="28"/>
+      <c r="DD3" s="28"/>
+      <c r="DE3" s="28"/>
+      <c r="DF3" s="28"/>
+      <c r="DG3" s="28"/>
+      <c r="DH3" s="28"/>
+      <c r="DI3" s="28"/>
+      <c r="DJ3" s="28"/>
+      <c r="DK3" s="28"/>
+      <c r="DL3" s="28"/>
+      <c r="DM3" s="28"/>
+      <c r="DN3" s="28"/>
+      <c r="DO3" s="28"/>
+      <c r="DP3" s="28"/>
+      <c r="DQ3" s="28"/>
+      <c r="DR3" s="28"/>
+      <c r="DS3" s="28"/>
+      <c r="DT3" s="28"/>
     </row>
     <row r="4" spans="1:125" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="48"/>
-      <c r="C4" s="33" t="s">
+      <c r="A4" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="49"/>
+      <c r="C4" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="35"/>
+      <c r="D4" s="51"/>
       <c r="E4" s="46"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="30"/>
-      <c r="O4" s="30"/>
-      <c r="P4" s="30"/>
-      <c r="Q4" s="30"/>
-      <c r="R4" s="30"/>
-      <c r="S4" s="30"/>
-      <c r="T4" s="30"/>
-      <c r="U4" s="30"/>
-      <c r="V4" s="55"/>
-      <c r="W4" s="55"/>
-      <c r="X4" s="30"/>
-      <c r="Y4" s="30"/>
-      <c r="Z4" s="53"/>
-      <c r="AA4" s="53"/>
-      <c r="AB4" s="53"/>
-      <c r="AC4" s="53"/>
-      <c r="AD4" s="30"/>
-      <c r="AE4" s="30"/>
-      <c r="AF4" s="30"/>
-      <c r="AG4" s="30"/>
-      <c r="AH4" s="30"/>
-      <c r="AI4" s="30"/>
-      <c r="AJ4" s="30"/>
-      <c r="AK4" s="30"/>
-      <c r="AL4" s="30"/>
-      <c r="AM4" s="30"/>
-      <c r="AN4" s="30"/>
-      <c r="AO4" s="30"/>
-      <c r="AP4" s="30"/>
-      <c r="AQ4" s="30"/>
-      <c r="AR4" s="30"/>
-      <c r="AS4" s="30"/>
-      <c r="AT4" s="30"/>
-      <c r="AU4" s="30"/>
-      <c r="AV4" s="30"/>
-      <c r="AW4" s="30"/>
-      <c r="AX4" s="30"/>
-      <c r="AY4" s="30"/>
-      <c r="AZ4" s="30"/>
-      <c r="BA4" s="30"/>
-      <c r="BB4" s="30"/>
-      <c r="BC4" s="30"/>
-      <c r="BD4" s="30"/>
-      <c r="BE4" s="30"/>
-      <c r="BF4" s="30"/>
-      <c r="BG4" s="30"/>
-      <c r="BH4" s="30"/>
-      <c r="BI4" s="30"/>
-      <c r="BJ4" s="30"/>
-      <c r="BK4" s="30"/>
-      <c r="BL4" s="30"/>
-      <c r="BM4" s="30"/>
-      <c r="BN4" s="30"/>
-      <c r="BO4" s="30"/>
-      <c r="BP4" s="30"/>
-      <c r="BQ4" s="30"/>
-      <c r="BR4" s="30"/>
-      <c r="BS4" s="30"/>
-      <c r="BT4" s="30"/>
-      <c r="BU4" s="30"/>
-      <c r="BV4" s="30"/>
-      <c r="BW4" s="30"/>
-      <c r="BX4" s="30"/>
-      <c r="BY4" s="30"/>
-      <c r="BZ4" s="30"/>
-      <c r="CA4" s="30"/>
-      <c r="CB4" s="30"/>
-      <c r="CC4" s="30"/>
-      <c r="CD4" s="30"/>
-      <c r="CE4" s="30"/>
-      <c r="CF4" s="30"/>
-      <c r="CG4" s="30"/>
-      <c r="CH4" s="30"/>
-      <c r="CI4" s="30"/>
-      <c r="CJ4" s="30"/>
-      <c r="CK4" s="30"/>
-      <c r="CL4" s="30"/>
-      <c r="CM4" s="30"/>
-      <c r="CN4" s="30"/>
-      <c r="CO4" s="30"/>
-      <c r="CP4" s="30"/>
-      <c r="CQ4" s="30"/>
-      <c r="CR4" s="30"/>
-      <c r="CS4" s="30"/>
-      <c r="CT4" s="30"/>
-      <c r="CU4" s="30"/>
-      <c r="CV4" s="30"/>
-      <c r="CW4" s="30"/>
-      <c r="CX4" s="30"/>
-      <c r="CY4" s="30"/>
-      <c r="CZ4" s="30"/>
-      <c r="DA4" s="30"/>
-      <c r="DB4" s="30"/>
-      <c r="DC4" s="30"/>
-      <c r="DD4" s="30"/>
-      <c r="DE4" s="30"/>
-      <c r="DF4" s="30"/>
-      <c r="DG4" s="30"/>
-      <c r="DH4" s="30"/>
-      <c r="DI4" s="30"/>
-      <c r="DJ4" s="30"/>
-      <c r="DK4" s="30"/>
-      <c r="DL4" s="30"/>
-      <c r="DM4" s="30"/>
-      <c r="DN4" s="30"/>
-      <c r="DO4" s="30"/>
-      <c r="DP4" s="30"/>
-      <c r="DQ4" s="30"/>
-      <c r="DR4" s="30"/>
-      <c r="DS4" s="30"/>
-      <c r="DT4" s="30"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="28"/>
+      <c r="Q4" s="28"/>
+      <c r="R4" s="28"/>
+      <c r="S4" s="28"/>
+      <c r="T4" s="28"/>
+      <c r="U4" s="28"/>
+      <c r="V4" s="30"/>
+      <c r="W4" s="30"/>
+      <c r="X4" s="28"/>
+      <c r="Y4" s="28"/>
+      <c r="Z4" s="37"/>
+      <c r="AA4" s="37"/>
+      <c r="AB4" s="37"/>
+      <c r="AC4" s="37"/>
+      <c r="AD4" s="28"/>
+      <c r="AE4" s="28"/>
+      <c r="AF4" s="28"/>
+      <c r="AG4" s="28"/>
+      <c r="AH4" s="28"/>
+      <c r="AI4" s="28"/>
+      <c r="AJ4" s="28"/>
+      <c r="AK4" s="28"/>
+      <c r="AL4" s="28"/>
+      <c r="AM4" s="28"/>
+      <c r="AN4" s="28"/>
+      <c r="AO4" s="28"/>
+      <c r="AP4" s="28"/>
+      <c r="AQ4" s="28"/>
+      <c r="AR4" s="28"/>
+      <c r="AS4" s="28"/>
+      <c r="AT4" s="28"/>
+      <c r="AU4" s="28"/>
+      <c r="AV4" s="28"/>
+      <c r="AW4" s="28"/>
+      <c r="AX4" s="28"/>
+      <c r="AY4" s="28"/>
+      <c r="AZ4" s="28"/>
+      <c r="BA4" s="28"/>
+      <c r="BB4" s="28"/>
+      <c r="BC4" s="28"/>
+      <c r="BD4" s="28"/>
+      <c r="BE4" s="28"/>
+      <c r="BF4" s="28"/>
+      <c r="BG4" s="28"/>
+      <c r="BH4" s="28"/>
+      <c r="BI4" s="28"/>
+      <c r="BJ4" s="28"/>
+      <c r="BK4" s="28"/>
+      <c r="BL4" s="28"/>
+      <c r="BM4" s="28"/>
+      <c r="BN4" s="28"/>
+      <c r="BO4" s="28"/>
+      <c r="BP4" s="28"/>
+      <c r="BQ4" s="28"/>
+      <c r="BR4" s="28"/>
+      <c r="BS4" s="28"/>
+      <c r="BT4" s="28"/>
+      <c r="BU4" s="28"/>
+      <c r="BV4" s="28"/>
+      <c r="BW4" s="28"/>
+      <c r="BX4" s="28"/>
+      <c r="BY4" s="28"/>
+      <c r="BZ4" s="28"/>
+      <c r="CA4" s="28"/>
+      <c r="CB4" s="28"/>
+      <c r="CC4" s="28"/>
+      <c r="CD4" s="28"/>
+      <c r="CE4" s="28"/>
+      <c r="CF4" s="28"/>
+      <c r="CG4" s="28"/>
+      <c r="CH4" s="28"/>
+      <c r="CI4" s="28"/>
+      <c r="CJ4" s="28"/>
+      <c r="CK4" s="28"/>
+      <c r="CL4" s="28"/>
+      <c r="CM4" s="28"/>
+      <c r="CN4" s="28"/>
+      <c r="CO4" s="28"/>
+      <c r="CP4" s="28"/>
+      <c r="CQ4" s="28"/>
+      <c r="CR4" s="28"/>
+      <c r="CS4" s="28"/>
+      <c r="CT4" s="28"/>
+      <c r="CU4" s="28"/>
+      <c r="CV4" s="28"/>
+      <c r="CW4" s="28"/>
+      <c r="CX4" s="28"/>
+      <c r="CY4" s="28"/>
+      <c r="CZ4" s="28"/>
+      <c r="DA4" s="28"/>
+      <c r="DB4" s="28"/>
+      <c r="DC4" s="28"/>
+      <c r="DD4" s="28"/>
+      <c r="DE4" s="28"/>
+      <c r="DF4" s="28"/>
+      <c r="DG4" s="28"/>
+      <c r="DH4" s="28"/>
+      <c r="DI4" s="28"/>
+      <c r="DJ4" s="28"/>
+      <c r="DK4" s="28"/>
+      <c r="DL4" s="28"/>
+      <c r="DM4" s="28"/>
+      <c r="DN4" s="28"/>
+      <c r="DO4" s="28"/>
+      <c r="DP4" s="28"/>
+      <c r="DQ4" s="28"/>
+      <c r="DR4" s="28"/>
+      <c r="DS4" s="28"/>
+      <c r="DT4" s="28"/>
     </row>
     <row r="5" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="49"/>
-      <c r="C5" s="50">
+      <c r="B5" s="52"/>
+      <c r="C5" s="53">
         <v>60</v>
       </c>
-      <c r="D5" s="51"/>
+      <c r="D5" s="54"/>
       <c r="E5" s="46"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="30"/>
-      <c r="K5" s="30"/>
-      <c r="L5" s="30"/>
-      <c r="M5" s="30"/>
-      <c r="N5" s="30"/>
-      <c r="O5" s="30"/>
-      <c r="P5" s="30"/>
-      <c r="Q5" s="30"/>
-      <c r="R5" s="30"/>
-      <c r="S5" s="30"/>
-      <c r="T5" s="30"/>
-      <c r="U5" s="30"/>
-      <c r="V5" s="55"/>
-      <c r="W5" s="55"/>
-      <c r="X5" s="30"/>
-      <c r="Y5" s="30"/>
-      <c r="Z5" s="53"/>
-      <c r="AA5" s="53"/>
-      <c r="AB5" s="53"/>
-      <c r="AC5" s="53"/>
-      <c r="AD5" s="30"/>
-      <c r="AE5" s="30"/>
-      <c r="AF5" s="30"/>
-      <c r="AG5" s="30"/>
-      <c r="AH5" s="30"/>
-      <c r="AI5" s="30"/>
-      <c r="AJ5" s="30"/>
-      <c r="AK5" s="30"/>
-      <c r="AL5" s="30"/>
-      <c r="AM5" s="30"/>
-      <c r="AN5" s="30"/>
-      <c r="AO5" s="30"/>
-      <c r="AP5" s="30"/>
-      <c r="AQ5" s="30"/>
-      <c r="AR5" s="30"/>
-      <c r="AS5" s="30"/>
-      <c r="AT5" s="30"/>
-      <c r="AU5" s="30"/>
-      <c r="AV5" s="30"/>
-      <c r="AW5" s="30"/>
-      <c r="AX5" s="30"/>
-      <c r="AY5" s="30"/>
-      <c r="AZ5" s="30"/>
-      <c r="BA5" s="30"/>
-      <c r="BB5" s="30"/>
-      <c r="BC5" s="30"/>
-      <c r="BD5" s="30"/>
-      <c r="BE5" s="30"/>
-      <c r="BF5" s="30"/>
-      <c r="BG5" s="30"/>
-      <c r="BH5" s="30"/>
-      <c r="BI5" s="30"/>
-      <c r="BJ5" s="30"/>
-      <c r="BK5" s="30"/>
-      <c r="BL5" s="30"/>
-      <c r="BM5" s="30"/>
-      <c r="BN5" s="30"/>
-      <c r="BO5" s="30"/>
-      <c r="BP5" s="30"/>
-      <c r="BQ5" s="30"/>
-      <c r="BR5" s="30"/>
-      <c r="BS5" s="30"/>
-      <c r="BT5" s="30"/>
-      <c r="BU5" s="30"/>
-      <c r="BV5" s="30"/>
-      <c r="BW5" s="30"/>
-      <c r="BX5" s="30"/>
-      <c r="BY5" s="30"/>
-      <c r="BZ5" s="30"/>
-      <c r="CA5" s="30"/>
-      <c r="CB5" s="30"/>
-      <c r="CC5" s="30"/>
-      <c r="CD5" s="30"/>
-      <c r="CE5" s="30"/>
-      <c r="CF5" s="30"/>
-      <c r="CG5" s="30"/>
-      <c r="CH5" s="30"/>
-      <c r="CI5" s="30"/>
-      <c r="CJ5" s="30"/>
-      <c r="CK5" s="30"/>
-      <c r="CL5" s="30"/>
-      <c r="CM5" s="30"/>
-      <c r="CN5" s="30"/>
-      <c r="CO5" s="30"/>
-      <c r="CP5" s="30"/>
-      <c r="CQ5" s="30"/>
-      <c r="CR5" s="30"/>
-      <c r="CS5" s="30"/>
-      <c r="CT5" s="30"/>
-      <c r="CU5" s="30"/>
-      <c r="CV5" s="30"/>
-      <c r="CW5" s="30"/>
-      <c r="CX5" s="30"/>
-      <c r="CY5" s="30"/>
-      <c r="CZ5" s="30"/>
-      <c r="DA5" s="30"/>
-      <c r="DB5" s="30"/>
-      <c r="DC5" s="30"/>
-      <c r="DD5" s="30"/>
-      <c r="DE5" s="30"/>
-      <c r="DF5" s="30"/>
-      <c r="DG5" s="30"/>
-      <c r="DH5" s="30"/>
-      <c r="DI5" s="30"/>
-      <c r="DJ5" s="30"/>
-      <c r="DK5" s="30"/>
-      <c r="DL5" s="30"/>
-      <c r="DM5" s="30"/>
-      <c r="DN5" s="30"/>
-      <c r="DO5" s="30"/>
-      <c r="DP5" s="30"/>
-      <c r="DQ5" s="30"/>
-      <c r="DR5" s="30"/>
-      <c r="DS5" s="30"/>
-      <c r="DT5" s="30"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
+      <c r="Q5" s="28"/>
+      <c r="R5" s="28"/>
+      <c r="S5" s="28"/>
+      <c r="T5" s="28"/>
+      <c r="U5" s="28"/>
+      <c r="V5" s="30"/>
+      <c r="W5" s="30"/>
+      <c r="X5" s="28"/>
+      <c r="Y5" s="28"/>
+      <c r="Z5" s="37"/>
+      <c r="AA5" s="37"/>
+      <c r="AB5" s="37"/>
+      <c r="AC5" s="37"/>
+      <c r="AD5" s="28"/>
+      <c r="AE5" s="28"/>
+      <c r="AF5" s="28"/>
+      <c r="AG5" s="28"/>
+      <c r="AH5" s="28"/>
+      <c r="AI5" s="28"/>
+      <c r="AJ5" s="28"/>
+      <c r="AK5" s="28"/>
+      <c r="AL5" s="28"/>
+      <c r="AM5" s="28"/>
+      <c r="AN5" s="28"/>
+      <c r="AO5" s="28"/>
+      <c r="AP5" s="28"/>
+      <c r="AQ5" s="28"/>
+      <c r="AR5" s="28"/>
+      <c r="AS5" s="28"/>
+      <c r="AT5" s="28"/>
+      <c r="AU5" s="28"/>
+      <c r="AV5" s="28"/>
+      <c r="AW5" s="28"/>
+      <c r="AX5" s="28"/>
+      <c r="AY5" s="28"/>
+      <c r="AZ5" s="28"/>
+      <c r="BA5" s="28"/>
+      <c r="BB5" s="28"/>
+      <c r="BC5" s="28"/>
+      <c r="BD5" s="28"/>
+      <c r="BE5" s="28"/>
+      <c r="BF5" s="28"/>
+      <c r="BG5" s="28"/>
+      <c r="BH5" s="28"/>
+      <c r="BI5" s="28"/>
+      <c r="BJ5" s="28"/>
+      <c r="BK5" s="28"/>
+      <c r="BL5" s="28"/>
+      <c r="BM5" s="28"/>
+      <c r="BN5" s="28"/>
+      <c r="BO5" s="28"/>
+      <c r="BP5" s="28"/>
+      <c r="BQ5" s="28"/>
+      <c r="BR5" s="28"/>
+      <c r="BS5" s="28"/>
+      <c r="BT5" s="28"/>
+      <c r="BU5" s="28"/>
+      <c r="BV5" s="28"/>
+      <c r="BW5" s="28"/>
+      <c r="BX5" s="28"/>
+      <c r="BY5" s="28"/>
+      <c r="BZ5" s="28"/>
+      <c r="CA5" s="28"/>
+      <c r="CB5" s="28"/>
+      <c r="CC5" s="28"/>
+      <c r="CD5" s="28"/>
+      <c r="CE5" s="28"/>
+      <c r="CF5" s="28"/>
+      <c r="CG5" s="28"/>
+      <c r="CH5" s="28"/>
+      <c r="CI5" s="28"/>
+      <c r="CJ5" s="28"/>
+      <c r="CK5" s="28"/>
+      <c r="CL5" s="28"/>
+      <c r="CM5" s="28"/>
+      <c r="CN5" s="28"/>
+      <c r="CO5" s="28"/>
+      <c r="CP5" s="28"/>
+      <c r="CQ5" s="28"/>
+      <c r="CR5" s="28"/>
+      <c r="CS5" s="28"/>
+      <c r="CT5" s="28"/>
+      <c r="CU5" s="28"/>
+      <c r="CV5" s="28"/>
+      <c r="CW5" s="28"/>
+      <c r="CX5" s="28"/>
+      <c r="CY5" s="28"/>
+      <c r="CZ5" s="28"/>
+      <c r="DA5" s="28"/>
+      <c r="DB5" s="28"/>
+      <c r="DC5" s="28"/>
+      <c r="DD5" s="28"/>
+      <c r="DE5" s="28"/>
+      <c r="DF5" s="28"/>
+      <c r="DG5" s="28"/>
+      <c r="DH5" s="28"/>
+      <c r="DI5" s="28"/>
+      <c r="DJ5" s="28"/>
+      <c r="DK5" s="28"/>
+      <c r="DL5" s="28"/>
+      <c r="DM5" s="28"/>
+      <c r="DN5" s="28"/>
+      <c r="DO5" s="28"/>
+      <c r="DP5" s="28"/>
+      <c r="DQ5" s="28"/>
+      <c r="DR5" s="28"/>
+      <c r="DS5" s="28"/>
+      <c r="DT5" s="28"/>
     </row>
     <row r="6" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="50">
+      <c r="B6" s="52"/>
+      <c r="C6" s="53">
         <v>4</v>
       </c>
-      <c r="D6" s="51"/>
+      <c r="D6" s="54"/>
       <c r="E6" s="46"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="30"/>
-      <c r="J6" s="30"/>
-      <c r="K6" s="30"/>
-      <c r="L6" s="30"/>
-      <c r="M6" s="30"/>
-      <c r="N6" s="30"/>
-      <c r="O6" s="30"/>
-      <c r="P6" s="30"/>
-      <c r="Q6" s="30"/>
-      <c r="R6" s="30"/>
-      <c r="S6" s="30"/>
-      <c r="T6" s="30"/>
-      <c r="U6" s="30"/>
-      <c r="V6" s="55"/>
-      <c r="W6" s="55"/>
-      <c r="X6" s="30"/>
-      <c r="Y6" s="30"/>
-      <c r="Z6" s="53"/>
-      <c r="AA6" s="53"/>
-      <c r="AB6" s="53"/>
-      <c r="AC6" s="53"/>
-      <c r="AD6" s="30"/>
-      <c r="AE6" s="30"/>
-      <c r="AF6" s="30"/>
-      <c r="AG6" s="30"/>
-      <c r="AH6" s="30"/>
-      <c r="AI6" s="30"/>
-      <c r="AJ6" s="30"/>
-      <c r="AK6" s="30"/>
-      <c r="AL6" s="30"/>
-      <c r="AM6" s="30"/>
-      <c r="AN6" s="30"/>
-      <c r="AO6" s="30"/>
-      <c r="AP6" s="30"/>
-      <c r="AQ6" s="30"/>
-      <c r="AR6" s="30"/>
-      <c r="AS6" s="30"/>
-      <c r="AT6" s="30"/>
-      <c r="AU6" s="30"/>
-      <c r="AV6" s="30"/>
-      <c r="AW6" s="30"/>
-      <c r="AX6" s="30"/>
-      <c r="AY6" s="30"/>
-      <c r="AZ6" s="30"/>
-      <c r="BA6" s="30"/>
-      <c r="BB6" s="30"/>
-      <c r="BC6" s="30"/>
-      <c r="BD6" s="30"/>
-      <c r="BE6" s="30"/>
-      <c r="BF6" s="30"/>
-      <c r="BG6" s="30"/>
-      <c r="BH6" s="30"/>
-      <c r="BI6" s="30"/>
-      <c r="BJ6" s="30"/>
-      <c r="BK6" s="30"/>
-      <c r="BL6" s="30"/>
-      <c r="BM6" s="30"/>
-      <c r="BN6" s="30"/>
-      <c r="BO6" s="30"/>
-      <c r="BP6" s="30"/>
-      <c r="BQ6" s="30"/>
-      <c r="BR6" s="30"/>
-      <c r="BS6" s="30"/>
-      <c r="BT6" s="30"/>
-      <c r="BU6" s="30"/>
-      <c r="BV6" s="30"/>
-      <c r="BW6" s="30"/>
-      <c r="BX6" s="30"/>
-      <c r="BY6" s="30"/>
-      <c r="BZ6" s="30"/>
-      <c r="CA6" s="30"/>
-      <c r="CB6" s="30"/>
-      <c r="CC6" s="30"/>
-      <c r="CD6" s="30"/>
-      <c r="CE6" s="30"/>
-      <c r="CF6" s="30"/>
-      <c r="CG6" s="30"/>
-      <c r="CH6" s="30"/>
-      <c r="CI6" s="30"/>
-      <c r="CJ6" s="30"/>
-      <c r="CK6" s="30"/>
-      <c r="CL6" s="30"/>
-      <c r="CM6" s="30"/>
-      <c r="CN6" s="30"/>
-      <c r="CO6" s="30"/>
-      <c r="CP6" s="30"/>
-      <c r="CQ6" s="30"/>
-      <c r="CR6" s="30"/>
-      <c r="CS6" s="30"/>
-      <c r="CT6" s="30"/>
-      <c r="CU6" s="30"/>
-      <c r="CV6" s="30"/>
-      <c r="CW6" s="30"/>
-      <c r="CX6" s="30"/>
-      <c r="CY6" s="30"/>
-      <c r="CZ6" s="30"/>
-      <c r="DA6" s="30"/>
-      <c r="DB6" s="30"/>
-      <c r="DC6" s="30"/>
-      <c r="DD6" s="30"/>
-      <c r="DE6" s="30"/>
-      <c r="DF6" s="30"/>
-      <c r="DG6" s="30"/>
-      <c r="DH6" s="30"/>
-      <c r="DI6" s="30"/>
-      <c r="DJ6" s="30"/>
-      <c r="DK6" s="30"/>
-      <c r="DL6" s="30"/>
-      <c r="DM6" s="30"/>
-      <c r="DN6" s="30"/>
-      <c r="DO6" s="30"/>
-      <c r="DP6" s="30"/>
-      <c r="DQ6" s="30"/>
-      <c r="DR6" s="30"/>
-      <c r="DS6" s="30"/>
-      <c r="DT6" s="30"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="28"/>
+      <c r="M6" s="28"/>
+      <c r="N6" s="28"/>
+      <c r="O6" s="28"/>
+      <c r="P6" s="28"/>
+      <c r="Q6" s="28"/>
+      <c r="R6" s="28"/>
+      <c r="S6" s="28"/>
+      <c r="T6" s="28"/>
+      <c r="U6" s="28"/>
+      <c r="V6" s="30"/>
+      <c r="W6" s="30"/>
+      <c r="X6" s="28"/>
+      <c r="Y6" s="28"/>
+      <c r="Z6" s="37"/>
+      <c r="AA6" s="37"/>
+      <c r="AB6" s="37"/>
+      <c r="AC6" s="37"/>
+      <c r="AD6" s="28"/>
+      <c r="AE6" s="28"/>
+      <c r="AF6" s="28"/>
+      <c r="AG6" s="28"/>
+      <c r="AH6" s="28"/>
+      <c r="AI6" s="28"/>
+      <c r="AJ6" s="28"/>
+      <c r="AK6" s="28"/>
+      <c r="AL6" s="28"/>
+      <c r="AM6" s="28"/>
+      <c r="AN6" s="28"/>
+      <c r="AO6" s="28"/>
+      <c r="AP6" s="28"/>
+      <c r="AQ6" s="28"/>
+      <c r="AR6" s="28"/>
+      <c r="AS6" s="28"/>
+      <c r="AT6" s="28"/>
+      <c r="AU6" s="28"/>
+      <c r="AV6" s="28"/>
+      <c r="AW6" s="28"/>
+      <c r="AX6" s="28"/>
+      <c r="AY6" s="28"/>
+      <c r="AZ6" s="28"/>
+      <c r="BA6" s="28"/>
+      <c r="BB6" s="28"/>
+      <c r="BC6" s="28"/>
+      <c r="BD6" s="28"/>
+      <c r="BE6" s="28"/>
+      <c r="BF6" s="28"/>
+      <c r="BG6" s="28"/>
+      <c r="BH6" s="28"/>
+      <c r="BI6" s="28"/>
+      <c r="BJ6" s="28"/>
+      <c r="BK6" s="28"/>
+      <c r="BL6" s="28"/>
+      <c r="BM6" s="28"/>
+      <c r="BN6" s="28"/>
+      <c r="BO6" s="28"/>
+      <c r="BP6" s="28"/>
+      <c r="BQ6" s="28"/>
+      <c r="BR6" s="28"/>
+      <c r="BS6" s="28"/>
+      <c r="BT6" s="28"/>
+      <c r="BU6" s="28"/>
+      <c r="BV6" s="28"/>
+      <c r="BW6" s="28"/>
+      <c r="BX6" s="28"/>
+      <c r="BY6" s="28"/>
+      <c r="BZ6" s="28"/>
+      <c r="CA6" s="28"/>
+      <c r="CB6" s="28"/>
+      <c r="CC6" s="28"/>
+      <c r="CD6" s="28"/>
+      <c r="CE6" s="28"/>
+      <c r="CF6" s="28"/>
+      <c r="CG6" s="28"/>
+      <c r="CH6" s="28"/>
+      <c r="CI6" s="28"/>
+      <c r="CJ6" s="28"/>
+      <c r="CK6" s="28"/>
+      <c r="CL6" s="28"/>
+      <c r="CM6" s="28"/>
+      <c r="CN6" s="28"/>
+      <c r="CO6" s="28"/>
+      <c r="CP6" s="28"/>
+      <c r="CQ6" s="28"/>
+      <c r="CR6" s="28"/>
+      <c r="CS6" s="28"/>
+      <c r="CT6" s="28"/>
+      <c r="CU6" s="28"/>
+      <c r="CV6" s="28"/>
+      <c r="CW6" s="28"/>
+      <c r="CX6" s="28"/>
+      <c r="CY6" s="28"/>
+      <c r="CZ6" s="28"/>
+      <c r="DA6" s="28"/>
+      <c r="DB6" s="28"/>
+      <c r="DC6" s="28"/>
+      <c r="DD6" s="28"/>
+      <c r="DE6" s="28"/>
+      <c r="DF6" s="28"/>
+      <c r="DG6" s="28"/>
+      <c r="DH6" s="28"/>
+      <c r="DI6" s="28"/>
+      <c r="DJ6" s="28"/>
+      <c r="DK6" s="28"/>
+      <c r="DL6" s="28"/>
+      <c r="DM6" s="28"/>
+      <c r="DN6" s="28"/>
+      <c r="DO6" s="28"/>
+      <c r="DP6" s="28"/>
+      <c r="DQ6" s="28"/>
+      <c r="DR6" s="28"/>
+      <c r="DS6" s="28"/>
+      <c r="DT6" s="28"/>
     </row>
     <row r="7" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="52"/>
-      <c r="C7" s="50">
+      <c r="B7" s="55"/>
+      <c r="C7" s="53">
         <v>11</v>
       </c>
-      <c r="D7" s="51"/>
+      <c r="D7" s="54"/>
       <c r="E7" s="47"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="31"/>
-      <c r="M7" s="31"/>
-      <c r="N7" s="31"/>
-      <c r="O7" s="31"/>
-      <c r="P7" s="31"/>
-      <c r="Q7" s="31"/>
-      <c r="R7" s="31"/>
-      <c r="S7" s="31"/>
-      <c r="T7" s="31"/>
-      <c r="U7" s="31"/>
-      <c r="V7" s="56"/>
-      <c r="W7" s="56"/>
-      <c r="X7" s="31"/>
-      <c r="Y7" s="31"/>
-      <c r="Z7" s="54"/>
-      <c r="AA7" s="54"/>
-      <c r="AB7" s="54"/>
-      <c r="AC7" s="54"/>
-      <c r="AD7" s="31"/>
-      <c r="AE7" s="31"/>
-      <c r="AF7" s="31"/>
-      <c r="AG7" s="31"/>
-      <c r="AH7" s="31"/>
-      <c r="AI7" s="31"/>
-      <c r="AJ7" s="31"/>
-      <c r="AK7" s="31"/>
-      <c r="AL7" s="31"/>
-      <c r="AM7" s="31"/>
-      <c r="AN7" s="31"/>
-      <c r="AO7" s="31"/>
-      <c r="AP7" s="31"/>
-      <c r="AQ7" s="31"/>
-      <c r="AR7" s="31"/>
-      <c r="AS7" s="31"/>
-      <c r="AT7" s="31"/>
-      <c r="AU7" s="31"/>
-      <c r="AV7" s="31"/>
-      <c r="AW7" s="31"/>
-      <c r="AX7" s="31"/>
-      <c r="AY7" s="31"/>
-      <c r="AZ7" s="31"/>
-      <c r="BA7" s="31"/>
-      <c r="BB7" s="31"/>
-      <c r="BC7" s="31"/>
-      <c r="BD7" s="31"/>
-      <c r="BE7" s="31"/>
-      <c r="BF7" s="31"/>
-      <c r="BG7" s="31"/>
-      <c r="BH7" s="31"/>
-      <c r="BI7" s="31"/>
-      <c r="BJ7" s="31"/>
-      <c r="BK7" s="31"/>
-      <c r="BL7" s="31"/>
-      <c r="BM7" s="31"/>
-      <c r="BN7" s="31"/>
-      <c r="BO7" s="31"/>
-      <c r="BP7" s="31"/>
-      <c r="BQ7" s="31"/>
-      <c r="BR7" s="31"/>
-      <c r="BS7" s="31"/>
-      <c r="BT7" s="31"/>
-      <c r="BU7" s="31"/>
-      <c r="BV7" s="31"/>
-      <c r="BW7" s="31"/>
-      <c r="BX7" s="31"/>
-      <c r="BY7" s="31"/>
-      <c r="BZ7" s="31"/>
-      <c r="CA7" s="31"/>
-      <c r="CB7" s="31"/>
-      <c r="CC7" s="31"/>
-      <c r="CD7" s="31"/>
-      <c r="CE7" s="31"/>
-      <c r="CF7" s="31"/>
-      <c r="CG7" s="31"/>
-      <c r="CH7" s="31"/>
-      <c r="CI7" s="31"/>
-      <c r="CJ7" s="31"/>
-      <c r="CK7" s="31"/>
-      <c r="CL7" s="31"/>
-      <c r="CM7" s="31"/>
-      <c r="CN7" s="31"/>
-      <c r="CO7" s="31"/>
-      <c r="CP7" s="31"/>
-      <c r="CQ7" s="31"/>
-      <c r="CR7" s="31"/>
-      <c r="CS7" s="31"/>
-      <c r="CT7" s="31"/>
-      <c r="CU7" s="31"/>
-      <c r="CV7" s="31"/>
-      <c r="CW7" s="31"/>
-      <c r="CX7" s="31"/>
-      <c r="CY7" s="31"/>
-      <c r="CZ7" s="31"/>
-      <c r="DA7" s="31"/>
-      <c r="DB7" s="31"/>
-      <c r="DC7" s="31"/>
-      <c r="DD7" s="31"/>
-      <c r="DE7" s="31"/>
-      <c r="DF7" s="31"/>
-      <c r="DG7" s="31"/>
-      <c r="DH7" s="31"/>
-      <c r="DI7" s="31"/>
-      <c r="DJ7" s="31"/>
-      <c r="DK7" s="31"/>
-      <c r="DL7" s="31"/>
-      <c r="DM7" s="31"/>
-      <c r="DN7" s="31"/>
-      <c r="DO7" s="31"/>
-      <c r="DP7" s="31"/>
-      <c r="DQ7" s="31"/>
-      <c r="DR7" s="31"/>
-      <c r="DS7" s="31"/>
-      <c r="DT7" s="31"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="29"/>
+      <c r="N7" s="29"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="29"/>
+      <c r="Q7" s="29"/>
+      <c r="R7" s="29"/>
+      <c r="S7" s="29"/>
+      <c r="T7" s="29"/>
+      <c r="U7" s="29"/>
+      <c r="V7" s="31"/>
+      <c r="W7" s="31"/>
+      <c r="X7" s="29"/>
+      <c r="Y7" s="29"/>
+      <c r="Z7" s="38"/>
+      <c r="AA7" s="38"/>
+      <c r="AB7" s="38"/>
+      <c r="AC7" s="38"/>
+      <c r="AD7" s="29"/>
+      <c r="AE7" s="29"/>
+      <c r="AF7" s="29"/>
+      <c r="AG7" s="29"/>
+      <c r="AH7" s="29"/>
+      <c r="AI7" s="29"/>
+      <c r="AJ7" s="29"/>
+      <c r="AK7" s="29"/>
+      <c r="AL7" s="29"/>
+      <c r="AM7" s="29"/>
+      <c r="AN7" s="29"/>
+      <c r="AO7" s="29"/>
+      <c r="AP7" s="29"/>
+      <c r="AQ7" s="29"/>
+      <c r="AR7" s="29"/>
+      <c r="AS7" s="29"/>
+      <c r="AT7" s="29"/>
+      <c r="AU7" s="29"/>
+      <c r="AV7" s="29"/>
+      <c r="AW7" s="29"/>
+      <c r="AX7" s="29"/>
+      <c r="AY7" s="29"/>
+      <c r="AZ7" s="29"/>
+      <c r="BA7" s="29"/>
+      <c r="BB7" s="29"/>
+      <c r="BC7" s="29"/>
+      <c r="BD7" s="29"/>
+      <c r="BE7" s="29"/>
+      <c r="BF7" s="29"/>
+      <c r="BG7" s="29"/>
+      <c r="BH7" s="29"/>
+      <c r="BI7" s="29"/>
+      <c r="BJ7" s="29"/>
+      <c r="BK7" s="29"/>
+      <c r="BL7" s="29"/>
+      <c r="BM7" s="29"/>
+      <c r="BN7" s="29"/>
+      <c r="BO7" s="29"/>
+      <c r="BP7" s="29"/>
+      <c r="BQ7" s="29"/>
+      <c r="BR7" s="29"/>
+      <c r="BS7" s="29"/>
+      <c r="BT7" s="29"/>
+      <c r="BU7" s="29"/>
+      <c r="BV7" s="29"/>
+      <c r="BW7" s="29"/>
+      <c r="BX7" s="29"/>
+      <c r="BY7" s="29"/>
+      <c r="BZ7" s="29"/>
+      <c r="CA7" s="29"/>
+      <c r="CB7" s="29"/>
+      <c r="CC7" s="29"/>
+      <c r="CD7" s="29"/>
+      <c r="CE7" s="29"/>
+      <c r="CF7" s="29"/>
+      <c r="CG7" s="29"/>
+      <c r="CH7" s="29"/>
+      <c r="CI7" s="29"/>
+      <c r="CJ7" s="29"/>
+      <c r="CK7" s="29"/>
+      <c r="CL7" s="29"/>
+      <c r="CM7" s="29"/>
+      <c r="CN7" s="29"/>
+      <c r="CO7" s="29"/>
+      <c r="CP7" s="29"/>
+      <c r="CQ7" s="29"/>
+      <c r="CR7" s="29"/>
+      <c r="CS7" s="29"/>
+      <c r="CT7" s="29"/>
+      <c r="CU7" s="29"/>
+      <c r="CV7" s="29"/>
+      <c r="CW7" s="29"/>
+      <c r="CX7" s="29"/>
+      <c r="CY7" s="29"/>
+      <c r="CZ7" s="29"/>
+      <c r="DA7" s="29"/>
+      <c r="DB7" s="29"/>
+      <c r="DC7" s="29"/>
+      <c r="DD7" s="29"/>
+      <c r="DE7" s="29"/>
+      <c r="DF7" s="29"/>
+      <c r="DG7" s="29"/>
+      <c r="DH7" s="29"/>
+      <c r="DI7" s="29"/>
+      <c r="DJ7" s="29"/>
+      <c r="DK7" s="29"/>
+      <c r="DL7" s="29"/>
+      <c r="DM7" s="29"/>
+      <c r="DN7" s="29"/>
+      <c r="DO7" s="29"/>
+      <c r="DP7" s="29"/>
+      <c r="DQ7" s="29"/>
+      <c r="DR7" s="29"/>
+      <c r="DS7" s="29"/>
+      <c r="DT7" s="29"/>
     </row>
     <row r="8" spans="1:125" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="32">
+      <c r="B8" s="56"/>
+      <c r="C8" s="57">
         <f>SUM(C5:D7)</f>
         <v>75</v>
       </c>
-      <c r="D8" s="35"/>
+      <c r="D8" s="51"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="28">
-        <v>1</v>
-      </c>
-      <c r="G8" s="28">
+      <c r="F8" s="35">
+        <v>1</v>
+      </c>
+      <c r="G8" s="35">
         <v>2</v>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="35">
         <v>3</v>
       </c>
-      <c r="I8" s="28">
+      <c r="I8" s="35">
         <v>4</v>
       </c>
-      <c r="J8" s="28">
+      <c r="J8" s="35">
         <v>5</v>
       </c>
-      <c r="K8" s="28">
+      <c r="K8" s="35">
         <v>6</v>
       </c>
-      <c r="L8" s="28">
+      <c r="L8" s="35">
         <v>7</v>
       </c>
-      <c r="M8" s="28">
+      <c r="M8" s="35">
         <v>8</v>
       </c>
-      <c r="N8" s="28">
+      <c r="N8" s="35">
         <v>9</v>
       </c>
-      <c r="O8" s="28">
+      <c r="O8" s="35">
         <v>10</v>
       </c>
-      <c r="P8" s="28">
+      <c r="P8" s="35">
         <v>11</v>
       </c>
-      <c r="Q8" s="28">
+      <c r="Q8" s="35">
         <v>12</v>
       </c>
-      <c r="R8" s="28">
+      <c r="R8" s="35">
         <v>13</v>
       </c>
-      <c r="S8" s="28">
+      <c r="S8" s="35">
         <v>14</v>
       </c>
-      <c r="T8" s="28">
+      <c r="T8" s="35">
         <v>15</v>
       </c>
-      <c r="U8" s="28">
+      <c r="U8" s="35">
         <v>16</v>
       </c>
-      <c r="V8" s="28">
+      <c r="V8" s="35">
         <v>17</v>
       </c>
-      <c r="W8" s="28">
+      <c r="W8" s="35">
         <v>18</v>
       </c>
-      <c r="X8" s="28">
+      <c r="X8" s="35">
         <v>19</v>
       </c>
-      <c r="Y8" s="28">
+      <c r="Y8" s="35">
         <v>20</v>
       </c>
-      <c r="Z8" s="28">
+      <c r="Z8" s="35">
         <v>21</v>
       </c>
-      <c r="AA8" s="28">
+      <c r="AA8" s="35">
         <v>22</v>
       </c>
-      <c r="AB8" s="28">
+      <c r="AB8" s="35">
         <v>23</v>
       </c>
-      <c r="AC8" s="28">
+      <c r="AC8" s="35">
         <v>24</v>
       </c>
-      <c r="AD8" s="28">
+      <c r="AD8" s="35">
         <v>25</v>
       </c>
-      <c r="AE8" s="28">
+      <c r="AE8" s="35">
         <v>26</v>
       </c>
-      <c r="AF8" s="28">
+      <c r="AF8" s="35">
         <v>27</v>
       </c>
-      <c r="AG8" s="28">
+      <c r="AG8" s="35">
         <v>28</v>
       </c>
-      <c r="AH8" s="28">
+      <c r="AH8" s="35">
         <v>29</v>
       </c>
-      <c r="AI8" s="28">
+      <c r="AI8" s="35">
         <v>30</v>
       </c>
-      <c r="AJ8" s="28">
+      <c r="AJ8" s="35">
         <v>31</v>
       </c>
-      <c r="AK8" s="28">
+      <c r="AK8" s="35">
         <v>32</v>
       </c>
-      <c r="AL8" s="28">
+      <c r="AL8" s="35">
         <v>33</v>
       </c>
-      <c r="AM8" s="28">
+      <c r="AM8" s="35">
         <v>34</v>
       </c>
-      <c r="AN8" s="28">
+      <c r="AN8" s="35">
         <v>35</v>
       </c>
-      <c r="AO8" s="28">
+      <c r="AO8" s="35">
         <v>36</v>
       </c>
-      <c r="AP8" s="28">
+      <c r="AP8" s="35">
         <v>37</v>
       </c>
-      <c r="AQ8" s="28">
+      <c r="AQ8" s="35">
         <v>38</v>
       </c>
-      <c r="AR8" s="28">
+      <c r="AR8" s="35">
         <v>39</v>
       </c>
-      <c r="AS8" s="28">
+      <c r="AS8" s="35">
         <v>40</v>
       </c>
-      <c r="AT8" s="28">
+      <c r="AT8" s="35">
         <v>41</v>
       </c>
-      <c r="AU8" s="28">
+      <c r="AU8" s="35">
         <v>42</v>
       </c>
-      <c r="AV8" s="28">
+      <c r="AV8" s="35">
         <v>43</v>
       </c>
-      <c r="AW8" s="28">
+      <c r="AW8" s="35">
         <v>44</v>
       </c>
-      <c r="AX8" s="28">
+      <c r="AX8" s="35">
         <v>45</v>
       </c>
-      <c r="AY8" s="28">
+      <c r="AY8" s="35">
         <v>46</v>
       </c>
-      <c r="AZ8" s="28">
+      <c r="AZ8" s="35">
         <v>47</v>
       </c>
-      <c r="BA8" s="28">
+      <c r="BA8" s="35">
         <v>48</v>
       </c>
-      <c r="BB8" s="28">
+      <c r="BB8" s="35">
         <v>49</v>
       </c>
-      <c r="BC8" s="28">
+      <c r="BC8" s="35">
         <v>50</v>
       </c>
-      <c r="BD8" s="28">
+      <c r="BD8" s="35">
         <v>51</v>
       </c>
-      <c r="BE8" s="28">
+      <c r="BE8" s="35">
         <v>52</v>
       </c>
-      <c r="BF8" s="28">
+      <c r="BF8" s="35">
         <v>53</v>
       </c>
-      <c r="BG8" s="28">
+      <c r="BG8" s="35">
         <v>54</v>
       </c>
-      <c r="BH8" s="28">
+      <c r="BH8" s="35">
         <v>55</v>
       </c>
-      <c r="BI8" s="28">
+      <c r="BI8" s="35">
         <v>56</v>
       </c>
-      <c r="BJ8" s="28">
+      <c r="BJ8" s="35">
         <v>57</v>
       </c>
-      <c r="BK8" s="28">
+      <c r="BK8" s="35">
         <v>58</v>
       </c>
-      <c r="BL8" s="28">
+      <c r="BL8" s="35">
         <v>59</v>
       </c>
-      <c r="BM8" s="28">
+      <c r="BM8" s="35">
         <v>60</v>
       </c>
-      <c r="BN8" s="28">
+      <c r="BN8" s="35">
         <v>61</v>
       </c>
-      <c r="BO8" s="28">
+      <c r="BO8" s="35">
         <v>62</v>
       </c>
-      <c r="BP8" s="28">
+      <c r="BP8" s="35">
         <v>63</v>
       </c>
-      <c r="BQ8" s="28">
+      <c r="BQ8" s="35">
         <v>64</v>
       </c>
-      <c r="BR8" s="28">
+      <c r="BR8" s="35">
         <v>65</v>
       </c>
-      <c r="BS8" s="28">
+      <c r="BS8" s="35">
         <v>66</v>
       </c>
-      <c r="BT8" s="28">
+      <c r="BT8" s="35">
         <v>67</v>
       </c>
-      <c r="BU8" s="28">
+      <c r="BU8" s="35">
         <v>68</v>
       </c>
-      <c r="BV8" s="28">
+      <c r="BV8" s="35">
         <v>69</v>
       </c>
-      <c r="BW8" s="28">
+      <c r="BW8" s="35">
         <v>70</v>
       </c>
-      <c r="BX8" s="28">
+      <c r="BX8" s="35">
         <v>71</v>
       </c>
-      <c r="BY8" s="28">
+      <c r="BY8" s="35">
         <v>72</v>
       </c>
-      <c r="BZ8" s="28">
+      <c r="BZ8" s="35">
         <v>73</v>
       </c>
-      <c r="CA8" s="28">
+      <c r="CA8" s="35">
         <v>74</v>
       </c>
-      <c r="CB8" s="28">
+      <c r="CB8" s="35">
         <v>75</v>
       </c>
-      <c r="CC8" s="28">
+      <c r="CC8" s="35">
         <v>76</v>
       </c>
-      <c r="CD8" s="28">
+      <c r="CD8" s="35">
         <v>77</v>
       </c>
-      <c r="CE8" s="28">
+      <c r="CE8" s="35">
         <v>78</v>
       </c>
-      <c r="CF8" s="28">
+      <c r="CF8" s="35">
         <v>79</v>
       </c>
-      <c r="CG8" s="28">
+      <c r="CG8" s="35">
         <v>80</v>
       </c>
-      <c r="CH8" s="28">
+      <c r="CH8" s="35">
         <v>81</v>
       </c>
-      <c r="CI8" s="28">
+      <c r="CI8" s="35">
         <v>82</v>
       </c>
-      <c r="CJ8" s="28">
+      <c r="CJ8" s="35">
         <v>83</v>
       </c>
-      <c r="CK8" s="28">
+      <c r="CK8" s="35">
         <v>84</v>
       </c>
-      <c r="CL8" s="28">
+      <c r="CL8" s="35">
         <v>85</v>
       </c>
-      <c r="CM8" s="28">
+      <c r="CM8" s="35">
         <v>86</v>
       </c>
-      <c r="CN8" s="28">
+      <c r="CN8" s="35">
         <v>87</v>
       </c>
-      <c r="CO8" s="28">
+      <c r="CO8" s="35">
         <v>88</v>
       </c>
-      <c r="CP8" s="28">
+      <c r="CP8" s="35">
         <v>89</v>
       </c>
-      <c r="CQ8" s="28">
+      <c r="CQ8" s="35">
         <v>90</v>
       </c>
-      <c r="CR8" s="28">
+      <c r="CR8" s="35">
         <v>91</v>
       </c>
-      <c r="CS8" s="28">
+      <c r="CS8" s="35">
         <v>92</v>
       </c>
-      <c r="CT8" s="28">
+      <c r="CT8" s="35">
         <v>93</v>
       </c>
-      <c r="CU8" s="28">
+      <c r="CU8" s="35">
         <v>94</v>
       </c>
-      <c r="CV8" s="28">
+      <c r="CV8" s="35">
         <v>95</v>
       </c>
-      <c r="CW8" s="28">
+      <c r="CW8" s="35">
         <v>96</v>
       </c>
-      <c r="CX8" s="28">
+      <c r="CX8" s="35">
         <v>97</v>
       </c>
-      <c r="CY8" s="28">
+      <c r="CY8" s="35">
         <v>98</v>
       </c>
-      <c r="CZ8" s="28">
+      <c r="CZ8" s="35">
         <v>99</v>
       </c>
-      <c r="DA8" s="28">
+      <c r="DA8" s="35">
         <v>100</v>
       </c>
-      <c r="DB8" s="28">
+      <c r="DB8" s="35">
         <v>101</v>
       </c>
-      <c r="DC8" s="28">
+      <c r="DC8" s="35">
         <v>102</v>
       </c>
-      <c r="DD8" s="28">
+      <c r="DD8" s="35">
         <v>103</v>
       </c>
-      <c r="DE8" s="28">
+      <c r="DE8" s="35">
         <v>104</v>
       </c>
-      <c r="DF8" s="28">
+      <c r="DF8" s="35">
         <v>105</v>
       </c>
-      <c r="DG8" s="28">
+      <c r="DG8" s="35">
         <v>106</v>
       </c>
-      <c r="DH8" s="28">
+      <c r="DH8" s="35">
         <v>107</v>
       </c>
-      <c r="DI8" s="28">
+      <c r="DI8" s="35">
         <v>108</v>
       </c>
-      <c r="DJ8" s="28">
+      <c r="DJ8" s="35">
         <v>109</v>
       </c>
-      <c r="DK8" s="28">
+      <c r="DK8" s="35">
         <v>110</v>
       </c>
-      <c r="DL8" s="28">
+      <c r="DL8" s="35">
         <v>111</v>
       </c>
-      <c r="DM8" s="28">
+      <c r="DM8" s="35">
         <v>112</v>
       </c>
-      <c r="DN8" s="28">
+      <c r="DN8" s="35">
         <v>113</v>
       </c>
-      <c r="DO8" s="28">
+      <c r="DO8" s="35">
         <v>114</v>
       </c>
-      <c r="DP8" s="28">
+      <c r="DP8" s="35">
         <v>115</v>
       </c>
-      <c r="DQ8" s="28">
+      <c r="DQ8" s="35">
         <v>116</v>
       </c>
-      <c r="DR8" s="28">
+      <c r="DR8" s="35">
         <v>117</v>
       </c>
-      <c r="DS8" s="28">
+      <c r="DS8" s="35">
         <v>118</v>
       </c>
-      <c r="DT8" s="28">
+      <c r="DT8" s="35">
         <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="37" t="s">
+      <c r="B9" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="38" t="s">
+      <c r="C9" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="37"/>
+      <c r="D9" s="58"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="29"/>
-      <c r="P9" s="29"/>
-      <c r="Q9" s="29"/>
-      <c r="R9" s="29"/>
-      <c r="S9" s="29"/>
-      <c r="T9" s="29"/>
-      <c r="U9" s="29"/>
-      <c r="V9" s="29"/>
-      <c r="W9" s="29"/>
-      <c r="X9" s="29"/>
-      <c r="Y9" s="29"/>
-      <c r="Z9" s="29"/>
-      <c r="AA9" s="29"/>
-      <c r="AB9" s="29"/>
-      <c r="AC9" s="29"/>
-      <c r="AD9" s="29"/>
-      <c r="AE9" s="29"/>
-      <c r="AF9" s="29"/>
-      <c r="AG9" s="29"/>
-      <c r="AH9" s="29"/>
-      <c r="AI9" s="29"/>
-      <c r="AJ9" s="29"/>
-      <c r="AK9" s="29"/>
-      <c r="AL9" s="29"/>
-      <c r="AM9" s="29"/>
-      <c r="AN9" s="29"/>
-      <c r="AO9" s="29"/>
-      <c r="AP9" s="29"/>
-      <c r="AQ9" s="29"/>
-      <c r="AR9" s="29"/>
-      <c r="AS9" s="29"/>
-      <c r="AT9" s="29"/>
-      <c r="AU9" s="29"/>
-      <c r="AV9" s="29"/>
-      <c r="AW9" s="29"/>
-      <c r="AX9" s="29"/>
-      <c r="AY9" s="29"/>
-      <c r="AZ9" s="29"/>
-      <c r="BA9" s="29"/>
-      <c r="BB9" s="29"/>
-      <c r="BC9" s="29"/>
-      <c r="BD9" s="29"/>
-      <c r="BE9" s="29"/>
-      <c r="BF9" s="29"/>
-      <c r="BG9" s="29"/>
-      <c r="BH9" s="29"/>
-      <c r="BI9" s="29"/>
-      <c r="BJ9" s="29"/>
-      <c r="BK9" s="29"/>
-      <c r="BL9" s="29"/>
-      <c r="BM9" s="29"/>
-      <c r="BN9" s="29"/>
-      <c r="BO9" s="29"/>
-      <c r="BP9" s="29"/>
-      <c r="BQ9" s="29"/>
-      <c r="BR9" s="29"/>
-      <c r="BS9" s="29"/>
-      <c r="BT9" s="29"/>
-      <c r="BU9" s="29"/>
-      <c r="BV9" s="29"/>
-      <c r="BW9" s="29"/>
-      <c r="BX9" s="29"/>
-      <c r="BY9" s="29"/>
-      <c r="BZ9" s="29"/>
-      <c r="CA9" s="29"/>
-      <c r="CB9" s="29"/>
-      <c r="CC9" s="29"/>
-      <c r="CD9" s="29"/>
-      <c r="CE9" s="29"/>
-      <c r="CF9" s="29"/>
-      <c r="CG9" s="29"/>
-      <c r="CH9" s="29"/>
-      <c r="CI9" s="29"/>
-      <c r="CJ9" s="29"/>
-      <c r="CK9" s="29"/>
-      <c r="CL9" s="29"/>
-      <c r="CM9" s="29"/>
-      <c r="CN9" s="29"/>
-      <c r="CO9" s="29"/>
-      <c r="CP9" s="29"/>
-      <c r="CQ9" s="29"/>
-      <c r="CR9" s="29"/>
-      <c r="CS9" s="29"/>
-      <c r="CT9" s="29"/>
-      <c r="CU9" s="29"/>
-      <c r="CV9" s="29"/>
-      <c r="CW9" s="29"/>
-      <c r="CX9" s="29"/>
-      <c r="CY9" s="29"/>
-      <c r="CZ9" s="29"/>
-      <c r="DA9" s="29"/>
-      <c r="DB9" s="29"/>
-      <c r="DC9" s="29"/>
-      <c r="DD9" s="29"/>
-      <c r="DE9" s="29"/>
-      <c r="DF9" s="29"/>
-      <c r="DG9" s="29"/>
-      <c r="DH9" s="29"/>
-      <c r="DI9" s="29"/>
-      <c r="DJ9" s="29"/>
-      <c r="DK9" s="29"/>
-      <c r="DL9" s="29"/>
-      <c r="DM9" s="29"/>
-      <c r="DN9" s="29"/>
-      <c r="DO9" s="29"/>
-      <c r="DP9" s="29"/>
-      <c r="DQ9" s="29"/>
-      <c r="DR9" s="29"/>
-      <c r="DS9" s="29"/>
-      <c r="DT9" s="29"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="36"/>
+      <c r="K9" s="36"/>
+      <c r="L9" s="36"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="36"/>
+      <c r="S9" s="36"/>
+      <c r="T9" s="36"/>
+      <c r="U9" s="36"/>
+      <c r="V9" s="36"/>
+      <c r="W9" s="36"/>
+      <c r="X9" s="36"/>
+      <c r="Y9" s="36"/>
+      <c r="Z9" s="36"/>
+      <c r="AA9" s="36"/>
+      <c r="AB9" s="36"/>
+      <c r="AC9" s="36"/>
+      <c r="AD9" s="36"/>
+      <c r="AE9" s="36"/>
+      <c r="AF9" s="36"/>
+      <c r="AG9" s="36"/>
+      <c r="AH9" s="36"/>
+      <c r="AI9" s="36"/>
+      <c r="AJ9" s="36"/>
+      <c r="AK9" s="36"/>
+      <c r="AL9" s="36"/>
+      <c r="AM9" s="36"/>
+      <c r="AN9" s="36"/>
+      <c r="AO9" s="36"/>
+      <c r="AP9" s="36"/>
+      <c r="AQ9" s="36"/>
+      <c r="AR9" s="36"/>
+      <c r="AS9" s="36"/>
+      <c r="AT9" s="36"/>
+      <c r="AU9" s="36"/>
+      <c r="AV9" s="36"/>
+      <c r="AW9" s="36"/>
+      <c r="AX9" s="36"/>
+      <c r="AY9" s="36"/>
+      <c r="AZ9" s="36"/>
+      <c r="BA9" s="36"/>
+      <c r="BB9" s="36"/>
+      <c r="BC9" s="36"/>
+      <c r="BD9" s="36"/>
+      <c r="BE9" s="36"/>
+      <c r="BF9" s="36"/>
+      <c r="BG9" s="36"/>
+      <c r="BH9" s="36"/>
+      <c r="BI9" s="36"/>
+      <c r="BJ9" s="36"/>
+      <c r="BK9" s="36"/>
+      <c r="BL9" s="36"/>
+      <c r="BM9" s="36"/>
+      <c r="BN9" s="36"/>
+      <c r="BO9" s="36"/>
+      <c r="BP9" s="36"/>
+      <c r="BQ9" s="36"/>
+      <c r="BR9" s="36"/>
+      <c r="BS9" s="36"/>
+      <c r="BT9" s="36"/>
+      <c r="BU9" s="36"/>
+      <c r="BV9" s="36"/>
+      <c r="BW9" s="36"/>
+      <c r="BX9" s="36"/>
+      <c r="BY9" s="36"/>
+      <c r="BZ9" s="36"/>
+      <c r="CA9" s="36"/>
+      <c r="CB9" s="36"/>
+      <c r="CC9" s="36"/>
+      <c r="CD9" s="36"/>
+      <c r="CE9" s="36"/>
+      <c r="CF9" s="36"/>
+      <c r="CG9" s="36"/>
+      <c r="CH9" s="36"/>
+      <c r="CI9" s="36"/>
+      <c r="CJ9" s="36"/>
+      <c r="CK9" s="36"/>
+      <c r="CL9" s="36"/>
+      <c r="CM9" s="36"/>
+      <c r="CN9" s="36"/>
+      <c r="CO9" s="36"/>
+      <c r="CP9" s="36"/>
+      <c r="CQ9" s="36"/>
+      <c r="CR9" s="36"/>
+      <c r="CS9" s="36"/>
+      <c r="CT9" s="36"/>
+      <c r="CU9" s="36"/>
+      <c r="CV9" s="36"/>
+      <c r="CW9" s="36"/>
+      <c r="CX9" s="36"/>
+      <c r="CY9" s="36"/>
+      <c r="CZ9" s="36"/>
+      <c r="DA9" s="36"/>
+      <c r="DB9" s="36"/>
+      <c r="DC9" s="36"/>
+      <c r="DD9" s="36"/>
+      <c r="DE9" s="36"/>
+      <c r="DF9" s="36"/>
+      <c r="DG9" s="36"/>
+      <c r="DH9" s="36"/>
+      <c r="DI9" s="36"/>
+      <c r="DJ9" s="36"/>
+      <c r="DK9" s="36"/>
+      <c r="DL9" s="36"/>
+      <c r="DM9" s="36"/>
+      <c r="DN9" s="36"/>
+      <c r="DO9" s="36"/>
+      <c r="DP9" s="36"/>
+      <c r="DQ9" s="36"/>
+      <c r="DR9" s="36"/>
+      <c r="DS9" s="36"/>
+      <c r="DT9" s="36"/>
     </row>
     <row r="10" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="36"/>
-      <c r="B10" s="37"/>
+      <c r="A10" s="48"/>
+      <c r="B10" s="58"/>
       <c r="C10" s="6"/>
       <c r="D10" s="4" t="s">
         <v>10</v>
@@ -4828,250 +4828,250 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E26" s="32"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33"/>
-      <c r="K26" s="33"/>
-      <c r="L26" s="33"/>
-      <c r="M26" s="33"/>
-      <c r="N26" s="33"/>
-      <c r="O26" s="33"/>
-      <c r="P26" s="33"/>
-      <c r="Q26" s="33"/>
-      <c r="R26" s="33"/>
-      <c r="S26" s="33"/>
-      <c r="T26" s="33"/>
-      <c r="U26" s="33"/>
-      <c r="V26" s="33"/>
-      <c r="W26" s="33"/>
-      <c r="X26" s="33"/>
-      <c r="Y26" s="33"/>
-      <c r="Z26" s="33"/>
-      <c r="AA26" s="33"/>
-      <c r="AB26" s="33"/>
-      <c r="AC26" s="33"/>
-      <c r="AD26" s="33"/>
-      <c r="AE26" s="33"/>
-      <c r="AF26" s="33"/>
-      <c r="AG26" s="33"/>
-      <c r="AH26" s="33"/>
-      <c r="AI26" s="33"/>
-      <c r="AJ26" s="33"/>
-      <c r="AK26" s="33"/>
-      <c r="AL26" s="33"/>
-      <c r="AM26" s="33"/>
-      <c r="AN26" s="33"/>
-      <c r="AO26" s="33"/>
-      <c r="AP26" s="33"/>
-      <c r="AQ26" s="33"/>
-      <c r="AR26" s="33"/>
-      <c r="AS26" s="33"/>
-      <c r="AT26" s="33"/>
-      <c r="AU26" s="33"/>
-      <c r="AV26" s="33"/>
-      <c r="AW26" s="33"/>
-      <c r="AX26" s="33"/>
-      <c r="AY26" s="33"/>
-      <c r="AZ26" s="33"/>
-      <c r="BA26" s="33"/>
-      <c r="BB26" s="33"/>
-      <c r="BC26" s="33"/>
-      <c r="BD26" s="33"/>
-      <c r="BE26" s="33"/>
-      <c r="BF26" s="33"/>
-      <c r="BG26" s="33"/>
-      <c r="BH26" s="33"/>
-      <c r="BI26" s="33"/>
-      <c r="BJ26" s="33"/>
-      <c r="BK26" s="33"/>
-      <c r="BL26" s="33"/>
-      <c r="BM26" s="33"/>
-      <c r="BN26" s="33"/>
-      <c r="BO26" s="33"/>
-      <c r="BP26" s="33"/>
-      <c r="BQ26" s="33"/>
-      <c r="BR26" s="33"/>
-      <c r="BS26" s="33"/>
-      <c r="BT26" s="33"/>
-      <c r="BU26" s="33"/>
-      <c r="BV26" s="33"/>
-      <c r="BW26" s="33"/>
-      <c r="BX26" s="33"/>
-      <c r="BY26" s="33"/>
-      <c r="BZ26" s="33"/>
-      <c r="CA26" s="33"/>
-      <c r="CB26" s="33"/>
-      <c r="CC26" s="33"/>
-      <c r="CD26" s="33"/>
-      <c r="CE26" s="33"/>
-      <c r="CF26" s="33"/>
-      <c r="CG26" s="33"/>
-      <c r="CH26" s="33"/>
-      <c r="CI26" s="33"/>
-      <c r="CJ26" s="33"/>
-      <c r="CK26" s="33"/>
-      <c r="CL26" s="33"/>
-      <c r="CM26" s="33"/>
-      <c r="CN26" s="33"/>
-      <c r="CO26" s="33"/>
-      <c r="CP26" s="33"/>
-      <c r="CQ26" s="33"/>
-      <c r="CR26" s="33"/>
-      <c r="CS26" s="33"/>
-      <c r="CT26" s="33"/>
-      <c r="CU26" s="33"/>
-      <c r="CV26" s="33"/>
-      <c r="CW26" s="33"/>
-      <c r="CX26" s="33"/>
-      <c r="CY26" s="33"/>
-      <c r="CZ26" s="33"/>
-      <c r="DA26" s="33"/>
-      <c r="DB26" s="33"/>
-      <c r="DC26" s="33"/>
-      <c r="DD26" s="33"/>
-      <c r="DE26" s="33"/>
-      <c r="DF26" s="33"/>
-      <c r="DG26" s="33"/>
-      <c r="DH26" s="33"/>
-      <c r="DI26" s="33"/>
-      <c r="DJ26" s="33"/>
-      <c r="DK26" s="33"/>
-      <c r="DL26" s="33"/>
-      <c r="DM26" s="33"/>
-      <c r="DN26" s="33"/>
-      <c r="DO26" s="33"/>
-      <c r="DP26" s="33"/>
-      <c r="DQ26" s="33"/>
-      <c r="DR26" s="33"/>
-      <c r="DS26" s="33"/>
-      <c r="DT26" s="33"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="50"/>
+      <c r="G26" s="50"/>
+      <c r="H26" s="50"/>
+      <c r="I26" s="50"/>
+      <c r="J26" s="50"/>
+      <c r="K26" s="50"/>
+      <c r="L26" s="50"/>
+      <c r="M26" s="50"/>
+      <c r="N26" s="50"/>
+      <c r="O26" s="50"/>
+      <c r="P26" s="50"/>
+      <c r="Q26" s="50"/>
+      <c r="R26" s="50"/>
+      <c r="S26" s="50"/>
+      <c r="T26" s="50"/>
+      <c r="U26" s="50"/>
+      <c r="V26" s="50"/>
+      <c r="W26" s="50"/>
+      <c r="X26" s="50"/>
+      <c r="Y26" s="50"/>
+      <c r="Z26" s="50"/>
+      <c r="AA26" s="50"/>
+      <c r="AB26" s="50"/>
+      <c r="AC26" s="50"/>
+      <c r="AD26" s="50"/>
+      <c r="AE26" s="50"/>
+      <c r="AF26" s="50"/>
+      <c r="AG26" s="50"/>
+      <c r="AH26" s="50"/>
+      <c r="AI26" s="50"/>
+      <c r="AJ26" s="50"/>
+      <c r="AK26" s="50"/>
+      <c r="AL26" s="50"/>
+      <c r="AM26" s="50"/>
+      <c r="AN26" s="50"/>
+      <c r="AO26" s="50"/>
+      <c r="AP26" s="50"/>
+      <c r="AQ26" s="50"/>
+      <c r="AR26" s="50"/>
+      <c r="AS26" s="50"/>
+      <c r="AT26" s="50"/>
+      <c r="AU26" s="50"/>
+      <c r="AV26" s="50"/>
+      <c r="AW26" s="50"/>
+      <c r="AX26" s="50"/>
+      <c r="AY26" s="50"/>
+      <c r="AZ26" s="50"/>
+      <c r="BA26" s="50"/>
+      <c r="BB26" s="50"/>
+      <c r="BC26" s="50"/>
+      <c r="BD26" s="50"/>
+      <c r="BE26" s="50"/>
+      <c r="BF26" s="50"/>
+      <c r="BG26" s="50"/>
+      <c r="BH26" s="50"/>
+      <c r="BI26" s="50"/>
+      <c r="BJ26" s="50"/>
+      <c r="BK26" s="50"/>
+      <c r="BL26" s="50"/>
+      <c r="BM26" s="50"/>
+      <c r="BN26" s="50"/>
+      <c r="BO26" s="50"/>
+      <c r="BP26" s="50"/>
+      <c r="BQ26" s="50"/>
+      <c r="BR26" s="50"/>
+      <c r="BS26" s="50"/>
+      <c r="BT26" s="50"/>
+      <c r="BU26" s="50"/>
+      <c r="BV26" s="50"/>
+      <c r="BW26" s="50"/>
+      <c r="BX26" s="50"/>
+      <c r="BY26" s="50"/>
+      <c r="BZ26" s="50"/>
+      <c r="CA26" s="50"/>
+      <c r="CB26" s="50"/>
+      <c r="CC26" s="50"/>
+      <c r="CD26" s="50"/>
+      <c r="CE26" s="50"/>
+      <c r="CF26" s="50"/>
+      <c r="CG26" s="50"/>
+      <c r="CH26" s="50"/>
+      <c r="CI26" s="50"/>
+      <c r="CJ26" s="50"/>
+      <c r="CK26" s="50"/>
+      <c r="CL26" s="50"/>
+      <c r="CM26" s="50"/>
+      <c r="CN26" s="50"/>
+      <c r="CO26" s="50"/>
+      <c r="CP26" s="50"/>
+      <c r="CQ26" s="50"/>
+      <c r="CR26" s="50"/>
+      <c r="CS26" s="50"/>
+      <c r="CT26" s="50"/>
+      <c r="CU26" s="50"/>
+      <c r="CV26" s="50"/>
+      <c r="CW26" s="50"/>
+      <c r="CX26" s="50"/>
+      <c r="CY26" s="50"/>
+      <c r="CZ26" s="50"/>
+      <c r="DA26" s="50"/>
+      <c r="DB26" s="50"/>
+      <c r="DC26" s="50"/>
+      <c r="DD26" s="50"/>
+      <c r="DE26" s="50"/>
+      <c r="DF26" s="50"/>
+      <c r="DG26" s="50"/>
+      <c r="DH26" s="50"/>
+      <c r="DI26" s="50"/>
+      <c r="DJ26" s="50"/>
+      <c r="DK26" s="50"/>
+      <c r="DL26" s="50"/>
+      <c r="DM26" s="50"/>
+      <c r="DN26" s="50"/>
+      <c r="DO26" s="50"/>
+      <c r="DP26" s="50"/>
+      <c r="DQ26" s="50"/>
+      <c r="DR26" s="50"/>
+      <c r="DS26" s="50"/>
+      <c r="DT26" s="50"/>
     </row>
     <row r="27" spans="1:124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E27" s="1">
         <v>4</v>
       </c>
-      <c r="F27" s="57"/>
-      <c r="G27" s="57"/>
-      <c r="H27" s="57"/>
-      <c r="I27" s="57"/>
-      <c r="J27" s="57"/>
-      <c r="K27" s="57"/>
-      <c r="L27" s="57"/>
-      <c r="M27" s="57"/>
-      <c r="N27" s="57"/>
-      <c r="O27" s="57"/>
-      <c r="P27" s="57"/>
-      <c r="Q27" s="57"/>
-      <c r="R27" s="57"/>
-      <c r="S27" s="57"/>
-      <c r="T27" s="57"/>
-      <c r="U27" s="57"/>
-      <c r="V27" s="57"/>
-      <c r="W27" s="57"/>
-      <c r="X27" s="57"/>
-      <c r="Y27" s="57"/>
-      <c r="Z27" s="57"/>
-      <c r="AA27" s="57"/>
-      <c r="AB27" s="57"/>
-      <c r="AC27" s="57"/>
-      <c r="AD27" s="57"/>
-      <c r="AE27" s="57"/>
-      <c r="AF27" s="57"/>
-      <c r="AG27" s="57"/>
-      <c r="AH27" s="57"/>
-      <c r="AI27" s="57"/>
-      <c r="AJ27" s="57"/>
-      <c r="AK27" s="57"/>
-      <c r="AL27" s="57"/>
-      <c r="AM27" s="57"/>
-      <c r="AN27" s="57"/>
-      <c r="AO27" s="57"/>
-      <c r="AP27" s="57"/>
-      <c r="AQ27" s="57"/>
-      <c r="AR27" s="57"/>
-      <c r="AS27" s="57"/>
-      <c r="AT27" s="57"/>
-      <c r="AU27" s="57"/>
-      <c r="AV27" s="57"/>
-      <c r="AW27" s="57"/>
-      <c r="AX27" s="57"/>
-      <c r="AY27" s="57"/>
-      <c r="AZ27" s="57"/>
-      <c r="BA27" s="57"/>
-      <c r="BB27" s="57"/>
-      <c r="BC27" s="57"/>
-      <c r="BD27" s="57"/>
-      <c r="BE27" s="57"/>
-      <c r="BF27" s="57"/>
-      <c r="BG27" s="57"/>
-      <c r="BH27" s="57"/>
-      <c r="BI27" s="57"/>
-      <c r="BJ27" s="57"/>
-      <c r="BK27" s="57"/>
-      <c r="BL27" s="57"/>
-      <c r="BM27" s="57"/>
-      <c r="BN27" s="57"/>
-      <c r="BO27" s="57"/>
-      <c r="BP27" s="57"/>
-      <c r="BQ27" s="57"/>
-      <c r="BR27" s="57"/>
-      <c r="BS27" s="57"/>
-      <c r="BT27" s="57"/>
-      <c r="BU27" s="57"/>
-      <c r="BV27" s="57"/>
-      <c r="BW27" s="57"/>
-      <c r="BX27" s="57"/>
-      <c r="BY27" s="57"/>
-      <c r="BZ27" s="57"/>
-      <c r="CA27" s="57"/>
-      <c r="CB27" s="57"/>
-      <c r="CC27" s="57"/>
-      <c r="CD27" s="57"/>
-      <c r="CE27" s="58"/>
-      <c r="CF27" s="59"/>
-      <c r="CG27" s="59"/>
-      <c r="CH27" s="59"/>
-      <c r="CI27" s="59"/>
-      <c r="CJ27" s="59"/>
-      <c r="CK27" s="59"/>
-      <c r="CL27" s="59"/>
-      <c r="CM27" s="59"/>
-      <c r="CN27" s="59"/>
-      <c r="CO27" s="59"/>
-      <c r="CP27" s="59"/>
-      <c r="CQ27" s="59"/>
-      <c r="CR27" s="59"/>
-      <c r="CS27" s="59"/>
-      <c r="CT27" s="59"/>
-      <c r="CU27" s="59"/>
-      <c r="CV27" s="59"/>
-      <c r="CW27" s="59"/>
-      <c r="CX27" s="59"/>
-      <c r="CY27" s="59"/>
-      <c r="CZ27" s="59"/>
-      <c r="DA27" s="59"/>
-      <c r="DB27" s="59"/>
-      <c r="DC27" s="59"/>
-      <c r="DD27" s="59"/>
-      <c r="DE27" s="59"/>
-      <c r="DF27" s="59"/>
-      <c r="DG27" s="59"/>
-      <c r="DH27" s="59"/>
-      <c r="DI27" s="59"/>
-      <c r="DJ27" s="59"/>
-      <c r="DK27" s="59"/>
-      <c r="DL27" s="59"/>
-      <c r="DM27" s="59"/>
-      <c r="DN27" s="59"/>
-      <c r="DO27" s="59"/>
-      <c r="DP27" s="59"/>
-      <c r="DQ27" s="59"/>
-      <c r="DR27" s="59"/>
-      <c r="DS27" s="59"/>
-      <c r="DT27" s="59"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="32"/>
+      <c r="J27" s="32"/>
+      <c r="K27" s="32"/>
+      <c r="L27" s="32"/>
+      <c r="M27" s="32"/>
+      <c r="N27" s="32"/>
+      <c r="O27" s="32"/>
+      <c r="P27" s="32"/>
+      <c r="Q27" s="32"/>
+      <c r="R27" s="32"/>
+      <c r="S27" s="32"/>
+      <c r="T27" s="32"/>
+      <c r="U27" s="32"/>
+      <c r="V27" s="32"/>
+      <c r="W27" s="32"/>
+      <c r="X27" s="32"/>
+      <c r="Y27" s="32"/>
+      <c r="Z27" s="32"/>
+      <c r="AA27" s="32"/>
+      <c r="AB27" s="32"/>
+      <c r="AC27" s="32"/>
+      <c r="AD27" s="32"/>
+      <c r="AE27" s="32"/>
+      <c r="AF27" s="32"/>
+      <c r="AG27" s="32"/>
+      <c r="AH27" s="32"/>
+      <c r="AI27" s="32"/>
+      <c r="AJ27" s="32"/>
+      <c r="AK27" s="32"/>
+      <c r="AL27" s="32"/>
+      <c r="AM27" s="32"/>
+      <c r="AN27" s="32"/>
+      <c r="AO27" s="32"/>
+      <c r="AP27" s="32"/>
+      <c r="AQ27" s="32"/>
+      <c r="AR27" s="32"/>
+      <c r="AS27" s="32"/>
+      <c r="AT27" s="32"/>
+      <c r="AU27" s="32"/>
+      <c r="AV27" s="32"/>
+      <c r="AW27" s="32"/>
+      <c r="AX27" s="32"/>
+      <c r="AY27" s="32"/>
+      <c r="AZ27" s="32"/>
+      <c r="BA27" s="32"/>
+      <c r="BB27" s="32"/>
+      <c r="BC27" s="32"/>
+      <c r="BD27" s="32"/>
+      <c r="BE27" s="32"/>
+      <c r="BF27" s="32"/>
+      <c r="BG27" s="32"/>
+      <c r="BH27" s="32"/>
+      <c r="BI27" s="32"/>
+      <c r="BJ27" s="32"/>
+      <c r="BK27" s="32"/>
+      <c r="BL27" s="32"/>
+      <c r="BM27" s="32"/>
+      <c r="BN27" s="32"/>
+      <c r="BO27" s="32"/>
+      <c r="BP27" s="32"/>
+      <c r="BQ27" s="32"/>
+      <c r="BR27" s="32"/>
+      <c r="BS27" s="32"/>
+      <c r="BT27" s="32"/>
+      <c r="BU27" s="32"/>
+      <c r="BV27" s="32"/>
+      <c r="BW27" s="32"/>
+      <c r="BX27" s="32"/>
+      <c r="BY27" s="32"/>
+      <c r="BZ27" s="32"/>
+      <c r="CA27" s="32"/>
+      <c r="CB27" s="32"/>
+      <c r="CC27" s="32"/>
+      <c r="CD27" s="32"/>
+      <c r="CE27" s="33"/>
+      <c r="CF27" s="34"/>
+      <c r="CG27" s="34"/>
+      <c r="CH27" s="34"/>
+      <c r="CI27" s="34"/>
+      <c r="CJ27" s="34"/>
+      <c r="CK27" s="34"/>
+      <c r="CL27" s="34"/>
+      <c r="CM27" s="34"/>
+      <c r="CN27" s="34"/>
+      <c r="CO27" s="34"/>
+      <c r="CP27" s="34"/>
+      <c r="CQ27" s="34"/>
+      <c r="CR27" s="34"/>
+      <c r="CS27" s="34"/>
+      <c r="CT27" s="34"/>
+      <c r="CU27" s="34"/>
+      <c r="CV27" s="34"/>
+      <c r="CW27" s="34"/>
+      <c r="CX27" s="34"/>
+      <c r="CY27" s="34"/>
+      <c r="CZ27" s="34"/>
+      <c r="DA27" s="34"/>
+      <c r="DB27" s="34"/>
+      <c r="DC27" s="34"/>
+      <c r="DD27" s="34"/>
+      <c r="DE27" s="34"/>
+      <c r="DF27" s="34"/>
+      <c r="DG27" s="34"/>
+      <c r="DH27" s="34"/>
+      <c r="DI27" s="34"/>
+      <c r="DJ27" s="34"/>
+      <c r="DK27" s="34"/>
+      <c r="DL27" s="34"/>
+      <c r="DM27" s="34"/>
+      <c r="DN27" s="34"/>
+      <c r="DO27" s="34"/>
+      <c r="DP27" s="34"/>
+      <c r="DQ27" s="34"/>
+      <c r="DR27" s="34"/>
+      <c r="DS27" s="34"/>
+      <c r="DT27" s="34"/>
     </row>
     <row r="29" spans="1:124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E29" s="22">
@@ -5097,6 +5097,248 @@
     </row>
   </sheetData>
   <mergeCells count="266">
+    <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="N1:Q1"/>
+    <mergeCell ref="BC8:BC9"/>
+    <mergeCell ref="BD8:BD9"/>
+    <mergeCell ref="BE8:BE9"/>
+    <mergeCell ref="AN8:AN9"/>
+    <mergeCell ref="AO8:AO9"/>
+    <mergeCell ref="AP8:AP9"/>
+    <mergeCell ref="AQ8:AQ9"/>
+    <mergeCell ref="AR8:AR9"/>
+    <mergeCell ref="AS8:AS9"/>
+    <mergeCell ref="AT8:AT9"/>
+    <mergeCell ref="AU8:AU9"/>
+    <mergeCell ref="AV8:AV9"/>
+    <mergeCell ref="AE8:AE9"/>
+    <mergeCell ref="AF8:AF9"/>
+    <mergeCell ref="AG8:AG9"/>
+    <mergeCell ref="AH8:AH9"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AJ8:AJ9"/>
+    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="AL8:AL9"/>
+    <mergeCell ref="AM8:AM9"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="BO8:BO9"/>
+    <mergeCell ref="BP8:BP9"/>
+    <mergeCell ref="BQ8:BQ9"/>
+    <mergeCell ref="BR8:BR9"/>
+    <mergeCell ref="BS8:BS9"/>
+    <mergeCell ref="BT8:BT9"/>
+    <mergeCell ref="BZ8:BZ9"/>
+    <mergeCell ref="CA8:CA9"/>
+    <mergeCell ref="BH8:BH9"/>
+    <mergeCell ref="BI8:BI9"/>
+    <mergeCell ref="BJ8:BJ9"/>
+    <mergeCell ref="BK8:BK9"/>
+    <mergeCell ref="BL8:BL9"/>
+    <mergeCell ref="BM8:BM9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
+    <mergeCell ref="CB8:CB9"/>
+    <mergeCell ref="CC8:CC9"/>
+    <mergeCell ref="CD8:CD9"/>
+    <mergeCell ref="CE8:CE9"/>
+    <mergeCell ref="CF8:CF9"/>
+    <mergeCell ref="CV8:CV9"/>
+    <mergeCell ref="BQ2:BQ7"/>
+    <mergeCell ref="BR2:BR7"/>
+    <mergeCell ref="BS2:BS7"/>
+    <mergeCell ref="BT2:BT7"/>
+    <mergeCell ref="BU2:BU7"/>
+    <mergeCell ref="BV2:BV7"/>
+    <mergeCell ref="CO8:CO9"/>
+    <mergeCell ref="CP8:CP9"/>
+    <mergeCell ref="CH2:CH7"/>
+    <mergeCell ref="CT8:CT9"/>
+    <mergeCell ref="CU8:CU9"/>
+    <mergeCell ref="CB2:CB7"/>
+    <mergeCell ref="CC2:CC7"/>
+    <mergeCell ref="CD2:CD7"/>
+    <mergeCell ref="CE2:CE7"/>
+    <mergeCell ref="CF2:CF7"/>
+    <mergeCell ref="CG2:CG7"/>
+    <mergeCell ref="CJ8:CJ9"/>
+    <mergeCell ref="E26:DT26"/>
+    <mergeCell ref="DF8:DF9"/>
+    <mergeCell ref="DQ8:DQ9"/>
+    <mergeCell ref="DR8:DR9"/>
+    <mergeCell ref="DS8:DS9"/>
+    <mergeCell ref="DT8:DT9"/>
+    <mergeCell ref="CY8:CY9"/>
+    <mergeCell ref="CZ8:CZ9"/>
+    <mergeCell ref="CM8:CM9"/>
+    <mergeCell ref="CW8:CW9"/>
+    <mergeCell ref="CX8:CX9"/>
+    <mergeCell ref="BU8:BU9"/>
+    <mergeCell ref="BV8:BV9"/>
+    <mergeCell ref="BW8:BW9"/>
+    <mergeCell ref="BF8:BF9"/>
+    <mergeCell ref="BG8:BG9"/>
+    <mergeCell ref="CG8:CG9"/>
+    <mergeCell ref="CH8:CH9"/>
+    <mergeCell ref="AW8:AW9"/>
+    <mergeCell ref="AX8:AX9"/>
+    <mergeCell ref="AY8:AY9"/>
+    <mergeCell ref="AZ8:AZ9"/>
+    <mergeCell ref="BA8:BA9"/>
+    <mergeCell ref="BB8:BB9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="F2:F7"/>
+    <mergeCell ref="G2:G7"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="I2:I7"/>
+    <mergeCell ref="J2:J7"/>
+    <mergeCell ref="K2:K7"/>
+    <mergeCell ref="L2:L7"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="M2:M7"/>
+    <mergeCell ref="N2:N7"/>
+    <mergeCell ref="O2:O7"/>
+    <mergeCell ref="P2:P7"/>
+    <mergeCell ref="Q2:Q7"/>
+    <mergeCell ref="R2:R7"/>
+    <mergeCell ref="S2:S7"/>
+    <mergeCell ref="T2:T7"/>
+    <mergeCell ref="CN8:CN9"/>
+    <mergeCell ref="Y2:Y7"/>
+    <mergeCell ref="Z2:Z7"/>
+    <mergeCell ref="AA2:AA7"/>
+    <mergeCell ref="AB2:AB7"/>
+    <mergeCell ref="AC2:AC7"/>
+    <mergeCell ref="AD2:AD7"/>
+    <mergeCell ref="AE2:AE7"/>
+    <mergeCell ref="AH2:AH7"/>
+    <mergeCell ref="AI2:AI7"/>
+    <mergeCell ref="AJ2:AJ7"/>
+    <mergeCell ref="AK2:AK7"/>
+    <mergeCell ref="AL2:AL7"/>
+    <mergeCell ref="AM2:AM7"/>
+    <mergeCell ref="AN2:AN7"/>
+    <mergeCell ref="AO2:AO7"/>
+    <mergeCell ref="AG2:AG7"/>
+    <mergeCell ref="X2:X7"/>
+    <mergeCell ref="AF2:AF7"/>
+    <mergeCell ref="AX2:AX7"/>
+    <mergeCell ref="AY2:AY7"/>
+    <mergeCell ref="AZ2:AZ7"/>
+    <mergeCell ref="BL2:BL7"/>
+    <mergeCell ref="BA2:BA7"/>
+    <mergeCell ref="BB2:BB7"/>
+    <mergeCell ref="BC2:BC7"/>
+    <mergeCell ref="AP2:AP7"/>
+    <mergeCell ref="AQ2:AQ7"/>
+    <mergeCell ref="AR2:AR7"/>
+    <mergeCell ref="AS2:AS7"/>
+    <mergeCell ref="AT2:AT7"/>
+    <mergeCell ref="AU2:AU7"/>
+    <mergeCell ref="AV2:AV7"/>
+    <mergeCell ref="AW2:AW7"/>
+    <mergeCell ref="BD2:BD7"/>
+    <mergeCell ref="BE2:BE7"/>
+    <mergeCell ref="BF2:BF7"/>
+    <mergeCell ref="BG2:BG7"/>
+    <mergeCell ref="BM2:BM7"/>
+    <mergeCell ref="BN2:BN7"/>
+    <mergeCell ref="BO2:BO7"/>
+    <mergeCell ref="BP2:BP7"/>
+    <mergeCell ref="CA2:CA7"/>
+    <mergeCell ref="BW2:BW7"/>
+    <mergeCell ref="BX2:BX7"/>
+    <mergeCell ref="BY2:BY7"/>
+    <mergeCell ref="BZ2:BZ7"/>
+    <mergeCell ref="BH2:BH7"/>
+    <mergeCell ref="BI2:BI7"/>
+    <mergeCell ref="BJ2:BJ7"/>
+    <mergeCell ref="BK2:BK7"/>
+    <mergeCell ref="BN8:BN9"/>
+    <mergeCell ref="CI8:CI9"/>
+    <mergeCell ref="CK8:CK9"/>
+    <mergeCell ref="CL8:CL9"/>
+    <mergeCell ref="BX8:BX9"/>
+    <mergeCell ref="BY8:BY9"/>
+    <mergeCell ref="DL2:DL7"/>
+    <mergeCell ref="DM2:DM7"/>
+    <mergeCell ref="DF2:DF7"/>
+    <mergeCell ref="CW2:CW7"/>
+    <mergeCell ref="CU2:CU7"/>
+    <mergeCell ref="CV2:CV7"/>
+    <mergeCell ref="CQ2:CQ7"/>
+    <mergeCell ref="CR2:CR7"/>
+    <mergeCell ref="CS2:CS7"/>
+    <mergeCell ref="CT2:CT7"/>
+    <mergeCell ref="CI2:CI7"/>
+    <mergeCell ref="CJ2:CJ7"/>
+    <mergeCell ref="CK2:CK7"/>
+    <mergeCell ref="CL2:CL7"/>
+    <mergeCell ref="CM2:CM7"/>
+    <mergeCell ref="CN2:CN7"/>
+    <mergeCell ref="CO2:CO7"/>
+    <mergeCell ref="CP2:CP7"/>
+    <mergeCell ref="V2:V7"/>
+    <mergeCell ref="W2:W7"/>
+    <mergeCell ref="F27:S27"/>
+    <mergeCell ref="T27:AW27"/>
+    <mergeCell ref="AX27:CD27"/>
+    <mergeCell ref="CE27:DT27"/>
+    <mergeCell ref="DG8:DG9"/>
+    <mergeCell ref="DH8:DH9"/>
+    <mergeCell ref="DI8:DI9"/>
+    <mergeCell ref="DJ8:DJ9"/>
+    <mergeCell ref="DK8:DK9"/>
+    <mergeCell ref="DL8:DL9"/>
+    <mergeCell ref="DM8:DM9"/>
+    <mergeCell ref="DN8:DN9"/>
+    <mergeCell ref="DO8:DO9"/>
+    <mergeCell ref="DP8:DP9"/>
+    <mergeCell ref="DA8:DA9"/>
+    <mergeCell ref="DB8:DB9"/>
+    <mergeCell ref="DC8:DC9"/>
+    <mergeCell ref="DD8:DD9"/>
+    <mergeCell ref="DE8:DE9"/>
+    <mergeCell ref="CQ8:CQ9"/>
+    <mergeCell ref="CR8:CR9"/>
+    <mergeCell ref="CS8:CS9"/>
     <mergeCell ref="AD1:AG1"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="R1:U1"/>
@@ -5121,248 +5363,6 @@
     <mergeCell ref="DJ2:DJ7"/>
     <mergeCell ref="DK2:DK7"/>
     <mergeCell ref="U2:U7"/>
-    <mergeCell ref="V2:V7"/>
-    <mergeCell ref="W2:W7"/>
-    <mergeCell ref="F27:S27"/>
-    <mergeCell ref="T27:AW27"/>
-    <mergeCell ref="AX27:CD27"/>
-    <mergeCell ref="CE27:DT27"/>
-    <mergeCell ref="DG8:DG9"/>
-    <mergeCell ref="DH8:DH9"/>
-    <mergeCell ref="DI8:DI9"/>
-    <mergeCell ref="DJ8:DJ9"/>
-    <mergeCell ref="DK8:DK9"/>
-    <mergeCell ref="DL8:DL9"/>
-    <mergeCell ref="DM8:DM9"/>
-    <mergeCell ref="DN8:DN9"/>
-    <mergeCell ref="DO8:DO9"/>
-    <mergeCell ref="DP8:DP9"/>
-    <mergeCell ref="DA8:DA9"/>
-    <mergeCell ref="DB8:DB9"/>
-    <mergeCell ref="DC8:DC9"/>
-    <mergeCell ref="DD8:DD9"/>
-    <mergeCell ref="DE8:DE9"/>
-    <mergeCell ref="CQ8:CQ9"/>
-    <mergeCell ref="CR8:CR9"/>
-    <mergeCell ref="CS8:CS9"/>
-    <mergeCell ref="BN8:BN9"/>
-    <mergeCell ref="CI8:CI9"/>
-    <mergeCell ref="CK8:CK9"/>
-    <mergeCell ref="CL8:CL9"/>
-    <mergeCell ref="BX8:BX9"/>
-    <mergeCell ref="BY8:BY9"/>
-    <mergeCell ref="DL2:DL7"/>
-    <mergeCell ref="DM2:DM7"/>
-    <mergeCell ref="DF2:DF7"/>
-    <mergeCell ref="BD2:BD7"/>
-    <mergeCell ref="BE2:BE7"/>
-    <mergeCell ref="BF2:BF7"/>
-    <mergeCell ref="BG2:BG7"/>
-    <mergeCell ref="BM2:BM7"/>
-    <mergeCell ref="BN2:BN7"/>
-    <mergeCell ref="BO2:BO7"/>
-    <mergeCell ref="BP2:BP7"/>
-    <mergeCell ref="CA2:CA7"/>
-    <mergeCell ref="BW2:BW7"/>
-    <mergeCell ref="BX2:BX7"/>
-    <mergeCell ref="BY2:BY7"/>
-    <mergeCell ref="BZ2:BZ7"/>
-    <mergeCell ref="BH2:BH7"/>
-    <mergeCell ref="BI2:BI7"/>
-    <mergeCell ref="BJ2:BJ7"/>
-    <mergeCell ref="BK2:BK7"/>
-    <mergeCell ref="X2:X7"/>
-    <mergeCell ref="AF2:AF7"/>
-    <mergeCell ref="AX2:AX7"/>
-    <mergeCell ref="AY2:AY7"/>
-    <mergeCell ref="AZ2:AZ7"/>
-    <mergeCell ref="BL2:BL7"/>
-    <mergeCell ref="BA2:BA7"/>
-    <mergeCell ref="BB2:BB7"/>
-    <mergeCell ref="BC2:BC7"/>
-    <mergeCell ref="AP2:AP7"/>
-    <mergeCell ref="AQ2:AQ7"/>
-    <mergeCell ref="AR2:AR7"/>
-    <mergeCell ref="AS2:AS7"/>
-    <mergeCell ref="AT2:AT7"/>
-    <mergeCell ref="AU2:AU7"/>
-    <mergeCell ref="AV2:AV7"/>
-    <mergeCell ref="AW2:AW7"/>
-    <mergeCell ref="CW2:CW7"/>
-    <mergeCell ref="CU2:CU7"/>
-    <mergeCell ref="CV2:CV7"/>
-    <mergeCell ref="CQ2:CQ7"/>
-    <mergeCell ref="CR2:CR7"/>
-    <mergeCell ref="CS2:CS7"/>
-    <mergeCell ref="CT2:CT7"/>
-    <mergeCell ref="CI2:CI7"/>
-    <mergeCell ref="CJ2:CJ7"/>
-    <mergeCell ref="CK2:CK7"/>
-    <mergeCell ref="CL2:CL7"/>
-    <mergeCell ref="CM2:CM7"/>
-    <mergeCell ref="CN2:CN7"/>
-    <mergeCell ref="CO2:CO7"/>
-    <mergeCell ref="CP2:CP7"/>
-    <mergeCell ref="N2:N7"/>
-    <mergeCell ref="O2:O7"/>
-    <mergeCell ref="P2:P7"/>
-    <mergeCell ref="Q2:Q7"/>
-    <mergeCell ref="R2:R7"/>
-    <mergeCell ref="S2:S7"/>
-    <mergeCell ref="T2:T7"/>
-    <mergeCell ref="CN8:CN9"/>
-    <mergeCell ref="Y2:Y7"/>
-    <mergeCell ref="Z2:Z7"/>
-    <mergeCell ref="AA2:AA7"/>
-    <mergeCell ref="AB2:AB7"/>
-    <mergeCell ref="AC2:AC7"/>
-    <mergeCell ref="AD2:AD7"/>
-    <mergeCell ref="AE2:AE7"/>
-    <mergeCell ref="AH2:AH7"/>
-    <mergeCell ref="AI2:AI7"/>
-    <mergeCell ref="AJ2:AJ7"/>
-    <mergeCell ref="AK2:AK7"/>
-    <mergeCell ref="AL2:AL7"/>
-    <mergeCell ref="AM2:AM7"/>
-    <mergeCell ref="AN2:AN7"/>
-    <mergeCell ref="AO2:AO7"/>
-    <mergeCell ref="AG2:AG7"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="F2:F7"/>
-    <mergeCell ref="G2:G7"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="I2:I7"/>
-    <mergeCell ref="J2:J7"/>
-    <mergeCell ref="K2:K7"/>
-    <mergeCell ref="L2:L7"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="M2:M7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="E26:DT26"/>
-    <mergeCell ref="DF8:DF9"/>
-    <mergeCell ref="DQ8:DQ9"/>
-    <mergeCell ref="DR8:DR9"/>
-    <mergeCell ref="DS8:DS9"/>
-    <mergeCell ref="DT8:DT9"/>
-    <mergeCell ref="CY8:CY9"/>
-    <mergeCell ref="CZ8:CZ9"/>
-    <mergeCell ref="CM8:CM9"/>
-    <mergeCell ref="CW8:CW9"/>
-    <mergeCell ref="CX8:CX9"/>
-    <mergeCell ref="BU8:BU9"/>
-    <mergeCell ref="BV8:BV9"/>
-    <mergeCell ref="BW8:BW9"/>
-    <mergeCell ref="BF8:BF9"/>
-    <mergeCell ref="BG8:BG9"/>
-    <mergeCell ref="CG8:CG9"/>
-    <mergeCell ref="CH8:CH9"/>
-    <mergeCell ref="AW8:AW9"/>
-    <mergeCell ref="AX8:AX9"/>
-    <mergeCell ref="AY8:AY9"/>
-    <mergeCell ref="AZ8:AZ9"/>
-    <mergeCell ref="BA8:BA9"/>
-    <mergeCell ref="BB8:BB9"/>
-    <mergeCell ref="CB8:CB9"/>
-    <mergeCell ref="CC8:CC9"/>
-    <mergeCell ref="CD8:CD9"/>
-    <mergeCell ref="CE8:CE9"/>
-    <mergeCell ref="CF8:CF9"/>
-    <mergeCell ref="CV8:CV9"/>
-    <mergeCell ref="BQ2:BQ7"/>
-    <mergeCell ref="BR2:BR7"/>
-    <mergeCell ref="BS2:BS7"/>
-    <mergeCell ref="BT2:BT7"/>
-    <mergeCell ref="BU2:BU7"/>
-    <mergeCell ref="BV2:BV7"/>
-    <mergeCell ref="CO8:CO9"/>
-    <mergeCell ref="CP8:CP9"/>
-    <mergeCell ref="CH2:CH7"/>
-    <mergeCell ref="CT8:CT9"/>
-    <mergeCell ref="CU8:CU9"/>
-    <mergeCell ref="CB2:CB7"/>
-    <mergeCell ref="CC2:CC7"/>
-    <mergeCell ref="CD2:CD7"/>
-    <mergeCell ref="CE2:CE7"/>
-    <mergeCell ref="CF2:CF7"/>
-    <mergeCell ref="CG2:CG7"/>
-    <mergeCell ref="CJ8:CJ9"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="BO8:BO9"/>
-    <mergeCell ref="BP8:BP9"/>
-    <mergeCell ref="BQ8:BQ9"/>
-    <mergeCell ref="BR8:BR9"/>
-    <mergeCell ref="BS8:BS9"/>
-    <mergeCell ref="BT8:BT9"/>
-    <mergeCell ref="BZ8:BZ9"/>
-    <mergeCell ref="CA8:CA9"/>
-    <mergeCell ref="BH8:BH9"/>
-    <mergeCell ref="BI8:BI9"/>
-    <mergeCell ref="BJ8:BJ9"/>
-    <mergeCell ref="BK8:BK9"/>
-    <mergeCell ref="BL8:BL9"/>
-    <mergeCell ref="BM8:BM9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="Z1:AC1"/>
-    <mergeCell ref="N1:Q1"/>
-    <mergeCell ref="BC8:BC9"/>
-    <mergeCell ref="BD8:BD9"/>
-    <mergeCell ref="BE8:BE9"/>
-    <mergeCell ref="AN8:AN9"/>
-    <mergeCell ref="AO8:AO9"/>
-    <mergeCell ref="AP8:AP9"/>
-    <mergeCell ref="AQ8:AQ9"/>
-    <mergeCell ref="AR8:AR9"/>
-    <mergeCell ref="AS8:AS9"/>
-    <mergeCell ref="AT8:AT9"/>
-    <mergeCell ref="AU8:AU9"/>
-    <mergeCell ref="AV8:AV9"/>
-    <mergeCell ref="AE8:AE9"/>
-    <mergeCell ref="AF8:AF9"/>
-    <mergeCell ref="AG8:AG9"/>
-    <mergeCell ref="AH8:AH9"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AJ8:AJ9"/>
-    <mergeCell ref="AK8:AK9"/>
-    <mergeCell ref="AL8:AL9"/>
-    <mergeCell ref="AM8:AM9"/>
-    <mergeCell ref="V8:V9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -5395,7 +5395,7 @@
       <c r="H2" s="61"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="48" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="63" t="s">
@@ -5419,7 +5419,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="36"/>
+      <c r="A4" s="48"/>
       <c r="B4" s="65"/>
       <c r="C4" s="66"/>
       <c r="D4" s="68"/>

--- a/Journals/Angular ჟურნალი.xlsx
+++ b/Journals/Angular ჟურნალი.xlsx
@@ -5,14 +5,14 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\411\Desktop\12-2024 - web\Mermisi-main\Journals\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\411\Desktop\12-2024 - web\0 -Mermisi-main\Journals\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
   </bookViews>
   <sheets>
-    <sheet name="cms" sheetId="1" r:id="rId1"/>
+    <sheet name="Angular" sheetId="1" r:id="rId1"/>
     <sheet name="გაცდენები" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="152511"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="44">
   <si>
     <t>რიცხვი</t>
   </si>
@@ -125,9 +125,6 @@
   </si>
   <si>
     <t>გავაცდინე ეს საათი</t>
-  </si>
-  <si>
-    <t>წინა მასწავლებელმა ჩაატარა</t>
   </si>
   <si>
     <t>მარტი</t>
@@ -269,7 +266,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -308,6 +305,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,7 +497,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -537,7 +540,6 @@
     <xf numFmtId="10" fontId="10" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -557,12 +559,87 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="2" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -578,81 +655,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="16" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="16" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -679,6 +681,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -896,7 +904,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:DU31"/>
+  <dimension ref="A1:DU30"/>
   <sheetFormatPr defaultColWidth="3.5703125" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.5703125" style="2"/>
@@ -914,1484 +922,1494 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="41"/>
-      <c r="F1" s="25">
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="40"/>
+      <c r="F1" s="24">
         <v>8</v>
       </c>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="25">
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="24">
         <v>4</v>
       </c>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="25">
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="24">
         <v>4</v>
       </c>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="25">
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="24">
         <v>4</v>
       </c>
-      <c r="S1" s="26"/>
-      <c r="T1" s="26"/>
-      <c r="U1" s="27"/>
-      <c r="V1" s="25">
+      <c r="S1" s="25"/>
+      <c r="T1" s="25"/>
+      <c r="U1" s="26"/>
+      <c r="V1" s="24">
         <v>4</v>
       </c>
-      <c r="W1" s="26"/>
-      <c r="X1" s="26"/>
-      <c r="Y1" s="27"/>
-      <c r="Z1" s="25"/>
-      <c r="AA1" s="26"/>
-      <c r="AB1" s="26"/>
-      <c r="AC1" s="27"/>
-      <c r="AD1" s="25">
+      <c r="W1" s="25"/>
+      <c r="X1" s="25"/>
+      <c r="Y1" s="26"/>
+      <c r="Z1" s="24"/>
+      <c r="AA1" s="25"/>
+      <c r="AB1" s="25"/>
+      <c r="AC1" s="26"/>
+      <c r="AD1" s="24">
         <v>4</v>
       </c>
-      <c r="AE1" s="26"/>
-      <c r="AF1" s="26"/>
-      <c r="AG1" s="27"/>
-      <c r="AH1" s="23"/>
-      <c r="AI1" s="23"/>
-      <c r="AJ1" s="23"/>
-      <c r="AK1" s="23"/>
-      <c r="AL1" s="23"/>
-      <c r="AM1" s="23"/>
-      <c r="AN1" s="23"/>
-      <c r="AO1" s="23"/>
-      <c r="AP1" s="23"/>
-      <c r="AQ1" s="23"/>
-      <c r="AR1" s="23"/>
-      <c r="AS1" s="23"/>
-      <c r="AT1" s="23"/>
-      <c r="AU1" s="23"/>
-      <c r="AV1" s="23"/>
-      <c r="AW1" s="23"/>
-      <c r="AX1" s="23"/>
-      <c r="AY1" s="23"/>
-      <c r="AZ1" s="23"/>
-      <c r="BA1" s="23"/>
-      <c r="BB1" s="23"/>
-      <c r="BC1" s="23"/>
-      <c r="BD1" s="23"/>
-      <c r="BE1" s="23"/>
-      <c r="BF1" s="23"/>
-      <c r="BG1" s="23"/>
-      <c r="BH1" s="23"/>
-      <c r="BI1" s="23"/>
-      <c r="BJ1" s="23"/>
-      <c r="BK1" s="23"/>
-      <c r="BL1" s="23"/>
-      <c r="BM1" s="23"/>
-      <c r="BN1" s="23"/>
-      <c r="BO1" s="23"/>
-      <c r="BP1" s="23"/>
-      <c r="BQ1" s="23"/>
-      <c r="BR1" s="23"/>
-      <c r="BS1" s="23"/>
-      <c r="BT1" s="23"/>
-      <c r="BU1" s="23"/>
-      <c r="BV1" s="23"/>
-      <c r="BW1" s="23"/>
-      <c r="BX1" s="23"/>
-      <c r="BY1" s="23"/>
-      <c r="BZ1" s="23"/>
-      <c r="CA1" s="23"/>
-      <c r="CB1" s="23"/>
-      <c r="CC1" s="23"/>
-      <c r="CD1" s="23"/>
-      <c r="CE1" s="23"/>
-      <c r="CF1" s="23"/>
-      <c r="CG1" s="23"/>
-      <c r="CH1" s="23"/>
-      <c r="CI1" s="23"/>
-      <c r="CJ1" s="23"/>
-      <c r="CK1" s="23"/>
-      <c r="CL1" s="23"/>
-      <c r="CM1" s="23"/>
-      <c r="CN1" s="23"/>
-      <c r="CO1" s="23"/>
-      <c r="CP1" s="23"/>
-      <c r="CQ1" s="23"/>
-      <c r="CR1" s="23"/>
-      <c r="CS1" s="23"/>
-      <c r="CT1" s="23"/>
-      <c r="CU1" s="23"/>
-      <c r="CV1" s="23"/>
-      <c r="CW1" s="23"/>
-      <c r="CX1" s="23"/>
-      <c r="CY1" s="23"/>
-      <c r="CZ1" s="23"/>
-      <c r="DA1" s="23"/>
-      <c r="DB1" s="23"/>
-      <c r="DC1" s="23"/>
-      <c r="DD1" s="23"/>
-      <c r="DE1" s="23"/>
-      <c r="DF1" s="23"/>
-      <c r="DG1" s="23"/>
-      <c r="DH1" s="23"/>
-      <c r="DI1" s="24"/>
-      <c r="DJ1" s="24"/>
-      <c r="DK1" s="24"/>
-      <c r="DL1" s="24"/>
-      <c r="DM1" s="24"/>
-      <c r="DN1" s="24"/>
-      <c r="DO1" s="24"/>
-      <c r="DP1" s="24"/>
-      <c r="DQ1" s="24"/>
-      <c r="DR1" s="24"/>
-      <c r="DS1" s="24"/>
-      <c r="DT1" s="24"/>
+      <c r="AE1" s="25"/>
+      <c r="AF1" s="25"/>
+      <c r="AG1" s="26"/>
+      <c r="AH1" s="24">
+        <v>4</v>
+      </c>
+      <c r="AI1" s="25"/>
+      <c r="AJ1" s="25"/>
+      <c r="AK1" s="26"/>
+      <c r="AL1" s="22"/>
+      <c r="AM1" s="22"/>
+      <c r="AN1" s="22"/>
+      <c r="AO1" s="22"/>
+      <c r="AP1" s="22"/>
+      <c r="AQ1" s="22"/>
+      <c r="AR1" s="22"/>
+      <c r="AS1" s="22"/>
+      <c r="AT1" s="22"/>
+      <c r="AU1" s="22"/>
+      <c r="AV1" s="22"/>
+      <c r="AW1" s="22"/>
+      <c r="AX1" s="22"/>
+      <c r="AY1" s="22"/>
+      <c r="AZ1" s="22"/>
+      <c r="BA1" s="22"/>
+      <c r="BB1" s="22"/>
+      <c r="BC1" s="22"/>
+      <c r="BD1" s="22"/>
+      <c r="BE1" s="22"/>
+      <c r="BF1" s="22"/>
+      <c r="BG1" s="22"/>
+      <c r="BH1" s="22"/>
+      <c r="BI1" s="22"/>
+      <c r="BJ1" s="22"/>
+      <c r="BK1" s="22"/>
+      <c r="BL1" s="22"/>
+      <c r="BM1" s="22"/>
+      <c r="BN1" s="22"/>
+      <c r="BO1" s="22"/>
+      <c r="BP1" s="22"/>
+      <c r="BQ1" s="22"/>
+      <c r="BR1" s="22"/>
+      <c r="BS1" s="22"/>
+      <c r="BT1" s="22"/>
+      <c r="BU1" s="22"/>
+      <c r="BV1" s="22"/>
+      <c r="BW1" s="22"/>
+      <c r="BX1" s="22"/>
+      <c r="BY1" s="22"/>
+      <c r="BZ1" s="22"/>
+      <c r="CA1" s="22"/>
+      <c r="CB1" s="22"/>
+      <c r="CC1" s="22"/>
+      <c r="CD1" s="22"/>
+      <c r="CE1" s="22"/>
+      <c r="CF1" s="22"/>
+      <c r="CG1" s="22"/>
+      <c r="CH1" s="22"/>
+      <c r="CI1" s="22"/>
+      <c r="CJ1" s="22"/>
+      <c r="CK1" s="22"/>
+      <c r="CL1" s="22"/>
+      <c r="CM1" s="22"/>
+      <c r="CN1" s="22"/>
+      <c r="CO1" s="22"/>
+      <c r="CP1" s="22"/>
+      <c r="CQ1" s="22"/>
+      <c r="CR1" s="22"/>
+      <c r="CS1" s="22"/>
+      <c r="CT1" s="22"/>
+      <c r="CU1" s="22"/>
+      <c r="CV1" s="22"/>
+      <c r="CW1" s="22"/>
+      <c r="CX1" s="22"/>
+      <c r="CY1" s="22"/>
+      <c r="CZ1" s="22"/>
+      <c r="DA1" s="22"/>
+      <c r="DB1" s="22"/>
+      <c r="DC1" s="22"/>
+      <c r="DD1" s="22"/>
+      <c r="DE1" s="22"/>
+      <c r="DF1" s="22"/>
+      <c r="DG1" s="22"/>
+      <c r="DH1" s="22"/>
+      <c r="DI1" s="23"/>
+      <c r="DJ1" s="23"/>
+      <c r="DK1" s="23"/>
+      <c r="DL1" s="23"/>
+      <c r="DM1" s="23"/>
+      <c r="DN1" s="23"/>
+      <c r="DO1" s="23"/>
+      <c r="DP1" s="23"/>
+      <c r="DQ1" s="23"/>
+      <c r="DR1" s="23"/>
+      <c r="DS1" s="23"/>
+      <c r="DT1" s="23"/>
       <c r="DU1" s="1">
         <f>SUM(F1:DT1)</f>
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:125" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="42"/>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="45" t="s">
+      <c r="A2" s="41"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="28">
+      <c r="F2" s="29">
         <v>46276</v>
       </c>
-      <c r="G2" s="28">
+      <c r="G2" s="29">
         <v>46276</v>
       </c>
-      <c r="H2" s="28">
+      <c r="H2" s="29">
         <v>46276</v>
       </c>
-      <c r="I2" s="28">
+      <c r="I2" s="29">
         <v>46276</v>
       </c>
-      <c r="J2" s="28">
+      <c r="J2" s="29">
         <v>46283</v>
       </c>
-      <c r="K2" s="28">
+      <c r="K2" s="29">
         <v>46283</v>
       </c>
-      <c r="L2" s="28">
+      <c r="L2" s="29">
         <v>46283</v>
       </c>
-      <c r="M2" s="28">
+      <c r="M2" s="29">
         <v>46283</v>
       </c>
-      <c r="N2" s="28">
+      <c r="N2" s="29">
         <v>46290</v>
       </c>
-      <c r="O2" s="28">
+      <c r="O2" s="29">
         <v>46290</v>
       </c>
-      <c r="P2" s="28">
+      <c r="P2" s="68">
         <v>46290</v>
       </c>
-      <c r="Q2" s="28">
+      <c r="Q2" s="68">
         <v>46290</v>
       </c>
-      <c r="R2" s="28">
+      <c r="R2" s="29">
         <v>46297</v>
       </c>
-      <c r="S2" s="28">
+      <c r="S2" s="29">
         <v>46297</v>
       </c>
-      <c r="T2" s="28">
+      <c r="T2" s="29">
         <v>46297</v>
       </c>
-      <c r="U2" s="28">
+      <c r="U2" s="29">
         <v>46297</v>
       </c>
-      <c r="V2" s="30">
+      <c r="V2" s="54">
         <v>46304</v>
       </c>
-      <c r="W2" s="30">
+      <c r="W2" s="54">
         <v>46304</v>
       </c>
-      <c r="X2" s="28">
+      <c r="X2" s="29">
         <v>46304</v>
       </c>
-      <c r="Y2" s="28">
+      <c r="Y2" s="29">
         <v>46304</v>
       </c>
-      <c r="Z2" s="37">
+      <c r="Z2" s="52">
         <v>46311</v>
       </c>
-      <c r="AA2" s="37">
+      <c r="AA2" s="52">
         <v>46311</v>
       </c>
-      <c r="AB2" s="37">
+      <c r="AB2" s="52">
         <v>46311</v>
       </c>
-      <c r="AC2" s="37">
+      <c r="AC2" s="52">
         <v>46311</v>
       </c>
-      <c r="AD2" s="28">
+      <c r="AD2" s="29">
         <v>46318</v>
       </c>
-      <c r="AE2" s="28">
+      <c r="AE2" s="29">
         <v>46318</v>
       </c>
-      <c r="AF2" s="28">
+      <c r="AF2" s="29">
         <v>46318</v>
       </c>
-      <c r="AG2" s="28">
+      <c r="AG2" s="29">
         <v>46318</v>
       </c>
-      <c r="AH2" s="28"/>
-      <c r="AI2" s="28"/>
-      <c r="AJ2" s="28"/>
-      <c r="AK2" s="28"/>
-      <c r="AL2" s="28"/>
-      <c r="AM2" s="28"/>
-      <c r="AN2" s="28"/>
-      <c r="AO2" s="28"/>
-      <c r="AP2" s="28"/>
-      <c r="AQ2" s="28"/>
-      <c r="AR2" s="28"/>
-      <c r="AS2" s="28"/>
-      <c r="AT2" s="28"/>
-      <c r="AU2" s="28"/>
-      <c r="AV2" s="28"/>
-      <c r="AW2" s="28"/>
-      <c r="AX2" s="28"/>
-      <c r="AY2" s="28"/>
-      <c r="AZ2" s="28"/>
-      <c r="BA2" s="28"/>
-      <c r="BB2" s="28"/>
-      <c r="BC2" s="28"/>
-      <c r="BD2" s="28"/>
-      <c r="BE2" s="28"/>
-      <c r="BF2" s="28"/>
-      <c r="BG2" s="28"/>
-      <c r="BH2" s="28"/>
-      <c r="BI2" s="28"/>
-      <c r="BJ2" s="28"/>
-      <c r="BK2" s="28"/>
-      <c r="BL2" s="28"/>
-      <c r="BM2" s="28"/>
-      <c r="BN2" s="28"/>
-      <c r="BO2" s="28"/>
-      <c r="BP2" s="28"/>
-      <c r="BQ2" s="28"/>
-      <c r="BR2" s="28"/>
-      <c r="BS2" s="28"/>
-      <c r="BT2" s="28"/>
-      <c r="BU2" s="28"/>
-      <c r="BV2" s="28"/>
-      <c r="BW2" s="28"/>
-      <c r="BX2" s="28"/>
-      <c r="BY2" s="28"/>
-      <c r="BZ2" s="28"/>
-      <c r="CA2" s="28"/>
-      <c r="CB2" s="28"/>
-      <c r="CC2" s="28"/>
-      <c r="CD2" s="28"/>
-      <c r="CE2" s="28"/>
-      <c r="CF2" s="28"/>
-      <c r="CG2" s="28"/>
-      <c r="CH2" s="28"/>
-      <c r="CI2" s="28"/>
-      <c r="CJ2" s="28"/>
-      <c r="CK2" s="28"/>
-      <c r="CL2" s="28"/>
-      <c r="CM2" s="28"/>
-      <c r="CN2" s="28"/>
-      <c r="CO2" s="28"/>
-      <c r="CP2" s="28"/>
-      <c r="CQ2" s="28"/>
-      <c r="CR2" s="28"/>
-      <c r="CS2" s="28"/>
-      <c r="CT2" s="28"/>
-      <c r="CU2" s="28"/>
-      <c r="CV2" s="28"/>
-      <c r="CW2" s="28"/>
-      <c r="CX2" s="28"/>
-      <c r="CY2" s="28"/>
-      <c r="CZ2" s="28"/>
-      <c r="DA2" s="28"/>
-      <c r="DB2" s="28"/>
-      <c r="DC2" s="28"/>
-      <c r="DD2" s="28"/>
-      <c r="DE2" s="28"/>
-      <c r="DF2" s="28"/>
-      <c r="DG2" s="28"/>
-      <c r="DH2" s="28"/>
-      <c r="DI2" s="28"/>
-      <c r="DJ2" s="28"/>
-      <c r="DK2" s="28"/>
-      <c r="DL2" s="28"/>
-      <c r="DM2" s="28"/>
-      <c r="DN2" s="28"/>
-      <c r="DO2" s="28"/>
-      <c r="DP2" s="28"/>
-      <c r="DQ2" s="28"/>
-      <c r="DR2" s="28"/>
-      <c r="DS2" s="28"/>
-      <c r="DT2" s="28"/>
+      <c r="AH2" s="68">
+        <v>46325</v>
+      </c>
+      <c r="AI2" s="68">
+        <v>46325</v>
+      </c>
+      <c r="AJ2" s="68">
+        <v>46325</v>
+      </c>
+      <c r="AK2" s="68">
+        <v>46325</v>
+      </c>
+      <c r="AL2" s="29"/>
+      <c r="AM2" s="29"/>
+      <c r="AN2" s="29"/>
+      <c r="AO2" s="29"/>
+      <c r="AP2" s="29"/>
+      <c r="AQ2" s="29"/>
+      <c r="AR2" s="29"/>
+      <c r="AS2" s="29"/>
+      <c r="AT2" s="29"/>
+      <c r="AU2" s="29"/>
+      <c r="AV2" s="29"/>
+      <c r="AW2" s="29"/>
+      <c r="AX2" s="29"/>
+      <c r="AY2" s="29"/>
+      <c r="AZ2" s="29"/>
+      <c r="BA2" s="29"/>
+      <c r="BB2" s="29"/>
+      <c r="BC2" s="29"/>
+      <c r="BD2" s="29"/>
+      <c r="BE2" s="29"/>
+      <c r="BF2" s="29"/>
+      <c r="BG2" s="29"/>
+      <c r="BH2" s="29"/>
+      <c r="BI2" s="29"/>
+      <c r="BJ2" s="29"/>
+      <c r="BK2" s="29"/>
+      <c r="BL2" s="29"/>
+      <c r="BM2" s="29"/>
+      <c r="BN2" s="29"/>
+      <c r="BO2" s="29"/>
+      <c r="BP2" s="29"/>
+      <c r="BQ2" s="29"/>
+      <c r="BR2" s="29"/>
+      <c r="BS2" s="29"/>
+      <c r="BT2" s="29"/>
+      <c r="BU2" s="29"/>
+      <c r="BV2" s="29"/>
+      <c r="BW2" s="29"/>
+      <c r="BX2" s="29"/>
+      <c r="BY2" s="29"/>
+      <c r="BZ2" s="29"/>
+      <c r="CA2" s="29"/>
+      <c r="CB2" s="29"/>
+      <c r="CC2" s="29"/>
+      <c r="CD2" s="29"/>
+      <c r="CE2" s="29"/>
+      <c r="CF2" s="29"/>
+      <c r="CG2" s="29"/>
+      <c r="CH2" s="29"/>
+      <c r="CI2" s="29"/>
+      <c r="CJ2" s="29"/>
+      <c r="CK2" s="29"/>
+      <c r="CL2" s="29"/>
+      <c r="CM2" s="29"/>
+      <c r="CN2" s="29"/>
+      <c r="CO2" s="29"/>
+      <c r="CP2" s="29"/>
+      <c r="CQ2" s="29"/>
+      <c r="CR2" s="29"/>
+      <c r="CS2" s="29"/>
+      <c r="CT2" s="29"/>
+      <c r="CU2" s="29"/>
+      <c r="CV2" s="29"/>
+      <c r="CW2" s="29"/>
+      <c r="CX2" s="29"/>
+      <c r="CY2" s="29"/>
+      <c r="CZ2" s="29"/>
+      <c r="DA2" s="29"/>
+      <c r="DB2" s="29"/>
+      <c r="DC2" s="29"/>
+      <c r="DD2" s="29"/>
+      <c r="DE2" s="29"/>
+      <c r="DF2" s="29"/>
+      <c r="DG2" s="29"/>
+      <c r="DH2" s="29"/>
+      <c r="DI2" s="29"/>
+      <c r="DJ2" s="29"/>
+      <c r="DK2" s="29"/>
+      <c r="DL2" s="29"/>
+      <c r="DM2" s="29"/>
+      <c r="DN2" s="29"/>
+      <c r="DO2" s="29"/>
+      <c r="DP2" s="29"/>
+      <c r="DQ2" s="29"/>
+      <c r="DR2" s="29"/>
+      <c r="DS2" s="29"/>
+      <c r="DT2" s="29"/>
     </row>
     <row r="3" spans="1:125" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="48" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="28"/>
-      <c r="O3" s="28"/>
-      <c r="P3" s="28"/>
-      <c r="Q3" s="28"/>
-      <c r="R3" s="28"/>
-      <c r="S3" s="28"/>
-      <c r="T3" s="28"/>
-      <c r="U3" s="28"/>
-      <c r="V3" s="30"/>
-      <c r="W3" s="30"/>
-      <c r="X3" s="28"/>
-      <c r="Y3" s="28"/>
-      <c r="Z3" s="37"/>
-      <c r="AA3" s="37"/>
-      <c r="AB3" s="37"/>
-      <c r="AC3" s="37"/>
-      <c r="AD3" s="28"/>
-      <c r="AE3" s="28"/>
-      <c r="AF3" s="28"/>
-      <c r="AG3" s="28"/>
-      <c r="AH3" s="28"/>
-      <c r="AI3" s="28"/>
-      <c r="AJ3" s="28"/>
-      <c r="AK3" s="28"/>
-      <c r="AL3" s="28"/>
-      <c r="AM3" s="28"/>
-      <c r="AN3" s="28"/>
-      <c r="AO3" s="28"/>
-      <c r="AP3" s="28"/>
-      <c r="AQ3" s="28"/>
-      <c r="AR3" s="28"/>
-      <c r="AS3" s="28"/>
-      <c r="AT3" s="28"/>
-      <c r="AU3" s="28"/>
-      <c r="AV3" s="28"/>
-      <c r="AW3" s="28"/>
-      <c r="AX3" s="28"/>
-      <c r="AY3" s="28"/>
-      <c r="AZ3" s="28"/>
-      <c r="BA3" s="28"/>
-      <c r="BB3" s="28"/>
-      <c r="BC3" s="28"/>
-      <c r="BD3" s="28"/>
-      <c r="BE3" s="28"/>
-      <c r="BF3" s="28"/>
-      <c r="BG3" s="28"/>
-      <c r="BH3" s="28"/>
-      <c r="BI3" s="28"/>
-      <c r="BJ3" s="28"/>
-      <c r="BK3" s="28"/>
-      <c r="BL3" s="28"/>
-      <c r="BM3" s="28"/>
-      <c r="BN3" s="28"/>
-      <c r="BO3" s="28"/>
-      <c r="BP3" s="28"/>
-      <c r="BQ3" s="28"/>
-      <c r="BR3" s="28"/>
-      <c r="BS3" s="28"/>
-      <c r="BT3" s="28"/>
-      <c r="BU3" s="28"/>
-      <c r="BV3" s="28"/>
-      <c r="BW3" s="28"/>
-      <c r="BX3" s="28"/>
-      <c r="BY3" s="28"/>
-      <c r="BZ3" s="28"/>
-      <c r="CA3" s="28"/>
-      <c r="CB3" s="28"/>
-      <c r="CC3" s="28"/>
-      <c r="CD3" s="28"/>
-      <c r="CE3" s="28"/>
-      <c r="CF3" s="28"/>
-      <c r="CG3" s="28"/>
-      <c r="CH3" s="28"/>
-      <c r="CI3" s="28"/>
-      <c r="CJ3" s="28"/>
-      <c r="CK3" s="28"/>
-      <c r="CL3" s="28"/>
-      <c r="CM3" s="28"/>
-      <c r="CN3" s="28"/>
-      <c r="CO3" s="28"/>
-      <c r="CP3" s="28"/>
-      <c r="CQ3" s="28"/>
-      <c r="CR3" s="28"/>
-      <c r="CS3" s="28"/>
-      <c r="CT3" s="28"/>
-      <c r="CU3" s="28"/>
-      <c r="CV3" s="28"/>
-      <c r="CW3" s="28"/>
-      <c r="CX3" s="28"/>
-      <c r="CY3" s="28"/>
-      <c r="CZ3" s="28"/>
-      <c r="DA3" s="28"/>
-      <c r="DB3" s="28"/>
-      <c r="DC3" s="28"/>
-      <c r="DD3" s="28"/>
-      <c r="DE3" s="28"/>
-      <c r="DF3" s="28"/>
-      <c r="DG3" s="28"/>
-      <c r="DH3" s="28"/>
-      <c r="DI3" s="28"/>
-      <c r="DJ3" s="28"/>
-      <c r="DK3" s="28"/>
-      <c r="DL3" s="28"/>
-      <c r="DM3" s="28"/>
-      <c r="DN3" s="28"/>
-      <c r="DO3" s="28"/>
-      <c r="DP3" s="28"/>
-      <c r="DQ3" s="28"/>
-      <c r="DR3" s="28"/>
-      <c r="DS3" s="28"/>
-      <c r="DT3" s="28"/>
+      <c r="A3" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="29"/>
+      <c r="P3" s="68"/>
+      <c r="Q3" s="68"/>
+      <c r="R3" s="29"/>
+      <c r="S3" s="29"/>
+      <c r="T3" s="29"/>
+      <c r="U3" s="29"/>
+      <c r="V3" s="54"/>
+      <c r="W3" s="54"/>
+      <c r="X3" s="29"/>
+      <c r="Y3" s="29"/>
+      <c r="Z3" s="52"/>
+      <c r="AA3" s="52"/>
+      <c r="AB3" s="52"/>
+      <c r="AC3" s="52"/>
+      <c r="AD3" s="29"/>
+      <c r="AE3" s="29"/>
+      <c r="AF3" s="29"/>
+      <c r="AG3" s="29"/>
+      <c r="AH3" s="68"/>
+      <c r="AI3" s="68"/>
+      <c r="AJ3" s="68"/>
+      <c r="AK3" s="68"/>
+      <c r="AL3" s="29"/>
+      <c r="AM3" s="29"/>
+      <c r="AN3" s="29"/>
+      <c r="AO3" s="29"/>
+      <c r="AP3" s="29"/>
+      <c r="AQ3" s="29"/>
+      <c r="AR3" s="29"/>
+      <c r="AS3" s="29"/>
+      <c r="AT3" s="29"/>
+      <c r="AU3" s="29"/>
+      <c r="AV3" s="29"/>
+      <c r="AW3" s="29"/>
+      <c r="AX3" s="29"/>
+      <c r="AY3" s="29"/>
+      <c r="AZ3" s="29"/>
+      <c r="BA3" s="29"/>
+      <c r="BB3" s="29"/>
+      <c r="BC3" s="29"/>
+      <c r="BD3" s="29"/>
+      <c r="BE3" s="29"/>
+      <c r="BF3" s="29"/>
+      <c r="BG3" s="29"/>
+      <c r="BH3" s="29"/>
+      <c r="BI3" s="29"/>
+      <c r="BJ3" s="29"/>
+      <c r="BK3" s="29"/>
+      <c r="BL3" s="29"/>
+      <c r="BM3" s="29"/>
+      <c r="BN3" s="29"/>
+      <c r="BO3" s="29"/>
+      <c r="BP3" s="29"/>
+      <c r="BQ3" s="29"/>
+      <c r="BR3" s="29"/>
+      <c r="BS3" s="29"/>
+      <c r="BT3" s="29"/>
+      <c r="BU3" s="29"/>
+      <c r="BV3" s="29"/>
+      <c r="BW3" s="29"/>
+      <c r="BX3" s="29"/>
+      <c r="BY3" s="29"/>
+      <c r="BZ3" s="29"/>
+      <c r="CA3" s="29"/>
+      <c r="CB3" s="29"/>
+      <c r="CC3" s="29"/>
+      <c r="CD3" s="29"/>
+      <c r="CE3" s="29"/>
+      <c r="CF3" s="29"/>
+      <c r="CG3" s="29"/>
+      <c r="CH3" s="29"/>
+      <c r="CI3" s="29"/>
+      <c r="CJ3" s="29"/>
+      <c r="CK3" s="29"/>
+      <c r="CL3" s="29"/>
+      <c r="CM3" s="29"/>
+      <c r="CN3" s="29"/>
+      <c r="CO3" s="29"/>
+      <c r="CP3" s="29"/>
+      <c r="CQ3" s="29"/>
+      <c r="CR3" s="29"/>
+      <c r="CS3" s="29"/>
+      <c r="CT3" s="29"/>
+      <c r="CU3" s="29"/>
+      <c r="CV3" s="29"/>
+      <c r="CW3" s="29"/>
+      <c r="CX3" s="29"/>
+      <c r="CY3" s="29"/>
+      <c r="CZ3" s="29"/>
+      <c r="DA3" s="29"/>
+      <c r="DB3" s="29"/>
+      <c r="DC3" s="29"/>
+      <c r="DD3" s="29"/>
+      <c r="DE3" s="29"/>
+      <c r="DF3" s="29"/>
+      <c r="DG3" s="29"/>
+      <c r="DH3" s="29"/>
+      <c r="DI3" s="29"/>
+      <c r="DJ3" s="29"/>
+      <c r="DK3" s="29"/>
+      <c r="DL3" s="29"/>
+      <c r="DM3" s="29"/>
+      <c r="DN3" s="29"/>
+      <c r="DO3" s="29"/>
+      <c r="DP3" s="29"/>
+      <c r="DQ3" s="29"/>
+      <c r="DR3" s="29"/>
+      <c r="DS3" s="29"/>
+      <c r="DT3" s="29"/>
     </row>
     <row r="4" spans="1:125" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="49"/>
-      <c r="C4" s="50" t="s">
+      <c r="A4" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="47"/>
+      <c r="C4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="51"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="28"/>
-      <c r="M4" s="28"/>
-      <c r="N4" s="28"/>
-      <c r="O4" s="28"/>
-      <c r="P4" s="28"/>
-      <c r="Q4" s="28"/>
-      <c r="R4" s="28"/>
-      <c r="S4" s="28"/>
-      <c r="T4" s="28"/>
-      <c r="U4" s="28"/>
-      <c r="V4" s="30"/>
-      <c r="W4" s="30"/>
-      <c r="X4" s="28"/>
-      <c r="Y4" s="28"/>
-      <c r="Z4" s="37"/>
-      <c r="AA4" s="37"/>
-      <c r="AB4" s="37"/>
-      <c r="AC4" s="37"/>
-      <c r="AD4" s="28"/>
-      <c r="AE4" s="28"/>
-      <c r="AF4" s="28"/>
-      <c r="AG4" s="28"/>
-      <c r="AH4" s="28"/>
-      <c r="AI4" s="28"/>
-      <c r="AJ4" s="28"/>
-      <c r="AK4" s="28"/>
-      <c r="AL4" s="28"/>
-      <c r="AM4" s="28"/>
-      <c r="AN4" s="28"/>
-      <c r="AO4" s="28"/>
-      <c r="AP4" s="28"/>
-      <c r="AQ4" s="28"/>
-      <c r="AR4" s="28"/>
-      <c r="AS4" s="28"/>
-      <c r="AT4" s="28"/>
-      <c r="AU4" s="28"/>
-      <c r="AV4" s="28"/>
-      <c r="AW4" s="28"/>
-      <c r="AX4" s="28"/>
-      <c r="AY4" s="28"/>
-      <c r="AZ4" s="28"/>
-      <c r="BA4" s="28"/>
-      <c r="BB4" s="28"/>
-      <c r="BC4" s="28"/>
-      <c r="BD4" s="28"/>
-      <c r="BE4" s="28"/>
-      <c r="BF4" s="28"/>
-      <c r="BG4" s="28"/>
-      <c r="BH4" s="28"/>
-      <c r="BI4" s="28"/>
-      <c r="BJ4" s="28"/>
-      <c r="BK4" s="28"/>
-      <c r="BL4" s="28"/>
-      <c r="BM4" s="28"/>
-      <c r="BN4" s="28"/>
-      <c r="BO4" s="28"/>
-      <c r="BP4" s="28"/>
-      <c r="BQ4" s="28"/>
-      <c r="BR4" s="28"/>
-      <c r="BS4" s="28"/>
-      <c r="BT4" s="28"/>
-      <c r="BU4" s="28"/>
-      <c r="BV4" s="28"/>
-      <c r="BW4" s="28"/>
-      <c r="BX4" s="28"/>
-      <c r="BY4" s="28"/>
-      <c r="BZ4" s="28"/>
-      <c r="CA4" s="28"/>
-      <c r="CB4" s="28"/>
-      <c r="CC4" s="28"/>
-      <c r="CD4" s="28"/>
-      <c r="CE4" s="28"/>
-      <c r="CF4" s="28"/>
-      <c r="CG4" s="28"/>
-      <c r="CH4" s="28"/>
-      <c r="CI4" s="28"/>
-      <c r="CJ4" s="28"/>
-      <c r="CK4" s="28"/>
-      <c r="CL4" s="28"/>
-      <c r="CM4" s="28"/>
-      <c r="CN4" s="28"/>
-      <c r="CO4" s="28"/>
-      <c r="CP4" s="28"/>
-      <c r="CQ4" s="28"/>
-      <c r="CR4" s="28"/>
-      <c r="CS4" s="28"/>
-      <c r="CT4" s="28"/>
-      <c r="CU4" s="28"/>
-      <c r="CV4" s="28"/>
-      <c r="CW4" s="28"/>
-      <c r="CX4" s="28"/>
-      <c r="CY4" s="28"/>
-      <c r="CZ4" s="28"/>
-      <c r="DA4" s="28"/>
-      <c r="DB4" s="28"/>
-      <c r="DC4" s="28"/>
-      <c r="DD4" s="28"/>
-      <c r="DE4" s="28"/>
-      <c r="DF4" s="28"/>
-      <c r="DG4" s="28"/>
-      <c r="DH4" s="28"/>
-      <c r="DI4" s="28"/>
-      <c r="DJ4" s="28"/>
-      <c r="DK4" s="28"/>
-      <c r="DL4" s="28"/>
-      <c r="DM4" s="28"/>
-      <c r="DN4" s="28"/>
-      <c r="DO4" s="28"/>
-      <c r="DP4" s="28"/>
-      <c r="DQ4" s="28"/>
-      <c r="DR4" s="28"/>
-      <c r="DS4" s="28"/>
-      <c r="DT4" s="28"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="29"/>
+      <c r="N4" s="29"/>
+      <c r="O4" s="29"/>
+      <c r="P4" s="68"/>
+      <c r="Q4" s="68"/>
+      <c r="R4" s="29"/>
+      <c r="S4" s="29"/>
+      <c r="T4" s="29"/>
+      <c r="U4" s="29"/>
+      <c r="V4" s="54"/>
+      <c r="W4" s="54"/>
+      <c r="X4" s="29"/>
+      <c r="Y4" s="29"/>
+      <c r="Z4" s="52"/>
+      <c r="AA4" s="52"/>
+      <c r="AB4" s="52"/>
+      <c r="AC4" s="52"/>
+      <c r="AD4" s="29"/>
+      <c r="AE4" s="29"/>
+      <c r="AF4" s="29"/>
+      <c r="AG4" s="29"/>
+      <c r="AH4" s="68"/>
+      <c r="AI4" s="68"/>
+      <c r="AJ4" s="68"/>
+      <c r="AK4" s="68"/>
+      <c r="AL4" s="29"/>
+      <c r="AM4" s="29"/>
+      <c r="AN4" s="29"/>
+      <c r="AO4" s="29"/>
+      <c r="AP4" s="29"/>
+      <c r="AQ4" s="29"/>
+      <c r="AR4" s="29"/>
+      <c r="AS4" s="29"/>
+      <c r="AT4" s="29"/>
+      <c r="AU4" s="29"/>
+      <c r="AV4" s="29"/>
+      <c r="AW4" s="29"/>
+      <c r="AX4" s="29"/>
+      <c r="AY4" s="29"/>
+      <c r="AZ4" s="29"/>
+      <c r="BA4" s="29"/>
+      <c r="BB4" s="29"/>
+      <c r="BC4" s="29"/>
+      <c r="BD4" s="29"/>
+      <c r="BE4" s="29"/>
+      <c r="BF4" s="29"/>
+      <c r="BG4" s="29"/>
+      <c r="BH4" s="29"/>
+      <c r="BI4" s="29"/>
+      <c r="BJ4" s="29"/>
+      <c r="BK4" s="29"/>
+      <c r="BL4" s="29"/>
+      <c r="BM4" s="29"/>
+      <c r="BN4" s="29"/>
+      <c r="BO4" s="29"/>
+      <c r="BP4" s="29"/>
+      <c r="BQ4" s="29"/>
+      <c r="BR4" s="29"/>
+      <c r="BS4" s="29"/>
+      <c r="BT4" s="29"/>
+      <c r="BU4" s="29"/>
+      <c r="BV4" s="29"/>
+      <c r="BW4" s="29"/>
+      <c r="BX4" s="29"/>
+      <c r="BY4" s="29"/>
+      <c r="BZ4" s="29"/>
+      <c r="CA4" s="29"/>
+      <c r="CB4" s="29"/>
+      <c r="CC4" s="29"/>
+      <c r="CD4" s="29"/>
+      <c r="CE4" s="29"/>
+      <c r="CF4" s="29"/>
+      <c r="CG4" s="29"/>
+      <c r="CH4" s="29"/>
+      <c r="CI4" s="29"/>
+      <c r="CJ4" s="29"/>
+      <c r="CK4" s="29"/>
+      <c r="CL4" s="29"/>
+      <c r="CM4" s="29"/>
+      <c r="CN4" s="29"/>
+      <c r="CO4" s="29"/>
+      <c r="CP4" s="29"/>
+      <c r="CQ4" s="29"/>
+      <c r="CR4" s="29"/>
+      <c r="CS4" s="29"/>
+      <c r="CT4" s="29"/>
+      <c r="CU4" s="29"/>
+      <c r="CV4" s="29"/>
+      <c r="CW4" s="29"/>
+      <c r="CX4" s="29"/>
+      <c r="CY4" s="29"/>
+      <c r="CZ4" s="29"/>
+      <c r="DA4" s="29"/>
+      <c r="DB4" s="29"/>
+      <c r="DC4" s="29"/>
+      <c r="DD4" s="29"/>
+      <c r="DE4" s="29"/>
+      <c r="DF4" s="29"/>
+      <c r="DG4" s="29"/>
+      <c r="DH4" s="29"/>
+      <c r="DI4" s="29"/>
+      <c r="DJ4" s="29"/>
+      <c r="DK4" s="29"/>
+      <c r="DL4" s="29"/>
+      <c r="DM4" s="29"/>
+      <c r="DN4" s="29"/>
+      <c r="DO4" s="29"/>
+      <c r="DP4" s="29"/>
+      <c r="DQ4" s="29"/>
+      <c r="DR4" s="29"/>
+      <c r="DS4" s="29"/>
+      <c r="DT4" s="29"/>
     </row>
     <row r="5" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="53">
+      <c r="B5" s="48"/>
+      <c r="C5" s="49">
         <v>60</v>
       </c>
-      <c r="D5" s="54"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
-      <c r="K5" s="28"/>
-      <c r="L5" s="28"/>
-      <c r="M5" s="28"/>
-      <c r="N5" s="28"/>
-      <c r="O5" s="28"/>
-      <c r="P5" s="28"/>
-      <c r="Q5" s="28"/>
-      <c r="R5" s="28"/>
-      <c r="S5" s="28"/>
-      <c r="T5" s="28"/>
-      <c r="U5" s="28"/>
-      <c r="V5" s="30"/>
-      <c r="W5" s="30"/>
-      <c r="X5" s="28"/>
-      <c r="Y5" s="28"/>
-      <c r="Z5" s="37"/>
-      <c r="AA5" s="37"/>
-      <c r="AB5" s="37"/>
-      <c r="AC5" s="37"/>
-      <c r="AD5" s="28"/>
-      <c r="AE5" s="28"/>
-      <c r="AF5" s="28"/>
-      <c r="AG5" s="28"/>
-      <c r="AH5" s="28"/>
-      <c r="AI5" s="28"/>
-      <c r="AJ5" s="28"/>
-      <c r="AK5" s="28"/>
-      <c r="AL5" s="28"/>
-      <c r="AM5" s="28"/>
-      <c r="AN5" s="28"/>
-      <c r="AO5" s="28"/>
-      <c r="AP5" s="28"/>
-      <c r="AQ5" s="28"/>
-      <c r="AR5" s="28"/>
-      <c r="AS5" s="28"/>
-      <c r="AT5" s="28"/>
-      <c r="AU5" s="28"/>
-      <c r="AV5" s="28"/>
-      <c r="AW5" s="28"/>
-      <c r="AX5" s="28"/>
-      <c r="AY5" s="28"/>
-      <c r="AZ5" s="28"/>
-      <c r="BA5" s="28"/>
-      <c r="BB5" s="28"/>
-      <c r="BC5" s="28"/>
-      <c r="BD5" s="28"/>
-      <c r="BE5" s="28"/>
-      <c r="BF5" s="28"/>
-      <c r="BG5" s="28"/>
-      <c r="BH5" s="28"/>
-      <c r="BI5" s="28"/>
-      <c r="BJ5" s="28"/>
-      <c r="BK5" s="28"/>
-      <c r="BL5" s="28"/>
-      <c r="BM5" s="28"/>
-      <c r="BN5" s="28"/>
-      <c r="BO5" s="28"/>
-      <c r="BP5" s="28"/>
-      <c r="BQ5" s="28"/>
-      <c r="BR5" s="28"/>
-      <c r="BS5" s="28"/>
-      <c r="BT5" s="28"/>
-      <c r="BU5" s="28"/>
-      <c r="BV5" s="28"/>
-      <c r="BW5" s="28"/>
-      <c r="BX5" s="28"/>
-      <c r="BY5" s="28"/>
-      <c r="BZ5" s="28"/>
-      <c r="CA5" s="28"/>
-      <c r="CB5" s="28"/>
-      <c r="CC5" s="28"/>
-      <c r="CD5" s="28"/>
-      <c r="CE5" s="28"/>
-      <c r="CF5" s="28"/>
-      <c r="CG5" s="28"/>
-      <c r="CH5" s="28"/>
-      <c r="CI5" s="28"/>
-      <c r="CJ5" s="28"/>
-      <c r="CK5" s="28"/>
-      <c r="CL5" s="28"/>
-      <c r="CM5" s="28"/>
-      <c r="CN5" s="28"/>
-      <c r="CO5" s="28"/>
-      <c r="CP5" s="28"/>
-      <c r="CQ5" s="28"/>
-      <c r="CR5" s="28"/>
-      <c r="CS5" s="28"/>
-      <c r="CT5" s="28"/>
-      <c r="CU5" s="28"/>
-      <c r="CV5" s="28"/>
-      <c r="CW5" s="28"/>
-      <c r="CX5" s="28"/>
-      <c r="CY5" s="28"/>
-      <c r="CZ5" s="28"/>
-      <c r="DA5" s="28"/>
-      <c r="DB5" s="28"/>
-      <c r="DC5" s="28"/>
-      <c r="DD5" s="28"/>
-      <c r="DE5" s="28"/>
-      <c r="DF5" s="28"/>
-      <c r="DG5" s="28"/>
-      <c r="DH5" s="28"/>
-      <c r="DI5" s="28"/>
-      <c r="DJ5" s="28"/>
-      <c r="DK5" s="28"/>
-      <c r="DL5" s="28"/>
-      <c r="DM5" s="28"/>
-      <c r="DN5" s="28"/>
-      <c r="DO5" s="28"/>
-      <c r="DP5" s="28"/>
-      <c r="DQ5" s="28"/>
-      <c r="DR5" s="28"/>
-      <c r="DS5" s="28"/>
-      <c r="DT5" s="28"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="29"/>
+      <c r="N5" s="29"/>
+      <c r="O5" s="29"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="29"/>
+      <c r="S5" s="29"/>
+      <c r="T5" s="29"/>
+      <c r="U5" s="29"/>
+      <c r="V5" s="54"/>
+      <c r="W5" s="54"/>
+      <c r="X5" s="29"/>
+      <c r="Y5" s="29"/>
+      <c r="Z5" s="52"/>
+      <c r="AA5" s="52"/>
+      <c r="AB5" s="52"/>
+      <c r="AC5" s="52"/>
+      <c r="AD5" s="29"/>
+      <c r="AE5" s="29"/>
+      <c r="AF5" s="29"/>
+      <c r="AG5" s="29"/>
+      <c r="AH5" s="68"/>
+      <c r="AI5" s="68"/>
+      <c r="AJ5" s="68"/>
+      <c r="AK5" s="68"/>
+      <c r="AL5" s="29"/>
+      <c r="AM5" s="29"/>
+      <c r="AN5" s="29"/>
+      <c r="AO5" s="29"/>
+      <c r="AP5" s="29"/>
+      <c r="AQ5" s="29"/>
+      <c r="AR5" s="29"/>
+      <c r="AS5" s="29"/>
+      <c r="AT5" s="29"/>
+      <c r="AU5" s="29"/>
+      <c r="AV5" s="29"/>
+      <c r="AW5" s="29"/>
+      <c r="AX5" s="29"/>
+      <c r="AY5" s="29"/>
+      <c r="AZ5" s="29"/>
+      <c r="BA5" s="29"/>
+      <c r="BB5" s="29"/>
+      <c r="BC5" s="29"/>
+      <c r="BD5" s="29"/>
+      <c r="BE5" s="29"/>
+      <c r="BF5" s="29"/>
+      <c r="BG5" s="29"/>
+      <c r="BH5" s="29"/>
+      <c r="BI5" s="29"/>
+      <c r="BJ5" s="29"/>
+      <c r="BK5" s="29"/>
+      <c r="BL5" s="29"/>
+      <c r="BM5" s="29"/>
+      <c r="BN5" s="29"/>
+      <c r="BO5" s="29"/>
+      <c r="BP5" s="29"/>
+      <c r="BQ5" s="29"/>
+      <c r="BR5" s="29"/>
+      <c r="BS5" s="29"/>
+      <c r="BT5" s="29"/>
+      <c r="BU5" s="29"/>
+      <c r="BV5" s="29"/>
+      <c r="BW5" s="29"/>
+      <c r="BX5" s="29"/>
+      <c r="BY5" s="29"/>
+      <c r="BZ5" s="29"/>
+      <c r="CA5" s="29"/>
+      <c r="CB5" s="29"/>
+      <c r="CC5" s="29"/>
+      <c r="CD5" s="29"/>
+      <c r="CE5" s="29"/>
+      <c r="CF5" s="29"/>
+      <c r="CG5" s="29"/>
+      <c r="CH5" s="29"/>
+      <c r="CI5" s="29"/>
+      <c r="CJ5" s="29"/>
+      <c r="CK5" s="29"/>
+      <c r="CL5" s="29"/>
+      <c r="CM5" s="29"/>
+      <c r="CN5" s="29"/>
+      <c r="CO5" s="29"/>
+      <c r="CP5" s="29"/>
+      <c r="CQ5" s="29"/>
+      <c r="CR5" s="29"/>
+      <c r="CS5" s="29"/>
+      <c r="CT5" s="29"/>
+      <c r="CU5" s="29"/>
+      <c r="CV5" s="29"/>
+      <c r="CW5" s="29"/>
+      <c r="CX5" s="29"/>
+      <c r="CY5" s="29"/>
+      <c r="CZ5" s="29"/>
+      <c r="DA5" s="29"/>
+      <c r="DB5" s="29"/>
+      <c r="DC5" s="29"/>
+      <c r="DD5" s="29"/>
+      <c r="DE5" s="29"/>
+      <c r="DF5" s="29"/>
+      <c r="DG5" s="29"/>
+      <c r="DH5" s="29"/>
+      <c r="DI5" s="29"/>
+      <c r="DJ5" s="29"/>
+      <c r="DK5" s="29"/>
+      <c r="DL5" s="29"/>
+      <c r="DM5" s="29"/>
+      <c r="DN5" s="29"/>
+      <c r="DO5" s="29"/>
+      <c r="DP5" s="29"/>
+      <c r="DQ5" s="29"/>
+      <c r="DR5" s="29"/>
+      <c r="DS5" s="29"/>
+      <c r="DT5" s="29"/>
     </row>
     <row r="6" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="52"/>
-      <c r="C6" s="53">
+      <c r="B6" s="48"/>
+      <c r="C6" s="49">
         <v>4</v>
       </c>
-      <c r="D6" s="54"/>
-      <c r="E6" s="46"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="28"/>
-      <c r="K6" s="28"/>
-      <c r="L6" s="28"/>
-      <c r="M6" s="28"/>
-      <c r="N6" s="28"/>
-      <c r="O6" s="28"/>
-      <c r="P6" s="28"/>
-      <c r="Q6" s="28"/>
-      <c r="R6" s="28"/>
-      <c r="S6" s="28"/>
-      <c r="T6" s="28"/>
-      <c r="U6" s="28"/>
-      <c r="V6" s="30"/>
-      <c r="W6" s="30"/>
-      <c r="X6" s="28"/>
-      <c r="Y6" s="28"/>
-      <c r="Z6" s="37"/>
-      <c r="AA6" s="37"/>
-      <c r="AB6" s="37"/>
-      <c r="AC6" s="37"/>
-      <c r="AD6" s="28"/>
-      <c r="AE6" s="28"/>
-      <c r="AF6" s="28"/>
-      <c r="AG6" s="28"/>
-      <c r="AH6" s="28"/>
-      <c r="AI6" s="28"/>
-      <c r="AJ6" s="28"/>
-      <c r="AK6" s="28"/>
-      <c r="AL6" s="28"/>
-      <c r="AM6" s="28"/>
-      <c r="AN6" s="28"/>
-      <c r="AO6" s="28"/>
-      <c r="AP6" s="28"/>
-      <c r="AQ6" s="28"/>
-      <c r="AR6" s="28"/>
-      <c r="AS6" s="28"/>
-      <c r="AT6" s="28"/>
-      <c r="AU6" s="28"/>
-      <c r="AV6" s="28"/>
-      <c r="AW6" s="28"/>
-      <c r="AX6" s="28"/>
-      <c r="AY6" s="28"/>
-      <c r="AZ6" s="28"/>
-      <c r="BA6" s="28"/>
-      <c r="BB6" s="28"/>
-      <c r="BC6" s="28"/>
-      <c r="BD6" s="28"/>
-      <c r="BE6" s="28"/>
-      <c r="BF6" s="28"/>
-      <c r="BG6" s="28"/>
-      <c r="BH6" s="28"/>
-      <c r="BI6" s="28"/>
-      <c r="BJ6" s="28"/>
-      <c r="BK6" s="28"/>
-      <c r="BL6" s="28"/>
-      <c r="BM6" s="28"/>
-      <c r="BN6" s="28"/>
-      <c r="BO6" s="28"/>
-      <c r="BP6" s="28"/>
-      <c r="BQ6" s="28"/>
-      <c r="BR6" s="28"/>
-      <c r="BS6" s="28"/>
-      <c r="BT6" s="28"/>
-      <c r="BU6" s="28"/>
-      <c r="BV6" s="28"/>
-      <c r="BW6" s="28"/>
-      <c r="BX6" s="28"/>
-      <c r="BY6" s="28"/>
-      <c r="BZ6" s="28"/>
-      <c r="CA6" s="28"/>
-      <c r="CB6" s="28"/>
-      <c r="CC6" s="28"/>
-      <c r="CD6" s="28"/>
-      <c r="CE6" s="28"/>
-      <c r="CF6" s="28"/>
-      <c r="CG6" s="28"/>
-      <c r="CH6" s="28"/>
-      <c r="CI6" s="28"/>
-      <c r="CJ6" s="28"/>
-      <c r="CK6" s="28"/>
-      <c r="CL6" s="28"/>
-      <c r="CM6" s="28"/>
-      <c r="CN6" s="28"/>
-      <c r="CO6" s="28"/>
-      <c r="CP6" s="28"/>
-      <c r="CQ6" s="28"/>
-      <c r="CR6" s="28"/>
-      <c r="CS6" s="28"/>
-      <c r="CT6" s="28"/>
-      <c r="CU6" s="28"/>
-      <c r="CV6" s="28"/>
-      <c r="CW6" s="28"/>
-      <c r="CX6" s="28"/>
-      <c r="CY6" s="28"/>
-      <c r="CZ6" s="28"/>
-      <c r="DA6" s="28"/>
-      <c r="DB6" s="28"/>
-      <c r="DC6" s="28"/>
-      <c r="DD6" s="28"/>
-      <c r="DE6" s="28"/>
-      <c r="DF6" s="28"/>
-      <c r="DG6" s="28"/>
-      <c r="DH6" s="28"/>
-      <c r="DI6" s="28"/>
-      <c r="DJ6" s="28"/>
-      <c r="DK6" s="28"/>
-      <c r="DL6" s="28"/>
-      <c r="DM6" s="28"/>
-      <c r="DN6" s="28"/>
-      <c r="DO6" s="28"/>
-      <c r="DP6" s="28"/>
-      <c r="DQ6" s="28"/>
-      <c r="DR6" s="28"/>
-      <c r="DS6" s="28"/>
-      <c r="DT6" s="28"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="29"/>
+      <c r="N6" s="29"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="68"/>
+      <c r="Q6" s="68"/>
+      <c r="R6" s="29"/>
+      <c r="S6" s="29"/>
+      <c r="T6" s="29"/>
+      <c r="U6" s="29"/>
+      <c r="V6" s="54"/>
+      <c r="W6" s="54"/>
+      <c r="X6" s="29"/>
+      <c r="Y6" s="29"/>
+      <c r="Z6" s="52"/>
+      <c r="AA6" s="52"/>
+      <c r="AB6" s="52"/>
+      <c r="AC6" s="52"/>
+      <c r="AD6" s="29"/>
+      <c r="AE6" s="29"/>
+      <c r="AF6" s="29"/>
+      <c r="AG6" s="29"/>
+      <c r="AH6" s="68"/>
+      <c r="AI6" s="68"/>
+      <c r="AJ6" s="68"/>
+      <c r="AK6" s="68"/>
+      <c r="AL6" s="29"/>
+      <c r="AM6" s="29"/>
+      <c r="AN6" s="29"/>
+      <c r="AO6" s="29"/>
+      <c r="AP6" s="29"/>
+      <c r="AQ6" s="29"/>
+      <c r="AR6" s="29"/>
+      <c r="AS6" s="29"/>
+      <c r="AT6" s="29"/>
+      <c r="AU6" s="29"/>
+      <c r="AV6" s="29"/>
+      <c r="AW6" s="29"/>
+      <c r="AX6" s="29"/>
+      <c r="AY6" s="29"/>
+      <c r="AZ6" s="29"/>
+      <c r="BA6" s="29"/>
+      <c r="BB6" s="29"/>
+      <c r="BC6" s="29"/>
+      <c r="BD6" s="29"/>
+      <c r="BE6" s="29"/>
+      <c r="BF6" s="29"/>
+      <c r="BG6" s="29"/>
+      <c r="BH6" s="29"/>
+      <c r="BI6" s="29"/>
+      <c r="BJ6" s="29"/>
+      <c r="BK6" s="29"/>
+      <c r="BL6" s="29"/>
+      <c r="BM6" s="29"/>
+      <c r="BN6" s="29"/>
+      <c r="BO6" s="29"/>
+      <c r="BP6" s="29"/>
+      <c r="BQ6" s="29"/>
+      <c r="BR6" s="29"/>
+      <c r="BS6" s="29"/>
+      <c r="BT6" s="29"/>
+      <c r="BU6" s="29"/>
+      <c r="BV6" s="29"/>
+      <c r="BW6" s="29"/>
+      <c r="BX6" s="29"/>
+      <c r="BY6" s="29"/>
+      <c r="BZ6" s="29"/>
+      <c r="CA6" s="29"/>
+      <c r="CB6" s="29"/>
+      <c r="CC6" s="29"/>
+      <c r="CD6" s="29"/>
+      <c r="CE6" s="29"/>
+      <c r="CF6" s="29"/>
+      <c r="CG6" s="29"/>
+      <c r="CH6" s="29"/>
+      <c r="CI6" s="29"/>
+      <c r="CJ6" s="29"/>
+      <c r="CK6" s="29"/>
+      <c r="CL6" s="29"/>
+      <c r="CM6" s="29"/>
+      <c r="CN6" s="29"/>
+      <c r="CO6" s="29"/>
+      <c r="CP6" s="29"/>
+      <c r="CQ6" s="29"/>
+      <c r="CR6" s="29"/>
+      <c r="CS6" s="29"/>
+      <c r="CT6" s="29"/>
+      <c r="CU6" s="29"/>
+      <c r="CV6" s="29"/>
+      <c r="CW6" s="29"/>
+      <c r="CX6" s="29"/>
+      <c r="CY6" s="29"/>
+      <c r="CZ6" s="29"/>
+      <c r="DA6" s="29"/>
+      <c r="DB6" s="29"/>
+      <c r="DC6" s="29"/>
+      <c r="DD6" s="29"/>
+      <c r="DE6" s="29"/>
+      <c r="DF6" s="29"/>
+      <c r="DG6" s="29"/>
+      <c r="DH6" s="29"/>
+      <c r="DI6" s="29"/>
+      <c r="DJ6" s="29"/>
+      <c r="DK6" s="29"/>
+      <c r="DL6" s="29"/>
+      <c r="DM6" s="29"/>
+      <c r="DN6" s="29"/>
+      <c r="DO6" s="29"/>
+      <c r="DP6" s="29"/>
+      <c r="DQ6" s="29"/>
+      <c r="DR6" s="29"/>
+      <c r="DS6" s="29"/>
+      <c r="DT6" s="29"/>
     </row>
     <row r="7" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="55" t="s">
+      <c r="A7" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="55"/>
-      <c r="C7" s="53">
+      <c r="B7" s="51"/>
+      <c r="C7" s="49">
         <v>11</v>
       </c>
-      <c r="D7" s="54"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="29"/>
-      <c r="J7" s="29"/>
-      <c r="K7" s="29"/>
-      <c r="L7" s="29"/>
-      <c r="M7" s="29"/>
-      <c r="N7" s="29"/>
-      <c r="O7" s="29"/>
-      <c r="P7" s="29"/>
-      <c r="Q7" s="29"/>
-      <c r="R7" s="29"/>
-      <c r="S7" s="29"/>
-      <c r="T7" s="29"/>
-      <c r="U7" s="29"/>
-      <c r="V7" s="31"/>
-      <c r="W7" s="31"/>
-      <c r="X7" s="29"/>
-      <c r="Y7" s="29"/>
-      <c r="Z7" s="38"/>
-      <c r="AA7" s="38"/>
-      <c r="AB7" s="38"/>
-      <c r="AC7" s="38"/>
-      <c r="AD7" s="29"/>
-      <c r="AE7" s="29"/>
-      <c r="AF7" s="29"/>
-      <c r="AG7" s="29"/>
-      <c r="AH7" s="29"/>
-      <c r="AI7" s="29"/>
-      <c r="AJ7" s="29"/>
-      <c r="AK7" s="29"/>
-      <c r="AL7" s="29"/>
-      <c r="AM7" s="29"/>
-      <c r="AN7" s="29"/>
-      <c r="AO7" s="29"/>
-      <c r="AP7" s="29"/>
-      <c r="AQ7" s="29"/>
-      <c r="AR7" s="29"/>
-      <c r="AS7" s="29"/>
-      <c r="AT7" s="29"/>
-      <c r="AU7" s="29"/>
-      <c r="AV7" s="29"/>
-      <c r="AW7" s="29"/>
-      <c r="AX7" s="29"/>
-      <c r="AY7" s="29"/>
-      <c r="AZ7" s="29"/>
-      <c r="BA7" s="29"/>
-      <c r="BB7" s="29"/>
-      <c r="BC7" s="29"/>
-      <c r="BD7" s="29"/>
-      <c r="BE7" s="29"/>
-      <c r="BF7" s="29"/>
-      <c r="BG7" s="29"/>
-      <c r="BH7" s="29"/>
-      <c r="BI7" s="29"/>
-      <c r="BJ7" s="29"/>
-      <c r="BK7" s="29"/>
-      <c r="BL7" s="29"/>
-      <c r="BM7" s="29"/>
-      <c r="BN7" s="29"/>
-      <c r="BO7" s="29"/>
-      <c r="BP7" s="29"/>
-      <c r="BQ7" s="29"/>
-      <c r="BR7" s="29"/>
-      <c r="BS7" s="29"/>
-      <c r="BT7" s="29"/>
-      <c r="BU7" s="29"/>
-      <c r="BV7" s="29"/>
-      <c r="BW7" s="29"/>
-      <c r="BX7" s="29"/>
-      <c r="BY7" s="29"/>
-      <c r="BZ7" s="29"/>
-      <c r="CA7" s="29"/>
-      <c r="CB7" s="29"/>
-      <c r="CC7" s="29"/>
-      <c r="CD7" s="29"/>
-      <c r="CE7" s="29"/>
-      <c r="CF7" s="29"/>
-      <c r="CG7" s="29"/>
-      <c r="CH7" s="29"/>
-      <c r="CI7" s="29"/>
-      <c r="CJ7" s="29"/>
-      <c r="CK7" s="29"/>
-      <c r="CL7" s="29"/>
-      <c r="CM7" s="29"/>
-      <c r="CN7" s="29"/>
-      <c r="CO7" s="29"/>
-      <c r="CP7" s="29"/>
-      <c r="CQ7" s="29"/>
-      <c r="CR7" s="29"/>
-      <c r="CS7" s="29"/>
-      <c r="CT7" s="29"/>
-      <c r="CU7" s="29"/>
-      <c r="CV7" s="29"/>
-      <c r="CW7" s="29"/>
-      <c r="CX7" s="29"/>
-      <c r="CY7" s="29"/>
-      <c r="CZ7" s="29"/>
-      <c r="DA7" s="29"/>
-      <c r="DB7" s="29"/>
-      <c r="DC7" s="29"/>
-      <c r="DD7" s="29"/>
-      <c r="DE7" s="29"/>
-      <c r="DF7" s="29"/>
-      <c r="DG7" s="29"/>
-      <c r="DH7" s="29"/>
-      <c r="DI7" s="29"/>
-      <c r="DJ7" s="29"/>
-      <c r="DK7" s="29"/>
-      <c r="DL7" s="29"/>
-      <c r="DM7" s="29"/>
-      <c r="DN7" s="29"/>
-      <c r="DO7" s="29"/>
-      <c r="DP7" s="29"/>
-      <c r="DQ7" s="29"/>
-      <c r="DR7" s="29"/>
-      <c r="DS7" s="29"/>
-      <c r="DT7" s="29"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="30"/>
+      <c r="O7" s="30"/>
+      <c r="P7" s="69"/>
+      <c r="Q7" s="69"/>
+      <c r="R7" s="30"/>
+      <c r="S7" s="30"/>
+      <c r="T7" s="30"/>
+      <c r="U7" s="30"/>
+      <c r="V7" s="55"/>
+      <c r="W7" s="55"/>
+      <c r="X7" s="30"/>
+      <c r="Y7" s="30"/>
+      <c r="Z7" s="53"/>
+      <c r="AA7" s="53"/>
+      <c r="AB7" s="53"/>
+      <c r="AC7" s="53"/>
+      <c r="AD7" s="30"/>
+      <c r="AE7" s="30"/>
+      <c r="AF7" s="30"/>
+      <c r="AG7" s="30"/>
+      <c r="AH7" s="69"/>
+      <c r="AI7" s="69"/>
+      <c r="AJ7" s="69"/>
+      <c r="AK7" s="69"/>
+      <c r="AL7" s="30"/>
+      <c r="AM7" s="30"/>
+      <c r="AN7" s="30"/>
+      <c r="AO7" s="30"/>
+      <c r="AP7" s="30"/>
+      <c r="AQ7" s="30"/>
+      <c r="AR7" s="30"/>
+      <c r="AS7" s="30"/>
+      <c r="AT7" s="30"/>
+      <c r="AU7" s="30"/>
+      <c r="AV7" s="30"/>
+      <c r="AW7" s="30"/>
+      <c r="AX7" s="30"/>
+      <c r="AY7" s="30"/>
+      <c r="AZ7" s="30"/>
+      <c r="BA7" s="30"/>
+      <c r="BB7" s="30"/>
+      <c r="BC7" s="30"/>
+      <c r="BD7" s="30"/>
+      <c r="BE7" s="30"/>
+      <c r="BF7" s="30"/>
+      <c r="BG7" s="30"/>
+      <c r="BH7" s="30"/>
+      <c r="BI7" s="30"/>
+      <c r="BJ7" s="30"/>
+      <c r="BK7" s="30"/>
+      <c r="BL7" s="30"/>
+      <c r="BM7" s="30"/>
+      <c r="BN7" s="30"/>
+      <c r="BO7" s="30"/>
+      <c r="BP7" s="30"/>
+      <c r="BQ7" s="30"/>
+      <c r="BR7" s="30"/>
+      <c r="BS7" s="30"/>
+      <c r="BT7" s="30"/>
+      <c r="BU7" s="30"/>
+      <c r="BV7" s="30"/>
+      <c r="BW7" s="30"/>
+      <c r="BX7" s="30"/>
+      <c r="BY7" s="30"/>
+      <c r="BZ7" s="30"/>
+      <c r="CA7" s="30"/>
+      <c r="CB7" s="30"/>
+      <c r="CC7" s="30"/>
+      <c r="CD7" s="30"/>
+      <c r="CE7" s="30"/>
+      <c r="CF7" s="30"/>
+      <c r="CG7" s="30"/>
+      <c r="CH7" s="30"/>
+      <c r="CI7" s="30"/>
+      <c r="CJ7" s="30"/>
+      <c r="CK7" s="30"/>
+      <c r="CL7" s="30"/>
+      <c r="CM7" s="30"/>
+      <c r="CN7" s="30"/>
+      <c r="CO7" s="30"/>
+      <c r="CP7" s="30"/>
+      <c r="CQ7" s="30"/>
+      <c r="CR7" s="30"/>
+      <c r="CS7" s="30"/>
+      <c r="CT7" s="30"/>
+      <c r="CU7" s="30"/>
+      <c r="CV7" s="30"/>
+      <c r="CW7" s="30"/>
+      <c r="CX7" s="30"/>
+      <c r="CY7" s="30"/>
+      <c r="CZ7" s="30"/>
+      <c r="DA7" s="30"/>
+      <c r="DB7" s="30"/>
+      <c r="DC7" s="30"/>
+      <c r="DD7" s="30"/>
+      <c r="DE7" s="30"/>
+      <c r="DF7" s="30"/>
+      <c r="DG7" s="30"/>
+      <c r="DH7" s="30"/>
+      <c r="DI7" s="30"/>
+      <c r="DJ7" s="30"/>
+      <c r="DK7" s="30"/>
+      <c r="DL7" s="30"/>
+      <c r="DM7" s="30"/>
+      <c r="DN7" s="30"/>
+      <c r="DO7" s="30"/>
+      <c r="DP7" s="30"/>
+      <c r="DQ7" s="30"/>
+      <c r="DR7" s="30"/>
+      <c r="DS7" s="30"/>
+      <c r="DT7" s="30"/>
     </row>
     <row r="8" spans="1:125" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="56" t="s">
+      <c r="A8" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="56"/>
-      <c r="C8" s="57">
+      <c r="B8" s="33"/>
+      <c r="C8" s="31">
         <f>SUM(C5:D7)</f>
         <v>75</v>
       </c>
-      <c r="D8" s="51"/>
+      <c r="D8" s="34"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="35">
-        <v>1</v>
-      </c>
-      <c r="G8" s="35">
+      <c r="F8" s="27">
+        <v>1</v>
+      </c>
+      <c r="G8" s="27">
         <v>2</v>
       </c>
-      <c r="H8" s="35">
+      <c r="H8" s="27">
         <v>3</v>
       </c>
-      <c r="I8" s="35">
+      <c r="I8" s="27">
         <v>4</v>
       </c>
-      <c r="J8" s="35">
+      <c r="J8" s="27">
         <v>5</v>
       </c>
-      <c r="K8" s="35">
+      <c r="K8" s="27">
         <v>6</v>
       </c>
-      <c r="L8" s="35">
+      <c r="L8" s="27">
         <v>7</v>
       </c>
-      <c r="M8" s="35">
+      <c r="M8" s="27">
         <v>8</v>
       </c>
-      <c r="N8" s="35">
+      <c r="N8" s="27">
         <v>9</v>
       </c>
-      <c r="O8" s="35">
+      <c r="O8" s="27">
         <v>10</v>
       </c>
-      <c r="P8" s="35">
+      <c r="P8" s="27">
         <v>11</v>
       </c>
-      <c r="Q8" s="35">
+      <c r="Q8" s="27">
         <v>12</v>
       </c>
-      <c r="R8" s="35">
+      <c r="R8" s="27">
         <v>13</v>
       </c>
-      <c r="S8" s="35">
+      <c r="S8" s="27">
         <v>14</v>
       </c>
-      <c r="T8" s="35">
+      <c r="T8" s="27">
         <v>15</v>
       </c>
-      <c r="U8" s="35">
+      <c r="U8" s="27">
         <v>16</v>
       </c>
-      <c r="V8" s="35">
+      <c r="V8" s="27">
         <v>17</v>
       </c>
-      <c r="W8" s="35">
+      <c r="W8" s="27">
         <v>18</v>
       </c>
-      <c r="X8" s="35">
+      <c r="X8" s="27">
         <v>19</v>
       </c>
-      <c r="Y8" s="35">
+      <c r="Y8" s="27">
         <v>20</v>
       </c>
-      <c r="Z8" s="35">
+      <c r="Z8" s="27">
         <v>21</v>
       </c>
-      <c r="AA8" s="35">
+      <c r="AA8" s="27">
         <v>22</v>
       </c>
-      <c r="AB8" s="35">
+      <c r="AB8" s="27">
         <v>23</v>
       </c>
-      <c r="AC8" s="35">
+      <c r="AC8" s="27">
         <v>24</v>
       </c>
-      <c r="AD8" s="35">
+      <c r="AD8" s="27">
         <v>25</v>
       </c>
-      <c r="AE8" s="35">
+      <c r="AE8" s="27">
         <v>26</v>
       </c>
-      <c r="AF8" s="35">
+      <c r="AF8" s="27">
         <v>27</v>
       </c>
-      <c r="AG8" s="35">
+      <c r="AG8" s="27">
         <v>28</v>
       </c>
-      <c r="AH8" s="35">
+      <c r="AH8" s="27">
         <v>29</v>
       </c>
-      <c r="AI8" s="35">
+      <c r="AI8" s="27">
         <v>30</v>
       </c>
-      <c r="AJ8" s="35">
+      <c r="AJ8" s="27">
         <v>31</v>
       </c>
-      <c r="AK8" s="35">
+      <c r="AK8" s="27">
         <v>32</v>
       </c>
-      <c r="AL8" s="35">
+      <c r="AL8" s="27">
         <v>33</v>
       </c>
-      <c r="AM8" s="35">
+      <c r="AM8" s="27">
         <v>34</v>
       </c>
-      <c r="AN8" s="35">
+      <c r="AN8" s="27">
         <v>35</v>
       </c>
-      <c r="AO8" s="35">
+      <c r="AO8" s="27">
         <v>36</v>
       </c>
-      <c r="AP8" s="35">
+      <c r="AP8" s="27">
         <v>37</v>
       </c>
-      <c r="AQ8" s="35">
+      <c r="AQ8" s="27">
         <v>38</v>
       </c>
-      <c r="AR8" s="35">
+      <c r="AR8" s="27">
         <v>39</v>
       </c>
-      <c r="AS8" s="35">
+      <c r="AS8" s="27">
         <v>40</v>
       </c>
-      <c r="AT8" s="35">
+      <c r="AT8" s="27">
         <v>41</v>
       </c>
-      <c r="AU8" s="35">
+      <c r="AU8" s="27">
         <v>42</v>
       </c>
-      <c r="AV8" s="35">
+      <c r="AV8" s="27">
         <v>43</v>
       </c>
-      <c r="AW8" s="35">
+      <c r="AW8" s="27">
         <v>44</v>
       </c>
-      <c r="AX8" s="35">
+      <c r="AX8" s="27">
         <v>45</v>
       </c>
-      <c r="AY8" s="35">
+      <c r="AY8" s="27">
         <v>46</v>
       </c>
-      <c r="AZ8" s="35">
+      <c r="AZ8" s="27">
         <v>47</v>
       </c>
-      <c r="BA8" s="35">
+      <c r="BA8" s="27">
         <v>48</v>
       </c>
-      <c r="BB8" s="35">
+      <c r="BB8" s="27">
         <v>49</v>
       </c>
-      <c r="BC8" s="35">
+      <c r="BC8" s="27">
         <v>50</v>
       </c>
-      <c r="BD8" s="35">
+      <c r="BD8" s="27">
         <v>51</v>
       </c>
-      <c r="BE8" s="35">
+      <c r="BE8" s="27">
         <v>52</v>
       </c>
-      <c r="BF8" s="35">
+      <c r="BF8" s="27">
         <v>53</v>
       </c>
-      <c r="BG8" s="35">
+      <c r="BG8" s="27">
         <v>54</v>
       </c>
-      <c r="BH8" s="35">
+      <c r="BH8" s="27">
         <v>55</v>
       </c>
-      <c r="BI8" s="35">
+      <c r="BI8" s="27">
         <v>56</v>
       </c>
-      <c r="BJ8" s="35">
+      <c r="BJ8" s="27">
         <v>57</v>
       </c>
-      <c r="BK8" s="35">
+      <c r="BK8" s="27">
         <v>58</v>
       </c>
-      <c r="BL8" s="35">
+      <c r="BL8" s="27">
         <v>59</v>
       </c>
-      <c r="BM8" s="35">
+      <c r="BM8" s="27">
         <v>60</v>
       </c>
-      <c r="BN8" s="35">
+      <c r="BN8" s="27">
         <v>61</v>
       </c>
-      <c r="BO8" s="35">
+      <c r="BO8" s="27">
         <v>62</v>
       </c>
-      <c r="BP8" s="35">
+      <c r="BP8" s="27">
         <v>63</v>
       </c>
-      <c r="BQ8" s="35">
+      <c r="BQ8" s="27">
         <v>64</v>
       </c>
-      <c r="BR8" s="35">
+      <c r="BR8" s="27">
         <v>65</v>
       </c>
-      <c r="BS8" s="35">
+      <c r="BS8" s="27">
         <v>66</v>
       </c>
-      <c r="BT8" s="35">
+      <c r="BT8" s="27">
         <v>67</v>
       </c>
-      <c r="BU8" s="35">
+      <c r="BU8" s="27">
         <v>68</v>
       </c>
-      <c r="BV8" s="35">
+      <c r="BV8" s="27">
         <v>69</v>
       </c>
-      <c r="BW8" s="35">
+      <c r="BW8" s="27">
         <v>70</v>
       </c>
-      <c r="BX8" s="35">
+      <c r="BX8" s="27">
         <v>71</v>
       </c>
-      <c r="BY8" s="35">
+      <c r="BY8" s="27">
         <v>72</v>
       </c>
-      <c r="BZ8" s="35">
+      <c r="BZ8" s="27">
         <v>73</v>
       </c>
-      <c r="CA8" s="35">
+      <c r="CA8" s="27">
         <v>74</v>
       </c>
-      <c r="CB8" s="35">
+      <c r="CB8" s="27">
         <v>75</v>
       </c>
-      <c r="CC8" s="35">
+      <c r="CC8" s="27">
         <v>76</v>
       </c>
-      <c r="CD8" s="35">
+      <c r="CD8" s="27">
         <v>77</v>
       </c>
-      <c r="CE8" s="35">
+      <c r="CE8" s="27">
         <v>78</v>
       </c>
-      <c r="CF8" s="35">
+      <c r="CF8" s="27">
         <v>79</v>
       </c>
-      <c r="CG8" s="35">
+      <c r="CG8" s="27">
         <v>80</v>
       </c>
-      <c r="CH8" s="35">
+      <c r="CH8" s="27">
         <v>81</v>
       </c>
-      <c r="CI8" s="35">
+      <c r="CI8" s="27">
         <v>82</v>
       </c>
-      <c r="CJ8" s="35">
+      <c r="CJ8" s="27">
         <v>83</v>
       </c>
-      <c r="CK8" s="35">
+      <c r="CK8" s="27">
         <v>84</v>
       </c>
-      <c r="CL8" s="35">
+      <c r="CL8" s="27">
         <v>85</v>
       </c>
-      <c r="CM8" s="35">
+      <c r="CM8" s="27">
         <v>86</v>
       </c>
-      <c r="CN8" s="35">
+      <c r="CN8" s="27">
         <v>87</v>
       </c>
-      <c r="CO8" s="35">
+      <c r="CO8" s="27">
         <v>88</v>
       </c>
-      <c r="CP8" s="35">
+      <c r="CP8" s="27">
         <v>89</v>
       </c>
-      <c r="CQ8" s="35">
+      <c r="CQ8" s="27">
         <v>90</v>
       </c>
-      <c r="CR8" s="35">
+      <c r="CR8" s="27">
         <v>91</v>
       </c>
-      <c r="CS8" s="35">
+      <c r="CS8" s="27">
         <v>92</v>
       </c>
-      <c r="CT8" s="35">
+      <c r="CT8" s="27">
         <v>93</v>
       </c>
-      <c r="CU8" s="35">
+      <c r="CU8" s="27">
         <v>94</v>
       </c>
-      <c r="CV8" s="35">
+      <c r="CV8" s="27">
         <v>95</v>
       </c>
-      <c r="CW8" s="35">
+      <c r="CW8" s="27">
         <v>96</v>
       </c>
-      <c r="CX8" s="35">
+      <c r="CX8" s="27">
         <v>97</v>
       </c>
-      <c r="CY8" s="35">
+      <c r="CY8" s="27">
         <v>98</v>
       </c>
-      <c r="CZ8" s="35">
+      <c r="CZ8" s="27">
         <v>99</v>
       </c>
-      <c r="DA8" s="35">
+      <c r="DA8" s="27">
         <v>100</v>
       </c>
-      <c r="DB8" s="35">
+      <c r="DB8" s="27">
         <v>101</v>
       </c>
-      <c r="DC8" s="35">
+      <c r="DC8" s="27">
         <v>102</v>
       </c>
-      <c r="DD8" s="35">
+      <c r="DD8" s="27">
         <v>103</v>
       </c>
-      <c r="DE8" s="35">
+      <c r="DE8" s="27">
         <v>104</v>
       </c>
-      <c r="DF8" s="35">
+      <c r="DF8" s="27">
         <v>105</v>
       </c>
-      <c r="DG8" s="35">
+      <c r="DG8" s="27">
         <v>106</v>
       </c>
-      <c r="DH8" s="35">
+      <c r="DH8" s="27">
         <v>107</v>
       </c>
-      <c r="DI8" s="35">
+      <c r="DI8" s="27">
         <v>108</v>
       </c>
-      <c r="DJ8" s="35">
+      <c r="DJ8" s="27">
         <v>109</v>
       </c>
-      <c r="DK8" s="35">
+      <c r="DK8" s="27">
         <v>110</v>
       </c>
-      <c r="DL8" s="35">
+      <c r="DL8" s="27">
         <v>111</v>
       </c>
-      <c r="DM8" s="35">
+      <c r="DM8" s="27">
         <v>112</v>
       </c>
-      <c r="DN8" s="35">
+      <c r="DN8" s="27">
         <v>113</v>
       </c>
-      <c r="DO8" s="35">
+      <c r="DO8" s="27">
         <v>114</v>
       </c>
-      <c r="DP8" s="35">
+      <c r="DP8" s="27">
         <v>115</v>
       </c>
-      <c r="DQ8" s="35">
+      <c r="DQ8" s="27">
         <v>116</v>
       </c>
-      <c r="DR8" s="35">
+      <c r="DR8" s="27">
         <v>117</v>
       </c>
-      <c r="DS8" s="35">
+      <c r="DS8" s="27">
         <v>118</v>
       </c>
-      <c r="DT8" s="35">
+      <c r="DT8" s="27">
         <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="48" t="s">
+      <c r="A9" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="58" t="s">
+      <c r="B9" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="59" t="s">
+      <c r="C9" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="58"/>
+      <c r="D9" s="36"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="36"/>
-      <c r="K9" s="36"/>
-      <c r="L9" s="36"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="36"/>
-      <c r="P9" s="36"/>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="36"/>
-      <c r="S9" s="36"/>
-      <c r="T9" s="36"/>
-      <c r="U9" s="36"/>
-      <c r="V9" s="36"/>
-      <c r="W9" s="36"/>
-      <c r="X9" s="36"/>
-      <c r="Y9" s="36"/>
-      <c r="Z9" s="36"/>
-      <c r="AA9" s="36"/>
-      <c r="AB9" s="36"/>
-      <c r="AC9" s="36"/>
-      <c r="AD9" s="36"/>
-      <c r="AE9" s="36"/>
-      <c r="AF9" s="36"/>
-      <c r="AG9" s="36"/>
-      <c r="AH9" s="36"/>
-      <c r="AI9" s="36"/>
-      <c r="AJ9" s="36"/>
-      <c r="AK9" s="36"/>
-      <c r="AL9" s="36"/>
-      <c r="AM9" s="36"/>
-      <c r="AN9" s="36"/>
-      <c r="AO9" s="36"/>
-      <c r="AP9" s="36"/>
-      <c r="AQ9" s="36"/>
-      <c r="AR9" s="36"/>
-      <c r="AS9" s="36"/>
-      <c r="AT9" s="36"/>
-      <c r="AU9" s="36"/>
-      <c r="AV9" s="36"/>
-      <c r="AW9" s="36"/>
-      <c r="AX9" s="36"/>
-      <c r="AY9" s="36"/>
-      <c r="AZ9" s="36"/>
-      <c r="BA9" s="36"/>
-      <c r="BB9" s="36"/>
-      <c r="BC9" s="36"/>
-      <c r="BD9" s="36"/>
-      <c r="BE9" s="36"/>
-      <c r="BF9" s="36"/>
-      <c r="BG9" s="36"/>
-      <c r="BH9" s="36"/>
-      <c r="BI9" s="36"/>
-      <c r="BJ9" s="36"/>
-      <c r="BK9" s="36"/>
-      <c r="BL9" s="36"/>
-      <c r="BM9" s="36"/>
-      <c r="BN9" s="36"/>
-      <c r="BO9" s="36"/>
-      <c r="BP9" s="36"/>
-      <c r="BQ9" s="36"/>
-      <c r="BR9" s="36"/>
-      <c r="BS9" s="36"/>
-      <c r="BT9" s="36"/>
-      <c r="BU9" s="36"/>
-      <c r="BV9" s="36"/>
-      <c r="BW9" s="36"/>
-      <c r="BX9" s="36"/>
-      <c r="BY9" s="36"/>
-      <c r="BZ9" s="36"/>
-      <c r="CA9" s="36"/>
-      <c r="CB9" s="36"/>
-      <c r="CC9" s="36"/>
-      <c r="CD9" s="36"/>
-      <c r="CE9" s="36"/>
-      <c r="CF9" s="36"/>
-      <c r="CG9" s="36"/>
-      <c r="CH9" s="36"/>
-      <c r="CI9" s="36"/>
-      <c r="CJ9" s="36"/>
-      <c r="CK9" s="36"/>
-      <c r="CL9" s="36"/>
-      <c r="CM9" s="36"/>
-      <c r="CN9" s="36"/>
-      <c r="CO9" s="36"/>
-      <c r="CP9" s="36"/>
-      <c r="CQ9" s="36"/>
-      <c r="CR9" s="36"/>
-      <c r="CS9" s="36"/>
-      <c r="CT9" s="36"/>
-      <c r="CU9" s="36"/>
-      <c r="CV9" s="36"/>
-      <c r="CW9" s="36"/>
-      <c r="CX9" s="36"/>
-      <c r="CY9" s="36"/>
-      <c r="CZ9" s="36"/>
-      <c r="DA9" s="36"/>
-      <c r="DB9" s="36"/>
-      <c r="DC9" s="36"/>
-      <c r="DD9" s="36"/>
-      <c r="DE9" s="36"/>
-      <c r="DF9" s="36"/>
-      <c r="DG9" s="36"/>
-      <c r="DH9" s="36"/>
-      <c r="DI9" s="36"/>
-      <c r="DJ9" s="36"/>
-      <c r="DK9" s="36"/>
-      <c r="DL9" s="36"/>
-      <c r="DM9" s="36"/>
-      <c r="DN9" s="36"/>
-      <c r="DO9" s="36"/>
-      <c r="DP9" s="36"/>
-      <c r="DQ9" s="36"/>
-      <c r="DR9" s="36"/>
-      <c r="DS9" s="36"/>
-      <c r="DT9" s="36"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="28"/>
+      <c r="Q9" s="28"/>
+      <c r="R9" s="28"/>
+      <c r="S9" s="28"/>
+      <c r="T9" s="28"/>
+      <c r="U9" s="28"/>
+      <c r="V9" s="28"/>
+      <c r="W9" s="28"/>
+      <c r="X9" s="28"/>
+      <c r="Y9" s="28"/>
+      <c r="Z9" s="28"/>
+      <c r="AA9" s="28"/>
+      <c r="AB9" s="28"/>
+      <c r="AC9" s="28"/>
+      <c r="AD9" s="28"/>
+      <c r="AE9" s="28"/>
+      <c r="AF9" s="28"/>
+      <c r="AG9" s="28"/>
+      <c r="AH9" s="28"/>
+      <c r="AI9" s="28"/>
+      <c r="AJ9" s="28"/>
+      <c r="AK9" s="28"/>
+      <c r="AL9" s="28"/>
+      <c r="AM9" s="28"/>
+      <c r="AN9" s="28"/>
+      <c r="AO9" s="28"/>
+      <c r="AP9" s="28"/>
+      <c r="AQ9" s="28"/>
+      <c r="AR9" s="28"/>
+      <c r="AS9" s="28"/>
+      <c r="AT9" s="28"/>
+      <c r="AU9" s="28"/>
+      <c r="AV9" s="28"/>
+      <c r="AW9" s="28"/>
+      <c r="AX9" s="28"/>
+      <c r="AY9" s="28"/>
+      <c r="AZ9" s="28"/>
+      <c r="BA9" s="28"/>
+      <c r="BB9" s="28"/>
+      <c r="BC9" s="28"/>
+      <c r="BD9" s="28"/>
+      <c r="BE9" s="28"/>
+      <c r="BF9" s="28"/>
+      <c r="BG9" s="28"/>
+      <c r="BH9" s="28"/>
+      <c r="BI9" s="28"/>
+      <c r="BJ9" s="28"/>
+      <c r="BK9" s="28"/>
+      <c r="BL9" s="28"/>
+      <c r="BM9" s="28"/>
+      <c r="BN9" s="28"/>
+      <c r="BO9" s="28"/>
+      <c r="BP9" s="28"/>
+      <c r="BQ9" s="28"/>
+      <c r="BR9" s="28"/>
+      <c r="BS9" s="28"/>
+      <c r="BT9" s="28"/>
+      <c r="BU9" s="28"/>
+      <c r="BV9" s="28"/>
+      <c r="BW9" s="28"/>
+      <c r="BX9" s="28"/>
+      <c r="BY9" s="28"/>
+      <c r="BZ9" s="28"/>
+      <c r="CA9" s="28"/>
+      <c r="CB9" s="28"/>
+      <c r="CC9" s="28"/>
+      <c r="CD9" s="28"/>
+      <c r="CE9" s="28"/>
+      <c r="CF9" s="28"/>
+      <c r="CG9" s="28"/>
+      <c r="CH9" s="28"/>
+      <c r="CI9" s="28"/>
+      <c r="CJ9" s="28"/>
+      <c r="CK9" s="28"/>
+      <c r="CL9" s="28"/>
+      <c r="CM9" s="28"/>
+      <c r="CN9" s="28"/>
+      <c r="CO9" s="28"/>
+      <c r="CP9" s="28"/>
+      <c r="CQ9" s="28"/>
+      <c r="CR9" s="28"/>
+      <c r="CS9" s="28"/>
+      <c r="CT9" s="28"/>
+      <c r="CU9" s="28"/>
+      <c r="CV9" s="28"/>
+      <c r="CW9" s="28"/>
+      <c r="CX9" s="28"/>
+      <c r="CY9" s="28"/>
+      <c r="CZ9" s="28"/>
+      <c r="DA9" s="28"/>
+      <c r="DB9" s="28"/>
+      <c r="DC9" s="28"/>
+      <c r="DD9" s="28"/>
+      <c r="DE9" s="28"/>
+      <c r="DF9" s="28"/>
+      <c r="DG9" s="28"/>
+      <c r="DH9" s="28"/>
+      <c r="DI9" s="28"/>
+      <c r="DJ9" s="28"/>
+      <c r="DK9" s="28"/>
+      <c r="DL9" s="28"/>
+      <c r="DM9" s="28"/>
+      <c r="DN9" s="28"/>
+      <c r="DO9" s="28"/>
+      <c r="DP9" s="28"/>
+      <c r="DQ9" s="28"/>
+      <c r="DR9" s="28"/>
+      <c r="DS9" s="28"/>
+      <c r="DT9" s="28"/>
     </row>
     <row r="10" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="48"/>
-      <c r="B10" s="58"/>
+      <c r="A10" s="35"/>
+      <c r="B10" s="36"/>
       <c r="C10" s="6"/>
       <c r="D10" s="4" t="s">
         <v>10</v>
@@ -2778,7 +2796,7 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
@@ -4828,253 +4846,253 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E26" s="57"/>
-      <c r="F26" s="50"/>
-      <c r="G26" s="50"/>
-      <c r="H26" s="50"/>
-      <c r="I26" s="50"/>
-      <c r="J26" s="50"/>
-      <c r="K26" s="50"/>
-      <c r="L26" s="50"/>
-      <c r="M26" s="50"/>
-      <c r="N26" s="50"/>
-      <c r="O26" s="50"/>
-      <c r="P26" s="50"/>
-      <c r="Q26" s="50"/>
-      <c r="R26" s="50"/>
-      <c r="S26" s="50"/>
-      <c r="T26" s="50"/>
-      <c r="U26" s="50"/>
-      <c r="V26" s="50"/>
-      <c r="W26" s="50"/>
-      <c r="X26" s="50"/>
-      <c r="Y26" s="50"/>
-      <c r="Z26" s="50"/>
-      <c r="AA26" s="50"/>
-      <c r="AB26" s="50"/>
-      <c r="AC26" s="50"/>
-      <c r="AD26" s="50"/>
-      <c r="AE26" s="50"/>
-      <c r="AF26" s="50"/>
-      <c r="AG26" s="50"/>
-      <c r="AH26" s="50"/>
-      <c r="AI26" s="50"/>
-      <c r="AJ26" s="50"/>
-      <c r="AK26" s="50"/>
-      <c r="AL26" s="50"/>
-      <c r="AM26" s="50"/>
-      <c r="AN26" s="50"/>
-      <c r="AO26" s="50"/>
-      <c r="AP26" s="50"/>
-      <c r="AQ26" s="50"/>
-      <c r="AR26" s="50"/>
-      <c r="AS26" s="50"/>
-      <c r="AT26" s="50"/>
-      <c r="AU26" s="50"/>
-      <c r="AV26" s="50"/>
-      <c r="AW26" s="50"/>
-      <c r="AX26" s="50"/>
-      <c r="AY26" s="50"/>
-      <c r="AZ26" s="50"/>
-      <c r="BA26" s="50"/>
-      <c r="BB26" s="50"/>
-      <c r="BC26" s="50"/>
-      <c r="BD26" s="50"/>
-      <c r="BE26" s="50"/>
-      <c r="BF26" s="50"/>
-      <c r="BG26" s="50"/>
-      <c r="BH26" s="50"/>
-      <c r="BI26" s="50"/>
-      <c r="BJ26" s="50"/>
-      <c r="BK26" s="50"/>
-      <c r="BL26" s="50"/>
-      <c r="BM26" s="50"/>
-      <c r="BN26" s="50"/>
-      <c r="BO26" s="50"/>
-      <c r="BP26" s="50"/>
-      <c r="BQ26" s="50"/>
-      <c r="BR26" s="50"/>
-      <c r="BS26" s="50"/>
-      <c r="BT26" s="50"/>
-      <c r="BU26" s="50"/>
-      <c r="BV26" s="50"/>
-      <c r="BW26" s="50"/>
-      <c r="BX26" s="50"/>
-      <c r="BY26" s="50"/>
-      <c r="BZ26" s="50"/>
-      <c r="CA26" s="50"/>
-      <c r="CB26" s="50"/>
-      <c r="CC26" s="50"/>
-      <c r="CD26" s="50"/>
-      <c r="CE26" s="50"/>
-      <c r="CF26" s="50"/>
-      <c r="CG26" s="50"/>
-      <c r="CH26" s="50"/>
-      <c r="CI26" s="50"/>
-      <c r="CJ26" s="50"/>
-      <c r="CK26" s="50"/>
-      <c r="CL26" s="50"/>
-      <c r="CM26" s="50"/>
-      <c r="CN26" s="50"/>
-      <c r="CO26" s="50"/>
-      <c r="CP26" s="50"/>
-      <c r="CQ26" s="50"/>
-      <c r="CR26" s="50"/>
-      <c r="CS26" s="50"/>
-      <c r="CT26" s="50"/>
-      <c r="CU26" s="50"/>
-      <c r="CV26" s="50"/>
-      <c r="CW26" s="50"/>
-      <c r="CX26" s="50"/>
-      <c r="CY26" s="50"/>
-      <c r="CZ26" s="50"/>
-      <c r="DA26" s="50"/>
-      <c r="DB26" s="50"/>
-      <c r="DC26" s="50"/>
-      <c r="DD26" s="50"/>
-      <c r="DE26" s="50"/>
-      <c r="DF26" s="50"/>
-      <c r="DG26" s="50"/>
-      <c r="DH26" s="50"/>
-      <c r="DI26" s="50"/>
-      <c r="DJ26" s="50"/>
-      <c r="DK26" s="50"/>
-      <c r="DL26" s="50"/>
-      <c r="DM26" s="50"/>
-      <c r="DN26" s="50"/>
-      <c r="DO26" s="50"/>
-      <c r="DP26" s="50"/>
-      <c r="DQ26" s="50"/>
-      <c r="DR26" s="50"/>
-      <c r="DS26" s="50"/>
-      <c r="DT26" s="50"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="32"/>
+      <c r="L26" s="32"/>
+      <c r="M26" s="32"/>
+      <c r="N26" s="32"/>
+      <c r="O26" s="32"/>
+      <c r="P26" s="32"/>
+      <c r="Q26" s="32"/>
+      <c r="R26" s="32"/>
+      <c r="S26" s="32"/>
+      <c r="T26" s="32"/>
+      <c r="U26" s="32"/>
+      <c r="V26" s="32"/>
+      <c r="W26" s="32"/>
+      <c r="X26" s="32"/>
+      <c r="Y26" s="32"/>
+      <c r="Z26" s="32"/>
+      <c r="AA26" s="32"/>
+      <c r="AB26" s="32"/>
+      <c r="AC26" s="32"/>
+      <c r="AD26" s="32"/>
+      <c r="AE26" s="32"/>
+      <c r="AF26" s="32"/>
+      <c r="AG26" s="32"/>
+      <c r="AH26" s="32"/>
+      <c r="AI26" s="32"/>
+      <c r="AJ26" s="32"/>
+      <c r="AK26" s="32"/>
+      <c r="AL26" s="32"/>
+      <c r="AM26" s="32"/>
+      <c r="AN26" s="32"/>
+      <c r="AO26" s="32"/>
+      <c r="AP26" s="32"/>
+      <c r="AQ26" s="32"/>
+      <c r="AR26" s="32"/>
+      <c r="AS26" s="32"/>
+      <c r="AT26" s="32"/>
+      <c r="AU26" s="32"/>
+      <c r="AV26" s="32"/>
+      <c r="AW26" s="32"/>
+      <c r="AX26" s="32"/>
+      <c r="AY26" s="32"/>
+      <c r="AZ26" s="32"/>
+      <c r="BA26" s="32"/>
+      <c r="BB26" s="32"/>
+      <c r="BC26" s="32"/>
+      <c r="BD26" s="32"/>
+      <c r="BE26" s="32"/>
+      <c r="BF26" s="32"/>
+      <c r="BG26" s="32"/>
+      <c r="BH26" s="32"/>
+      <c r="BI26" s="32"/>
+      <c r="BJ26" s="32"/>
+      <c r="BK26" s="32"/>
+      <c r="BL26" s="32"/>
+      <c r="BM26" s="32"/>
+      <c r="BN26" s="32"/>
+      <c r="BO26" s="32"/>
+      <c r="BP26" s="32"/>
+      <c r="BQ26" s="32"/>
+      <c r="BR26" s="32"/>
+      <c r="BS26" s="32"/>
+      <c r="BT26" s="32"/>
+      <c r="BU26" s="32"/>
+      <c r="BV26" s="32"/>
+      <c r="BW26" s="32"/>
+      <c r="BX26" s="32"/>
+      <c r="BY26" s="32"/>
+      <c r="BZ26" s="32"/>
+      <c r="CA26" s="32"/>
+      <c r="CB26" s="32"/>
+      <c r="CC26" s="32"/>
+      <c r="CD26" s="32"/>
+      <c r="CE26" s="32"/>
+      <c r="CF26" s="32"/>
+      <c r="CG26" s="32"/>
+      <c r="CH26" s="32"/>
+      <c r="CI26" s="32"/>
+      <c r="CJ26" s="32"/>
+      <c r="CK26" s="32"/>
+      <c r="CL26" s="32"/>
+      <c r="CM26" s="32"/>
+      <c r="CN26" s="32"/>
+      <c r="CO26" s="32"/>
+      <c r="CP26" s="32"/>
+      <c r="CQ26" s="32"/>
+      <c r="CR26" s="32"/>
+      <c r="CS26" s="32"/>
+      <c r="CT26" s="32"/>
+      <c r="CU26" s="32"/>
+      <c r="CV26" s="32"/>
+      <c r="CW26" s="32"/>
+      <c r="CX26" s="32"/>
+      <c r="CY26" s="32"/>
+      <c r="CZ26" s="32"/>
+      <c r="DA26" s="32"/>
+      <c r="DB26" s="32"/>
+      <c r="DC26" s="32"/>
+      <c r="DD26" s="32"/>
+      <c r="DE26" s="32"/>
+      <c r="DF26" s="32"/>
+      <c r="DG26" s="32"/>
+      <c r="DH26" s="32"/>
+      <c r="DI26" s="32"/>
+      <c r="DJ26" s="32"/>
+      <c r="DK26" s="32"/>
+      <c r="DL26" s="32"/>
+      <c r="DM26" s="32"/>
+      <c r="DN26" s="32"/>
+      <c r="DO26" s="32"/>
+      <c r="DP26" s="32"/>
+      <c r="DQ26" s="32"/>
+      <c r="DR26" s="32"/>
+      <c r="DS26" s="32"/>
+      <c r="DT26" s="32"/>
     </row>
     <row r="27" spans="1:124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E27" s="1">
         <v>4</v>
       </c>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="32"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="32"/>
-      <c r="K27" s="32"/>
-      <c r="L27" s="32"/>
-      <c r="M27" s="32"/>
-      <c r="N27" s="32"/>
-      <c r="O27" s="32"/>
-      <c r="P27" s="32"/>
-      <c r="Q27" s="32"/>
-      <c r="R27" s="32"/>
-      <c r="S27" s="32"/>
-      <c r="T27" s="32"/>
-      <c r="U27" s="32"/>
-      <c r="V27" s="32"/>
-      <c r="W27" s="32"/>
-      <c r="X27" s="32"/>
-      <c r="Y27" s="32"/>
-      <c r="Z27" s="32"/>
-      <c r="AA27" s="32"/>
-      <c r="AB27" s="32"/>
-      <c r="AC27" s="32"/>
-      <c r="AD27" s="32"/>
-      <c r="AE27" s="32"/>
-      <c r="AF27" s="32"/>
-      <c r="AG27" s="32"/>
-      <c r="AH27" s="32"/>
-      <c r="AI27" s="32"/>
-      <c r="AJ27" s="32"/>
-      <c r="AK27" s="32"/>
-      <c r="AL27" s="32"/>
-      <c r="AM27" s="32"/>
-      <c r="AN27" s="32"/>
-      <c r="AO27" s="32"/>
-      <c r="AP27" s="32"/>
-      <c r="AQ27" s="32"/>
-      <c r="AR27" s="32"/>
-      <c r="AS27" s="32"/>
-      <c r="AT27" s="32"/>
-      <c r="AU27" s="32"/>
-      <c r="AV27" s="32"/>
-      <c r="AW27" s="32"/>
-      <c r="AX27" s="32"/>
-      <c r="AY27" s="32"/>
-      <c r="AZ27" s="32"/>
-      <c r="BA27" s="32"/>
-      <c r="BB27" s="32"/>
-      <c r="BC27" s="32"/>
-      <c r="BD27" s="32"/>
-      <c r="BE27" s="32"/>
-      <c r="BF27" s="32"/>
-      <c r="BG27" s="32"/>
-      <c r="BH27" s="32"/>
-      <c r="BI27" s="32"/>
-      <c r="BJ27" s="32"/>
-      <c r="BK27" s="32"/>
-      <c r="BL27" s="32"/>
-      <c r="BM27" s="32"/>
-      <c r="BN27" s="32"/>
-      <c r="BO27" s="32"/>
-      <c r="BP27" s="32"/>
-      <c r="BQ27" s="32"/>
-      <c r="BR27" s="32"/>
-      <c r="BS27" s="32"/>
-      <c r="BT27" s="32"/>
-      <c r="BU27" s="32"/>
-      <c r="BV27" s="32"/>
-      <c r="BW27" s="32"/>
-      <c r="BX27" s="32"/>
-      <c r="BY27" s="32"/>
-      <c r="BZ27" s="32"/>
-      <c r="CA27" s="32"/>
-      <c r="CB27" s="32"/>
-      <c r="CC27" s="32"/>
-      <c r="CD27" s="32"/>
-      <c r="CE27" s="33"/>
-      <c r="CF27" s="34"/>
-      <c r="CG27" s="34"/>
-      <c r="CH27" s="34"/>
-      <c r="CI27" s="34"/>
-      <c r="CJ27" s="34"/>
-      <c r="CK27" s="34"/>
-      <c r="CL27" s="34"/>
-      <c r="CM27" s="34"/>
-      <c r="CN27" s="34"/>
-      <c r="CO27" s="34"/>
-      <c r="CP27" s="34"/>
-      <c r="CQ27" s="34"/>
-      <c r="CR27" s="34"/>
-      <c r="CS27" s="34"/>
-      <c r="CT27" s="34"/>
-      <c r="CU27" s="34"/>
-      <c r="CV27" s="34"/>
-      <c r="CW27" s="34"/>
-      <c r="CX27" s="34"/>
-      <c r="CY27" s="34"/>
-      <c r="CZ27" s="34"/>
-      <c r="DA27" s="34"/>
-      <c r="DB27" s="34"/>
-      <c r="DC27" s="34"/>
-      <c r="DD27" s="34"/>
-      <c r="DE27" s="34"/>
-      <c r="DF27" s="34"/>
-      <c r="DG27" s="34"/>
-      <c r="DH27" s="34"/>
-      <c r="DI27" s="34"/>
-      <c r="DJ27" s="34"/>
-      <c r="DK27" s="34"/>
-      <c r="DL27" s="34"/>
-      <c r="DM27" s="34"/>
-      <c r="DN27" s="34"/>
-      <c r="DO27" s="34"/>
-      <c r="DP27" s="34"/>
-      <c r="DQ27" s="34"/>
-      <c r="DR27" s="34"/>
-      <c r="DS27" s="34"/>
-      <c r="DT27" s="34"/>
+      <c r="F27" s="56"/>
+      <c r="G27" s="56"/>
+      <c r="H27" s="56"/>
+      <c r="I27" s="56"/>
+      <c r="J27" s="56"/>
+      <c r="K27" s="56"/>
+      <c r="L27" s="56"/>
+      <c r="M27" s="56"/>
+      <c r="N27" s="56"/>
+      <c r="O27" s="56"/>
+      <c r="P27" s="56"/>
+      <c r="Q27" s="56"/>
+      <c r="R27" s="56"/>
+      <c r="S27" s="56"/>
+      <c r="T27" s="56"/>
+      <c r="U27" s="56"/>
+      <c r="V27" s="56"/>
+      <c r="W27" s="56"/>
+      <c r="X27" s="56"/>
+      <c r="Y27" s="56"/>
+      <c r="Z27" s="56"/>
+      <c r="AA27" s="56"/>
+      <c r="AB27" s="56"/>
+      <c r="AC27" s="56"/>
+      <c r="AD27" s="56"/>
+      <c r="AE27" s="56"/>
+      <c r="AF27" s="56"/>
+      <c r="AG27" s="56"/>
+      <c r="AH27" s="56"/>
+      <c r="AI27" s="56"/>
+      <c r="AJ27" s="56"/>
+      <c r="AK27" s="56"/>
+      <c r="AL27" s="56"/>
+      <c r="AM27" s="56"/>
+      <c r="AN27" s="56"/>
+      <c r="AO27" s="56"/>
+      <c r="AP27" s="56"/>
+      <c r="AQ27" s="56"/>
+      <c r="AR27" s="56"/>
+      <c r="AS27" s="56"/>
+      <c r="AT27" s="56"/>
+      <c r="AU27" s="56"/>
+      <c r="AV27" s="56"/>
+      <c r="AW27" s="56"/>
+      <c r="AX27" s="56"/>
+      <c r="AY27" s="56"/>
+      <c r="AZ27" s="56"/>
+      <c r="BA27" s="56"/>
+      <c r="BB27" s="56"/>
+      <c r="BC27" s="56"/>
+      <c r="BD27" s="56"/>
+      <c r="BE27" s="56"/>
+      <c r="BF27" s="56"/>
+      <c r="BG27" s="56"/>
+      <c r="BH27" s="56"/>
+      <c r="BI27" s="56"/>
+      <c r="BJ27" s="56"/>
+      <c r="BK27" s="56"/>
+      <c r="BL27" s="56"/>
+      <c r="BM27" s="56"/>
+      <c r="BN27" s="56"/>
+      <c r="BO27" s="56"/>
+      <c r="BP27" s="56"/>
+      <c r="BQ27" s="56"/>
+      <c r="BR27" s="56"/>
+      <c r="BS27" s="56"/>
+      <c r="BT27" s="56"/>
+      <c r="BU27" s="56"/>
+      <c r="BV27" s="56"/>
+      <c r="BW27" s="56"/>
+      <c r="BX27" s="56"/>
+      <c r="BY27" s="56"/>
+      <c r="BZ27" s="56"/>
+      <c r="CA27" s="56"/>
+      <c r="CB27" s="56"/>
+      <c r="CC27" s="56"/>
+      <c r="CD27" s="56"/>
+      <c r="CE27" s="57"/>
+      <c r="CF27" s="58"/>
+      <c r="CG27" s="58"/>
+      <c r="CH27" s="58"/>
+      <c r="CI27" s="58"/>
+      <c r="CJ27" s="58"/>
+      <c r="CK27" s="58"/>
+      <c r="CL27" s="58"/>
+      <c r="CM27" s="58"/>
+      <c r="CN27" s="58"/>
+      <c r="CO27" s="58"/>
+      <c r="CP27" s="58"/>
+      <c r="CQ27" s="58"/>
+      <c r="CR27" s="58"/>
+      <c r="CS27" s="58"/>
+      <c r="CT27" s="58"/>
+      <c r="CU27" s="58"/>
+      <c r="CV27" s="58"/>
+      <c r="CW27" s="58"/>
+      <c r="CX27" s="58"/>
+      <c r="CY27" s="58"/>
+      <c r="CZ27" s="58"/>
+      <c r="DA27" s="58"/>
+      <c r="DB27" s="58"/>
+      <c r="DC27" s="58"/>
+      <c r="DD27" s="58"/>
+      <c r="DE27" s="58"/>
+      <c r="DF27" s="58"/>
+      <c r="DG27" s="58"/>
+      <c r="DH27" s="58"/>
+      <c r="DI27" s="58"/>
+      <c r="DJ27" s="58"/>
+      <c r="DK27" s="58"/>
+      <c r="DL27" s="58"/>
+      <c r="DM27" s="58"/>
+      <c r="DN27" s="58"/>
+      <c r="DO27" s="58"/>
+      <c r="DP27" s="58"/>
+      <c r="DQ27" s="58"/>
+      <c r="DR27" s="58"/>
+      <c r="DS27" s="58"/>
+      <c r="DT27" s="58"/>
     </row>
     <row r="29" spans="1:124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E29" s="22">
+      <c r="E29" s="21">
         <f>SUM(E11:E18)/8</f>
         <v>3.9583333333333331E-2</v>
       </c>
@@ -5084,19 +5102,256 @@
       </c>
     </row>
     <row r="30" spans="1:124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AJ30" s="18"/>
-      <c r="AK30" s="17" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" spans="1:124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AJ31" s="21"/>
-      <c r="AK31" s="1" t="s">
-        <v>42</v>
+      <c r="AJ30" s="20"/>
+      <c r="AK30" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="266">
+  <mergeCells count="267">
+    <mergeCell ref="U2:U7"/>
+    <mergeCell ref="AH1:AK1"/>
+    <mergeCell ref="CS8:CS9"/>
+    <mergeCell ref="AD1:AG1"/>
+    <mergeCell ref="V1:Y1"/>
+    <mergeCell ref="R1:U1"/>
+    <mergeCell ref="DQ2:DQ7"/>
+    <mergeCell ref="DR2:DR7"/>
+    <mergeCell ref="DS2:DS7"/>
+    <mergeCell ref="DT2:DT7"/>
+    <mergeCell ref="CX2:CX7"/>
+    <mergeCell ref="CY2:CY7"/>
+    <mergeCell ref="DA2:DA7"/>
+    <mergeCell ref="DB2:DB7"/>
+    <mergeCell ref="DC2:DC7"/>
+    <mergeCell ref="DD2:DD7"/>
+    <mergeCell ref="DE2:DE7"/>
+    <mergeCell ref="CZ2:CZ7"/>
+    <mergeCell ref="DN2:DN7"/>
+    <mergeCell ref="DO2:DO7"/>
+    <mergeCell ref="DP2:DP7"/>
+    <mergeCell ref="DG2:DG7"/>
+    <mergeCell ref="DH2:DH7"/>
+    <mergeCell ref="DI2:DI7"/>
+    <mergeCell ref="DJ2:DJ7"/>
+    <mergeCell ref="DK2:DK7"/>
+    <mergeCell ref="CP2:CP7"/>
+    <mergeCell ref="V2:V7"/>
+    <mergeCell ref="W2:W7"/>
+    <mergeCell ref="F27:S27"/>
+    <mergeCell ref="T27:AW27"/>
+    <mergeCell ref="AX27:CD27"/>
+    <mergeCell ref="CE27:DT27"/>
+    <mergeCell ref="DG8:DG9"/>
+    <mergeCell ref="DH8:DH9"/>
+    <mergeCell ref="DI8:DI9"/>
+    <mergeCell ref="DJ8:DJ9"/>
+    <mergeCell ref="DK8:DK9"/>
+    <mergeCell ref="DL8:DL9"/>
+    <mergeCell ref="DM8:DM9"/>
+    <mergeCell ref="DN8:DN9"/>
+    <mergeCell ref="DO8:DO9"/>
+    <mergeCell ref="DP8:DP9"/>
+    <mergeCell ref="DA8:DA9"/>
+    <mergeCell ref="DB8:DB9"/>
+    <mergeCell ref="DC8:DC9"/>
+    <mergeCell ref="DD8:DD9"/>
+    <mergeCell ref="DE8:DE9"/>
+    <mergeCell ref="CQ8:CQ9"/>
+    <mergeCell ref="CR8:CR9"/>
+    <mergeCell ref="BK2:BK7"/>
+    <mergeCell ref="BN8:BN9"/>
+    <mergeCell ref="CI8:CI9"/>
+    <mergeCell ref="CK8:CK9"/>
+    <mergeCell ref="CL8:CL9"/>
+    <mergeCell ref="BX8:BX9"/>
+    <mergeCell ref="BY8:BY9"/>
+    <mergeCell ref="DL2:DL7"/>
+    <mergeCell ref="DM2:DM7"/>
+    <mergeCell ref="DF2:DF7"/>
+    <mergeCell ref="CW2:CW7"/>
+    <mergeCell ref="CU2:CU7"/>
+    <mergeCell ref="CV2:CV7"/>
+    <mergeCell ref="CQ2:CQ7"/>
+    <mergeCell ref="CR2:CR7"/>
+    <mergeCell ref="CS2:CS7"/>
+    <mergeCell ref="CT2:CT7"/>
+    <mergeCell ref="CI2:CI7"/>
+    <mergeCell ref="CJ2:CJ7"/>
+    <mergeCell ref="CK2:CK7"/>
+    <mergeCell ref="CL2:CL7"/>
+    <mergeCell ref="CM2:CM7"/>
+    <mergeCell ref="CN2:CN7"/>
+    <mergeCell ref="CO2:CO7"/>
+    <mergeCell ref="BM2:BM7"/>
+    <mergeCell ref="BN2:BN7"/>
+    <mergeCell ref="BO2:BO7"/>
+    <mergeCell ref="BP2:BP7"/>
+    <mergeCell ref="CA2:CA7"/>
+    <mergeCell ref="BW2:BW7"/>
+    <mergeCell ref="BX2:BX7"/>
+    <mergeCell ref="BY2:BY7"/>
+    <mergeCell ref="BZ2:BZ7"/>
+    <mergeCell ref="X2:X7"/>
+    <mergeCell ref="AF2:AF7"/>
+    <mergeCell ref="AX2:AX7"/>
+    <mergeCell ref="AY2:AY7"/>
+    <mergeCell ref="AZ2:AZ7"/>
+    <mergeCell ref="BL2:BL7"/>
+    <mergeCell ref="BA2:BA7"/>
+    <mergeCell ref="BB2:BB7"/>
+    <mergeCell ref="BC2:BC7"/>
+    <mergeCell ref="AP2:AP7"/>
+    <mergeCell ref="AQ2:AQ7"/>
+    <mergeCell ref="AR2:AR7"/>
+    <mergeCell ref="AS2:AS7"/>
+    <mergeCell ref="AT2:AT7"/>
+    <mergeCell ref="AU2:AU7"/>
+    <mergeCell ref="AV2:AV7"/>
+    <mergeCell ref="AW2:AW7"/>
+    <mergeCell ref="BD2:BD7"/>
+    <mergeCell ref="BE2:BE7"/>
+    <mergeCell ref="BF2:BF7"/>
+    <mergeCell ref="BG2:BG7"/>
+    <mergeCell ref="BH2:BH7"/>
+    <mergeCell ref="BI2:BI7"/>
+    <mergeCell ref="BJ2:BJ7"/>
+    <mergeCell ref="N2:N7"/>
+    <mergeCell ref="O2:O7"/>
+    <mergeCell ref="P2:P7"/>
+    <mergeCell ref="Q2:Q7"/>
+    <mergeCell ref="R2:R7"/>
+    <mergeCell ref="S2:S7"/>
+    <mergeCell ref="T2:T7"/>
+    <mergeCell ref="CN8:CN9"/>
+    <mergeCell ref="Y2:Y7"/>
+    <mergeCell ref="Z2:Z7"/>
+    <mergeCell ref="AA2:AA7"/>
+    <mergeCell ref="AB2:AB7"/>
+    <mergeCell ref="AC2:AC7"/>
+    <mergeCell ref="AD2:AD7"/>
+    <mergeCell ref="AE2:AE7"/>
+    <mergeCell ref="AH2:AH7"/>
+    <mergeCell ref="AI2:AI7"/>
+    <mergeCell ref="AJ2:AJ7"/>
+    <mergeCell ref="AK2:AK7"/>
+    <mergeCell ref="AL2:AL7"/>
+    <mergeCell ref="AM2:AM7"/>
+    <mergeCell ref="AN2:AN7"/>
+    <mergeCell ref="AO2:AO7"/>
+    <mergeCell ref="AG2:AG7"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="F2:F7"/>
+    <mergeCell ref="G2:G7"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="I2:I7"/>
+    <mergeCell ref="J2:J7"/>
+    <mergeCell ref="K2:K7"/>
+    <mergeCell ref="L2:L7"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="M2:M7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="E26:DT26"/>
+    <mergeCell ref="DF8:DF9"/>
+    <mergeCell ref="DQ8:DQ9"/>
+    <mergeCell ref="DR8:DR9"/>
+    <mergeCell ref="DS8:DS9"/>
+    <mergeCell ref="DT8:DT9"/>
+    <mergeCell ref="CY8:CY9"/>
+    <mergeCell ref="CZ8:CZ9"/>
+    <mergeCell ref="CM8:CM9"/>
+    <mergeCell ref="CW8:CW9"/>
+    <mergeCell ref="CX8:CX9"/>
+    <mergeCell ref="BU8:BU9"/>
+    <mergeCell ref="BV8:BV9"/>
+    <mergeCell ref="BW8:BW9"/>
+    <mergeCell ref="BF8:BF9"/>
+    <mergeCell ref="BG8:BG9"/>
+    <mergeCell ref="CG8:CG9"/>
+    <mergeCell ref="CH8:CH9"/>
+    <mergeCell ref="AW8:AW9"/>
+    <mergeCell ref="AX8:AX9"/>
+    <mergeCell ref="AY8:AY9"/>
+    <mergeCell ref="AZ8:AZ9"/>
+    <mergeCell ref="BA8:BA9"/>
+    <mergeCell ref="BB8:BB9"/>
+    <mergeCell ref="CB8:CB9"/>
+    <mergeCell ref="CC8:CC9"/>
+    <mergeCell ref="CD8:CD9"/>
+    <mergeCell ref="CE8:CE9"/>
+    <mergeCell ref="CF8:CF9"/>
+    <mergeCell ref="CV8:CV9"/>
+    <mergeCell ref="BQ2:BQ7"/>
+    <mergeCell ref="BR2:BR7"/>
+    <mergeCell ref="BS2:BS7"/>
+    <mergeCell ref="BT2:BT7"/>
+    <mergeCell ref="BU2:BU7"/>
+    <mergeCell ref="BV2:BV7"/>
+    <mergeCell ref="CO8:CO9"/>
+    <mergeCell ref="CP8:CP9"/>
+    <mergeCell ref="CH2:CH7"/>
+    <mergeCell ref="CT8:CT9"/>
+    <mergeCell ref="CU8:CU9"/>
+    <mergeCell ref="CB2:CB7"/>
+    <mergeCell ref="CC2:CC7"/>
+    <mergeCell ref="CD2:CD7"/>
+    <mergeCell ref="CE2:CE7"/>
+    <mergeCell ref="CF2:CF7"/>
+    <mergeCell ref="CG2:CG7"/>
+    <mergeCell ref="CJ8:CJ9"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="BO8:BO9"/>
+    <mergeCell ref="BP8:BP9"/>
+    <mergeCell ref="BQ8:BQ9"/>
+    <mergeCell ref="BR8:BR9"/>
+    <mergeCell ref="BS8:BS9"/>
+    <mergeCell ref="BT8:BT9"/>
+    <mergeCell ref="BZ8:BZ9"/>
+    <mergeCell ref="CA8:CA9"/>
+    <mergeCell ref="BH8:BH9"/>
+    <mergeCell ref="BI8:BI9"/>
+    <mergeCell ref="BJ8:BJ9"/>
+    <mergeCell ref="BK8:BK9"/>
+    <mergeCell ref="BL8:BL9"/>
+    <mergeCell ref="BM8:BM9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="N1:Q1"/>
     <mergeCell ref="BC8:BC9"/>
@@ -5121,248 +5376,6 @@
     <mergeCell ref="AL8:AL9"/>
     <mergeCell ref="AM8:AM9"/>
     <mergeCell ref="V8:V9"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="BO8:BO9"/>
-    <mergeCell ref="BP8:BP9"/>
-    <mergeCell ref="BQ8:BQ9"/>
-    <mergeCell ref="BR8:BR9"/>
-    <mergeCell ref="BS8:BS9"/>
-    <mergeCell ref="BT8:BT9"/>
-    <mergeCell ref="BZ8:BZ9"/>
-    <mergeCell ref="CA8:CA9"/>
-    <mergeCell ref="BH8:BH9"/>
-    <mergeCell ref="BI8:BI9"/>
-    <mergeCell ref="BJ8:BJ9"/>
-    <mergeCell ref="BK8:BK9"/>
-    <mergeCell ref="BL8:BL9"/>
-    <mergeCell ref="BM8:BM9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="CB8:CB9"/>
-    <mergeCell ref="CC8:CC9"/>
-    <mergeCell ref="CD8:CD9"/>
-    <mergeCell ref="CE8:CE9"/>
-    <mergeCell ref="CF8:CF9"/>
-    <mergeCell ref="CV8:CV9"/>
-    <mergeCell ref="BQ2:BQ7"/>
-    <mergeCell ref="BR2:BR7"/>
-    <mergeCell ref="BS2:BS7"/>
-    <mergeCell ref="BT2:BT7"/>
-    <mergeCell ref="BU2:BU7"/>
-    <mergeCell ref="BV2:BV7"/>
-    <mergeCell ref="CO8:CO9"/>
-    <mergeCell ref="CP8:CP9"/>
-    <mergeCell ref="CH2:CH7"/>
-    <mergeCell ref="CT8:CT9"/>
-    <mergeCell ref="CU8:CU9"/>
-    <mergeCell ref="CB2:CB7"/>
-    <mergeCell ref="CC2:CC7"/>
-    <mergeCell ref="CD2:CD7"/>
-    <mergeCell ref="CE2:CE7"/>
-    <mergeCell ref="CF2:CF7"/>
-    <mergeCell ref="CG2:CG7"/>
-    <mergeCell ref="CJ8:CJ9"/>
-    <mergeCell ref="E26:DT26"/>
-    <mergeCell ref="DF8:DF9"/>
-    <mergeCell ref="DQ8:DQ9"/>
-    <mergeCell ref="DR8:DR9"/>
-    <mergeCell ref="DS8:DS9"/>
-    <mergeCell ref="DT8:DT9"/>
-    <mergeCell ref="CY8:CY9"/>
-    <mergeCell ref="CZ8:CZ9"/>
-    <mergeCell ref="CM8:CM9"/>
-    <mergeCell ref="CW8:CW9"/>
-    <mergeCell ref="CX8:CX9"/>
-    <mergeCell ref="BU8:BU9"/>
-    <mergeCell ref="BV8:BV9"/>
-    <mergeCell ref="BW8:BW9"/>
-    <mergeCell ref="BF8:BF9"/>
-    <mergeCell ref="BG8:BG9"/>
-    <mergeCell ref="CG8:CG9"/>
-    <mergeCell ref="CH8:CH9"/>
-    <mergeCell ref="AW8:AW9"/>
-    <mergeCell ref="AX8:AX9"/>
-    <mergeCell ref="AY8:AY9"/>
-    <mergeCell ref="AZ8:AZ9"/>
-    <mergeCell ref="BA8:BA9"/>
-    <mergeCell ref="BB8:BB9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="F2:F7"/>
-    <mergeCell ref="G2:G7"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="I2:I7"/>
-    <mergeCell ref="J2:J7"/>
-    <mergeCell ref="K2:K7"/>
-    <mergeCell ref="L2:L7"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="M2:M7"/>
-    <mergeCell ref="N2:N7"/>
-    <mergeCell ref="O2:O7"/>
-    <mergeCell ref="P2:P7"/>
-    <mergeCell ref="Q2:Q7"/>
-    <mergeCell ref="R2:R7"/>
-    <mergeCell ref="S2:S7"/>
-    <mergeCell ref="T2:T7"/>
-    <mergeCell ref="CN8:CN9"/>
-    <mergeCell ref="Y2:Y7"/>
-    <mergeCell ref="Z2:Z7"/>
-    <mergeCell ref="AA2:AA7"/>
-    <mergeCell ref="AB2:AB7"/>
-    <mergeCell ref="AC2:AC7"/>
-    <mergeCell ref="AD2:AD7"/>
-    <mergeCell ref="AE2:AE7"/>
-    <mergeCell ref="AH2:AH7"/>
-    <mergeCell ref="AI2:AI7"/>
-    <mergeCell ref="AJ2:AJ7"/>
-    <mergeCell ref="AK2:AK7"/>
-    <mergeCell ref="AL2:AL7"/>
-    <mergeCell ref="AM2:AM7"/>
-    <mergeCell ref="AN2:AN7"/>
-    <mergeCell ref="AO2:AO7"/>
-    <mergeCell ref="AG2:AG7"/>
-    <mergeCell ref="X2:X7"/>
-    <mergeCell ref="AF2:AF7"/>
-    <mergeCell ref="AX2:AX7"/>
-    <mergeCell ref="AY2:AY7"/>
-    <mergeCell ref="AZ2:AZ7"/>
-    <mergeCell ref="BL2:BL7"/>
-    <mergeCell ref="BA2:BA7"/>
-    <mergeCell ref="BB2:BB7"/>
-    <mergeCell ref="BC2:BC7"/>
-    <mergeCell ref="AP2:AP7"/>
-    <mergeCell ref="AQ2:AQ7"/>
-    <mergeCell ref="AR2:AR7"/>
-    <mergeCell ref="AS2:AS7"/>
-    <mergeCell ref="AT2:AT7"/>
-    <mergeCell ref="AU2:AU7"/>
-    <mergeCell ref="AV2:AV7"/>
-    <mergeCell ref="AW2:AW7"/>
-    <mergeCell ref="BD2:BD7"/>
-    <mergeCell ref="BE2:BE7"/>
-    <mergeCell ref="BF2:BF7"/>
-    <mergeCell ref="BG2:BG7"/>
-    <mergeCell ref="BM2:BM7"/>
-    <mergeCell ref="BN2:BN7"/>
-    <mergeCell ref="BO2:BO7"/>
-    <mergeCell ref="BP2:BP7"/>
-    <mergeCell ref="CA2:CA7"/>
-    <mergeCell ref="BW2:BW7"/>
-    <mergeCell ref="BX2:BX7"/>
-    <mergeCell ref="BY2:BY7"/>
-    <mergeCell ref="BZ2:BZ7"/>
-    <mergeCell ref="BH2:BH7"/>
-    <mergeCell ref="BI2:BI7"/>
-    <mergeCell ref="BJ2:BJ7"/>
-    <mergeCell ref="BK2:BK7"/>
-    <mergeCell ref="BN8:BN9"/>
-    <mergeCell ref="CI8:CI9"/>
-    <mergeCell ref="CK8:CK9"/>
-    <mergeCell ref="CL8:CL9"/>
-    <mergeCell ref="BX8:BX9"/>
-    <mergeCell ref="BY8:BY9"/>
-    <mergeCell ref="DL2:DL7"/>
-    <mergeCell ref="DM2:DM7"/>
-    <mergeCell ref="DF2:DF7"/>
-    <mergeCell ref="CW2:CW7"/>
-    <mergeCell ref="CU2:CU7"/>
-    <mergeCell ref="CV2:CV7"/>
-    <mergeCell ref="CQ2:CQ7"/>
-    <mergeCell ref="CR2:CR7"/>
-    <mergeCell ref="CS2:CS7"/>
-    <mergeCell ref="CT2:CT7"/>
-    <mergeCell ref="CI2:CI7"/>
-    <mergeCell ref="CJ2:CJ7"/>
-    <mergeCell ref="CK2:CK7"/>
-    <mergeCell ref="CL2:CL7"/>
-    <mergeCell ref="CM2:CM7"/>
-    <mergeCell ref="CN2:CN7"/>
-    <mergeCell ref="CO2:CO7"/>
-    <mergeCell ref="CP2:CP7"/>
-    <mergeCell ref="V2:V7"/>
-    <mergeCell ref="W2:W7"/>
-    <mergeCell ref="F27:S27"/>
-    <mergeCell ref="T27:AW27"/>
-    <mergeCell ref="AX27:CD27"/>
-    <mergeCell ref="CE27:DT27"/>
-    <mergeCell ref="DG8:DG9"/>
-    <mergeCell ref="DH8:DH9"/>
-    <mergeCell ref="DI8:DI9"/>
-    <mergeCell ref="DJ8:DJ9"/>
-    <mergeCell ref="DK8:DK9"/>
-    <mergeCell ref="DL8:DL9"/>
-    <mergeCell ref="DM8:DM9"/>
-    <mergeCell ref="DN8:DN9"/>
-    <mergeCell ref="DO8:DO9"/>
-    <mergeCell ref="DP8:DP9"/>
-    <mergeCell ref="DA8:DA9"/>
-    <mergeCell ref="DB8:DB9"/>
-    <mergeCell ref="DC8:DC9"/>
-    <mergeCell ref="DD8:DD9"/>
-    <mergeCell ref="DE8:DE9"/>
-    <mergeCell ref="CQ8:CQ9"/>
-    <mergeCell ref="CR8:CR9"/>
-    <mergeCell ref="CS8:CS9"/>
-    <mergeCell ref="AD1:AG1"/>
-    <mergeCell ref="V1:Y1"/>
-    <mergeCell ref="R1:U1"/>
-    <mergeCell ref="DQ2:DQ7"/>
-    <mergeCell ref="DR2:DR7"/>
-    <mergeCell ref="DS2:DS7"/>
-    <mergeCell ref="DT2:DT7"/>
-    <mergeCell ref="CX2:CX7"/>
-    <mergeCell ref="CY2:CY7"/>
-    <mergeCell ref="DA2:DA7"/>
-    <mergeCell ref="DB2:DB7"/>
-    <mergeCell ref="DC2:DC7"/>
-    <mergeCell ref="DD2:DD7"/>
-    <mergeCell ref="DE2:DE7"/>
-    <mergeCell ref="CZ2:CZ7"/>
-    <mergeCell ref="DN2:DN7"/>
-    <mergeCell ref="DO2:DO7"/>
-    <mergeCell ref="DP2:DP7"/>
-    <mergeCell ref="DG2:DG7"/>
-    <mergeCell ref="DH2:DH7"/>
-    <mergeCell ref="DI2:DI7"/>
-    <mergeCell ref="DJ2:DJ7"/>
-    <mergeCell ref="DK2:DK7"/>
-    <mergeCell ref="U2:U7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -5384,49 +5397,49 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="61" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="60" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="63" t="s">
+      <c r="B3" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="64"/>
-      <c r="D3" s="67" t="s">
+      <c r="C3" s="63"/>
+      <c r="D3" s="66" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="60" t="s">
+      <c r="F3" s="59" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="60" t="s">
-        <v>40</v>
-      </c>
-      <c r="G3" s="60" t="s">
+      <c r="H3" s="60" t="s">
         <v>38</v>
-      </c>
-      <c r="H3" s="61" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="48"/>
-      <c r="B4" s="65"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="61"/>
+      <c r="A4" s="35"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="60"/>
     </row>
     <row r="5" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
@@ -5438,23 +5451,23 @@
       <c r="C5" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="19">
-        <f>COUNTIF(cms!F11:G11,0)</f>
+      <c r="D5" s="18">
+        <f>COUNTIF(Angular!F11:G11,0)</f>
         <v>0</v>
       </c>
-      <c r="E5" s="19">
-        <f>COUNTIF(cms!H11:Y11,0)</f>
+      <c r="E5" s="18">
+        <f>COUNTIF(Angular!H11:Y11,0)</f>
         <v>2</v>
       </c>
-      <c r="F5" s="19">
-        <f>COUNTIF(cms!Z11:AY11,0)</f>
+      <c r="F5" s="18">
+        <f>COUNTIF(Angular!Z11:AY11,0)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="19">
-        <f>COUNTIF(cms!AZ11:BU11,0)</f>
+      <c r="G5" s="18">
+        <f>COUNTIF(Angular!AZ11:BU11,0)</f>
         <v>0</v>
       </c>
-      <c r="H5" s="20"/>
+      <c r="H5" s="19"/>
     </row>
     <row r="6" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
@@ -5466,23 +5479,23 @@
       <c r="C6" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="19" t="e">
-        <f>COUNTIF(cms!#REF!,0)</f>
+      <c r="D6" s="18" t="e">
+        <f>COUNTIF(Angular!#REF!,0)</f>
         <v>#REF!</v>
       </c>
-      <c r="E6" s="19" t="e">
-        <f>COUNTIF(cms!#REF!,0)</f>
+      <c r="E6" s="18" t="e">
+        <f>COUNTIF(Angular!#REF!,0)</f>
         <v>#REF!</v>
       </c>
-      <c r="F6" s="19" t="e">
-        <f>COUNTIF(cms!#REF!,0)</f>
+      <c r="F6" s="18" t="e">
+        <f>COUNTIF(Angular!#REF!,0)</f>
         <v>#REF!</v>
       </c>
-      <c r="G6" s="19" t="e">
-        <f>COUNTIF(cms!#REF!,0)</f>
+      <c r="G6" s="18" t="e">
+        <f>COUNTIF(Angular!#REF!,0)</f>
         <v>#REF!</v>
       </c>
-      <c r="H6" s="20"/>
+      <c r="H6" s="19"/>
     </row>
     <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
@@ -5494,23 +5507,23 @@
       <c r="C7" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="19">
-        <f>COUNTIF(cms!F12:G12,0)</f>
+      <c r="D7" s="18">
+        <f>COUNTIF(Angular!F12:G12,0)</f>
         <v>0</v>
       </c>
-      <c r="E7" s="19">
-        <f>COUNTIF(cms!H12:Y12,0)</f>
+      <c r="E7" s="18">
+        <f>COUNTIF(Angular!H12:Y12,0)</f>
         <v>2</v>
       </c>
-      <c r="F7" s="19">
-        <f>COUNTIF(cms!Z12:AY12,0)</f>
+      <c r="F7" s="18">
+        <f>COUNTIF(Angular!Z12:AY12,0)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="19">
-        <f>COUNTIF(cms!AZ12:BU12,0)</f>
+      <c r="G7" s="18">
+        <f>COUNTIF(Angular!AZ12:BU12,0)</f>
         <v>0</v>
       </c>
-      <c r="H7" s="20"/>
+      <c r="H7" s="19"/>
     </row>
     <row r="8" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
@@ -5522,23 +5535,23 @@
       <c r="C8" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="19">
-        <f>COUNTIF(cms!F13:G13,0)</f>
+      <c r="D8" s="18">
+        <f>COUNTIF(Angular!F13:G13,0)</f>
         <v>0</v>
       </c>
-      <c r="E8" s="19">
-        <f>COUNTIF(cms!H13:Y13,0)</f>
+      <c r="E8" s="18">
+        <f>COUNTIF(Angular!H13:Y13,0)</f>
         <v>2</v>
       </c>
-      <c r="F8" s="19">
-        <f>COUNTIF(cms!Z13:AY13,0)</f>
+      <c r="F8" s="18">
+        <f>COUNTIF(Angular!Z13:AY13,0)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="19">
-        <f>COUNTIF(cms!AZ13:BU13,0)</f>
+      <c r="G8" s="18">
+        <f>COUNTIF(Angular!AZ13:BU13,0)</f>
         <v>0</v>
       </c>
-      <c r="H8" s="20"/>
+      <c r="H8" s="19"/>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
@@ -5550,23 +5563,23 @@
       <c r="C9" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="19" t="e">
-        <f>COUNTIF(cms!#REF!,0)</f>
+      <c r="D9" s="18" t="e">
+        <f>COUNTIF(Angular!#REF!,0)</f>
         <v>#REF!</v>
       </c>
-      <c r="E9" s="19" t="e">
-        <f>COUNTIF(cms!#REF!,0)</f>
+      <c r="E9" s="18" t="e">
+        <f>COUNTIF(Angular!#REF!,0)</f>
         <v>#REF!</v>
       </c>
-      <c r="F9" s="19" t="e">
-        <f>COUNTIF(cms!#REF!,0)</f>
+      <c r="F9" s="18" t="e">
+        <f>COUNTIF(Angular!#REF!,0)</f>
         <v>#REF!</v>
       </c>
-      <c r="G9" s="19" t="e">
-        <f>COUNTIF(cms!#REF!,0)</f>
+      <c r="G9" s="18" t="e">
+        <f>COUNTIF(Angular!#REF!,0)</f>
         <v>#REF!</v>
       </c>
-      <c r="H9" s="20"/>
+      <c r="H9" s="19"/>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
@@ -5578,23 +5591,23 @@
       <c r="C10" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="19">
-        <f>COUNTIF(cms!F14:G14,0)</f>
+      <c r="D10" s="18">
+        <f>COUNTIF(Angular!F14:G14,0)</f>
         <v>0</v>
       </c>
-      <c r="E10" s="19">
-        <f>COUNTIF(cms!H14:Y14,0)</f>
+      <c r="E10" s="18">
+        <f>COUNTIF(Angular!H14:Y14,0)</f>
         <v>2</v>
       </c>
-      <c r="F10" s="19">
-        <f>COUNTIF(cms!Z14:AY14,0)</f>
+      <c r="F10" s="18">
+        <f>COUNTIF(Angular!Z14:AY14,0)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="19">
-        <f>COUNTIF(cms!AZ14:BU14,0)</f>
+      <c r="G10" s="18">
+        <f>COUNTIF(Angular!AZ14:BU14,0)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="20"/>
+      <c r="H10" s="19"/>
     </row>
     <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
@@ -5606,23 +5619,23 @@
       <c r="C11" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="19">
-        <f>COUNTIF(cms!F15:G15,0)</f>
+      <c r="D11" s="18">
+        <f>COUNTIF(Angular!F15:G15,0)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="19">
-        <f>COUNTIF(cms!H15:Y15,0)</f>
+      <c r="E11" s="18">
+        <f>COUNTIF(Angular!H15:Y15,0)</f>
         <v>2</v>
       </c>
-      <c r="F11" s="19">
-        <f>COUNTIF(cms!Z15:AY15,0)</f>
+      <c r="F11" s="18">
+        <f>COUNTIF(Angular!Z15:AY15,0)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="19">
-        <f>COUNTIF(cms!AZ15:BU15,0)</f>
+      <c r="G11" s="18">
+        <f>COUNTIF(Angular!AZ15:BU15,0)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="20"/>
+      <c r="H11" s="19"/>
     </row>
     <row r="12" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
@@ -5634,23 +5647,23 @@
       <c r="C12" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="19">
-        <f>COUNTIF(cms!F16:G16,0)</f>
+      <c r="D12" s="18">
+        <f>COUNTIF(Angular!F16:G16,0)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="19">
-        <f>COUNTIF(cms!H16:Y16,0)</f>
+      <c r="E12" s="18">
+        <f>COUNTIF(Angular!H16:Y16,0)</f>
         <v>2</v>
       </c>
-      <c r="F12" s="19">
-        <f>COUNTIF(cms!Z16:AY16,0)</f>
+      <c r="F12" s="18">
+        <f>COUNTIF(Angular!Z16:AY16,0)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="19">
-        <f>COUNTIF(cms!AZ16:BU16,0)</f>
+      <c r="G12" s="18">
+        <f>COUNTIF(Angular!AZ16:BU16,0)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="20"/>
+      <c r="H12" s="19"/>
     </row>
     <row r="13" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
@@ -5662,23 +5675,23 @@
       <c r="C13" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="19" t="e">
-        <f>COUNTIF(cms!#REF!,0)</f>
+      <c r="D13" s="18" t="e">
+        <f>COUNTIF(Angular!#REF!,0)</f>
         <v>#REF!</v>
       </c>
-      <c r="E13" s="19" t="e">
-        <f>COUNTIF(cms!#REF!,0)</f>
+      <c r="E13" s="18" t="e">
+        <f>COUNTIF(Angular!#REF!,0)</f>
         <v>#REF!</v>
       </c>
-      <c r="F13" s="19" t="e">
-        <f>COUNTIF(cms!#REF!,0)</f>
+      <c r="F13" s="18" t="e">
+        <f>COUNTIF(Angular!#REF!,0)</f>
         <v>#REF!</v>
       </c>
-      <c r="G13" s="19" t="e">
-        <f>COUNTIF(cms!#REF!,0)</f>
+      <c r="G13" s="18" t="e">
+        <f>COUNTIF(Angular!#REF!,0)</f>
         <v>#REF!</v>
       </c>
-      <c r="H13" s="20"/>
+      <c r="H13" s="19"/>
     </row>
     <row r="14" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
@@ -5690,23 +5703,23 @@
       <c r="C14" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="19">
-        <f>COUNTIF(cms!F17:G17,0)</f>
-        <v>1</v>
-      </c>
-      <c r="E14" s="19">
-        <f>COUNTIF(cms!H17:Y17,0)</f>
-        <v>1</v>
-      </c>
-      <c r="F14" s="19">
-        <f>COUNTIF(cms!Z17:AY17,0)</f>
+      <c r="D14" s="18">
+        <f>COUNTIF(Angular!F17:G17,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E14" s="18">
+        <f>COUNTIF(Angular!H17:Y17,0)</f>
+        <v>1</v>
+      </c>
+      <c r="F14" s="18">
+        <f>COUNTIF(Angular!Z17:AY17,0)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="19">
-        <f>COUNTIF(cms!AZ17:BU17,0)</f>
+      <c r="G14" s="18">
+        <f>COUNTIF(Angular!AZ17:BU17,0)</f>
         <v>0</v>
       </c>
-      <c r="H14" s="20"/>
+      <c r="H14" s="19"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
@@ -5718,23 +5731,23 @@
       <c r="C15" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="19">
-        <f>COUNTIF(cms!F18:G18,0)</f>
+      <c r="D15" s="18">
+        <f>COUNTIF(Angular!F18:G18,0)</f>
         <v>2</v>
       </c>
-      <c r="E15" s="19">
-        <f>COUNTIF(cms!H18:Y18,0)</f>
+      <c r="E15" s="18">
+        <f>COUNTIF(Angular!H18:Y18,0)</f>
         <v>3</v>
       </c>
-      <c r="F15" s="19">
-        <f>COUNTIF(cms!Z18:AY18,0)</f>
+      <c r="F15" s="18">
+        <f>COUNTIF(Angular!Z18:AY18,0)</f>
         <v>0</v>
       </c>
-      <c r="G15" s="19">
-        <f>COUNTIF(cms!AZ18:BU18,0)</f>
+      <c r="G15" s="18">
+        <f>COUNTIF(Angular!AZ18:BU18,0)</f>
         <v>0</v>
       </c>
-      <c r="H15" s="20"/>
+      <c r="H15" s="19"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
@@ -5742,11 +5755,11 @@
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
@@ -5754,11 +5767,11 @@
       </c>
       <c r="B17" s="13"/>
       <c r="C17" s="10"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
@@ -5766,11 +5779,11 @@
       </c>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
@@ -5778,11 +5791,11 @@
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
@@ -5790,11 +5803,11 @@
       </c>
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
@@ -5802,11 +5815,11 @@
       </c>
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
@@ -5814,11 +5827,11 @@
       </c>
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
@@ -5826,11 +5839,11 @@
       </c>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="9">

--- a/Journals/Angular ჟურნალი.xlsx
+++ b/Journals/Angular ჟურნალი.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="45">
   <si>
     <t>რიცხვი</t>
   </si>
@@ -152,6 +152,9 @@
   </si>
   <si>
     <t>Angular</t>
+  </si>
+  <si>
+    <t>თვის დასასრული</t>
   </si>
 </sst>
 </file>
@@ -497,7 +500,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -550,6 +553,12 @@
     <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="2" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -565,96 +574,96 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="16" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="16" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -682,12 +691,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -904,7 +908,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:DU30"/>
+  <dimension ref="A1:DU31"/>
   <sheetFormatPr defaultColWidth="3.5703125" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.5703125" style="2"/>
@@ -922,58 +926,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="40"/>
-      <c r="F1" s="24">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="42"/>
+      <c r="F1" s="26">
         <v>8</v>
       </c>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="24">
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="26">
         <v>4</v>
       </c>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="24">
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="26">
         <v>4</v>
       </c>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="26"/>
-      <c r="R1" s="24">
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="26">
         <v>4</v>
       </c>
-      <c r="S1" s="25"/>
-      <c r="T1" s="25"/>
-      <c r="U1" s="26"/>
-      <c r="V1" s="24">
+      <c r="S1" s="27"/>
+      <c r="T1" s="27"/>
+      <c r="U1" s="28"/>
+      <c r="V1" s="26">
         <v>4</v>
       </c>
-      <c r="W1" s="25"/>
-      <c r="X1" s="25"/>
-      <c r="Y1" s="26"/>
-      <c r="Z1" s="24"/>
-      <c r="AA1" s="25"/>
-      <c r="AB1" s="25"/>
-      <c r="AC1" s="26"/>
-      <c r="AD1" s="24">
+      <c r="W1" s="27"/>
+      <c r="X1" s="27"/>
+      <c r="Y1" s="28"/>
+      <c r="Z1" s="26"/>
+      <c r="AA1" s="27"/>
+      <c r="AB1" s="27"/>
+      <c r="AC1" s="28"/>
+      <c r="AD1" s="26">
         <v>4</v>
       </c>
-      <c r="AE1" s="25"/>
-      <c r="AF1" s="25"/>
-      <c r="AG1" s="26"/>
-      <c r="AH1" s="24">
+      <c r="AE1" s="27"/>
+      <c r="AF1" s="27"/>
+      <c r="AG1" s="28"/>
+      <c r="AH1" s="26">
         <v>4</v>
       </c>
-      <c r="AI1" s="25"/>
-      <c r="AJ1" s="25"/>
-      <c r="AK1" s="26"/>
+      <c r="AI1" s="27"/>
+      <c r="AJ1" s="27"/>
+      <c r="AK1" s="28"/>
       <c r="AL1" s="22"/>
       <c r="AM1" s="22"/>
       <c r="AN1" s="22"/>
@@ -1067,1349 +1071,1349 @@
       </c>
     </row>
     <row r="2" spans="1:125" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="41"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="44" t="s">
+      <c r="A2" s="43"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="29">
+      <c r="F2" s="24">
         <v>46276</v>
       </c>
-      <c r="G2" s="29">
+      <c r="G2" s="24">
         <v>46276</v>
       </c>
-      <c r="H2" s="29">
+      <c r="H2" s="24">
         <v>46276</v>
       </c>
-      <c r="I2" s="29">
+      <c r="I2" s="24">
         <v>46276</v>
       </c>
-      <c r="J2" s="29">
+      <c r="J2" s="24">
         <v>46283</v>
       </c>
-      <c r="K2" s="29">
+      <c r="K2" s="24">
         <v>46283</v>
       </c>
-      <c r="L2" s="29">
+      <c r="L2" s="24">
         <v>46283</v>
       </c>
-      <c r="M2" s="29">
+      <c r="M2" s="24">
         <v>46283</v>
       </c>
-      <c r="N2" s="29">
+      <c r="N2" s="24">
         <v>46290</v>
       </c>
-      <c r="O2" s="29">
+      <c r="O2" s="24">
         <v>46290</v>
       </c>
-      <c r="P2" s="68">
+      <c r="P2" s="36">
         <v>46290</v>
       </c>
-      <c r="Q2" s="68">
+      <c r="Q2" s="36">
         <v>46290</v>
       </c>
-      <c r="R2" s="29">
+      <c r="R2" s="24">
         <v>46297</v>
       </c>
-      <c r="S2" s="29">
+      <c r="S2" s="24">
         <v>46297</v>
       </c>
-      <c r="T2" s="29">
+      <c r="T2" s="24">
         <v>46297</v>
       </c>
-      <c r="U2" s="29">
+      <c r="U2" s="24">
         <v>46297</v>
       </c>
-      <c r="V2" s="54">
+      <c r="V2" s="31">
         <v>46304</v>
       </c>
-      <c r="W2" s="54">
+      <c r="W2" s="31">
         <v>46304</v>
       </c>
-      <c r="X2" s="29">
+      <c r="X2" s="24">
         <v>46304</v>
       </c>
-      <c r="Y2" s="29">
+      <c r="Y2" s="24">
         <v>46304</v>
       </c>
-      <c r="Z2" s="52">
+      <c r="Z2" s="38">
         <v>46311</v>
       </c>
-      <c r="AA2" s="52">
+      <c r="AA2" s="38">
         <v>46311</v>
       </c>
-      <c r="AB2" s="52">
+      <c r="AB2" s="38">
         <v>46311</v>
       </c>
-      <c r="AC2" s="52">
+      <c r="AC2" s="38">
         <v>46311</v>
       </c>
-      <c r="AD2" s="29">
+      <c r="AD2" s="24">
         <v>46318</v>
       </c>
-      <c r="AE2" s="29">
+      <c r="AE2" s="24">
         <v>46318</v>
       </c>
-      <c r="AF2" s="29">
+      <c r="AF2" s="24">
         <v>46318</v>
       </c>
-      <c r="AG2" s="29">
+      <c r="AG2" s="24">
         <v>46318</v>
       </c>
-      <c r="AH2" s="68">
+      <c r="AH2" s="36">
         <v>46325</v>
       </c>
-      <c r="AI2" s="68">
+      <c r="AI2" s="36">
         <v>46325</v>
       </c>
-      <c r="AJ2" s="68">
+      <c r="AJ2" s="36">
         <v>46325</v>
       </c>
-      <c r="AK2" s="68">
+      <c r="AK2" s="36">
         <v>46325</v>
       </c>
-      <c r="AL2" s="29"/>
-      <c r="AM2" s="29"/>
-      <c r="AN2" s="29"/>
-      <c r="AO2" s="29"/>
-      <c r="AP2" s="29"/>
-      <c r="AQ2" s="29"/>
-      <c r="AR2" s="29"/>
-      <c r="AS2" s="29"/>
-      <c r="AT2" s="29"/>
-      <c r="AU2" s="29"/>
-      <c r="AV2" s="29"/>
-      <c r="AW2" s="29"/>
-      <c r="AX2" s="29"/>
-      <c r="AY2" s="29"/>
-      <c r="AZ2" s="29"/>
-      <c r="BA2" s="29"/>
-      <c r="BB2" s="29"/>
-      <c r="BC2" s="29"/>
-      <c r="BD2" s="29"/>
-      <c r="BE2" s="29"/>
-      <c r="BF2" s="29"/>
-      <c r="BG2" s="29"/>
-      <c r="BH2" s="29"/>
-      <c r="BI2" s="29"/>
-      <c r="BJ2" s="29"/>
-      <c r="BK2" s="29"/>
-      <c r="BL2" s="29"/>
-      <c r="BM2" s="29"/>
-      <c r="BN2" s="29"/>
-      <c r="BO2" s="29"/>
-      <c r="BP2" s="29"/>
-      <c r="BQ2" s="29"/>
-      <c r="BR2" s="29"/>
-      <c r="BS2" s="29"/>
-      <c r="BT2" s="29"/>
-      <c r="BU2" s="29"/>
-      <c r="BV2" s="29"/>
-      <c r="BW2" s="29"/>
-      <c r="BX2" s="29"/>
-      <c r="BY2" s="29"/>
-      <c r="BZ2" s="29"/>
-      <c r="CA2" s="29"/>
-      <c r="CB2" s="29"/>
-      <c r="CC2" s="29"/>
-      <c r="CD2" s="29"/>
-      <c r="CE2" s="29"/>
-      <c r="CF2" s="29"/>
-      <c r="CG2" s="29"/>
-      <c r="CH2" s="29"/>
-      <c r="CI2" s="29"/>
-      <c r="CJ2" s="29"/>
-      <c r="CK2" s="29"/>
-      <c r="CL2" s="29"/>
-      <c r="CM2" s="29"/>
-      <c r="CN2" s="29"/>
-      <c r="CO2" s="29"/>
-      <c r="CP2" s="29"/>
-      <c r="CQ2" s="29"/>
-      <c r="CR2" s="29"/>
-      <c r="CS2" s="29"/>
-      <c r="CT2" s="29"/>
-      <c r="CU2" s="29"/>
-      <c r="CV2" s="29"/>
-      <c r="CW2" s="29"/>
-      <c r="CX2" s="29"/>
-      <c r="CY2" s="29"/>
-      <c r="CZ2" s="29"/>
-      <c r="DA2" s="29"/>
-      <c r="DB2" s="29"/>
-      <c r="DC2" s="29"/>
-      <c r="DD2" s="29"/>
-      <c r="DE2" s="29"/>
-      <c r="DF2" s="29"/>
-      <c r="DG2" s="29"/>
-      <c r="DH2" s="29"/>
-      <c r="DI2" s="29"/>
-      <c r="DJ2" s="29"/>
-      <c r="DK2" s="29"/>
-      <c r="DL2" s="29"/>
-      <c r="DM2" s="29"/>
-      <c r="DN2" s="29"/>
-      <c r="DO2" s="29"/>
-      <c r="DP2" s="29"/>
-      <c r="DQ2" s="29"/>
-      <c r="DR2" s="29"/>
-      <c r="DS2" s="29"/>
-      <c r="DT2" s="29"/>
+      <c r="AL2" s="24"/>
+      <c r="AM2" s="24"/>
+      <c r="AN2" s="24"/>
+      <c r="AO2" s="24"/>
+      <c r="AP2" s="24"/>
+      <c r="AQ2" s="24"/>
+      <c r="AR2" s="24"/>
+      <c r="AS2" s="24"/>
+      <c r="AT2" s="24"/>
+      <c r="AU2" s="24"/>
+      <c r="AV2" s="24"/>
+      <c r="AW2" s="24"/>
+      <c r="AX2" s="24"/>
+      <c r="AY2" s="24"/>
+      <c r="AZ2" s="24"/>
+      <c r="BA2" s="24"/>
+      <c r="BB2" s="24"/>
+      <c r="BC2" s="24"/>
+      <c r="BD2" s="24"/>
+      <c r="BE2" s="24"/>
+      <c r="BF2" s="24"/>
+      <c r="BG2" s="24"/>
+      <c r="BH2" s="24"/>
+      <c r="BI2" s="24"/>
+      <c r="BJ2" s="24"/>
+      <c r="BK2" s="24"/>
+      <c r="BL2" s="24"/>
+      <c r="BM2" s="24"/>
+      <c r="BN2" s="24"/>
+      <c r="BO2" s="24"/>
+      <c r="BP2" s="24"/>
+      <c r="BQ2" s="24"/>
+      <c r="BR2" s="24"/>
+      <c r="BS2" s="24"/>
+      <c r="BT2" s="24"/>
+      <c r="BU2" s="24"/>
+      <c r="BV2" s="24"/>
+      <c r="BW2" s="24"/>
+      <c r="BX2" s="24"/>
+      <c r="BY2" s="24"/>
+      <c r="BZ2" s="24"/>
+      <c r="CA2" s="24"/>
+      <c r="CB2" s="24"/>
+      <c r="CC2" s="24"/>
+      <c r="CD2" s="24"/>
+      <c r="CE2" s="24"/>
+      <c r="CF2" s="24"/>
+      <c r="CG2" s="24"/>
+      <c r="CH2" s="24"/>
+      <c r="CI2" s="24"/>
+      <c r="CJ2" s="24"/>
+      <c r="CK2" s="24"/>
+      <c r="CL2" s="24"/>
+      <c r="CM2" s="24"/>
+      <c r="CN2" s="24"/>
+      <c r="CO2" s="24"/>
+      <c r="CP2" s="24"/>
+      <c r="CQ2" s="24"/>
+      <c r="CR2" s="24"/>
+      <c r="CS2" s="24"/>
+      <c r="CT2" s="24"/>
+      <c r="CU2" s="24"/>
+      <c r="CV2" s="24"/>
+      <c r="CW2" s="24"/>
+      <c r="CX2" s="24"/>
+      <c r="CY2" s="24"/>
+      <c r="CZ2" s="24"/>
+      <c r="DA2" s="24"/>
+      <c r="DB2" s="24"/>
+      <c r="DC2" s="24"/>
+      <c r="DD2" s="24"/>
+      <c r="DE2" s="24"/>
+      <c r="DF2" s="24"/>
+      <c r="DG2" s="24"/>
+      <c r="DH2" s="24"/>
+      <c r="DI2" s="24"/>
+      <c r="DJ2" s="24"/>
+      <c r="DK2" s="24"/>
+      <c r="DL2" s="24"/>
+      <c r="DM2" s="24"/>
+      <c r="DN2" s="24"/>
+      <c r="DO2" s="24"/>
+      <c r="DP2" s="24"/>
+      <c r="DQ2" s="24"/>
+      <c r="DR2" s="24"/>
+      <c r="DS2" s="24"/>
+      <c r="DT2" s="24"/>
     </row>
     <row r="3" spans="1:125" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="29"/>
-      <c r="N3" s="29"/>
-      <c r="O3" s="29"/>
-      <c r="P3" s="68"/>
-      <c r="Q3" s="68"/>
-      <c r="R3" s="29"/>
-      <c r="S3" s="29"/>
-      <c r="T3" s="29"/>
-      <c r="U3" s="29"/>
-      <c r="V3" s="54"/>
-      <c r="W3" s="54"/>
-      <c r="X3" s="29"/>
-      <c r="Y3" s="29"/>
-      <c r="Z3" s="52"/>
-      <c r="AA3" s="52"/>
-      <c r="AB3" s="52"/>
-      <c r="AC3" s="52"/>
-      <c r="AD3" s="29"/>
-      <c r="AE3" s="29"/>
-      <c r="AF3" s="29"/>
-      <c r="AG3" s="29"/>
-      <c r="AH3" s="68"/>
-      <c r="AI3" s="68"/>
-      <c r="AJ3" s="68"/>
-      <c r="AK3" s="68"/>
-      <c r="AL3" s="29"/>
-      <c r="AM3" s="29"/>
-      <c r="AN3" s="29"/>
-      <c r="AO3" s="29"/>
-      <c r="AP3" s="29"/>
-      <c r="AQ3" s="29"/>
-      <c r="AR3" s="29"/>
-      <c r="AS3" s="29"/>
-      <c r="AT3" s="29"/>
-      <c r="AU3" s="29"/>
-      <c r="AV3" s="29"/>
-      <c r="AW3" s="29"/>
-      <c r="AX3" s="29"/>
-      <c r="AY3" s="29"/>
-      <c r="AZ3" s="29"/>
-      <c r="BA3" s="29"/>
-      <c r="BB3" s="29"/>
-      <c r="BC3" s="29"/>
-      <c r="BD3" s="29"/>
-      <c r="BE3" s="29"/>
-      <c r="BF3" s="29"/>
-      <c r="BG3" s="29"/>
-      <c r="BH3" s="29"/>
-      <c r="BI3" s="29"/>
-      <c r="BJ3" s="29"/>
-      <c r="BK3" s="29"/>
-      <c r="BL3" s="29"/>
-      <c r="BM3" s="29"/>
-      <c r="BN3" s="29"/>
-      <c r="BO3" s="29"/>
-      <c r="BP3" s="29"/>
-      <c r="BQ3" s="29"/>
-      <c r="BR3" s="29"/>
-      <c r="BS3" s="29"/>
-      <c r="BT3" s="29"/>
-      <c r="BU3" s="29"/>
-      <c r="BV3" s="29"/>
-      <c r="BW3" s="29"/>
-      <c r="BX3" s="29"/>
-      <c r="BY3" s="29"/>
-      <c r="BZ3" s="29"/>
-      <c r="CA3" s="29"/>
-      <c r="CB3" s="29"/>
-      <c r="CC3" s="29"/>
-      <c r="CD3" s="29"/>
-      <c r="CE3" s="29"/>
-      <c r="CF3" s="29"/>
-      <c r="CG3" s="29"/>
-      <c r="CH3" s="29"/>
-      <c r="CI3" s="29"/>
-      <c r="CJ3" s="29"/>
-      <c r="CK3" s="29"/>
-      <c r="CL3" s="29"/>
-      <c r="CM3" s="29"/>
-      <c r="CN3" s="29"/>
-      <c r="CO3" s="29"/>
-      <c r="CP3" s="29"/>
-      <c r="CQ3" s="29"/>
-      <c r="CR3" s="29"/>
-      <c r="CS3" s="29"/>
-      <c r="CT3" s="29"/>
-      <c r="CU3" s="29"/>
-      <c r="CV3" s="29"/>
-      <c r="CW3" s="29"/>
-      <c r="CX3" s="29"/>
-      <c r="CY3" s="29"/>
-      <c r="CZ3" s="29"/>
-      <c r="DA3" s="29"/>
-      <c r="DB3" s="29"/>
-      <c r="DC3" s="29"/>
-      <c r="DD3" s="29"/>
-      <c r="DE3" s="29"/>
-      <c r="DF3" s="29"/>
-      <c r="DG3" s="29"/>
-      <c r="DH3" s="29"/>
-      <c r="DI3" s="29"/>
-      <c r="DJ3" s="29"/>
-      <c r="DK3" s="29"/>
-      <c r="DL3" s="29"/>
-      <c r="DM3" s="29"/>
-      <c r="DN3" s="29"/>
-      <c r="DO3" s="29"/>
-      <c r="DP3" s="29"/>
-      <c r="DQ3" s="29"/>
-      <c r="DR3" s="29"/>
-      <c r="DS3" s="29"/>
-      <c r="DT3" s="29"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="36"/>
+      <c r="Q3" s="36"/>
+      <c r="R3" s="24"/>
+      <c r="S3" s="24"/>
+      <c r="T3" s="24"/>
+      <c r="U3" s="24"/>
+      <c r="V3" s="31"/>
+      <c r="W3" s="31"/>
+      <c r="X3" s="24"/>
+      <c r="Y3" s="24"/>
+      <c r="Z3" s="38"/>
+      <c r="AA3" s="38"/>
+      <c r="AB3" s="38"/>
+      <c r="AC3" s="38"/>
+      <c r="AD3" s="24"/>
+      <c r="AE3" s="24"/>
+      <c r="AF3" s="24"/>
+      <c r="AG3" s="24"/>
+      <c r="AH3" s="36"/>
+      <c r="AI3" s="36"/>
+      <c r="AJ3" s="36"/>
+      <c r="AK3" s="36"/>
+      <c r="AL3" s="24"/>
+      <c r="AM3" s="24"/>
+      <c r="AN3" s="24"/>
+      <c r="AO3" s="24"/>
+      <c r="AP3" s="24"/>
+      <c r="AQ3" s="24"/>
+      <c r="AR3" s="24"/>
+      <c r="AS3" s="24"/>
+      <c r="AT3" s="24"/>
+      <c r="AU3" s="24"/>
+      <c r="AV3" s="24"/>
+      <c r="AW3" s="24"/>
+      <c r="AX3" s="24"/>
+      <c r="AY3" s="24"/>
+      <c r="AZ3" s="24"/>
+      <c r="BA3" s="24"/>
+      <c r="BB3" s="24"/>
+      <c r="BC3" s="24"/>
+      <c r="BD3" s="24"/>
+      <c r="BE3" s="24"/>
+      <c r="BF3" s="24"/>
+      <c r="BG3" s="24"/>
+      <c r="BH3" s="24"/>
+      <c r="BI3" s="24"/>
+      <c r="BJ3" s="24"/>
+      <c r="BK3" s="24"/>
+      <c r="BL3" s="24"/>
+      <c r="BM3" s="24"/>
+      <c r="BN3" s="24"/>
+      <c r="BO3" s="24"/>
+      <c r="BP3" s="24"/>
+      <c r="BQ3" s="24"/>
+      <c r="BR3" s="24"/>
+      <c r="BS3" s="24"/>
+      <c r="BT3" s="24"/>
+      <c r="BU3" s="24"/>
+      <c r="BV3" s="24"/>
+      <c r="BW3" s="24"/>
+      <c r="BX3" s="24"/>
+      <c r="BY3" s="24"/>
+      <c r="BZ3" s="24"/>
+      <c r="CA3" s="24"/>
+      <c r="CB3" s="24"/>
+      <c r="CC3" s="24"/>
+      <c r="CD3" s="24"/>
+      <c r="CE3" s="24"/>
+      <c r="CF3" s="24"/>
+      <c r="CG3" s="24"/>
+      <c r="CH3" s="24"/>
+      <c r="CI3" s="24"/>
+      <c r="CJ3" s="24"/>
+      <c r="CK3" s="24"/>
+      <c r="CL3" s="24"/>
+      <c r="CM3" s="24"/>
+      <c r="CN3" s="24"/>
+      <c r="CO3" s="24"/>
+      <c r="CP3" s="24"/>
+      <c r="CQ3" s="24"/>
+      <c r="CR3" s="24"/>
+      <c r="CS3" s="24"/>
+      <c r="CT3" s="24"/>
+      <c r="CU3" s="24"/>
+      <c r="CV3" s="24"/>
+      <c r="CW3" s="24"/>
+      <c r="CX3" s="24"/>
+      <c r="CY3" s="24"/>
+      <c r="CZ3" s="24"/>
+      <c r="DA3" s="24"/>
+      <c r="DB3" s="24"/>
+      <c r="DC3" s="24"/>
+      <c r="DD3" s="24"/>
+      <c r="DE3" s="24"/>
+      <c r="DF3" s="24"/>
+      <c r="DG3" s="24"/>
+      <c r="DH3" s="24"/>
+      <c r="DI3" s="24"/>
+      <c r="DJ3" s="24"/>
+      <c r="DK3" s="24"/>
+      <c r="DL3" s="24"/>
+      <c r="DM3" s="24"/>
+      <c r="DN3" s="24"/>
+      <c r="DO3" s="24"/>
+      <c r="DP3" s="24"/>
+      <c r="DQ3" s="24"/>
+      <c r="DR3" s="24"/>
+      <c r="DS3" s="24"/>
+      <c r="DT3" s="24"/>
     </row>
     <row r="4" spans="1:125" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="32" t="s">
+      <c r="A4" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="34"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
-      <c r="L4" s="29"/>
-      <c r="M4" s="29"/>
-      <c r="N4" s="29"/>
-      <c r="O4" s="29"/>
-      <c r="P4" s="68"/>
-      <c r="Q4" s="68"/>
-      <c r="R4" s="29"/>
-      <c r="S4" s="29"/>
-      <c r="T4" s="29"/>
-      <c r="U4" s="29"/>
-      <c r="V4" s="54"/>
-      <c r="W4" s="54"/>
-      <c r="X4" s="29"/>
-      <c r="Y4" s="29"/>
-      <c r="Z4" s="52"/>
-      <c r="AA4" s="52"/>
-      <c r="AB4" s="52"/>
-      <c r="AC4" s="52"/>
-      <c r="AD4" s="29"/>
-      <c r="AE4" s="29"/>
-      <c r="AF4" s="29"/>
-      <c r="AG4" s="29"/>
-      <c r="AH4" s="68"/>
-      <c r="AI4" s="68"/>
-      <c r="AJ4" s="68"/>
-      <c r="AK4" s="68"/>
-      <c r="AL4" s="29"/>
-      <c r="AM4" s="29"/>
-      <c r="AN4" s="29"/>
-      <c r="AO4" s="29"/>
-      <c r="AP4" s="29"/>
-      <c r="AQ4" s="29"/>
-      <c r="AR4" s="29"/>
-      <c r="AS4" s="29"/>
-      <c r="AT4" s="29"/>
-      <c r="AU4" s="29"/>
-      <c r="AV4" s="29"/>
-      <c r="AW4" s="29"/>
-      <c r="AX4" s="29"/>
-      <c r="AY4" s="29"/>
-      <c r="AZ4" s="29"/>
-      <c r="BA4" s="29"/>
-      <c r="BB4" s="29"/>
-      <c r="BC4" s="29"/>
-      <c r="BD4" s="29"/>
-      <c r="BE4" s="29"/>
-      <c r="BF4" s="29"/>
-      <c r="BG4" s="29"/>
-      <c r="BH4" s="29"/>
-      <c r="BI4" s="29"/>
-      <c r="BJ4" s="29"/>
-      <c r="BK4" s="29"/>
-      <c r="BL4" s="29"/>
-      <c r="BM4" s="29"/>
-      <c r="BN4" s="29"/>
-      <c r="BO4" s="29"/>
-      <c r="BP4" s="29"/>
-      <c r="BQ4" s="29"/>
-      <c r="BR4" s="29"/>
-      <c r="BS4" s="29"/>
-      <c r="BT4" s="29"/>
-      <c r="BU4" s="29"/>
-      <c r="BV4" s="29"/>
-      <c r="BW4" s="29"/>
-      <c r="BX4" s="29"/>
-      <c r="BY4" s="29"/>
-      <c r="BZ4" s="29"/>
-      <c r="CA4" s="29"/>
-      <c r="CB4" s="29"/>
-      <c r="CC4" s="29"/>
-      <c r="CD4" s="29"/>
-      <c r="CE4" s="29"/>
-      <c r="CF4" s="29"/>
-      <c r="CG4" s="29"/>
-      <c r="CH4" s="29"/>
-      <c r="CI4" s="29"/>
-      <c r="CJ4" s="29"/>
-      <c r="CK4" s="29"/>
-      <c r="CL4" s="29"/>
-      <c r="CM4" s="29"/>
-      <c r="CN4" s="29"/>
-      <c r="CO4" s="29"/>
-      <c r="CP4" s="29"/>
-      <c r="CQ4" s="29"/>
-      <c r="CR4" s="29"/>
-      <c r="CS4" s="29"/>
-      <c r="CT4" s="29"/>
-      <c r="CU4" s="29"/>
-      <c r="CV4" s="29"/>
-      <c r="CW4" s="29"/>
-      <c r="CX4" s="29"/>
-      <c r="CY4" s="29"/>
-      <c r="CZ4" s="29"/>
-      <c r="DA4" s="29"/>
-      <c r="DB4" s="29"/>
-      <c r="DC4" s="29"/>
-      <c r="DD4" s="29"/>
-      <c r="DE4" s="29"/>
-      <c r="DF4" s="29"/>
-      <c r="DG4" s="29"/>
-      <c r="DH4" s="29"/>
-      <c r="DI4" s="29"/>
-      <c r="DJ4" s="29"/>
-      <c r="DK4" s="29"/>
-      <c r="DL4" s="29"/>
-      <c r="DM4" s="29"/>
-      <c r="DN4" s="29"/>
-      <c r="DO4" s="29"/>
-      <c r="DP4" s="29"/>
-      <c r="DQ4" s="29"/>
-      <c r="DR4" s="29"/>
-      <c r="DS4" s="29"/>
-      <c r="DT4" s="29"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="24"/>
+      <c r="S4" s="24"/>
+      <c r="T4" s="24"/>
+      <c r="U4" s="24"/>
+      <c r="V4" s="31"/>
+      <c r="W4" s="31"/>
+      <c r="X4" s="24"/>
+      <c r="Y4" s="24"/>
+      <c r="Z4" s="38"/>
+      <c r="AA4" s="38"/>
+      <c r="AB4" s="38"/>
+      <c r="AC4" s="38"/>
+      <c r="AD4" s="24"/>
+      <c r="AE4" s="24"/>
+      <c r="AF4" s="24"/>
+      <c r="AG4" s="24"/>
+      <c r="AH4" s="36"/>
+      <c r="AI4" s="36"/>
+      <c r="AJ4" s="36"/>
+      <c r="AK4" s="36"/>
+      <c r="AL4" s="24"/>
+      <c r="AM4" s="24"/>
+      <c r="AN4" s="24"/>
+      <c r="AO4" s="24"/>
+      <c r="AP4" s="24"/>
+      <c r="AQ4" s="24"/>
+      <c r="AR4" s="24"/>
+      <c r="AS4" s="24"/>
+      <c r="AT4" s="24"/>
+      <c r="AU4" s="24"/>
+      <c r="AV4" s="24"/>
+      <c r="AW4" s="24"/>
+      <c r="AX4" s="24"/>
+      <c r="AY4" s="24"/>
+      <c r="AZ4" s="24"/>
+      <c r="BA4" s="24"/>
+      <c r="BB4" s="24"/>
+      <c r="BC4" s="24"/>
+      <c r="BD4" s="24"/>
+      <c r="BE4" s="24"/>
+      <c r="BF4" s="24"/>
+      <c r="BG4" s="24"/>
+      <c r="BH4" s="24"/>
+      <c r="BI4" s="24"/>
+      <c r="BJ4" s="24"/>
+      <c r="BK4" s="24"/>
+      <c r="BL4" s="24"/>
+      <c r="BM4" s="24"/>
+      <c r="BN4" s="24"/>
+      <c r="BO4" s="24"/>
+      <c r="BP4" s="24"/>
+      <c r="BQ4" s="24"/>
+      <c r="BR4" s="24"/>
+      <c r="BS4" s="24"/>
+      <c r="BT4" s="24"/>
+      <c r="BU4" s="24"/>
+      <c r="BV4" s="24"/>
+      <c r="BW4" s="24"/>
+      <c r="BX4" s="24"/>
+      <c r="BY4" s="24"/>
+      <c r="BZ4" s="24"/>
+      <c r="CA4" s="24"/>
+      <c r="CB4" s="24"/>
+      <c r="CC4" s="24"/>
+      <c r="CD4" s="24"/>
+      <c r="CE4" s="24"/>
+      <c r="CF4" s="24"/>
+      <c r="CG4" s="24"/>
+      <c r="CH4" s="24"/>
+      <c r="CI4" s="24"/>
+      <c r="CJ4" s="24"/>
+      <c r="CK4" s="24"/>
+      <c r="CL4" s="24"/>
+      <c r="CM4" s="24"/>
+      <c r="CN4" s="24"/>
+      <c r="CO4" s="24"/>
+      <c r="CP4" s="24"/>
+      <c r="CQ4" s="24"/>
+      <c r="CR4" s="24"/>
+      <c r="CS4" s="24"/>
+      <c r="CT4" s="24"/>
+      <c r="CU4" s="24"/>
+      <c r="CV4" s="24"/>
+      <c r="CW4" s="24"/>
+      <c r="CX4" s="24"/>
+      <c r="CY4" s="24"/>
+      <c r="CZ4" s="24"/>
+      <c r="DA4" s="24"/>
+      <c r="DB4" s="24"/>
+      <c r="DC4" s="24"/>
+      <c r="DD4" s="24"/>
+      <c r="DE4" s="24"/>
+      <c r="DF4" s="24"/>
+      <c r="DG4" s="24"/>
+      <c r="DH4" s="24"/>
+      <c r="DI4" s="24"/>
+      <c r="DJ4" s="24"/>
+      <c r="DK4" s="24"/>
+      <c r="DL4" s="24"/>
+      <c r="DM4" s="24"/>
+      <c r="DN4" s="24"/>
+      <c r="DO4" s="24"/>
+      <c r="DP4" s="24"/>
+      <c r="DQ4" s="24"/>
+      <c r="DR4" s="24"/>
+      <c r="DS4" s="24"/>
+      <c r="DT4" s="24"/>
     </row>
     <row r="5" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="49">
+      <c r="B5" s="53"/>
+      <c r="C5" s="54">
         <v>60</v>
       </c>
-      <c r="D5" s="50"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="29"/>
-      <c r="S5" s="29"/>
-      <c r="T5" s="29"/>
-      <c r="U5" s="29"/>
-      <c r="V5" s="54"/>
-      <c r="W5" s="54"/>
-      <c r="X5" s="29"/>
-      <c r="Y5" s="29"/>
-      <c r="Z5" s="52"/>
-      <c r="AA5" s="52"/>
-      <c r="AB5" s="52"/>
-      <c r="AC5" s="52"/>
-      <c r="AD5" s="29"/>
-      <c r="AE5" s="29"/>
-      <c r="AF5" s="29"/>
-      <c r="AG5" s="29"/>
-      <c r="AH5" s="68"/>
-      <c r="AI5" s="68"/>
-      <c r="AJ5" s="68"/>
-      <c r="AK5" s="68"/>
-      <c r="AL5" s="29"/>
-      <c r="AM5" s="29"/>
-      <c r="AN5" s="29"/>
-      <c r="AO5" s="29"/>
-      <c r="AP5" s="29"/>
-      <c r="AQ5" s="29"/>
-      <c r="AR5" s="29"/>
-      <c r="AS5" s="29"/>
-      <c r="AT5" s="29"/>
-      <c r="AU5" s="29"/>
-      <c r="AV5" s="29"/>
-      <c r="AW5" s="29"/>
-      <c r="AX5" s="29"/>
-      <c r="AY5" s="29"/>
-      <c r="AZ5" s="29"/>
-      <c r="BA5" s="29"/>
-      <c r="BB5" s="29"/>
-      <c r="BC5" s="29"/>
-      <c r="BD5" s="29"/>
-      <c r="BE5" s="29"/>
-      <c r="BF5" s="29"/>
-      <c r="BG5" s="29"/>
-      <c r="BH5" s="29"/>
-      <c r="BI5" s="29"/>
-      <c r="BJ5" s="29"/>
-      <c r="BK5" s="29"/>
-      <c r="BL5" s="29"/>
-      <c r="BM5" s="29"/>
-      <c r="BN5" s="29"/>
-      <c r="BO5" s="29"/>
-      <c r="BP5" s="29"/>
-      <c r="BQ5" s="29"/>
-      <c r="BR5" s="29"/>
-      <c r="BS5" s="29"/>
-      <c r="BT5" s="29"/>
-      <c r="BU5" s="29"/>
-      <c r="BV5" s="29"/>
-      <c r="BW5" s="29"/>
-      <c r="BX5" s="29"/>
-      <c r="BY5" s="29"/>
-      <c r="BZ5" s="29"/>
-      <c r="CA5" s="29"/>
-      <c r="CB5" s="29"/>
-      <c r="CC5" s="29"/>
-      <c r="CD5" s="29"/>
-      <c r="CE5" s="29"/>
-      <c r="CF5" s="29"/>
-      <c r="CG5" s="29"/>
-      <c r="CH5" s="29"/>
-      <c r="CI5" s="29"/>
-      <c r="CJ5" s="29"/>
-      <c r="CK5" s="29"/>
-      <c r="CL5" s="29"/>
-      <c r="CM5" s="29"/>
-      <c r="CN5" s="29"/>
-      <c r="CO5" s="29"/>
-      <c r="CP5" s="29"/>
-      <c r="CQ5" s="29"/>
-      <c r="CR5" s="29"/>
-      <c r="CS5" s="29"/>
-      <c r="CT5" s="29"/>
-      <c r="CU5" s="29"/>
-      <c r="CV5" s="29"/>
-      <c r="CW5" s="29"/>
-      <c r="CX5" s="29"/>
-      <c r="CY5" s="29"/>
-      <c r="CZ5" s="29"/>
-      <c r="DA5" s="29"/>
-      <c r="DB5" s="29"/>
-      <c r="DC5" s="29"/>
-      <c r="DD5" s="29"/>
-      <c r="DE5" s="29"/>
-      <c r="DF5" s="29"/>
-      <c r="DG5" s="29"/>
-      <c r="DH5" s="29"/>
-      <c r="DI5" s="29"/>
-      <c r="DJ5" s="29"/>
-      <c r="DK5" s="29"/>
-      <c r="DL5" s="29"/>
-      <c r="DM5" s="29"/>
-      <c r="DN5" s="29"/>
-      <c r="DO5" s="29"/>
-      <c r="DP5" s="29"/>
-      <c r="DQ5" s="29"/>
-      <c r="DR5" s="29"/>
-      <c r="DS5" s="29"/>
-      <c r="DT5" s="29"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="24"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="24"/>
+      <c r="S5" s="24"/>
+      <c r="T5" s="24"/>
+      <c r="U5" s="24"/>
+      <c r="V5" s="31"/>
+      <c r="W5" s="31"/>
+      <c r="X5" s="24"/>
+      <c r="Y5" s="24"/>
+      <c r="Z5" s="38"/>
+      <c r="AA5" s="38"/>
+      <c r="AB5" s="38"/>
+      <c r="AC5" s="38"/>
+      <c r="AD5" s="24"/>
+      <c r="AE5" s="24"/>
+      <c r="AF5" s="24"/>
+      <c r="AG5" s="24"/>
+      <c r="AH5" s="36"/>
+      <c r="AI5" s="36"/>
+      <c r="AJ5" s="36"/>
+      <c r="AK5" s="36"/>
+      <c r="AL5" s="24"/>
+      <c r="AM5" s="24"/>
+      <c r="AN5" s="24"/>
+      <c r="AO5" s="24"/>
+      <c r="AP5" s="24"/>
+      <c r="AQ5" s="24"/>
+      <c r="AR5" s="24"/>
+      <c r="AS5" s="24"/>
+      <c r="AT5" s="24"/>
+      <c r="AU5" s="24"/>
+      <c r="AV5" s="24"/>
+      <c r="AW5" s="24"/>
+      <c r="AX5" s="24"/>
+      <c r="AY5" s="24"/>
+      <c r="AZ5" s="24"/>
+      <c r="BA5" s="24"/>
+      <c r="BB5" s="24"/>
+      <c r="BC5" s="24"/>
+      <c r="BD5" s="24"/>
+      <c r="BE5" s="24"/>
+      <c r="BF5" s="24"/>
+      <c r="BG5" s="24"/>
+      <c r="BH5" s="24"/>
+      <c r="BI5" s="24"/>
+      <c r="BJ5" s="24"/>
+      <c r="BK5" s="24"/>
+      <c r="BL5" s="24"/>
+      <c r="BM5" s="24"/>
+      <c r="BN5" s="24"/>
+      <c r="BO5" s="24"/>
+      <c r="BP5" s="24"/>
+      <c r="BQ5" s="24"/>
+      <c r="BR5" s="24"/>
+      <c r="BS5" s="24"/>
+      <c r="BT5" s="24"/>
+      <c r="BU5" s="24"/>
+      <c r="BV5" s="24"/>
+      <c r="BW5" s="24"/>
+      <c r="BX5" s="24"/>
+      <c r="BY5" s="24"/>
+      <c r="BZ5" s="24"/>
+      <c r="CA5" s="24"/>
+      <c r="CB5" s="24"/>
+      <c r="CC5" s="24"/>
+      <c r="CD5" s="24"/>
+      <c r="CE5" s="24"/>
+      <c r="CF5" s="24"/>
+      <c r="CG5" s="24"/>
+      <c r="CH5" s="24"/>
+      <c r="CI5" s="24"/>
+      <c r="CJ5" s="24"/>
+      <c r="CK5" s="24"/>
+      <c r="CL5" s="24"/>
+      <c r="CM5" s="24"/>
+      <c r="CN5" s="24"/>
+      <c r="CO5" s="24"/>
+      <c r="CP5" s="24"/>
+      <c r="CQ5" s="24"/>
+      <c r="CR5" s="24"/>
+      <c r="CS5" s="24"/>
+      <c r="CT5" s="24"/>
+      <c r="CU5" s="24"/>
+      <c r="CV5" s="24"/>
+      <c r="CW5" s="24"/>
+      <c r="CX5" s="24"/>
+      <c r="CY5" s="24"/>
+      <c r="CZ5" s="24"/>
+      <c r="DA5" s="24"/>
+      <c r="DB5" s="24"/>
+      <c r="DC5" s="24"/>
+      <c r="DD5" s="24"/>
+      <c r="DE5" s="24"/>
+      <c r="DF5" s="24"/>
+      <c r="DG5" s="24"/>
+      <c r="DH5" s="24"/>
+      <c r="DI5" s="24"/>
+      <c r="DJ5" s="24"/>
+      <c r="DK5" s="24"/>
+      <c r="DL5" s="24"/>
+      <c r="DM5" s="24"/>
+      <c r="DN5" s="24"/>
+      <c r="DO5" s="24"/>
+      <c r="DP5" s="24"/>
+      <c r="DQ5" s="24"/>
+      <c r="DR5" s="24"/>
+      <c r="DS5" s="24"/>
+      <c r="DT5" s="24"/>
     </row>
     <row r="6" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="48" t="s">
+      <c r="A6" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="49">
+      <c r="B6" s="53"/>
+      <c r="C6" s="54">
         <v>4</v>
       </c>
-      <c r="D6" s="50"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29"/>
-      <c r="N6" s="29"/>
-      <c r="O6" s="29"/>
-      <c r="P6" s="68"/>
-      <c r="Q6" s="68"/>
-      <c r="R6" s="29"/>
-      <c r="S6" s="29"/>
-      <c r="T6" s="29"/>
-      <c r="U6" s="29"/>
-      <c r="V6" s="54"/>
-      <c r="W6" s="54"/>
-      <c r="X6" s="29"/>
-      <c r="Y6" s="29"/>
-      <c r="Z6" s="52"/>
-      <c r="AA6" s="52"/>
-      <c r="AB6" s="52"/>
-      <c r="AC6" s="52"/>
-      <c r="AD6" s="29"/>
-      <c r="AE6" s="29"/>
-      <c r="AF6" s="29"/>
-      <c r="AG6" s="29"/>
-      <c r="AH6" s="68"/>
-      <c r="AI6" s="68"/>
-      <c r="AJ6" s="68"/>
-      <c r="AK6" s="68"/>
-      <c r="AL6" s="29"/>
-      <c r="AM6" s="29"/>
-      <c r="AN6" s="29"/>
-      <c r="AO6" s="29"/>
-      <c r="AP6" s="29"/>
-      <c r="AQ6" s="29"/>
-      <c r="AR6" s="29"/>
-      <c r="AS6" s="29"/>
-      <c r="AT6" s="29"/>
-      <c r="AU6" s="29"/>
-      <c r="AV6" s="29"/>
-      <c r="AW6" s="29"/>
-      <c r="AX6" s="29"/>
-      <c r="AY6" s="29"/>
-      <c r="AZ6" s="29"/>
-      <c r="BA6" s="29"/>
-      <c r="BB6" s="29"/>
-      <c r="BC6" s="29"/>
-      <c r="BD6" s="29"/>
-      <c r="BE6" s="29"/>
-      <c r="BF6" s="29"/>
-      <c r="BG6" s="29"/>
-      <c r="BH6" s="29"/>
-      <c r="BI6" s="29"/>
-      <c r="BJ6" s="29"/>
-      <c r="BK6" s="29"/>
-      <c r="BL6" s="29"/>
-      <c r="BM6" s="29"/>
-      <c r="BN6" s="29"/>
-      <c r="BO6" s="29"/>
-      <c r="BP6" s="29"/>
-      <c r="BQ6" s="29"/>
-      <c r="BR6" s="29"/>
-      <c r="BS6" s="29"/>
-      <c r="BT6" s="29"/>
-      <c r="BU6" s="29"/>
-      <c r="BV6" s="29"/>
-      <c r="BW6" s="29"/>
-      <c r="BX6" s="29"/>
-      <c r="BY6" s="29"/>
-      <c r="BZ6" s="29"/>
-      <c r="CA6" s="29"/>
-      <c r="CB6" s="29"/>
-      <c r="CC6" s="29"/>
-      <c r="CD6" s="29"/>
-      <c r="CE6" s="29"/>
-      <c r="CF6" s="29"/>
-      <c r="CG6" s="29"/>
-      <c r="CH6" s="29"/>
-      <c r="CI6" s="29"/>
-      <c r="CJ6" s="29"/>
-      <c r="CK6" s="29"/>
-      <c r="CL6" s="29"/>
-      <c r="CM6" s="29"/>
-      <c r="CN6" s="29"/>
-      <c r="CO6" s="29"/>
-      <c r="CP6" s="29"/>
-      <c r="CQ6" s="29"/>
-      <c r="CR6" s="29"/>
-      <c r="CS6" s="29"/>
-      <c r="CT6" s="29"/>
-      <c r="CU6" s="29"/>
-      <c r="CV6" s="29"/>
-      <c r="CW6" s="29"/>
-      <c r="CX6" s="29"/>
-      <c r="CY6" s="29"/>
-      <c r="CZ6" s="29"/>
-      <c r="DA6" s="29"/>
-      <c r="DB6" s="29"/>
-      <c r="DC6" s="29"/>
-      <c r="DD6" s="29"/>
-      <c r="DE6" s="29"/>
-      <c r="DF6" s="29"/>
-      <c r="DG6" s="29"/>
-      <c r="DH6" s="29"/>
-      <c r="DI6" s="29"/>
-      <c r="DJ6" s="29"/>
-      <c r="DK6" s="29"/>
-      <c r="DL6" s="29"/>
-      <c r="DM6" s="29"/>
-      <c r="DN6" s="29"/>
-      <c r="DO6" s="29"/>
-      <c r="DP6" s="29"/>
-      <c r="DQ6" s="29"/>
-      <c r="DR6" s="29"/>
-      <c r="DS6" s="29"/>
-      <c r="DT6" s="29"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="24"/>
+      <c r="S6" s="24"/>
+      <c r="T6" s="24"/>
+      <c r="U6" s="24"/>
+      <c r="V6" s="31"/>
+      <c r="W6" s="31"/>
+      <c r="X6" s="24"/>
+      <c r="Y6" s="24"/>
+      <c r="Z6" s="38"/>
+      <c r="AA6" s="38"/>
+      <c r="AB6" s="38"/>
+      <c r="AC6" s="38"/>
+      <c r="AD6" s="24"/>
+      <c r="AE6" s="24"/>
+      <c r="AF6" s="24"/>
+      <c r="AG6" s="24"/>
+      <c r="AH6" s="36"/>
+      <c r="AI6" s="36"/>
+      <c r="AJ6" s="36"/>
+      <c r="AK6" s="36"/>
+      <c r="AL6" s="24"/>
+      <c r="AM6" s="24"/>
+      <c r="AN6" s="24"/>
+      <c r="AO6" s="24"/>
+      <c r="AP6" s="24"/>
+      <c r="AQ6" s="24"/>
+      <c r="AR6" s="24"/>
+      <c r="AS6" s="24"/>
+      <c r="AT6" s="24"/>
+      <c r="AU6" s="24"/>
+      <c r="AV6" s="24"/>
+      <c r="AW6" s="24"/>
+      <c r="AX6" s="24"/>
+      <c r="AY6" s="24"/>
+      <c r="AZ6" s="24"/>
+      <c r="BA6" s="24"/>
+      <c r="BB6" s="24"/>
+      <c r="BC6" s="24"/>
+      <c r="BD6" s="24"/>
+      <c r="BE6" s="24"/>
+      <c r="BF6" s="24"/>
+      <c r="BG6" s="24"/>
+      <c r="BH6" s="24"/>
+      <c r="BI6" s="24"/>
+      <c r="BJ6" s="24"/>
+      <c r="BK6" s="24"/>
+      <c r="BL6" s="24"/>
+      <c r="BM6" s="24"/>
+      <c r="BN6" s="24"/>
+      <c r="BO6" s="24"/>
+      <c r="BP6" s="24"/>
+      <c r="BQ6" s="24"/>
+      <c r="BR6" s="24"/>
+      <c r="BS6" s="24"/>
+      <c r="BT6" s="24"/>
+      <c r="BU6" s="24"/>
+      <c r="BV6" s="24"/>
+      <c r="BW6" s="24"/>
+      <c r="BX6" s="24"/>
+      <c r="BY6" s="24"/>
+      <c r="BZ6" s="24"/>
+      <c r="CA6" s="24"/>
+      <c r="CB6" s="24"/>
+      <c r="CC6" s="24"/>
+      <c r="CD6" s="24"/>
+      <c r="CE6" s="24"/>
+      <c r="CF6" s="24"/>
+      <c r="CG6" s="24"/>
+      <c r="CH6" s="24"/>
+      <c r="CI6" s="24"/>
+      <c r="CJ6" s="24"/>
+      <c r="CK6" s="24"/>
+      <c r="CL6" s="24"/>
+      <c r="CM6" s="24"/>
+      <c r="CN6" s="24"/>
+      <c r="CO6" s="24"/>
+      <c r="CP6" s="24"/>
+      <c r="CQ6" s="24"/>
+      <c r="CR6" s="24"/>
+      <c r="CS6" s="24"/>
+      <c r="CT6" s="24"/>
+      <c r="CU6" s="24"/>
+      <c r="CV6" s="24"/>
+      <c r="CW6" s="24"/>
+      <c r="CX6" s="24"/>
+      <c r="CY6" s="24"/>
+      <c r="CZ6" s="24"/>
+      <c r="DA6" s="24"/>
+      <c r="DB6" s="24"/>
+      <c r="DC6" s="24"/>
+      <c r="DD6" s="24"/>
+      <c r="DE6" s="24"/>
+      <c r="DF6" s="24"/>
+      <c r="DG6" s="24"/>
+      <c r="DH6" s="24"/>
+      <c r="DI6" s="24"/>
+      <c r="DJ6" s="24"/>
+      <c r="DK6" s="24"/>
+      <c r="DL6" s="24"/>
+      <c r="DM6" s="24"/>
+      <c r="DN6" s="24"/>
+      <c r="DO6" s="24"/>
+      <c r="DP6" s="24"/>
+      <c r="DQ6" s="24"/>
+      <c r="DR6" s="24"/>
+      <c r="DS6" s="24"/>
+      <c r="DT6" s="24"/>
     </row>
     <row r="7" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="51" t="s">
+      <c r="A7" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="51"/>
-      <c r="C7" s="49">
+      <c r="B7" s="56"/>
+      <c r="C7" s="54">
         <v>11</v>
       </c>
-      <c r="D7" s="50"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="30"/>
-      <c r="L7" s="30"/>
-      <c r="M7" s="30"/>
-      <c r="N7" s="30"/>
-      <c r="O7" s="30"/>
-      <c r="P7" s="69"/>
-      <c r="Q7" s="69"/>
-      <c r="R7" s="30"/>
-      <c r="S7" s="30"/>
-      <c r="T7" s="30"/>
-      <c r="U7" s="30"/>
-      <c r="V7" s="55"/>
-      <c r="W7" s="55"/>
-      <c r="X7" s="30"/>
-      <c r="Y7" s="30"/>
-      <c r="Z7" s="53"/>
-      <c r="AA7" s="53"/>
-      <c r="AB7" s="53"/>
-      <c r="AC7" s="53"/>
-      <c r="AD7" s="30"/>
-      <c r="AE7" s="30"/>
-      <c r="AF7" s="30"/>
-      <c r="AG7" s="30"/>
-      <c r="AH7" s="69"/>
-      <c r="AI7" s="69"/>
-      <c r="AJ7" s="69"/>
-      <c r="AK7" s="69"/>
-      <c r="AL7" s="30"/>
-      <c r="AM7" s="30"/>
-      <c r="AN7" s="30"/>
-      <c r="AO7" s="30"/>
-      <c r="AP7" s="30"/>
-      <c r="AQ7" s="30"/>
-      <c r="AR7" s="30"/>
-      <c r="AS7" s="30"/>
-      <c r="AT7" s="30"/>
-      <c r="AU7" s="30"/>
-      <c r="AV7" s="30"/>
-      <c r="AW7" s="30"/>
-      <c r="AX7" s="30"/>
-      <c r="AY7" s="30"/>
-      <c r="AZ7" s="30"/>
-      <c r="BA7" s="30"/>
-      <c r="BB7" s="30"/>
-      <c r="BC7" s="30"/>
-      <c r="BD7" s="30"/>
-      <c r="BE7" s="30"/>
-      <c r="BF7" s="30"/>
-      <c r="BG7" s="30"/>
-      <c r="BH7" s="30"/>
-      <c r="BI7" s="30"/>
-      <c r="BJ7" s="30"/>
-      <c r="BK7" s="30"/>
-      <c r="BL7" s="30"/>
-      <c r="BM7" s="30"/>
-      <c r="BN7" s="30"/>
-      <c r="BO7" s="30"/>
-      <c r="BP7" s="30"/>
-      <c r="BQ7" s="30"/>
-      <c r="BR7" s="30"/>
-      <c r="BS7" s="30"/>
-      <c r="BT7" s="30"/>
-      <c r="BU7" s="30"/>
-      <c r="BV7" s="30"/>
-      <c r="BW7" s="30"/>
-      <c r="BX7" s="30"/>
-      <c r="BY7" s="30"/>
-      <c r="BZ7" s="30"/>
-      <c r="CA7" s="30"/>
-      <c r="CB7" s="30"/>
-      <c r="CC7" s="30"/>
-      <c r="CD7" s="30"/>
-      <c r="CE7" s="30"/>
-      <c r="CF7" s="30"/>
-      <c r="CG7" s="30"/>
-      <c r="CH7" s="30"/>
-      <c r="CI7" s="30"/>
-      <c r="CJ7" s="30"/>
-      <c r="CK7" s="30"/>
-      <c r="CL7" s="30"/>
-      <c r="CM7" s="30"/>
-      <c r="CN7" s="30"/>
-      <c r="CO7" s="30"/>
-      <c r="CP7" s="30"/>
-      <c r="CQ7" s="30"/>
-      <c r="CR7" s="30"/>
-      <c r="CS7" s="30"/>
-      <c r="CT7" s="30"/>
-      <c r="CU7" s="30"/>
-      <c r="CV7" s="30"/>
-      <c r="CW7" s="30"/>
-      <c r="CX7" s="30"/>
-      <c r="CY7" s="30"/>
-      <c r="CZ7" s="30"/>
-      <c r="DA7" s="30"/>
-      <c r="DB7" s="30"/>
-      <c r="DC7" s="30"/>
-      <c r="DD7" s="30"/>
-      <c r="DE7" s="30"/>
-      <c r="DF7" s="30"/>
-      <c r="DG7" s="30"/>
-      <c r="DH7" s="30"/>
-      <c r="DI7" s="30"/>
-      <c r="DJ7" s="30"/>
-      <c r="DK7" s="30"/>
-      <c r="DL7" s="30"/>
-      <c r="DM7" s="30"/>
-      <c r="DN7" s="30"/>
-      <c r="DO7" s="30"/>
-      <c r="DP7" s="30"/>
-      <c r="DQ7" s="30"/>
-      <c r="DR7" s="30"/>
-      <c r="DS7" s="30"/>
-      <c r="DT7" s="30"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
+      <c r="P7" s="37"/>
+      <c r="Q7" s="37"/>
+      <c r="R7" s="25"/>
+      <c r="S7" s="25"/>
+      <c r="T7" s="25"/>
+      <c r="U7" s="25"/>
+      <c r="V7" s="32"/>
+      <c r="W7" s="32"/>
+      <c r="X7" s="25"/>
+      <c r="Y7" s="25"/>
+      <c r="Z7" s="39"/>
+      <c r="AA7" s="39"/>
+      <c r="AB7" s="39"/>
+      <c r="AC7" s="39"/>
+      <c r="AD7" s="25"/>
+      <c r="AE7" s="25"/>
+      <c r="AF7" s="25"/>
+      <c r="AG7" s="25"/>
+      <c r="AH7" s="37"/>
+      <c r="AI7" s="37"/>
+      <c r="AJ7" s="37"/>
+      <c r="AK7" s="37"/>
+      <c r="AL7" s="25"/>
+      <c r="AM7" s="25"/>
+      <c r="AN7" s="25"/>
+      <c r="AO7" s="25"/>
+      <c r="AP7" s="25"/>
+      <c r="AQ7" s="25"/>
+      <c r="AR7" s="25"/>
+      <c r="AS7" s="25"/>
+      <c r="AT7" s="25"/>
+      <c r="AU7" s="25"/>
+      <c r="AV7" s="25"/>
+      <c r="AW7" s="25"/>
+      <c r="AX7" s="25"/>
+      <c r="AY7" s="25"/>
+      <c r="AZ7" s="25"/>
+      <c r="BA7" s="25"/>
+      <c r="BB7" s="25"/>
+      <c r="BC7" s="25"/>
+      <c r="BD7" s="25"/>
+      <c r="BE7" s="25"/>
+      <c r="BF7" s="25"/>
+      <c r="BG7" s="25"/>
+      <c r="BH7" s="25"/>
+      <c r="BI7" s="25"/>
+      <c r="BJ7" s="25"/>
+      <c r="BK7" s="25"/>
+      <c r="BL7" s="25"/>
+      <c r="BM7" s="25"/>
+      <c r="BN7" s="25"/>
+      <c r="BO7" s="25"/>
+      <c r="BP7" s="25"/>
+      <c r="BQ7" s="25"/>
+      <c r="BR7" s="25"/>
+      <c r="BS7" s="25"/>
+      <c r="BT7" s="25"/>
+      <c r="BU7" s="25"/>
+      <c r="BV7" s="25"/>
+      <c r="BW7" s="25"/>
+      <c r="BX7" s="25"/>
+      <c r="BY7" s="25"/>
+      <c r="BZ7" s="25"/>
+      <c r="CA7" s="25"/>
+      <c r="CB7" s="25"/>
+      <c r="CC7" s="25"/>
+      <c r="CD7" s="25"/>
+      <c r="CE7" s="25"/>
+      <c r="CF7" s="25"/>
+      <c r="CG7" s="25"/>
+      <c r="CH7" s="25"/>
+      <c r="CI7" s="25"/>
+      <c r="CJ7" s="25"/>
+      <c r="CK7" s="25"/>
+      <c r="CL7" s="25"/>
+      <c r="CM7" s="25"/>
+      <c r="CN7" s="25"/>
+      <c r="CO7" s="25"/>
+      <c r="CP7" s="25"/>
+      <c r="CQ7" s="25"/>
+      <c r="CR7" s="25"/>
+      <c r="CS7" s="25"/>
+      <c r="CT7" s="25"/>
+      <c r="CU7" s="25"/>
+      <c r="CV7" s="25"/>
+      <c r="CW7" s="25"/>
+      <c r="CX7" s="25"/>
+      <c r="CY7" s="25"/>
+      <c r="CZ7" s="25"/>
+      <c r="DA7" s="25"/>
+      <c r="DB7" s="25"/>
+      <c r="DC7" s="25"/>
+      <c r="DD7" s="25"/>
+      <c r="DE7" s="25"/>
+      <c r="DF7" s="25"/>
+      <c r="DG7" s="25"/>
+      <c r="DH7" s="25"/>
+      <c r="DI7" s="25"/>
+      <c r="DJ7" s="25"/>
+      <c r="DK7" s="25"/>
+      <c r="DL7" s="25"/>
+      <c r="DM7" s="25"/>
+      <c r="DN7" s="25"/>
+      <c r="DO7" s="25"/>
+      <c r="DP7" s="25"/>
+      <c r="DQ7" s="25"/>
+      <c r="DR7" s="25"/>
+      <c r="DS7" s="25"/>
+      <c r="DT7" s="25"/>
     </row>
     <row r="8" spans="1:125" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="31">
+      <c r="B8" s="57"/>
+      <c r="C8" s="58">
         <f>SUM(C5:D7)</f>
         <v>75</v>
       </c>
-      <c r="D8" s="34"/>
+      <c r="D8" s="52"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="27">
-        <v>1</v>
-      </c>
-      <c r="G8" s="27">
+      <c r="F8" s="29">
+        <v>1</v>
+      </c>
+      <c r="G8" s="29">
         <v>2</v>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="29">
         <v>3</v>
       </c>
-      <c r="I8" s="27">
+      <c r="I8" s="29">
         <v>4</v>
       </c>
-      <c r="J8" s="27">
+      <c r="J8" s="29">
         <v>5</v>
       </c>
-      <c r="K8" s="27">
+      <c r="K8" s="29">
         <v>6</v>
       </c>
-      <c r="L8" s="27">
+      <c r="L8" s="29">
         <v>7</v>
       </c>
-      <c r="M8" s="27">
+      <c r="M8" s="29">
         <v>8</v>
       </c>
-      <c r="N8" s="27">
+      <c r="N8" s="29">
         <v>9</v>
       </c>
-      <c r="O8" s="27">
+      <c r="O8" s="29">
         <v>10</v>
       </c>
-      <c r="P8" s="27">
+      <c r="P8" s="29">
         <v>11</v>
       </c>
-      <c r="Q8" s="27">
+      <c r="Q8" s="29">
         <v>12</v>
       </c>
-      <c r="R8" s="27">
+      <c r="R8" s="29">
         <v>13</v>
       </c>
-      <c r="S8" s="27">
+      <c r="S8" s="29">
         <v>14</v>
       </c>
-      <c r="T8" s="27">
+      <c r="T8" s="29">
         <v>15</v>
       </c>
-      <c r="U8" s="27">
+      <c r="U8" s="29">
         <v>16</v>
       </c>
-      <c r="V8" s="27">
+      <c r="V8" s="29">
         <v>17</v>
       </c>
-      <c r="W8" s="27">
+      <c r="W8" s="29">
         <v>18</v>
       </c>
-      <c r="X8" s="27">
+      <c r="X8" s="29">
         <v>19</v>
       </c>
-      <c r="Y8" s="27">
+      <c r="Y8" s="29">
         <v>20</v>
       </c>
-      <c r="Z8" s="27">
+      <c r="Z8" s="29">
         <v>21</v>
       </c>
-      <c r="AA8" s="27">
+      <c r="AA8" s="29">
         <v>22</v>
       </c>
-      <c r="AB8" s="27">
+      <c r="AB8" s="29">
         <v>23</v>
       </c>
-      <c r="AC8" s="27">
+      <c r="AC8" s="29">
         <v>24</v>
       </c>
-      <c r="AD8" s="27">
+      <c r="AD8" s="29">
         <v>25</v>
       </c>
-      <c r="AE8" s="27">
+      <c r="AE8" s="29">
         <v>26</v>
       </c>
-      <c r="AF8" s="27">
+      <c r="AF8" s="29">
         <v>27</v>
       </c>
-      <c r="AG8" s="27">
+      <c r="AG8" s="29">
         <v>28</v>
       </c>
-      <c r="AH8" s="27">
+      <c r="AH8" s="29">
         <v>29</v>
       </c>
-      <c r="AI8" s="27">
+      <c r="AI8" s="29">
         <v>30</v>
       </c>
-      <c r="AJ8" s="27">
+      <c r="AJ8" s="29">
         <v>31</v>
       </c>
-      <c r="AK8" s="27">
+      <c r="AK8" s="29">
         <v>32</v>
       </c>
-      <c r="AL8" s="27">
+      <c r="AL8" s="29">
         <v>33</v>
       </c>
-      <c r="AM8" s="27">
+      <c r="AM8" s="29">
         <v>34</v>
       </c>
-      <c r="AN8" s="27">
+      <c r="AN8" s="29">
         <v>35</v>
       </c>
-      <c r="AO8" s="27">
+      <c r="AO8" s="29">
         <v>36</v>
       </c>
-      <c r="AP8" s="27">
+      <c r="AP8" s="29">
         <v>37</v>
       </c>
-      <c r="AQ8" s="27">
+      <c r="AQ8" s="29">
         <v>38</v>
       </c>
-      <c r="AR8" s="27">
+      <c r="AR8" s="29">
         <v>39</v>
       </c>
-      <c r="AS8" s="27">
+      <c r="AS8" s="29">
         <v>40</v>
       </c>
-      <c r="AT8" s="27">
+      <c r="AT8" s="29">
         <v>41</v>
       </c>
-      <c r="AU8" s="27">
+      <c r="AU8" s="29">
         <v>42</v>
       </c>
-      <c r="AV8" s="27">
+      <c r="AV8" s="29">
         <v>43</v>
       </c>
-      <c r="AW8" s="27">
+      <c r="AW8" s="29">
         <v>44</v>
       </c>
-      <c r="AX8" s="27">
+      <c r="AX8" s="29">
         <v>45</v>
       </c>
-      <c r="AY8" s="27">
+      <c r="AY8" s="29">
         <v>46</v>
       </c>
-      <c r="AZ8" s="27">
+      <c r="AZ8" s="29">
         <v>47</v>
       </c>
-      <c r="BA8" s="27">
+      <c r="BA8" s="29">
         <v>48</v>
       </c>
-      <c r="BB8" s="27">
+      <c r="BB8" s="29">
         <v>49</v>
       </c>
-      <c r="BC8" s="27">
+      <c r="BC8" s="29">
         <v>50</v>
       </c>
-      <c r="BD8" s="27">
+      <c r="BD8" s="29">
         <v>51</v>
       </c>
-      <c r="BE8" s="27">
+      <c r="BE8" s="29">
         <v>52</v>
       </c>
-      <c r="BF8" s="27">
+      <c r="BF8" s="29">
         <v>53</v>
       </c>
-      <c r="BG8" s="27">
+      <c r="BG8" s="29">
         <v>54</v>
       </c>
-      <c r="BH8" s="27">
+      <c r="BH8" s="29">
         <v>55</v>
       </c>
-      <c r="BI8" s="27">
+      <c r="BI8" s="29">
         <v>56</v>
       </c>
-      <c r="BJ8" s="27">
+      <c r="BJ8" s="29">
         <v>57</v>
       </c>
-      <c r="BK8" s="27">
+      <c r="BK8" s="29">
         <v>58</v>
       </c>
-      <c r="BL8" s="27">
+      <c r="BL8" s="29">
         <v>59</v>
       </c>
-      <c r="BM8" s="27">
+      <c r="BM8" s="29">
         <v>60</v>
       </c>
-      <c r="BN8" s="27">
+      <c r="BN8" s="29">
         <v>61</v>
       </c>
-      <c r="BO8" s="27">
+      <c r="BO8" s="29">
         <v>62</v>
       </c>
-      <c r="BP8" s="27">
+      <c r="BP8" s="29">
         <v>63</v>
       </c>
-      <c r="BQ8" s="27">
+      <c r="BQ8" s="29">
         <v>64</v>
       </c>
-      <c r="BR8" s="27">
+      <c r="BR8" s="29">
         <v>65</v>
       </c>
-      <c r="BS8" s="27">
+      <c r="BS8" s="29">
         <v>66</v>
       </c>
-      <c r="BT8" s="27">
+      <c r="BT8" s="29">
         <v>67</v>
       </c>
-      <c r="BU8" s="27">
+      <c r="BU8" s="29">
         <v>68</v>
       </c>
-      <c r="BV8" s="27">
+      <c r="BV8" s="29">
         <v>69</v>
       </c>
-      <c r="BW8" s="27">
+      <c r="BW8" s="29">
         <v>70</v>
       </c>
-      <c r="BX8" s="27">
+      <c r="BX8" s="29">
         <v>71</v>
       </c>
-      <c r="BY8" s="27">
+      <c r="BY8" s="29">
         <v>72</v>
       </c>
-      <c r="BZ8" s="27">
+      <c r="BZ8" s="29">
         <v>73</v>
       </c>
-      <c r="CA8" s="27">
+      <c r="CA8" s="29">
         <v>74</v>
       </c>
-      <c r="CB8" s="27">
+      <c r="CB8" s="29">
         <v>75</v>
       </c>
-      <c r="CC8" s="27">
+      <c r="CC8" s="29">
         <v>76</v>
       </c>
-      <c r="CD8" s="27">
+      <c r="CD8" s="29">
         <v>77</v>
       </c>
-      <c r="CE8" s="27">
+      <c r="CE8" s="29">
         <v>78</v>
       </c>
-      <c r="CF8" s="27">
+      <c r="CF8" s="29">
         <v>79</v>
       </c>
-      <c r="CG8" s="27">
+      <c r="CG8" s="29">
         <v>80</v>
       </c>
-      <c r="CH8" s="27">
+      <c r="CH8" s="29">
         <v>81</v>
       </c>
-      <c r="CI8" s="27">
+      <c r="CI8" s="29">
         <v>82</v>
       </c>
-      <c r="CJ8" s="27">
+      <c r="CJ8" s="29">
         <v>83</v>
       </c>
-      <c r="CK8" s="27">
+      <c r="CK8" s="29">
         <v>84</v>
       </c>
-      <c r="CL8" s="27">
+      <c r="CL8" s="29">
         <v>85</v>
       </c>
-      <c r="CM8" s="27">
+      <c r="CM8" s="29">
         <v>86</v>
       </c>
-      <c r="CN8" s="27">
+      <c r="CN8" s="29">
         <v>87</v>
       </c>
-      <c r="CO8" s="27">
+      <c r="CO8" s="29">
         <v>88</v>
       </c>
-      <c r="CP8" s="27">
+      <c r="CP8" s="29">
         <v>89</v>
       </c>
-      <c r="CQ8" s="27">
+      <c r="CQ8" s="29">
         <v>90</v>
       </c>
-      <c r="CR8" s="27">
+      <c r="CR8" s="29">
         <v>91</v>
       </c>
-      <c r="CS8" s="27">
+      <c r="CS8" s="29">
         <v>92</v>
       </c>
-      <c r="CT8" s="27">
+      <c r="CT8" s="29">
         <v>93</v>
       </c>
-      <c r="CU8" s="27">
+      <c r="CU8" s="29">
         <v>94</v>
       </c>
-      <c r="CV8" s="27">
+      <c r="CV8" s="29">
         <v>95</v>
       </c>
-      <c r="CW8" s="27">
+      <c r="CW8" s="29">
         <v>96</v>
       </c>
-      <c r="CX8" s="27">
+      <c r="CX8" s="29">
         <v>97</v>
       </c>
-      <c r="CY8" s="27">
+      <c r="CY8" s="29">
         <v>98</v>
       </c>
-      <c r="CZ8" s="27">
+      <c r="CZ8" s="29">
         <v>99</v>
       </c>
-      <c r="DA8" s="27">
+      <c r="DA8" s="29">
         <v>100</v>
       </c>
-      <c r="DB8" s="27">
+      <c r="DB8" s="29">
         <v>101</v>
       </c>
-      <c r="DC8" s="27">
+      <c r="DC8" s="29">
         <v>102</v>
       </c>
-      <c r="DD8" s="27">
+      <c r="DD8" s="29">
         <v>103</v>
       </c>
-      <c r="DE8" s="27">
+      <c r="DE8" s="29">
         <v>104</v>
       </c>
-      <c r="DF8" s="27">
+      <c r="DF8" s="29">
         <v>105</v>
       </c>
-      <c r="DG8" s="27">
+      <c r="DG8" s="29">
         <v>106</v>
       </c>
-      <c r="DH8" s="27">
+      <c r="DH8" s="29">
         <v>107</v>
       </c>
-      <c r="DI8" s="27">
+      <c r="DI8" s="29">
         <v>108</v>
       </c>
-      <c r="DJ8" s="27">
+      <c r="DJ8" s="29">
         <v>109</v>
       </c>
-      <c r="DK8" s="27">
+      <c r="DK8" s="29">
         <v>110</v>
       </c>
-      <c r="DL8" s="27">
+      <c r="DL8" s="29">
         <v>111</v>
       </c>
-      <c r="DM8" s="27">
+      <c r="DM8" s="29">
         <v>112</v>
       </c>
-      <c r="DN8" s="27">
+      <c r="DN8" s="29">
         <v>113</v>
       </c>
-      <c r="DO8" s="27">
+      <c r="DO8" s="29">
         <v>114</v>
       </c>
-      <c r="DP8" s="27">
+      <c r="DP8" s="29">
         <v>115</v>
       </c>
-      <c r="DQ8" s="27">
+      <c r="DQ8" s="29">
         <v>116</v>
       </c>
-      <c r="DR8" s="27">
+      <c r="DR8" s="29">
         <v>117</v>
       </c>
-      <c r="DS8" s="27">
+      <c r="DS8" s="29">
         <v>118</v>
       </c>
-      <c r="DT8" s="27">
+      <c r="DT8" s="29">
         <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="35" t="s">
+      <c r="A9" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="36" t="s">
+      <c r="B9" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="36"/>
+      <c r="D9" s="59"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="28"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="28"/>
-      <c r="M9" s="28"/>
-      <c r="N9" s="28"/>
-      <c r="O9" s="28"/>
-      <c r="P9" s="28"/>
-      <c r="Q9" s="28"/>
-      <c r="R9" s="28"/>
-      <c r="S9" s="28"/>
-      <c r="T9" s="28"/>
-      <c r="U9" s="28"/>
-      <c r="V9" s="28"/>
-      <c r="W9" s="28"/>
-      <c r="X9" s="28"/>
-      <c r="Y9" s="28"/>
-      <c r="Z9" s="28"/>
-      <c r="AA9" s="28"/>
-      <c r="AB9" s="28"/>
-      <c r="AC9" s="28"/>
-      <c r="AD9" s="28"/>
-      <c r="AE9" s="28"/>
-      <c r="AF9" s="28"/>
-      <c r="AG9" s="28"/>
-      <c r="AH9" s="28"/>
-      <c r="AI9" s="28"/>
-      <c r="AJ9" s="28"/>
-      <c r="AK9" s="28"/>
-      <c r="AL9" s="28"/>
-      <c r="AM9" s="28"/>
-      <c r="AN9" s="28"/>
-      <c r="AO9" s="28"/>
-      <c r="AP9" s="28"/>
-      <c r="AQ9" s="28"/>
-      <c r="AR9" s="28"/>
-      <c r="AS9" s="28"/>
-      <c r="AT9" s="28"/>
-      <c r="AU9" s="28"/>
-      <c r="AV9" s="28"/>
-      <c r="AW9" s="28"/>
-      <c r="AX9" s="28"/>
-      <c r="AY9" s="28"/>
-      <c r="AZ9" s="28"/>
-      <c r="BA9" s="28"/>
-      <c r="BB9" s="28"/>
-      <c r="BC9" s="28"/>
-      <c r="BD9" s="28"/>
-      <c r="BE9" s="28"/>
-      <c r="BF9" s="28"/>
-      <c r="BG9" s="28"/>
-      <c r="BH9" s="28"/>
-      <c r="BI9" s="28"/>
-      <c r="BJ9" s="28"/>
-      <c r="BK9" s="28"/>
-      <c r="BL9" s="28"/>
-      <c r="BM9" s="28"/>
-      <c r="BN9" s="28"/>
-      <c r="BO9" s="28"/>
-      <c r="BP9" s="28"/>
-      <c r="BQ9" s="28"/>
-      <c r="BR9" s="28"/>
-      <c r="BS9" s="28"/>
-      <c r="BT9" s="28"/>
-      <c r="BU9" s="28"/>
-      <c r="BV9" s="28"/>
-      <c r="BW9" s="28"/>
-      <c r="BX9" s="28"/>
-      <c r="BY9" s="28"/>
-      <c r="BZ9" s="28"/>
-      <c r="CA9" s="28"/>
-      <c r="CB9" s="28"/>
-      <c r="CC9" s="28"/>
-      <c r="CD9" s="28"/>
-      <c r="CE9" s="28"/>
-      <c r="CF9" s="28"/>
-      <c r="CG9" s="28"/>
-      <c r="CH9" s="28"/>
-      <c r="CI9" s="28"/>
-      <c r="CJ9" s="28"/>
-      <c r="CK9" s="28"/>
-      <c r="CL9" s="28"/>
-      <c r="CM9" s="28"/>
-      <c r="CN9" s="28"/>
-      <c r="CO9" s="28"/>
-      <c r="CP9" s="28"/>
-      <c r="CQ9" s="28"/>
-      <c r="CR9" s="28"/>
-      <c r="CS9" s="28"/>
-      <c r="CT9" s="28"/>
-      <c r="CU9" s="28"/>
-      <c r="CV9" s="28"/>
-      <c r="CW9" s="28"/>
-      <c r="CX9" s="28"/>
-      <c r="CY9" s="28"/>
-      <c r="CZ9" s="28"/>
-      <c r="DA9" s="28"/>
-      <c r="DB9" s="28"/>
-      <c r="DC9" s="28"/>
-      <c r="DD9" s="28"/>
-      <c r="DE9" s="28"/>
-      <c r="DF9" s="28"/>
-      <c r="DG9" s="28"/>
-      <c r="DH9" s="28"/>
-      <c r="DI9" s="28"/>
-      <c r="DJ9" s="28"/>
-      <c r="DK9" s="28"/>
-      <c r="DL9" s="28"/>
-      <c r="DM9" s="28"/>
-      <c r="DN9" s="28"/>
-      <c r="DO9" s="28"/>
-      <c r="DP9" s="28"/>
-      <c r="DQ9" s="28"/>
-      <c r="DR9" s="28"/>
-      <c r="DS9" s="28"/>
-      <c r="DT9" s="28"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="30"/>
+      <c r="O9" s="30"/>
+      <c r="P9" s="30"/>
+      <c r="Q9" s="30"/>
+      <c r="R9" s="30"/>
+      <c r="S9" s="30"/>
+      <c r="T9" s="30"/>
+      <c r="U9" s="30"/>
+      <c r="V9" s="30"/>
+      <c r="W9" s="30"/>
+      <c r="X9" s="30"/>
+      <c r="Y9" s="30"/>
+      <c r="Z9" s="30"/>
+      <c r="AA9" s="30"/>
+      <c r="AB9" s="30"/>
+      <c r="AC9" s="30"/>
+      <c r="AD9" s="30"/>
+      <c r="AE9" s="30"/>
+      <c r="AF9" s="30"/>
+      <c r="AG9" s="30"/>
+      <c r="AH9" s="30"/>
+      <c r="AI9" s="30"/>
+      <c r="AJ9" s="30"/>
+      <c r="AK9" s="30"/>
+      <c r="AL9" s="30"/>
+      <c r="AM9" s="30"/>
+      <c r="AN9" s="30"/>
+      <c r="AO9" s="30"/>
+      <c r="AP9" s="30"/>
+      <c r="AQ9" s="30"/>
+      <c r="AR9" s="30"/>
+      <c r="AS9" s="30"/>
+      <c r="AT9" s="30"/>
+      <c r="AU9" s="30"/>
+      <c r="AV9" s="30"/>
+      <c r="AW9" s="30"/>
+      <c r="AX9" s="30"/>
+      <c r="AY9" s="30"/>
+      <c r="AZ9" s="30"/>
+      <c r="BA9" s="30"/>
+      <c r="BB9" s="30"/>
+      <c r="BC9" s="30"/>
+      <c r="BD9" s="30"/>
+      <c r="BE9" s="30"/>
+      <c r="BF9" s="30"/>
+      <c r="BG9" s="30"/>
+      <c r="BH9" s="30"/>
+      <c r="BI9" s="30"/>
+      <c r="BJ9" s="30"/>
+      <c r="BK9" s="30"/>
+      <c r="BL9" s="30"/>
+      <c r="BM9" s="30"/>
+      <c r="BN9" s="30"/>
+      <c r="BO9" s="30"/>
+      <c r="BP9" s="30"/>
+      <c r="BQ9" s="30"/>
+      <c r="BR9" s="30"/>
+      <c r="BS9" s="30"/>
+      <c r="BT9" s="30"/>
+      <c r="BU9" s="30"/>
+      <c r="BV9" s="30"/>
+      <c r="BW9" s="30"/>
+      <c r="BX9" s="30"/>
+      <c r="BY9" s="30"/>
+      <c r="BZ9" s="30"/>
+      <c r="CA9" s="30"/>
+      <c r="CB9" s="30"/>
+      <c r="CC9" s="30"/>
+      <c r="CD9" s="30"/>
+      <c r="CE9" s="30"/>
+      <c r="CF9" s="30"/>
+      <c r="CG9" s="30"/>
+      <c r="CH9" s="30"/>
+      <c r="CI9" s="30"/>
+      <c r="CJ9" s="30"/>
+      <c r="CK9" s="30"/>
+      <c r="CL9" s="30"/>
+      <c r="CM9" s="30"/>
+      <c r="CN9" s="30"/>
+      <c r="CO9" s="30"/>
+      <c r="CP9" s="30"/>
+      <c r="CQ9" s="30"/>
+      <c r="CR9" s="30"/>
+      <c r="CS9" s="30"/>
+      <c r="CT9" s="30"/>
+      <c r="CU9" s="30"/>
+      <c r="CV9" s="30"/>
+      <c r="CW9" s="30"/>
+      <c r="CX9" s="30"/>
+      <c r="CY9" s="30"/>
+      <c r="CZ9" s="30"/>
+      <c r="DA9" s="30"/>
+      <c r="DB9" s="30"/>
+      <c r="DC9" s="30"/>
+      <c r="DD9" s="30"/>
+      <c r="DE9" s="30"/>
+      <c r="DF9" s="30"/>
+      <c r="DG9" s="30"/>
+      <c r="DH9" s="30"/>
+      <c r="DI9" s="30"/>
+      <c r="DJ9" s="30"/>
+      <c r="DK9" s="30"/>
+      <c r="DL9" s="30"/>
+      <c r="DM9" s="30"/>
+      <c r="DN9" s="30"/>
+      <c r="DO9" s="30"/>
+      <c r="DP9" s="30"/>
+      <c r="DQ9" s="30"/>
+      <c r="DR9" s="30"/>
+      <c r="DS9" s="30"/>
+      <c r="DT9" s="30"/>
     </row>
     <row r="10" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="35"/>
-      <c r="B10" s="36"/>
+      <c r="A10" s="49"/>
+      <c r="B10" s="59"/>
       <c r="C10" s="6"/>
       <c r="D10" s="4" t="s">
         <v>10</v>
@@ -4846,250 +4850,250 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E26" s="31"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="32"/>
-      <c r="K26" s="32"/>
-      <c r="L26" s="32"/>
-      <c r="M26" s="32"/>
-      <c r="N26" s="32"/>
-      <c r="O26" s="32"/>
-      <c r="P26" s="32"/>
-      <c r="Q26" s="32"/>
-      <c r="R26" s="32"/>
-      <c r="S26" s="32"/>
-      <c r="T26" s="32"/>
-      <c r="U26" s="32"/>
-      <c r="V26" s="32"/>
-      <c r="W26" s="32"/>
-      <c r="X26" s="32"/>
-      <c r="Y26" s="32"/>
-      <c r="Z26" s="32"/>
-      <c r="AA26" s="32"/>
-      <c r="AB26" s="32"/>
-      <c r="AC26" s="32"/>
-      <c r="AD26" s="32"/>
-      <c r="AE26" s="32"/>
-      <c r="AF26" s="32"/>
-      <c r="AG26" s="32"/>
-      <c r="AH26" s="32"/>
-      <c r="AI26" s="32"/>
-      <c r="AJ26" s="32"/>
-      <c r="AK26" s="32"/>
-      <c r="AL26" s="32"/>
-      <c r="AM26" s="32"/>
-      <c r="AN26" s="32"/>
-      <c r="AO26" s="32"/>
-      <c r="AP26" s="32"/>
-      <c r="AQ26" s="32"/>
-      <c r="AR26" s="32"/>
-      <c r="AS26" s="32"/>
-      <c r="AT26" s="32"/>
-      <c r="AU26" s="32"/>
-      <c r="AV26" s="32"/>
-      <c r="AW26" s="32"/>
-      <c r="AX26" s="32"/>
-      <c r="AY26" s="32"/>
-      <c r="AZ26" s="32"/>
-      <c r="BA26" s="32"/>
-      <c r="BB26" s="32"/>
-      <c r="BC26" s="32"/>
-      <c r="BD26" s="32"/>
-      <c r="BE26" s="32"/>
-      <c r="BF26" s="32"/>
-      <c r="BG26" s="32"/>
-      <c r="BH26" s="32"/>
-      <c r="BI26" s="32"/>
-      <c r="BJ26" s="32"/>
-      <c r="BK26" s="32"/>
-      <c r="BL26" s="32"/>
-      <c r="BM26" s="32"/>
-      <c r="BN26" s="32"/>
-      <c r="BO26" s="32"/>
-      <c r="BP26" s="32"/>
-      <c r="BQ26" s="32"/>
-      <c r="BR26" s="32"/>
-      <c r="BS26" s="32"/>
-      <c r="BT26" s="32"/>
-      <c r="BU26" s="32"/>
-      <c r="BV26" s="32"/>
-      <c r="BW26" s="32"/>
-      <c r="BX26" s="32"/>
-      <c r="BY26" s="32"/>
-      <c r="BZ26" s="32"/>
-      <c r="CA26" s="32"/>
-      <c r="CB26" s="32"/>
-      <c r="CC26" s="32"/>
-      <c r="CD26" s="32"/>
-      <c r="CE26" s="32"/>
-      <c r="CF26" s="32"/>
-      <c r="CG26" s="32"/>
-      <c r="CH26" s="32"/>
-      <c r="CI26" s="32"/>
-      <c r="CJ26" s="32"/>
-      <c r="CK26" s="32"/>
-      <c r="CL26" s="32"/>
-      <c r="CM26" s="32"/>
-      <c r="CN26" s="32"/>
-      <c r="CO26" s="32"/>
-      <c r="CP26" s="32"/>
-      <c r="CQ26" s="32"/>
-      <c r="CR26" s="32"/>
-      <c r="CS26" s="32"/>
-      <c r="CT26" s="32"/>
-      <c r="CU26" s="32"/>
-      <c r="CV26" s="32"/>
-      <c r="CW26" s="32"/>
-      <c r="CX26" s="32"/>
-      <c r="CY26" s="32"/>
-      <c r="CZ26" s="32"/>
-      <c r="DA26" s="32"/>
-      <c r="DB26" s="32"/>
-      <c r="DC26" s="32"/>
-      <c r="DD26" s="32"/>
-      <c r="DE26" s="32"/>
-      <c r="DF26" s="32"/>
-      <c r="DG26" s="32"/>
-      <c r="DH26" s="32"/>
-      <c r="DI26" s="32"/>
-      <c r="DJ26" s="32"/>
-      <c r="DK26" s="32"/>
-      <c r="DL26" s="32"/>
-      <c r="DM26" s="32"/>
-      <c r="DN26" s="32"/>
-      <c r="DO26" s="32"/>
-      <c r="DP26" s="32"/>
-      <c r="DQ26" s="32"/>
-      <c r="DR26" s="32"/>
-      <c r="DS26" s="32"/>
-      <c r="DT26" s="32"/>
+      <c r="E26" s="58"/>
+      <c r="F26" s="51"/>
+      <c r="G26" s="51"/>
+      <c r="H26" s="51"/>
+      <c r="I26" s="51"/>
+      <c r="J26" s="51"/>
+      <c r="K26" s="51"/>
+      <c r="L26" s="51"/>
+      <c r="M26" s="51"/>
+      <c r="N26" s="51"/>
+      <c r="O26" s="51"/>
+      <c r="P26" s="51"/>
+      <c r="Q26" s="51"/>
+      <c r="R26" s="51"/>
+      <c r="S26" s="51"/>
+      <c r="T26" s="51"/>
+      <c r="U26" s="51"/>
+      <c r="V26" s="51"/>
+      <c r="W26" s="51"/>
+      <c r="X26" s="51"/>
+      <c r="Y26" s="51"/>
+      <c r="Z26" s="51"/>
+      <c r="AA26" s="51"/>
+      <c r="AB26" s="51"/>
+      <c r="AC26" s="51"/>
+      <c r="AD26" s="51"/>
+      <c r="AE26" s="51"/>
+      <c r="AF26" s="51"/>
+      <c r="AG26" s="51"/>
+      <c r="AH26" s="51"/>
+      <c r="AI26" s="51"/>
+      <c r="AJ26" s="51"/>
+      <c r="AK26" s="51"/>
+      <c r="AL26" s="51"/>
+      <c r="AM26" s="51"/>
+      <c r="AN26" s="51"/>
+      <c r="AO26" s="51"/>
+      <c r="AP26" s="51"/>
+      <c r="AQ26" s="51"/>
+      <c r="AR26" s="51"/>
+      <c r="AS26" s="51"/>
+      <c r="AT26" s="51"/>
+      <c r="AU26" s="51"/>
+      <c r="AV26" s="51"/>
+      <c r="AW26" s="51"/>
+      <c r="AX26" s="51"/>
+      <c r="AY26" s="51"/>
+      <c r="AZ26" s="51"/>
+      <c r="BA26" s="51"/>
+      <c r="BB26" s="51"/>
+      <c r="BC26" s="51"/>
+      <c r="BD26" s="51"/>
+      <c r="BE26" s="51"/>
+      <c r="BF26" s="51"/>
+      <c r="BG26" s="51"/>
+      <c r="BH26" s="51"/>
+      <c r="BI26" s="51"/>
+      <c r="BJ26" s="51"/>
+      <c r="BK26" s="51"/>
+      <c r="BL26" s="51"/>
+      <c r="BM26" s="51"/>
+      <c r="BN26" s="51"/>
+      <c r="BO26" s="51"/>
+      <c r="BP26" s="51"/>
+      <c r="BQ26" s="51"/>
+      <c r="BR26" s="51"/>
+      <c r="BS26" s="51"/>
+      <c r="BT26" s="51"/>
+      <c r="BU26" s="51"/>
+      <c r="BV26" s="51"/>
+      <c r="BW26" s="51"/>
+      <c r="BX26" s="51"/>
+      <c r="BY26" s="51"/>
+      <c r="BZ26" s="51"/>
+      <c r="CA26" s="51"/>
+      <c r="CB26" s="51"/>
+      <c r="CC26" s="51"/>
+      <c r="CD26" s="51"/>
+      <c r="CE26" s="51"/>
+      <c r="CF26" s="51"/>
+      <c r="CG26" s="51"/>
+      <c r="CH26" s="51"/>
+      <c r="CI26" s="51"/>
+      <c r="CJ26" s="51"/>
+      <c r="CK26" s="51"/>
+      <c r="CL26" s="51"/>
+      <c r="CM26" s="51"/>
+      <c r="CN26" s="51"/>
+      <c r="CO26" s="51"/>
+      <c r="CP26" s="51"/>
+      <c r="CQ26" s="51"/>
+      <c r="CR26" s="51"/>
+      <c r="CS26" s="51"/>
+      <c r="CT26" s="51"/>
+      <c r="CU26" s="51"/>
+      <c r="CV26" s="51"/>
+      <c r="CW26" s="51"/>
+      <c r="CX26" s="51"/>
+      <c r="CY26" s="51"/>
+      <c r="CZ26" s="51"/>
+      <c r="DA26" s="51"/>
+      <c r="DB26" s="51"/>
+      <c r="DC26" s="51"/>
+      <c r="DD26" s="51"/>
+      <c r="DE26" s="51"/>
+      <c r="DF26" s="51"/>
+      <c r="DG26" s="51"/>
+      <c r="DH26" s="51"/>
+      <c r="DI26" s="51"/>
+      <c r="DJ26" s="51"/>
+      <c r="DK26" s="51"/>
+      <c r="DL26" s="51"/>
+      <c r="DM26" s="51"/>
+      <c r="DN26" s="51"/>
+      <c r="DO26" s="51"/>
+      <c r="DP26" s="51"/>
+      <c r="DQ26" s="51"/>
+      <c r="DR26" s="51"/>
+      <c r="DS26" s="51"/>
+      <c r="DT26" s="51"/>
     </row>
     <row r="27" spans="1:124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E27" s="1">
         <v>4</v>
       </c>
-      <c r="F27" s="56"/>
-      <c r="G27" s="56"/>
-      <c r="H27" s="56"/>
-      <c r="I27" s="56"/>
-      <c r="J27" s="56"/>
-      <c r="K27" s="56"/>
-      <c r="L27" s="56"/>
-      <c r="M27" s="56"/>
-      <c r="N27" s="56"/>
-      <c r="O27" s="56"/>
-      <c r="P27" s="56"/>
-      <c r="Q27" s="56"/>
-      <c r="R27" s="56"/>
-      <c r="S27" s="56"/>
-      <c r="T27" s="56"/>
-      <c r="U27" s="56"/>
-      <c r="V27" s="56"/>
-      <c r="W27" s="56"/>
-      <c r="X27" s="56"/>
-      <c r="Y27" s="56"/>
-      <c r="Z27" s="56"/>
-      <c r="AA27" s="56"/>
-      <c r="AB27" s="56"/>
-      <c r="AC27" s="56"/>
-      <c r="AD27" s="56"/>
-      <c r="AE27" s="56"/>
-      <c r="AF27" s="56"/>
-      <c r="AG27" s="56"/>
-      <c r="AH27" s="56"/>
-      <c r="AI27" s="56"/>
-      <c r="AJ27" s="56"/>
-      <c r="AK27" s="56"/>
-      <c r="AL27" s="56"/>
-      <c r="AM27" s="56"/>
-      <c r="AN27" s="56"/>
-      <c r="AO27" s="56"/>
-      <c r="AP27" s="56"/>
-      <c r="AQ27" s="56"/>
-      <c r="AR27" s="56"/>
-      <c r="AS27" s="56"/>
-      <c r="AT27" s="56"/>
-      <c r="AU27" s="56"/>
-      <c r="AV27" s="56"/>
-      <c r="AW27" s="56"/>
-      <c r="AX27" s="56"/>
-      <c r="AY27" s="56"/>
-      <c r="AZ27" s="56"/>
-      <c r="BA27" s="56"/>
-      <c r="BB27" s="56"/>
-      <c r="BC27" s="56"/>
-      <c r="BD27" s="56"/>
-      <c r="BE27" s="56"/>
-      <c r="BF27" s="56"/>
-      <c r="BG27" s="56"/>
-      <c r="BH27" s="56"/>
-      <c r="BI27" s="56"/>
-      <c r="BJ27" s="56"/>
-      <c r="BK27" s="56"/>
-      <c r="BL27" s="56"/>
-      <c r="BM27" s="56"/>
-      <c r="BN27" s="56"/>
-      <c r="BO27" s="56"/>
-      <c r="BP27" s="56"/>
-      <c r="BQ27" s="56"/>
-      <c r="BR27" s="56"/>
-      <c r="BS27" s="56"/>
-      <c r="BT27" s="56"/>
-      <c r="BU27" s="56"/>
-      <c r="BV27" s="56"/>
-      <c r="BW27" s="56"/>
-      <c r="BX27" s="56"/>
-      <c r="BY27" s="56"/>
-      <c r="BZ27" s="56"/>
-      <c r="CA27" s="56"/>
-      <c r="CB27" s="56"/>
-      <c r="CC27" s="56"/>
-      <c r="CD27" s="56"/>
-      <c r="CE27" s="57"/>
-      <c r="CF27" s="58"/>
-      <c r="CG27" s="58"/>
-      <c r="CH27" s="58"/>
-      <c r="CI27" s="58"/>
-      <c r="CJ27" s="58"/>
-      <c r="CK27" s="58"/>
-      <c r="CL27" s="58"/>
-      <c r="CM27" s="58"/>
-      <c r="CN27" s="58"/>
-      <c r="CO27" s="58"/>
-      <c r="CP27" s="58"/>
-      <c r="CQ27" s="58"/>
-      <c r="CR27" s="58"/>
-      <c r="CS27" s="58"/>
-      <c r="CT27" s="58"/>
-      <c r="CU27" s="58"/>
-      <c r="CV27" s="58"/>
-      <c r="CW27" s="58"/>
-      <c r="CX27" s="58"/>
-      <c r="CY27" s="58"/>
-      <c r="CZ27" s="58"/>
-      <c r="DA27" s="58"/>
-      <c r="DB27" s="58"/>
-      <c r="DC27" s="58"/>
-      <c r="DD27" s="58"/>
-      <c r="DE27" s="58"/>
-      <c r="DF27" s="58"/>
-      <c r="DG27" s="58"/>
-      <c r="DH27" s="58"/>
-      <c r="DI27" s="58"/>
-      <c r="DJ27" s="58"/>
-      <c r="DK27" s="58"/>
-      <c r="DL27" s="58"/>
-      <c r="DM27" s="58"/>
-      <c r="DN27" s="58"/>
-      <c r="DO27" s="58"/>
-      <c r="DP27" s="58"/>
-      <c r="DQ27" s="58"/>
-      <c r="DR27" s="58"/>
-      <c r="DS27" s="58"/>
-      <c r="DT27" s="58"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="33"/>
+      <c r="I27" s="33"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="33"/>
+      <c r="M27" s="33"/>
+      <c r="N27" s="33"/>
+      <c r="O27" s="33"/>
+      <c r="P27" s="33"/>
+      <c r="Q27" s="33"/>
+      <c r="R27" s="33"/>
+      <c r="S27" s="33"/>
+      <c r="T27" s="33"/>
+      <c r="U27" s="33"/>
+      <c r="V27" s="33"/>
+      <c r="W27" s="33"/>
+      <c r="X27" s="33"/>
+      <c r="Y27" s="33"/>
+      <c r="Z27" s="33"/>
+      <c r="AA27" s="33"/>
+      <c r="AB27" s="33"/>
+      <c r="AC27" s="33"/>
+      <c r="AD27" s="33"/>
+      <c r="AE27" s="33"/>
+      <c r="AF27" s="33"/>
+      <c r="AG27" s="33"/>
+      <c r="AH27" s="33"/>
+      <c r="AI27" s="33"/>
+      <c r="AJ27" s="33"/>
+      <c r="AK27" s="33"/>
+      <c r="AL27" s="33"/>
+      <c r="AM27" s="33"/>
+      <c r="AN27" s="33"/>
+      <c r="AO27" s="33"/>
+      <c r="AP27" s="33"/>
+      <c r="AQ27" s="33"/>
+      <c r="AR27" s="33"/>
+      <c r="AS27" s="33"/>
+      <c r="AT27" s="33"/>
+      <c r="AU27" s="33"/>
+      <c r="AV27" s="33"/>
+      <c r="AW27" s="33"/>
+      <c r="AX27" s="33"/>
+      <c r="AY27" s="33"/>
+      <c r="AZ27" s="33"/>
+      <c r="BA27" s="33"/>
+      <c r="BB27" s="33"/>
+      <c r="BC27" s="33"/>
+      <c r="BD27" s="33"/>
+      <c r="BE27" s="33"/>
+      <c r="BF27" s="33"/>
+      <c r="BG27" s="33"/>
+      <c r="BH27" s="33"/>
+      <c r="BI27" s="33"/>
+      <c r="BJ27" s="33"/>
+      <c r="BK27" s="33"/>
+      <c r="BL27" s="33"/>
+      <c r="BM27" s="33"/>
+      <c r="BN27" s="33"/>
+      <c r="BO27" s="33"/>
+      <c r="BP27" s="33"/>
+      <c r="BQ27" s="33"/>
+      <c r="BR27" s="33"/>
+      <c r="BS27" s="33"/>
+      <c r="BT27" s="33"/>
+      <c r="BU27" s="33"/>
+      <c r="BV27" s="33"/>
+      <c r="BW27" s="33"/>
+      <c r="BX27" s="33"/>
+      <c r="BY27" s="33"/>
+      <c r="BZ27" s="33"/>
+      <c r="CA27" s="33"/>
+      <c r="CB27" s="33"/>
+      <c r="CC27" s="33"/>
+      <c r="CD27" s="33"/>
+      <c r="CE27" s="34"/>
+      <c r="CF27" s="35"/>
+      <c r="CG27" s="35"/>
+      <c r="CH27" s="35"/>
+      <c r="CI27" s="35"/>
+      <c r="CJ27" s="35"/>
+      <c r="CK27" s="35"/>
+      <c r="CL27" s="35"/>
+      <c r="CM27" s="35"/>
+      <c r="CN27" s="35"/>
+      <c r="CO27" s="35"/>
+      <c r="CP27" s="35"/>
+      <c r="CQ27" s="35"/>
+      <c r="CR27" s="35"/>
+      <c r="CS27" s="35"/>
+      <c r="CT27" s="35"/>
+      <c r="CU27" s="35"/>
+      <c r="CV27" s="35"/>
+      <c r="CW27" s="35"/>
+      <c r="CX27" s="35"/>
+      <c r="CY27" s="35"/>
+      <c r="CZ27" s="35"/>
+      <c r="DA27" s="35"/>
+      <c r="DB27" s="35"/>
+      <c r="DC27" s="35"/>
+      <c r="DD27" s="35"/>
+      <c r="DE27" s="35"/>
+      <c r="DF27" s="35"/>
+      <c r="DG27" s="35"/>
+      <c r="DH27" s="35"/>
+      <c r="DI27" s="35"/>
+      <c r="DJ27" s="35"/>
+      <c r="DK27" s="35"/>
+      <c r="DL27" s="35"/>
+      <c r="DM27" s="35"/>
+      <c r="DN27" s="35"/>
+      <c r="DO27" s="35"/>
+      <c r="DP27" s="35"/>
+      <c r="DQ27" s="35"/>
+      <c r="DR27" s="35"/>
+      <c r="DS27" s="35"/>
+      <c r="DT27" s="35"/>
     </row>
     <row r="29" spans="1:124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E29" s="21">
@@ -5107,91 +5111,174 @@
         <v>41</v>
       </c>
     </row>
+    <row r="31" spans="1:124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AJ31" s="70"/>
+      <c r="AK31" s="17" t="s">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="267">
-    <mergeCell ref="U2:U7"/>
-    <mergeCell ref="AH1:AK1"/>
-    <mergeCell ref="CS8:CS9"/>
-    <mergeCell ref="AD1:AG1"/>
-    <mergeCell ref="V1:Y1"/>
-    <mergeCell ref="R1:U1"/>
-    <mergeCell ref="DQ2:DQ7"/>
-    <mergeCell ref="DR2:DR7"/>
-    <mergeCell ref="DS2:DS7"/>
-    <mergeCell ref="DT2:DT7"/>
-    <mergeCell ref="CX2:CX7"/>
-    <mergeCell ref="CY2:CY7"/>
-    <mergeCell ref="DA2:DA7"/>
-    <mergeCell ref="DB2:DB7"/>
-    <mergeCell ref="DC2:DC7"/>
-    <mergeCell ref="DD2:DD7"/>
-    <mergeCell ref="DE2:DE7"/>
-    <mergeCell ref="CZ2:CZ7"/>
-    <mergeCell ref="DN2:DN7"/>
-    <mergeCell ref="DO2:DO7"/>
-    <mergeCell ref="DP2:DP7"/>
-    <mergeCell ref="DG2:DG7"/>
-    <mergeCell ref="DH2:DH7"/>
-    <mergeCell ref="DI2:DI7"/>
-    <mergeCell ref="DJ2:DJ7"/>
-    <mergeCell ref="DK2:DK7"/>
-    <mergeCell ref="CP2:CP7"/>
-    <mergeCell ref="V2:V7"/>
-    <mergeCell ref="W2:W7"/>
-    <mergeCell ref="F27:S27"/>
-    <mergeCell ref="T27:AW27"/>
-    <mergeCell ref="AX27:CD27"/>
-    <mergeCell ref="CE27:DT27"/>
-    <mergeCell ref="DG8:DG9"/>
-    <mergeCell ref="DH8:DH9"/>
-    <mergeCell ref="DI8:DI9"/>
-    <mergeCell ref="DJ8:DJ9"/>
-    <mergeCell ref="DK8:DK9"/>
-    <mergeCell ref="DL8:DL9"/>
-    <mergeCell ref="DM8:DM9"/>
-    <mergeCell ref="DN8:DN9"/>
-    <mergeCell ref="DO8:DO9"/>
-    <mergeCell ref="DP8:DP9"/>
-    <mergeCell ref="DA8:DA9"/>
-    <mergeCell ref="DB8:DB9"/>
-    <mergeCell ref="DC8:DC9"/>
-    <mergeCell ref="DD8:DD9"/>
-    <mergeCell ref="DE8:DE9"/>
-    <mergeCell ref="CQ8:CQ9"/>
-    <mergeCell ref="CR8:CR9"/>
-    <mergeCell ref="BK2:BK7"/>
-    <mergeCell ref="BN8:BN9"/>
-    <mergeCell ref="CI8:CI9"/>
-    <mergeCell ref="CK8:CK9"/>
-    <mergeCell ref="CL8:CL9"/>
-    <mergeCell ref="BX8:BX9"/>
-    <mergeCell ref="BY8:BY9"/>
-    <mergeCell ref="DL2:DL7"/>
-    <mergeCell ref="DM2:DM7"/>
-    <mergeCell ref="DF2:DF7"/>
-    <mergeCell ref="CW2:CW7"/>
-    <mergeCell ref="CU2:CU7"/>
-    <mergeCell ref="CV2:CV7"/>
-    <mergeCell ref="CQ2:CQ7"/>
-    <mergeCell ref="CR2:CR7"/>
-    <mergeCell ref="CS2:CS7"/>
-    <mergeCell ref="CT2:CT7"/>
-    <mergeCell ref="CI2:CI7"/>
-    <mergeCell ref="CJ2:CJ7"/>
-    <mergeCell ref="CK2:CK7"/>
-    <mergeCell ref="CL2:CL7"/>
-    <mergeCell ref="CM2:CM7"/>
-    <mergeCell ref="CN2:CN7"/>
-    <mergeCell ref="CO2:CO7"/>
-    <mergeCell ref="BM2:BM7"/>
-    <mergeCell ref="BN2:BN7"/>
-    <mergeCell ref="BO2:BO7"/>
-    <mergeCell ref="BP2:BP7"/>
-    <mergeCell ref="CA2:CA7"/>
-    <mergeCell ref="BW2:BW7"/>
-    <mergeCell ref="BX2:BX7"/>
-    <mergeCell ref="BY2:BY7"/>
-    <mergeCell ref="BZ2:BZ7"/>
+    <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="N1:Q1"/>
+    <mergeCell ref="BC8:BC9"/>
+    <mergeCell ref="BD8:BD9"/>
+    <mergeCell ref="BE8:BE9"/>
+    <mergeCell ref="AN8:AN9"/>
+    <mergeCell ref="AO8:AO9"/>
+    <mergeCell ref="AP8:AP9"/>
+    <mergeCell ref="AQ8:AQ9"/>
+    <mergeCell ref="AR8:AR9"/>
+    <mergeCell ref="AS8:AS9"/>
+    <mergeCell ref="AT8:AT9"/>
+    <mergeCell ref="AU8:AU9"/>
+    <mergeCell ref="AV8:AV9"/>
+    <mergeCell ref="AE8:AE9"/>
+    <mergeCell ref="AF8:AF9"/>
+    <mergeCell ref="AG8:AG9"/>
+    <mergeCell ref="AH8:AH9"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AJ8:AJ9"/>
+    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="AL8:AL9"/>
+    <mergeCell ref="AM8:AM9"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="BO8:BO9"/>
+    <mergeCell ref="BP8:BP9"/>
+    <mergeCell ref="BQ8:BQ9"/>
+    <mergeCell ref="BR8:BR9"/>
+    <mergeCell ref="BS8:BS9"/>
+    <mergeCell ref="BT8:BT9"/>
+    <mergeCell ref="BZ8:BZ9"/>
+    <mergeCell ref="CA8:CA9"/>
+    <mergeCell ref="BH8:BH9"/>
+    <mergeCell ref="BI8:BI9"/>
+    <mergeCell ref="BJ8:BJ9"/>
+    <mergeCell ref="BK8:BK9"/>
+    <mergeCell ref="BL8:BL9"/>
+    <mergeCell ref="BM8:BM9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
+    <mergeCell ref="CB8:CB9"/>
+    <mergeCell ref="CC8:CC9"/>
+    <mergeCell ref="CD8:CD9"/>
+    <mergeCell ref="CE8:CE9"/>
+    <mergeCell ref="CF8:CF9"/>
+    <mergeCell ref="CV8:CV9"/>
+    <mergeCell ref="BQ2:BQ7"/>
+    <mergeCell ref="BR2:BR7"/>
+    <mergeCell ref="BS2:BS7"/>
+    <mergeCell ref="BT2:BT7"/>
+    <mergeCell ref="BU2:BU7"/>
+    <mergeCell ref="BV2:BV7"/>
+    <mergeCell ref="CO8:CO9"/>
+    <mergeCell ref="CP8:CP9"/>
+    <mergeCell ref="CH2:CH7"/>
+    <mergeCell ref="CT8:CT9"/>
+    <mergeCell ref="CU8:CU9"/>
+    <mergeCell ref="CB2:CB7"/>
+    <mergeCell ref="CC2:CC7"/>
+    <mergeCell ref="CD2:CD7"/>
+    <mergeCell ref="CE2:CE7"/>
+    <mergeCell ref="CF2:CF7"/>
+    <mergeCell ref="CG2:CG7"/>
+    <mergeCell ref="CJ8:CJ9"/>
+    <mergeCell ref="E26:DT26"/>
+    <mergeCell ref="DF8:DF9"/>
+    <mergeCell ref="DQ8:DQ9"/>
+    <mergeCell ref="DR8:DR9"/>
+    <mergeCell ref="DS8:DS9"/>
+    <mergeCell ref="DT8:DT9"/>
+    <mergeCell ref="CY8:CY9"/>
+    <mergeCell ref="CZ8:CZ9"/>
+    <mergeCell ref="CM8:CM9"/>
+    <mergeCell ref="CW8:CW9"/>
+    <mergeCell ref="CX8:CX9"/>
+    <mergeCell ref="BU8:BU9"/>
+    <mergeCell ref="BV8:BV9"/>
+    <mergeCell ref="BW8:BW9"/>
+    <mergeCell ref="BF8:BF9"/>
+    <mergeCell ref="BG8:BG9"/>
+    <mergeCell ref="CG8:CG9"/>
+    <mergeCell ref="CH8:CH9"/>
+    <mergeCell ref="AW8:AW9"/>
+    <mergeCell ref="AX8:AX9"/>
+    <mergeCell ref="AY8:AY9"/>
+    <mergeCell ref="AZ8:AZ9"/>
+    <mergeCell ref="BA8:BA9"/>
+    <mergeCell ref="BB8:BB9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="F2:F7"/>
+    <mergeCell ref="G2:G7"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="I2:I7"/>
+    <mergeCell ref="J2:J7"/>
+    <mergeCell ref="K2:K7"/>
+    <mergeCell ref="L2:L7"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="M2:M7"/>
+    <mergeCell ref="N2:N7"/>
+    <mergeCell ref="O2:O7"/>
+    <mergeCell ref="P2:P7"/>
+    <mergeCell ref="Q2:Q7"/>
+    <mergeCell ref="R2:R7"/>
+    <mergeCell ref="S2:S7"/>
+    <mergeCell ref="T2:T7"/>
+    <mergeCell ref="CN8:CN9"/>
+    <mergeCell ref="Y2:Y7"/>
+    <mergeCell ref="Z2:Z7"/>
+    <mergeCell ref="AA2:AA7"/>
+    <mergeCell ref="AB2:AB7"/>
+    <mergeCell ref="AC2:AC7"/>
+    <mergeCell ref="AD2:AD7"/>
+    <mergeCell ref="AE2:AE7"/>
+    <mergeCell ref="AH2:AH7"/>
+    <mergeCell ref="AI2:AI7"/>
+    <mergeCell ref="AJ2:AJ7"/>
+    <mergeCell ref="AK2:AK7"/>
+    <mergeCell ref="AL2:AL7"/>
+    <mergeCell ref="AM2:AM7"/>
+    <mergeCell ref="AN2:AN7"/>
+    <mergeCell ref="AO2:AO7"/>
+    <mergeCell ref="AG2:AG7"/>
     <mergeCell ref="X2:X7"/>
     <mergeCell ref="AF2:AF7"/>
     <mergeCell ref="AX2:AX7"/>
@@ -5216,166 +5303,89 @@
     <mergeCell ref="BH2:BH7"/>
     <mergeCell ref="BI2:BI7"/>
     <mergeCell ref="BJ2:BJ7"/>
-    <mergeCell ref="N2:N7"/>
-    <mergeCell ref="O2:O7"/>
-    <mergeCell ref="P2:P7"/>
-    <mergeCell ref="Q2:Q7"/>
-    <mergeCell ref="R2:R7"/>
-    <mergeCell ref="S2:S7"/>
-    <mergeCell ref="T2:T7"/>
-    <mergeCell ref="CN8:CN9"/>
-    <mergeCell ref="Y2:Y7"/>
-    <mergeCell ref="Z2:Z7"/>
-    <mergeCell ref="AA2:AA7"/>
-    <mergeCell ref="AB2:AB7"/>
-    <mergeCell ref="AC2:AC7"/>
-    <mergeCell ref="AD2:AD7"/>
-    <mergeCell ref="AE2:AE7"/>
-    <mergeCell ref="AH2:AH7"/>
-    <mergeCell ref="AI2:AI7"/>
-    <mergeCell ref="AJ2:AJ7"/>
-    <mergeCell ref="AK2:AK7"/>
-    <mergeCell ref="AL2:AL7"/>
-    <mergeCell ref="AM2:AM7"/>
-    <mergeCell ref="AN2:AN7"/>
-    <mergeCell ref="AO2:AO7"/>
-    <mergeCell ref="AG2:AG7"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="F2:F7"/>
-    <mergeCell ref="G2:G7"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="I2:I7"/>
-    <mergeCell ref="J2:J7"/>
-    <mergeCell ref="K2:K7"/>
-    <mergeCell ref="L2:L7"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="M2:M7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="E26:DT26"/>
-    <mergeCell ref="DF8:DF9"/>
-    <mergeCell ref="DQ8:DQ9"/>
-    <mergeCell ref="DR8:DR9"/>
-    <mergeCell ref="DS8:DS9"/>
-    <mergeCell ref="DT8:DT9"/>
-    <mergeCell ref="CY8:CY9"/>
-    <mergeCell ref="CZ8:CZ9"/>
-    <mergeCell ref="CM8:CM9"/>
-    <mergeCell ref="CW8:CW9"/>
-    <mergeCell ref="CX8:CX9"/>
-    <mergeCell ref="BU8:BU9"/>
-    <mergeCell ref="BV8:BV9"/>
-    <mergeCell ref="BW8:BW9"/>
-    <mergeCell ref="BF8:BF9"/>
-    <mergeCell ref="BG8:BG9"/>
-    <mergeCell ref="CG8:CG9"/>
-    <mergeCell ref="CH8:CH9"/>
-    <mergeCell ref="AW8:AW9"/>
-    <mergeCell ref="AX8:AX9"/>
-    <mergeCell ref="AY8:AY9"/>
-    <mergeCell ref="AZ8:AZ9"/>
-    <mergeCell ref="BA8:BA9"/>
-    <mergeCell ref="BB8:BB9"/>
-    <mergeCell ref="CB8:CB9"/>
-    <mergeCell ref="CC8:CC9"/>
-    <mergeCell ref="CD8:CD9"/>
-    <mergeCell ref="CE8:CE9"/>
-    <mergeCell ref="CF8:CF9"/>
-    <mergeCell ref="CV8:CV9"/>
-    <mergeCell ref="BQ2:BQ7"/>
-    <mergeCell ref="BR2:BR7"/>
-    <mergeCell ref="BS2:BS7"/>
-    <mergeCell ref="BT2:BT7"/>
-    <mergeCell ref="BU2:BU7"/>
-    <mergeCell ref="BV2:BV7"/>
-    <mergeCell ref="CO8:CO9"/>
-    <mergeCell ref="CP8:CP9"/>
-    <mergeCell ref="CH2:CH7"/>
-    <mergeCell ref="CT8:CT9"/>
-    <mergeCell ref="CU8:CU9"/>
-    <mergeCell ref="CB2:CB7"/>
-    <mergeCell ref="CC2:CC7"/>
-    <mergeCell ref="CD2:CD7"/>
-    <mergeCell ref="CE2:CE7"/>
-    <mergeCell ref="CF2:CF7"/>
-    <mergeCell ref="CG2:CG7"/>
-    <mergeCell ref="CJ8:CJ9"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="BO8:BO9"/>
-    <mergeCell ref="BP8:BP9"/>
-    <mergeCell ref="BQ8:BQ9"/>
-    <mergeCell ref="BR8:BR9"/>
-    <mergeCell ref="BS8:BS9"/>
-    <mergeCell ref="BT8:BT9"/>
-    <mergeCell ref="BZ8:BZ9"/>
-    <mergeCell ref="CA8:CA9"/>
-    <mergeCell ref="BH8:BH9"/>
-    <mergeCell ref="BI8:BI9"/>
-    <mergeCell ref="BJ8:BJ9"/>
-    <mergeCell ref="BK8:BK9"/>
-    <mergeCell ref="BL8:BL9"/>
-    <mergeCell ref="BM8:BM9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="Z1:AC1"/>
-    <mergeCell ref="N1:Q1"/>
-    <mergeCell ref="BC8:BC9"/>
-    <mergeCell ref="BD8:BD9"/>
-    <mergeCell ref="BE8:BE9"/>
-    <mergeCell ref="AN8:AN9"/>
-    <mergeCell ref="AO8:AO9"/>
-    <mergeCell ref="AP8:AP9"/>
-    <mergeCell ref="AQ8:AQ9"/>
-    <mergeCell ref="AR8:AR9"/>
-    <mergeCell ref="AS8:AS9"/>
-    <mergeCell ref="AT8:AT9"/>
-    <mergeCell ref="AU8:AU9"/>
-    <mergeCell ref="AV8:AV9"/>
-    <mergeCell ref="AE8:AE9"/>
-    <mergeCell ref="AF8:AF9"/>
-    <mergeCell ref="AG8:AG9"/>
-    <mergeCell ref="AH8:AH9"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AJ8:AJ9"/>
-    <mergeCell ref="AK8:AK9"/>
-    <mergeCell ref="AL8:AL9"/>
-    <mergeCell ref="AM8:AM9"/>
-    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="CJ2:CJ7"/>
+    <mergeCell ref="CK2:CK7"/>
+    <mergeCell ref="CL2:CL7"/>
+    <mergeCell ref="CM2:CM7"/>
+    <mergeCell ref="CN2:CN7"/>
+    <mergeCell ref="CO2:CO7"/>
+    <mergeCell ref="BM2:BM7"/>
+    <mergeCell ref="BN2:BN7"/>
+    <mergeCell ref="BO2:BO7"/>
+    <mergeCell ref="BP2:BP7"/>
+    <mergeCell ref="CA2:CA7"/>
+    <mergeCell ref="BW2:BW7"/>
+    <mergeCell ref="BX2:BX7"/>
+    <mergeCell ref="BY2:BY7"/>
+    <mergeCell ref="BZ2:BZ7"/>
+    <mergeCell ref="F27:S27"/>
+    <mergeCell ref="T27:AW27"/>
+    <mergeCell ref="AX27:CD27"/>
+    <mergeCell ref="CE27:DT27"/>
+    <mergeCell ref="DG8:DG9"/>
+    <mergeCell ref="DH8:DH9"/>
+    <mergeCell ref="DI8:DI9"/>
+    <mergeCell ref="DJ8:DJ9"/>
+    <mergeCell ref="DK8:DK9"/>
+    <mergeCell ref="DL8:DL9"/>
+    <mergeCell ref="DM8:DM9"/>
+    <mergeCell ref="DN8:DN9"/>
+    <mergeCell ref="DO8:DO9"/>
+    <mergeCell ref="DP8:DP9"/>
+    <mergeCell ref="DA8:DA9"/>
+    <mergeCell ref="DB8:DB9"/>
+    <mergeCell ref="DC8:DC9"/>
+    <mergeCell ref="DD8:DD9"/>
+    <mergeCell ref="DE8:DE9"/>
+    <mergeCell ref="CQ8:CQ9"/>
+    <mergeCell ref="CR8:CR9"/>
+    <mergeCell ref="BN8:BN9"/>
+    <mergeCell ref="CI8:CI9"/>
+    <mergeCell ref="CK8:CK9"/>
+    <mergeCell ref="DT2:DT7"/>
+    <mergeCell ref="CX2:CX7"/>
+    <mergeCell ref="CY2:CY7"/>
+    <mergeCell ref="DA2:DA7"/>
+    <mergeCell ref="DB2:DB7"/>
+    <mergeCell ref="DC2:DC7"/>
+    <mergeCell ref="DD2:DD7"/>
+    <mergeCell ref="DE2:DE7"/>
+    <mergeCell ref="CZ2:CZ7"/>
+    <mergeCell ref="DN2:DN7"/>
+    <mergeCell ref="DO2:DO7"/>
+    <mergeCell ref="DP2:DP7"/>
+    <mergeCell ref="DG2:DG7"/>
+    <mergeCell ref="DH2:DH7"/>
+    <mergeCell ref="DI2:DI7"/>
+    <mergeCell ref="DJ2:DJ7"/>
+    <mergeCell ref="DK2:DK7"/>
+    <mergeCell ref="DL2:DL7"/>
+    <mergeCell ref="DM2:DM7"/>
+    <mergeCell ref="DF2:DF7"/>
+    <mergeCell ref="U2:U7"/>
+    <mergeCell ref="AH1:AK1"/>
+    <mergeCell ref="CS8:CS9"/>
+    <mergeCell ref="AD1:AG1"/>
+    <mergeCell ref="V1:Y1"/>
+    <mergeCell ref="R1:U1"/>
+    <mergeCell ref="DQ2:DQ7"/>
+    <mergeCell ref="DR2:DR7"/>
+    <mergeCell ref="DS2:DS7"/>
+    <mergeCell ref="CP2:CP7"/>
+    <mergeCell ref="V2:V7"/>
+    <mergeCell ref="W2:W7"/>
+    <mergeCell ref="BK2:BK7"/>
+    <mergeCell ref="CL8:CL9"/>
+    <mergeCell ref="BX8:BX9"/>
+    <mergeCell ref="BY8:BY9"/>
+    <mergeCell ref="CW2:CW7"/>
+    <mergeCell ref="CU2:CU7"/>
+    <mergeCell ref="CV2:CV7"/>
+    <mergeCell ref="CQ2:CQ7"/>
+    <mergeCell ref="CR2:CR7"/>
+    <mergeCell ref="CS2:CS7"/>
+    <mergeCell ref="CT2:CT7"/>
+    <mergeCell ref="CI2:CI7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -5397,49 +5407,49 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="60" t="s">
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="62" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="63"/>
-      <c r="D3" s="66" t="s">
+      <c r="C3" s="65"/>
+      <c r="D3" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="59" t="s">
+      <c r="E3" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="59" t="s">
+      <c r="F3" s="61" t="s">
         <v>39</v>
       </c>
-      <c r="G3" s="59" t="s">
+      <c r="G3" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="60" t="s">
+      <c r="H3" s="62" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="35"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="60"/>
+      <c r="A4" s="49"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="62"/>
     </row>
     <row r="5" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
